--- a/output/cyclepapa_risk_reward_workbook.xlsx
+++ b/output/cyclepapa_risk_reward_workbook.xlsx
@@ -6791,7 +6791,7 @@
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
     <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
     <col width="40" customWidth="1" min="4" max="4"/>
     <col width="22" customWidth="1" min="5" max="5"/>
     <col width="8" customWidth="1" min="6" max="6"/>
@@ -6814,7 +6814,7 @@
     <row r="2" ht="38" customHeight="1">
       <c r="A2" s="7" t="inlineStr">
         <is>
-          <t>Universe coverage: 123 investable names (20 REAL waterfalls · 103 PROXY).  REAL uses the hand-built YAML's bottom-up bear/base/bull. PROXY uses a transparent formula on the universe-screener score + archetype tilt.</t>
+          <t>Universe coverage: 125 investable names (20 REAL waterfalls · 105 PROXY).  REAL uses the hand-built YAML's bottom-up bear/base/bull. PROXY uses a transparent formula on the universe-screener score + archetype tilt.</t>
         </is>
       </c>
     </row>
@@ -7410,29 +7410,29 @@
       <c r="A13" s="9" t="n">
         <v>9</v>
       </c>
-      <c r="B13" s="10" t="inlineStr">
-        <is>
-          <t>REAL</t>
+      <c r="B13" s="15" t="inlineStr">
+        <is>
+          <t>PROXY</t>
         </is>
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>XETR:TKA</t>
+          <t>3544</t>
         </is>
       </c>
       <c r="D13" s="11" t="inlineStr">
         <is>
-          <t>Thyssenkrupp Steel</t>
+          <t>サツドラＨＤ</t>
         </is>
       </c>
       <c r="E13" s="11" t="inlineStr">
         <is>
-          <t>Continental Europe</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="F13" s="11" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="G13" s="11" t="inlineStr">
@@ -7442,32 +7442,32 @@
       </c>
       <c r="H13" s="11" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>A2+C</t>
         </is>
       </c>
       <c r="I13" s="11" t="inlineStr">
         <is>
-          <t>45%</t>
+          <t>29%</t>
         </is>
       </c>
       <c r="J13" s="11" t="inlineStr">
         <is>
-          <t>2.30×</t>
+          <t>2.26×</t>
         </is>
       </c>
       <c r="K13" s="11" t="inlineStr">
         <is>
-          <t>4.20×</t>
+          <t>2.80×</t>
         </is>
       </c>
       <c r="L13" s="11" t="inlineStr">
         <is>
-          <t>2.34×</t>
+          <t>1.93×</t>
         </is>
       </c>
       <c r="M13" s="11" t="inlineStr">
         <is>
-          <t>3.0×</t>
+          <t>3.2×</t>
         </is>
       </c>
     </row>
@@ -7475,29 +7475,29 @@
       <c r="A14" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="B14" s="16" t="inlineStr">
-        <is>
-          <t>REAL</t>
+      <c r="B14" s="13" t="inlineStr">
+        <is>
+          <t>PROXY</t>
         </is>
       </c>
       <c r="C14" s="14" t="inlineStr">
         <is>
-          <t>NGX:GTCO</t>
+          <t>6897</t>
         </is>
       </c>
       <c r="D14" s="14" t="inlineStr">
         <is>
-          <t>GTCO (Guaranty Trust)</t>
+          <t>ツインバード</t>
         </is>
       </c>
       <c r="E14" s="14" t="inlineStr">
         <is>
-          <t>MEA / Frontier</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="F14" s="14" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="G14" s="14" t="inlineStr">
@@ -7507,32 +7507,32 @@
       </c>
       <c r="H14" s="14" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>A2+C</t>
         </is>
       </c>
       <c r="I14" s="14" t="inlineStr">
         <is>
-          <t>40%</t>
+          <t>29%</t>
         </is>
       </c>
       <c r="J14" s="14" t="inlineStr">
         <is>
-          <t>2.10×</t>
+          <t>2.26×</t>
         </is>
       </c>
       <c r="K14" s="14" t="inlineStr">
         <is>
-          <t>3.80×</t>
+          <t>2.80×</t>
         </is>
       </c>
       <c r="L14" s="14" t="inlineStr">
         <is>
-          <t>2.15×</t>
+          <t>1.93×</t>
         </is>
       </c>
       <c r="M14" s="14" t="inlineStr">
         <is>
-          <t>2.9×</t>
+          <t>3.2×</t>
         </is>
       </c>
     </row>
@@ -7540,29 +7540,29 @@
       <c r="A15" s="9" t="n">
         <v>11</v>
       </c>
-      <c r="B15" s="10" t="inlineStr">
-        <is>
-          <t>REAL</t>
+      <c r="B15" s="15" t="inlineStr">
+        <is>
+          <t>PROXY</t>
         </is>
       </c>
       <c r="C15" s="11" t="inlineStr">
         <is>
-          <t>STO:ELUX-B</t>
+          <t>4951</t>
         </is>
       </c>
       <c r="D15" s="11" t="inlineStr">
         <is>
-          <t>AB Electrolux (Series B)</t>
+          <t>エステー</t>
         </is>
       </c>
       <c r="E15" s="11" t="inlineStr">
         <is>
-          <t>Continental Europe</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="F15" s="11" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="G15" s="11" t="inlineStr">
@@ -7572,32 +7572,32 @@
       </c>
       <c r="H15" s="11" t="inlineStr">
         <is>
-          <t>A1+D</t>
+          <t>A2+C</t>
         </is>
       </c>
       <c r="I15" s="11" t="inlineStr">
         <is>
-          <t>45%</t>
+          <t>29%</t>
         </is>
       </c>
       <c r="J15" s="11" t="inlineStr">
         <is>
-          <t>2.20×</t>
+          <t>2.26×</t>
         </is>
       </c>
       <c r="K15" s="11" t="inlineStr">
         <is>
-          <t>4.00×</t>
+          <t>2.80×</t>
         </is>
       </c>
       <c r="L15" s="11" t="inlineStr">
         <is>
-          <t>2.32×</t>
+          <t>1.93×</t>
         </is>
       </c>
       <c r="M15" s="11" t="inlineStr">
         <is>
-          <t>2.9×</t>
+          <t>3.2×</t>
         </is>
       </c>
     </row>
@@ -7605,19 +7605,19 @@
       <c r="A16" s="12" t="n">
         <v>12</v>
       </c>
-      <c r="B16" s="16" t="inlineStr">
-        <is>
-          <t>REAL</t>
+      <c r="B16" s="13" t="inlineStr">
+        <is>
+          <t>PROXY</t>
         </is>
       </c>
       <c r="C16" s="14" t="inlineStr">
         <is>
-          <t>TSE:6305</t>
+          <t>3659</t>
         </is>
       </c>
       <c r="D16" s="14" t="inlineStr">
         <is>
-          <t>Hitachi Construction Machinery</t>
+          <t>ネクソン</t>
         </is>
       </c>
       <c r="E16" s="14" t="inlineStr">
@@ -7627,7 +7627,7 @@
       </c>
       <c r="F16" s="14" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="G16" s="14" t="inlineStr">
@@ -7637,17 +7637,17 @@
       </c>
       <c r="H16" s="14" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>A2+C</t>
         </is>
       </c>
       <c r="I16" s="14" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>29%</t>
         </is>
       </c>
       <c r="J16" s="14" t="inlineStr">
         <is>
-          <t>1.70×</t>
+          <t>2.26×</t>
         </is>
       </c>
       <c r="K16" s="14" t="inlineStr">
@@ -7657,12 +7657,12 @@
       </c>
       <c r="L16" s="14" t="inlineStr">
         <is>
-          <t>1.69×</t>
+          <t>1.93×</t>
         </is>
       </c>
       <c r="M16" s="14" t="inlineStr">
         <is>
-          <t>2.8×</t>
+          <t>3.2×</t>
         </is>
       </c>
     </row>
@@ -7677,22 +7677,22 @@
       </c>
       <c r="C17" s="11" t="inlineStr">
         <is>
-          <t>DFM:DSI</t>
+          <t>XETR:TKA</t>
         </is>
       </c>
       <c r="D17" s="11" t="inlineStr">
         <is>
-          <t>Drake &amp; Scull</t>
+          <t>Thyssenkrupp Steel</t>
         </is>
       </c>
       <c r="E17" s="11" t="inlineStr">
         <is>
-          <t>MEA / Frontier</t>
+          <t>Continental Europe</t>
         </is>
       </c>
       <c r="F17" s="11" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="G17" s="11" t="inlineStr">
@@ -7702,7 +7702,7 @@
       </c>
       <c r="H17" s="11" t="inlineStr">
         <is>
-          <t>A2</t>
+          <t>H</t>
         </is>
       </c>
       <c r="I17" s="11" t="inlineStr">
@@ -7722,12 +7722,12 @@
       </c>
       <c r="L17" s="11" t="inlineStr">
         <is>
-          <t>2.25×</t>
+          <t>2.34×</t>
         </is>
       </c>
       <c r="M17" s="11" t="inlineStr">
         <is>
-          <t>2.8×</t>
+          <t>3.0×</t>
         </is>
       </c>
     </row>
@@ -7742,22 +7742,22 @@
       </c>
       <c r="C18" s="14" t="inlineStr">
         <is>
-          <t>BME:OHLA</t>
+          <t>NGX:GTCO</t>
         </is>
       </c>
       <c r="D18" s="14" t="inlineStr">
         <is>
-          <t>OHLA (former OHL)</t>
+          <t>GTCO (Guaranty Trust)</t>
         </is>
       </c>
       <c r="E18" s="14" t="inlineStr">
         <is>
-          <t>Continental Europe</t>
+          <t>MEA / Frontier</t>
         </is>
       </c>
       <c r="F18" s="14" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="G18" s="14" t="inlineStr">
@@ -7767,32 +7767,32 @@
       </c>
       <c r="H18" s="14" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>G</t>
         </is>
       </c>
       <c r="I18" s="14" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>40%</t>
         </is>
       </c>
       <c r="J18" s="14" t="inlineStr">
         <is>
-          <t>2.40×</t>
+          <t>2.10×</t>
         </is>
       </c>
       <c r="K18" s="14" t="inlineStr">
         <is>
-          <t>4.50×</t>
+          <t>3.80×</t>
         </is>
       </c>
       <c r="L18" s="14" t="inlineStr">
         <is>
-          <t>2.35×</t>
+          <t>2.15×</t>
         </is>
       </c>
       <c r="M18" s="14" t="inlineStr">
         <is>
-          <t>2.7×</t>
+          <t>2.9×</t>
         </is>
       </c>
     </row>
@@ -7807,22 +7807,22 @@
       </c>
       <c r="C19" s="11" t="inlineStr">
         <is>
-          <t>KRX:241560</t>
+          <t>STO:ELUX-B</t>
         </is>
       </c>
       <c r="D19" s="11" t="inlineStr">
         <is>
-          <t>Doosan Bobcat → Doosan Robotics merger</t>
+          <t>AB Electrolux (Series B)</t>
         </is>
       </c>
       <c r="E19" s="11" t="inlineStr">
         <is>
-          <t>Korea</t>
+          <t>Continental Europe</t>
         </is>
       </c>
       <c r="F19" s="11" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="G19" s="11" t="inlineStr">
@@ -7832,32 +7832,32 @@
       </c>
       <c r="H19" s="11" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>A1+D</t>
         </is>
       </c>
       <c r="I19" s="11" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>45%</t>
         </is>
       </c>
       <c r="J19" s="11" t="inlineStr">
         <is>
-          <t>1.70×</t>
+          <t>2.20×</t>
         </is>
       </c>
       <c r="K19" s="11" t="inlineStr">
         <is>
-          <t>2.50×</t>
+          <t>4.00×</t>
         </is>
       </c>
       <c r="L19" s="11" t="inlineStr">
         <is>
-          <t>1.66×</t>
+          <t>2.32×</t>
         </is>
       </c>
       <c r="M19" s="11" t="inlineStr">
         <is>
-          <t>2.7×</t>
+          <t>2.9×</t>
         </is>
       </c>
     </row>
@@ -7872,22 +7872,22 @@
       </c>
       <c r="C20" s="14" t="inlineStr">
         <is>
-          <t>EPA:ETL</t>
+          <t>TSE:6305</t>
         </is>
       </c>
       <c r="D20" s="14" t="inlineStr">
         <is>
-          <t>Eutelsat Communications</t>
+          <t>Hitachi Construction Machinery</t>
         </is>
       </c>
       <c r="E20" s="14" t="inlineStr">
         <is>
-          <t>Continental Europe</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="F20" s="14" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="G20" s="14" t="inlineStr">
@@ -7897,32 +7897,32 @@
       </c>
       <c r="H20" s="14" t="inlineStr">
         <is>
-          <t>A1+F</t>
+          <t>H</t>
         </is>
       </c>
       <c r="I20" s="14" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>25%</t>
         </is>
       </c>
       <c r="J20" s="14" t="inlineStr">
         <is>
-          <t>2.20×</t>
+          <t>1.70×</t>
         </is>
       </c>
       <c r="K20" s="14" t="inlineStr">
         <is>
-          <t>4.50×</t>
+          <t>2.80×</t>
         </is>
       </c>
       <c r="L20" s="14" t="inlineStr">
         <is>
-          <t>2.35×</t>
+          <t>1.69×</t>
         </is>
       </c>
       <c r="M20" s="14" t="inlineStr">
         <is>
-          <t>2.7×</t>
+          <t>2.8×</t>
         </is>
       </c>
     </row>
@@ -7930,29 +7930,29 @@
       <c r="A21" s="9" t="n">
         <v>17</v>
       </c>
-      <c r="B21" s="10" t="inlineStr">
-        <is>
-          <t>REAL</t>
+      <c r="B21" s="15" t="inlineStr">
+        <is>
+          <t>PROXY</t>
         </is>
       </c>
       <c r="C21" s="11" t="inlineStr">
         <is>
-          <t>BME:SAB</t>
+          <t>8074</t>
         </is>
       </c>
       <c r="D21" s="11" t="inlineStr">
         <is>
-          <t>Banco Sabadell</t>
+          <t>ＹＵＡＳＡ</t>
         </is>
       </c>
       <c r="E21" s="11" t="inlineStr">
         <is>
-          <t>Continental Europe</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="F21" s="11" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="G21" s="11" t="inlineStr">
@@ -7962,32 +7962,32 @@
       </c>
       <c r="H21" s="11" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2</t>
         </is>
       </c>
       <c r="I21" s="11" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>31%</t>
         </is>
       </c>
       <c r="J21" s="11" t="inlineStr">
         <is>
-          <t>1.65×</t>
+          <t>2.19×</t>
         </is>
       </c>
       <c r="K21" s="11" t="inlineStr">
         <is>
-          <t>2.40×</t>
+          <t>2.69×</t>
         </is>
       </c>
       <c r="L21" s="11" t="inlineStr">
         <is>
-          <t>1.66×</t>
+          <t>1.86×</t>
         </is>
       </c>
       <c r="M21" s="11" t="inlineStr">
         <is>
-          <t>2.6×</t>
+          <t>2.8×</t>
         </is>
       </c>
     </row>
@@ -8002,22 +8002,22 @@
       </c>
       <c r="C22" s="14" t="inlineStr">
         <is>
-          <t>BME:TLGO</t>
+          <t>2198</t>
         </is>
       </c>
       <c r="D22" s="14" t="inlineStr">
         <is>
-          <t>Talgo</t>
+          <t>アイ・ケイ・ケイＨＤ</t>
         </is>
       </c>
       <c r="E22" s="14" t="inlineStr">
         <is>
-          <t>Continental Europe</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="F22" s="14" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="G22" s="14" t="inlineStr">
@@ -8027,32 +8027,32 @@
       </c>
       <c r="H22" s="14" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2</t>
         </is>
       </c>
       <c r="I22" s="14" t="inlineStr">
         <is>
-          <t>32%</t>
+          <t>31%</t>
         </is>
       </c>
       <c r="J22" s="14" t="inlineStr">
         <is>
-          <t>2.16×</t>
+          <t>2.19×</t>
         </is>
       </c>
       <c r="K22" s="14" t="inlineStr">
         <is>
-          <t>2.64×</t>
+          <t>2.69×</t>
         </is>
       </c>
       <c r="L22" s="14" t="inlineStr">
         <is>
-          <t>1.84×</t>
+          <t>1.86×</t>
         </is>
       </c>
       <c r="M22" s="14" t="inlineStr">
         <is>
-          <t>2.6×</t>
+          <t>2.8×</t>
         </is>
       </c>
     </row>
@@ -8060,29 +8060,29 @@
       <c r="A23" s="9" t="n">
         <v>19</v>
       </c>
-      <c r="B23" s="10" t="inlineStr">
-        <is>
-          <t>REAL</t>
+      <c r="B23" s="15" t="inlineStr">
+        <is>
+          <t>PROXY</t>
         </is>
       </c>
       <c r="C23" s="11" t="inlineStr">
         <is>
-          <t>NYSE:YPF</t>
+          <t>3454</t>
         </is>
       </c>
       <c r="D23" s="11" t="inlineStr">
         <is>
-          <t>YPF</t>
+          <t>ファーストブラザーズ</t>
         </is>
       </c>
       <c r="E23" s="11" t="inlineStr">
         <is>
-          <t>Latin America</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="F23" s="11" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="G23" s="11" t="inlineStr">
@@ -8092,32 +8092,32 @@
       </c>
       <c r="H23" s="11" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2</t>
         </is>
       </c>
       <c r="I23" s="11" t="inlineStr">
         <is>
-          <t>35%</t>
+          <t>31%</t>
         </is>
       </c>
       <c r="J23" s="11" t="inlineStr">
         <is>
-          <t>1.80×</t>
+          <t>2.19×</t>
         </is>
       </c>
       <c r="K23" s="11" t="inlineStr">
         <is>
-          <t>3.20×</t>
+          <t>2.69×</t>
         </is>
       </c>
       <c r="L23" s="11" t="inlineStr">
         <is>
-          <t>1.92×</t>
+          <t>1.86×</t>
         </is>
       </c>
       <c r="M23" s="11" t="inlineStr">
         <is>
-          <t>2.6×</t>
+          <t>2.8×</t>
         </is>
       </c>
     </row>
@@ -8132,22 +8132,22 @@
       </c>
       <c r="C24" s="14" t="inlineStr">
         <is>
-          <t>LSE:ASC</t>
+          <t>3803</t>
         </is>
       </c>
       <c r="D24" s="14" t="inlineStr">
         <is>
-          <t>ASOS</t>
+          <t>Ｇ－イメージ情</t>
         </is>
       </c>
       <c r="E24" s="14" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="F24" s="14" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="G24" s="14" t="inlineStr">
@@ -8157,32 +8157,32 @@
       </c>
       <c r="H24" s="14" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2</t>
         </is>
       </c>
       <c r="I24" s="14" t="inlineStr">
         <is>
-          <t>32%</t>
+          <t>31%</t>
         </is>
       </c>
       <c r="J24" s="14" t="inlineStr">
         <is>
-          <t>2.16×</t>
+          <t>2.19×</t>
         </is>
       </c>
       <c r="K24" s="14" t="inlineStr">
         <is>
-          <t>2.64×</t>
+          <t>2.69×</t>
         </is>
       </c>
       <c r="L24" s="14" t="inlineStr">
         <is>
-          <t>1.84×</t>
+          <t>1.86×</t>
         </is>
       </c>
       <c r="M24" s="14" t="inlineStr">
         <is>
-          <t>2.6×</t>
+          <t>2.8×</t>
         </is>
       </c>
     </row>
@@ -8190,29 +8190,29 @@
       <c r="A25" s="9" t="n">
         <v>21</v>
       </c>
-      <c r="B25" s="10" t="inlineStr">
-        <is>
-          <t>REAL</t>
+      <c r="B25" s="15" t="inlineStr">
+        <is>
+          <t>PROXY</t>
         </is>
       </c>
       <c r="C25" s="11" t="inlineStr">
         <is>
-          <t>LSE:DRX</t>
+          <t>4641</t>
         </is>
       </c>
       <c r="D25" s="11" t="inlineStr">
         <is>
-          <t>Drax Group</t>
+          <t>アルプス技</t>
         </is>
       </c>
       <c r="E25" s="11" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="F25" s="11" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="G25" s="11" t="inlineStr">
@@ -8222,32 +8222,32 @@
       </c>
       <c r="H25" s="11" t="inlineStr">
         <is>
-          <t>A1+G</t>
+          <t>A2</t>
         </is>
       </c>
       <c r="I25" s="11" t="inlineStr">
         <is>
-          <t>55%</t>
+          <t>31%</t>
         </is>
       </c>
       <c r="J25" s="11" t="inlineStr">
         <is>
-          <t>2.20×</t>
+          <t>2.19×</t>
         </is>
       </c>
       <c r="K25" s="11" t="inlineStr">
         <is>
-          <t>4.50×</t>
+          <t>2.69×</t>
         </is>
       </c>
       <c r="L25" s="11" t="inlineStr">
         <is>
-          <t>2.45×</t>
+          <t>1.86×</t>
         </is>
       </c>
       <c r="M25" s="11" t="inlineStr">
         <is>
-          <t>2.6×</t>
+          <t>2.8×</t>
         </is>
       </c>
     </row>
@@ -8255,29 +8255,29 @@
       <c r="A26" s="12" t="n">
         <v>22</v>
       </c>
-      <c r="B26" s="16" t="inlineStr">
-        <is>
-          <t>REAL</t>
+      <c r="B26" s="13" t="inlineStr">
+        <is>
+          <t>PROXY</t>
         </is>
       </c>
       <c r="C26" s="14" t="inlineStr">
         <is>
-          <t>NASDAQ:UREE</t>
+          <t>4170</t>
         </is>
       </c>
       <c r="D26" s="14" t="inlineStr">
         <is>
-          <t>USA Rare Earth</t>
+          <t>Ｇ－ＫａｉｚｅｎＰＦ</t>
         </is>
       </c>
       <c r="E26" s="14" t="inlineStr">
         <is>
-          <t>United States/Canada</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="F26" s="14" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="G26" s="14" t="inlineStr">
@@ -8292,27 +8292,27 @@
       </c>
       <c r="I26" s="14" t="inlineStr">
         <is>
-          <t>65%</t>
+          <t>31%</t>
         </is>
       </c>
       <c r="J26" s="14" t="inlineStr">
         <is>
-          <t>2.50×</t>
+          <t>2.19×</t>
         </is>
       </c>
       <c r="K26" s="14" t="inlineStr">
         <is>
-          <t>5.50×</t>
+          <t>2.69×</t>
         </is>
       </c>
       <c r="L26" s="14" t="inlineStr">
         <is>
-          <t>2.71×</t>
+          <t>1.86×</t>
         </is>
       </c>
       <c r="M26" s="14" t="inlineStr">
         <is>
-          <t>2.6×</t>
+          <t>2.8×</t>
         </is>
       </c>
     </row>
@@ -8320,29 +8320,29 @@
       <c r="A27" s="9" t="n">
         <v>23</v>
       </c>
-      <c r="B27" s="15" t="inlineStr">
-        <is>
-          <t>PROXY</t>
+      <c r="B27" s="10" t="inlineStr">
+        <is>
+          <t>REAL</t>
         </is>
       </c>
       <c r="C27" s="11" t="inlineStr">
         <is>
-          <t>TSX:CFW</t>
+          <t>DFM:DSI</t>
         </is>
       </c>
       <c r="D27" s="11" t="inlineStr">
         <is>
-          <t>Calfrac Well Services</t>
+          <t>Drake &amp; Scull</t>
         </is>
       </c>
       <c r="E27" s="11" t="inlineStr">
         <is>
-          <t>United States/Canada</t>
+          <t>MEA / Frontier</t>
         </is>
       </c>
       <c r="F27" s="11" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="G27" s="11" t="inlineStr">
@@ -8352,32 +8352,32 @@
       </c>
       <c r="H27" s="11" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2</t>
         </is>
       </c>
       <c r="I27" s="11" t="inlineStr">
         <is>
-          <t>32%</t>
+          <t>45%</t>
         </is>
       </c>
       <c r="J27" s="11" t="inlineStr">
         <is>
-          <t>2.14×</t>
+          <t>2.30×</t>
         </is>
       </c>
       <c r="K27" s="11" t="inlineStr">
         <is>
-          <t>2.59×</t>
+          <t>4.20×</t>
         </is>
       </c>
       <c r="L27" s="11" t="inlineStr">
         <is>
-          <t>1.81×</t>
+          <t>2.25×</t>
         </is>
       </c>
       <c r="M27" s="11" t="inlineStr">
         <is>
-          <t>2.5×</t>
+          <t>2.8×</t>
         </is>
       </c>
     </row>
@@ -8385,29 +8385,29 @@
       <c r="A28" s="12" t="n">
         <v>24</v>
       </c>
-      <c r="B28" s="13" t="inlineStr">
-        <is>
-          <t>PROXY</t>
+      <c r="B28" s="16" t="inlineStr">
+        <is>
+          <t>REAL</t>
         </is>
       </c>
       <c r="C28" s="14" t="inlineStr">
         <is>
-          <t>KRX:028260</t>
+          <t>BME:OHLA</t>
         </is>
       </c>
       <c r="D28" s="14" t="inlineStr">
         <is>
-          <t>Samsung C&amp;T</t>
+          <t>OHLA (former OHL)</t>
         </is>
       </c>
       <c r="E28" s="14" t="inlineStr">
         <is>
-          <t>Korea</t>
+          <t>Continental Europe</t>
         </is>
       </c>
       <c r="F28" s="14" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="G28" s="14" t="inlineStr">
@@ -8417,32 +8417,32 @@
       </c>
       <c r="H28" s="14" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>A1</t>
         </is>
       </c>
       <c r="I28" s="14" t="inlineStr">
         <is>
-          <t>40%</t>
+          <t>50%</t>
         </is>
       </c>
       <c r="J28" s="14" t="inlineStr">
         <is>
-          <t>2.30×</t>
+          <t>2.40×</t>
         </is>
       </c>
       <c r="K28" s="14" t="inlineStr">
         <is>
-          <t>3.00×</t>
+          <t>4.50×</t>
         </is>
       </c>
       <c r="L28" s="14" t="inlineStr">
         <is>
-          <t>1.96×</t>
+          <t>2.35×</t>
         </is>
       </c>
       <c r="M28" s="14" t="inlineStr">
         <is>
-          <t>2.4×</t>
+          <t>2.7×</t>
         </is>
       </c>
     </row>
@@ -8450,29 +8450,29 @@
       <c r="A29" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="B29" s="15" t="inlineStr">
-        <is>
-          <t>PROXY</t>
+      <c r="B29" s="10" t="inlineStr">
+        <is>
+          <t>REAL</t>
         </is>
       </c>
       <c r="C29" s="11" t="inlineStr">
         <is>
-          <t>LSE:AML</t>
+          <t>KRX:241560</t>
         </is>
       </c>
       <c r="D29" s="11" t="inlineStr">
         <is>
-          <t>Aston Martin Lagonda</t>
+          <t>Doosan Bobcat → Doosan Robotics merger</t>
         </is>
       </c>
       <c r="E29" s="11" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Korea</t>
         </is>
       </c>
       <c r="F29" s="11" t="inlineStr">
         <is>
-          <t>0.70</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="G29" s="11" t="inlineStr">
@@ -8482,32 +8482,32 @@
       </c>
       <c r="H29" s="11" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>H</t>
         </is>
       </c>
       <c r="I29" s="11" t="inlineStr">
         <is>
-          <t>33%</t>
+          <t>25%</t>
         </is>
       </c>
       <c r="J29" s="11" t="inlineStr">
         <is>
-          <t>2.11×</t>
+          <t>1.70×</t>
         </is>
       </c>
       <c r="K29" s="11" t="inlineStr">
         <is>
-          <t>2.55×</t>
+          <t>2.50×</t>
         </is>
       </c>
       <c r="L29" s="11" t="inlineStr">
         <is>
-          <t>1.79×</t>
+          <t>1.66×</t>
         </is>
       </c>
       <c r="M29" s="11" t="inlineStr">
         <is>
-          <t>2.4×</t>
+          <t>2.7×</t>
         </is>
       </c>
     </row>
@@ -8550,7 +8550,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
     <col width="37" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
     <col width="8" customWidth="1" min="5" max="5"/>
@@ -8818,156 +8818,156 @@
     </row>
     <row r="10">
       <c r="A10" s="12" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>BME:TLGO</t>
+          <t>3544</t>
         </is>
       </c>
       <c r="C10" s="14" t="inlineStr">
         <is>
-          <t>Talgo</t>
+          <t>サツドラＨＤ</t>
         </is>
       </c>
       <c r="D10" s="14" t="inlineStr">
         <is>
-          <t>Continental Europe</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="E10" s="14" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="F10" s="14" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2+C</t>
         </is>
       </c>
       <c r="G10" s="14" t="inlineStr">
         <is>
-          <t>2.6×</t>
+          <t>3.2×</t>
         </is>
       </c>
       <c r="H10" s="14" t="inlineStr">
         <is>
-          <t>Tier 2 — verify primary docs first</t>
+          <t>Tier 1 — hand-deepen ASAP</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="9" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>LSE:ASC</t>
+          <t>6897</t>
         </is>
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>ASOS</t>
+          <t>ツインバード</t>
         </is>
       </c>
       <c r="D11" s="11" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="E11" s="11" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="F11" s="11" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2+C</t>
         </is>
       </c>
       <c r="G11" s="11" t="inlineStr">
         <is>
-          <t>2.6×</t>
+          <t>3.2×</t>
         </is>
       </c>
       <c r="H11" s="11" t="inlineStr">
         <is>
-          <t>Tier 2 — verify primary docs first</t>
+          <t>Tier 1 — hand-deepen ASAP</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="12" t="n">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="B12" s="14" t="inlineStr">
         <is>
-          <t>TSX:CFW</t>
+          <t>4951</t>
         </is>
       </c>
       <c r="C12" s="14" t="inlineStr">
         <is>
-          <t>Calfrac Well Services</t>
+          <t>エステー</t>
         </is>
       </c>
       <c r="D12" s="14" t="inlineStr">
         <is>
-          <t>United States/Canada</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="E12" s="14" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="F12" s="14" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2+C</t>
         </is>
       </c>
       <c r="G12" s="14" t="inlineStr">
         <is>
-          <t>2.5×</t>
+          <t>3.2×</t>
         </is>
       </c>
       <c r="H12" s="14" t="inlineStr">
         <is>
-          <t>Tier 2 — verify primary docs first</t>
+          <t>Tier 1 — hand-deepen ASAP</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="9" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>KRX:028260</t>
+          <t>3659</t>
         </is>
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>Samsung C&amp;T</t>
+          <t>ネクソン</t>
         </is>
       </c>
       <c r="D13" s="11" t="inlineStr">
         <is>
-          <t>Korea</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="E13" s="11" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="F13" s="11" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>A2+C</t>
         </is>
       </c>
       <c r="G13" s="11" t="inlineStr">
         <is>
-          <t>2.4×</t>
+          <t>3.2×</t>
         </is>
       </c>
       <c r="H13" s="11" t="inlineStr">
@@ -8978,36 +8978,36 @@
     </row>
     <row r="14">
       <c r="A14" s="12" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="B14" s="14" t="inlineStr">
         <is>
-          <t>LSE:AML</t>
+          <t>8074</t>
         </is>
       </c>
       <c r="C14" s="14" t="inlineStr">
         <is>
-          <t>Aston Martin Lagonda</t>
+          <t>ＹＵＡＳＡ</t>
         </is>
       </c>
       <c r="D14" s="14" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="E14" s="14" t="inlineStr">
         <is>
-          <t>0.70</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="F14" s="14" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2</t>
         </is>
       </c>
       <c r="G14" s="14" t="inlineStr">
         <is>
-          <t>2.4×</t>
+          <t>2.8×</t>
         </is>
       </c>
       <c r="H14" s="14" t="inlineStr">
@@ -9018,36 +9018,36 @@
     </row>
     <row r="15">
       <c r="A15" s="9" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>HK:2202</t>
+          <t>2198</t>
         </is>
       </c>
       <c r="C15" s="11" t="inlineStr">
         <is>
-          <t>Vanke</t>
+          <t>アイ・ケイ・ケイＨＤ</t>
         </is>
       </c>
       <c r="D15" s="11" t="inlineStr">
         <is>
-          <t>Greater China / HK</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="E15" s="11" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="F15" s="11" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2</t>
         </is>
       </c>
       <c r="G15" s="11" t="inlineStr">
         <is>
-          <t>2.3×</t>
+          <t>2.8×</t>
         </is>
       </c>
       <c r="H15" s="11" t="inlineStr">
@@ -9058,36 +9058,36 @@
     </row>
     <row r="16">
       <c r="A16" s="12" t="n">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="B16" s="14" t="inlineStr">
         <is>
-          <t>LSE:VOD</t>
+          <t>3454</t>
         </is>
       </c>
       <c r="C16" s="14" t="inlineStr">
         <is>
-          <t>Vodafone</t>
+          <t>ファーストブラザーズ</t>
         </is>
       </c>
       <c r="D16" s="14" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="E16" s="14" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="F16" s="14" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2</t>
         </is>
       </c>
       <c r="G16" s="14" t="inlineStr">
         <is>
-          <t>2.3×</t>
+          <t>2.8×</t>
         </is>
       </c>
       <c r="H16" s="14" t="inlineStr">
@@ -9098,36 +9098,36 @@
     </row>
     <row r="17">
       <c r="A17" s="9" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>LSE:TLW</t>
+          <t>3803</t>
         </is>
       </c>
       <c r="C17" s="11" t="inlineStr">
         <is>
-          <t>Tullow Oil</t>
+          <t>Ｇ－イメージ情</t>
         </is>
       </c>
       <c r="D17" s="11" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="E17" s="11" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="F17" s="11" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2</t>
         </is>
       </c>
       <c r="G17" s="11" t="inlineStr">
         <is>
-          <t>2.3×</t>
+          <t>2.8×</t>
         </is>
       </c>
       <c r="H17" s="11" t="inlineStr">
@@ -9138,36 +9138,36 @@
     </row>
     <row r="18">
       <c r="A18" s="12" t="n">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="B18" s="14" t="inlineStr">
         <is>
-          <t>NYSE:FFWM</t>
+          <t>4641</t>
         </is>
       </c>
       <c r="C18" s="14" t="inlineStr">
         <is>
-          <t>First Foundation</t>
+          <t>アルプス技</t>
         </is>
       </c>
       <c r="D18" s="14" t="inlineStr">
         <is>
-          <t>United States/Canada</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="E18" s="14" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="F18" s="14" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2</t>
         </is>
       </c>
       <c r="G18" s="14" t="inlineStr">
         <is>
-          <t>2.3×</t>
+          <t>2.8×</t>
         </is>
       </c>
       <c r="H18" s="14" t="inlineStr">
@@ -9178,16 +9178,16 @@
     </row>
     <row r="19">
       <c r="A19" s="9" t="n">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>TSE:8304</t>
+          <t>4170</t>
         </is>
       </c>
       <c r="C19" s="11" t="inlineStr">
         <is>
-          <t>Aozora Bank</t>
+          <t>Ｇ－ＫａｉｚｅｎＰＦ</t>
         </is>
       </c>
       <c r="D19" s="11" t="inlineStr">
@@ -9197,17 +9197,17 @@
       </c>
       <c r="E19" s="11" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="F19" s="11" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>A2</t>
         </is>
       </c>
       <c r="G19" s="11" t="inlineStr">
         <is>
-          <t>2.1×</t>
+          <t>2.8×</t>
         </is>
       </c>
       <c r="H19" s="11" t="inlineStr">
@@ -9218,16 +9218,16 @@
     </row>
     <row r="20">
       <c r="A20" s="12" t="n">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="B20" s="14" t="inlineStr">
         <is>
-          <t>XETR:TUI1</t>
+          <t>BME:TLGO</t>
         </is>
       </c>
       <c r="C20" s="14" t="inlineStr">
         <is>
-          <t>Tui AG</t>
+          <t>Talgo</t>
         </is>
       </c>
       <c r="D20" s="14" t="inlineStr">
@@ -9237,17 +9237,17 @@
       </c>
       <c r="E20" s="14" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="F20" s="14" t="inlineStr">
         <is>
-          <t>A2</t>
+          <t>A1</t>
         </is>
       </c>
       <c r="G20" s="14" t="inlineStr">
         <is>
-          <t>2.0×</t>
+          <t>2.6×</t>
         </is>
       </c>
       <c r="H20" s="14" t="inlineStr">
@@ -9258,16 +9258,16 @@
     </row>
     <row r="21">
       <c r="A21" s="9" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t>LSE:PDL</t>
+          <t>LSE:ASC</t>
         </is>
       </c>
       <c r="C21" s="11" t="inlineStr">
         <is>
-          <t>Petra Diamonds</t>
+          <t>ASOS</t>
         </is>
       </c>
       <c r="D21" s="11" t="inlineStr">
@@ -9277,7 +9277,7 @@
       </c>
       <c r="E21" s="11" t="inlineStr">
         <is>
-          <t>0.60</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="F21" s="11" t="inlineStr">
@@ -9287,7 +9287,7 @@
       </c>
       <c r="G21" s="11" t="inlineStr">
         <is>
-          <t>2.0×</t>
+          <t>2.6×</t>
         </is>
       </c>
       <c r="H21" s="11" t="inlineStr">
@@ -9298,36 +9298,36 @@
     </row>
     <row r="22">
       <c r="A22" s="12" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="B22" s="14" t="inlineStr">
         <is>
-          <t>NYSE:AENZ</t>
+          <t>TSX:CFW</t>
         </is>
       </c>
       <c r="C22" s="14" t="inlineStr">
         <is>
-          <t>Aenza (former Graña y Montero)</t>
+          <t>Calfrac Well Services</t>
         </is>
       </c>
       <c r="D22" s="14" t="inlineStr">
         <is>
-          <t>Continental Europe</t>
+          <t>United States/Canada</t>
         </is>
       </c>
       <c r="E22" s="14" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="F22" s="14" t="inlineStr">
         <is>
-          <t>A2</t>
+          <t>A1</t>
         </is>
       </c>
       <c r="G22" s="14" t="inlineStr">
         <is>
-          <t>1.9×</t>
+          <t>2.5×</t>
         </is>
       </c>
       <c r="H22" s="14" t="inlineStr">
@@ -9338,16 +9338,16 @@
     </row>
     <row r="23">
       <c r="A23" s="9" t="n">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="B23" s="11" t="inlineStr">
         <is>
-          <t>KRX:034730</t>
+          <t>KRX:028260</t>
         </is>
       </c>
       <c r="C23" s="11" t="inlineStr">
         <is>
-          <t>SK Inc</t>
+          <t>Samsung C&amp;T</t>
         </is>
       </c>
       <c r="D23" s="11" t="inlineStr">
@@ -9357,7 +9357,7 @@
       </c>
       <c r="E23" s="11" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="F23" s="11" t="inlineStr">
@@ -9367,47 +9367,47 @@
       </c>
       <c r="G23" s="11" t="inlineStr">
         <is>
-          <t>1.9×</t>
+          <t>2.4×</t>
         </is>
       </c>
       <c r="H23" s="11" t="inlineStr">
         <is>
-          <t>Tier 2 — verify primary docs first</t>
+          <t>Tier 1 — hand-deepen ASAP</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="12" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="B24" s="14" t="inlineStr">
         <is>
-          <t>NGX:ZENITHBANK</t>
+          <t>LSE:AML</t>
         </is>
       </c>
       <c r="C24" s="14" t="inlineStr">
         <is>
-          <t>Zenith Bank</t>
+          <t>Aston Martin Lagonda</t>
         </is>
       </c>
       <c r="D24" s="14" t="inlineStr">
         <is>
-          <t>MEA / Frontier</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="E24" s="14" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="F24" s="14" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>A1</t>
         </is>
       </c>
       <c r="G24" s="14" t="inlineStr">
         <is>
-          <t>1.9×</t>
+          <t>2.4×</t>
         </is>
       </c>
       <c r="H24" s="14" t="inlineStr">

--- a/output/cyclepapa_risk_reward_workbook.xlsx
+++ b/output/cyclepapa_risk_reward_workbook.xlsx
@@ -608,7 +608,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Generated 2026-06-20</t>
+          <t>Generated 2026-06-21</t>
         </is>
       </c>
     </row>
@@ -6814,7 +6814,7 @@
     <row r="2" ht="38" customHeight="1">
       <c r="A2" s="7" t="inlineStr">
         <is>
-          <t>Universe coverage: 125 investable names (20 REAL waterfalls · 105 PROXY).  REAL uses the hand-built YAML's bottom-up bear/base/bull. PROXY uses a transparent formula on the universe-screener score + archetype tilt.</t>
+          <t>Universe coverage: 126 investable names (21 REAL waterfalls · 105 PROXY).  REAL uses the hand-built YAML's bottom-up bear/base/bull. PROXY uses a transparent formula on the universe-screener score + archetype tilt.</t>
         </is>
       </c>
     </row>
@@ -9218,7 +9218,7 @@
     </row>
     <row r="20">
       <c r="A20" s="12" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B20" s="14" t="inlineStr">
         <is>
@@ -9258,7 +9258,7 @@
     </row>
     <row r="21">
       <c r="A21" s="9" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
@@ -9298,7 +9298,7 @@
     </row>
     <row r="22">
       <c r="A22" s="12" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B22" s="14" t="inlineStr">
         <is>
@@ -9338,7 +9338,7 @@
     </row>
     <row r="23">
       <c r="A23" s="9" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B23" s="11" t="inlineStr">
         <is>
@@ -9378,7 +9378,7 @@
     </row>
     <row r="24">
       <c r="A24" s="12" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B24" s="14" t="inlineStr">
         <is>

--- a/output/cyclepapa_risk_reward_workbook.xlsx
+++ b/output/cyclepapa_risk_reward_workbook.xlsx
@@ -22,10 +22,7 @@
     <sheet name="GTCO" sheetId="13" state="visible" r:id="rId13"/>
     <sheet name="ELUX-B" sheetId="14" state="visible" r:id="rId14"/>
     <sheet name="6305" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="DSI" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="OHLA" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet name="241560" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet name="Methodology" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="Methodology" sheetId="16" state="visible" r:id="rId16"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -4841,1815 +4838,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D53"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="60" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Drake &amp; Scull International</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>DSI  ·  AE  ·  Bucket A  ·  Archetype E  ·  Tier 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>Risk-reward snapshot</t>
-        </is>
-      </c>
-      <c r="B4" s="19" t="n"/>
-      <c r="C4" s="19" t="n"/>
-      <c r="D4" s="19" t="n"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="20" t="inlineStr">
-        <is>
-          <t>Expected EV×</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>2.25×</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="20" t="inlineStr">
-        <is>
-          <t>Bear / Base / Bull return</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t>0.55× / 2.30× / 4.20×</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="20" t="inlineStr">
-        <is>
-          <t>Bear loss</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>45%</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="20" t="inlineStr">
-        <is>
-          <t>Skew (upside/downside)</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>7.1×</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="20" t="inlineStr">
-        <is>
-          <t>Reward/Risk ratio</t>
-        </is>
-      </c>
-      <c r="B9" s="5" t="inlineStr">
-        <is>
-          <t>2.8×</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="20" t="inlineStr">
-        <is>
-          <t>Portfolio weight</t>
-        </is>
-      </c>
-      <c r="B10" s="5" t="inlineStr">
-        <is>
-          <t>3.00%</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="20" t="inlineStr">
-        <is>
-          <t>Cluster</t>
-        </is>
-      </c>
-      <c r="B11" s="5" t="inlineStr">
-        <is>
-          <t>EM_bank</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="20" t="inlineStr">
-        <is>
-          <t>Primary factor</t>
-        </is>
-      </c>
-      <c r="B12" s="5" t="inlineStr">
-        <is>
-          <t>idiosyncratic</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t>Deal</t>
-        </is>
-      </c>
-      <c r="B14" s="19" t="n"/>
-      <c r="C14" s="19" t="n"/>
-      <c r="D14" s="19" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="20" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="B15" s="5" t="inlineStr">
-        <is>
-          <t>2024-04-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="20" t="inlineStr">
-        <is>
-          <t>Mechanic</t>
-        </is>
-      </c>
-      <c r="B16" s="5" t="inlineStr">
-        <is>
-          <t>E — UAE-equivalent restructuring with capital restoration. April 2024: AED 4.18bn debt write-off (90pct); AED 600m mandatory convertible sukuk issued; AED 800m capital reduction. Tabarak Investment (strategic since 2017) increased stake. Trading resumed May 2024 after 5-year halt. CEO Mansour Lootah leading recovery.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="4" t="inlineStr">
-        <is>
-          <t>Scorecard</t>
-        </is>
-      </c>
-      <c r="B18" s="19" t="n"/>
-      <c r="C18" s="19" t="n"/>
-      <c r="D18" s="19" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="20" t="inlineStr">
-        <is>
-          <t>D4 Dilution Pct</t>
-        </is>
-      </c>
-      <c r="B19" s="5" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="20" t="inlineStr">
-        <is>
-          <t>D9 Alignment Gap</t>
-        </is>
-      </c>
-      <c r="B20" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="20" t="inlineStr">
-        <is>
-          <t>D11 Consensus Ebitda Cagr</t>
-        </is>
-      </c>
-      <c r="B21" s="5" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="20" t="inlineStr">
-        <is>
-          <t>D14 Liquidity Quarters</t>
-        </is>
-      </c>
-      <c r="B22" s="5" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="4" t="inlineStr">
-        <is>
-          <t>Catalysts</t>
-        </is>
-      </c>
-      <c r="B24" s="19" t="n"/>
-      <c r="C24" s="19" t="n"/>
-      <c r="D24" s="19" t="n"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="8" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B25" s="8" t="inlineStr">
-        <is>
-          <t>Window</t>
-        </is>
-      </c>
-      <c r="C25" s="8" t="inlineStr">
-        <is>
-          <t>P(yes)</t>
-        </is>
-      </c>
-      <c r="D25" s="8" t="inlineStr">
-        <is>
-          <t>Re-rate if yes / hit if no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="32" customHeight="1">
-      <c r="A26" s="21" t="inlineStr">
-        <is>
-          <t>Backlog rebuild (UAE/GCC infrastructure pipeline)</t>
-        </is>
-      </c>
-      <c r="B26" s="11" t="inlineStr">
-        <is>
-          <t>2026-06-01 → 2028-06-30</t>
-        </is>
-      </c>
-      <c r="C26" s="11" t="inlineStr">
-        <is>
-          <t>0.55</t>
-        </is>
-      </c>
-      <c r="D26" s="11" t="inlineStr">
-        <is>
-          <t>Up 1.8-2.5× / Down -0.2--0.3</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="32" customHeight="1">
-      <c r="A27" s="22" t="inlineStr">
-        <is>
-          <t>Convertible sukuk conversion + capital structure simplification</t>
-        </is>
-      </c>
-      <c r="B27" s="14" t="inlineStr">
-        <is>
-          <t>2026-09-01 → 2027-12-31</t>
-        </is>
-      </c>
-      <c r="C27" s="14" t="inlineStr">
-        <is>
-          <t>0.55</t>
-        </is>
-      </c>
-      <c r="D27" s="14" t="inlineStr">
-        <is>
-          <t>Up 1.3-1.6× / Down -0.1--0.15</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="32" customHeight="1">
-      <c r="A28" s="21" t="inlineStr">
-        <is>
-          <t>Tabarak strategic-buyer follow-on or international JV partner</t>
-        </is>
-      </c>
-      <c r="B28" s="11" t="inlineStr">
-        <is>
-          <t>2026-09-01 → 2028-12-31</t>
-        </is>
-      </c>
-      <c r="C28" s="11" t="inlineStr">
-        <is>
-          <t>0.4</t>
-        </is>
-      </c>
-      <c r="D28" s="11" t="inlineStr">
-        <is>
-          <t>Up 1.8-2.5× / Down -0.05--0.1</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="4" t="inlineStr">
-        <is>
-          <t>Triangulation (3-leg test)</t>
-        </is>
-      </c>
-      <c r="B30" s="19" t="n"/>
-      <c r="C30" s="19" t="n"/>
-      <c r="D30" s="19" t="n"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="20" t="inlineStr">
-        <is>
-          <t>Leg 1 — Valuation</t>
-        </is>
-      </c>
-      <c r="B31" s="5" t="inlineStr">
-        <is>
-          <t>partial</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="20" t="inlineStr">
-        <is>
-          <t>Leg 2 — Game theory</t>
-        </is>
-      </c>
-      <c r="B32" s="5" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="20" t="inlineStr">
-        <is>
-          <t>Leg 3 — Revealed preference</t>
-        </is>
-      </c>
-      <c r="B33" s="5" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="20" t="inlineStr">
-        <is>
-          <t>Notes</t>
-        </is>
-      </c>
-      <c r="B34" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Leg 1: Post-recap cap structure clean; 90pct of legacy debt
-written off creates large operating leverage to backlog
-rebuild. But absolute valuation tough without normalised
-EBITDA reference.
-Leg 2: Tabarak in since 2017 = patient anchor + UAE
-sovereign-adjacent capital base.
-Leg 3: AED 4.18bn debt forgiveness = creditor revealed
-preference for survival over liquidation.
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="4" t="inlineStr">
-        <is>
-          <t>Anchor</t>
-        </is>
-      </c>
-      <c r="B36" s="19" t="n"/>
-      <c r="C36" s="19" t="n"/>
-      <c r="D36" s="19" t="n"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="20" t="inlineStr">
-        <is>
-          <t>Parties</t>
-        </is>
-      </c>
-      <c r="B37" s="5" t="inlineStr">
-        <is>
-          <t>Tabarak Investment (strategic anchor 2017+)</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="20" t="inlineStr">
-        <is>
-          <t>Stake (% est.)</t>
-        </is>
-      </c>
-      <c r="B38" s="5" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="4" t="inlineStr">
-        <is>
-          <t>Red flags</t>
-        </is>
-      </c>
-      <c r="B40" s="19" t="n"/>
-      <c r="C40" s="19" t="n"/>
-      <c r="D40" s="19" t="n"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="20" t="inlineStr">
-        <is>
-          <t>Triggered</t>
-        </is>
-      </c>
-      <c r="B41" s="5" t="inlineStr">
-        <is>
-          <t>None of 11 active</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="20" t="inlineStr">
-        <is>
-          <t>Watch list</t>
-        </is>
-      </c>
-      <c r="B42" s="5" t="inlineStr">
-        <is>
-          <t>5-year trading halt history; legacy litigation overhang; limited float</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="4" t="inlineStr">
-        <is>
-          <t>Kill criteria</t>
-        </is>
-      </c>
-      <c r="B44" s="19" t="n"/>
-      <c r="C44" s="19" t="n"/>
-      <c r="D44" s="19" t="n"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="20" t="inlineStr">
-        <is>
-          <t>1.</t>
-        </is>
-      </c>
-      <c r="B45" s="5" t="inlineStr">
-        <is>
-          <t>Second restructuring needed before 2027</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="20" t="inlineStr">
-        <is>
-          <t>2.</t>
-        </is>
-      </c>
-      <c r="B46" s="5" t="inlineStr">
-        <is>
-          <t>Tabarak reduces stake</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="20" t="inlineStr">
-        <is>
-          <t>3.</t>
-        </is>
-      </c>
-      <c r="B47" s="5" t="inlineStr">
-        <is>
-          <t>Backlog material below normalised expectations through 2027</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="4" t="inlineStr">
-        <is>
-          <t>Pre-mortem</t>
-        </is>
-      </c>
-      <c r="B49" s="19" t="n"/>
-      <c r="C49" s="19" t="n"/>
-      <c r="D49" s="19" t="n"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="20" t="inlineStr"/>
-      <c r="B50" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">It is end-2027 and DSI is down 60pct.
-Most likely: Backlog rebuild stalled; legacy litigation
-reactivated; GCC infrastructure cycle slowed; second
-restructuring or distressed equity raise.
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="4" t="inlineStr">
-        <is>
-          <t>Tier rationale</t>
-        </is>
-      </c>
-      <c r="B52" s="19" t="n"/>
-      <c r="C52" s="19" t="n"/>
-      <c r="D52" s="19" t="n"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="20" t="inlineStr"/>
-      <c r="B53" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bucket A, Archetype E (national bankruptcy framework / DIFC
-restructuring). Universe-screener 0.78 (15th). Tier 2 because
-legacy 5-year-halt history + low float + limited operational
-evidence post-recap. Builds for diversification within MEA
-basket; complements GTCO Nigerian recap basket exposure.
-</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="37">
-    <mergeCell ref="B11:D11"/>
-    <mergeCell ref="B42:D42"/>
-    <mergeCell ref="A4:D4"/>
-    <mergeCell ref="B8:D8"/>
-    <mergeCell ref="A52:D52"/>
-    <mergeCell ref="B53:D53"/>
-    <mergeCell ref="B38:D38"/>
-    <mergeCell ref="B34:D34"/>
-    <mergeCell ref="A44:D44"/>
-    <mergeCell ref="B10:D10"/>
-    <mergeCell ref="A40:D40"/>
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="B37:D37"/>
-    <mergeCell ref="A30:D30"/>
-    <mergeCell ref="B9:D9"/>
-    <mergeCell ref="A24:D24"/>
-    <mergeCell ref="A49:D49"/>
-    <mergeCell ref="B15:D15"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="A36:D36"/>
-    <mergeCell ref="B20:D20"/>
-    <mergeCell ref="B33:D33"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="B45:D45"/>
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B32:D32"/>
-    <mergeCell ref="B50:D50"/>
-    <mergeCell ref="B7:D7"/>
-    <mergeCell ref="B47:D47"/>
-    <mergeCell ref="B16:D16"/>
-    <mergeCell ref="A18:D18"/>
-    <mergeCell ref="B31:D31"/>
-    <mergeCell ref="B46:D46"/>
-    <mergeCell ref="B22:D22"/>
-    <mergeCell ref="B21:D21"/>
-    <mergeCell ref="B12:D12"/>
-    <mergeCell ref="A14:D14"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D55"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="60" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>OHLA (former OHL — Obrascón Huarte Lain)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>OHLA  ·  ES  ·  Bucket A  ·  Archetype A1, E  ·  Tier 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>Risk-reward snapshot</t>
-        </is>
-      </c>
-      <c r="B4" s="19" t="n"/>
-      <c r="C4" s="19" t="n"/>
-      <c r="D4" s="19" t="n"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="20" t="inlineStr">
-        <is>
-          <t>Expected EV×</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>2.35×</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="20" t="inlineStr">
-        <is>
-          <t>Bear / Base / Bull return</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t>0.50× / 2.40× / 4.50×</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="20" t="inlineStr">
-        <is>
-          <t>Bear loss</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>50%</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="20" t="inlineStr">
-        <is>
-          <t>Skew (upside/downside)</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>7.0×</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="20" t="inlineStr">
-        <is>
-          <t>Reward/Risk ratio</t>
-        </is>
-      </c>
-      <c r="B9" s="5" t="inlineStr">
-        <is>
-          <t>2.7×</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="20" t="inlineStr">
-        <is>
-          <t>Portfolio weight</t>
-        </is>
-      </c>
-      <c r="B10" s="5" t="inlineStr">
-        <is>
-          <t>3.00%</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="20" t="inlineStr">
-        <is>
-          <t>Cluster</t>
-        </is>
-      </c>
-      <c r="B11" s="5" t="inlineStr">
-        <is>
-          <t>Spanish_recovery</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="20" t="inlineStr">
-        <is>
-          <t>Primary factor</t>
-        </is>
-      </c>
-      <c r="B12" s="5" t="inlineStr">
-        <is>
-          <t>idiosyncratic</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t>Deal</t>
-        </is>
-      </c>
-      <c r="B14" s="19" t="n"/>
-      <c r="C14" s="19" t="n"/>
-      <c r="D14" s="19" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="20" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="B15" s="5" t="inlineStr">
-        <is>
-          <t>2024-01-15</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="20" t="inlineStr">
-        <is>
-          <t>Mechanic</t>
-        </is>
-      </c>
-      <c r="B16" s="5" t="inlineStr">
-        <is>
-          <t>A1 + E — Spanish accelerated-safeguard-equivalent recap. Amodio family + Atitlán capital injection Jan 2024: €70m initial at €0.25 + €40m Atitlán additional commitment. Sister-company Apollo separately offered €1.2bn rejected. Second restructuring since 2020 (Villar Mir family lost control 2020). Construction/concessions cycle support; Latin America infrastructure backlog plus Eastern European motorway concessions.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="4" t="inlineStr">
-        <is>
-          <t>Scorecard</t>
-        </is>
-      </c>
-      <c r="B18" s="19" t="n"/>
-      <c r="C18" s="19" t="n"/>
-      <c r="D18" s="19" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="20" t="inlineStr">
-        <is>
-          <t>D2 Issue Discount Pct</t>
-        </is>
-      </c>
-      <c r="B19" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="20" t="inlineStr">
-        <is>
-          <t>D4 Dilution Pct</t>
-        </is>
-      </c>
-      <c r="B20" s="5" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="20" t="inlineStr">
-        <is>
-          <t>D9 Alignment Gap</t>
-        </is>
-      </c>
-      <c r="B21" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="20" t="inlineStr">
-        <is>
-          <t>D11 Consensus Ebitda Cagr</t>
-        </is>
-      </c>
-      <c r="B22" s="5" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="20" t="inlineStr">
-        <is>
-          <t>D14 Liquidity Quarters</t>
-        </is>
-      </c>
-      <c r="B23" s="5" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="4" t="inlineStr">
-        <is>
-          <t>Catalysts</t>
-        </is>
-      </c>
-      <c r="B25" s="19" t="n"/>
-      <c r="C25" s="19" t="n"/>
-      <c r="D25" s="19" t="n"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="8" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B26" s="8" t="inlineStr">
-        <is>
-          <t>Window</t>
-        </is>
-      </c>
-      <c r="C26" s="8" t="inlineStr">
-        <is>
-          <t>P(yes)</t>
-        </is>
-      </c>
-      <c r="D26" s="8" t="inlineStr">
-        <is>
-          <t>Re-rate if yes / hit if no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="32" customHeight="1">
-      <c r="A27" s="21" t="inlineStr">
-        <is>
-          <t>Concessions cycle inflection (Spain + Latin America infrastructure)</t>
-        </is>
-      </c>
-      <c r="B27" s="11" t="inlineStr">
-        <is>
-          <t>2026-09-01 → 2027-12-31</t>
-        </is>
-      </c>
-      <c r="C27" s="11" t="inlineStr">
-        <is>
-          <t>0.5</t>
-        </is>
-      </c>
-      <c r="D27" s="11" t="inlineStr">
-        <is>
-          <t>Up 1.8-2.8× / Down -0.2--0.35</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="32" customHeight="1">
-      <c r="A28" s="22" t="inlineStr">
-        <is>
-          <t>Apollo (or alternative buyer) revives strategic-review offer</t>
-        </is>
-      </c>
-      <c r="B28" s="14" t="inlineStr">
-        <is>
-          <t>2026-06-01 → 2027-12-31</t>
-        </is>
-      </c>
-      <c r="C28" s="14" t="inlineStr">
-        <is>
-          <t>0.35</t>
-        </is>
-      </c>
-      <c r="D28" s="14" t="inlineStr">
-        <is>
-          <t>Up 2.0-3.5× / Down -0.1--0.15</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="32" customHeight="1">
-      <c r="A29" s="21" t="inlineStr">
-        <is>
-          <t>Operational margin recovery on backlog execution</t>
-        </is>
-      </c>
-      <c r="B29" s="11" t="inlineStr">
-        <is>
-          <t>2026-06-01 → 2028-06-30</t>
-        </is>
-      </c>
-      <c r="C29" s="11" t="inlineStr">
-        <is>
-          <t>0.55</t>
-        </is>
-      </c>
-      <c r="D29" s="11" t="inlineStr">
-        <is>
-          <t>Up 1.5-2.5× / Down -0.2--0.3</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="4" t="inlineStr">
-        <is>
-          <t>Triangulation (3-leg test)</t>
-        </is>
-      </c>
-      <c r="B31" s="19" t="n"/>
-      <c r="C31" s="19" t="n"/>
-      <c r="D31" s="19" t="n"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="20" t="inlineStr">
-        <is>
-          <t>Leg 1 — Valuation</t>
-        </is>
-      </c>
-      <c r="B32" s="5" t="inlineStr">
-        <is>
-          <t>partial</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="20" t="inlineStr">
-        <is>
-          <t>Leg 2 — Game theory</t>
-        </is>
-      </c>
-      <c r="B33" s="5" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="20" t="inlineStr">
-        <is>
-          <t>Leg 3 — Revealed preference</t>
-        </is>
-      </c>
-      <c r="B34" s="5" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="20" t="inlineStr">
-        <is>
-          <t>Notes</t>
-        </is>
-      </c>
-      <c r="B35" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Leg 1: Construction cycle troughed; multiple compressed vs peer
-average; backlog supports mid-cycle EBITDA ~2x current.
-Leg 2: Amodio family in for ~5 years; Atitlán additional
-commitment = follow-on conviction; Apollo offer establishes
-private-market floor.
-Leg 3: Apollo €1.2bn offer = revealed-preference floor at ~4x
-current market cap; Amodio + Atitlán continued participation =
-insider conviction.
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="4" t="inlineStr">
-        <is>
-          <t>Anchor</t>
-        </is>
-      </c>
-      <c r="B37" s="19" t="n"/>
-      <c r="C37" s="19" t="n"/>
-      <c r="D37" s="19" t="n"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="20" t="inlineStr">
-        <is>
-          <t>Parties</t>
-        </is>
-      </c>
-      <c r="B38" s="5" t="inlineStr">
-        <is>
-          <t>Amodio family, Atitlán Capital, Apollo (rejected offer — sets price floor)</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="20" t="inlineStr">
-        <is>
-          <t>Stake (% est.)</t>
-        </is>
-      </c>
-      <c r="B39" s="5" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="4" t="inlineStr">
-        <is>
-          <t>Red flags</t>
-        </is>
-      </c>
-      <c r="B41" s="19" t="n"/>
-      <c r="C41" s="19" t="n"/>
-      <c r="D41" s="19" t="n"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="20" t="inlineStr">
-        <is>
-          <t>Triggered</t>
-        </is>
-      </c>
-      <c r="B42" s="5" t="inlineStr">
-        <is>
-          <t>None of 11 active</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="20" t="inlineStr">
-        <is>
-          <t>Watch list</t>
-        </is>
-      </c>
-      <c r="B43" s="5" t="inlineStr">
-        <is>
-          <t>Second restructuring since 2020 = serial-RX yellow flag pattern</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="4" t="inlineStr">
-        <is>
-          <t>Kill criteria</t>
-        </is>
-      </c>
-      <c r="B45" s="19" t="n"/>
-      <c r="C45" s="19" t="n"/>
-      <c r="D45" s="19" t="n"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="20" t="inlineStr">
-        <is>
-          <t>1.</t>
-        </is>
-      </c>
-      <c r="B46" s="5" t="inlineStr">
-        <is>
-          <t>Third restructuring announced before mid-2027</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="20" t="inlineStr">
-        <is>
-          <t>2.</t>
-        </is>
-      </c>
-      <c r="B47" s="5" t="inlineStr">
-        <is>
-          <t>Amodio family reduces stake or steps back from board</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="20" t="inlineStr">
-        <is>
-          <t>3.</t>
-        </is>
-      </c>
-      <c r="B48" s="5" t="inlineStr">
-        <is>
-          <t>Apollo formally withdraws strategic interest</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="20" t="inlineStr">
-        <is>
-          <t>4.</t>
-        </is>
-      </c>
-      <c r="B49" s="5" t="inlineStr">
-        <is>
-          <t>Concession-renewal cliff in Spain or LatAm before backlog converts</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="4" t="inlineStr">
-        <is>
-          <t>Pre-mortem</t>
-        </is>
-      </c>
-      <c r="B51" s="19" t="n"/>
-      <c r="C51" s="19" t="n"/>
-      <c r="D51" s="19" t="n"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="20" t="inlineStr"/>
-      <c r="B52" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">It is end-2027 and OHLA is down 60% from current ~€0.20.
-Most likely: construction cycle did not recover; legacy
-litigation surprised (recurring on prior Villar Mir-era contracts);
-third restructuring required at distressed terms.
-Second most likely: Apollo or alternative buyer formally
-withdrew and no strategic alternative emerged; Amodio family
-considered take-private at lowball; minority squeezed.
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="4" t="inlineStr">
-        <is>
-          <t>Tier rationale</t>
-        </is>
-      </c>
-      <c r="B54" s="19" t="n"/>
-      <c r="C54" s="19" t="n"/>
-      <c r="D54" s="19" t="n"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="20" t="inlineStr"/>
-      <c r="B55" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bucket A, Archetype A1 (insider/promoter recap) + E (Spanish
-accelerated-safeguard-equivalent). Top universe-screen score
-(1.22 / highest of 697 names). Serial-restructuring yellow flag
-prevents direct Tier 1 promotion despite top score.
-</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="39">
-    <mergeCell ref="B11:D11"/>
-    <mergeCell ref="B42:D42"/>
-    <mergeCell ref="B23:D23"/>
-    <mergeCell ref="A4:D4"/>
-    <mergeCell ref="B8:D8"/>
-    <mergeCell ref="B38:D38"/>
-    <mergeCell ref="B34:D34"/>
-    <mergeCell ref="B10:D10"/>
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="A31:D31"/>
-    <mergeCell ref="B49:D49"/>
-    <mergeCell ref="B9:D9"/>
-    <mergeCell ref="A51:D51"/>
-    <mergeCell ref="B15:D15"/>
-    <mergeCell ref="B55:D55"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="B20:D20"/>
-    <mergeCell ref="B33:D33"/>
-    <mergeCell ref="A45:D45"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="B32:D32"/>
-    <mergeCell ref="B35:D35"/>
-    <mergeCell ref="A54:D54"/>
-    <mergeCell ref="A25:D25"/>
-    <mergeCell ref="A41:D41"/>
-    <mergeCell ref="B7:D7"/>
-    <mergeCell ref="B47:D47"/>
-    <mergeCell ref="B16:D16"/>
-    <mergeCell ref="A37:D37"/>
-    <mergeCell ref="A18:D18"/>
-    <mergeCell ref="B46:D46"/>
-    <mergeCell ref="B22:D22"/>
-    <mergeCell ref="B52:D52"/>
-    <mergeCell ref="B21:D21"/>
-    <mergeCell ref="B43:D43"/>
-    <mergeCell ref="B12:D12"/>
-    <mergeCell ref="B39:D39"/>
-    <mergeCell ref="B48:D48"/>
-    <mergeCell ref="A14:D14"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D53"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="60" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Doosan Bobcat (+ Doosan Robotics merger)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>241560  ·  KR  ·  Bucket A  ·  Archetype H, E  ·  Tier 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>Risk-reward snapshot</t>
-        </is>
-      </c>
-      <c r="B4" s="19" t="n"/>
-      <c r="C4" s="19" t="n"/>
-      <c r="D4" s="19" t="n"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="20" t="inlineStr">
-        <is>
-          <t>Expected EV×</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>1.66×</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="20" t="inlineStr">
-        <is>
-          <t>Bear / Base / Bull return</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t>0.75× / 1.70× / 2.50×</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="20" t="inlineStr">
-        <is>
-          <t>Bear loss</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>25%</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="20" t="inlineStr">
-        <is>
-          <t>Skew (upside/downside)</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>6.0×</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="20" t="inlineStr">
-        <is>
-          <t>Reward/Risk ratio</t>
-        </is>
-      </c>
-      <c r="B9" s="5" t="inlineStr">
-        <is>
-          <t>2.7×</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="20" t="inlineStr">
-        <is>
-          <t>Portfolio weight</t>
-        </is>
-      </c>
-      <c r="B10" s="5" t="inlineStr">
-        <is>
-          <t>3.00%</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="20" t="inlineStr">
-        <is>
-          <t>Cluster</t>
-        </is>
-      </c>
-      <c r="B11" s="5" t="inlineStr">
-        <is>
-          <t>Asian_governance_reform</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="20" t="inlineStr">
-        <is>
-          <t>Primary factor</t>
-        </is>
-      </c>
-      <c r="B12" s="5" t="inlineStr">
-        <is>
-          <t>policy</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t>Deal</t>
-        </is>
-      </c>
-      <c r="B14" s="19" t="n"/>
-      <c r="C14" s="19" t="n"/>
-      <c r="D14" s="19" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="20" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="B15" s="5" t="inlineStr">
-        <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="20" t="inlineStr">
-        <is>
-          <t>Mechanic</t>
-        </is>
-      </c>
-      <c r="B16" s="5" t="inlineStr">
-        <is>
-          <t>H + E — Korean H6 governance overhaul. Aug 2024 original stock-swap proposal blocked by minority opposition + K-FSC ruling original ratio undervalued Bobcat. Q2 2026 revised terms tabled; Doosan Group cannot drop restructuring. Korean Commercial Act third amendment effective March 6, 2026 mandates treasury-share cancellation + cumulative voting for large companies + strengthened minority-shareholder rights — reform forcing chaebol governance overhaul.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="4" t="inlineStr">
-        <is>
-          <t>Scorecard</t>
-        </is>
-      </c>
-      <c r="B18" s="19" t="n"/>
-      <c r="C18" s="19" t="n"/>
-      <c r="D18" s="19" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="20" t="inlineStr">
-        <is>
-          <t>D4 Dilution Pct</t>
-        </is>
-      </c>
-      <c r="B19" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="20" t="inlineStr">
-        <is>
-          <t>D9 Alignment Gap</t>
-        </is>
-      </c>
-      <c r="B20" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="20" t="inlineStr">
-        <is>
-          <t>D11 Consensus Ebitda Cagr</t>
-        </is>
-      </c>
-      <c r="B21" s="5" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="20" t="inlineStr">
-        <is>
-          <t>D14 Liquidity Quarters</t>
-        </is>
-      </c>
-      <c r="B22" s="5" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="4" t="inlineStr">
-        <is>
-          <t>Catalysts</t>
-        </is>
-      </c>
-      <c r="B24" s="19" t="n"/>
-      <c r="C24" s="19" t="n"/>
-      <c r="D24" s="19" t="n"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="8" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B25" s="8" t="inlineStr">
-        <is>
-          <t>Window</t>
-        </is>
-      </c>
-      <c r="C25" s="8" t="inlineStr">
-        <is>
-          <t>P(yes)</t>
-        </is>
-      </c>
-      <c r="D25" s="8" t="inlineStr">
-        <is>
-          <t>Re-rate if yes / hit if no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="32" customHeight="1">
-      <c r="A26" s="21" t="inlineStr">
-        <is>
-          <t>Revised stock-swap terms approved at Q2 2026 EGM (or alternative restructuring)</t>
-        </is>
-      </c>
-      <c r="B26" s="11" t="inlineStr">
-        <is>
-          <t>2026-06-01 → 2026-12-31</t>
-        </is>
-      </c>
-      <c r="C26" s="11" t="inlineStr">
-        <is>
-          <t>0.6</t>
-        </is>
-      </c>
-      <c r="D26" s="11" t="inlineStr">
-        <is>
-          <t>Up 1.4-2.0× / Down -0.1--0.2</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="32" customHeight="1">
-      <c r="A27" s="22" t="inlineStr">
-        <is>
-          <t>Treasury-share cancellation announcement (Commercial Act compliance)</t>
-        </is>
-      </c>
-      <c r="B27" s="14" t="inlineStr">
-        <is>
-          <t>2026-09-01 → 2027-09-06</t>
-        </is>
-      </c>
-      <c r="C27" s="14" t="inlineStr">
-        <is>
-          <t>0.65</t>
-        </is>
-      </c>
-      <c r="D27" s="14" t="inlineStr">
-        <is>
-          <t>Up 1.2-1.5× / Down -0.05--0.1</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="32" customHeight="1">
-      <c r="A28" s="21" t="inlineStr">
-        <is>
-          <t>Korea Value-Up cohort re-rating (chaebol holdcos + treasury cancellation cascade)</t>
-        </is>
-      </c>
-      <c r="B28" s="11" t="inlineStr">
-        <is>
-          <t>2026-06-01 → 2028-06-30</t>
-        </is>
-      </c>
-      <c r="C28" s="11" t="inlineStr">
-        <is>
-          <t>0.55</t>
-        </is>
-      </c>
-      <c r="D28" s="11" t="inlineStr">
-        <is>
-          <t>Up 1.3-1.8× / Down -0.1--0.2</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="4" t="inlineStr">
-        <is>
-          <t>Triangulation (3-leg test)</t>
-        </is>
-      </c>
-      <c r="B30" s="19" t="n"/>
-      <c r="C30" s="19" t="n"/>
-      <c r="D30" s="19" t="n"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="20" t="inlineStr">
-        <is>
-          <t>Leg 1 — Valuation</t>
-        </is>
-      </c>
-      <c r="B31" s="5" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="20" t="inlineStr">
-        <is>
-          <t>Leg 2 — Game theory</t>
-        </is>
-      </c>
-      <c r="B32" s="5" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="20" t="inlineStr">
-        <is>
-          <t>Leg 3 — Revealed preference</t>
-        </is>
-      </c>
-      <c r="B33" s="5" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="20" t="inlineStr">
-        <is>
-          <t>Notes</t>
-        </is>
-      </c>
-      <c r="B34" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Leg 1: Bobcat at materially below SOTP; Robotics premium
-reflects valuation gap.
-Leg 2: Three forcing functions converge — Q2 2026 revised
-terms, Commercial Act amendment, treasury-share deadlines.
-Leg 3: K-FSC original-ratio rejection = revealed-preference
-floor; minority shareholders showed they can block; Park
-family must engage in good faith.
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="4" t="inlineStr">
-        <is>
-          <t>Anchor</t>
-        </is>
-      </c>
-      <c r="B36" s="19" t="n"/>
-      <c r="C36" s="19" t="n"/>
-      <c r="D36" s="19" t="n"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="20" t="inlineStr">
-        <is>
-          <t>Parties</t>
-        </is>
-      </c>
-      <c r="B37" s="5" t="inlineStr">
-        <is>
-          <t>Doosan Group (Park family), Korea Value-Up framework + K-FSC enforcement</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="20" t="inlineStr">
-        <is>
-          <t>Stake (% est.)</t>
-        </is>
-      </c>
-      <c r="B38" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="4" t="inlineStr">
-        <is>
-          <t>Red flags</t>
-        </is>
-      </c>
-      <c r="B40" s="19" t="n"/>
-      <c r="C40" s="19" t="n"/>
-      <c r="D40" s="19" t="n"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="20" t="inlineStr">
-        <is>
-          <t>Triggered</t>
-        </is>
-      </c>
-      <c r="B41" s="5" t="inlineStr">
-        <is>
-          <t>None of 11 active</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="20" t="inlineStr">
-        <is>
-          <t>Watch list</t>
-        </is>
-      </c>
-      <c r="B42" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="4" t="inlineStr">
-        <is>
-          <t>Kill criteria</t>
-        </is>
-      </c>
-      <c r="B44" s="19" t="n"/>
-      <c r="C44" s="19" t="n"/>
-      <c r="D44" s="19" t="n"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="20" t="inlineStr">
-        <is>
-          <t>1.</t>
-        </is>
-      </c>
-      <c r="B45" s="5" t="inlineStr">
-        <is>
-          <t>Park family abandons restructuring; Bobcat trades as standalone</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="20" t="inlineStr">
-        <is>
-          <t>2.</t>
-        </is>
-      </c>
-      <c r="B46" s="5" t="inlineStr">
-        <is>
-          <t>Construction cycle deepens; Bobcat margins compress</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="20" t="inlineStr">
-        <is>
-          <t>3.</t>
-        </is>
-      </c>
-      <c r="B47" s="5" t="inlineStr">
-        <is>
-          <t>Doosan Group financial stress forces distressed disposal</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="4" t="inlineStr">
-        <is>
-          <t>Pre-mortem</t>
-        </is>
-      </c>
-      <c r="B49" s="19" t="n"/>
-      <c r="C49" s="19" t="n"/>
-      <c r="D49" s="19" t="n"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="20" t="inlineStr"/>
-      <c r="B50" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">It is end-2027 and 241560 is down 50pct.
-Most likely: Restructuring postponed; chaebol family
-prioritised group-level liquidity needs; construction cycle
-weakened; multiple compressed.
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="4" t="inlineStr">
-        <is>
-          <t>Tier rationale</t>
-        </is>
-      </c>
-      <c r="B52" s="19" t="n"/>
-      <c r="C52" s="19" t="n"/>
-      <c r="D52" s="19" t="n"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="20" t="inlineStr"/>
-      <c r="B53" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bucket A, Archetype H (governance overhaul via K-FSC + Korean
-reform regime) + E (court/regulatory-sanctioned restructuring).
-Universe-screener 0.86. Tier 1 on multiple dated triggers
-+ clear forcing functions + minority-shareholder protection
-precedent established.
-</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="37">
-    <mergeCell ref="B11:D11"/>
-    <mergeCell ref="B42:D42"/>
-    <mergeCell ref="A4:D4"/>
-    <mergeCell ref="B8:D8"/>
-    <mergeCell ref="A52:D52"/>
-    <mergeCell ref="B53:D53"/>
-    <mergeCell ref="B38:D38"/>
-    <mergeCell ref="B34:D34"/>
-    <mergeCell ref="A44:D44"/>
-    <mergeCell ref="B10:D10"/>
-    <mergeCell ref="A40:D40"/>
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="B37:D37"/>
-    <mergeCell ref="A30:D30"/>
-    <mergeCell ref="B9:D9"/>
-    <mergeCell ref="A24:D24"/>
-    <mergeCell ref="A49:D49"/>
-    <mergeCell ref="B15:D15"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="A36:D36"/>
-    <mergeCell ref="B20:D20"/>
-    <mergeCell ref="B33:D33"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="B45:D45"/>
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B32:D32"/>
-    <mergeCell ref="B50:D50"/>
-    <mergeCell ref="B7:D7"/>
-    <mergeCell ref="B47:D47"/>
-    <mergeCell ref="B16:D16"/>
-    <mergeCell ref="A18:D18"/>
-    <mergeCell ref="B31:D31"/>
-    <mergeCell ref="B46:D46"/>
-    <mergeCell ref="B22:D22"/>
-    <mergeCell ref="B21:D21"/>
-    <mergeCell ref="B12:D12"/>
-    <mergeCell ref="A14:D14"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:A25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -6791,7 +4979,7 @@
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
     <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
     <col width="40" customWidth="1" min="4" max="4"/>
     <col width="22" customWidth="1" min="5" max="5"/>
     <col width="8" customWidth="1" min="6" max="6"/>
@@ -6814,7 +5002,7 @@
     <row r="2" ht="38" customHeight="1">
       <c r="A2" s="7" t="inlineStr">
         <is>
-          <t>Universe coverage: 126 investable names (21 REAL waterfalls · 105 PROXY).  REAL uses the hand-built YAML's bottom-up bear/base/bull. PROXY uses a transparent formula on the universe-screener score + archetype tilt.</t>
+          <t>Universe coverage: 108 investable names (20 REAL waterfalls · 88 PROXY).  REAL uses the hand-built YAML's bottom-up bear/base/bull. PROXY uses a transparent formula on the universe-screener score + archetype tilt.</t>
         </is>
       </c>
     </row>
@@ -7157,22 +5345,22 @@
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>NYSE:GGAL</t>
+          <t>ACF</t>
         </is>
       </c>
       <c r="D9" s="11" t="inlineStr">
         <is>
-          <t>Banco Galicia</t>
+          <t>ACROW LIMITED</t>
         </is>
       </c>
       <c r="E9" s="11" t="inlineStr">
         <is>
-          <t>Latin America</t>
+          <t>SE Asia / Pacific</t>
         </is>
       </c>
       <c r="F9" s="11" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="G9" s="11" t="inlineStr">
@@ -7182,7 +5370,7 @@
       </c>
       <c r="H9" s="11" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2+A1</t>
         </is>
       </c>
       <c r="I9" s="11" t="inlineStr">
@@ -7197,7 +5385,7 @@
       </c>
       <c r="K9" s="11" t="inlineStr">
         <is>
-          <t>2.92×</t>
+          <t>2.94×</t>
         </is>
       </c>
       <c r="L9" s="11" t="inlineStr">
@@ -7207,7 +5395,7 @@
       </c>
       <c r="M9" s="11" t="inlineStr">
         <is>
-          <t>3.6×</t>
+          <t>3.7×</t>
         </is>
       </c>
     </row>
@@ -7215,29 +5403,29 @@
       <c r="A10" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="B10" s="16" t="inlineStr">
-        <is>
-          <t>REAL</t>
+      <c r="B10" s="13" t="inlineStr">
+        <is>
+          <t>PROXY</t>
         </is>
       </c>
       <c r="C10" s="14" t="inlineStr">
         <is>
-          <t>NYSE:LAC</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="D10" s="14" t="inlineStr">
         <is>
-          <t>Lithium Americas</t>
+          <t>MEMPHASYS LIMITED.</t>
         </is>
       </c>
       <c r="E10" s="14" t="inlineStr">
         <is>
-          <t>United States/Canada</t>
+          <t>SE Asia / Pacific</t>
         </is>
       </c>
       <c r="F10" s="14" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="G10" s="14" t="inlineStr">
@@ -7247,32 +5435,32 @@
       </c>
       <c r="H10" s="14" t="inlineStr">
         <is>
-          <t>A2</t>
+          <t>A2+B</t>
         </is>
       </c>
       <c r="I10" s="14" t="inlineStr">
         <is>
-          <t>60%</t>
+          <t>27%</t>
         </is>
       </c>
       <c r="J10" s="14" t="inlineStr">
         <is>
-          <t>3.00×</t>
+          <t>2.33×</t>
         </is>
       </c>
       <c r="K10" s="14" t="inlineStr">
         <is>
-          <t>6.00×</t>
+          <t>2.94×</t>
         </is>
       </c>
       <c r="L10" s="14" t="inlineStr">
         <is>
-          <t>3.10×</t>
+          <t>2.00×</t>
         </is>
       </c>
       <c r="M10" s="14" t="inlineStr">
         <is>
-          <t>3.5×</t>
+          <t>3.7×</t>
         </is>
       </c>
     </row>
@@ -7280,29 +5468,29 @@
       <c r="A11" s="9" t="n">
         <v>7</v>
       </c>
-      <c r="B11" s="10" t="inlineStr">
-        <is>
-          <t>REAL</t>
+      <c r="B11" s="15" t="inlineStr">
+        <is>
+          <t>PROXY</t>
         </is>
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>XETR:SZG</t>
+          <t>NYSE:GGAL</t>
         </is>
       </c>
       <c r="D11" s="11" t="inlineStr">
         <is>
-          <t>Salzgitter</t>
+          <t>Banco Galicia</t>
         </is>
       </c>
       <c r="E11" s="11" t="inlineStr">
         <is>
-          <t>Continental Europe</t>
+          <t>Latin America</t>
         </is>
       </c>
       <c r="F11" s="11" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="G11" s="11" t="inlineStr">
@@ -7312,32 +5500,32 @@
       </c>
       <c r="H11" s="11" t="inlineStr">
         <is>
-          <t>A2</t>
+          <t>A1</t>
         </is>
       </c>
       <c r="I11" s="11" t="inlineStr">
         <is>
-          <t>45%</t>
+          <t>27%</t>
         </is>
       </c>
       <c r="J11" s="11" t="inlineStr">
         <is>
-          <t>2.50×</t>
+          <t>2.33×</t>
         </is>
       </c>
       <c r="K11" s="11" t="inlineStr">
         <is>
-          <t>4.50×</t>
+          <t>2.92×</t>
         </is>
       </c>
       <c r="L11" s="11" t="inlineStr">
         <is>
-          <t>2.51×</t>
+          <t>2.00×</t>
         </is>
       </c>
       <c r="M11" s="11" t="inlineStr">
         <is>
-          <t>3.4×</t>
+          <t>3.6×</t>
         </is>
       </c>
     </row>
@@ -7345,29 +5533,29 @@
       <c r="A12" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="B12" s="13" t="inlineStr">
-        <is>
-          <t>PROXY</t>
+      <c r="B12" s="16" t="inlineStr">
+        <is>
+          <t>REAL</t>
         </is>
       </c>
       <c r="C12" s="14" t="inlineStr">
         <is>
-          <t>NYSE:PAM</t>
+          <t>NYSE:LAC</t>
         </is>
       </c>
       <c r="D12" s="14" t="inlineStr">
         <is>
-          <t>Pampa Energía</t>
+          <t>Lithium Americas</t>
         </is>
       </c>
       <c r="E12" s="14" t="inlineStr">
         <is>
-          <t>Latin America</t>
+          <t>United States/Canada</t>
         </is>
       </c>
       <c r="F12" s="14" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="G12" s="14" t="inlineStr">
@@ -7377,32 +5565,32 @@
       </c>
       <c r="H12" s="14" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2</t>
         </is>
       </c>
       <c r="I12" s="14" t="inlineStr">
         <is>
-          <t>28%</t>
+          <t>60%</t>
         </is>
       </c>
       <c r="J12" s="14" t="inlineStr">
         <is>
-          <t>2.29×</t>
+          <t>3.00×</t>
         </is>
       </c>
       <c r="K12" s="14" t="inlineStr">
         <is>
-          <t>2.87×</t>
+          <t>6.00×</t>
         </is>
       </c>
       <c r="L12" s="14" t="inlineStr">
         <is>
-          <t>1.96×</t>
+          <t>3.10×</t>
         </is>
       </c>
       <c r="M12" s="14" t="inlineStr">
         <is>
-          <t>3.4×</t>
+          <t>3.5×</t>
         </is>
       </c>
     </row>
@@ -7410,29 +5598,29 @@
       <c r="A13" s="9" t="n">
         <v>9</v>
       </c>
-      <c r="B13" s="15" t="inlineStr">
-        <is>
-          <t>PROXY</t>
+      <c r="B13" s="10" t="inlineStr">
+        <is>
+          <t>REAL</t>
         </is>
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>3544</t>
+          <t>XETR:SZG</t>
         </is>
       </c>
       <c r="D13" s="11" t="inlineStr">
         <is>
-          <t>サツドラＨＤ</t>
+          <t>Salzgitter</t>
         </is>
       </c>
       <c r="E13" s="11" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Continental Europe</t>
         </is>
       </c>
       <c r="F13" s="11" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="G13" s="11" t="inlineStr">
@@ -7442,32 +5630,32 @@
       </c>
       <c r="H13" s="11" t="inlineStr">
         <is>
-          <t>A2+C</t>
+          <t>A2</t>
         </is>
       </c>
       <c r="I13" s="11" t="inlineStr">
         <is>
-          <t>29%</t>
+          <t>45%</t>
         </is>
       </c>
       <c r="J13" s="11" t="inlineStr">
         <is>
-          <t>2.26×</t>
+          <t>2.50×</t>
         </is>
       </c>
       <c r="K13" s="11" t="inlineStr">
         <is>
-          <t>2.80×</t>
+          <t>4.50×</t>
         </is>
       </c>
       <c r="L13" s="11" t="inlineStr">
         <is>
-          <t>1.93×</t>
+          <t>2.51×</t>
         </is>
       </c>
       <c r="M13" s="11" t="inlineStr">
         <is>
-          <t>3.2×</t>
+          <t>3.4×</t>
         </is>
       </c>
     </row>
@@ -7482,22 +5670,22 @@
       </c>
       <c r="C14" s="14" t="inlineStr">
         <is>
-          <t>6897</t>
+          <t>NYSE:PAM</t>
         </is>
       </c>
       <c r="D14" s="14" t="inlineStr">
         <is>
-          <t>ツインバード</t>
+          <t>Pampa Energía</t>
         </is>
       </c>
       <c r="E14" s="14" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Latin America</t>
         </is>
       </c>
       <c r="F14" s="14" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="G14" s="14" t="inlineStr">
@@ -7507,32 +5695,32 @@
       </c>
       <c r="H14" s="14" t="inlineStr">
         <is>
-          <t>A2+C</t>
+          <t>A1</t>
         </is>
       </c>
       <c r="I14" s="14" t="inlineStr">
         <is>
-          <t>29%</t>
+          <t>28%</t>
         </is>
       </c>
       <c r="J14" s="14" t="inlineStr">
         <is>
-          <t>2.26×</t>
+          <t>2.29×</t>
         </is>
       </c>
       <c r="K14" s="14" t="inlineStr">
         <is>
-          <t>2.80×</t>
+          <t>2.87×</t>
         </is>
       </c>
       <c r="L14" s="14" t="inlineStr">
         <is>
-          <t>1.93×</t>
+          <t>1.96×</t>
         </is>
       </c>
       <c r="M14" s="14" t="inlineStr">
         <is>
-          <t>3.2×</t>
+          <t>3.4×</t>
         </is>
       </c>
     </row>
@@ -7547,12 +5735,12 @@
       </c>
       <c r="C15" s="11" t="inlineStr">
         <is>
-          <t>4951</t>
+          <t>3544</t>
         </is>
       </c>
       <c r="D15" s="11" t="inlineStr">
         <is>
-          <t>エステー</t>
+          <t>サツドラＨＤ</t>
         </is>
       </c>
       <c r="E15" s="11" t="inlineStr">
@@ -7612,12 +5800,12 @@
       </c>
       <c r="C16" s="14" t="inlineStr">
         <is>
-          <t>3659</t>
+          <t>6897</t>
         </is>
       </c>
       <c r="D16" s="14" t="inlineStr">
         <is>
-          <t>ネクソン</t>
+          <t>ツインバード</t>
         </is>
       </c>
       <c r="E16" s="14" t="inlineStr">
@@ -7670,29 +5858,29 @@
       <c r="A17" s="9" t="n">
         <v>13</v>
       </c>
-      <c r="B17" s="10" t="inlineStr">
-        <is>
-          <t>REAL</t>
+      <c r="B17" s="15" t="inlineStr">
+        <is>
+          <t>PROXY</t>
         </is>
       </c>
       <c r="C17" s="11" t="inlineStr">
         <is>
-          <t>XETR:TKA</t>
+          <t>4951</t>
         </is>
       </c>
       <c r="D17" s="11" t="inlineStr">
         <is>
-          <t>Thyssenkrupp Steel</t>
+          <t>エステー</t>
         </is>
       </c>
       <c r="E17" s="11" t="inlineStr">
         <is>
-          <t>Continental Europe</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="F17" s="11" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="G17" s="11" t="inlineStr">
@@ -7702,32 +5890,32 @@
       </c>
       <c r="H17" s="11" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>A2+C</t>
         </is>
       </c>
       <c r="I17" s="11" t="inlineStr">
         <is>
-          <t>45%</t>
+          <t>29%</t>
         </is>
       </c>
       <c r="J17" s="11" t="inlineStr">
         <is>
-          <t>2.30×</t>
+          <t>2.26×</t>
         </is>
       </c>
       <c r="K17" s="11" t="inlineStr">
         <is>
-          <t>4.20×</t>
+          <t>2.80×</t>
         </is>
       </c>
       <c r="L17" s="11" t="inlineStr">
         <is>
-          <t>2.34×</t>
+          <t>1.93×</t>
         </is>
       </c>
       <c r="M17" s="11" t="inlineStr">
         <is>
-          <t>3.0×</t>
+          <t>3.2×</t>
         </is>
       </c>
     </row>
@@ -7735,29 +5923,29 @@
       <c r="A18" s="12" t="n">
         <v>14</v>
       </c>
-      <c r="B18" s="16" t="inlineStr">
-        <is>
-          <t>REAL</t>
+      <c r="B18" s="13" t="inlineStr">
+        <is>
+          <t>PROXY</t>
         </is>
       </c>
       <c r="C18" s="14" t="inlineStr">
         <is>
-          <t>NGX:GTCO</t>
+          <t>3659</t>
         </is>
       </c>
       <c r="D18" s="14" t="inlineStr">
         <is>
-          <t>GTCO (Guaranty Trust)</t>
+          <t>ネクソン</t>
         </is>
       </c>
       <c r="E18" s="14" t="inlineStr">
         <is>
-          <t>MEA / Frontier</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="F18" s="14" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="G18" s="14" t="inlineStr">
@@ -7767,32 +5955,32 @@
       </c>
       <c r="H18" s="14" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>A2+C</t>
         </is>
       </c>
       <c r="I18" s="14" t="inlineStr">
         <is>
-          <t>40%</t>
+          <t>29%</t>
         </is>
       </c>
       <c r="J18" s="14" t="inlineStr">
         <is>
-          <t>2.10×</t>
+          <t>2.26×</t>
         </is>
       </c>
       <c r="K18" s="14" t="inlineStr">
         <is>
-          <t>3.80×</t>
+          <t>2.80×</t>
         </is>
       </c>
       <c r="L18" s="14" t="inlineStr">
         <is>
-          <t>2.15×</t>
+          <t>1.93×</t>
         </is>
       </c>
       <c r="M18" s="14" t="inlineStr">
         <is>
-          <t>2.9×</t>
+          <t>3.2×</t>
         </is>
       </c>
     </row>
@@ -7800,29 +5988,29 @@
       <c r="A19" s="9" t="n">
         <v>15</v>
       </c>
-      <c r="B19" s="10" t="inlineStr">
-        <is>
-          <t>REAL</t>
+      <c r="B19" s="15" t="inlineStr">
+        <is>
+          <t>PROXY</t>
         </is>
       </c>
       <c r="C19" s="11" t="inlineStr">
         <is>
-          <t>STO:ELUX-B</t>
+          <t>DTZ</t>
         </is>
       </c>
       <c r="D19" s="11" t="inlineStr">
         <is>
-          <t>AB Electrolux (Series B)</t>
+          <t>DOTZ NANO LIMITED</t>
         </is>
       </c>
       <c r="E19" s="11" t="inlineStr">
         <is>
-          <t>Continental Europe</t>
+          <t>SE Asia / Pacific</t>
         </is>
       </c>
       <c r="F19" s="11" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="G19" s="11" t="inlineStr">
@@ -7832,32 +6020,32 @@
       </c>
       <c r="H19" s="11" t="inlineStr">
         <is>
-          <t>A1+D</t>
+          <t>A2</t>
         </is>
       </c>
       <c r="I19" s="11" t="inlineStr">
         <is>
-          <t>45%</t>
+          <t>29%</t>
         </is>
       </c>
       <c r="J19" s="11" t="inlineStr">
         <is>
-          <t>2.20×</t>
+          <t>2.27×</t>
         </is>
       </c>
       <c r="K19" s="11" t="inlineStr">
         <is>
-          <t>4.00×</t>
+          <t>2.82×</t>
         </is>
       </c>
       <c r="L19" s="11" t="inlineStr">
         <is>
-          <t>2.32×</t>
+          <t>1.94×</t>
         </is>
       </c>
       <c r="M19" s="11" t="inlineStr">
         <is>
-          <t>2.9×</t>
+          <t>3.2×</t>
         </is>
       </c>
     </row>
@@ -7865,29 +6053,29 @@
       <c r="A20" s="12" t="n">
         <v>16</v>
       </c>
-      <c r="B20" s="16" t="inlineStr">
-        <is>
-          <t>REAL</t>
+      <c r="B20" s="13" t="inlineStr">
+        <is>
+          <t>PROXY</t>
         </is>
       </c>
       <c r="C20" s="14" t="inlineStr">
         <is>
-          <t>TSE:6305</t>
+          <t>BMR</t>
         </is>
       </c>
       <c r="D20" s="14" t="inlineStr">
         <is>
-          <t>Hitachi Construction Machinery</t>
+          <t>BALLYMORE RESOURCES LIMITED</t>
         </is>
       </c>
       <c r="E20" s="14" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>SE Asia / Pacific</t>
         </is>
       </c>
       <c r="F20" s="14" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="G20" s="14" t="inlineStr">
@@ -7897,32 +6085,32 @@
       </c>
       <c r="H20" s="14" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>A2</t>
         </is>
       </c>
       <c r="I20" s="14" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>29%</t>
         </is>
       </c>
       <c r="J20" s="14" t="inlineStr">
         <is>
-          <t>1.70×</t>
+          <t>2.27×</t>
         </is>
       </c>
       <c r="K20" s="14" t="inlineStr">
         <is>
-          <t>2.80×</t>
+          <t>2.82×</t>
         </is>
       </c>
       <c r="L20" s="14" t="inlineStr">
         <is>
-          <t>1.69×</t>
+          <t>1.94×</t>
         </is>
       </c>
       <c r="M20" s="14" t="inlineStr">
         <is>
-          <t>2.8×</t>
+          <t>3.2×</t>
         </is>
       </c>
     </row>
@@ -7937,22 +6125,22 @@
       </c>
       <c r="C21" s="11" t="inlineStr">
         <is>
-          <t>8074</t>
+          <t>CQT</t>
         </is>
       </c>
       <c r="D21" s="11" t="inlineStr">
         <is>
-          <t>ＹＵＡＳＡ</t>
+          <t>CONNEQT HEALTH LIMITED</t>
         </is>
       </c>
       <c r="E21" s="11" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>SE Asia / Pacific</t>
         </is>
       </c>
       <c r="F21" s="11" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="G21" s="11" t="inlineStr">
@@ -7967,27 +6155,27 @@
       </c>
       <c r="I21" s="11" t="inlineStr">
         <is>
-          <t>31%</t>
+          <t>29%</t>
         </is>
       </c>
       <c r="J21" s="11" t="inlineStr">
         <is>
-          <t>2.19×</t>
+          <t>2.27×</t>
         </is>
       </c>
       <c r="K21" s="11" t="inlineStr">
         <is>
-          <t>2.69×</t>
+          <t>2.82×</t>
         </is>
       </c>
       <c r="L21" s="11" t="inlineStr">
         <is>
-          <t>1.86×</t>
+          <t>1.94×</t>
         </is>
       </c>
       <c r="M21" s="11" t="inlineStr">
         <is>
-          <t>2.8×</t>
+          <t>3.2×</t>
         </is>
       </c>
     </row>
@@ -8002,22 +6190,22 @@
       </c>
       <c r="C22" s="14" t="inlineStr">
         <is>
-          <t>2198</t>
+          <t>JLL</t>
         </is>
       </c>
       <c r="D22" s="14" t="inlineStr">
         <is>
-          <t>アイ・ケイ・ケイＨＤ</t>
+          <t>JINDALEE LITHIUM LIMITED</t>
         </is>
       </c>
       <c r="E22" s="14" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>SE Asia / Pacific</t>
         </is>
       </c>
       <c r="F22" s="14" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="G22" s="14" t="inlineStr">
@@ -8032,27 +6220,27 @@
       </c>
       <c r="I22" s="14" t="inlineStr">
         <is>
-          <t>31%</t>
+          <t>29%</t>
         </is>
       </c>
       <c r="J22" s="14" t="inlineStr">
         <is>
-          <t>2.19×</t>
+          <t>2.27×</t>
         </is>
       </c>
       <c r="K22" s="14" t="inlineStr">
         <is>
-          <t>2.69×</t>
+          <t>2.82×</t>
         </is>
       </c>
       <c r="L22" s="14" t="inlineStr">
         <is>
-          <t>1.86×</t>
+          <t>1.94×</t>
         </is>
       </c>
       <c r="M22" s="14" t="inlineStr">
         <is>
-          <t>2.8×</t>
+          <t>3.2×</t>
         </is>
       </c>
     </row>
@@ -8067,22 +6255,22 @@
       </c>
       <c r="C23" s="11" t="inlineStr">
         <is>
-          <t>3454</t>
+          <t>KSN</t>
         </is>
       </c>
       <c r="D23" s="11" t="inlineStr">
         <is>
-          <t>ファーストブラザーズ</t>
+          <t>KINGSTON RESOURCES LIMITED</t>
         </is>
       </c>
       <c r="E23" s="11" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>SE Asia / Pacific</t>
         </is>
       </c>
       <c r="F23" s="11" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="G23" s="11" t="inlineStr">
@@ -8097,27 +6285,27 @@
       </c>
       <c r="I23" s="11" t="inlineStr">
         <is>
-          <t>31%</t>
+          <t>29%</t>
         </is>
       </c>
       <c r="J23" s="11" t="inlineStr">
         <is>
-          <t>2.19×</t>
+          <t>2.27×</t>
         </is>
       </c>
       <c r="K23" s="11" t="inlineStr">
         <is>
-          <t>2.69×</t>
+          <t>2.82×</t>
         </is>
       </c>
       <c r="L23" s="11" t="inlineStr">
         <is>
-          <t>1.86×</t>
+          <t>1.94×</t>
         </is>
       </c>
       <c r="M23" s="11" t="inlineStr">
         <is>
-          <t>2.8×</t>
+          <t>3.2×</t>
         </is>
       </c>
     </row>
@@ -8132,22 +6320,22 @@
       </c>
       <c r="C24" s="14" t="inlineStr">
         <is>
-          <t>3803</t>
+          <t>PNN</t>
         </is>
       </c>
       <c r="D24" s="14" t="inlineStr">
         <is>
-          <t>Ｇ－イメージ情</t>
+          <t>POWER MINERALS LIMITED</t>
         </is>
       </c>
       <c r="E24" s="14" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>SE Asia / Pacific</t>
         </is>
       </c>
       <c r="F24" s="14" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="G24" s="14" t="inlineStr">
@@ -8162,27 +6350,27 @@
       </c>
       <c r="I24" s="14" t="inlineStr">
         <is>
-          <t>31%</t>
+          <t>29%</t>
         </is>
       </c>
       <c r="J24" s="14" t="inlineStr">
         <is>
-          <t>2.19×</t>
+          <t>2.27×</t>
         </is>
       </c>
       <c r="K24" s="14" t="inlineStr">
         <is>
-          <t>2.69×</t>
+          <t>2.82×</t>
         </is>
       </c>
       <c r="L24" s="14" t="inlineStr">
         <is>
-          <t>1.86×</t>
+          <t>1.94×</t>
         </is>
       </c>
       <c r="M24" s="14" t="inlineStr">
         <is>
-          <t>2.8×</t>
+          <t>3.2×</t>
         </is>
       </c>
     </row>
@@ -8197,22 +6385,22 @@
       </c>
       <c r="C25" s="11" t="inlineStr">
         <is>
-          <t>4641</t>
+          <t>ERM</t>
         </is>
       </c>
       <c r="D25" s="11" t="inlineStr">
         <is>
-          <t>アルプス技</t>
+          <t>EMMERSON RESOURCES LIMITED</t>
         </is>
       </c>
       <c r="E25" s="11" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>SE Asia / Pacific</t>
         </is>
       </c>
       <c r="F25" s="11" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="G25" s="11" t="inlineStr">
@@ -8222,32 +6410,32 @@
       </c>
       <c r="H25" s="11" t="inlineStr">
         <is>
-          <t>A2</t>
+          <t>A2+E</t>
         </is>
       </c>
       <c r="I25" s="11" t="inlineStr">
         <is>
-          <t>31%</t>
+          <t>29%</t>
         </is>
       </c>
       <c r="J25" s="11" t="inlineStr">
         <is>
-          <t>2.19×</t>
+          <t>2.26×</t>
         </is>
       </c>
       <c r="K25" s="11" t="inlineStr">
         <is>
-          <t>2.69×</t>
+          <t>2.80×</t>
         </is>
       </c>
       <c r="L25" s="11" t="inlineStr">
         <is>
-          <t>1.86×</t>
+          <t>1.93×</t>
         </is>
       </c>
       <c r="M25" s="11" t="inlineStr">
         <is>
-          <t>2.8×</t>
+          <t>3.2×</t>
         </is>
       </c>
     </row>
@@ -8262,22 +6450,22 @@
       </c>
       <c r="C26" s="14" t="inlineStr">
         <is>
-          <t>4170</t>
+          <t>PEX</t>
         </is>
       </c>
       <c r="D26" s="14" t="inlineStr">
         <is>
-          <t>Ｇ－ＫａｉｚｅｎＰＦ</t>
+          <t>PEEL MINING LIMITED</t>
         </is>
       </c>
       <c r="E26" s="14" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>SE Asia / Pacific</t>
         </is>
       </c>
       <c r="F26" s="14" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="G26" s="14" t="inlineStr">
@@ -8287,32 +6475,32 @@
       </c>
       <c r="H26" s="14" t="inlineStr">
         <is>
-          <t>A2</t>
+          <t>A2+E</t>
         </is>
       </c>
       <c r="I26" s="14" t="inlineStr">
         <is>
-          <t>31%</t>
+          <t>29%</t>
         </is>
       </c>
       <c r="J26" s="14" t="inlineStr">
         <is>
-          <t>2.19×</t>
+          <t>2.26×</t>
         </is>
       </c>
       <c r="K26" s="14" t="inlineStr">
         <is>
-          <t>2.69×</t>
+          <t>2.80×</t>
         </is>
       </c>
       <c r="L26" s="14" t="inlineStr">
         <is>
-          <t>1.86×</t>
+          <t>1.93×</t>
         </is>
       </c>
       <c r="M26" s="14" t="inlineStr">
         <is>
-          <t>2.8×</t>
+          <t>3.2×</t>
         </is>
       </c>
     </row>
@@ -8320,29 +6508,29 @@
       <c r="A27" s="9" t="n">
         <v>23</v>
       </c>
-      <c r="B27" s="10" t="inlineStr">
-        <is>
-          <t>REAL</t>
+      <c r="B27" s="15" t="inlineStr">
+        <is>
+          <t>PROXY</t>
         </is>
       </c>
       <c r="C27" s="11" t="inlineStr">
         <is>
-          <t>DFM:DSI</t>
+          <t>AIS</t>
         </is>
       </c>
       <c r="D27" s="11" t="inlineStr">
         <is>
-          <t>Drake &amp; Scull</t>
+          <t>AERIS RESOURCES LIMITED</t>
         </is>
       </c>
       <c r="E27" s="11" t="inlineStr">
         <is>
-          <t>MEA / Frontier</t>
+          <t>SE Asia / Pacific</t>
         </is>
       </c>
       <c r="F27" s="11" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="G27" s="11" t="inlineStr">
@@ -8352,32 +6540,32 @@
       </c>
       <c r="H27" s="11" t="inlineStr">
         <is>
-          <t>A2</t>
+          <t>A2+E</t>
         </is>
       </c>
       <c r="I27" s="11" t="inlineStr">
         <is>
-          <t>45%</t>
+          <t>29%</t>
         </is>
       </c>
       <c r="J27" s="11" t="inlineStr">
         <is>
-          <t>2.30×</t>
+          <t>2.26×</t>
         </is>
       </c>
       <c r="K27" s="11" t="inlineStr">
         <is>
-          <t>4.20×</t>
+          <t>2.80×</t>
         </is>
       </c>
       <c r="L27" s="11" t="inlineStr">
         <is>
-          <t>2.25×</t>
+          <t>1.93×</t>
         </is>
       </c>
       <c r="M27" s="11" t="inlineStr">
         <is>
-          <t>2.8×</t>
+          <t>3.2×</t>
         </is>
       </c>
     </row>
@@ -8385,29 +6573,29 @@
       <c r="A28" s="12" t="n">
         <v>24</v>
       </c>
-      <c r="B28" s="16" t="inlineStr">
-        <is>
-          <t>REAL</t>
+      <c r="B28" s="13" t="inlineStr">
+        <is>
+          <t>PROXY</t>
         </is>
       </c>
       <c r="C28" s="14" t="inlineStr">
         <is>
-          <t>BME:OHLA</t>
+          <t>ASM</t>
         </is>
       </c>
       <c r="D28" s="14" t="inlineStr">
         <is>
-          <t>OHLA (former OHL)</t>
+          <t>AUSTRALIAN STRATEGIC MATERIALS LIMITED</t>
         </is>
       </c>
       <c r="E28" s="14" t="inlineStr">
         <is>
-          <t>Continental Europe</t>
+          <t>SE Asia / Pacific</t>
         </is>
       </c>
       <c r="F28" s="14" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="G28" s="14" t="inlineStr">
@@ -8417,32 +6605,32 @@
       </c>
       <c r="H28" s="14" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2+E</t>
         </is>
       </c>
       <c r="I28" s="14" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>29%</t>
         </is>
       </c>
       <c r="J28" s="14" t="inlineStr">
         <is>
-          <t>2.40×</t>
+          <t>2.26×</t>
         </is>
       </c>
       <c r="K28" s="14" t="inlineStr">
         <is>
-          <t>4.50×</t>
+          <t>2.80×</t>
         </is>
       </c>
       <c r="L28" s="14" t="inlineStr">
         <is>
-          <t>2.35×</t>
+          <t>1.93×</t>
         </is>
       </c>
       <c r="M28" s="14" t="inlineStr">
         <is>
-          <t>2.7×</t>
+          <t>3.2×</t>
         </is>
       </c>
     </row>
@@ -8450,29 +6638,29 @@
       <c r="A29" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="B29" s="10" t="inlineStr">
-        <is>
-          <t>REAL</t>
+      <c r="B29" s="15" t="inlineStr">
+        <is>
+          <t>PROXY</t>
         </is>
       </c>
       <c r="C29" s="11" t="inlineStr">
         <is>
-          <t>KRX:241560</t>
+          <t>QUB</t>
         </is>
       </c>
       <c r="D29" s="11" t="inlineStr">
         <is>
-          <t>Doosan Bobcat → Doosan Robotics merger</t>
+          <t>QUBE HOLDINGS LIMITED</t>
         </is>
       </c>
       <c r="E29" s="11" t="inlineStr">
         <is>
-          <t>Korea</t>
+          <t>SE Asia / Pacific</t>
         </is>
       </c>
       <c r="F29" s="11" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="G29" s="11" t="inlineStr">
@@ -8482,32 +6670,32 @@
       </c>
       <c r="H29" s="11" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>A2+E</t>
         </is>
       </c>
       <c r="I29" s="11" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>29%</t>
         </is>
       </c>
       <c r="J29" s="11" t="inlineStr">
         <is>
-          <t>1.70×</t>
+          <t>2.26×</t>
         </is>
       </c>
       <c r="K29" s="11" t="inlineStr">
         <is>
-          <t>2.50×</t>
+          <t>2.80×</t>
         </is>
       </c>
       <c r="L29" s="11" t="inlineStr">
         <is>
-          <t>1.66×</t>
+          <t>1.93×</t>
         </is>
       </c>
       <c r="M29" s="11" t="inlineStr">
         <is>
-          <t>2.7×</t>
+          <t>3.2×</t>
         </is>
       </c>
     </row>
@@ -8550,13 +6738,13 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
     <col width="37" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
     <col width="8" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="36" customWidth="1" min="8" max="8"/>
+    <col width="27" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -8742,32 +6930,32 @@
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>NYSE:GGAL</t>
+          <t>ACF</t>
         </is>
       </c>
       <c r="C8" s="14" t="inlineStr">
         <is>
-          <t>Banco Galicia</t>
+          <t>ACROW LIMITED</t>
         </is>
       </c>
       <c r="D8" s="14" t="inlineStr">
         <is>
-          <t>Latin America</t>
+          <t>SE Asia / Pacific</t>
         </is>
       </c>
       <c r="E8" s="14" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="F8" s="14" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2+A1</t>
         </is>
       </c>
       <c r="G8" s="14" t="inlineStr">
         <is>
-          <t>3.6×</t>
+          <t>3.7×</t>
         </is>
       </c>
       <c r="H8" s="14" t="inlineStr">
@@ -8778,36 +6966,36 @@
     </row>
     <row r="9">
       <c r="A9" s="9" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>NYSE:PAM</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>Pampa Energía</t>
+          <t>MEMPHASYS LIMITED.</t>
         </is>
       </c>
       <c r="D9" s="11" t="inlineStr">
         <is>
-          <t>Latin America</t>
+          <t>SE Asia / Pacific</t>
         </is>
       </c>
       <c r="E9" s="11" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="F9" s="11" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2+B</t>
         </is>
       </c>
       <c r="G9" s="11" t="inlineStr">
         <is>
-          <t>3.4×</t>
+          <t>3.7×</t>
         </is>
       </c>
       <c r="H9" s="11" t="inlineStr">
@@ -8818,36 +7006,36 @@
     </row>
     <row r="10">
       <c r="A10" s="12" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>3544</t>
+          <t>NYSE:GGAL</t>
         </is>
       </c>
       <c r="C10" s="14" t="inlineStr">
         <is>
-          <t>サツドラＨＤ</t>
+          <t>Banco Galicia</t>
         </is>
       </c>
       <c r="D10" s="14" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Latin America</t>
         </is>
       </c>
       <c r="E10" s="14" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="F10" s="14" t="inlineStr">
         <is>
-          <t>A2+C</t>
+          <t>A1</t>
         </is>
       </c>
       <c r="G10" s="14" t="inlineStr">
         <is>
-          <t>3.2×</t>
+          <t>3.6×</t>
         </is>
       </c>
       <c r="H10" s="14" t="inlineStr">
@@ -8862,32 +7050,32 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>6897</t>
+          <t>NYSE:PAM</t>
         </is>
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>ツインバード</t>
+          <t>Pampa Energía</t>
         </is>
       </c>
       <c r="D11" s="11" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Latin America</t>
         </is>
       </c>
       <c r="E11" s="11" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="F11" s="11" t="inlineStr">
         <is>
-          <t>A2+C</t>
+          <t>A1</t>
         </is>
       </c>
       <c r="G11" s="11" t="inlineStr">
         <is>
-          <t>3.2×</t>
+          <t>3.4×</t>
         </is>
       </c>
       <c r="H11" s="11" t="inlineStr">
@@ -8902,12 +7090,12 @@
       </c>
       <c r="B12" s="14" t="inlineStr">
         <is>
-          <t>4951</t>
+          <t>3544</t>
         </is>
       </c>
       <c r="C12" s="14" t="inlineStr">
         <is>
-          <t>エステー</t>
+          <t>サツドラＨＤ</t>
         </is>
       </c>
       <c r="D12" s="14" t="inlineStr">
@@ -8942,12 +7130,12 @@
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>3659</t>
+          <t>6897</t>
         </is>
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>ネクソン</t>
+          <t>ツインバード</t>
         </is>
       </c>
       <c r="D13" s="11" t="inlineStr">
@@ -8978,16 +7166,16 @@
     </row>
     <row r="14">
       <c r="A14" s="12" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="B14" s="14" t="inlineStr">
         <is>
-          <t>8074</t>
+          <t>4951</t>
         </is>
       </c>
       <c r="C14" s="14" t="inlineStr">
         <is>
-          <t>ＹＵＡＳＡ</t>
+          <t>エステー</t>
         </is>
       </c>
       <c r="D14" s="14" t="inlineStr">
@@ -8997,37 +7185,37 @@
       </c>
       <c r="E14" s="14" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="F14" s="14" t="inlineStr">
         <is>
-          <t>A2</t>
+          <t>A2+C</t>
         </is>
       </c>
       <c r="G14" s="14" t="inlineStr">
         <is>
-          <t>2.8×</t>
+          <t>3.2×</t>
         </is>
       </c>
       <c r="H14" s="14" t="inlineStr">
         <is>
-          <t>Tier 2 — verify primary docs first</t>
+          <t>Tier 1 — hand-deepen ASAP</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="9" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>2198</t>
+          <t>3659</t>
         </is>
       </c>
       <c r="C15" s="11" t="inlineStr">
         <is>
-          <t>アイ・ケイ・ケイＨＤ</t>
+          <t>ネクソン</t>
         </is>
       </c>
       <c r="D15" s="11" t="inlineStr">
@@ -9037,47 +7225,47 @@
       </c>
       <c r="E15" s="11" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="F15" s="11" t="inlineStr">
         <is>
-          <t>A2</t>
+          <t>A2+C</t>
         </is>
       </c>
       <c r="G15" s="11" t="inlineStr">
         <is>
-          <t>2.8×</t>
+          <t>3.2×</t>
         </is>
       </c>
       <c r="H15" s="11" t="inlineStr">
         <is>
-          <t>Tier 2 — verify primary docs first</t>
+          <t>Tier 1 — hand-deepen ASAP</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="12" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="B16" s="14" t="inlineStr">
         <is>
-          <t>3454</t>
+          <t>DTZ</t>
         </is>
       </c>
       <c r="C16" s="14" t="inlineStr">
         <is>
-          <t>ファーストブラザーズ</t>
+          <t>DOTZ NANO LIMITED</t>
         </is>
       </c>
       <c r="D16" s="14" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>SE Asia / Pacific</t>
         </is>
       </c>
       <c r="E16" s="14" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="F16" s="14" t="inlineStr">
@@ -9087,37 +7275,37 @@
       </c>
       <c r="G16" s="14" t="inlineStr">
         <is>
-          <t>2.8×</t>
+          <t>3.2×</t>
         </is>
       </c>
       <c r="H16" s="14" t="inlineStr">
         <is>
-          <t>Tier 2 — verify primary docs first</t>
+          <t>Tier 1 — hand-deepen ASAP</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="9" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>3803</t>
+          <t>BMR</t>
         </is>
       </c>
       <c r="C17" s="11" t="inlineStr">
         <is>
-          <t>Ｇ－イメージ情</t>
+          <t>BALLYMORE RESOURCES LIMITED</t>
         </is>
       </c>
       <c r="D17" s="11" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>SE Asia / Pacific</t>
         </is>
       </c>
       <c r="E17" s="11" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="F17" s="11" t="inlineStr">
@@ -9127,37 +7315,37 @@
       </c>
       <c r="G17" s="11" t="inlineStr">
         <is>
-          <t>2.8×</t>
+          <t>3.2×</t>
         </is>
       </c>
       <c r="H17" s="11" t="inlineStr">
         <is>
-          <t>Tier 2 — verify primary docs first</t>
+          <t>Tier 1 — hand-deepen ASAP</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="12" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="B18" s="14" t="inlineStr">
         <is>
-          <t>4641</t>
+          <t>CQT</t>
         </is>
       </c>
       <c r="C18" s="14" t="inlineStr">
         <is>
-          <t>アルプス技</t>
+          <t>CONNEQT HEALTH LIMITED</t>
         </is>
       </c>
       <c r="D18" s="14" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>SE Asia / Pacific</t>
         </is>
       </c>
       <c r="E18" s="14" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="F18" s="14" t="inlineStr">
@@ -9167,37 +7355,37 @@
       </c>
       <c r="G18" s="14" t="inlineStr">
         <is>
-          <t>2.8×</t>
+          <t>3.2×</t>
         </is>
       </c>
       <c r="H18" s="14" t="inlineStr">
         <is>
-          <t>Tier 2 — verify primary docs first</t>
+          <t>Tier 1 — hand-deepen ASAP</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="9" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>4170</t>
+          <t>JLL</t>
         </is>
       </c>
       <c r="C19" s="11" t="inlineStr">
         <is>
-          <t>Ｇ－ＫａｉｚｅｎＰＦ</t>
+          <t>JINDALEE LITHIUM LIMITED</t>
         </is>
       </c>
       <c r="D19" s="11" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>SE Asia / Pacific</t>
         </is>
       </c>
       <c r="E19" s="11" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="F19" s="11" t="inlineStr">
@@ -9207,167 +7395,167 @@
       </c>
       <c r="G19" s="11" t="inlineStr">
         <is>
-          <t>2.8×</t>
+          <t>3.2×</t>
         </is>
       </c>
       <c r="H19" s="11" t="inlineStr">
         <is>
-          <t>Tier 2 — verify primary docs first</t>
+          <t>Tier 1 — hand-deepen ASAP</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="12" t="n">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="B20" s="14" t="inlineStr">
         <is>
-          <t>BME:TLGO</t>
+          <t>KSN</t>
         </is>
       </c>
       <c r="C20" s="14" t="inlineStr">
         <is>
-          <t>Talgo</t>
+          <t>KINGSTON RESOURCES LIMITED</t>
         </is>
       </c>
       <c r="D20" s="14" t="inlineStr">
         <is>
-          <t>Continental Europe</t>
+          <t>SE Asia / Pacific</t>
         </is>
       </c>
       <c r="E20" s="14" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="F20" s="14" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2</t>
         </is>
       </c>
       <c r="G20" s="14" t="inlineStr">
         <is>
-          <t>2.6×</t>
+          <t>3.2×</t>
         </is>
       </c>
       <c r="H20" s="14" t="inlineStr">
         <is>
-          <t>Tier 2 — verify primary docs first</t>
+          <t>Tier 1 — hand-deepen ASAP</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="9" t="n">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t>LSE:ASC</t>
+          <t>PNN</t>
         </is>
       </c>
       <c r="C21" s="11" t="inlineStr">
         <is>
-          <t>ASOS</t>
+          <t>POWER MINERALS LIMITED</t>
         </is>
       </c>
       <c r="D21" s="11" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>SE Asia / Pacific</t>
         </is>
       </c>
       <c r="E21" s="11" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="F21" s="11" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2</t>
         </is>
       </c>
       <c r="G21" s="11" t="inlineStr">
         <is>
-          <t>2.6×</t>
+          <t>3.2×</t>
         </is>
       </c>
       <c r="H21" s="11" t="inlineStr">
         <is>
-          <t>Tier 2 — verify primary docs first</t>
+          <t>Tier 1 — hand-deepen ASAP</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="12" t="n">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="B22" s="14" t="inlineStr">
         <is>
-          <t>TSX:CFW</t>
+          <t>ERM</t>
         </is>
       </c>
       <c r="C22" s="14" t="inlineStr">
         <is>
-          <t>Calfrac Well Services</t>
+          <t>EMMERSON RESOURCES LIMITED</t>
         </is>
       </c>
       <c r="D22" s="14" t="inlineStr">
         <is>
-          <t>United States/Canada</t>
+          <t>SE Asia / Pacific</t>
         </is>
       </c>
       <c r="E22" s="14" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="F22" s="14" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2+E</t>
         </is>
       </c>
       <c r="G22" s="14" t="inlineStr">
         <is>
-          <t>2.5×</t>
+          <t>3.2×</t>
         </is>
       </c>
       <c r="H22" s="14" t="inlineStr">
         <is>
-          <t>Tier 2 — verify primary docs first</t>
+          <t>Tier 1 — hand-deepen ASAP</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="9" t="n">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="B23" s="11" t="inlineStr">
         <is>
-          <t>KRX:028260</t>
+          <t>PEX</t>
         </is>
       </c>
       <c r="C23" s="11" t="inlineStr">
         <is>
-          <t>Samsung C&amp;T</t>
+          <t>PEEL MINING LIMITED</t>
         </is>
       </c>
       <c r="D23" s="11" t="inlineStr">
         <is>
-          <t>Korea</t>
+          <t>SE Asia / Pacific</t>
         </is>
       </c>
       <c r="E23" s="11" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="F23" s="11" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>A2+E</t>
         </is>
       </c>
       <c r="G23" s="11" t="inlineStr">
         <is>
-          <t>2.4×</t>
+          <t>3.2×</t>
         </is>
       </c>
       <c r="H23" s="11" t="inlineStr">
@@ -9378,41 +7566,41 @@
     </row>
     <row r="24">
       <c r="A24" s="12" t="n">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="B24" s="14" t="inlineStr">
         <is>
-          <t>LSE:AML</t>
+          <t>AIS</t>
         </is>
       </c>
       <c r="C24" s="14" t="inlineStr">
         <is>
-          <t>Aston Martin Lagonda</t>
+          <t>AERIS RESOURCES LIMITED</t>
         </is>
       </c>
       <c r="D24" s="14" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>SE Asia / Pacific</t>
         </is>
       </c>
       <c r="E24" s="14" t="inlineStr">
         <is>
-          <t>0.70</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="F24" s="14" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2+E</t>
         </is>
       </c>
       <c r="G24" s="14" t="inlineStr">
         <is>
-          <t>2.4×</t>
+          <t>3.2×</t>
         </is>
       </c>
       <c r="H24" s="14" t="inlineStr">
         <is>
-          <t>Tier 2 — verify primary docs first</t>
+          <t>Tier 1 — hand-deepen ASAP</t>
         </is>
       </c>
     </row>
@@ -17684,7 +15872,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D60"/>
+  <dimension ref="A1:D65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -17932,200 +16120,260 @@
     <row r="25">
       <c r="A25" s="20" t="inlineStr">
         <is>
-          <t>D13 Altman Z</t>
+          <t>D11 Consensus Ebitda Cagr Lo</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>15</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="20" t="inlineStr">
         <is>
+          <t>D11 Consensus Ebitda Cagr Hi</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="20" t="inlineStr">
+        <is>
+          <t>D13 Altman Z</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="20" t="inlineStr">
+        <is>
           <t>D14 Liquidity Quarters</t>
         </is>
       </c>
-      <c r="B26" s="5" t="inlineStr">
+      <c r="B28" s="5" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="4" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="20" t="inlineStr">
+        <is>
+          <t>D20 Crowd Check Analysts</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="20" t="inlineStr">
+        <is>
+          <t>D21 Sellside Conflict</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="20" t="inlineStr">
+        <is>
+          <t>D22 Days Since Recap</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>660</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
         <is>
           <t>Catalysts</t>
         </is>
       </c>
-      <c r="B28" s="19" t="n"/>
-      <c r="C28" s="19" t="n"/>
-      <c r="D28" s="19" t="n"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="8" t="inlineStr">
+      <c r="B33" s="19" t="n"/>
+      <c r="C33" s="19" t="n"/>
+      <c r="D33" s="19" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="8" t="inlineStr">
         <is>
           <t>Event</t>
         </is>
       </c>
-      <c r="B29" s="8" t="inlineStr">
+      <c r="B34" s="8" t="inlineStr">
         <is>
           <t>Window</t>
         </is>
       </c>
-      <c r="C29" s="8" t="inlineStr">
+      <c r="C34" s="8" t="inlineStr">
         <is>
           <t>P(yes)</t>
         </is>
       </c>
-      <c r="D29" s="8" t="inlineStr">
+      <c r="D34" s="8" t="inlineStr">
         <is>
           <t>Re-rate if yes / hit if no</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="32" customHeight="1">
-      <c r="A30" s="21" t="inlineStr">
+    <row r="35" ht="32" customHeight="1">
+      <c r="A35" s="21" t="inlineStr">
         <is>
           <t>FY2026 revenue trajectory tracking toward €500m FY2027</t>
         </is>
       </c>
-      <c r="B30" s="11" t="inlineStr">
+      <c r="B35" s="11" t="inlineStr">
         <is>
           <t>2026-07-01 → 2027-12-31</t>
         </is>
       </c>
-      <c r="C30" s="11" t="inlineStr">
+      <c r="C35" s="11" t="inlineStr">
         <is>
           <t>0.45</t>
         </is>
       </c>
-      <c r="D30" s="11" t="inlineStr">
+      <c r="D35" s="11" t="inlineStr">
         <is>
           <t>Up 3.0-6.0× / Down -0.2--0.4</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="32" customHeight="1">
-      <c r="A31" s="22" t="inlineStr">
+    <row r="36" ht="32" customHeight="1">
+      <c r="A36" s="22" t="inlineStr">
         <is>
           <t>EBITDA margin expansion toward 25%</t>
         </is>
       </c>
-      <c r="B31" s="14" t="inlineStr">
+      <c r="B36" s="14" t="inlineStr">
         <is>
           <t>2026-07-01 → 2027-12-31</t>
         </is>
       </c>
-      <c r="C31" s="14" t="inlineStr">
+      <c r="C36" s="14" t="inlineStr">
         <is>
           <t>0.4</t>
         </is>
       </c>
-      <c r="D31" s="14" t="inlineStr">
+      <c r="D36" s="14" t="inlineStr">
         <is>
           <t>Up 2.0-4.0× / Down -0.15--0.3</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="32" customHeight="1">
-      <c r="A32" s="21" t="inlineStr">
+    <row r="37" ht="32" customHeight="1">
+      <c r="A37" s="21" t="inlineStr">
         <is>
           <t>Niel/Lévy strategic action (digital-network roll-up, sale)</t>
         </is>
       </c>
-      <c r="B32" s="11" t="inlineStr">
+      <c r="B37" s="11" t="inlineStr">
         <is>
           <t>2026-07-01 → 2028-12-31</t>
         </is>
       </c>
-      <c r="C32" s="11" t="inlineStr">
+      <c r="C37" s="11" t="inlineStr">
         <is>
           <t>0.3</t>
         </is>
       </c>
-      <c r="D32" s="11" t="inlineStr">
+      <c r="D37" s="11" t="inlineStr">
         <is>
           <t>Up 2.5-5.0× / Down -0.1--0.15</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="32" customHeight="1">
-      <c r="A33" s="22" t="inlineStr">
+    <row r="38" ht="32" customHeight="1">
+      <c r="A38" s="22" t="inlineStr">
         <is>
           <t>Special dividend / share buyback from net-cash surplus</t>
         </is>
       </c>
-      <c r="B33" s="14" t="inlineStr">
+      <c r="B38" s="14" t="inlineStr">
         <is>
           <t>2027-01-01 → 2028-12-31</t>
         </is>
       </c>
-      <c r="C33" s="14" t="inlineStr">
+      <c r="C38" s="14" t="inlineStr">
         <is>
           <t>0.35</t>
         </is>
       </c>
-      <c r="D33" s="14" t="inlineStr">
+      <c r="D38" s="14" t="inlineStr">
         <is>
           <t>Up 1.2-1.5× / Down 0.0-0.0</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="4" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
         <is>
           <t>Triangulation (3-leg test)</t>
         </is>
       </c>
-      <c r="B35" s="19" t="n"/>
-      <c r="C35" s="19" t="n"/>
-      <c r="D35" s="19" t="n"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="20" t="inlineStr">
+      <c r="B40" s="19" t="n"/>
+      <c r="C40" s="19" t="n"/>
+      <c r="D40" s="19" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="20" t="inlineStr">
         <is>
           <t>Leg 1 — Valuation</t>
         </is>
       </c>
-      <c r="B36" s="5" t="inlineStr">
+      <c r="B41" s="5" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="20" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="20" t="inlineStr">
         <is>
           <t>Leg 2 — Game theory</t>
         </is>
       </c>
-      <c r="B37" s="5" t="inlineStr">
+      <c r="B42" s="5" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="20" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="20" t="inlineStr">
         <is>
           <t>Leg 3 — Revealed preference</t>
         </is>
       </c>
-      <c r="B38" s="5" t="inlineStr">
+      <c r="B43" s="5" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="20" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="20" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="B39" s="5" t="inlineStr">
+      <c r="B44" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">Leg 1: €60m EBITDA at ~€20-30m market cap = trades &lt;0.5x EV/EBITDA
 vs French digital-advertising peers 4-6x EV/EBITDA. Pure gap-closure
@@ -18142,157 +16390,157 @@
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="4" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
         <is>
           <t>Anchor</t>
         </is>
       </c>
-      <c r="B41" s="19" t="n"/>
-      <c r="C41" s="19" t="n"/>
-      <c r="D41" s="19" t="n"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="20" t="inlineStr">
-        <is>
-          <t>Parties</t>
-        </is>
-      </c>
-      <c r="B42" s="5" t="inlineStr">
-        <is>
-          <t>Maurice Lévy (Ycor), Xavier Niel (Ycor)</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="20" t="inlineStr">
-        <is>
-          <t>Stake (% est.)</t>
-        </is>
-      </c>
-      <c r="B43" s="5" t="inlineStr">
-        <is>
-          <t>64.8</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="4" t="inlineStr">
-        <is>
-          <t>Red flags</t>
-        </is>
-      </c>
-      <c r="B45" s="19" t="n"/>
-      <c r="C45" s="19" t="n"/>
-      <c r="D45" s="19" t="n"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="20" t="inlineStr">
-        <is>
-          <t>Triggered</t>
-        </is>
-      </c>
-      <c r="B46" s="5" t="inlineStr">
-        <is>
-          <t>None of 11 active</t>
-        </is>
-      </c>
+      <c r="B46" s="19" t="n"/>
+      <c r="C46" s="19" t="n"/>
+      <c r="D46" s="19" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="20" t="inlineStr">
         <is>
-          <t>Watch list</t>
+          <t>Parties</t>
         </is>
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>Microcap illiquidity is the practical constraint, not a structural red flag</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="4" t="inlineStr">
-        <is>
-          <t>Kill criteria</t>
-        </is>
-      </c>
-      <c r="B49" s="19" t="n"/>
-      <c r="C49" s="19" t="n"/>
-      <c r="D49" s="19" t="n"/>
+          <t>Maurice Lévy (Ycor), Xavier Niel (Ycor)</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="20" t="inlineStr">
+        <is>
+          <t>Stake (% est.)</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="inlineStr">
+        <is>
+          <t>64.8</t>
+        </is>
+      </c>
     </row>
     <row r="50">
-      <c r="A50" s="20" t="inlineStr">
-        <is>
-          <t>1.</t>
-        </is>
-      </c>
-      <c r="B50" s="5" t="inlineStr">
-        <is>
-          <t>FY2026 revenue down &gt;5% (suggests trajectory off target by ~€100m to plan)</t>
-        </is>
-      </c>
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>Red flags</t>
+        </is>
+      </c>
+      <c r="B50" s="19" t="n"/>
+      <c r="C50" s="19" t="n"/>
+      <c r="D50" s="19" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="20" t="inlineStr">
         <is>
-          <t>2.</t>
+          <t>Triggered</t>
         </is>
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>EBITDA margin compression below 15%</t>
+          <t>None of 11 active</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="20" t="inlineStr">
         <is>
+          <t>Watch list</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="inlineStr">
+        <is>
+          <t>Microcap illiquidity is the practical constraint, not a structural red flag</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>Kill criteria</t>
+        </is>
+      </c>
+      <c r="B54" s="19" t="n"/>
+      <c r="C54" s="19" t="n"/>
+      <c r="D54" s="19" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="20" t="inlineStr">
+        <is>
+          <t>1.</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="inlineStr">
+        <is>
+          <t>FY2026 revenue down &gt;5% (suggests trajectory off target by ~€100m to plan)</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="20" t="inlineStr">
+        <is>
+          <t>2.</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="inlineStr">
+        <is>
+          <t>EBITDA margin compression below 15%</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="20" t="inlineStr">
+        <is>
           <t>3.</t>
         </is>
       </c>
-      <c r="B52" s="5" t="inlineStr">
+      <c r="B57" s="5" t="inlineStr">
         <is>
           <t>Net cash falls below €30m without explanation</t>
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="20" t="inlineStr">
+    <row r="58">
+      <c r="A58" s="20" t="inlineStr">
         <is>
           <t>4.</t>
         </is>
       </c>
-      <c r="B53" s="5" t="inlineStr">
+      <c r="B58" s="5" t="inlineStr">
         <is>
           <t>Niel or Lévy reduces Ycor stake</t>
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="20" t="inlineStr">
+    <row r="59">
+      <c r="A59" s="20" t="inlineStr">
         <is>
           <t>5.</t>
         </is>
       </c>
-      <c r="B54" s="5" t="inlineStr">
+      <c r="B59" s="5" t="inlineStr">
         <is>
           <t>Second dilutive event</t>
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="4" t="inlineStr">
+    <row r="61">
+      <c r="A61" s="4" t="inlineStr">
         <is>
           <t>Pre-mortem</t>
         </is>
       </c>
-      <c r="B56" s="19" t="n"/>
-      <c r="C56" s="19" t="n"/>
-      <c r="D56" s="19" t="n"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="20" t="inlineStr"/>
-      <c r="B57" s="5" t="inlineStr">
+      <c r="B61" s="19" t="n"/>
+      <c r="C61" s="19" t="n"/>
+      <c r="D61" s="19" t="n"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="20" t="inlineStr"/>
+      <c r="B62" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">It is end-2028 and LOCAL is down 70% from current ~€0.07-0.08
 microcap level.
@@ -18312,19 +16560,19 @@
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="4" t="inlineStr">
+    <row r="64">
+      <c r="A64" s="4" t="inlineStr">
         <is>
           <t>Tier rationale</t>
         </is>
       </c>
-      <c r="B59" s="19" t="n"/>
-      <c r="C59" s="19" t="n"/>
-      <c r="D59" s="19" t="n"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="20" t="inlineStr"/>
-      <c r="B60" s="5" t="inlineStr">
+      <c r="B64" s="19" t="n"/>
+      <c r="C64" s="19" t="n"/>
+      <c r="D64" s="19" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="20" t="inlineStr"/>
+      <c r="B65" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">Bucket A (listed common is the trade), Archetype E (French accelerated
 safeguard) + A1 (Ycor reserved + rights). Triangulation 3/3.
@@ -18352,49 +16600,54 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="43">
+  <mergeCells count="48">
     <mergeCell ref="B11:D11"/>
     <mergeCell ref="B42:D42"/>
-    <mergeCell ref="B60:D60"/>
     <mergeCell ref="B23:D23"/>
-    <mergeCell ref="A35:D35"/>
     <mergeCell ref="A4:D4"/>
     <mergeCell ref="B8:D8"/>
     <mergeCell ref="B57:D57"/>
-    <mergeCell ref="B53:D53"/>
-    <mergeCell ref="A28:D28"/>
-    <mergeCell ref="B38:D38"/>
+    <mergeCell ref="B44:D44"/>
+    <mergeCell ref="B29:D29"/>
     <mergeCell ref="B10:D10"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="A40:D40"/>
     <mergeCell ref="B19:D19"/>
-    <mergeCell ref="B37:D37"/>
     <mergeCell ref="B9:D9"/>
-    <mergeCell ref="A59:D59"/>
-    <mergeCell ref="A49:D49"/>
+    <mergeCell ref="A64:D64"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="B65:D65"/>
     <mergeCell ref="B15:D15"/>
+    <mergeCell ref="B55:D55"/>
     <mergeCell ref="B6:D6"/>
     <mergeCell ref="B24:D24"/>
     <mergeCell ref="B51:D51"/>
     <mergeCell ref="B20:D20"/>
-    <mergeCell ref="A45:D45"/>
     <mergeCell ref="B5:D5"/>
-    <mergeCell ref="B36:D36"/>
-    <mergeCell ref="B50:D50"/>
+    <mergeCell ref="A61:D61"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="A54:D54"/>
     <mergeCell ref="B26:D26"/>
-    <mergeCell ref="A41:D41"/>
+    <mergeCell ref="B62:D62"/>
     <mergeCell ref="B7:D7"/>
     <mergeCell ref="B25:D25"/>
+    <mergeCell ref="A46:D46"/>
     <mergeCell ref="B47:D47"/>
     <mergeCell ref="B16:D16"/>
-    <mergeCell ref="B54:D54"/>
     <mergeCell ref="A18:D18"/>
-    <mergeCell ref="A56:D56"/>
-    <mergeCell ref="B46:D46"/>
+    <mergeCell ref="B59:D59"/>
+    <mergeCell ref="B31:D31"/>
+    <mergeCell ref="A50:D50"/>
     <mergeCell ref="B22:D22"/>
+    <mergeCell ref="B27:D27"/>
+    <mergeCell ref="B56:D56"/>
+    <mergeCell ref="B58:D58"/>
     <mergeCell ref="B52:D52"/>
     <mergeCell ref="B21:D21"/>
+    <mergeCell ref="A33:D33"/>
     <mergeCell ref="B43:D43"/>
     <mergeCell ref="B12:D12"/>
-    <mergeCell ref="B39:D39"/>
+    <mergeCell ref="B48:D48"/>
     <mergeCell ref="A14:D14"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/output/cyclepapa_risk_reward_workbook.xlsx
+++ b/output/cyclepapa_risk_reward_workbook.xlsx
@@ -18,11 +18,7 @@
     <sheet name="LOCAL" sheetId="9" state="visible" r:id="rId9"/>
     <sheet name="LAC" sheetId="10" state="visible" r:id="rId10"/>
     <sheet name="SZG" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="TKA" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="GTCO" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="ELUX-B" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="6305" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="Methodology" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="Methodology" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -605,7 +601,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Generated 2026-06-21</t>
+          <t>Generated 2026-06-22</t>
         </is>
       </c>
     </row>
@@ -2212,2632 +2208,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D55"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="60" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Thyssenkrupp AG (Steel Europe)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>TKA  ·  DE  ·  Bucket A  ·  Archetype A1, A2, H  ·  Tier 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>Risk-reward snapshot</t>
-        </is>
-      </c>
-      <c r="B4" s="19" t="n"/>
-      <c r="C4" s="19" t="n"/>
-      <c r="D4" s="19" t="n"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="20" t="inlineStr">
-        <is>
-          <t>Expected EV×</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>2.34×</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="20" t="inlineStr">
-        <is>
-          <t>Bear / Base / Bull return</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t>0.55× / 2.30× / 4.20×</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="20" t="inlineStr">
-        <is>
-          <t>Bear loss</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>45%</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="20" t="inlineStr">
-        <is>
-          <t>Skew (upside/downside)</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>7.1×</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="20" t="inlineStr">
-        <is>
-          <t>Reward/Risk ratio</t>
-        </is>
-      </c>
-      <c r="B9" s="5" t="inlineStr">
-        <is>
-          <t>3.0×</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="20" t="inlineStr">
-        <is>
-          <t>Portfolio weight</t>
-        </is>
-      </c>
-      <c r="B10" s="5" t="inlineStr">
-        <is>
-          <t>3.00%</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="20" t="inlineStr">
-        <is>
-          <t>Cluster</t>
-        </is>
-      </c>
-      <c r="B11" s="5" t="inlineStr">
-        <is>
-          <t>EU_industrial_policy</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="20" t="inlineStr">
-        <is>
-          <t>Primary factor</t>
-        </is>
-      </c>
-      <c r="B12" s="5" t="inlineStr">
-        <is>
-          <t>policy</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t>Deal</t>
-        </is>
-      </c>
-      <c r="B14" s="19" t="n"/>
-      <c r="C14" s="19" t="n"/>
-      <c r="D14" s="19" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="20" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="B15" s="5" t="inlineStr">
-        <is>
-          <t>2024-07-04</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="20" t="inlineStr">
-        <is>
-          <t>Mechanic</t>
-        </is>
-      </c>
-      <c r="B16" s="5" t="inlineStr">
-        <is>
-          <t>A1 + A2 + H — Daniel Kretinsky's EPCG took 20pct stake in Thyssenkrupp Steel Europe subsidiary July 2024 (€1.0-1.5bn implied valuation). JV with German State pending (Lower Saxony + federal govt). €2bn EU state aid for green-steel transition approved Jul 2023 (SA.103861). Multi-decade decarbonisation pivot: Hydrogen-DRI plant Salzgitter site; Marine Systems carve-out worth €1-1.5bn separately. Iduna Aurelius industrial JV pending under EU IAA framework.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="4" t="inlineStr">
-        <is>
-          <t>Scorecard</t>
-        </is>
-      </c>
-      <c r="B18" s="19" t="n"/>
-      <c r="C18" s="19" t="n"/>
-      <c r="D18" s="19" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="20" t="inlineStr">
-        <is>
-          <t>D4 Dilution Pct</t>
-        </is>
-      </c>
-      <c r="B19" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="20" t="inlineStr">
-        <is>
-          <t>D9 Alignment Gap</t>
-        </is>
-      </c>
-      <c r="B20" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="20" t="inlineStr">
-        <is>
-          <t>D11 Consensus Ebitda Cagr</t>
-        </is>
-      </c>
-      <c r="B21" s="5" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="20" t="inlineStr">
-        <is>
-          <t>D14 Liquidity Quarters</t>
-        </is>
-      </c>
-      <c r="B22" s="5" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="4" t="inlineStr">
-        <is>
-          <t>Catalysts</t>
-        </is>
-      </c>
-      <c r="B24" s="19" t="n"/>
-      <c r="C24" s="19" t="n"/>
-      <c r="D24" s="19" t="n"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="8" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B25" s="8" t="inlineStr">
-        <is>
-          <t>Window</t>
-        </is>
-      </c>
-      <c r="C25" s="8" t="inlineStr">
-        <is>
-          <t>P(yes)</t>
-        </is>
-      </c>
-      <c r="D25" s="8" t="inlineStr">
-        <is>
-          <t>Re-rate if yes / hit if no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="32" customHeight="1">
-      <c r="A26" s="21" t="inlineStr">
-        <is>
-          <t>Thyssenkrupp Steel JV with German state closes (Kretinsky 50pct / state 50pct)</t>
-        </is>
-      </c>
-      <c r="B26" s="11" t="inlineStr">
-        <is>
-          <t>2026-09-01 → 2027-09-30</t>
-        </is>
-      </c>
-      <c r="C26" s="11" t="inlineStr">
-        <is>
-          <t>0.55</t>
-        </is>
-      </c>
-      <c r="D26" s="11" t="inlineStr">
-        <is>
-          <t>Up 1.6-2.4× / Down -0.2--0.3</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="32" customHeight="1">
-      <c r="A27" s="22" t="inlineStr">
-        <is>
-          <t>Marine Systems carve-out / IPO completion</t>
-        </is>
-      </c>
-      <c r="B27" s="14" t="inlineStr">
-        <is>
-          <t>2026-09-01 → 2027-12-31</t>
-        </is>
-      </c>
-      <c r="C27" s="14" t="inlineStr">
-        <is>
-          <t>0.55</t>
-        </is>
-      </c>
-      <c r="D27" s="14" t="inlineStr">
-        <is>
-          <t>Up 1.4-1.8× / Down -0.05--0.1</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="32" customHeight="1">
-      <c r="A28" s="21" t="inlineStr">
-        <is>
-          <t>European steel cycle inflection (HRC &gt;€600/t)</t>
-        </is>
-      </c>
-      <c r="B28" s="11" t="inlineStr">
-        <is>
-          <t>2026-06-01 → 2028-06-30</t>
-        </is>
-      </c>
-      <c r="C28" s="11" t="inlineStr">
-        <is>
-          <t>0.5</t>
-        </is>
-      </c>
-      <c r="D28" s="11" t="inlineStr">
-        <is>
-          <t>Up 1.5-2.2× / Down -0.2--0.3</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="32" customHeight="1">
-      <c r="A29" s="22" t="inlineStr">
-        <is>
-          <t>SALCOS first green-steel production at converted Duisburg blast furnace</t>
-        </is>
-      </c>
-      <c r="B29" s="14" t="inlineStr">
-        <is>
-          <t>2026-12-01 → 2027-12-31</t>
-        </is>
-      </c>
-      <c r="C29" s="14" t="inlineStr">
-        <is>
-          <t>0.55</t>
-        </is>
-      </c>
-      <c r="D29" s="14" t="inlineStr">
-        <is>
-          <t>Up 1.3-1.8× / Down -0.15--0.2</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="4" t="inlineStr">
-        <is>
-          <t>Triangulation (3-leg test)</t>
-        </is>
-      </c>
-      <c r="B31" s="19" t="n"/>
-      <c r="C31" s="19" t="n"/>
-      <c r="D31" s="19" t="n"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="20" t="inlineStr">
-        <is>
-          <t>Leg 1 — Valuation</t>
-        </is>
-      </c>
-      <c r="B32" s="5" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="20" t="inlineStr">
-        <is>
-          <t>Leg 2 — Game theory</t>
-        </is>
-      </c>
-      <c r="B33" s="5" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="20" t="inlineStr">
-        <is>
-          <t>Leg 3 — Revealed preference</t>
-        </is>
-      </c>
-      <c r="B34" s="5" t="inlineStr">
-        <is>
-          <t>partial</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="20" t="inlineStr">
-        <is>
-          <t>Notes</t>
-        </is>
-      </c>
-      <c r="B35" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Leg 1: 0.4x book with €2bn approved state aid + Marine
-Systems €1-1.5bn carve-out implies SOTP gap to ~€4-5bn vs
-current cap €3.2bn.
-Leg 2: Kretinsky 20pct in Steel sub + Krupp-Stiftung 21pct
-in parent = aligned cap-stack.
-Leg 3: PARTIAL — Kretinsky stake = revealed preference;
-KfW second-tranche commit not yet placed; Carlyle Marine
-interest is signal but not signed.
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="4" t="inlineStr">
-        <is>
-          <t>Anchor</t>
-        </is>
-      </c>
-      <c r="B37" s="19" t="n"/>
-      <c r="C37" s="19" t="n"/>
-      <c r="D37" s="19" t="n"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="20" t="inlineStr">
-        <is>
-          <t>Parties</t>
-        </is>
-      </c>
-      <c r="B38" s="5" t="inlineStr">
-        <is>
-          <t>EPCG / Daniel Kretinsky, German Federal State + Lower Saxony, Krupp-Stiftung foundation (21pct legacy)</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="20" t="inlineStr">
-        <is>
-          <t>Stake (% est.)</t>
-        </is>
-      </c>
-      <c r="B39" s="5" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="4" t="inlineStr">
-        <is>
-          <t>Red flags</t>
-        </is>
-      </c>
-      <c r="B41" s="19" t="n"/>
-      <c r="C41" s="19" t="n"/>
-      <c r="D41" s="19" t="n"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="20" t="inlineStr">
-        <is>
-          <t>Triggered</t>
-        </is>
-      </c>
-      <c r="B42" s="5" t="inlineStr">
-        <is>
-          <t>None of 11 active</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="20" t="inlineStr">
-        <is>
-          <t>Watch list</t>
-        </is>
-      </c>
-      <c r="B43" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="4" t="inlineStr">
-        <is>
-          <t>Kill criteria</t>
-        </is>
-      </c>
-      <c r="B45" s="19" t="n"/>
-      <c r="C45" s="19" t="n"/>
-      <c r="D45" s="19" t="n"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="20" t="inlineStr">
-        <is>
-          <t>1.</t>
-        </is>
-      </c>
-      <c r="B46" s="5" t="inlineStr">
-        <is>
-          <t>Kretinsky / state JV terms materially worsen (state share &lt;40pct)</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="20" t="inlineStr">
-        <is>
-          <t>2.</t>
-        </is>
-      </c>
-      <c r="B47" s="5" t="inlineStr">
-        <is>
-          <t>SALCOS Phase 1 slips beyond mid-2027</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="20" t="inlineStr">
-        <is>
-          <t>3.</t>
-        </is>
-      </c>
-      <c r="B48" s="5" t="inlineStr">
-        <is>
-          <t>CBAM materially watered down by EU Council</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="20" t="inlineStr">
-        <is>
-          <t>4.</t>
-        </is>
-      </c>
-      <c r="B49" s="5" t="inlineStr">
-        <is>
-          <t>Marine Systems carve-out cancelled or distressed sale</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="4" t="inlineStr">
-        <is>
-          <t>Pre-mortem</t>
-        </is>
-      </c>
-      <c r="B51" s="19" t="n"/>
-      <c r="C51" s="19" t="n"/>
-      <c r="D51" s="19" t="n"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="20" t="inlineStr"/>
-      <c r="B52" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">It is end-2027 and TKA is down 60pct from current ~€5.
-Most likely: Steel-JV negotiations stalled on state commitment;
-Marine Systems carve-out priced at distressed multiple; SALCOS
-cost overran by €1bn; Chinese steel dumping intensified; multiple
-to 0.3x book; another asset disposal at distressed terms.
-Second most likely: EU IAA fiscal envelope cut in EU budget
-negotiation; KfW declined; SALCOS deferred.
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="4" t="inlineStr">
-        <is>
-          <t>Tier rationale</t>
-        </is>
-      </c>
-      <c r="B54" s="19" t="n"/>
-      <c r="C54" s="19" t="n"/>
-      <c r="D54" s="19" t="n"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="20" t="inlineStr"/>
-      <c r="B55" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bucket A, Archetype A1 (Kretinsky 20pct + Krupp-Stiftung 21pct
-aligned anchors) + A2 (EU state aid €2bn) + H (governance reset
-via Steel-JV restructure). Universe score 0.95 = 7th-highest;
-multi-leg catalyst structure puts it in Tier 1 (4 dated catalysts
-+ 2 floors).
-</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="38">
-    <mergeCell ref="B11:D11"/>
-    <mergeCell ref="B42:D42"/>
-    <mergeCell ref="A4:D4"/>
-    <mergeCell ref="B8:D8"/>
-    <mergeCell ref="B38:D38"/>
-    <mergeCell ref="B34:D34"/>
-    <mergeCell ref="B10:D10"/>
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="A31:D31"/>
-    <mergeCell ref="B49:D49"/>
-    <mergeCell ref="B9:D9"/>
-    <mergeCell ref="A24:D24"/>
-    <mergeCell ref="A51:D51"/>
-    <mergeCell ref="B15:D15"/>
-    <mergeCell ref="B55:D55"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="B20:D20"/>
-    <mergeCell ref="B33:D33"/>
-    <mergeCell ref="A45:D45"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="B32:D32"/>
-    <mergeCell ref="B35:D35"/>
-    <mergeCell ref="A54:D54"/>
-    <mergeCell ref="A41:D41"/>
-    <mergeCell ref="B7:D7"/>
-    <mergeCell ref="B47:D47"/>
-    <mergeCell ref="B16:D16"/>
-    <mergeCell ref="A37:D37"/>
-    <mergeCell ref="A18:D18"/>
-    <mergeCell ref="B46:D46"/>
-    <mergeCell ref="B22:D22"/>
-    <mergeCell ref="B52:D52"/>
-    <mergeCell ref="B21:D21"/>
-    <mergeCell ref="B43:D43"/>
-    <mergeCell ref="B12:D12"/>
-    <mergeCell ref="B39:D39"/>
-    <mergeCell ref="B48:D48"/>
-    <mergeCell ref="A14:D14"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D54"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="60" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Guaranty Trust Holding Company</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>GTCO  ·  NG  ·  Bucket A  ·  Archetype G, A1  ·  Tier 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>Risk-reward snapshot</t>
-        </is>
-      </c>
-      <c r="B4" s="19" t="n"/>
-      <c r="C4" s="19" t="n"/>
-      <c r="D4" s="19" t="n"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="20" t="inlineStr">
-        <is>
-          <t>Expected EV×</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>2.15×</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="20" t="inlineStr">
-        <is>
-          <t>Bear / Base / Bull return</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t>0.60× / 2.10× / 3.80×</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="20" t="inlineStr">
-        <is>
-          <t>Bear loss</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>40%</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="20" t="inlineStr">
-        <is>
-          <t>Skew (upside/downside)</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>7.0×</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="20" t="inlineStr">
-        <is>
-          <t>Reward/Risk ratio</t>
-        </is>
-      </c>
-      <c r="B9" s="5" t="inlineStr">
-        <is>
-          <t>2.9×</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="20" t="inlineStr">
-        <is>
-          <t>Portfolio weight</t>
-        </is>
-      </c>
-      <c r="B10" s="5" t="inlineStr">
-        <is>
-          <t>3.00%</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="20" t="inlineStr">
-        <is>
-          <t>Cluster</t>
-        </is>
-      </c>
-      <c r="B11" s="5" t="inlineStr">
-        <is>
-          <t>EM_bank</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="20" t="inlineStr">
-        <is>
-          <t>Primary factor</t>
-        </is>
-      </c>
-      <c r="B12" s="5" t="inlineStr">
-        <is>
-          <t>idiosyncratic</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t>Deal</t>
-        </is>
-      </c>
-      <c r="B14" s="19" t="n"/>
-      <c r="C14" s="19" t="n"/>
-      <c r="D14" s="19" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="20" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="B15" s="5" t="inlineStr">
-        <is>
-          <t>2025-11</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="20" t="inlineStr">
-        <is>
-          <t>Mechanic</t>
-        </is>
-      </c>
-      <c r="B16" s="5" t="inlineStr">
-        <is>
-          <t>G — Central Bank of Nigeria mandated capital floor of ₦500bn for international-licensed banks by 31 March 2026. GTCO recapped via ₦209bn local rights + ₦366bn LSE primary listing at ₦70 (2.28bn new shares). Total ₦575bn raised. Sector-wide CBN floor triggered ₦4.6tn in raises across all major Nigerian banks. CAR 15.20pct; Tier-1 capital +21pct YoY. Trades single-digit P/E + &lt;1x book despite &gt;20pct ROE due to Naira FX volatility.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="4" t="inlineStr">
-        <is>
-          <t>Scorecard</t>
-        </is>
-      </c>
-      <c r="B18" s="19" t="n"/>
-      <c r="C18" s="19" t="n"/>
-      <c r="D18" s="19" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="20" t="inlineStr">
-        <is>
-          <t>D4 Dilution Pct</t>
-        </is>
-      </c>
-      <c r="B19" s="5" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="20" t="inlineStr">
-        <is>
-          <t>D9 Alignment Gap</t>
-        </is>
-      </c>
-      <c r="B20" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="20" t="inlineStr">
-        <is>
-          <t>D11 Consensus Ebitda Cagr</t>
-        </is>
-      </c>
-      <c r="B21" s="5" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="20" t="inlineStr">
-        <is>
-          <t>D14 Liquidity Quarters</t>
-        </is>
-      </c>
-      <c r="B22" s="5" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="4" t="inlineStr">
-        <is>
-          <t>Catalysts</t>
-        </is>
-      </c>
-      <c r="B24" s="19" t="n"/>
-      <c r="C24" s="19" t="n"/>
-      <c r="D24" s="19" t="n"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="8" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B25" s="8" t="inlineStr">
-        <is>
-          <t>Window</t>
-        </is>
-      </c>
-      <c r="C25" s="8" t="inlineStr">
-        <is>
-          <t>P(yes)</t>
-        </is>
-      </c>
-      <c r="D25" s="8" t="inlineStr">
-        <is>
-          <t>Re-rate if yes / hit if no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="32" customHeight="1">
-      <c r="A26" s="21" t="inlineStr">
-        <is>
-          <t>Naira stabilisation + FX policy normalisation</t>
-        </is>
-      </c>
-      <c r="B26" s="11" t="inlineStr">
-        <is>
-          <t>2026-06-01 → 2027-12-31</t>
-        </is>
-      </c>
-      <c r="C26" s="11" t="inlineStr">
-        <is>
-          <t>0.5</t>
-        </is>
-      </c>
-      <c r="D26" s="11" t="inlineStr">
-        <is>
-          <t>Up 1.6-2.5× / Down -0.2--0.3</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="32" customHeight="1">
-      <c r="A27" s="22" t="inlineStr">
-        <is>
-          <t>Sector consolidation — Nigerian smaller banks fail compliance</t>
-        </is>
-      </c>
-      <c r="B27" s="14" t="inlineStr">
-        <is>
-          <t>2026-04-01 → 2027-12-31</t>
-        </is>
-      </c>
-      <c r="C27" s="14" t="inlineStr">
-        <is>
-          <t>0.45</t>
-        </is>
-      </c>
-      <c r="D27" s="14" t="inlineStr">
-        <is>
-          <t>Up 1.3-1.8× / Down -0.05--0.1</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="32" customHeight="1">
-      <c r="A28" s="21" t="inlineStr">
-        <is>
-          <t>Pan-African expansion (UEMOA + East African subsidiaries)</t>
-        </is>
-      </c>
-      <c r="B28" s="11" t="inlineStr">
-        <is>
-          <t>2026-09-01 → 2028-12-31</t>
-        </is>
-      </c>
-      <c r="C28" s="11" t="inlineStr">
-        <is>
-          <t>0.55</t>
-        </is>
-      </c>
-      <c r="D28" s="11" t="inlineStr">
-        <is>
-          <t>Up 1.3-1.8× / Down -0.1--0.2</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="32" customHeight="1">
-      <c r="A29" s="22" t="inlineStr">
-        <is>
-          <t>Dividend re-rate (current yield distorted by Naira)</t>
-        </is>
-      </c>
-      <c r="B29" s="14" t="inlineStr">
-        <is>
-          <t>2026-12-01 → 2028-12-31</t>
-        </is>
-      </c>
-      <c r="C29" s="14" t="inlineStr">
-        <is>
-          <t>0.55</t>
-        </is>
-      </c>
-      <c r="D29" s="14" t="inlineStr">
-        <is>
-          <t>Up 1.2-1.5× / Down 0.0-0.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="4" t="inlineStr">
-        <is>
-          <t>Triangulation (3-leg test)</t>
-        </is>
-      </c>
-      <c r="B31" s="19" t="n"/>
-      <c r="C31" s="19" t="n"/>
-      <c r="D31" s="19" t="n"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="20" t="inlineStr">
-        <is>
-          <t>Leg 1 — Valuation</t>
-        </is>
-      </c>
-      <c r="B32" s="5" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="20" t="inlineStr">
-        <is>
-          <t>Leg 2 — Game theory</t>
-        </is>
-      </c>
-      <c r="B33" s="5" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="20" t="inlineStr">
-        <is>
-          <t>Leg 3 — Revealed preference</t>
-        </is>
-      </c>
-      <c r="B34" s="5" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="20" t="inlineStr">
-        <is>
-          <t>Notes</t>
-        </is>
-      </c>
-      <c r="B35" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Leg 1: &lt;1x book at &gt;20pct ROE = &gt;25pct USD-adjusted earnings
-yield. Single-digit P/E.
-Leg 2: CBN-mandated capital floor = regulatory anchor;
-GTCO already over-complied; sector consolidation forces
-rivals to follow.
-Leg 3: LSE listing 2025 at ₦70 = revealed-preference floor
-by international institutional capital; UK pension fund
-interest demonstrates capital depth.
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="4" t="inlineStr">
-        <is>
-          <t>Anchor</t>
-        </is>
-      </c>
-      <c r="B37" s="19" t="n"/>
-      <c r="C37" s="19" t="n"/>
-      <c r="D37" s="19" t="n"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="20" t="inlineStr">
-        <is>
-          <t>Parties</t>
-        </is>
-      </c>
-      <c r="B38" s="5" t="inlineStr">
-        <is>
-          <t>GTCO retail + institutional float (LSE listing 2025), Pan-African pension + sovereign holders</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="20" t="inlineStr">
-        <is>
-          <t>Stake (% est.)</t>
-        </is>
-      </c>
-      <c r="B39" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="4" t="inlineStr">
-        <is>
-          <t>Red flags</t>
-        </is>
-      </c>
-      <c r="B41" s="19" t="n"/>
-      <c r="C41" s="19" t="n"/>
-      <c r="D41" s="19" t="n"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="20" t="inlineStr">
-        <is>
-          <t>Triggered</t>
-        </is>
-      </c>
-      <c r="B42" s="5" t="inlineStr">
-        <is>
-          <t>None of 11 active</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="20" t="inlineStr">
-        <is>
-          <t>Watch list</t>
-        </is>
-      </c>
-      <c r="B43" s="5" t="inlineStr">
-        <is>
-          <t>Naira FX volatility is the dominant variable</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="4" t="inlineStr">
-        <is>
-          <t>Kill criteria</t>
-        </is>
-      </c>
-      <c r="B45" s="19" t="n"/>
-      <c r="C45" s="19" t="n"/>
-      <c r="D45" s="19" t="n"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="20" t="inlineStr">
-        <is>
-          <t>1.</t>
-        </is>
-      </c>
-      <c r="B46" s="5" t="inlineStr">
-        <is>
-          <t>Naira devalues another 30pct+ over 12 months</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="20" t="inlineStr">
-        <is>
-          <t>2.</t>
-        </is>
-      </c>
-      <c r="B47" s="5" t="inlineStr">
-        <is>
-          <t>CBN-mandated forbearance escalates banking losses</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="20" t="inlineStr">
-        <is>
-          <t>3.</t>
-        </is>
-      </c>
-      <c r="B48" s="5" t="inlineStr">
-        <is>
-          <t>Heritage-Bank-style failure cascades across mid-tier</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="4" t="inlineStr">
-        <is>
-          <t>Pre-mortem</t>
-        </is>
-      </c>
-      <c r="B50" s="19" t="n"/>
-      <c r="C50" s="19" t="n"/>
-      <c r="D50" s="19" t="n"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="20" t="inlineStr"/>
-      <c r="B51" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Naira devalued to ₦3000/USD; GTCO USD-translated book and
-earnings collapsed; FX losses materialised; multiple
-contracted to 0.4x book.
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="4" t="inlineStr">
-        <is>
-          <t>Tier rationale</t>
-        </is>
-      </c>
-      <c r="B53" s="19" t="n"/>
-      <c r="C53" s="19" t="n"/>
-      <c r="D53" s="19" t="n"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="20" t="inlineStr"/>
-      <c r="B54" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bucket A, Archetype G (regulator-forced sector recap — canonical
-Yes Bank / Greek banks template) + A1 (LSE listing as sovereign-
-adjacent international float). Universe screen 0.79. Tier 1 on
-triangulation + dated regulatory floor + cleanest USD-adjusted
-asymmetric setup in MEA basket.
-</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="37">
-    <mergeCell ref="B11:D11"/>
-    <mergeCell ref="B42:D42"/>
-    <mergeCell ref="A53:D53"/>
-    <mergeCell ref="A4:D4"/>
-    <mergeCell ref="B8:D8"/>
-    <mergeCell ref="B38:D38"/>
-    <mergeCell ref="B34:D34"/>
-    <mergeCell ref="B10:D10"/>
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="A31:D31"/>
-    <mergeCell ref="B9:D9"/>
-    <mergeCell ref="A24:D24"/>
-    <mergeCell ref="B15:D15"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="B51:D51"/>
-    <mergeCell ref="B20:D20"/>
-    <mergeCell ref="B33:D33"/>
-    <mergeCell ref="A45:D45"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="B32:D32"/>
-    <mergeCell ref="B35:D35"/>
-    <mergeCell ref="A41:D41"/>
-    <mergeCell ref="B7:D7"/>
-    <mergeCell ref="B47:D47"/>
-    <mergeCell ref="B16:D16"/>
-    <mergeCell ref="B54:D54"/>
-    <mergeCell ref="A37:D37"/>
-    <mergeCell ref="A18:D18"/>
-    <mergeCell ref="B46:D46"/>
-    <mergeCell ref="A50:D50"/>
-    <mergeCell ref="B22:D22"/>
-    <mergeCell ref="B21:D21"/>
-    <mergeCell ref="B43:D43"/>
-    <mergeCell ref="B12:D12"/>
-    <mergeCell ref="B39:D39"/>
-    <mergeCell ref="B48:D48"/>
-    <mergeCell ref="A14:D14"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D65"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="60" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>AB Electrolux (Series B)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>ELUX-B  ·  SE  ·  Bucket A  ·  Archetype A1, D  ·  Tier 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>Risk-reward snapshot</t>
-        </is>
-      </c>
-      <c r="B4" s="19" t="n"/>
-      <c r="C4" s="19" t="n"/>
-      <c r="D4" s="19" t="n"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="20" t="inlineStr">
-        <is>
-          <t>Expected EV×</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>2.32×</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="20" t="inlineStr">
-        <is>
-          <t>Bear / Base / Bull return</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t>0.55× / 2.20× / 4.00×</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="20" t="inlineStr">
-        <is>
-          <t>Bear loss</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>45%</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="20" t="inlineStr">
-        <is>
-          <t>Skew (upside/downside)</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>6.7×</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="20" t="inlineStr">
-        <is>
-          <t>Reward/Risk ratio</t>
-        </is>
-      </c>
-      <c r="B9" s="5" t="inlineStr">
-        <is>
-          <t>2.9×</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="20" t="inlineStr">
-        <is>
-          <t>Portfolio weight</t>
-        </is>
-      </c>
-      <c r="B10" s="5" t="inlineStr">
-        <is>
-          <t>3.00%</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="20" t="inlineStr">
-        <is>
-          <t>Cluster</t>
-        </is>
-      </c>
-      <c r="B11" s="5" t="inlineStr">
-        <is>
-          <t>Nordic_consumer</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="20" t="inlineStr">
-        <is>
-          <t>Primary factor</t>
-        </is>
-      </c>
-      <c r="B12" s="5" t="inlineStr">
-        <is>
-          <t>multiple_norm</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t>Deal</t>
-        </is>
-      </c>
-      <c r="B14" s="19" t="n"/>
-      <c r="C14" s="19" t="n"/>
-      <c r="D14" s="19" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="20" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="B15" s="5" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="20" t="inlineStr">
-        <is>
-          <t>Mechanic</t>
-        </is>
-      </c>
-      <c r="B16" s="5" t="inlineStr">
-        <is>
-          <t>SEK 9,062m fully underwritten rights issue (subscription Jun 2-16, 2026); Investor AB (Wallenberg) subscribes pro-rata SEK 1.7bn + guarantees additional SEK 1.7bn = 37.56% of issue. Tied to strategic partnership with Midea for North America, global organization optimization, and footprint restructuring.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="4" t="inlineStr">
-        <is>
-          <t>Scorecard</t>
-        </is>
-      </c>
-      <c r="B18" s="19" t="n"/>
-      <c r="C18" s="19" t="n"/>
-      <c r="D18" s="19" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="20" t="inlineStr">
-        <is>
-          <t>D2 Issue Discount Pct</t>
-        </is>
-      </c>
-      <c r="B19" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="20" t="inlineStr">
-        <is>
-          <t>D3 Backstop Cost Pct</t>
-        </is>
-      </c>
-      <c r="B20" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="20" t="inlineStr">
-        <is>
-          <t>D4 Dilution Pct</t>
-        </is>
-      </c>
-      <c r="B21" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="20" t="inlineStr">
-        <is>
-          <t>D5 Delta Wam Months</t>
-        </is>
-      </c>
-      <c r="B22" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="20" t="inlineStr">
-        <is>
-          <t>D6 Debt Tranches Post</t>
-        </is>
-      </c>
-      <c r="B23" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="20" t="inlineStr">
-        <is>
-          <t>D7 Ucc Terminations Pm30D</t>
-        </is>
-      </c>
-      <c r="B24" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="20" t="inlineStr">
-        <is>
-          <t>D8 Mip Strike Over Recap</t>
-        </is>
-      </c>
-      <c r="B25" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="20" t="inlineStr">
-        <is>
-          <t>D9 Alignment Gap</t>
-        </is>
-      </c>
-      <c r="B26" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="20" t="inlineStr">
-        <is>
-          <t>D9B Anchor Premium To Recap</t>
-        </is>
-      </c>
-      <c r="B27" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="20" t="inlineStr">
-        <is>
-          <t>D9C Premium To Vwap</t>
-        </is>
-      </c>
-      <c r="B28" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="20" t="inlineStr">
-        <is>
-          <t>D9D Liquidation Recovery Pct</t>
-        </is>
-      </c>
-      <c r="B29" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="20" t="inlineStr">
-        <is>
-          <t>D11 Consensus Ebitda Cagr</t>
-        </is>
-      </c>
-      <c r="B30" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="20" t="inlineStr">
-        <is>
-          <t>D13 Altman Z</t>
-        </is>
-      </c>
-      <c r="B31" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="20" t="inlineStr">
-        <is>
-          <t>D14 Liquidity Quarters</t>
-        </is>
-      </c>
-      <c r="B32" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="4" t="inlineStr">
-        <is>
-          <t>Catalysts</t>
-        </is>
-      </c>
-      <c r="B34" s="19" t="n"/>
-      <c r="C34" s="19" t="n"/>
-      <c r="D34" s="19" t="n"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="8" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B35" s="8" t="inlineStr">
-        <is>
-          <t>Window</t>
-        </is>
-      </c>
-      <c r="C35" s="8" t="inlineStr">
-        <is>
-          <t>P(yes)</t>
-        </is>
-      </c>
-      <c r="D35" s="8" t="inlineStr">
-        <is>
-          <t>Re-rate if yes / hit if no</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="32" customHeight="1">
-      <c r="A36" s="21" t="inlineStr">
-        <is>
-          <t>Midea North America partnership operational ramp</t>
-        </is>
-      </c>
-      <c r="B36" s="11" t="inlineStr">
-        <is>
-          <t>2026-09-01 → 2027-12-31</t>
-        </is>
-      </c>
-      <c r="C36" s="11" t="inlineStr">
-        <is>
-          <t>0.55</t>
-        </is>
-      </c>
-      <c r="D36" s="11" t="inlineStr">
-        <is>
-          <t>Up 1.6-2.5× / Down -0.2--0.4</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="32" customHeight="1">
-      <c r="A37" s="22" t="inlineStr">
-        <is>
-          <t>Global organization &amp; footprint optimization completion</t>
-        </is>
-      </c>
-      <c r="B37" s="14" t="inlineStr">
-        <is>
-          <t>2026-06-01 → 2027-06-30</t>
-        </is>
-      </c>
-      <c r="C37" s="14" t="inlineStr">
-        <is>
-          <t>0.65</t>
-        </is>
-      </c>
-      <c r="D37" s="14" t="inlineStr">
-        <is>
-          <t>Up 1.4-2.0× / Down -0.15--0.3</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="32" customHeight="1">
-      <c r="A38" s="21" t="inlineStr">
-        <is>
-          <t>Appliance cycle (US housing + EU disinflation) bottom</t>
-        </is>
-      </c>
-      <c r="B38" s="11" t="inlineStr">
-        <is>
-          <t>2026-06-01 → 2027-06-30</t>
-        </is>
-      </c>
-      <c r="C38" s="11" t="inlineStr">
-        <is>
-          <t>0.55</t>
-        </is>
-      </c>
-      <c r="D38" s="11" t="inlineStr">
-        <is>
-          <t>Up 1.5-2.2× / Down -0.15--0.3</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="4" t="inlineStr">
-        <is>
-          <t>Triangulation (3-leg test)</t>
-        </is>
-      </c>
-      <c r="B40" s="19" t="n"/>
-      <c r="C40" s="19" t="n"/>
-      <c r="D40" s="19" t="n"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="20" t="inlineStr">
-        <is>
-          <t>Leg 1 — Valuation</t>
-        </is>
-      </c>
-      <c r="B41" s="5" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="20" t="inlineStr">
-        <is>
-          <t>Leg 2 — Game theory</t>
-        </is>
-      </c>
-      <c r="B42" s="5" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="20" t="inlineStr">
-        <is>
-          <t>Leg 3 — Revealed preference</t>
-        </is>
-      </c>
-      <c r="B43" s="5" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="20" t="inlineStr">
-        <is>
-          <t>Notes</t>
-        </is>
-      </c>
-      <c r="B44" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Leg 1: Appliance multiples compressed; Whirlpool/peers trade at
-distressed margins; Electrolux's mid-cycle EBITDA on its
-pre-collapse base implies material upside on multiple
-normalisation alone.
-Leg 2: Investor AB (Wallenberg) as backstop is the cleanest
-natural-owner Nordic anchor pattern; Midea as strategic JV
-partner is Archetype D customer-aligned anchor; fully
-underwritten = no rump risk; EGM passed May 27 = governance
-settled.
-Leg 3: Investor AB undertaking 37.56% of the issue (pro-rata
-+ guarantee) is the revealed-preference signal. They could
-have taken just pro-rata; the additional SEK 1.7bn guarantee
-on market terms is the asymmetric commitment.
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="4" t="inlineStr">
-        <is>
-          <t>Anchor</t>
-        </is>
-      </c>
-      <c r="B46" s="19" t="n"/>
-      <c r="C46" s="19" t="n"/>
-      <c r="D46" s="19" t="n"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="20" t="inlineStr">
-        <is>
-          <t>Parties</t>
-        </is>
-      </c>
-      <c r="B47" s="5" t="inlineStr">
-        <is>
-          <t>Investor AB (Wallenberg Foundations), Midea Group (strategic JV partner)</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="20" t="inlineStr">
-        <is>
-          <t>Stake (% est.)</t>
-        </is>
-      </c>
-      <c r="B48" s="5" t="inlineStr">
-        <is>
-          <t>17.94</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="4" t="inlineStr">
-        <is>
-          <t>Red flags</t>
-        </is>
-      </c>
-      <c r="B50" s="19" t="n"/>
-      <c r="C50" s="19" t="n"/>
-      <c r="D50" s="19" t="n"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="20" t="inlineStr">
-        <is>
-          <t>Triggered</t>
-        </is>
-      </c>
-      <c r="B51" s="5" t="inlineStr">
-        <is>
-          <t>None of 11 active</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="20" t="inlineStr">
-        <is>
-          <t>Watch list</t>
-        </is>
-      </c>
-      <c r="B52" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="4" t="inlineStr">
-        <is>
-          <t>Kill criteria</t>
-        </is>
-      </c>
-      <c r="B54" s="19" t="n"/>
-      <c r="C54" s="19" t="n"/>
-      <c r="D54" s="19" t="n"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="20" t="inlineStr">
-        <is>
-          <t>1.</t>
-        </is>
-      </c>
-      <c r="B55" s="5" t="inlineStr">
-        <is>
-          <t>Midea JV terminated or delayed beyond H1 2027</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="20" t="inlineStr">
-        <is>
-          <t>2.</t>
-        </is>
-      </c>
-      <c r="B56" s="5" t="inlineStr">
-        <is>
-          <t>US administration imposes punitive tariffs on China-affiliated JVs that void North America economics</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="20" t="inlineStr">
-        <is>
-          <t>3.</t>
-        </is>
-      </c>
-      <c r="B57" s="5" t="inlineStr">
-        <is>
-          <t>Investor AB sells beyond pro-rata commitment</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="20" t="inlineStr">
-        <is>
-          <t>4.</t>
-        </is>
-      </c>
-      <c r="B58" s="5" t="inlineStr">
-        <is>
-          <t>Cost-out programme misses Q2 FY27 milestone by &gt;25%</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="20" t="inlineStr">
-        <is>
-          <t>5.</t>
-        </is>
-      </c>
-      <c r="B59" s="5" t="inlineStr">
-        <is>
-          <t>Second equity raise needed within 18 months</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="4" t="inlineStr">
-        <is>
-          <t>Pre-mortem</t>
-        </is>
-      </c>
-      <c r="B61" s="19" t="n"/>
-      <c r="C61" s="19" t="n"/>
-      <c r="D61" s="19" t="n"/>
-    </row>
-    <row r="62">
-      <c r="A62" s="20" t="inlineStr"/>
-      <c r="B62" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">It is end-2027 and ELUX-B is down 70% from rights price.
-Most likely cause: Midea JV economics undermined by US-China
-trade frictions (tariff escalation, FDI screening, executive
-order action against Chinese ownership in North American
-consumer appliance market). Wallenberg held its position but
-growth thesis evaporated; legacy European appliance market
-did not recover as expected.
-Second-most-likely cause: Cost-out programme execution failed
-(factory transitions slipped; severance costs ballooned; one-off
-impairments cascaded). Q3 FY27 print missed materially; analyst
-downgrades cascaded.
-Where this would show up first: US executive-order activity on
-Chinese appliance JVs; quarterly factory-transition milestones
-in interim reports; Midea quarterly disclosures.
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="4" t="inlineStr">
-        <is>
-          <t>Tier rationale</t>
-        </is>
-      </c>
-      <c r="B64" s="19" t="n"/>
-      <c r="C64" s="19" t="n"/>
-      <c r="D64" s="19" t="n"/>
-    </row>
-    <row r="65">
-      <c r="A65" s="20" t="inlineStr"/>
-      <c r="B65" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bucket A, Archetype A1 (Wallenberg as long-term natural-owner
-anchor at pro-rata + guarantee) + D (Midea as strategic customer
-partner). Triangulation 3/3 with verified anchor identity and
-voting power. C7 catalysts dated (Midea JV ramp H2 2026; cost-out
-H1 2027). No active red flags.
-This is the canonical Nordic Bucket A pattern that historically
-delivered 3-5x compounding (Wärtsilä, Atlas Copco split, SEB 2016
-rights). The Midea D-archetype layer is what makes the asymmetry
-meaningful — without the JV this would be a 2x normalisation
-trade; with it, the cycle + market-access combination supports
-base case 2.2x and bull 4.0x.
-Best Nordic recap candidate on the current screen.
-</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="49">
-    <mergeCell ref="B11:D11"/>
-    <mergeCell ref="B42:D42"/>
-    <mergeCell ref="B23:D23"/>
-    <mergeCell ref="A4:D4"/>
-    <mergeCell ref="B8:D8"/>
-    <mergeCell ref="B57:D57"/>
-    <mergeCell ref="B44:D44"/>
-    <mergeCell ref="B29:D29"/>
-    <mergeCell ref="B10:D10"/>
-    <mergeCell ref="B28:D28"/>
-    <mergeCell ref="A40:D40"/>
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="A34:D34"/>
-    <mergeCell ref="B9:D9"/>
-    <mergeCell ref="A64:D64"/>
-    <mergeCell ref="B30:D30"/>
-    <mergeCell ref="B65:D65"/>
-    <mergeCell ref="B15:D15"/>
-    <mergeCell ref="B55:D55"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="B24:D24"/>
-    <mergeCell ref="B51:D51"/>
-    <mergeCell ref="B20:D20"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="A61:D61"/>
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B32:D32"/>
-    <mergeCell ref="A54:D54"/>
-    <mergeCell ref="B26:D26"/>
-    <mergeCell ref="B62:D62"/>
-    <mergeCell ref="B7:D7"/>
-    <mergeCell ref="B25:D25"/>
-    <mergeCell ref="A46:D46"/>
-    <mergeCell ref="B47:D47"/>
-    <mergeCell ref="B16:D16"/>
-    <mergeCell ref="A18:D18"/>
-    <mergeCell ref="B59:D59"/>
-    <mergeCell ref="B31:D31"/>
-    <mergeCell ref="A50:D50"/>
-    <mergeCell ref="B22:D22"/>
-    <mergeCell ref="B27:D27"/>
-    <mergeCell ref="B56:D56"/>
-    <mergeCell ref="B58:D58"/>
-    <mergeCell ref="B52:D52"/>
-    <mergeCell ref="B21:D21"/>
-    <mergeCell ref="B43:D43"/>
-    <mergeCell ref="B12:D12"/>
-    <mergeCell ref="B48:D48"/>
-    <mergeCell ref="A14:D14"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D54"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="60" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Hitachi Construction Machinery</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>6305  ·  JP  ·  Bucket A  ·  Archetype H, A1  ·  Tier 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>Risk-reward snapshot</t>
-        </is>
-      </c>
-      <c r="B4" s="19" t="n"/>
-      <c r="C4" s="19" t="n"/>
-      <c r="D4" s="19" t="n"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="20" t="inlineStr">
-        <is>
-          <t>Expected EV×</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>1.69×</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="20" t="inlineStr">
-        <is>
-          <t>Bear / Base / Bull return</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t>0.75× / 1.70× / 2.80×</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="20" t="inlineStr">
-        <is>
-          <t>Bear loss</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>25%</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="20" t="inlineStr">
-        <is>
-          <t>Skew (upside/downside)</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>7.2×</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="20" t="inlineStr">
-        <is>
-          <t>Reward/Risk ratio</t>
-        </is>
-      </c>
-      <c r="B9" s="5" t="inlineStr">
-        <is>
-          <t>2.8×</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="20" t="inlineStr">
-        <is>
-          <t>Portfolio weight</t>
-        </is>
-      </c>
-      <c r="B10" s="5" t="inlineStr">
-        <is>
-          <t>3.00%</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="20" t="inlineStr">
-        <is>
-          <t>Cluster</t>
-        </is>
-      </c>
-      <c r="B11" s="5" t="inlineStr">
-        <is>
-          <t>Asian_governance_reform</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="20" t="inlineStr">
-        <is>
-          <t>Primary factor</t>
-        </is>
-      </c>
-      <c r="B12" s="5" t="inlineStr">
-        <is>
-          <t>policy</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t>Deal</t>
-        </is>
-      </c>
-      <c r="B14" s="19" t="n"/>
-      <c r="C14" s="19" t="n"/>
-      <c r="D14" s="19" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="20" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="B15" s="5" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="20" t="inlineStr">
-        <is>
-          <t>Mechanic</t>
-        </is>
-      </c>
-      <c r="B16" s="5" t="inlineStr">
-        <is>
-          <t>H — Japan FIEA mandatory-TOB threshold cut from 33.3pct to 30pct effective May 1, 2026. Hitachi parent owns 30.7pct + Itochu 25pct = combined 55.7pct. Post-amendment Hitachi cannot rationally hold 30.7pct indefinitely: either step back below threshold or commit full TOB. Construction-machinery cycle inflection; HEC was carved out from Hitachi Construction Holdings 2007 - now a candidate parent-subsidiary buy-in (HEC-Itochu MBO precedent in 2022 Alps Logistics 194pct premium).</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="4" t="inlineStr">
-        <is>
-          <t>Scorecard</t>
-        </is>
-      </c>
-      <c r="B18" s="19" t="n"/>
-      <c r="C18" s="19" t="n"/>
-      <c r="D18" s="19" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="20" t="inlineStr">
-        <is>
-          <t>D4 Dilution Pct</t>
-        </is>
-      </c>
-      <c r="B19" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="20" t="inlineStr">
-        <is>
-          <t>D9 Alignment Gap</t>
-        </is>
-      </c>
-      <c r="B20" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="20" t="inlineStr">
-        <is>
-          <t>D11 Consensus Ebitda Cagr</t>
-        </is>
-      </c>
-      <c r="B21" s="5" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="20" t="inlineStr">
-        <is>
-          <t>D14 Liquidity Quarters</t>
-        </is>
-      </c>
-      <c r="B22" s="5" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="4" t="inlineStr">
-        <is>
-          <t>Catalysts</t>
-        </is>
-      </c>
-      <c r="B24" s="19" t="n"/>
-      <c r="C24" s="19" t="n"/>
-      <c r="D24" s="19" t="n"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="8" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B25" s="8" t="inlineStr">
-        <is>
-          <t>Window</t>
-        </is>
-      </c>
-      <c r="C25" s="8" t="inlineStr">
-        <is>
-          <t>P(yes)</t>
-        </is>
-      </c>
-      <c r="D25" s="8" t="inlineStr">
-        <is>
-          <t>Re-rate if yes / hit if no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="32" customHeight="1">
-      <c r="A26" s="21" t="inlineStr">
-        <is>
-          <t>Hitachi parent decision on stake — step back below 30pct or full TOB</t>
-        </is>
-      </c>
-      <c r="B26" s="11" t="inlineStr">
-        <is>
-          <t>2026-09-01 → 2027-06-30</t>
-        </is>
-      </c>
-      <c r="C26" s="11" t="inlineStr">
-        <is>
-          <t>0.55</t>
-        </is>
-      </c>
-      <c r="D26" s="11" t="inlineStr">
-        <is>
-          <t>Up 1.5-2.5× / Down -0.1--0.2</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="32" customHeight="1">
-      <c r="A27" s="22" t="inlineStr">
-        <is>
-          <t>Construction cycle inflection (mining + infrastructure + EV-mining)</t>
-        </is>
-      </c>
-      <c r="B27" s="14" t="inlineStr">
-        <is>
-          <t>2026-06-01 → 2028-06-30</t>
-        </is>
-      </c>
-      <c r="C27" s="14" t="inlineStr">
-        <is>
-          <t>0.55</t>
-        </is>
-      </c>
-      <c r="D27" s="14" t="inlineStr">
-        <is>
-          <t>Up 1.3-1.8× / Down -0.1--0.2</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="32" customHeight="1">
-      <c r="A28" s="21" t="inlineStr">
-        <is>
-          <t>Itochu strategic action (counter-bid or MBO partnership)</t>
-        </is>
-      </c>
-      <c r="B28" s="11" t="inlineStr">
-        <is>
-          <t>2026-09-01 → 2027-12-31</t>
-        </is>
-      </c>
-      <c r="C28" s="11" t="inlineStr">
-        <is>
-          <t>0.4</t>
-        </is>
-      </c>
-      <c r="D28" s="11" t="inlineStr">
-        <is>
-          <t>Up 1.6-2.2× / Down -0.05--0.1</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="4" t="inlineStr">
-        <is>
-          <t>Triangulation (3-leg test)</t>
-        </is>
-      </c>
-      <c r="B30" s="19" t="n"/>
-      <c r="C30" s="19" t="n"/>
-      <c r="D30" s="19" t="n"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="20" t="inlineStr">
-        <is>
-          <t>Leg 1 — Valuation</t>
-        </is>
-      </c>
-      <c r="B31" s="5" t="inlineStr">
-        <is>
-          <t>partial</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="20" t="inlineStr">
-        <is>
-          <t>Leg 2 — Game theory</t>
-        </is>
-      </c>
-      <c r="B32" s="5" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="20" t="inlineStr">
-        <is>
-          <t>Leg 3 — Revealed preference</t>
-        </is>
-      </c>
-      <c r="B33" s="5" t="inlineStr">
-        <is>
-          <t>partial</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="20" t="inlineStr">
-        <is>
-          <t>Notes</t>
-        </is>
-      </c>
-      <c r="B34" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Leg 1: At 1.2x PBR not deeply undervalued vs sector; the
-alpha is in the takeout premium not the multiple gap.
-Leg 2: FIEA mandatory-TOB threshold has triggered for
-Hitachi parent. Game-theoretic option: step back (sale into
-market) or take out (TOB at premium). Either way creates
-forced flow.
-Leg 3: PARTIAL — Alps Logistics 194pct TOB premium (Itochu
-template) and Hitachi-Logisteed 40pct sale to KKR Apr 2023
-are precedents but no Hitachi statement of intent on HEC yet.
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="4" t="inlineStr">
-        <is>
-          <t>Anchor</t>
-        </is>
-      </c>
-      <c r="B36" s="19" t="n"/>
-      <c r="C36" s="19" t="n"/>
-      <c r="D36" s="19" t="n"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="20" t="inlineStr">
-        <is>
-          <t>Parties</t>
-        </is>
-      </c>
-      <c r="B37" s="5" t="inlineStr">
-        <is>
-          <t>Hitachi Ltd parent (30.7pct), Itochu Corp (25.0pct)</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="20" t="inlineStr">
-        <is>
-          <t>Stake (% est.)</t>
-        </is>
-      </c>
-      <c r="B38" s="5" t="inlineStr">
-        <is>
-          <t>55.7</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="4" t="inlineStr">
-        <is>
-          <t>Red flags</t>
-        </is>
-      </c>
-      <c r="B40" s="19" t="n"/>
-      <c r="C40" s="19" t="n"/>
-      <c r="D40" s="19" t="n"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="20" t="inlineStr">
-        <is>
-          <t>Triggered</t>
-        </is>
-      </c>
-      <c r="B41" s="5" t="inlineStr">
-        <is>
-          <t>None of 11 active</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="20" t="inlineStr">
-        <is>
-          <t>Watch list</t>
-        </is>
-      </c>
-      <c r="B42" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="4" t="inlineStr">
-        <is>
-          <t>Kill criteria</t>
-        </is>
-      </c>
-      <c r="B44" s="19" t="n"/>
-      <c r="C44" s="19" t="n"/>
-      <c r="D44" s="19" t="n"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="20" t="inlineStr">
-        <is>
-          <t>1.</t>
-        </is>
-      </c>
-      <c r="B45" s="5" t="inlineStr">
-        <is>
-          <t>Japan FIEA enforcement grace period extended &gt;24 months</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="20" t="inlineStr">
-        <is>
-          <t>2.</t>
-        </is>
-      </c>
-      <c r="B46" s="5" t="inlineStr">
-        <is>
-          <t>Hitachi parent announces 'long-term hold' positioning</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="20" t="inlineStr">
-        <is>
-          <t>3.</t>
-        </is>
-      </c>
-      <c r="B47" s="5" t="inlineStr">
-        <is>
-          <t>Construction cycle deepens beyond 2026 trough</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="20" t="inlineStr">
-        <is>
-          <t>4.</t>
-        </is>
-      </c>
-      <c r="B48" s="5" t="inlineStr">
-        <is>
-          <t>Itochu strategically retreats from machinery sector</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="4" t="inlineStr">
-        <is>
-          <t>Pre-mortem</t>
-        </is>
-      </c>
-      <c r="B50" s="19" t="n"/>
-      <c r="C50" s="19" t="n"/>
-      <c r="D50" s="19" t="n"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="20" t="inlineStr"/>
-      <c r="B51" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">It is end-2027 and 6305 is down 50pct from current.
-Most likely: Hitachi parent given long FIEA enforcement
-grace period; no TOB; construction cycle weakened on global
-CapEx slowdown; multiple compressed.
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="4" t="inlineStr">
-        <is>
-          <t>Tier rationale</t>
-        </is>
-      </c>
-      <c r="B53" s="19" t="n"/>
-      <c r="C53" s="19" t="n"/>
-      <c r="D53" s="19" t="n"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="20" t="inlineStr"/>
-      <c r="B54" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bucket A, Archetype H (governance reset via FIEA forced
-decision) + A1 (parent + Itochu as combined 55.7pct cap-stack
-anchor). Universe screen 0.86. Tier 2 because catalyst is dated
-but binary on Hitachi parent's specific decision.
-</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="38">
-    <mergeCell ref="B11:D11"/>
-    <mergeCell ref="B42:D42"/>
-    <mergeCell ref="A53:D53"/>
-    <mergeCell ref="A4:D4"/>
-    <mergeCell ref="B8:D8"/>
-    <mergeCell ref="B38:D38"/>
-    <mergeCell ref="B34:D34"/>
-    <mergeCell ref="A44:D44"/>
-    <mergeCell ref="B10:D10"/>
-    <mergeCell ref="A40:D40"/>
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="B37:D37"/>
-    <mergeCell ref="A30:D30"/>
-    <mergeCell ref="B9:D9"/>
-    <mergeCell ref="A24:D24"/>
-    <mergeCell ref="B15:D15"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="A36:D36"/>
-    <mergeCell ref="B20:D20"/>
-    <mergeCell ref="B51:D51"/>
-    <mergeCell ref="B33:D33"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="B45:D45"/>
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B32:D32"/>
-    <mergeCell ref="B7:D7"/>
-    <mergeCell ref="B47:D47"/>
-    <mergeCell ref="B16:D16"/>
-    <mergeCell ref="B54:D54"/>
-    <mergeCell ref="A18:D18"/>
-    <mergeCell ref="B31:D31"/>
-    <mergeCell ref="B46:D46"/>
-    <mergeCell ref="A50:D50"/>
-    <mergeCell ref="B22:D22"/>
-    <mergeCell ref="B21:D21"/>
-    <mergeCell ref="B12:D12"/>
-    <mergeCell ref="B48:D48"/>
-    <mergeCell ref="A14:D14"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:A25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -4979,8 +2349,8 @@
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
     <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="11" customWidth="1" min="3" max="3"/>
-    <col width="40" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="37" customWidth="1" min="4" max="4"/>
     <col width="22" customWidth="1" min="5" max="5"/>
     <col width="8" customWidth="1" min="6" max="6"/>
     <col width="8" customWidth="1" min="7" max="7"/>
@@ -5002,7 +2372,7 @@
     <row r="2" ht="38" customHeight="1">
       <c r="A2" s="7" t="inlineStr">
         <is>
-          <t>Universe coverage: 108 investable names (20 REAL waterfalls · 88 PROXY).  REAL uses the hand-built YAML's bottom-up bear/base/bull. PROXY uses a transparent formula on the universe-screener score + archetype tilt.</t>
+          <t>Universe coverage: 110 investable names (20 REAL waterfalls · 90 PROXY).  REAL uses the hand-built YAML's bottom-up bear/base/bull. PROXY uses a transparent formula on the universe-screener score + archetype tilt.</t>
         </is>
       </c>
     </row>
@@ -5475,22 +2845,22 @@
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>NYSE:GGAL</t>
+          <t>CIK:0001348911</t>
         </is>
       </c>
       <c r="D11" s="11" t="inlineStr">
         <is>
-          <t>Banco Galicia</t>
+          <t>KalVista Pharmaceuticals, Inc.</t>
         </is>
       </c>
       <c r="E11" s="11" t="inlineStr">
         <is>
-          <t>Latin America</t>
+          <t>United States/Canada</t>
         </is>
       </c>
       <c r="F11" s="11" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="G11" s="11" t="inlineStr">
@@ -5500,7 +2870,7 @@
       </c>
       <c r="H11" s="11" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2+K3</t>
         </is>
       </c>
       <c r="I11" s="11" t="inlineStr">
@@ -5515,7 +2885,7 @@
       </c>
       <c r="K11" s="11" t="inlineStr">
         <is>
-          <t>2.92×</t>
+          <t>2.94×</t>
         </is>
       </c>
       <c r="L11" s="11" t="inlineStr">
@@ -5525,7 +2895,7 @@
       </c>
       <c r="M11" s="11" t="inlineStr">
         <is>
-          <t>3.6×</t>
+          <t>3.7×</t>
         </is>
       </c>
     </row>
@@ -5533,19 +2903,19 @@
       <c r="A12" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="B12" s="16" t="inlineStr">
-        <is>
-          <t>REAL</t>
+      <c r="B12" s="13" t="inlineStr">
+        <is>
+          <t>PROXY</t>
         </is>
       </c>
       <c r="C12" s="14" t="inlineStr">
         <is>
-          <t>NYSE:LAC</t>
+          <t>CIK:0001909770</t>
         </is>
       </c>
       <c r="D12" s="14" t="inlineStr">
         <is>
-          <t>Lithium Americas</t>
+          <t>KHEOBA CORP.</t>
         </is>
       </c>
       <c r="E12" s="14" t="inlineStr">
@@ -5555,7 +2925,7 @@
       </c>
       <c r="F12" s="14" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="G12" s="14" t="inlineStr">
@@ -5565,32 +2935,32 @@
       </c>
       <c r="H12" s="14" t="inlineStr">
         <is>
-          <t>A2</t>
+          <t>A2+K3</t>
         </is>
       </c>
       <c r="I12" s="14" t="inlineStr">
         <is>
-          <t>60%</t>
+          <t>27%</t>
         </is>
       </c>
       <c r="J12" s="14" t="inlineStr">
         <is>
-          <t>3.00×</t>
+          <t>2.33×</t>
         </is>
       </c>
       <c r="K12" s="14" t="inlineStr">
         <is>
-          <t>6.00×</t>
+          <t>2.94×</t>
         </is>
       </c>
       <c r="L12" s="14" t="inlineStr">
         <is>
-          <t>3.10×</t>
+          <t>2.00×</t>
         </is>
       </c>
       <c r="M12" s="14" t="inlineStr">
         <is>
-          <t>3.5×</t>
+          <t>3.7×</t>
         </is>
       </c>
     </row>
@@ -5598,29 +2968,29 @@
       <c r="A13" s="9" t="n">
         <v>9</v>
       </c>
-      <c r="B13" s="10" t="inlineStr">
-        <is>
-          <t>REAL</t>
+      <c r="B13" s="15" t="inlineStr">
+        <is>
+          <t>PROXY</t>
         </is>
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>XETR:SZG</t>
+          <t>CIK:0001489096</t>
         </is>
       </c>
       <c r="D13" s="11" t="inlineStr">
         <is>
-          <t>Salzgitter</t>
+          <t>Thermon Group Holdings, Inc.</t>
         </is>
       </c>
       <c r="E13" s="11" t="inlineStr">
         <is>
-          <t>Continental Europe</t>
+          <t>United States/Canada</t>
         </is>
       </c>
       <c r="F13" s="11" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="G13" s="11" t="inlineStr">
@@ -5630,32 +3000,32 @@
       </c>
       <c r="H13" s="11" t="inlineStr">
         <is>
-          <t>A2</t>
+          <t>A2+K3</t>
         </is>
       </c>
       <c r="I13" s="11" t="inlineStr">
         <is>
-          <t>45%</t>
+          <t>27%</t>
         </is>
       </c>
       <c r="J13" s="11" t="inlineStr">
         <is>
-          <t>2.50×</t>
+          <t>2.33×</t>
         </is>
       </c>
       <c r="K13" s="11" t="inlineStr">
         <is>
-          <t>4.50×</t>
+          <t>2.94×</t>
         </is>
       </c>
       <c r="L13" s="11" t="inlineStr">
         <is>
-          <t>2.51×</t>
+          <t>2.00×</t>
         </is>
       </c>
       <c r="M13" s="11" t="inlineStr">
         <is>
-          <t>3.4×</t>
+          <t>3.7×</t>
         </is>
       </c>
     </row>
@@ -5670,12 +3040,12 @@
       </c>
       <c r="C14" s="14" t="inlineStr">
         <is>
-          <t>NYSE:PAM</t>
+          <t>NYSE:GGAL</t>
         </is>
       </c>
       <c r="D14" s="14" t="inlineStr">
         <is>
-          <t>Pampa Energía</t>
+          <t>Banco Galicia</t>
         </is>
       </c>
       <c r="E14" s="14" t="inlineStr">
@@ -5685,7 +3055,7 @@
       </c>
       <c r="F14" s="14" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="G14" s="14" t="inlineStr">
@@ -5700,27 +3070,27 @@
       </c>
       <c r="I14" s="14" t="inlineStr">
         <is>
-          <t>28%</t>
+          <t>27%</t>
         </is>
       </c>
       <c r="J14" s="14" t="inlineStr">
         <is>
-          <t>2.29×</t>
+          <t>2.33×</t>
         </is>
       </c>
       <c r="K14" s="14" t="inlineStr">
         <is>
-          <t>2.87×</t>
+          <t>2.92×</t>
         </is>
       </c>
       <c r="L14" s="14" t="inlineStr">
         <is>
-          <t>1.96×</t>
+          <t>2.00×</t>
         </is>
       </c>
       <c r="M14" s="14" t="inlineStr">
         <is>
-          <t>3.4×</t>
+          <t>3.6×</t>
         </is>
       </c>
     </row>
@@ -5728,29 +3098,29 @@
       <c r="A15" s="9" t="n">
         <v>11</v>
       </c>
-      <c r="B15" s="15" t="inlineStr">
-        <is>
-          <t>PROXY</t>
+      <c r="B15" s="10" t="inlineStr">
+        <is>
+          <t>REAL</t>
         </is>
       </c>
       <c r="C15" s="11" t="inlineStr">
         <is>
-          <t>3544</t>
+          <t>NYSE:LAC</t>
         </is>
       </c>
       <c r="D15" s="11" t="inlineStr">
         <is>
-          <t>サツドラＨＤ</t>
+          <t>Lithium Americas</t>
         </is>
       </c>
       <c r="E15" s="11" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States/Canada</t>
         </is>
       </c>
       <c r="F15" s="11" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="G15" s="11" t="inlineStr">
@@ -5760,32 +3130,32 @@
       </c>
       <c r="H15" s="11" t="inlineStr">
         <is>
-          <t>A2+C</t>
+          <t>A2</t>
         </is>
       </c>
       <c r="I15" s="11" t="inlineStr">
         <is>
-          <t>29%</t>
+          <t>60%</t>
         </is>
       </c>
       <c r="J15" s="11" t="inlineStr">
         <is>
-          <t>2.26×</t>
+          <t>3.00×</t>
         </is>
       </c>
       <c r="K15" s="11" t="inlineStr">
         <is>
-          <t>2.80×</t>
+          <t>6.00×</t>
         </is>
       </c>
       <c r="L15" s="11" t="inlineStr">
         <is>
-          <t>1.93×</t>
+          <t>3.10×</t>
         </is>
       </c>
       <c r="M15" s="11" t="inlineStr">
         <is>
-          <t>3.2×</t>
+          <t>3.5×</t>
         </is>
       </c>
     </row>
@@ -5793,29 +3163,29 @@
       <c r="A16" s="12" t="n">
         <v>12</v>
       </c>
-      <c r="B16" s="13" t="inlineStr">
-        <is>
-          <t>PROXY</t>
+      <c r="B16" s="16" t="inlineStr">
+        <is>
+          <t>REAL</t>
         </is>
       </c>
       <c r="C16" s="14" t="inlineStr">
         <is>
-          <t>6897</t>
+          <t>XETR:SZG</t>
         </is>
       </c>
       <c r="D16" s="14" t="inlineStr">
         <is>
-          <t>ツインバード</t>
+          <t>Salzgitter</t>
         </is>
       </c>
       <c r="E16" s="14" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Continental Europe</t>
         </is>
       </c>
       <c r="F16" s="14" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="G16" s="14" t="inlineStr">
@@ -5825,32 +3195,32 @@
       </c>
       <c r="H16" s="14" t="inlineStr">
         <is>
-          <t>A2+C</t>
+          <t>A2</t>
         </is>
       </c>
       <c r="I16" s="14" t="inlineStr">
         <is>
-          <t>29%</t>
+          <t>45%</t>
         </is>
       </c>
       <c r="J16" s="14" t="inlineStr">
         <is>
-          <t>2.26×</t>
+          <t>2.50×</t>
         </is>
       </c>
       <c r="K16" s="14" t="inlineStr">
         <is>
-          <t>2.80×</t>
+          <t>4.50×</t>
         </is>
       </c>
       <c r="L16" s="14" t="inlineStr">
         <is>
-          <t>1.93×</t>
+          <t>2.51×</t>
         </is>
       </c>
       <c r="M16" s="14" t="inlineStr">
         <is>
-          <t>3.2×</t>
+          <t>3.4×</t>
         </is>
       </c>
     </row>
@@ -5865,22 +3235,22 @@
       </c>
       <c r="C17" s="11" t="inlineStr">
         <is>
-          <t>4951</t>
+          <t>NYSE:PAM</t>
         </is>
       </c>
       <c r="D17" s="11" t="inlineStr">
         <is>
-          <t>エステー</t>
+          <t>Pampa Energía</t>
         </is>
       </c>
       <c r="E17" s="11" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Latin America</t>
         </is>
       </c>
       <c r="F17" s="11" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="G17" s="11" t="inlineStr">
@@ -5890,32 +3260,32 @@
       </c>
       <c r="H17" s="11" t="inlineStr">
         <is>
-          <t>A2+C</t>
+          <t>A1</t>
         </is>
       </c>
       <c r="I17" s="11" t="inlineStr">
         <is>
-          <t>29%</t>
+          <t>28%</t>
         </is>
       </c>
       <c r="J17" s="11" t="inlineStr">
         <is>
-          <t>2.26×</t>
+          <t>2.29×</t>
         </is>
       </c>
       <c r="K17" s="11" t="inlineStr">
         <is>
-          <t>2.80×</t>
+          <t>2.87×</t>
         </is>
       </c>
       <c r="L17" s="11" t="inlineStr">
         <is>
-          <t>1.93×</t>
+          <t>1.96×</t>
         </is>
       </c>
       <c r="M17" s="11" t="inlineStr">
         <is>
-          <t>3.2×</t>
+          <t>3.4×</t>
         </is>
       </c>
     </row>
@@ -5930,12 +3300,12 @@
       </c>
       <c r="C18" s="14" t="inlineStr">
         <is>
-          <t>3659</t>
+          <t>3544</t>
         </is>
       </c>
       <c r="D18" s="14" t="inlineStr">
         <is>
-          <t>ネクソン</t>
+          <t>サツドラＨＤ</t>
         </is>
       </c>
       <c r="E18" s="14" t="inlineStr">
@@ -5995,22 +3365,22 @@
       </c>
       <c r="C19" s="11" t="inlineStr">
         <is>
-          <t>DTZ</t>
+          <t>6897</t>
         </is>
       </c>
       <c r="D19" s="11" t="inlineStr">
         <is>
-          <t>DOTZ NANO LIMITED</t>
+          <t>ツインバード</t>
         </is>
       </c>
       <c r="E19" s="11" t="inlineStr">
         <is>
-          <t>SE Asia / Pacific</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="F19" s="11" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="G19" s="11" t="inlineStr">
@@ -6020,7 +3390,7 @@
       </c>
       <c r="H19" s="11" t="inlineStr">
         <is>
-          <t>A2</t>
+          <t>A2+C</t>
         </is>
       </c>
       <c r="I19" s="11" t="inlineStr">
@@ -6030,17 +3400,17 @@
       </c>
       <c r="J19" s="11" t="inlineStr">
         <is>
-          <t>2.27×</t>
+          <t>2.26×</t>
         </is>
       </c>
       <c r="K19" s="11" t="inlineStr">
         <is>
-          <t>2.82×</t>
+          <t>2.80×</t>
         </is>
       </c>
       <c r="L19" s="11" t="inlineStr">
         <is>
-          <t>1.94×</t>
+          <t>1.93×</t>
         </is>
       </c>
       <c r="M19" s="11" t="inlineStr">
@@ -6060,22 +3430,22 @@
       </c>
       <c r="C20" s="14" t="inlineStr">
         <is>
-          <t>BMR</t>
+          <t>4951</t>
         </is>
       </c>
       <c r="D20" s="14" t="inlineStr">
         <is>
-          <t>BALLYMORE RESOURCES LIMITED</t>
+          <t>エステー</t>
         </is>
       </c>
       <c r="E20" s="14" t="inlineStr">
         <is>
-          <t>SE Asia / Pacific</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="F20" s="14" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="G20" s="14" t="inlineStr">
@@ -6085,7 +3455,7 @@
       </c>
       <c r="H20" s="14" t="inlineStr">
         <is>
-          <t>A2</t>
+          <t>A2+C</t>
         </is>
       </c>
       <c r="I20" s="14" t="inlineStr">
@@ -6095,17 +3465,17 @@
       </c>
       <c r="J20" s="14" t="inlineStr">
         <is>
-          <t>2.27×</t>
+          <t>2.26×</t>
         </is>
       </c>
       <c r="K20" s="14" t="inlineStr">
         <is>
-          <t>2.82×</t>
+          <t>2.80×</t>
         </is>
       </c>
       <c r="L20" s="14" t="inlineStr">
         <is>
-          <t>1.94×</t>
+          <t>1.93×</t>
         </is>
       </c>
       <c r="M20" s="14" t="inlineStr">
@@ -6125,22 +3495,22 @@
       </c>
       <c r="C21" s="11" t="inlineStr">
         <is>
-          <t>CQT</t>
+          <t>3659</t>
         </is>
       </c>
       <c r="D21" s="11" t="inlineStr">
         <is>
-          <t>CONNEQT HEALTH LIMITED</t>
+          <t>ネクソン</t>
         </is>
       </c>
       <c r="E21" s="11" t="inlineStr">
         <is>
-          <t>SE Asia / Pacific</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="F21" s="11" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="G21" s="11" t="inlineStr">
@@ -6150,7 +3520,7 @@
       </c>
       <c r="H21" s="11" t="inlineStr">
         <is>
-          <t>A2</t>
+          <t>A2+C</t>
         </is>
       </c>
       <c r="I21" s="11" t="inlineStr">
@@ -6160,17 +3530,17 @@
       </c>
       <c r="J21" s="11" t="inlineStr">
         <is>
-          <t>2.27×</t>
+          <t>2.26×</t>
         </is>
       </c>
       <c r="K21" s="11" t="inlineStr">
         <is>
-          <t>2.82×</t>
+          <t>2.80×</t>
         </is>
       </c>
       <c r="L21" s="11" t="inlineStr">
         <is>
-          <t>1.94×</t>
+          <t>1.93×</t>
         </is>
       </c>
       <c r="M21" s="11" t="inlineStr">
@@ -6190,12 +3560,12 @@
       </c>
       <c r="C22" s="14" t="inlineStr">
         <is>
-          <t>JLL</t>
+          <t>DTZ</t>
         </is>
       </c>
       <c r="D22" s="14" t="inlineStr">
         <is>
-          <t>JINDALEE LITHIUM LIMITED</t>
+          <t>DOTZ NANO LIMITED</t>
         </is>
       </c>
       <c r="E22" s="14" t="inlineStr">
@@ -6255,12 +3625,12 @@
       </c>
       <c r="C23" s="11" t="inlineStr">
         <is>
-          <t>KSN</t>
+          <t>BMR</t>
         </is>
       </c>
       <c r="D23" s="11" t="inlineStr">
         <is>
-          <t>KINGSTON RESOURCES LIMITED</t>
+          <t>BALLYMORE RESOURCES LIMITED</t>
         </is>
       </c>
       <c r="E23" s="11" t="inlineStr">
@@ -6320,12 +3690,12 @@
       </c>
       <c r="C24" s="14" t="inlineStr">
         <is>
-          <t>PNN</t>
+          <t>CQT</t>
         </is>
       </c>
       <c r="D24" s="14" t="inlineStr">
         <is>
-          <t>POWER MINERALS LIMITED</t>
+          <t>CONNEQT HEALTH LIMITED</t>
         </is>
       </c>
       <c r="E24" s="14" t="inlineStr">
@@ -6385,12 +3755,12 @@
       </c>
       <c r="C25" s="11" t="inlineStr">
         <is>
-          <t>ERM</t>
+          <t>JLL</t>
         </is>
       </c>
       <c r="D25" s="11" t="inlineStr">
         <is>
-          <t>EMMERSON RESOURCES LIMITED</t>
+          <t>JINDALEE LITHIUM LIMITED</t>
         </is>
       </c>
       <c r="E25" s="11" t="inlineStr">
@@ -6400,7 +3770,7 @@
       </c>
       <c r="F25" s="11" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="G25" s="11" t="inlineStr">
@@ -6410,7 +3780,7 @@
       </c>
       <c r="H25" s="11" t="inlineStr">
         <is>
-          <t>A2+E</t>
+          <t>A2</t>
         </is>
       </c>
       <c r="I25" s="11" t="inlineStr">
@@ -6420,17 +3790,17 @@
       </c>
       <c r="J25" s="11" t="inlineStr">
         <is>
-          <t>2.26×</t>
+          <t>2.27×</t>
         </is>
       </c>
       <c r="K25" s="11" t="inlineStr">
         <is>
-          <t>2.80×</t>
+          <t>2.82×</t>
         </is>
       </c>
       <c r="L25" s="11" t="inlineStr">
         <is>
-          <t>1.93×</t>
+          <t>1.94×</t>
         </is>
       </c>
       <c r="M25" s="11" t="inlineStr">
@@ -6450,12 +3820,12 @@
       </c>
       <c r="C26" s="14" t="inlineStr">
         <is>
-          <t>PEX</t>
+          <t>KSN</t>
         </is>
       </c>
       <c r="D26" s="14" t="inlineStr">
         <is>
-          <t>PEEL MINING LIMITED</t>
+          <t>KINGSTON RESOURCES LIMITED</t>
         </is>
       </c>
       <c r="E26" s="14" t="inlineStr">
@@ -6465,7 +3835,7 @@
       </c>
       <c r="F26" s="14" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="G26" s="14" t="inlineStr">
@@ -6475,7 +3845,7 @@
       </c>
       <c r="H26" s="14" t="inlineStr">
         <is>
-          <t>A2+E</t>
+          <t>A2</t>
         </is>
       </c>
       <c r="I26" s="14" t="inlineStr">
@@ -6485,17 +3855,17 @@
       </c>
       <c r="J26" s="14" t="inlineStr">
         <is>
-          <t>2.26×</t>
+          <t>2.27×</t>
         </is>
       </c>
       <c r="K26" s="14" t="inlineStr">
         <is>
-          <t>2.80×</t>
+          <t>2.82×</t>
         </is>
       </c>
       <c r="L26" s="14" t="inlineStr">
         <is>
-          <t>1.93×</t>
+          <t>1.94×</t>
         </is>
       </c>
       <c r="M26" s="14" t="inlineStr">
@@ -6515,12 +3885,12 @@
       </c>
       <c r="C27" s="11" t="inlineStr">
         <is>
-          <t>AIS</t>
+          <t>PNN</t>
         </is>
       </c>
       <c r="D27" s="11" t="inlineStr">
         <is>
-          <t>AERIS RESOURCES LIMITED</t>
+          <t>POWER MINERALS LIMITED</t>
         </is>
       </c>
       <c r="E27" s="11" t="inlineStr">
@@ -6530,7 +3900,7 @@
       </c>
       <c r="F27" s="11" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="G27" s="11" t="inlineStr">
@@ -6540,7 +3910,7 @@
       </c>
       <c r="H27" s="11" t="inlineStr">
         <is>
-          <t>A2+E</t>
+          <t>A2</t>
         </is>
       </c>
       <c r="I27" s="11" t="inlineStr">
@@ -6550,17 +3920,17 @@
       </c>
       <c r="J27" s="11" t="inlineStr">
         <is>
-          <t>2.26×</t>
+          <t>2.27×</t>
         </is>
       </c>
       <c r="K27" s="11" t="inlineStr">
         <is>
-          <t>2.80×</t>
+          <t>2.82×</t>
         </is>
       </c>
       <c r="L27" s="11" t="inlineStr">
         <is>
-          <t>1.93×</t>
+          <t>1.94×</t>
         </is>
       </c>
       <c r="M27" s="11" t="inlineStr">
@@ -6580,12 +3950,12 @@
       </c>
       <c r="C28" s="14" t="inlineStr">
         <is>
-          <t>ASM</t>
+          <t>ERM</t>
         </is>
       </c>
       <c r="D28" s="14" t="inlineStr">
         <is>
-          <t>AUSTRALIAN STRATEGIC MATERIALS LIMITED</t>
+          <t>EMMERSON RESOURCES LIMITED</t>
         </is>
       </c>
       <c r="E28" s="14" t="inlineStr">
@@ -6645,12 +4015,12 @@
       </c>
       <c r="C29" s="11" t="inlineStr">
         <is>
-          <t>QUB</t>
+          <t>PEX</t>
         </is>
       </c>
       <c r="D29" s="11" t="inlineStr">
         <is>
-          <t>QUBE HOLDINGS LIMITED</t>
+          <t>PEEL MINING LIMITED</t>
         </is>
       </c>
       <c r="E29" s="11" t="inlineStr">
@@ -6738,9 +4108,9 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
     <col width="37" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
     <col width="8" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
@@ -7010,32 +4380,32 @@
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>NYSE:GGAL</t>
+          <t>CIK:0001348911</t>
         </is>
       </c>
       <c r="C10" s="14" t="inlineStr">
         <is>
-          <t>Banco Galicia</t>
+          <t>KalVista Pharmaceuticals, Inc.</t>
         </is>
       </c>
       <c r="D10" s="14" t="inlineStr">
         <is>
-          <t>Latin America</t>
+          <t>United States/Canada</t>
         </is>
       </c>
       <c r="E10" s="14" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="F10" s="14" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2+K3</t>
         </is>
       </c>
       <c r="G10" s="14" t="inlineStr">
         <is>
-          <t>3.6×</t>
+          <t>3.7×</t>
         </is>
       </c>
       <c r="H10" s="14" t="inlineStr">
@@ -7046,36 +4416,36 @@
     </row>
     <row r="11">
       <c r="A11" s="9" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>NYSE:PAM</t>
+          <t>CIK:0001909770</t>
         </is>
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>Pampa Energía</t>
+          <t>KHEOBA CORP.</t>
         </is>
       </c>
       <c r="D11" s="11" t="inlineStr">
         <is>
-          <t>Latin America</t>
+          <t>United States/Canada</t>
         </is>
       </c>
       <c r="E11" s="11" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="F11" s="11" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2+K3</t>
         </is>
       </c>
       <c r="G11" s="11" t="inlineStr">
         <is>
-          <t>3.4×</t>
+          <t>3.7×</t>
         </is>
       </c>
       <c r="H11" s="11" t="inlineStr">
@@ -7086,36 +4456,36 @@
     </row>
     <row r="12">
       <c r="A12" s="12" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B12" s="14" t="inlineStr">
         <is>
-          <t>3544</t>
+          <t>CIK:0001489096</t>
         </is>
       </c>
       <c r="C12" s="14" t="inlineStr">
         <is>
-          <t>サツドラＨＤ</t>
+          <t>Thermon Group Holdings, Inc.</t>
         </is>
       </c>
       <c r="D12" s="14" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States/Canada</t>
         </is>
       </c>
       <c r="E12" s="14" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="F12" s="14" t="inlineStr">
         <is>
-          <t>A2+C</t>
+          <t>A2+K3</t>
         </is>
       </c>
       <c r="G12" s="14" t="inlineStr">
         <is>
-          <t>3.2×</t>
+          <t>3.7×</t>
         </is>
       </c>
       <c r="H12" s="14" t="inlineStr">
@@ -7126,36 +4496,36 @@
     </row>
     <row r="13">
       <c r="A13" s="9" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>6897</t>
+          <t>NYSE:GGAL</t>
         </is>
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>ツインバード</t>
+          <t>Banco Galicia</t>
         </is>
       </c>
       <c r="D13" s="11" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Latin America</t>
         </is>
       </c>
       <c r="E13" s="11" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="F13" s="11" t="inlineStr">
         <is>
-          <t>A2+C</t>
+          <t>A1</t>
         </is>
       </c>
       <c r="G13" s="11" t="inlineStr">
         <is>
-          <t>3.2×</t>
+          <t>3.6×</t>
         </is>
       </c>
       <c r="H13" s="11" t="inlineStr">
@@ -7170,32 +4540,32 @@
       </c>
       <c r="B14" s="14" t="inlineStr">
         <is>
-          <t>4951</t>
+          <t>NYSE:PAM</t>
         </is>
       </c>
       <c r="C14" s="14" t="inlineStr">
         <is>
-          <t>エステー</t>
+          <t>Pampa Energía</t>
         </is>
       </c>
       <c r="D14" s="14" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Latin America</t>
         </is>
       </c>
       <c r="E14" s="14" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="F14" s="14" t="inlineStr">
         <is>
-          <t>A2+C</t>
+          <t>A1</t>
         </is>
       </c>
       <c r="G14" s="14" t="inlineStr">
         <is>
-          <t>3.2×</t>
+          <t>3.4×</t>
         </is>
       </c>
       <c r="H14" s="14" t="inlineStr">
@@ -7210,12 +4580,12 @@
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>3659</t>
+          <t>3544</t>
         </is>
       </c>
       <c r="C15" s="11" t="inlineStr">
         <is>
-          <t>ネクソン</t>
+          <t>サツドラＨＤ</t>
         </is>
       </c>
       <c r="D15" s="11" t="inlineStr">
@@ -7250,27 +4620,27 @@
       </c>
       <c r="B16" s="14" t="inlineStr">
         <is>
-          <t>DTZ</t>
+          <t>6897</t>
         </is>
       </c>
       <c r="C16" s="14" t="inlineStr">
         <is>
-          <t>DOTZ NANO LIMITED</t>
+          <t>ツインバード</t>
         </is>
       </c>
       <c r="D16" s="14" t="inlineStr">
         <is>
-          <t>SE Asia / Pacific</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="E16" s="14" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="F16" s="14" t="inlineStr">
         <is>
-          <t>A2</t>
+          <t>A2+C</t>
         </is>
       </c>
       <c r="G16" s="14" t="inlineStr">
@@ -7290,27 +4660,27 @@
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>BMR</t>
+          <t>4951</t>
         </is>
       </c>
       <c r="C17" s="11" t="inlineStr">
         <is>
-          <t>BALLYMORE RESOURCES LIMITED</t>
+          <t>エステー</t>
         </is>
       </c>
       <c r="D17" s="11" t="inlineStr">
         <is>
-          <t>SE Asia / Pacific</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="E17" s="11" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="F17" s="11" t="inlineStr">
         <is>
-          <t>A2</t>
+          <t>A2+C</t>
         </is>
       </c>
       <c r="G17" s="11" t="inlineStr">
@@ -7330,27 +4700,27 @@
       </c>
       <c r="B18" s="14" t="inlineStr">
         <is>
-          <t>CQT</t>
+          <t>3659</t>
         </is>
       </c>
       <c r="C18" s="14" t="inlineStr">
         <is>
-          <t>CONNEQT HEALTH LIMITED</t>
+          <t>ネクソン</t>
         </is>
       </c>
       <c r="D18" s="14" t="inlineStr">
         <is>
-          <t>SE Asia / Pacific</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="E18" s="14" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="F18" s="14" t="inlineStr">
         <is>
-          <t>A2</t>
+          <t>A2+C</t>
         </is>
       </c>
       <c r="G18" s="14" t="inlineStr">
@@ -7370,12 +4740,12 @@
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>JLL</t>
+          <t>DTZ</t>
         </is>
       </c>
       <c r="C19" s="11" t="inlineStr">
         <is>
-          <t>JINDALEE LITHIUM LIMITED</t>
+          <t>DOTZ NANO LIMITED</t>
         </is>
       </c>
       <c r="D19" s="11" t="inlineStr">
@@ -7410,12 +4780,12 @@
       </c>
       <c r="B20" s="14" t="inlineStr">
         <is>
-          <t>KSN</t>
+          <t>BMR</t>
         </is>
       </c>
       <c r="C20" s="14" t="inlineStr">
         <is>
-          <t>KINGSTON RESOURCES LIMITED</t>
+          <t>BALLYMORE RESOURCES LIMITED</t>
         </is>
       </c>
       <c r="D20" s="14" t="inlineStr">
@@ -7450,12 +4820,12 @@
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t>PNN</t>
+          <t>CQT</t>
         </is>
       </c>
       <c r="C21" s="11" t="inlineStr">
         <is>
-          <t>POWER MINERALS LIMITED</t>
+          <t>CONNEQT HEALTH LIMITED</t>
         </is>
       </c>
       <c r="D21" s="11" t="inlineStr">
@@ -7490,12 +4860,12 @@
       </c>
       <c r="B22" s="14" t="inlineStr">
         <is>
-          <t>ERM</t>
+          <t>JLL</t>
         </is>
       </c>
       <c r="C22" s="14" t="inlineStr">
         <is>
-          <t>EMMERSON RESOURCES LIMITED</t>
+          <t>JINDALEE LITHIUM LIMITED</t>
         </is>
       </c>
       <c r="D22" s="14" t="inlineStr">
@@ -7505,12 +4875,12 @@
       </c>
       <c r="E22" s="14" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="F22" s="14" t="inlineStr">
         <is>
-          <t>A2+E</t>
+          <t>A2</t>
         </is>
       </c>
       <c r="G22" s="14" t="inlineStr">
@@ -7530,12 +4900,12 @@
       </c>
       <c r="B23" s="11" t="inlineStr">
         <is>
-          <t>PEX</t>
+          <t>KSN</t>
         </is>
       </c>
       <c r="C23" s="11" t="inlineStr">
         <is>
-          <t>PEEL MINING LIMITED</t>
+          <t>KINGSTON RESOURCES LIMITED</t>
         </is>
       </c>
       <c r="D23" s="11" t="inlineStr">
@@ -7545,12 +4915,12 @@
       </c>
       <c r="E23" s="11" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="F23" s="11" t="inlineStr">
         <is>
-          <t>A2+E</t>
+          <t>A2</t>
         </is>
       </c>
       <c r="G23" s="11" t="inlineStr">
@@ -7570,12 +4940,12 @@
       </c>
       <c r="B24" s="14" t="inlineStr">
         <is>
-          <t>AIS</t>
+          <t>PNN</t>
         </is>
       </c>
       <c r="C24" s="14" t="inlineStr">
         <is>
-          <t>AERIS RESOURCES LIMITED</t>
+          <t>POWER MINERALS LIMITED</t>
         </is>
       </c>
       <c r="D24" s="14" t="inlineStr">
@@ -7585,12 +4955,12 @@
       </c>
       <c r="E24" s="14" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="F24" s="14" t="inlineStr">
         <is>
-          <t>A2+E</t>
+          <t>A2</t>
         </is>
       </c>
       <c r="G24" s="14" t="inlineStr">

--- a/output/cyclepapa_risk_reward_workbook.xlsx
+++ b/output/cyclepapa_risk_reward_workbook.xlsx
@@ -601,7 +601,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Generated 2026-06-22</t>
+          <t>Generated 2026-07-01</t>
         </is>
       </c>
     </row>

--- a/output/cyclepapa_risk_reward_workbook.xlsx
+++ b/output/cyclepapa_risk_reward_workbook.xlsx
@@ -18,7 +18,14 @@
     <sheet name="LOCAL" sheetId="9" state="visible" r:id="rId9"/>
     <sheet name="LAC" sheetId="10" state="visible" r:id="rId10"/>
     <sheet name="SZG" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="Methodology" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="TKA" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="ELUX-B" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="GTCO" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="6305" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="DSI" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="241560" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="ETL" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="Methodology" sheetId="19" state="visible" r:id="rId19"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -601,7 +608,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Generated 2026-07-01</t>
+          <t>Generated 2026-07-02</t>
         </is>
       </c>
     </row>
@@ -2208,6 +2215,4587 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:D55"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Thyssenkrupp AG (Steel Europe)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>TKA  ·  DE  ·  Bucket A  ·  Archetype A1, A2, H  ·  Tier 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>Risk-reward snapshot</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="n"/>
+      <c r="C4" s="19" t="n"/>
+      <c r="D4" s="19" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="20" t="inlineStr">
+        <is>
+          <t>Expected EV×</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>2.34×</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="20" t="inlineStr">
+        <is>
+          <t>Bear / Base / Bull return</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>0.55× / 2.30× / 4.20×</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="20" t="inlineStr">
+        <is>
+          <t>Bear loss</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>45%</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="20" t="inlineStr">
+        <is>
+          <t>Skew (upside/downside)</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>7.1×</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="20" t="inlineStr">
+        <is>
+          <t>Reward/Risk ratio</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>3.0×</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="20" t="inlineStr">
+        <is>
+          <t>Portfolio weight</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>3.00%</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="20" t="inlineStr">
+        <is>
+          <t>Cluster</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>EU_industrial_policy</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="20" t="inlineStr">
+        <is>
+          <t>Primary factor</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>policy</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>Deal</t>
+        </is>
+      </c>
+      <c r="B14" s="19" t="n"/>
+      <c r="C14" s="19" t="n"/>
+      <c r="D14" s="19" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="20" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>2024-07-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="20" t="inlineStr">
+        <is>
+          <t>Mechanic</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>A1 + A2 + H — Daniel Kretinsky's EPCG took 20pct stake in Thyssenkrupp Steel Europe subsidiary July 2024 (€1.0-1.5bn implied valuation). JV with German State pending (Lower Saxony + federal govt). €2bn EU state aid for green-steel transition approved Jul 2023 (SA.103861). Multi-decade decarbonisation pivot: Hydrogen-DRI plant Salzgitter site; Marine Systems carve-out worth €1-1.5bn separately. Iduna Aurelius industrial JV pending under EU IAA framework.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Scorecard</t>
+        </is>
+      </c>
+      <c r="B18" s="19" t="n"/>
+      <c r="C18" s="19" t="n"/>
+      <c r="D18" s="19" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="20" t="inlineStr">
+        <is>
+          <t>D4 Dilution Pct</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="20" t="inlineStr">
+        <is>
+          <t>D9 Alignment Gap</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="20" t="inlineStr">
+        <is>
+          <t>D11 Consensus Ebitda Cagr</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="20" t="inlineStr">
+        <is>
+          <t>D14 Liquidity Quarters</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>Catalysts</t>
+        </is>
+      </c>
+      <c r="B24" s="19" t="n"/>
+      <c r="C24" s="19" t="n"/>
+      <c r="D24" s="19" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="8" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B25" s="8" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="C25" s="8" t="inlineStr">
+        <is>
+          <t>P(yes)</t>
+        </is>
+      </c>
+      <c r="D25" s="8" t="inlineStr">
+        <is>
+          <t>Re-rate if yes / hit if no</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="32" customHeight="1">
+      <c r="A26" s="21" t="inlineStr">
+        <is>
+          <t>Thyssenkrupp Steel JV with German state closes (Kretinsky 50pct / state 50pct)</t>
+        </is>
+      </c>
+      <c r="B26" s="11" t="inlineStr">
+        <is>
+          <t>2026-09-01 → 2027-09-30</t>
+        </is>
+      </c>
+      <c r="C26" s="11" t="inlineStr">
+        <is>
+          <t>0.55</t>
+        </is>
+      </c>
+      <c r="D26" s="11" t="inlineStr">
+        <is>
+          <t>Up 1.6-2.4× / Down -0.2--0.3</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="32" customHeight="1">
+      <c r="A27" s="22" t="inlineStr">
+        <is>
+          <t>Marine Systems carve-out / IPO completion</t>
+        </is>
+      </c>
+      <c r="B27" s="14" t="inlineStr">
+        <is>
+          <t>2026-09-01 → 2027-12-31</t>
+        </is>
+      </c>
+      <c r="C27" s="14" t="inlineStr">
+        <is>
+          <t>0.55</t>
+        </is>
+      </c>
+      <c r="D27" s="14" t="inlineStr">
+        <is>
+          <t>Up 1.4-1.8× / Down -0.05--0.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="32" customHeight="1">
+      <c r="A28" s="21" t="inlineStr">
+        <is>
+          <t>European steel cycle inflection (HRC &gt;€600/t)</t>
+        </is>
+      </c>
+      <c r="B28" s="11" t="inlineStr">
+        <is>
+          <t>2026-06-01 → 2028-06-30</t>
+        </is>
+      </c>
+      <c r="C28" s="11" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="D28" s="11" t="inlineStr">
+        <is>
+          <t>Up 1.5-2.2× / Down -0.2--0.3</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="32" customHeight="1">
+      <c r="A29" s="22" t="inlineStr">
+        <is>
+          <t>SALCOS first green-steel production at converted Duisburg blast furnace</t>
+        </is>
+      </c>
+      <c r="B29" s="14" t="inlineStr">
+        <is>
+          <t>2026-12-01 → 2027-12-31</t>
+        </is>
+      </c>
+      <c r="C29" s="14" t="inlineStr">
+        <is>
+          <t>0.55</t>
+        </is>
+      </c>
+      <c r="D29" s="14" t="inlineStr">
+        <is>
+          <t>Up 1.3-1.8× / Down -0.15--0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>Triangulation (3-leg test)</t>
+        </is>
+      </c>
+      <c r="B31" s="19" t="n"/>
+      <c r="C31" s="19" t="n"/>
+      <c r="D31" s="19" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="20" t="inlineStr">
+        <is>
+          <t>Leg 1 — Valuation</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="20" t="inlineStr">
+        <is>
+          <t>Leg 2 — Game theory</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="20" t="inlineStr">
+        <is>
+          <t>Leg 3 — Revealed preference</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>partial</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="20" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Leg 1: 0.4x book with €2bn approved state aid + Marine
+Systems €1-1.5bn carve-out implies SOTP gap to ~€4-5bn vs
+current cap €3.2bn.
+Leg 2: Kretinsky 20pct in Steel sub + Krupp-Stiftung 21pct
+in parent = aligned cap-stack.
+Leg 3: PARTIAL — Kretinsky stake = revealed preference;
+KfW second-tranche commit not yet placed; Carlyle Marine
+interest is signal but not signed.
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>Anchor</t>
+        </is>
+      </c>
+      <c r="B37" s="19" t="n"/>
+      <c r="C37" s="19" t="n"/>
+      <c r="D37" s="19" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="20" t="inlineStr">
+        <is>
+          <t>Parties</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="inlineStr">
+        <is>
+          <t>EPCG / Daniel Kretinsky, German Federal State + Lower Saxony, Krupp-Stiftung foundation (21pct legacy)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="20" t="inlineStr">
+        <is>
+          <t>Stake (% est.)</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>Red flags</t>
+        </is>
+      </c>
+      <c r="B41" s="19" t="n"/>
+      <c r="C41" s="19" t="n"/>
+      <c r="D41" s="19" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="20" t="inlineStr">
+        <is>
+          <t>Triggered</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="inlineStr">
+        <is>
+          <t>None of 11 active</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="20" t="inlineStr">
+        <is>
+          <t>Watch list</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>Kill criteria</t>
+        </is>
+      </c>
+      <c r="B45" s="19" t="n"/>
+      <c r="C45" s="19" t="n"/>
+      <c r="D45" s="19" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="20" t="inlineStr">
+        <is>
+          <t>1.</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="inlineStr">
+        <is>
+          <t>Kretinsky / state JV terms materially worsen (state share &lt;40pct)</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="20" t="inlineStr">
+        <is>
+          <t>2.</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="inlineStr">
+        <is>
+          <t>SALCOS Phase 1 slips beyond mid-2027</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="20" t="inlineStr">
+        <is>
+          <t>3.</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="inlineStr">
+        <is>
+          <t>CBAM materially watered down by EU Council</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="20" t="inlineStr">
+        <is>
+          <t>4.</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="inlineStr">
+        <is>
+          <t>Marine Systems carve-out cancelled or distressed sale</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>Pre-mortem</t>
+        </is>
+      </c>
+      <c r="B51" s="19" t="n"/>
+      <c r="C51" s="19" t="n"/>
+      <c r="D51" s="19" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="20" t="inlineStr"/>
+      <c r="B52" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">It is end-2027 and TKA is down 60pct from current ~€5.
+Most likely: Steel-JV negotiations stalled on state commitment;
+Marine Systems carve-out priced at distressed multiple; SALCOS
+cost overran by €1bn; Chinese steel dumping intensified; multiple
+to 0.3x book; another asset disposal at distressed terms.
+Second most likely: EU IAA fiscal envelope cut in EU budget
+negotiation; KfW declined; SALCOS deferred.
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>Tier rationale</t>
+        </is>
+      </c>
+      <c r="B54" s="19" t="n"/>
+      <c r="C54" s="19" t="n"/>
+      <c r="D54" s="19" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="20" t="inlineStr"/>
+      <c r="B55" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bucket A, Archetype A1 (Kretinsky 20pct + Krupp-Stiftung 21pct
+aligned anchors) + A2 (EU state aid €2bn) + H (governance reset
+via Steel-JV restructure). Universe score 0.95 = 7th-highest;
+multi-leg catalyst structure puts it in Tier 1 (4 dated catalysts
++ 2 floors).
+</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="38">
+    <mergeCell ref="B11:D11"/>
+    <mergeCell ref="B42:D42"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="B38:D38"/>
+    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="B10:D10"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="B49:D49"/>
+    <mergeCell ref="B9:D9"/>
+    <mergeCell ref="A24:D24"/>
+    <mergeCell ref="A51:D51"/>
+    <mergeCell ref="B15:D15"/>
+    <mergeCell ref="B55:D55"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="B33:D33"/>
+    <mergeCell ref="A45:D45"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="B35:D35"/>
+    <mergeCell ref="A54:D54"/>
+    <mergeCell ref="A41:D41"/>
+    <mergeCell ref="B7:D7"/>
+    <mergeCell ref="B47:D47"/>
+    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="A37:D37"/>
+    <mergeCell ref="A18:D18"/>
+    <mergeCell ref="B46:D46"/>
+    <mergeCell ref="B22:D22"/>
+    <mergeCell ref="B52:D52"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="B43:D43"/>
+    <mergeCell ref="B12:D12"/>
+    <mergeCell ref="B39:D39"/>
+    <mergeCell ref="B48:D48"/>
+    <mergeCell ref="A14:D14"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D65"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>AB Electrolux (Series B)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>ELUX-B  ·  SE  ·  Bucket A  ·  Archetype A1, D  ·  Tier 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>Risk-reward snapshot</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="n"/>
+      <c r="C4" s="19" t="n"/>
+      <c r="D4" s="19" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="20" t="inlineStr">
+        <is>
+          <t>Expected EV×</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>2.32×</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="20" t="inlineStr">
+        <is>
+          <t>Bear / Base / Bull return</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>0.55× / 2.20× / 4.00×</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="20" t="inlineStr">
+        <is>
+          <t>Bear loss</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>45%</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="20" t="inlineStr">
+        <is>
+          <t>Skew (upside/downside)</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>6.7×</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="20" t="inlineStr">
+        <is>
+          <t>Reward/Risk ratio</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>2.9×</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="20" t="inlineStr">
+        <is>
+          <t>Portfolio weight</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>3.00%</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="20" t="inlineStr">
+        <is>
+          <t>Cluster</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>Nordic_consumer</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="20" t="inlineStr">
+        <is>
+          <t>Primary factor</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>multiple_norm</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>Deal</t>
+        </is>
+      </c>
+      <c r="B14" s="19" t="n"/>
+      <c r="C14" s="19" t="n"/>
+      <c r="D14" s="19" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="20" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="20" t="inlineStr">
+        <is>
+          <t>Mechanic</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>SEK 9,062m fully underwritten rights issue (subscription Jun 2-16, 2026); Investor AB (Wallenberg) subscribes pro-rata SEK 1.7bn + guarantees additional SEK 1.7bn = 37.56% of issue. Tied to strategic partnership with Midea for North America, global organization optimization, and footprint restructuring.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Scorecard</t>
+        </is>
+      </c>
+      <c r="B18" s="19" t="n"/>
+      <c r="C18" s="19" t="n"/>
+      <c r="D18" s="19" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="20" t="inlineStr">
+        <is>
+          <t>D2 Issue Discount Pct</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="20" t="inlineStr">
+        <is>
+          <t>D3 Backstop Cost Pct</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="20" t="inlineStr">
+        <is>
+          <t>D4 Dilution Pct</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="20" t="inlineStr">
+        <is>
+          <t>D5 Delta Wam Months</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="20" t="inlineStr">
+        <is>
+          <t>D6 Debt Tranches Post</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="20" t="inlineStr">
+        <is>
+          <t>D7 Ucc Terminations Pm30D</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="20" t="inlineStr">
+        <is>
+          <t>D8 Mip Strike Over Recap</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="20" t="inlineStr">
+        <is>
+          <t>D9 Alignment Gap</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="20" t="inlineStr">
+        <is>
+          <t>D9B Anchor Premium To Recap</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="20" t="inlineStr">
+        <is>
+          <t>D9C Premium To Vwap</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="20" t="inlineStr">
+        <is>
+          <t>D9D Liquidation Recovery Pct</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="20" t="inlineStr">
+        <is>
+          <t>D11 Consensus Ebitda Cagr</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="20" t="inlineStr">
+        <is>
+          <t>D13 Altman Z</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="20" t="inlineStr">
+        <is>
+          <t>D14 Liquidity Quarters</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>Catalysts</t>
+        </is>
+      </c>
+      <c r="B34" s="19" t="n"/>
+      <c r="C34" s="19" t="n"/>
+      <c r="D34" s="19" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="8" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B35" s="8" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="C35" s="8" t="inlineStr">
+        <is>
+          <t>P(yes)</t>
+        </is>
+      </c>
+      <c r="D35" s="8" t="inlineStr">
+        <is>
+          <t>Re-rate if yes / hit if no</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="32" customHeight="1">
+      <c r="A36" s="21" t="inlineStr">
+        <is>
+          <t>Midea North America partnership operational ramp</t>
+        </is>
+      </c>
+      <c r="B36" s="11" t="inlineStr">
+        <is>
+          <t>2026-09-01 → 2027-12-31</t>
+        </is>
+      </c>
+      <c r="C36" s="11" t="inlineStr">
+        <is>
+          <t>0.55</t>
+        </is>
+      </c>
+      <c r="D36" s="11" t="inlineStr">
+        <is>
+          <t>Up 1.6-2.5× / Down -0.2--0.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="32" customHeight="1">
+      <c r="A37" s="22" t="inlineStr">
+        <is>
+          <t>Global organization &amp; footprint optimization completion</t>
+        </is>
+      </c>
+      <c r="B37" s="14" t="inlineStr">
+        <is>
+          <t>2026-06-01 → 2027-06-30</t>
+        </is>
+      </c>
+      <c r="C37" s="14" t="inlineStr">
+        <is>
+          <t>0.65</t>
+        </is>
+      </c>
+      <c r="D37" s="14" t="inlineStr">
+        <is>
+          <t>Up 1.4-2.0× / Down -0.15--0.3</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="32" customHeight="1">
+      <c r="A38" s="21" t="inlineStr">
+        <is>
+          <t>Appliance cycle (US housing + EU disinflation) bottom</t>
+        </is>
+      </c>
+      <c r="B38" s="11" t="inlineStr">
+        <is>
+          <t>2026-06-01 → 2027-06-30</t>
+        </is>
+      </c>
+      <c r="C38" s="11" t="inlineStr">
+        <is>
+          <t>0.55</t>
+        </is>
+      </c>
+      <c r="D38" s="11" t="inlineStr">
+        <is>
+          <t>Up 1.5-2.2× / Down -0.15--0.3</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>Triangulation (3-leg test)</t>
+        </is>
+      </c>
+      <c r="B40" s="19" t="n"/>
+      <c r="C40" s="19" t="n"/>
+      <c r="D40" s="19" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="20" t="inlineStr">
+        <is>
+          <t>Leg 1 — Valuation</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="20" t="inlineStr">
+        <is>
+          <t>Leg 2 — Game theory</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="20" t="inlineStr">
+        <is>
+          <t>Leg 3 — Revealed preference</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="20" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Leg 1: Appliance multiples compressed; Whirlpool/peers trade at
+distressed margins; Electrolux's mid-cycle EBITDA on its
+pre-collapse base implies material upside on multiple
+normalisation alone.
+Leg 2: Investor AB (Wallenberg) as backstop is the cleanest
+natural-owner Nordic anchor pattern; Midea as strategic JV
+partner is Archetype D customer-aligned anchor; fully
+underwritten = no rump risk; EGM passed May 27 = governance
+settled.
+Leg 3: Investor AB undertaking 37.56% of the issue (pro-rata
++ guarantee) is the revealed-preference signal. They could
+have taken just pro-rata; the additional SEK 1.7bn guarantee
+on market terms is the asymmetric commitment.
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>Anchor</t>
+        </is>
+      </c>
+      <c r="B46" s="19" t="n"/>
+      <c r="C46" s="19" t="n"/>
+      <c r="D46" s="19" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="20" t="inlineStr">
+        <is>
+          <t>Parties</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="inlineStr">
+        <is>
+          <t>Investor AB (Wallenberg Foundations), Midea Group (strategic JV partner)</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="20" t="inlineStr">
+        <is>
+          <t>Stake (% est.)</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="inlineStr">
+        <is>
+          <t>17.94</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>Red flags</t>
+        </is>
+      </c>
+      <c r="B50" s="19" t="n"/>
+      <c r="C50" s="19" t="n"/>
+      <c r="D50" s="19" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="20" t="inlineStr">
+        <is>
+          <t>Triggered</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="inlineStr">
+        <is>
+          <t>None of 11 active</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="20" t="inlineStr">
+        <is>
+          <t>Watch list</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>Kill criteria</t>
+        </is>
+      </c>
+      <c r="B54" s="19" t="n"/>
+      <c r="C54" s="19" t="n"/>
+      <c r="D54" s="19" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="20" t="inlineStr">
+        <is>
+          <t>1.</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="inlineStr">
+        <is>
+          <t>Midea JV terminated or delayed beyond H1 2027</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="20" t="inlineStr">
+        <is>
+          <t>2.</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="inlineStr">
+        <is>
+          <t>US administration imposes punitive tariffs on China-affiliated JVs that void North America economics</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="20" t="inlineStr">
+        <is>
+          <t>3.</t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="inlineStr">
+        <is>
+          <t>Investor AB sells beyond pro-rata commitment</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="20" t="inlineStr">
+        <is>
+          <t>4.</t>
+        </is>
+      </c>
+      <c r="B58" s="5" t="inlineStr">
+        <is>
+          <t>Cost-out programme misses Q2 FY27 milestone by &gt;25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="20" t="inlineStr">
+        <is>
+          <t>5.</t>
+        </is>
+      </c>
+      <c r="B59" s="5" t="inlineStr">
+        <is>
+          <t>Second equity raise needed within 18 months</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="4" t="inlineStr">
+        <is>
+          <t>Pre-mortem</t>
+        </is>
+      </c>
+      <c r="B61" s="19" t="n"/>
+      <c r="C61" s="19" t="n"/>
+      <c r="D61" s="19" t="n"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="20" t="inlineStr"/>
+      <c r="B62" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">It is end-2027 and ELUX-B is down 70% from rights price.
+Most likely cause: Midea JV economics undermined by US-China
+trade frictions (tariff escalation, FDI screening, executive
+order action against Chinese ownership in North American
+consumer appliance market). Wallenberg held its position but
+growth thesis evaporated; legacy European appliance market
+did not recover as expected.
+Second-most-likely cause: Cost-out programme execution failed
+(factory transitions slipped; severance costs ballooned; one-off
+impairments cascaded). Q3 FY27 print missed materially; analyst
+downgrades cascaded.
+Where this would show up first: US executive-order activity on
+Chinese appliance JVs; quarterly factory-transition milestones
+in interim reports; Midea quarterly disclosures.
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="4" t="inlineStr">
+        <is>
+          <t>Tier rationale</t>
+        </is>
+      </c>
+      <c r="B64" s="19" t="n"/>
+      <c r="C64" s="19" t="n"/>
+      <c r="D64" s="19" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="20" t="inlineStr"/>
+      <c r="B65" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bucket A, Archetype A1 (Wallenberg as long-term natural-owner
+anchor at pro-rata + guarantee) + D (Midea as strategic customer
+partner). Triangulation 3/3 with verified anchor identity and
+voting power. C7 catalysts dated (Midea JV ramp H2 2026; cost-out
+H1 2027). No active red flags.
+This is the canonical Nordic Bucket A pattern that historically
+delivered 3-5x compounding (Wärtsilä, Atlas Copco split, SEB 2016
+rights). The Midea D-archetype layer is what makes the asymmetry
+meaningful — without the JV this would be a 2x normalisation
+trade; with it, the cycle + market-access combination supports
+base case 2.2x and bull 4.0x.
+Best Nordic recap candidate on the current screen.
+</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="49">
+    <mergeCell ref="B11:D11"/>
+    <mergeCell ref="B42:D42"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="B57:D57"/>
+    <mergeCell ref="B44:D44"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="B10:D10"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="A40:D40"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="B9:D9"/>
+    <mergeCell ref="A64:D64"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="B65:D65"/>
+    <mergeCell ref="B15:D15"/>
+    <mergeCell ref="B55:D55"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="B51:D51"/>
+    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="A61:D61"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="A54:D54"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B62:D62"/>
+    <mergeCell ref="B7:D7"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="A46:D46"/>
+    <mergeCell ref="B47:D47"/>
+    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="A18:D18"/>
+    <mergeCell ref="B59:D59"/>
+    <mergeCell ref="B31:D31"/>
+    <mergeCell ref="A50:D50"/>
+    <mergeCell ref="B22:D22"/>
+    <mergeCell ref="B27:D27"/>
+    <mergeCell ref="B56:D56"/>
+    <mergeCell ref="B58:D58"/>
+    <mergeCell ref="B52:D52"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="B43:D43"/>
+    <mergeCell ref="B12:D12"/>
+    <mergeCell ref="B48:D48"/>
+    <mergeCell ref="A14:D14"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D54"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Guaranty Trust Holding Company</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>GTCO  ·  NG  ·  Bucket A  ·  Archetype G, A1  ·  Tier 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>Risk-reward snapshot</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="n"/>
+      <c r="C4" s="19" t="n"/>
+      <c r="D4" s="19" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="20" t="inlineStr">
+        <is>
+          <t>Expected EV×</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>2.15×</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="20" t="inlineStr">
+        <is>
+          <t>Bear / Base / Bull return</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>0.60× / 2.10× / 3.80×</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="20" t="inlineStr">
+        <is>
+          <t>Bear loss</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>40%</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="20" t="inlineStr">
+        <is>
+          <t>Skew (upside/downside)</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>7.0×</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="20" t="inlineStr">
+        <is>
+          <t>Reward/Risk ratio</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>2.9×</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="20" t="inlineStr">
+        <is>
+          <t>Portfolio weight</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>3.00%</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="20" t="inlineStr">
+        <is>
+          <t>Cluster</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>EM_bank</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="20" t="inlineStr">
+        <is>
+          <t>Primary factor</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>idiosyncratic</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>Deal</t>
+        </is>
+      </c>
+      <c r="B14" s="19" t="n"/>
+      <c r="C14" s="19" t="n"/>
+      <c r="D14" s="19" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="20" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>2025-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="20" t="inlineStr">
+        <is>
+          <t>Mechanic</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>G — Central Bank of Nigeria mandated capital floor of ₦500bn for international-licensed banks by 31 March 2026. GTCO recapped via ₦209bn local rights + ₦366bn LSE primary listing at ₦70 (2.28bn new shares). Total ₦575bn raised. Sector-wide CBN floor triggered ₦4.6tn in raises across all major Nigerian banks. CAR 15.20pct; Tier-1 capital +21pct YoY. Trades single-digit P/E + &lt;1x book despite &gt;20pct ROE due to Naira FX volatility.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Scorecard</t>
+        </is>
+      </c>
+      <c r="B18" s="19" t="n"/>
+      <c r="C18" s="19" t="n"/>
+      <c r="D18" s="19" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="20" t="inlineStr">
+        <is>
+          <t>D4 Dilution Pct</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="20" t="inlineStr">
+        <is>
+          <t>D9 Alignment Gap</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="20" t="inlineStr">
+        <is>
+          <t>D11 Consensus Ebitda Cagr</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="20" t="inlineStr">
+        <is>
+          <t>D14 Liquidity Quarters</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>Catalysts</t>
+        </is>
+      </c>
+      <c r="B24" s="19" t="n"/>
+      <c r="C24" s="19" t="n"/>
+      <c r="D24" s="19" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="8" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B25" s="8" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="C25" s="8" t="inlineStr">
+        <is>
+          <t>P(yes)</t>
+        </is>
+      </c>
+      <c r="D25" s="8" t="inlineStr">
+        <is>
+          <t>Re-rate if yes / hit if no</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="32" customHeight="1">
+      <c r="A26" s="21" t="inlineStr">
+        <is>
+          <t>Naira stabilisation + FX policy normalisation</t>
+        </is>
+      </c>
+      <c r="B26" s="11" t="inlineStr">
+        <is>
+          <t>2026-06-01 → 2027-12-31</t>
+        </is>
+      </c>
+      <c r="C26" s="11" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="D26" s="11" t="inlineStr">
+        <is>
+          <t>Up 1.6-2.5× / Down -0.2--0.3</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="32" customHeight="1">
+      <c r="A27" s="22" t="inlineStr">
+        <is>
+          <t>Sector consolidation — Nigerian smaller banks fail compliance</t>
+        </is>
+      </c>
+      <c r="B27" s="14" t="inlineStr">
+        <is>
+          <t>2026-04-01 → 2027-12-31</t>
+        </is>
+      </c>
+      <c r="C27" s="14" t="inlineStr">
+        <is>
+          <t>0.45</t>
+        </is>
+      </c>
+      <c r="D27" s="14" t="inlineStr">
+        <is>
+          <t>Up 1.3-1.8× / Down -0.05--0.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="32" customHeight="1">
+      <c r="A28" s="21" t="inlineStr">
+        <is>
+          <t>Pan-African expansion (UEMOA + East African subsidiaries)</t>
+        </is>
+      </c>
+      <c r="B28" s="11" t="inlineStr">
+        <is>
+          <t>2026-09-01 → 2028-12-31</t>
+        </is>
+      </c>
+      <c r="C28" s="11" t="inlineStr">
+        <is>
+          <t>0.55</t>
+        </is>
+      </c>
+      <c r="D28" s="11" t="inlineStr">
+        <is>
+          <t>Up 1.3-1.8× / Down -0.1--0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="32" customHeight="1">
+      <c r="A29" s="22" t="inlineStr">
+        <is>
+          <t>Dividend re-rate (current yield distorted by Naira)</t>
+        </is>
+      </c>
+      <c r="B29" s="14" t="inlineStr">
+        <is>
+          <t>2026-12-01 → 2028-12-31</t>
+        </is>
+      </c>
+      <c r="C29" s="14" t="inlineStr">
+        <is>
+          <t>0.55</t>
+        </is>
+      </c>
+      <c r="D29" s="14" t="inlineStr">
+        <is>
+          <t>Up 1.2-1.5× / Down 0.0-0.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>Triangulation (3-leg test)</t>
+        </is>
+      </c>
+      <c r="B31" s="19" t="n"/>
+      <c r="C31" s="19" t="n"/>
+      <c r="D31" s="19" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="20" t="inlineStr">
+        <is>
+          <t>Leg 1 — Valuation</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="20" t="inlineStr">
+        <is>
+          <t>Leg 2 — Game theory</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="20" t="inlineStr">
+        <is>
+          <t>Leg 3 — Revealed preference</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="20" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Leg 1: &lt;1x book at &gt;20pct ROE = &gt;25pct USD-adjusted earnings
+yield. Single-digit P/E.
+Leg 2: CBN-mandated capital floor = regulatory anchor;
+GTCO already over-complied; sector consolidation forces
+rivals to follow.
+Leg 3: LSE listing 2025 at ₦70 = revealed-preference floor
+by international institutional capital; UK pension fund
+interest demonstrates capital depth.
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>Anchor</t>
+        </is>
+      </c>
+      <c r="B37" s="19" t="n"/>
+      <c r="C37" s="19" t="n"/>
+      <c r="D37" s="19" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="20" t="inlineStr">
+        <is>
+          <t>Parties</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="inlineStr">
+        <is>
+          <t>GTCO retail + institutional float (LSE listing 2025), Pan-African pension + sovereign holders</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="20" t="inlineStr">
+        <is>
+          <t>Stake (% est.)</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>Red flags</t>
+        </is>
+      </c>
+      <c r="B41" s="19" t="n"/>
+      <c r="C41" s="19" t="n"/>
+      <c r="D41" s="19" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="20" t="inlineStr">
+        <is>
+          <t>Triggered</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="inlineStr">
+        <is>
+          <t>None of 11 active</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="20" t="inlineStr">
+        <is>
+          <t>Watch list</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="inlineStr">
+        <is>
+          <t>Naira FX volatility is the dominant variable</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>Kill criteria</t>
+        </is>
+      </c>
+      <c r="B45" s="19" t="n"/>
+      <c r="C45" s="19" t="n"/>
+      <c r="D45" s="19" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="20" t="inlineStr">
+        <is>
+          <t>1.</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="inlineStr">
+        <is>
+          <t>Naira devalues another 30pct+ over 12 months</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="20" t="inlineStr">
+        <is>
+          <t>2.</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="inlineStr">
+        <is>
+          <t>CBN-mandated forbearance escalates banking losses</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="20" t="inlineStr">
+        <is>
+          <t>3.</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="inlineStr">
+        <is>
+          <t>Heritage-Bank-style failure cascades across mid-tier</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>Pre-mortem</t>
+        </is>
+      </c>
+      <c r="B50" s="19" t="n"/>
+      <c r="C50" s="19" t="n"/>
+      <c r="D50" s="19" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="20" t="inlineStr"/>
+      <c r="B51" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Naira devalued to ₦3000/USD; GTCO USD-translated book and
+earnings collapsed; FX losses materialised; multiple
+contracted to 0.4x book.
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>Tier rationale</t>
+        </is>
+      </c>
+      <c r="B53" s="19" t="n"/>
+      <c r="C53" s="19" t="n"/>
+      <c r="D53" s="19" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="20" t="inlineStr"/>
+      <c r="B54" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bucket A, Archetype G (regulator-forced sector recap — canonical
+Yes Bank / Greek banks template) + A1 (LSE listing as sovereign-
+adjacent international float). Universe screen 0.79. Tier 1 on
+triangulation + dated regulatory floor + cleanest USD-adjusted
+asymmetric setup in MEA basket.
+</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="37">
+    <mergeCell ref="B11:D11"/>
+    <mergeCell ref="B42:D42"/>
+    <mergeCell ref="A53:D53"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="B38:D38"/>
+    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="B10:D10"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="B9:D9"/>
+    <mergeCell ref="A24:D24"/>
+    <mergeCell ref="B15:D15"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="B51:D51"/>
+    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="B33:D33"/>
+    <mergeCell ref="A45:D45"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="B35:D35"/>
+    <mergeCell ref="A41:D41"/>
+    <mergeCell ref="B7:D7"/>
+    <mergeCell ref="B47:D47"/>
+    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="B54:D54"/>
+    <mergeCell ref="A37:D37"/>
+    <mergeCell ref="A18:D18"/>
+    <mergeCell ref="B46:D46"/>
+    <mergeCell ref="A50:D50"/>
+    <mergeCell ref="B22:D22"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="B43:D43"/>
+    <mergeCell ref="B12:D12"/>
+    <mergeCell ref="B39:D39"/>
+    <mergeCell ref="B48:D48"/>
+    <mergeCell ref="A14:D14"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D54"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Hitachi Construction Machinery</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>6305  ·  JP  ·  Bucket A  ·  Archetype H, A1  ·  Tier 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>Risk-reward snapshot</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="n"/>
+      <c r="C4" s="19" t="n"/>
+      <c r="D4" s="19" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="20" t="inlineStr">
+        <is>
+          <t>Expected EV×</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>1.69×</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="20" t="inlineStr">
+        <is>
+          <t>Bear / Base / Bull return</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>0.75× / 1.70× / 2.80×</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="20" t="inlineStr">
+        <is>
+          <t>Bear loss</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="20" t="inlineStr">
+        <is>
+          <t>Skew (upside/downside)</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>7.2×</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="20" t="inlineStr">
+        <is>
+          <t>Reward/Risk ratio</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>2.8×</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="20" t="inlineStr">
+        <is>
+          <t>Portfolio weight</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>3.00%</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="20" t="inlineStr">
+        <is>
+          <t>Cluster</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>Asian_governance_reform</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="20" t="inlineStr">
+        <is>
+          <t>Primary factor</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>policy</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>Deal</t>
+        </is>
+      </c>
+      <c r="B14" s="19" t="n"/>
+      <c r="C14" s="19" t="n"/>
+      <c r="D14" s="19" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="20" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="20" t="inlineStr">
+        <is>
+          <t>Mechanic</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>H — Japan FIEA mandatory-TOB threshold cut from 33.3pct to 30pct effective May 1, 2026. Hitachi parent owns 30.7pct + Itochu 25pct = combined 55.7pct. Post-amendment Hitachi cannot rationally hold 30.7pct indefinitely: either step back below threshold or commit full TOB. Construction-machinery cycle inflection; HEC was carved out from Hitachi Construction Holdings 2007 - now a candidate parent-subsidiary buy-in (HEC-Itochu MBO precedent in 2022 Alps Logistics 194pct premium).</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Scorecard</t>
+        </is>
+      </c>
+      <c r="B18" s="19" t="n"/>
+      <c r="C18" s="19" t="n"/>
+      <c r="D18" s="19" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="20" t="inlineStr">
+        <is>
+          <t>D4 Dilution Pct</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="20" t="inlineStr">
+        <is>
+          <t>D9 Alignment Gap</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="20" t="inlineStr">
+        <is>
+          <t>D11 Consensus Ebitda Cagr</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="20" t="inlineStr">
+        <is>
+          <t>D14 Liquidity Quarters</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>Catalysts</t>
+        </is>
+      </c>
+      <c r="B24" s="19" t="n"/>
+      <c r="C24" s="19" t="n"/>
+      <c r="D24" s="19" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="8" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B25" s="8" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="C25" s="8" t="inlineStr">
+        <is>
+          <t>P(yes)</t>
+        </is>
+      </c>
+      <c r="D25" s="8" t="inlineStr">
+        <is>
+          <t>Re-rate if yes / hit if no</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="32" customHeight="1">
+      <c r="A26" s="21" t="inlineStr">
+        <is>
+          <t>Hitachi parent decision on stake — step back below 30pct or full TOB</t>
+        </is>
+      </c>
+      <c r="B26" s="11" t="inlineStr">
+        <is>
+          <t>2026-09-01 → 2027-06-30</t>
+        </is>
+      </c>
+      <c r="C26" s="11" t="inlineStr">
+        <is>
+          <t>0.55</t>
+        </is>
+      </c>
+      <c r="D26" s="11" t="inlineStr">
+        <is>
+          <t>Up 1.5-2.5× / Down -0.1--0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="32" customHeight="1">
+      <c r="A27" s="22" t="inlineStr">
+        <is>
+          <t>Construction cycle inflection (mining + infrastructure + EV-mining)</t>
+        </is>
+      </c>
+      <c r="B27" s="14" t="inlineStr">
+        <is>
+          <t>2026-06-01 → 2028-06-30</t>
+        </is>
+      </c>
+      <c r="C27" s="14" t="inlineStr">
+        <is>
+          <t>0.55</t>
+        </is>
+      </c>
+      <c r="D27" s="14" t="inlineStr">
+        <is>
+          <t>Up 1.3-1.8× / Down -0.1--0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="32" customHeight="1">
+      <c r="A28" s="21" t="inlineStr">
+        <is>
+          <t>Itochu strategic action (counter-bid or MBO partnership)</t>
+        </is>
+      </c>
+      <c r="B28" s="11" t="inlineStr">
+        <is>
+          <t>2026-09-01 → 2027-12-31</t>
+        </is>
+      </c>
+      <c r="C28" s="11" t="inlineStr">
+        <is>
+          <t>0.4</t>
+        </is>
+      </c>
+      <c r="D28" s="11" t="inlineStr">
+        <is>
+          <t>Up 1.6-2.2× / Down -0.05--0.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>Triangulation (3-leg test)</t>
+        </is>
+      </c>
+      <c r="B30" s="19" t="n"/>
+      <c r="C30" s="19" t="n"/>
+      <c r="D30" s="19" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="20" t="inlineStr">
+        <is>
+          <t>Leg 1 — Valuation</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>partial</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="20" t="inlineStr">
+        <is>
+          <t>Leg 2 — Game theory</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="20" t="inlineStr">
+        <is>
+          <t>Leg 3 — Revealed preference</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>partial</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="20" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Leg 1: At 1.2x PBR not deeply undervalued vs sector; the
+alpha is in the takeout premium not the multiple gap.
+Leg 2: FIEA mandatory-TOB threshold has triggered for
+Hitachi parent. Game-theoretic option: step back (sale into
+market) or take out (TOB at premium). Either way creates
+forced flow.
+Leg 3: PARTIAL — Alps Logistics 194pct TOB premium (Itochu
+template) and Hitachi-Logisteed 40pct sale to KKR Apr 2023
+are precedents but no Hitachi statement of intent on HEC yet.
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>Anchor</t>
+        </is>
+      </c>
+      <c r="B36" s="19" t="n"/>
+      <c r="C36" s="19" t="n"/>
+      <c r="D36" s="19" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="20" t="inlineStr">
+        <is>
+          <t>Parties</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="inlineStr">
+        <is>
+          <t>Hitachi Ltd parent (30.7pct), Itochu Corp (25.0pct)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="20" t="inlineStr">
+        <is>
+          <t>Stake (% est.)</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="inlineStr">
+        <is>
+          <t>55.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>Red flags</t>
+        </is>
+      </c>
+      <c r="B40" s="19" t="n"/>
+      <c r="C40" s="19" t="n"/>
+      <c r="D40" s="19" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="20" t="inlineStr">
+        <is>
+          <t>Triggered</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>None of 11 active</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="20" t="inlineStr">
+        <is>
+          <t>Watch list</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>Kill criteria</t>
+        </is>
+      </c>
+      <c r="B44" s="19" t="n"/>
+      <c r="C44" s="19" t="n"/>
+      <c r="D44" s="19" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="20" t="inlineStr">
+        <is>
+          <t>1.</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="inlineStr">
+        <is>
+          <t>Japan FIEA enforcement grace period extended &gt;24 months</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="20" t="inlineStr">
+        <is>
+          <t>2.</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="inlineStr">
+        <is>
+          <t>Hitachi parent announces 'long-term hold' positioning</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="20" t="inlineStr">
+        <is>
+          <t>3.</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="inlineStr">
+        <is>
+          <t>Construction cycle deepens beyond 2026 trough</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="20" t="inlineStr">
+        <is>
+          <t>4.</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="inlineStr">
+        <is>
+          <t>Itochu strategically retreats from machinery sector</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>Pre-mortem</t>
+        </is>
+      </c>
+      <c r="B50" s="19" t="n"/>
+      <c r="C50" s="19" t="n"/>
+      <c r="D50" s="19" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="20" t="inlineStr"/>
+      <c r="B51" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">It is end-2027 and 6305 is down 50pct from current.
+Most likely: Hitachi parent given long FIEA enforcement
+grace period; no TOB; construction cycle weakened on global
+CapEx slowdown; multiple compressed.
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>Tier rationale</t>
+        </is>
+      </c>
+      <c r="B53" s="19" t="n"/>
+      <c r="C53" s="19" t="n"/>
+      <c r="D53" s="19" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="20" t="inlineStr"/>
+      <c r="B54" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bucket A, Archetype H (governance reset via FIEA forced
+decision) + A1 (parent + Itochu as combined 55.7pct cap-stack
+anchor). Universe screen 0.86. Tier 2 because catalyst is dated
+but binary on Hitachi parent's specific decision.
+</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="38">
+    <mergeCell ref="B11:D11"/>
+    <mergeCell ref="B42:D42"/>
+    <mergeCell ref="A53:D53"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="B38:D38"/>
+    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="A44:D44"/>
+    <mergeCell ref="B10:D10"/>
+    <mergeCell ref="A40:D40"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="B37:D37"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="B9:D9"/>
+    <mergeCell ref="A24:D24"/>
+    <mergeCell ref="B15:D15"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="A36:D36"/>
+    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="B51:D51"/>
+    <mergeCell ref="B33:D33"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="B45:D45"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="B7:D7"/>
+    <mergeCell ref="B47:D47"/>
+    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="B54:D54"/>
+    <mergeCell ref="A18:D18"/>
+    <mergeCell ref="B31:D31"/>
+    <mergeCell ref="B46:D46"/>
+    <mergeCell ref="A50:D50"/>
+    <mergeCell ref="B22:D22"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="B12:D12"/>
+    <mergeCell ref="B48:D48"/>
+    <mergeCell ref="A14:D14"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D53"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Drake &amp; Scull International</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>DSI  ·  AE  ·  Bucket A  ·  Archetype E  ·  Tier 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>Risk-reward snapshot</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="n"/>
+      <c r="C4" s="19" t="n"/>
+      <c r="D4" s="19" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="20" t="inlineStr">
+        <is>
+          <t>Expected EV×</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>2.25×</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="20" t="inlineStr">
+        <is>
+          <t>Bear / Base / Bull return</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>0.55× / 2.30× / 4.20×</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="20" t="inlineStr">
+        <is>
+          <t>Bear loss</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>45%</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="20" t="inlineStr">
+        <is>
+          <t>Skew (upside/downside)</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>7.1×</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="20" t="inlineStr">
+        <is>
+          <t>Reward/Risk ratio</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>2.8×</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="20" t="inlineStr">
+        <is>
+          <t>Portfolio weight</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>3.00%</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="20" t="inlineStr">
+        <is>
+          <t>Cluster</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>EM_bank</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="20" t="inlineStr">
+        <is>
+          <t>Primary factor</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>idiosyncratic</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>Deal</t>
+        </is>
+      </c>
+      <c r="B14" s="19" t="n"/>
+      <c r="C14" s="19" t="n"/>
+      <c r="D14" s="19" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="20" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>2024-04-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="20" t="inlineStr">
+        <is>
+          <t>Mechanic</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>E — UAE-equivalent restructuring with capital restoration. April 2024: AED 4.18bn debt write-off (90pct); AED 600m mandatory convertible sukuk issued; AED 800m capital reduction. Tabarak Investment (strategic since 2017) increased stake. Trading resumed May 2024 after 5-year halt. CEO Mansour Lootah leading recovery.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Scorecard</t>
+        </is>
+      </c>
+      <c r="B18" s="19" t="n"/>
+      <c r="C18" s="19" t="n"/>
+      <c r="D18" s="19" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="20" t="inlineStr">
+        <is>
+          <t>D4 Dilution Pct</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="20" t="inlineStr">
+        <is>
+          <t>D9 Alignment Gap</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="20" t="inlineStr">
+        <is>
+          <t>D11 Consensus Ebitda Cagr</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="20" t="inlineStr">
+        <is>
+          <t>D14 Liquidity Quarters</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>Catalysts</t>
+        </is>
+      </c>
+      <c r="B24" s="19" t="n"/>
+      <c r="C24" s="19" t="n"/>
+      <c r="D24" s="19" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="8" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B25" s="8" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="C25" s="8" t="inlineStr">
+        <is>
+          <t>P(yes)</t>
+        </is>
+      </c>
+      <c r="D25" s="8" t="inlineStr">
+        <is>
+          <t>Re-rate if yes / hit if no</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="32" customHeight="1">
+      <c r="A26" s="21" t="inlineStr">
+        <is>
+          <t>Backlog rebuild (UAE/GCC infrastructure pipeline)</t>
+        </is>
+      </c>
+      <c r="B26" s="11" t="inlineStr">
+        <is>
+          <t>2026-06-01 → 2028-06-30</t>
+        </is>
+      </c>
+      <c r="C26" s="11" t="inlineStr">
+        <is>
+          <t>0.55</t>
+        </is>
+      </c>
+      <c r="D26" s="11" t="inlineStr">
+        <is>
+          <t>Up 1.8-2.5× / Down -0.2--0.3</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="32" customHeight="1">
+      <c r="A27" s="22" t="inlineStr">
+        <is>
+          <t>Convertible sukuk conversion + capital structure simplification</t>
+        </is>
+      </c>
+      <c r="B27" s="14" t="inlineStr">
+        <is>
+          <t>2026-09-01 → 2027-12-31</t>
+        </is>
+      </c>
+      <c r="C27" s="14" t="inlineStr">
+        <is>
+          <t>0.55</t>
+        </is>
+      </c>
+      <c r="D27" s="14" t="inlineStr">
+        <is>
+          <t>Up 1.3-1.6× / Down -0.1--0.15</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="32" customHeight="1">
+      <c r="A28" s="21" t="inlineStr">
+        <is>
+          <t>Tabarak strategic-buyer follow-on or international JV partner</t>
+        </is>
+      </c>
+      <c r="B28" s="11" t="inlineStr">
+        <is>
+          <t>2026-09-01 → 2028-12-31</t>
+        </is>
+      </c>
+      <c r="C28" s="11" t="inlineStr">
+        <is>
+          <t>0.4</t>
+        </is>
+      </c>
+      <c r="D28" s="11" t="inlineStr">
+        <is>
+          <t>Up 1.8-2.5× / Down -0.05--0.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>Triangulation (3-leg test)</t>
+        </is>
+      </c>
+      <c r="B30" s="19" t="n"/>
+      <c r="C30" s="19" t="n"/>
+      <c r="D30" s="19" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="20" t="inlineStr">
+        <is>
+          <t>Leg 1 — Valuation</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>partial</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="20" t="inlineStr">
+        <is>
+          <t>Leg 2 — Game theory</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="20" t="inlineStr">
+        <is>
+          <t>Leg 3 — Revealed preference</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="20" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Leg 1: Post-recap cap structure clean; 90pct of legacy debt
+written off creates large operating leverage to backlog
+rebuild. But absolute valuation tough without normalised
+EBITDA reference.
+Leg 2: Tabarak in since 2017 = patient anchor + UAE
+sovereign-adjacent capital base.
+Leg 3: AED 4.18bn debt forgiveness = creditor revealed
+preference for survival over liquidation.
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>Anchor</t>
+        </is>
+      </c>
+      <c r="B36" s="19" t="n"/>
+      <c r="C36" s="19" t="n"/>
+      <c r="D36" s="19" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="20" t="inlineStr">
+        <is>
+          <t>Parties</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="inlineStr">
+        <is>
+          <t>Tabarak Investment (strategic anchor 2017+)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="20" t="inlineStr">
+        <is>
+          <t>Stake (% est.)</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>Red flags</t>
+        </is>
+      </c>
+      <c r="B40" s="19" t="n"/>
+      <c r="C40" s="19" t="n"/>
+      <c r="D40" s="19" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="20" t="inlineStr">
+        <is>
+          <t>Triggered</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>None of 11 active</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="20" t="inlineStr">
+        <is>
+          <t>Watch list</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="inlineStr">
+        <is>
+          <t>5-year trading halt history; legacy litigation overhang; limited float</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>Kill criteria</t>
+        </is>
+      </c>
+      <c r="B44" s="19" t="n"/>
+      <c r="C44" s="19" t="n"/>
+      <c r="D44" s="19" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="20" t="inlineStr">
+        <is>
+          <t>1.</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="inlineStr">
+        <is>
+          <t>Second restructuring needed before 2027</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="20" t="inlineStr">
+        <is>
+          <t>2.</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="inlineStr">
+        <is>
+          <t>Tabarak reduces stake</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="20" t="inlineStr">
+        <is>
+          <t>3.</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="inlineStr">
+        <is>
+          <t>Backlog material below normalised expectations through 2027</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>Pre-mortem</t>
+        </is>
+      </c>
+      <c r="B49" s="19" t="n"/>
+      <c r="C49" s="19" t="n"/>
+      <c r="D49" s="19" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="20" t="inlineStr"/>
+      <c r="B50" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">It is end-2027 and DSI is down 60pct.
+Most likely: Backlog rebuild stalled; legacy litigation
+reactivated; GCC infrastructure cycle slowed; second
+restructuring or distressed equity raise.
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>Tier rationale</t>
+        </is>
+      </c>
+      <c r="B52" s="19" t="n"/>
+      <c r="C52" s="19" t="n"/>
+      <c r="D52" s="19" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="20" t="inlineStr"/>
+      <c r="B53" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bucket A, Archetype E (national bankruptcy framework / DIFC
+restructuring). Universe-screener 0.78 (15th). Tier 2 because
+legacy 5-year-halt history + low float + limited operational
+evidence post-recap. Builds for diversification within MEA
+basket; complements GTCO Nigerian recap basket exposure.
+</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="37">
+    <mergeCell ref="B11:D11"/>
+    <mergeCell ref="B42:D42"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="A52:D52"/>
+    <mergeCell ref="B53:D53"/>
+    <mergeCell ref="B38:D38"/>
+    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="A44:D44"/>
+    <mergeCell ref="B10:D10"/>
+    <mergeCell ref="A40:D40"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="B37:D37"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="B9:D9"/>
+    <mergeCell ref="A24:D24"/>
+    <mergeCell ref="A49:D49"/>
+    <mergeCell ref="B15:D15"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="A36:D36"/>
+    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="B33:D33"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="B45:D45"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="B50:D50"/>
+    <mergeCell ref="B7:D7"/>
+    <mergeCell ref="B47:D47"/>
+    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="A18:D18"/>
+    <mergeCell ref="B31:D31"/>
+    <mergeCell ref="B46:D46"/>
+    <mergeCell ref="B22:D22"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="B12:D12"/>
+    <mergeCell ref="A14:D14"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D53"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Doosan Bobcat (+ Doosan Robotics merger)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>241560  ·  KR  ·  Bucket A  ·  Archetype H, E  ·  Tier 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>Risk-reward snapshot</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="n"/>
+      <c r="C4" s="19" t="n"/>
+      <c r="D4" s="19" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="20" t="inlineStr">
+        <is>
+          <t>Expected EV×</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>1.66×</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="20" t="inlineStr">
+        <is>
+          <t>Bear / Base / Bull return</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>0.75× / 1.70× / 2.50×</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="20" t="inlineStr">
+        <is>
+          <t>Bear loss</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="20" t="inlineStr">
+        <is>
+          <t>Skew (upside/downside)</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>6.0×</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="20" t="inlineStr">
+        <is>
+          <t>Reward/Risk ratio</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>2.7×</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="20" t="inlineStr">
+        <is>
+          <t>Portfolio weight</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>3.00%</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="20" t="inlineStr">
+        <is>
+          <t>Cluster</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>Asian_governance_reform</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="20" t="inlineStr">
+        <is>
+          <t>Primary factor</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>policy</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>Deal</t>
+        </is>
+      </c>
+      <c r="B14" s="19" t="n"/>
+      <c r="C14" s="19" t="n"/>
+      <c r="D14" s="19" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="20" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="20" t="inlineStr">
+        <is>
+          <t>Mechanic</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>H + E — Korean H6 governance overhaul. Aug 2024 original stock-swap proposal blocked by minority opposition + K-FSC ruling original ratio undervalued Bobcat. Q2 2026 revised terms tabled; Doosan Group cannot drop restructuring. Korean Commercial Act third amendment effective March 6, 2026 mandates treasury-share cancellation + cumulative voting for large companies + strengthened minority-shareholder rights — reform forcing chaebol governance overhaul.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Scorecard</t>
+        </is>
+      </c>
+      <c r="B18" s="19" t="n"/>
+      <c r="C18" s="19" t="n"/>
+      <c r="D18" s="19" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="20" t="inlineStr">
+        <is>
+          <t>D4 Dilution Pct</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="20" t="inlineStr">
+        <is>
+          <t>D9 Alignment Gap</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="20" t="inlineStr">
+        <is>
+          <t>D11 Consensus Ebitda Cagr</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="20" t="inlineStr">
+        <is>
+          <t>D14 Liquidity Quarters</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>Catalysts</t>
+        </is>
+      </c>
+      <c r="B24" s="19" t="n"/>
+      <c r="C24" s="19" t="n"/>
+      <c r="D24" s="19" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="8" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B25" s="8" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="C25" s="8" t="inlineStr">
+        <is>
+          <t>P(yes)</t>
+        </is>
+      </c>
+      <c r="D25" s="8" t="inlineStr">
+        <is>
+          <t>Re-rate if yes / hit if no</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="32" customHeight="1">
+      <c r="A26" s="21" t="inlineStr">
+        <is>
+          <t>Revised stock-swap terms approved at Q2 2026 EGM (or alternative restructuring)</t>
+        </is>
+      </c>
+      <c r="B26" s="11" t="inlineStr">
+        <is>
+          <t>2026-06-01 → 2026-12-31</t>
+        </is>
+      </c>
+      <c r="C26" s="11" t="inlineStr">
+        <is>
+          <t>0.6</t>
+        </is>
+      </c>
+      <c r="D26" s="11" t="inlineStr">
+        <is>
+          <t>Up 1.4-2.0× / Down -0.1--0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="32" customHeight="1">
+      <c r="A27" s="22" t="inlineStr">
+        <is>
+          <t>Treasury-share cancellation announcement (Commercial Act compliance)</t>
+        </is>
+      </c>
+      <c r="B27" s="14" t="inlineStr">
+        <is>
+          <t>2026-09-01 → 2027-09-06</t>
+        </is>
+      </c>
+      <c r="C27" s="14" t="inlineStr">
+        <is>
+          <t>0.65</t>
+        </is>
+      </c>
+      <c r="D27" s="14" t="inlineStr">
+        <is>
+          <t>Up 1.2-1.5× / Down -0.05--0.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="32" customHeight="1">
+      <c r="A28" s="21" t="inlineStr">
+        <is>
+          <t>Korea Value-Up cohort re-rating (chaebol holdcos + treasury cancellation cascade)</t>
+        </is>
+      </c>
+      <c r="B28" s="11" t="inlineStr">
+        <is>
+          <t>2026-06-01 → 2028-06-30</t>
+        </is>
+      </c>
+      <c r="C28" s="11" t="inlineStr">
+        <is>
+          <t>0.55</t>
+        </is>
+      </c>
+      <c r="D28" s="11" t="inlineStr">
+        <is>
+          <t>Up 1.3-1.8× / Down -0.1--0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>Triangulation (3-leg test)</t>
+        </is>
+      </c>
+      <c r="B30" s="19" t="n"/>
+      <c r="C30" s="19" t="n"/>
+      <c r="D30" s="19" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="20" t="inlineStr">
+        <is>
+          <t>Leg 1 — Valuation</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="20" t="inlineStr">
+        <is>
+          <t>Leg 2 — Game theory</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="20" t="inlineStr">
+        <is>
+          <t>Leg 3 — Revealed preference</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="20" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Leg 1: Bobcat at materially below SOTP; Robotics premium
+reflects valuation gap.
+Leg 2: Three forcing functions converge — Q2 2026 revised
+terms, Commercial Act amendment, treasury-share deadlines.
+Leg 3: K-FSC original-ratio rejection = revealed-preference
+floor; minority shareholders showed they can block; Park
+family must engage in good faith.
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>Anchor</t>
+        </is>
+      </c>
+      <c r="B36" s="19" t="n"/>
+      <c r="C36" s="19" t="n"/>
+      <c r="D36" s="19" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="20" t="inlineStr">
+        <is>
+          <t>Parties</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="inlineStr">
+        <is>
+          <t>Doosan Group (Park family), Korea Value-Up framework + K-FSC enforcement</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="20" t="inlineStr">
+        <is>
+          <t>Stake (% est.)</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>Red flags</t>
+        </is>
+      </c>
+      <c r="B40" s="19" t="n"/>
+      <c r="C40" s="19" t="n"/>
+      <c r="D40" s="19" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="20" t="inlineStr">
+        <is>
+          <t>Triggered</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>None of 11 active</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="20" t="inlineStr">
+        <is>
+          <t>Watch list</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>Kill criteria</t>
+        </is>
+      </c>
+      <c r="B44" s="19" t="n"/>
+      <c r="C44" s="19" t="n"/>
+      <c r="D44" s="19" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="20" t="inlineStr">
+        <is>
+          <t>1.</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="inlineStr">
+        <is>
+          <t>Park family abandons restructuring; Bobcat trades as standalone</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="20" t="inlineStr">
+        <is>
+          <t>2.</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="inlineStr">
+        <is>
+          <t>Construction cycle deepens; Bobcat margins compress</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="20" t="inlineStr">
+        <is>
+          <t>3.</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="inlineStr">
+        <is>
+          <t>Doosan Group financial stress forces distressed disposal</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>Pre-mortem</t>
+        </is>
+      </c>
+      <c r="B49" s="19" t="n"/>
+      <c r="C49" s="19" t="n"/>
+      <c r="D49" s="19" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="20" t="inlineStr"/>
+      <c r="B50" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">It is end-2027 and 241560 is down 50pct.
+Most likely: Restructuring postponed; chaebol family
+prioritised group-level liquidity needs; construction cycle
+weakened; multiple compressed.
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>Tier rationale</t>
+        </is>
+      </c>
+      <c r="B52" s="19" t="n"/>
+      <c r="C52" s="19" t="n"/>
+      <c r="D52" s="19" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="20" t="inlineStr"/>
+      <c r="B53" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bucket A, Archetype H (governance overhaul via K-FSC + Korean
+reform regime) + E (court/regulatory-sanctioned restructuring).
+Universe-screener 0.86. Tier 1 on multiple dated triggers
++ clear forcing functions + minority-shareholder protection
+precedent established.
+</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="37">
+    <mergeCell ref="B11:D11"/>
+    <mergeCell ref="B42:D42"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="A52:D52"/>
+    <mergeCell ref="B53:D53"/>
+    <mergeCell ref="B38:D38"/>
+    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="A44:D44"/>
+    <mergeCell ref="B10:D10"/>
+    <mergeCell ref="A40:D40"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="B37:D37"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="B9:D9"/>
+    <mergeCell ref="A24:D24"/>
+    <mergeCell ref="A49:D49"/>
+    <mergeCell ref="B15:D15"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="A36:D36"/>
+    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="B33:D33"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="B45:D45"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="B50:D50"/>
+    <mergeCell ref="B7:D7"/>
+    <mergeCell ref="B47:D47"/>
+    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="A18:D18"/>
+    <mergeCell ref="B31:D31"/>
+    <mergeCell ref="B46:D46"/>
+    <mergeCell ref="B22:D22"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="B12:D12"/>
+    <mergeCell ref="A14:D14"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D65"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Eutelsat Communications</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>ETL  ·  FR  ·  Bucket A  ·  Archetype A1, F  ·  Tier 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>Risk-reward snapshot</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="n"/>
+      <c r="C4" s="19" t="n"/>
+      <c r="D4" s="19" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="20" t="inlineStr">
+        <is>
+          <t>Expected EV×</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>2.35×</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="20" t="inlineStr">
+        <is>
+          <t>Bear / Base / Bull return</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>0.50× / 2.20× / 4.50×</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="20" t="inlineStr">
+        <is>
+          <t>Bear loss</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="20" t="inlineStr">
+        <is>
+          <t>Skew (upside/downside)</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>7.0×</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="20" t="inlineStr">
+        <is>
+          <t>Reward/Risk ratio</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>2.7×</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="20" t="inlineStr">
+        <is>
+          <t>Portfolio weight</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>3.00%</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="20" t="inlineStr">
+        <is>
+          <t>Cluster</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>French_sovereign</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="20" t="inlineStr">
+        <is>
+          <t>Primary factor</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>policy</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>Deal</t>
+        </is>
+      </c>
+      <c r="B14" s="19" t="n"/>
+      <c r="C14" s="19" t="n"/>
+      <c r="D14" s="19" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="20" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>2025-12-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="20" t="inlineStr">
+        <is>
+          <t>Mechanic</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>Two-tier capital raise: c.€830m reserved increase to French State/Bharti/UK Gov/CMA CGM at premium price + €670m 8-for-11 rights at €1.35 (settled Dec 16, 2025); part of c.€1.5bn package with €4bn investment programme through 2026-2029</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Scorecard</t>
+        </is>
+      </c>
+      <c r="B18" s="19" t="n"/>
+      <c r="C18" s="19" t="n"/>
+      <c r="D18" s="19" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="20" t="inlineStr">
+        <is>
+          <t>D2 Issue Discount Pct</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="20" t="inlineStr">
+        <is>
+          <t>D3 Backstop Cost Pct</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="20" t="inlineStr">
+        <is>
+          <t>D4 Dilution Pct</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="20" t="inlineStr">
+        <is>
+          <t>D5 Delta Wam Months</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="20" t="inlineStr">
+        <is>
+          <t>D6 Debt Tranches Post</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="20" t="inlineStr">
+        <is>
+          <t>D7 Ucc Terminations Pm30D</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="20" t="inlineStr">
+        <is>
+          <t>D8 Mip Strike Over Recap</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="20" t="inlineStr">
+        <is>
+          <t>D9 Alignment Gap</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>1.41</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="20" t="inlineStr">
+        <is>
+          <t>D9B Anchor Premium To Recap</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="20" t="inlineStr">
+        <is>
+          <t>D9C Premium To Vwap</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="20" t="inlineStr">
+        <is>
+          <t>D9D Liquidation Recovery Pct</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="20" t="inlineStr">
+        <is>
+          <t>D11 Consensus Ebitda Cagr</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="20" t="inlineStr">
+        <is>
+          <t>D13 Altman Z</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="20" t="inlineStr">
+        <is>
+          <t>D14 Liquidity Quarters</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>Catalysts</t>
+        </is>
+      </c>
+      <c r="B34" s="19" t="n"/>
+      <c r="C34" s="19" t="n"/>
+      <c r="D34" s="19" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="8" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B35" s="8" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="C35" s="8" t="inlineStr">
+        <is>
+          <t>P(yes)</t>
+        </is>
+      </c>
+      <c r="D35" s="8" t="inlineStr">
+        <is>
+          <t>Re-rate if yes / hit if no</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="32" customHeight="1">
+      <c r="A36" s="21" t="inlineStr">
+        <is>
+          <t>IRIS² European sovereign LEO constellation operational milestones</t>
+        </is>
+      </c>
+      <c r="B36" s="11" t="inlineStr">
+        <is>
+          <t>2026-01-01 → 2029-12-31</t>
+        </is>
+      </c>
+      <c r="C36" s="11" t="inlineStr">
+        <is>
+          <t>0.55</t>
+        </is>
+      </c>
+      <c r="D36" s="11" t="inlineStr">
+        <is>
+          <t>Up 1.8-3.5× / Down -0.3--0.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="32" customHeight="1">
+      <c r="A37" s="22" t="inlineStr">
+        <is>
+          <t>OneWeb integration / commercial revenue synergies</t>
+        </is>
+      </c>
+      <c r="B37" s="14" t="inlineStr">
+        <is>
+          <t>2026-06-01 → 2027-12-31</t>
+        </is>
+      </c>
+      <c r="C37" s="14" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="D37" s="14" t="inlineStr">
+        <is>
+          <t>Up 1.5-2.5× / Down -0.2--0.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="32" customHeight="1">
+      <c r="A38" s="21" t="inlineStr">
+        <is>
+          <t>Defence broadband contract wins (EU Strategic Compass)</t>
+        </is>
+      </c>
+      <c r="B38" s="11" t="inlineStr">
+        <is>
+          <t>2026-06-01 → 2028-06-30</t>
+        </is>
+      </c>
+      <c r="C38" s="11" t="inlineStr">
+        <is>
+          <t>0.45</t>
+        </is>
+      </c>
+      <c r="D38" s="11" t="inlineStr">
+        <is>
+          <t>Up 1.4-2.2× / Down -0.1--0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>Triangulation (3-leg test)</t>
+        </is>
+      </c>
+      <c r="B40" s="19" t="n"/>
+      <c r="C40" s="19" t="n"/>
+      <c r="D40" s="19" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="20" t="inlineStr">
+        <is>
+          <t>Leg 1 — Valuation</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="20" t="inlineStr">
+        <is>
+          <t>Leg 2 — Game theory</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="20" t="inlineStr">
+        <is>
+          <t>Leg 3 — Revealed preference</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="20" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Leg 1: Pre-IRIS² EBITDA ~€800m on cap c.€2.5bn = EV/EBITDA ~3.5x PF
+vs SES 5-6x, Iridium 12x. Clear through-cycle asymmetry.
+Leg 2: Sovereign + strategic anchors with no fee/warrant kicker, no
+cramdown, no DIP. Lockup 6 months from settlement.
+Leg 3: The reserved capital increase TO ANCHORS at a premium price
+while parallel rights cleared at €1.35 is itself the revealed-
+preference signal. Current market €2.84 sits between anchor entry
+€4.00 and rights price €1.35, so partial re-rate priced.
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>Anchor</t>
+        </is>
+      </c>
+      <c r="B46" s="19" t="n"/>
+      <c r="C46" s="19" t="n"/>
+      <c r="D46" s="19" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="20" t="inlineStr">
+        <is>
+          <t>Parties</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="inlineStr">
+        <is>
+          <t>French State (APE), Bharti Space, UK Government, CMA CGM, FSP</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="20" t="inlineStr">
+        <is>
+          <t>Stake (% est.)</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>Red flags</t>
+        </is>
+      </c>
+      <c r="B50" s="19" t="n"/>
+      <c r="C50" s="19" t="n"/>
+      <c r="D50" s="19" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="20" t="inlineStr">
+        <is>
+          <t>Triggered</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="inlineStr">
+        <is>
+          <t>None of 11 active</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="20" t="inlineStr">
+        <is>
+          <t>Watch list</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>Kill criteria</t>
+        </is>
+      </c>
+      <c r="B54" s="19" t="n"/>
+      <c r="C54" s="19" t="n"/>
+      <c r="D54" s="19" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="20" t="inlineStr">
+        <is>
+          <t>1.</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="inlineStr">
+        <is>
+          <t>IRIS² programme delay &gt;12 months announced</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="20" t="inlineStr">
+        <is>
+          <t>2.</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="inlineStr">
+        <is>
+          <t>Sovereign anchor exits lockup early or sells below cost</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="20" t="inlineStr">
+        <is>
+          <t>3.</t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="inlineStr">
+        <is>
+          <t>OneWeb integration write-down &gt;€500m</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="20" t="inlineStr">
+        <is>
+          <t>4.</t>
+        </is>
+      </c>
+      <c r="B58" s="5" t="inlineStr">
+        <is>
+          <t>SES/Starlink pricing war causes &gt;20% revenue impairment</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="20" t="inlineStr">
+        <is>
+          <t>5.</t>
+        </is>
+      </c>
+      <c r="B59" s="5" t="inlineStr">
+        <is>
+          <t>Quarterly LEO connectivity revenue growth decelerates below 0% YoY</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="4" t="inlineStr">
+        <is>
+          <t>Pre-mortem</t>
+        </is>
+      </c>
+      <c r="B61" s="19" t="n"/>
+      <c r="C61" s="19" t="n"/>
+      <c r="D61" s="19" t="n"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="20" t="inlineStr"/>
+      <c r="B62" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">It is end-2028 and ETL is down 70% from current ~€2.84.
+Most likely cause: IRIS² programme suffered material delays
+(mechanical: launch failures or contractor disputes; political:
+EU budget renegotiation under fiscal pressure). Eutelsat's role
+was reduced or contract terms re-cut. Concurrently, Starlink
+cleared regulatory hurdles for direct-to-cell competing with
+OneWeb in the same orbits, compressing OneWeb commercial value
+and triggering a goodwill write-down.
+Second-most-likely cause: SES merged with another operator and
+became a more aggressive competitor on price; LEO connectivity
+revenue growth decelerated; the partial re-rate from €1.35
+reversed back below €1.50.
+Where this would show up first: IRIS² programme milestone slips
+in EU Commission updates; Starlink direct-to-cell regulatory
+approvals; quarterly OneWeb revenue disclosure in interim reports.
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="4" t="inlineStr">
+        <is>
+          <t>Tier rationale</t>
+        </is>
+      </c>
+      <c r="B64" s="19" t="n"/>
+      <c r="C64" s="19" t="n"/>
+      <c r="D64" s="19" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="20" t="inlineStr"/>
+      <c r="B65" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bucket A, Archetype A1 (sovereign-strategic dual-tier raise) + F
+(post-recap orphan). Triangulation 3/3 with verified anchor
+presence. C7 partially visible (Q3 +3.1% YoY revenue, LEO-driven).
+IMPORTANT CORRECTION: The alignment gap is 1.41× not 2.9× as
+previously documented in shortlist.md. Current market €2.84 vs
+anchor €4.00 reserved. The €1.35 rights price is not the relevant
+denominator — the market price at announcement is. Lesson logged
+in methodology_review.md §1.4.
+Still investable but at narrower asymmetry than the prior screen
+implied. Remains Tier 1 on triangulation + C7 + dated catalyst
+basis but the "obvious mispricing" framing is weaker after the
+partial re-rate to €2.84 from late-Dec 2025 low ~€2.00.
+</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="49">
+    <mergeCell ref="B11:D11"/>
+    <mergeCell ref="B42:D42"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="B57:D57"/>
+    <mergeCell ref="B44:D44"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="B10:D10"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="A40:D40"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="B9:D9"/>
+    <mergeCell ref="A64:D64"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="B65:D65"/>
+    <mergeCell ref="B15:D15"/>
+    <mergeCell ref="B55:D55"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="B51:D51"/>
+    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="A61:D61"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="A54:D54"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B62:D62"/>
+    <mergeCell ref="B7:D7"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="A46:D46"/>
+    <mergeCell ref="B47:D47"/>
+    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="A18:D18"/>
+    <mergeCell ref="B59:D59"/>
+    <mergeCell ref="B31:D31"/>
+    <mergeCell ref="A50:D50"/>
+    <mergeCell ref="B22:D22"/>
+    <mergeCell ref="B27:D27"/>
+    <mergeCell ref="B56:D56"/>
+    <mergeCell ref="B58:D58"/>
+    <mergeCell ref="B52:D52"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="B43:D43"/>
+    <mergeCell ref="B12:D12"/>
+    <mergeCell ref="B48:D48"/>
+    <mergeCell ref="A14:D14"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:A25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>

--- a/output/cyclepapa_risk_reward_workbook.xlsx
+++ b/output/cyclepapa_risk_reward_workbook.xlsx
@@ -608,7 +608,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Generated 2026-07-02</t>
+          <t>Generated 2026-07-10</t>
         </is>
       </c>
     </row>
@@ -6938,7 +6938,7 @@
     <col width="60" customWidth="1" min="1" max="1"/>
     <col width="8" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="37" customWidth="1" min="4" max="4"/>
+    <col width="52" customWidth="1" min="4" max="4"/>
     <col width="22" customWidth="1" min="5" max="5"/>
     <col width="8" customWidth="1" min="6" max="6"/>
     <col width="8" customWidth="1" min="7" max="7"/>
@@ -6960,7 +6960,7 @@
     <row r="2" ht="38" customHeight="1">
       <c r="A2" s="7" t="inlineStr">
         <is>
-          <t>Universe coverage: 110 investable names (20 REAL waterfalls · 90 PROXY).  REAL uses the hand-built YAML's bottom-up bear/base/bull. PROXY uses a transparent formula on the universe-screener score + archetype tilt.</t>
+          <t>Universe coverage: 119 investable names (20 REAL waterfalls · 99 PROXY).  REAL uses the hand-built YAML's bottom-up bear/base/bull. PROXY uses a transparent formula on the universe-screener score + archetype tilt.</t>
         </is>
       </c>
     </row>
@@ -7108,22 +7108,22 @@
       </c>
       <c r="C6" s="14" t="inlineStr">
         <is>
-          <t>NYSE:TGS</t>
+          <t>CIK:0000882291</t>
         </is>
       </c>
       <c r="D6" s="14" t="inlineStr">
         <is>
-          <t>TGS (Transportadora de Gas del Sur)</t>
+          <t>AETHLON MEDICAL INC  (AEMD)  (CIK 0000882291)</t>
         </is>
       </c>
       <c r="E6" s="14" t="inlineStr">
         <is>
-          <t>Latin America</t>
+          <t>United States/Canada</t>
         </is>
       </c>
       <c r="F6" s="14" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="G6" s="14" t="inlineStr">
@@ -7133,32 +7133,32 @@
       </c>
       <c r="H6" s="14" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2+F2</t>
         </is>
       </c>
       <c r="I6" s="14" t="inlineStr">
         <is>
-          <t>24%</t>
+          <t>23%</t>
         </is>
       </c>
       <c r="J6" s="14" t="inlineStr">
         <is>
-          <t>2.44×</t>
+          <t>2.48×</t>
         </is>
       </c>
       <c r="K6" s="14" t="inlineStr">
         <is>
-          <t>3.12×</t>
+          <t>3.19×</t>
         </is>
       </c>
       <c r="L6" s="14" t="inlineStr">
         <is>
-          <t>2.10×</t>
+          <t>2.15×</t>
         </is>
       </c>
       <c r="M6" s="14" t="inlineStr">
         <is>
-          <t>4.5×</t>
+          <t>4.9×</t>
         </is>
       </c>
     </row>
@@ -7173,12 +7173,12 @@
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>NYSE:EDN</t>
+          <t>NYSE:TGS</t>
         </is>
       </c>
       <c r="D7" s="11" t="inlineStr">
         <is>
-          <t>Edenor</t>
+          <t>TGS (Transportadora de Gas del Sur)</t>
         </is>
       </c>
       <c r="E7" s="11" t="inlineStr">
@@ -7188,7 +7188,7 @@
       </c>
       <c r="F7" s="11" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="G7" s="11" t="inlineStr">
@@ -7203,27 +7203,27 @@
       </c>
       <c r="I7" s="11" t="inlineStr">
         <is>
-          <t>26%</t>
+          <t>24%</t>
         </is>
       </c>
       <c r="J7" s="11" t="inlineStr">
         <is>
-          <t>2.38×</t>
+          <t>2.44×</t>
         </is>
       </c>
       <c r="K7" s="11" t="inlineStr">
         <is>
-          <t>3.02×</t>
+          <t>3.12×</t>
         </is>
       </c>
       <c r="L7" s="11" t="inlineStr">
         <is>
-          <t>2.05×</t>
+          <t>2.10×</t>
         </is>
       </c>
       <c r="M7" s="11" t="inlineStr">
         <is>
-          <t>4.0×</t>
+          <t>4.5×</t>
         </is>
       </c>
     </row>
@@ -7238,22 +7238,22 @@
       </c>
       <c r="C8" s="14" t="inlineStr">
         <is>
-          <t>BIT:MB</t>
+          <t>CIK:0001130713</t>
         </is>
       </c>
       <c r="D8" s="14" t="inlineStr">
         <is>
-          <t>Mediobanca</t>
+          <t>BED BATH &amp; BEYOND, INC.  (BBBY, BBBY-WT)  (CIK 000</t>
         </is>
       </c>
       <c r="E8" s="14" t="inlineStr">
         <is>
-          <t>Continental Europe</t>
+          <t>United States/Canada</t>
         </is>
       </c>
       <c r="F8" s="14" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="G8" s="14" t="inlineStr">
@@ -7263,32 +7263,32 @@
       </c>
       <c r="H8" s="14" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2</t>
         </is>
       </c>
       <c r="I8" s="14" t="inlineStr">
         <is>
-          <t>27%</t>
+          <t>26%</t>
         </is>
       </c>
       <c r="J8" s="14" t="inlineStr">
         <is>
-          <t>2.33×</t>
+          <t>2.39×</t>
         </is>
       </c>
       <c r="K8" s="14" t="inlineStr">
         <is>
-          <t>2.94×</t>
+          <t>3.03×</t>
         </is>
       </c>
       <c r="L8" s="14" t="inlineStr">
         <is>
-          <t>2.00×</t>
+          <t>2.05×</t>
         </is>
       </c>
       <c r="M8" s="14" t="inlineStr">
         <is>
-          <t>3.7×</t>
+          <t>4.1×</t>
         </is>
       </c>
     </row>
@@ -7303,22 +7303,22 @@
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>ACF</t>
+          <t>CIK:0001438943</t>
         </is>
       </c>
       <c r="D9" s="11" t="inlineStr">
         <is>
-          <t>ACROW LIMITED</t>
+          <t>RANGE IMPACT, INC.  (RNGE)  (CIK 0001438943)</t>
         </is>
       </c>
       <c r="E9" s="11" t="inlineStr">
         <is>
-          <t>SE Asia / Pacific</t>
+          <t>United States/Canada</t>
         </is>
       </c>
       <c r="F9" s="11" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="G9" s="11" t="inlineStr">
@@ -7328,32 +7328,32 @@
       </c>
       <c r="H9" s="11" t="inlineStr">
         <is>
-          <t>A2+A1</t>
+          <t>A2</t>
         </is>
       </c>
       <c r="I9" s="11" t="inlineStr">
         <is>
-          <t>27%</t>
+          <t>26%</t>
         </is>
       </c>
       <c r="J9" s="11" t="inlineStr">
         <is>
-          <t>2.33×</t>
+          <t>2.39×</t>
         </is>
       </c>
       <c r="K9" s="11" t="inlineStr">
         <is>
-          <t>2.94×</t>
+          <t>3.03×</t>
         </is>
       </c>
       <c r="L9" s="11" t="inlineStr">
         <is>
-          <t>2.00×</t>
+          <t>2.05×</t>
         </is>
       </c>
       <c r="M9" s="11" t="inlineStr">
         <is>
-          <t>3.7×</t>
+          <t>4.1×</t>
         </is>
       </c>
     </row>
@@ -7368,22 +7368,22 @@
       </c>
       <c r="C10" s="14" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>CIK:0001740332</t>
         </is>
       </c>
       <c r="D10" s="14" t="inlineStr">
         <is>
-          <t>MEMPHASYS LIMITED.</t>
+          <t>RESIDEO TECHNOLOGIES, INC.  (REZI)  (CIK 000174033</t>
         </is>
       </c>
       <c r="E10" s="14" t="inlineStr">
         <is>
-          <t>SE Asia / Pacific</t>
+          <t>United States/Canada</t>
         </is>
       </c>
       <c r="F10" s="14" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="G10" s="14" t="inlineStr">
@@ -7393,32 +7393,32 @@
       </c>
       <c r="H10" s="14" t="inlineStr">
         <is>
-          <t>A2+B</t>
+          <t>A2</t>
         </is>
       </c>
       <c r="I10" s="14" t="inlineStr">
         <is>
-          <t>27%</t>
+          <t>26%</t>
         </is>
       </c>
       <c r="J10" s="14" t="inlineStr">
         <is>
-          <t>2.33×</t>
+          <t>2.39×</t>
         </is>
       </c>
       <c r="K10" s="14" t="inlineStr">
         <is>
-          <t>2.94×</t>
+          <t>3.03×</t>
         </is>
       </c>
       <c r="L10" s="14" t="inlineStr">
         <is>
-          <t>2.00×</t>
+          <t>2.05×</t>
         </is>
       </c>
       <c r="M10" s="14" t="inlineStr">
         <is>
-          <t>3.7×</t>
+          <t>4.1×</t>
         </is>
       </c>
     </row>
@@ -7433,12 +7433,12 @@
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>CIK:0001348911</t>
+          <t>CIK:0001937993</t>
         </is>
       </c>
       <c r="D11" s="11" t="inlineStr">
         <is>
-          <t>KalVista Pharmaceuticals, Inc.</t>
+          <t>Cadrenal Therapeutics, Inc.  (CVKD)  (CIK 00019379</t>
         </is>
       </c>
       <c r="E11" s="11" t="inlineStr">
@@ -7448,7 +7448,7 @@
       </c>
       <c r="F11" s="11" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="G11" s="11" t="inlineStr">
@@ -7458,32 +7458,32 @@
       </c>
       <c r="H11" s="11" t="inlineStr">
         <is>
-          <t>A2+K3</t>
+          <t>A2</t>
         </is>
       </c>
       <c r="I11" s="11" t="inlineStr">
         <is>
-          <t>27%</t>
+          <t>26%</t>
         </is>
       </c>
       <c r="J11" s="11" t="inlineStr">
         <is>
-          <t>2.33×</t>
+          <t>2.39×</t>
         </is>
       </c>
       <c r="K11" s="11" t="inlineStr">
         <is>
-          <t>2.94×</t>
+          <t>3.03×</t>
         </is>
       </c>
       <c r="L11" s="11" t="inlineStr">
         <is>
-          <t>2.00×</t>
+          <t>2.05×</t>
         </is>
       </c>
       <c r="M11" s="11" t="inlineStr">
         <is>
-          <t>3.7×</t>
+          <t>4.1×</t>
         </is>
       </c>
     </row>
@@ -7498,12 +7498,12 @@
       </c>
       <c r="C12" s="14" t="inlineStr">
         <is>
-          <t>CIK:0001909770</t>
+          <t>CIK:0001936224</t>
         </is>
       </c>
       <c r="D12" s="14" t="inlineStr">
         <is>
-          <t>KHEOBA CORP.</t>
+          <t>SURF AIR MOBILITY INC.  (SRFM)  (CIK 0001936224)</t>
         </is>
       </c>
       <c r="E12" s="14" t="inlineStr">
@@ -7513,7 +7513,7 @@
       </c>
       <c r="F12" s="14" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="G12" s="14" t="inlineStr">
@@ -7523,32 +7523,32 @@
       </c>
       <c r="H12" s="14" t="inlineStr">
         <is>
-          <t>A2+K3</t>
+          <t>A2</t>
         </is>
       </c>
       <c r="I12" s="14" t="inlineStr">
         <is>
-          <t>27%</t>
+          <t>26%</t>
         </is>
       </c>
       <c r="J12" s="14" t="inlineStr">
         <is>
-          <t>2.33×</t>
+          <t>2.39×</t>
         </is>
       </c>
       <c r="K12" s="14" t="inlineStr">
         <is>
-          <t>2.94×</t>
+          <t>3.03×</t>
         </is>
       </c>
       <c r="L12" s="14" t="inlineStr">
         <is>
-          <t>2.00×</t>
+          <t>2.05×</t>
         </is>
       </c>
       <c r="M12" s="14" t="inlineStr">
         <is>
-          <t>3.7×</t>
+          <t>4.1×</t>
         </is>
       </c>
     </row>
@@ -7563,12 +7563,12 @@
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>CIK:0001489096</t>
+          <t>CIK:0001720424</t>
         </is>
       </c>
       <c r="D13" s="11" t="inlineStr">
         <is>
-          <t>Thermon Group Holdings, Inc.</t>
+          <t>HIVE Digital Technologies Ltd.  (HIVE)  (CIK 00017</t>
         </is>
       </c>
       <c r="E13" s="11" t="inlineStr">
@@ -7578,7 +7578,7 @@
       </c>
       <c r="F13" s="11" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="G13" s="11" t="inlineStr">
@@ -7588,32 +7588,32 @@
       </c>
       <c r="H13" s="11" t="inlineStr">
         <is>
-          <t>A2+K3</t>
+          <t>A2</t>
         </is>
       </c>
       <c r="I13" s="11" t="inlineStr">
         <is>
-          <t>27%</t>
+          <t>26%</t>
         </is>
       </c>
       <c r="J13" s="11" t="inlineStr">
         <is>
-          <t>2.33×</t>
+          <t>2.39×</t>
         </is>
       </c>
       <c r="K13" s="11" t="inlineStr">
         <is>
-          <t>2.94×</t>
+          <t>3.03×</t>
         </is>
       </c>
       <c r="L13" s="11" t="inlineStr">
         <is>
-          <t>2.00×</t>
+          <t>2.05×</t>
         </is>
       </c>
       <c r="M13" s="11" t="inlineStr">
         <is>
-          <t>3.7×</t>
+          <t>4.1×</t>
         </is>
       </c>
     </row>
@@ -7628,22 +7628,22 @@
       </c>
       <c r="C14" s="14" t="inlineStr">
         <is>
-          <t>NYSE:GGAL</t>
+          <t>CIK:0000037785</t>
         </is>
       </c>
       <c r="D14" s="14" t="inlineStr">
         <is>
-          <t>Banco Galicia</t>
+          <t>FMC CORP  (FMC)  (CIK 0000037785)</t>
         </is>
       </c>
       <c r="E14" s="14" t="inlineStr">
         <is>
-          <t>Latin America</t>
+          <t>United States/Canada</t>
         </is>
       </c>
       <c r="F14" s="14" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="G14" s="14" t="inlineStr">
@@ -7653,32 +7653,32 @@
       </c>
       <c r="H14" s="14" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2</t>
         </is>
       </c>
       <c r="I14" s="14" t="inlineStr">
         <is>
-          <t>27%</t>
+          <t>26%</t>
         </is>
       </c>
       <c r="J14" s="14" t="inlineStr">
         <is>
-          <t>2.33×</t>
+          <t>2.39×</t>
         </is>
       </c>
       <c r="K14" s="14" t="inlineStr">
         <is>
-          <t>2.92×</t>
+          <t>3.03×</t>
         </is>
       </c>
       <c r="L14" s="14" t="inlineStr">
         <is>
-          <t>2.00×</t>
+          <t>2.05×</t>
         </is>
       </c>
       <c r="M14" s="14" t="inlineStr">
         <is>
-          <t>3.6×</t>
+          <t>4.1×</t>
         </is>
       </c>
     </row>
@@ -7686,19 +7686,19 @@
       <c r="A15" s="9" t="n">
         <v>11</v>
       </c>
-      <c r="B15" s="10" t="inlineStr">
-        <is>
-          <t>REAL</t>
+      <c r="B15" s="15" t="inlineStr">
+        <is>
+          <t>PROXY</t>
         </is>
       </c>
       <c r="C15" s="11" t="inlineStr">
         <is>
-          <t>NYSE:LAC</t>
+          <t>CIK:0002058873</t>
         </is>
       </c>
       <c r="D15" s="11" t="inlineStr">
         <is>
-          <t>Lithium Americas</t>
+          <t>Qnity Electronics, Inc.  (Q)  (CIK 0002058873)</t>
         </is>
       </c>
       <c r="E15" s="11" t="inlineStr">
@@ -7708,7 +7708,7 @@
       </c>
       <c r="F15" s="11" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="G15" s="11" t="inlineStr">
@@ -7723,27 +7723,27 @@
       </c>
       <c r="I15" s="11" t="inlineStr">
         <is>
-          <t>60%</t>
+          <t>26%</t>
         </is>
       </c>
       <c r="J15" s="11" t="inlineStr">
         <is>
-          <t>3.00×</t>
+          <t>2.39×</t>
         </is>
       </c>
       <c r="K15" s="11" t="inlineStr">
         <is>
-          <t>6.00×</t>
+          <t>3.03×</t>
         </is>
       </c>
       <c r="L15" s="11" t="inlineStr">
         <is>
-          <t>3.10×</t>
+          <t>2.05×</t>
         </is>
       </c>
       <c r="M15" s="11" t="inlineStr">
         <is>
-          <t>3.5×</t>
+          <t>4.1×</t>
         </is>
       </c>
     </row>
@@ -7751,29 +7751,29 @@
       <c r="A16" s="12" t="n">
         <v>12</v>
       </c>
-      <c r="B16" s="16" t="inlineStr">
-        <is>
-          <t>REAL</t>
+      <c r="B16" s="13" t="inlineStr">
+        <is>
+          <t>PROXY</t>
         </is>
       </c>
       <c r="C16" s="14" t="inlineStr">
         <is>
-          <t>XETR:SZG</t>
+          <t>CIK:0001141284</t>
         </is>
       </c>
       <c r="D16" s="14" t="inlineStr">
         <is>
-          <t>Salzgitter</t>
+          <t>ACTELIS NETWORKS INC  (ASNS)  (CIK 0001141284)</t>
         </is>
       </c>
       <c r="E16" s="14" t="inlineStr">
         <is>
-          <t>Continental Europe</t>
+          <t>United States/Canada</t>
         </is>
       </c>
       <c r="F16" s="14" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="G16" s="14" t="inlineStr">
@@ -7788,27 +7788,27 @@
       </c>
       <c r="I16" s="14" t="inlineStr">
         <is>
-          <t>45%</t>
+          <t>26%</t>
         </is>
       </c>
       <c r="J16" s="14" t="inlineStr">
         <is>
-          <t>2.50×</t>
+          <t>2.39×</t>
         </is>
       </c>
       <c r="K16" s="14" t="inlineStr">
         <is>
-          <t>4.50×</t>
+          <t>3.03×</t>
         </is>
       </c>
       <c r="L16" s="14" t="inlineStr">
         <is>
-          <t>2.51×</t>
+          <t>2.05×</t>
         </is>
       </c>
       <c r="M16" s="14" t="inlineStr">
         <is>
-          <t>3.4×</t>
+          <t>4.1×</t>
         </is>
       </c>
     </row>
@@ -7823,22 +7823,22 @@
       </c>
       <c r="C17" s="11" t="inlineStr">
         <is>
-          <t>NYSE:PAM</t>
+          <t>CIK:0000829323</t>
         </is>
       </c>
       <c r="D17" s="11" t="inlineStr">
         <is>
-          <t>Pampa Energía</t>
+          <t>Inuvo, Inc.  (INUV)  (CIK 0000829323)</t>
         </is>
       </c>
       <c r="E17" s="11" t="inlineStr">
         <is>
-          <t>Latin America</t>
+          <t>United States/Canada</t>
         </is>
       </c>
       <c r="F17" s="11" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="G17" s="11" t="inlineStr">
@@ -7848,32 +7848,32 @@
       </c>
       <c r="H17" s="11" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2</t>
         </is>
       </c>
       <c r="I17" s="11" t="inlineStr">
         <is>
-          <t>28%</t>
+          <t>26%</t>
         </is>
       </c>
       <c r="J17" s="11" t="inlineStr">
         <is>
-          <t>2.29×</t>
+          <t>2.39×</t>
         </is>
       </c>
       <c r="K17" s="11" t="inlineStr">
         <is>
-          <t>2.87×</t>
+          <t>3.03×</t>
         </is>
       </c>
       <c r="L17" s="11" t="inlineStr">
         <is>
-          <t>1.96×</t>
+          <t>2.05×</t>
         </is>
       </c>
       <c r="M17" s="11" t="inlineStr">
         <is>
-          <t>3.4×</t>
+          <t>4.1×</t>
         </is>
       </c>
     </row>
@@ -7888,22 +7888,22 @@
       </c>
       <c r="C18" s="14" t="inlineStr">
         <is>
-          <t>3544</t>
+          <t>CIK:0001282648</t>
         </is>
       </c>
       <c r="D18" s="14" t="inlineStr">
         <is>
-          <t>サツドラＨＤ</t>
+          <t>['BATTALION OIL CORP  (BATL)  (CIK 0001282648)']</t>
         </is>
       </c>
       <c r="E18" s="14" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States/Canada</t>
         </is>
       </c>
       <c r="F18" s="14" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="G18" s="14" t="inlineStr">
@@ -7913,32 +7913,32 @@
       </c>
       <c r="H18" s="14" t="inlineStr">
         <is>
-          <t>A2+C</t>
+          <t>A2</t>
         </is>
       </c>
       <c r="I18" s="14" t="inlineStr">
         <is>
-          <t>29%</t>
+          <t>26%</t>
         </is>
       </c>
       <c r="J18" s="14" t="inlineStr">
         <is>
-          <t>2.26×</t>
+          <t>2.39×</t>
         </is>
       </c>
       <c r="K18" s="14" t="inlineStr">
         <is>
-          <t>2.80×</t>
+          <t>3.03×</t>
         </is>
       </c>
       <c r="L18" s="14" t="inlineStr">
         <is>
-          <t>1.93×</t>
+          <t>2.05×</t>
         </is>
       </c>
       <c r="M18" s="14" t="inlineStr">
         <is>
-          <t>3.2×</t>
+          <t>4.1×</t>
         </is>
       </c>
     </row>
@@ -7953,22 +7953,22 @@
       </c>
       <c r="C19" s="11" t="inlineStr">
         <is>
-          <t>6897</t>
+          <t>NYSE:EDN</t>
         </is>
       </c>
       <c r="D19" s="11" t="inlineStr">
         <is>
-          <t>ツインバード</t>
+          <t>Edenor</t>
         </is>
       </c>
       <c r="E19" s="11" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Latin America</t>
         </is>
       </c>
       <c r="F19" s="11" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="G19" s="11" t="inlineStr">
@@ -7978,32 +7978,32 @@
       </c>
       <c r="H19" s="11" t="inlineStr">
         <is>
-          <t>A2+C</t>
+          <t>A1</t>
         </is>
       </c>
       <c r="I19" s="11" t="inlineStr">
         <is>
-          <t>29%</t>
+          <t>26%</t>
         </is>
       </c>
       <c r="J19" s="11" t="inlineStr">
         <is>
-          <t>2.26×</t>
+          <t>2.38×</t>
         </is>
       </c>
       <c r="K19" s="11" t="inlineStr">
         <is>
-          <t>2.80×</t>
+          <t>3.02×</t>
         </is>
       </c>
       <c r="L19" s="11" t="inlineStr">
         <is>
-          <t>1.93×</t>
+          <t>2.05×</t>
         </is>
       </c>
       <c r="M19" s="11" t="inlineStr">
         <is>
-          <t>3.2×</t>
+          <t>4.0×</t>
         </is>
       </c>
     </row>
@@ -8018,22 +8018,22 @@
       </c>
       <c r="C20" s="14" t="inlineStr">
         <is>
-          <t>4951</t>
+          <t>CIK:0001838003</t>
         </is>
       </c>
       <c r="D20" s="14" t="inlineStr">
         <is>
-          <t>エステー</t>
+          <t>Encore Medical, Inc.  (EMI)  (CIK 0001838003)</t>
         </is>
       </c>
       <c r="E20" s="14" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States/Canada</t>
         </is>
       </c>
       <c r="F20" s="14" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="G20" s="14" t="inlineStr">
@@ -8043,32 +8043,32 @@
       </c>
       <c r="H20" s="14" t="inlineStr">
         <is>
-          <t>A2+C</t>
+          <t>A2+F2</t>
         </is>
       </c>
       <c r="I20" s="14" t="inlineStr">
         <is>
-          <t>29%</t>
+          <t>26%</t>
         </is>
       </c>
       <c r="J20" s="14" t="inlineStr">
         <is>
-          <t>2.26×</t>
+          <t>2.37×</t>
         </is>
       </c>
       <c r="K20" s="14" t="inlineStr">
         <is>
-          <t>2.80×</t>
+          <t>3.00×</t>
         </is>
       </c>
       <c r="L20" s="14" t="inlineStr">
         <is>
-          <t>1.93×</t>
+          <t>2.04×</t>
         </is>
       </c>
       <c r="M20" s="14" t="inlineStr">
         <is>
-          <t>3.2×</t>
+          <t>4.0×</t>
         </is>
       </c>
     </row>
@@ -8083,22 +8083,22 @@
       </c>
       <c r="C21" s="11" t="inlineStr">
         <is>
-          <t>3659</t>
+          <t>BIT:MB</t>
         </is>
       </c>
       <c r="D21" s="11" t="inlineStr">
         <is>
-          <t>ネクソン</t>
+          <t>Mediobanca</t>
         </is>
       </c>
       <c r="E21" s="11" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Continental Europe</t>
         </is>
       </c>
       <c r="F21" s="11" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="G21" s="11" t="inlineStr">
@@ -8108,32 +8108,32 @@
       </c>
       <c r="H21" s="11" t="inlineStr">
         <is>
-          <t>A2+C</t>
+          <t>A1</t>
         </is>
       </c>
       <c r="I21" s="11" t="inlineStr">
         <is>
-          <t>29%</t>
+          <t>27%</t>
         </is>
       </c>
       <c r="J21" s="11" t="inlineStr">
         <is>
-          <t>2.26×</t>
+          <t>2.33×</t>
         </is>
       </c>
       <c r="K21" s="11" t="inlineStr">
         <is>
-          <t>2.80×</t>
+          <t>2.94×</t>
         </is>
       </c>
       <c r="L21" s="11" t="inlineStr">
         <is>
-          <t>1.93×</t>
+          <t>2.00×</t>
         </is>
       </c>
       <c r="M21" s="11" t="inlineStr">
         <is>
-          <t>3.2×</t>
+          <t>3.7×</t>
         </is>
       </c>
     </row>
@@ -8148,12 +8148,12 @@
       </c>
       <c r="C22" s="14" t="inlineStr">
         <is>
-          <t>DTZ</t>
+          <t>ACF</t>
         </is>
       </c>
       <c r="D22" s="14" t="inlineStr">
         <is>
-          <t>DOTZ NANO LIMITED</t>
+          <t>ACROW LIMITED</t>
         </is>
       </c>
       <c r="E22" s="14" t="inlineStr">
@@ -8163,7 +8163,7 @@
       </c>
       <c r="F22" s="14" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="G22" s="14" t="inlineStr">
@@ -8173,32 +8173,32 @@
       </c>
       <c r="H22" s="14" t="inlineStr">
         <is>
-          <t>A2</t>
+          <t>A2+A1</t>
         </is>
       </c>
       <c r="I22" s="14" t="inlineStr">
         <is>
-          <t>29%</t>
+          <t>27%</t>
         </is>
       </c>
       <c r="J22" s="14" t="inlineStr">
         <is>
-          <t>2.27×</t>
+          <t>2.33×</t>
         </is>
       </c>
       <c r="K22" s="14" t="inlineStr">
         <is>
-          <t>2.82×</t>
+          <t>2.94×</t>
         </is>
       </c>
       <c r="L22" s="14" t="inlineStr">
         <is>
-          <t>1.94×</t>
+          <t>2.00×</t>
         </is>
       </c>
       <c r="M22" s="14" t="inlineStr">
         <is>
-          <t>3.2×</t>
+          <t>3.7×</t>
         </is>
       </c>
     </row>
@@ -8213,12 +8213,12 @@
       </c>
       <c r="C23" s="11" t="inlineStr">
         <is>
-          <t>BMR</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="D23" s="11" t="inlineStr">
         <is>
-          <t>BALLYMORE RESOURCES LIMITED</t>
+          <t>MEMPHASYS LIMITED.</t>
         </is>
       </c>
       <c r="E23" s="11" t="inlineStr">
@@ -8228,7 +8228,7 @@
       </c>
       <c r="F23" s="11" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="G23" s="11" t="inlineStr">
@@ -8238,32 +8238,32 @@
       </c>
       <c r="H23" s="11" t="inlineStr">
         <is>
-          <t>A2</t>
+          <t>A2+B</t>
         </is>
       </c>
       <c r="I23" s="11" t="inlineStr">
         <is>
-          <t>29%</t>
+          <t>27%</t>
         </is>
       </c>
       <c r="J23" s="11" t="inlineStr">
         <is>
-          <t>2.27×</t>
+          <t>2.33×</t>
         </is>
       </c>
       <c r="K23" s="11" t="inlineStr">
         <is>
-          <t>2.82×</t>
+          <t>2.94×</t>
         </is>
       </c>
       <c r="L23" s="11" t="inlineStr">
         <is>
-          <t>1.94×</t>
+          <t>2.00×</t>
         </is>
       </c>
       <c r="M23" s="11" t="inlineStr">
         <is>
-          <t>3.2×</t>
+          <t>3.7×</t>
         </is>
       </c>
     </row>
@@ -8278,22 +8278,22 @@
       </c>
       <c r="C24" s="14" t="inlineStr">
         <is>
-          <t>CQT</t>
+          <t>CIK:0001348911</t>
         </is>
       </c>
       <c r="D24" s="14" t="inlineStr">
         <is>
-          <t>CONNEQT HEALTH LIMITED</t>
+          <t>KalVista Pharmaceuticals, Inc.</t>
         </is>
       </c>
       <c r="E24" s="14" t="inlineStr">
         <is>
-          <t>SE Asia / Pacific</t>
+          <t>United States/Canada</t>
         </is>
       </c>
       <c r="F24" s="14" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="G24" s="14" t="inlineStr">
@@ -8303,32 +8303,32 @@
       </c>
       <c r="H24" s="14" t="inlineStr">
         <is>
-          <t>A2</t>
+          <t>A2+K3</t>
         </is>
       </c>
       <c r="I24" s="14" t="inlineStr">
         <is>
-          <t>29%</t>
+          <t>27%</t>
         </is>
       </c>
       <c r="J24" s="14" t="inlineStr">
         <is>
-          <t>2.27×</t>
+          <t>2.33×</t>
         </is>
       </c>
       <c r="K24" s="14" t="inlineStr">
         <is>
-          <t>2.82×</t>
+          <t>2.94×</t>
         </is>
       </c>
       <c r="L24" s="14" t="inlineStr">
         <is>
-          <t>1.94×</t>
+          <t>2.00×</t>
         </is>
       </c>
       <c r="M24" s="14" t="inlineStr">
         <is>
-          <t>3.2×</t>
+          <t>3.7×</t>
         </is>
       </c>
     </row>
@@ -8343,22 +8343,22 @@
       </c>
       <c r="C25" s="11" t="inlineStr">
         <is>
-          <t>JLL</t>
+          <t>CIK:0001909770</t>
         </is>
       </c>
       <c r="D25" s="11" t="inlineStr">
         <is>
-          <t>JINDALEE LITHIUM LIMITED</t>
+          <t>KHEOBA CORP.</t>
         </is>
       </c>
       <c r="E25" s="11" t="inlineStr">
         <is>
-          <t>SE Asia / Pacific</t>
+          <t>United States/Canada</t>
         </is>
       </c>
       <c r="F25" s="11" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="G25" s="11" t="inlineStr">
@@ -8368,32 +8368,32 @@
       </c>
       <c r="H25" s="11" t="inlineStr">
         <is>
-          <t>A2</t>
+          <t>A2+K3</t>
         </is>
       </c>
       <c r="I25" s="11" t="inlineStr">
         <is>
-          <t>29%</t>
+          <t>27%</t>
         </is>
       </c>
       <c r="J25" s="11" t="inlineStr">
         <is>
-          <t>2.27×</t>
+          <t>2.33×</t>
         </is>
       </c>
       <c r="K25" s="11" t="inlineStr">
         <is>
-          <t>2.82×</t>
+          <t>2.94×</t>
         </is>
       </c>
       <c r="L25" s="11" t="inlineStr">
         <is>
-          <t>1.94×</t>
+          <t>2.00×</t>
         </is>
       </c>
       <c r="M25" s="11" t="inlineStr">
         <is>
-          <t>3.2×</t>
+          <t>3.7×</t>
         </is>
       </c>
     </row>
@@ -8408,22 +8408,22 @@
       </c>
       <c r="C26" s="14" t="inlineStr">
         <is>
-          <t>KSN</t>
+          <t>NYSE:GGAL</t>
         </is>
       </c>
       <c r="D26" s="14" t="inlineStr">
         <is>
-          <t>KINGSTON RESOURCES LIMITED</t>
+          <t>Banco Galicia</t>
         </is>
       </c>
       <c r="E26" s="14" t="inlineStr">
         <is>
-          <t>SE Asia / Pacific</t>
+          <t>Latin America</t>
         </is>
       </c>
       <c r="F26" s="14" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="G26" s="14" t="inlineStr">
@@ -8433,32 +8433,32 @@
       </c>
       <c r="H26" s="14" t="inlineStr">
         <is>
-          <t>A2</t>
+          <t>A1</t>
         </is>
       </c>
       <c r="I26" s="14" t="inlineStr">
         <is>
-          <t>29%</t>
+          <t>27%</t>
         </is>
       </c>
       <c r="J26" s="14" t="inlineStr">
         <is>
-          <t>2.27×</t>
+          <t>2.33×</t>
         </is>
       </c>
       <c r="K26" s="14" t="inlineStr">
         <is>
-          <t>2.82×</t>
+          <t>2.92×</t>
         </is>
       </c>
       <c r="L26" s="14" t="inlineStr">
         <is>
-          <t>1.94×</t>
+          <t>2.00×</t>
         </is>
       </c>
       <c r="M26" s="14" t="inlineStr">
         <is>
-          <t>3.2×</t>
+          <t>3.6×</t>
         </is>
       </c>
     </row>
@@ -8466,29 +8466,29 @@
       <c r="A27" s="9" t="n">
         <v>23</v>
       </c>
-      <c r="B27" s="15" t="inlineStr">
-        <is>
-          <t>PROXY</t>
+      <c r="B27" s="10" t="inlineStr">
+        <is>
+          <t>REAL</t>
         </is>
       </c>
       <c r="C27" s="11" t="inlineStr">
         <is>
-          <t>PNN</t>
+          <t>NYSE:LAC</t>
         </is>
       </c>
       <c r="D27" s="11" t="inlineStr">
         <is>
-          <t>POWER MINERALS LIMITED</t>
+          <t>Lithium Americas</t>
         </is>
       </c>
       <c r="E27" s="11" t="inlineStr">
         <is>
-          <t>SE Asia / Pacific</t>
+          <t>United States/Canada</t>
         </is>
       </c>
       <c r="F27" s="11" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="G27" s="11" t="inlineStr">
@@ -8503,27 +8503,27 @@
       </c>
       <c r="I27" s="11" t="inlineStr">
         <is>
-          <t>29%</t>
+          <t>60%</t>
         </is>
       </c>
       <c r="J27" s="11" t="inlineStr">
         <is>
-          <t>2.27×</t>
+          <t>3.00×</t>
         </is>
       </c>
       <c r="K27" s="11" t="inlineStr">
         <is>
-          <t>2.82×</t>
+          <t>6.00×</t>
         </is>
       </c>
       <c r="L27" s="11" t="inlineStr">
         <is>
-          <t>1.94×</t>
+          <t>3.10×</t>
         </is>
       </c>
       <c r="M27" s="11" t="inlineStr">
         <is>
-          <t>3.2×</t>
+          <t>3.5×</t>
         </is>
       </c>
     </row>
@@ -8531,29 +8531,29 @@
       <c r="A28" s="12" t="n">
         <v>24</v>
       </c>
-      <c r="B28" s="13" t="inlineStr">
-        <is>
-          <t>PROXY</t>
+      <c r="B28" s="16" t="inlineStr">
+        <is>
+          <t>REAL</t>
         </is>
       </c>
       <c r="C28" s="14" t="inlineStr">
         <is>
-          <t>ERM</t>
+          <t>XETR:SZG</t>
         </is>
       </c>
       <c r="D28" s="14" t="inlineStr">
         <is>
-          <t>EMMERSON RESOURCES LIMITED</t>
+          <t>Salzgitter</t>
         </is>
       </c>
       <c r="E28" s="14" t="inlineStr">
         <is>
-          <t>SE Asia / Pacific</t>
+          <t>Continental Europe</t>
         </is>
       </c>
       <c r="F28" s="14" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="G28" s="14" t="inlineStr">
@@ -8563,32 +8563,32 @@
       </c>
       <c r="H28" s="14" t="inlineStr">
         <is>
-          <t>A2+E</t>
+          <t>A2</t>
         </is>
       </c>
       <c r="I28" s="14" t="inlineStr">
         <is>
-          <t>29%</t>
+          <t>45%</t>
         </is>
       </c>
       <c r="J28" s="14" t="inlineStr">
         <is>
-          <t>2.26×</t>
+          <t>2.50×</t>
         </is>
       </c>
       <c r="K28" s="14" t="inlineStr">
         <is>
-          <t>2.80×</t>
+          <t>4.50×</t>
         </is>
       </c>
       <c r="L28" s="14" t="inlineStr">
         <is>
-          <t>1.93×</t>
+          <t>2.51×</t>
         </is>
       </c>
       <c r="M28" s="14" t="inlineStr">
         <is>
-          <t>3.2×</t>
+          <t>3.4×</t>
         </is>
       </c>
     </row>
@@ -8603,22 +8603,22 @@
       </c>
       <c r="C29" s="11" t="inlineStr">
         <is>
-          <t>PEX</t>
+          <t>NYSE:PAM</t>
         </is>
       </c>
       <c r="D29" s="11" t="inlineStr">
         <is>
-          <t>PEEL MINING LIMITED</t>
+          <t>Pampa Energía</t>
         </is>
       </c>
       <c r="E29" s="11" t="inlineStr">
         <is>
-          <t>SE Asia / Pacific</t>
+          <t>Latin America</t>
         </is>
       </c>
       <c r="F29" s="11" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="G29" s="11" t="inlineStr">
@@ -8628,32 +8628,32 @@
       </c>
       <c r="H29" s="11" t="inlineStr">
         <is>
-          <t>A2+E</t>
+          <t>A1</t>
         </is>
       </c>
       <c r="I29" s="11" t="inlineStr">
         <is>
-          <t>29%</t>
+          <t>28%</t>
         </is>
       </c>
       <c r="J29" s="11" t="inlineStr">
         <is>
-          <t>2.26×</t>
+          <t>2.29×</t>
         </is>
       </c>
       <c r="K29" s="11" t="inlineStr">
         <is>
-          <t>2.80×</t>
+          <t>2.87×</t>
         </is>
       </c>
       <c r="L29" s="11" t="inlineStr">
         <is>
-          <t>1.93×</t>
+          <t>1.96×</t>
         </is>
       </c>
       <c r="M29" s="11" t="inlineStr">
         <is>
-          <t>3.2×</t>
+          <t>3.4×</t>
         </is>
       </c>
     </row>
@@ -8697,7 +8697,7 @@
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="37" customWidth="1" min="3" max="3"/>
+    <col width="52" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
     <col width="8" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
@@ -8768,32 +8768,32 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>NYSE:TGS</t>
+          <t>CIK:0000882291</t>
         </is>
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>TGS (Transportadora de Gas del Sur)</t>
+          <t>AETHLON MEDICAL INC  (AEMD)  (CIK 0000882291)</t>
         </is>
       </c>
       <c r="D5" s="11" t="inlineStr">
         <is>
-          <t>Latin America</t>
+          <t>United States/Canada</t>
         </is>
       </c>
       <c r="E5" s="11" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="F5" s="11" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2+F2</t>
         </is>
       </c>
       <c r="G5" s="11" t="inlineStr">
         <is>
-          <t>4.5×</t>
+          <t>4.9×</t>
         </is>
       </c>
       <c r="H5" s="11" t="inlineStr">
@@ -8808,12 +8808,12 @@
       </c>
       <c r="B6" s="14" t="inlineStr">
         <is>
-          <t>NYSE:EDN</t>
+          <t>NYSE:TGS</t>
         </is>
       </c>
       <c r="C6" s="14" t="inlineStr">
         <is>
-          <t>Edenor</t>
+          <t>TGS (Transportadora de Gas del Sur)</t>
         </is>
       </c>
       <c r="D6" s="14" t="inlineStr">
@@ -8823,7 +8823,7 @@
       </c>
       <c r="E6" s="14" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="F6" s="14" t="inlineStr">
@@ -8833,7 +8833,7 @@
       </c>
       <c r="G6" s="14" t="inlineStr">
         <is>
-          <t>4.0×</t>
+          <t>4.5×</t>
         </is>
       </c>
       <c r="H6" s="14" t="inlineStr">
@@ -8848,32 +8848,32 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>BIT:MB</t>
+          <t>CIK:0001130713</t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>Mediobanca</t>
+          <t>BED BATH &amp; BEYOND, INC.  (BBBY, BBBY-WT)  (CIK 000</t>
         </is>
       </c>
       <c r="D7" s="11" t="inlineStr">
         <is>
-          <t>Continental Europe</t>
+          <t>United States/Canada</t>
         </is>
       </c>
       <c r="E7" s="11" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="F7" s="11" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2</t>
         </is>
       </c>
       <c r="G7" s="11" t="inlineStr">
         <is>
-          <t>3.7×</t>
+          <t>4.1×</t>
         </is>
       </c>
       <c r="H7" s="11" t="inlineStr">
@@ -8888,32 +8888,32 @@
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>ACF</t>
+          <t>CIK:0001438943</t>
         </is>
       </c>
       <c r="C8" s="14" t="inlineStr">
         <is>
-          <t>ACROW LIMITED</t>
+          <t>RANGE IMPACT, INC.  (RNGE)  (CIK 0001438943)</t>
         </is>
       </c>
       <c r="D8" s="14" t="inlineStr">
         <is>
-          <t>SE Asia / Pacific</t>
+          <t>United States/Canada</t>
         </is>
       </c>
       <c r="E8" s="14" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="F8" s="14" t="inlineStr">
         <is>
-          <t>A2+A1</t>
+          <t>A2</t>
         </is>
       </c>
       <c r="G8" s="14" t="inlineStr">
         <is>
-          <t>3.7×</t>
+          <t>4.1×</t>
         </is>
       </c>
       <c r="H8" s="14" t="inlineStr">
@@ -8928,32 +8928,32 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>CIK:0001740332</t>
         </is>
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>MEMPHASYS LIMITED.</t>
+          <t>RESIDEO TECHNOLOGIES, INC.  (REZI)  (CIK 000174033</t>
         </is>
       </c>
       <c r="D9" s="11" t="inlineStr">
         <is>
-          <t>SE Asia / Pacific</t>
+          <t>United States/Canada</t>
         </is>
       </c>
       <c r="E9" s="11" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="F9" s="11" t="inlineStr">
         <is>
-          <t>A2+B</t>
+          <t>A2</t>
         </is>
       </c>
       <c r="G9" s="11" t="inlineStr">
         <is>
-          <t>3.7×</t>
+          <t>4.1×</t>
         </is>
       </c>
       <c r="H9" s="11" t="inlineStr">
@@ -8968,12 +8968,12 @@
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>CIK:0001348911</t>
+          <t>CIK:0001937993</t>
         </is>
       </c>
       <c r="C10" s="14" t="inlineStr">
         <is>
-          <t>KalVista Pharmaceuticals, Inc.</t>
+          <t>Cadrenal Therapeutics, Inc.  (CVKD)  (CIK 00019379</t>
         </is>
       </c>
       <c r="D10" s="14" t="inlineStr">
@@ -8983,17 +8983,17 @@
       </c>
       <c r="E10" s="14" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="F10" s="14" t="inlineStr">
         <is>
-          <t>A2+K3</t>
+          <t>A2</t>
         </is>
       </c>
       <c r="G10" s="14" t="inlineStr">
         <is>
-          <t>3.7×</t>
+          <t>4.1×</t>
         </is>
       </c>
       <c r="H10" s="14" t="inlineStr">
@@ -9008,12 +9008,12 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>CIK:0001909770</t>
+          <t>CIK:0001936224</t>
         </is>
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>KHEOBA CORP.</t>
+          <t>SURF AIR MOBILITY INC.  (SRFM)  (CIK 0001936224)</t>
         </is>
       </c>
       <c r="D11" s="11" t="inlineStr">
@@ -9023,17 +9023,17 @@
       </c>
       <c r="E11" s="11" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="F11" s="11" t="inlineStr">
         <is>
-          <t>A2+K3</t>
+          <t>A2</t>
         </is>
       </c>
       <c r="G11" s="11" t="inlineStr">
         <is>
-          <t>3.7×</t>
+          <t>4.1×</t>
         </is>
       </c>
       <c r="H11" s="11" t="inlineStr">
@@ -9048,12 +9048,12 @@
       </c>
       <c r="B12" s="14" t="inlineStr">
         <is>
-          <t>CIK:0001489096</t>
+          <t>CIK:0001720424</t>
         </is>
       </c>
       <c r="C12" s="14" t="inlineStr">
         <is>
-          <t>Thermon Group Holdings, Inc.</t>
+          <t>HIVE Digital Technologies Ltd.  (HIVE)  (CIK 00017</t>
         </is>
       </c>
       <c r="D12" s="14" t="inlineStr">
@@ -9063,17 +9063,17 @@
       </c>
       <c r="E12" s="14" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="F12" s="14" t="inlineStr">
         <is>
-          <t>A2+K3</t>
+          <t>A2</t>
         </is>
       </c>
       <c r="G12" s="14" t="inlineStr">
         <is>
-          <t>3.7×</t>
+          <t>4.1×</t>
         </is>
       </c>
       <c r="H12" s="14" t="inlineStr">
@@ -9088,32 +9088,32 @@
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>NYSE:GGAL</t>
+          <t>CIK:0000037785</t>
         </is>
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>Banco Galicia</t>
+          <t>FMC CORP  (FMC)  (CIK 0000037785)</t>
         </is>
       </c>
       <c r="D13" s="11" t="inlineStr">
         <is>
-          <t>Latin America</t>
+          <t>United States/Canada</t>
         </is>
       </c>
       <c r="E13" s="11" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="F13" s="11" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2</t>
         </is>
       </c>
       <c r="G13" s="11" t="inlineStr">
         <is>
-          <t>3.6×</t>
+          <t>4.1×</t>
         </is>
       </c>
       <c r="H13" s="11" t="inlineStr">
@@ -9124,36 +9124,36 @@
     </row>
     <row r="14">
       <c r="A14" s="12" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B14" s="14" t="inlineStr">
         <is>
-          <t>NYSE:PAM</t>
+          <t>CIK:0002058873</t>
         </is>
       </c>
       <c r="C14" s="14" t="inlineStr">
         <is>
-          <t>Pampa Energía</t>
+          <t>Qnity Electronics, Inc.  (Q)  (CIK 0002058873)</t>
         </is>
       </c>
       <c r="D14" s="14" t="inlineStr">
         <is>
-          <t>Latin America</t>
+          <t>United States/Canada</t>
         </is>
       </c>
       <c r="E14" s="14" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="F14" s="14" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2</t>
         </is>
       </c>
       <c r="G14" s="14" t="inlineStr">
         <is>
-          <t>3.4×</t>
+          <t>4.1×</t>
         </is>
       </c>
       <c r="H14" s="14" t="inlineStr">
@@ -9164,36 +9164,36 @@
     </row>
     <row r="15">
       <c r="A15" s="9" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>3544</t>
+          <t>CIK:0001141284</t>
         </is>
       </c>
       <c r="C15" s="11" t="inlineStr">
         <is>
-          <t>サツドラＨＤ</t>
+          <t>ACTELIS NETWORKS INC  (ASNS)  (CIK 0001141284)</t>
         </is>
       </c>
       <c r="D15" s="11" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States/Canada</t>
         </is>
       </c>
       <c r="E15" s="11" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="F15" s="11" t="inlineStr">
         <is>
-          <t>A2+C</t>
+          <t>A2</t>
         </is>
       </c>
       <c r="G15" s="11" t="inlineStr">
         <is>
-          <t>3.2×</t>
+          <t>4.1×</t>
         </is>
       </c>
       <c r="H15" s="11" t="inlineStr">
@@ -9204,36 +9204,36 @@
     </row>
     <row r="16">
       <c r="A16" s="12" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B16" s="14" t="inlineStr">
         <is>
-          <t>6897</t>
+          <t>CIK:0000829323</t>
         </is>
       </c>
       <c r="C16" s="14" t="inlineStr">
         <is>
-          <t>ツインバード</t>
+          <t>Inuvo, Inc.  (INUV)  (CIK 0000829323)</t>
         </is>
       </c>
       <c r="D16" s="14" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States/Canada</t>
         </is>
       </c>
       <c r="E16" s="14" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="F16" s="14" t="inlineStr">
         <is>
-          <t>A2+C</t>
+          <t>A2</t>
         </is>
       </c>
       <c r="G16" s="14" t="inlineStr">
         <is>
-          <t>3.2×</t>
+          <t>4.1×</t>
         </is>
       </c>
       <c r="H16" s="14" t="inlineStr">
@@ -9244,36 +9244,36 @@
     </row>
     <row r="17">
       <c r="A17" s="9" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>4951</t>
+          <t>CIK:0001282648</t>
         </is>
       </c>
       <c r="C17" s="11" t="inlineStr">
         <is>
-          <t>エステー</t>
+          <t>['BATTALION OIL CORP  (BATL)  (CIK 0001282648)']</t>
         </is>
       </c>
       <c r="D17" s="11" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States/Canada</t>
         </is>
       </c>
       <c r="E17" s="11" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="F17" s="11" t="inlineStr">
         <is>
-          <t>A2+C</t>
+          <t>A2</t>
         </is>
       </c>
       <c r="G17" s="11" t="inlineStr">
         <is>
-          <t>3.2×</t>
+          <t>4.1×</t>
         </is>
       </c>
       <c r="H17" s="11" t="inlineStr">
@@ -9284,36 +9284,36 @@
     </row>
     <row r="18">
       <c r="A18" s="12" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B18" s="14" t="inlineStr">
         <is>
-          <t>3659</t>
+          <t>NYSE:EDN</t>
         </is>
       </c>
       <c r="C18" s="14" t="inlineStr">
         <is>
-          <t>ネクソン</t>
+          <t>Edenor</t>
         </is>
       </c>
       <c r="D18" s="14" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Latin America</t>
         </is>
       </c>
       <c r="E18" s="14" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="F18" s="14" t="inlineStr">
         <is>
-          <t>A2+C</t>
+          <t>A1</t>
         </is>
       </c>
       <c r="G18" s="14" t="inlineStr">
         <is>
-          <t>3.2×</t>
+          <t>4.0×</t>
         </is>
       </c>
       <c r="H18" s="14" t="inlineStr">
@@ -9324,36 +9324,36 @@
     </row>
     <row r="19">
       <c r="A19" s="9" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>DTZ</t>
+          <t>CIK:0001838003</t>
         </is>
       </c>
       <c r="C19" s="11" t="inlineStr">
         <is>
-          <t>DOTZ NANO LIMITED</t>
+          <t>Encore Medical, Inc.  (EMI)  (CIK 0001838003)</t>
         </is>
       </c>
       <c r="D19" s="11" t="inlineStr">
         <is>
-          <t>SE Asia / Pacific</t>
+          <t>United States/Canada</t>
         </is>
       </c>
       <c r="E19" s="11" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="F19" s="11" t="inlineStr">
         <is>
-          <t>A2</t>
+          <t>A2+F2</t>
         </is>
       </c>
       <c r="G19" s="11" t="inlineStr">
         <is>
-          <t>3.2×</t>
+          <t>4.0×</t>
         </is>
       </c>
       <c r="H19" s="11" t="inlineStr">
@@ -9364,36 +9364,36 @@
     </row>
     <row r="20">
       <c r="A20" s="12" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B20" s="14" t="inlineStr">
         <is>
-          <t>BMR</t>
+          <t>BIT:MB</t>
         </is>
       </c>
       <c r="C20" s="14" t="inlineStr">
         <is>
-          <t>BALLYMORE RESOURCES LIMITED</t>
+          <t>Mediobanca</t>
         </is>
       </c>
       <c r="D20" s="14" t="inlineStr">
         <is>
-          <t>SE Asia / Pacific</t>
+          <t>Continental Europe</t>
         </is>
       </c>
       <c r="E20" s="14" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="F20" s="14" t="inlineStr">
         <is>
-          <t>A2</t>
+          <t>A1</t>
         </is>
       </c>
       <c r="G20" s="14" t="inlineStr">
         <is>
-          <t>3.2×</t>
+          <t>3.7×</t>
         </is>
       </c>
       <c r="H20" s="14" t="inlineStr">
@@ -9404,16 +9404,16 @@
     </row>
     <row r="21">
       <c r="A21" s="9" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t>CQT</t>
+          <t>ACF</t>
         </is>
       </c>
       <c r="C21" s="11" t="inlineStr">
         <is>
-          <t>CONNEQT HEALTH LIMITED</t>
+          <t>ACROW LIMITED</t>
         </is>
       </c>
       <c r="D21" s="11" t="inlineStr">
@@ -9423,17 +9423,17 @@
       </c>
       <c r="E21" s="11" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="F21" s="11" t="inlineStr">
         <is>
-          <t>A2</t>
+          <t>A2+A1</t>
         </is>
       </c>
       <c r="G21" s="11" t="inlineStr">
         <is>
-          <t>3.2×</t>
+          <t>3.7×</t>
         </is>
       </c>
       <c r="H21" s="11" t="inlineStr">
@@ -9444,16 +9444,16 @@
     </row>
     <row r="22">
       <c r="A22" s="12" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B22" s="14" t="inlineStr">
         <is>
-          <t>JLL</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="C22" s="14" t="inlineStr">
         <is>
-          <t>JINDALEE LITHIUM LIMITED</t>
+          <t>MEMPHASYS LIMITED.</t>
         </is>
       </c>
       <c r="D22" s="14" t="inlineStr">
@@ -9463,17 +9463,17 @@
       </c>
       <c r="E22" s="14" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="F22" s="14" t="inlineStr">
         <is>
-          <t>A2</t>
+          <t>A2+B</t>
         </is>
       </c>
       <c r="G22" s="14" t="inlineStr">
         <is>
-          <t>3.2×</t>
+          <t>3.7×</t>
         </is>
       </c>
       <c r="H22" s="14" t="inlineStr">
@@ -9484,36 +9484,36 @@
     </row>
     <row r="23">
       <c r="A23" s="9" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B23" s="11" t="inlineStr">
         <is>
-          <t>KSN</t>
+          <t>CIK:0001348911</t>
         </is>
       </c>
       <c r="C23" s="11" t="inlineStr">
         <is>
-          <t>KINGSTON RESOURCES LIMITED</t>
+          <t>KalVista Pharmaceuticals, Inc.</t>
         </is>
       </c>
       <c r="D23" s="11" t="inlineStr">
         <is>
-          <t>SE Asia / Pacific</t>
+          <t>United States/Canada</t>
         </is>
       </c>
       <c r="E23" s="11" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="F23" s="11" t="inlineStr">
         <is>
-          <t>A2</t>
+          <t>A2+K3</t>
         </is>
       </c>
       <c r="G23" s="11" t="inlineStr">
         <is>
-          <t>3.2×</t>
+          <t>3.7×</t>
         </is>
       </c>
       <c r="H23" s="11" t="inlineStr">
@@ -9524,36 +9524,36 @@
     </row>
     <row r="24">
       <c r="A24" s="12" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B24" s="14" t="inlineStr">
         <is>
-          <t>PNN</t>
+          <t>CIK:0001909770</t>
         </is>
       </c>
       <c r="C24" s="14" t="inlineStr">
         <is>
-          <t>POWER MINERALS LIMITED</t>
+          <t>KHEOBA CORP.</t>
         </is>
       </c>
       <c r="D24" s="14" t="inlineStr">
         <is>
-          <t>SE Asia / Pacific</t>
+          <t>United States/Canada</t>
         </is>
       </c>
       <c r="E24" s="14" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="F24" s="14" t="inlineStr">
         <is>
-          <t>A2</t>
+          <t>A2+K3</t>
         </is>
       </c>
       <c r="G24" s="14" t="inlineStr">
         <is>
-          <t>3.2×</t>
+          <t>3.7×</t>
         </is>
       </c>
       <c r="H24" s="14" t="inlineStr">

--- a/output/cyclepapa_risk_reward_workbook.xlsx
+++ b/output/cyclepapa_risk_reward_workbook.xlsx
@@ -7108,7 +7108,7 @@
       </c>
       <c r="C6" s="14" t="inlineStr">
         <is>
-          <t>CIK:0000882291</t>
+          <t>AEMD</t>
         </is>
       </c>
       <c r="D6" s="14" t="inlineStr">
@@ -7238,7 +7238,7 @@
       </c>
       <c r="C8" s="14" t="inlineStr">
         <is>
-          <t>CIK:0001130713</t>
+          <t>BBBY-WT</t>
         </is>
       </c>
       <c r="D8" s="14" t="inlineStr">
@@ -7303,7 +7303,7 @@
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>CIK:0001438943</t>
+          <t>RNGE</t>
         </is>
       </c>
       <c r="D9" s="11" t="inlineStr">
@@ -7368,7 +7368,7 @@
       </c>
       <c r="C10" s="14" t="inlineStr">
         <is>
-          <t>CIK:0001740332</t>
+          <t>REZI</t>
         </is>
       </c>
       <c r="D10" s="14" t="inlineStr">
@@ -7433,7 +7433,7 @@
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>CIK:0001937993</t>
+          <t>CVKD</t>
         </is>
       </c>
       <c r="D11" s="11" t="inlineStr">
@@ -7498,7 +7498,7 @@
       </c>
       <c r="C12" s="14" t="inlineStr">
         <is>
-          <t>CIK:0001936224</t>
+          <t>SRFM</t>
         </is>
       </c>
       <c r="D12" s="14" t="inlineStr">
@@ -7563,7 +7563,7 @@
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>CIK:0001720424</t>
+          <t>HIVE</t>
         </is>
       </c>
       <c r="D13" s="11" t="inlineStr">
@@ -7628,7 +7628,7 @@
       </c>
       <c r="C14" s="14" t="inlineStr">
         <is>
-          <t>CIK:0000037785</t>
+          <t>FMC</t>
         </is>
       </c>
       <c r="D14" s="14" t="inlineStr">
@@ -7693,7 +7693,7 @@
       </c>
       <c r="C15" s="11" t="inlineStr">
         <is>
-          <t>CIK:0002058873</t>
+          <t>Q</t>
         </is>
       </c>
       <c r="D15" s="11" t="inlineStr">
@@ -7758,7 +7758,7 @@
       </c>
       <c r="C16" s="14" t="inlineStr">
         <is>
-          <t>CIK:0001141284</t>
+          <t>ASNS</t>
         </is>
       </c>
       <c r="D16" s="14" t="inlineStr">
@@ -7823,7 +7823,7 @@
       </c>
       <c r="C17" s="11" t="inlineStr">
         <is>
-          <t>CIK:0000829323</t>
+          <t>INUV</t>
         </is>
       </c>
       <c r="D17" s="11" t="inlineStr">
@@ -7888,7 +7888,7 @@
       </c>
       <c r="C18" s="14" t="inlineStr">
         <is>
-          <t>CIK:0001282648</t>
+          <t>BATL</t>
         </is>
       </c>
       <c r="D18" s="14" t="inlineStr">
@@ -8018,7 +8018,7 @@
       </c>
       <c r="C20" s="14" t="inlineStr">
         <is>
-          <t>CIK:0001838003</t>
+          <t>EMI</t>
         </is>
       </c>
       <c r="D20" s="14" t="inlineStr">
@@ -8768,7 +8768,7 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>CIK:0000882291</t>
+          <t>AEMD</t>
         </is>
       </c>
       <c r="C5" s="11" t="inlineStr">
@@ -8848,7 +8848,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>CIK:0001130713</t>
+          <t>BBBY-WT</t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr">
@@ -8888,7 +8888,7 @@
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>CIK:0001438943</t>
+          <t>RNGE</t>
         </is>
       </c>
       <c r="C8" s="14" t="inlineStr">
@@ -8928,7 +8928,7 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>CIK:0001740332</t>
+          <t>REZI</t>
         </is>
       </c>
       <c r="C9" s="11" t="inlineStr">
@@ -8968,7 +8968,7 @@
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>CIK:0001937993</t>
+          <t>CVKD</t>
         </is>
       </c>
       <c r="C10" s="14" t="inlineStr">
@@ -9008,7 +9008,7 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>CIK:0001936224</t>
+          <t>SRFM</t>
         </is>
       </c>
       <c r="C11" s="11" t="inlineStr">
@@ -9048,7 +9048,7 @@
       </c>
       <c r="B12" s="14" t="inlineStr">
         <is>
-          <t>CIK:0001720424</t>
+          <t>HIVE</t>
         </is>
       </c>
       <c r="C12" s="14" t="inlineStr">
@@ -9088,7 +9088,7 @@
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>CIK:0000037785</t>
+          <t>FMC</t>
         </is>
       </c>
       <c r="C13" s="11" t="inlineStr">
@@ -9128,7 +9128,7 @@
       </c>
       <c r="B14" s="14" t="inlineStr">
         <is>
-          <t>CIK:0002058873</t>
+          <t>Q</t>
         </is>
       </c>
       <c r="C14" s="14" t="inlineStr">
@@ -9168,7 +9168,7 @@
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>CIK:0001141284</t>
+          <t>ASNS</t>
         </is>
       </c>
       <c r="C15" s="11" t="inlineStr">
@@ -9208,7 +9208,7 @@
       </c>
       <c r="B16" s="14" t="inlineStr">
         <is>
-          <t>CIK:0000829323</t>
+          <t>INUV</t>
         </is>
       </c>
       <c r="C16" s="14" t="inlineStr">
@@ -9248,7 +9248,7 @@
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>CIK:0001282648</t>
+          <t>BATL</t>
         </is>
       </c>
       <c r="C17" s="11" t="inlineStr">
@@ -9328,7 +9328,7 @@
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>CIK:0001838003</t>
+          <t>EMI</t>
         </is>
       </c>
       <c r="C19" s="11" t="inlineStr">

--- a/output/cyclepapa_risk_reward_workbook.xlsx
+++ b/output/cyclepapa_risk_reward_workbook.xlsx
@@ -608,7 +608,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Generated 2026-07-10</t>
+          <t>Generated 2026-07-11</t>
         </is>
       </c>
     </row>
@@ -6937,8 +6937,8 @@
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
     <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="52" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="37" customWidth="1" min="4" max="4"/>
     <col width="22" customWidth="1" min="5" max="5"/>
     <col width="8" customWidth="1" min="6" max="6"/>
     <col width="8" customWidth="1" min="7" max="7"/>
@@ -6960,7 +6960,7 @@
     <row r="2" ht="38" customHeight="1">
       <c r="A2" s="7" t="inlineStr">
         <is>
-          <t>Universe coverage: 119 investable names (20 REAL waterfalls · 99 PROXY).  REAL uses the hand-built YAML's bottom-up bear/base/bull. PROXY uses a transparent formula on the universe-screener score + archetype tilt.</t>
+          <t>Universe coverage: 116 investable names (20 REAL waterfalls · 96 PROXY).  REAL uses the hand-built YAML's bottom-up bear/base/bull. PROXY uses a transparent formula on the universe-screener score + archetype tilt.</t>
         </is>
       </c>
     </row>
@@ -7108,12 +7108,12 @@
       </c>
       <c r="C6" s="14" t="inlineStr">
         <is>
-          <t>AEMD</t>
+          <t>TBRG</t>
         </is>
       </c>
       <c r="D6" s="14" t="inlineStr">
         <is>
-          <t>AETHLON MEDICAL INC  (AEMD)  (CIK 0000882291)</t>
+          <t>TruBridge, Inc.</t>
         </is>
       </c>
       <c r="E6" s="14" t="inlineStr">
@@ -7123,7 +7123,7 @@
       </c>
       <c r="F6" s="14" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="G6" s="14" t="inlineStr">
@@ -7133,32 +7133,32 @@
       </c>
       <c r="H6" s="14" t="inlineStr">
         <is>
-          <t>A2+F2</t>
+          <t>A2+K3</t>
         </is>
       </c>
       <c r="I6" s="14" t="inlineStr">
         <is>
-          <t>23%</t>
+          <t>20%</t>
         </is>
       </c>
       <c r="J6" s="14" t="inlineStr">
         <is>
-          <t>2.48×</t>
+          <t>2.63×</t>
         </is>
       </c>
       <c r="K6" s="14" t="inlineStr">
         <is>
-          <t>3.19×</t>
+          <t>3.45×</t>
         </is>
       </c>
       <c r="L6" s="14" t="inlineStr">
         <is>
-          <t>2.15×</t>
+          <t>2.29×</t>
         </is>
       </c>
       <c r="M6" s="14" t="inlineStr">
         <is>
-          <t>4.9×</t>
+          <t>6.6×</t>
         </is>
       </c>
     </row>
@@ -7173,22 +7173,22 @@
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>NYSE:TGS</t>
+          <t>APTOF</t>
         </is>
       </c>
       <c r="D7" s="11" t="inlineStr">
         <is>
-          <t>TGS (Transportadora de Gas del Sur)</t>
+          <t>Aptose Biosciences Inc.</t>
         </is>
       </c>
       <c r="E7" s="11" t="inlineStr">
         <is>
-          <t>Latin America</t>
+          <t>United States/Canada</t>
         </is>
       </c>
       <c r="F7" s="11" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="G7" s="11" t="inlineStr">
@@ -7198,32 +7198,32 @@
       </c>
       <c r="H7" s="11" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2+K3</t>
         </is>
       </c>
       <c r="I7" s="11" t="inlineStr">
         <is>
-          <t>24%</t>
+          <t>21%</t>
         </is>
       </c>
       <c r="J7" s="11" t="inlineStr">
         <is>
-          <t>2.44×</t>
+          <t>2.58×</t>
         </is>
       </c>
       <c r="K7" s="11" t="inlineStr">
         <is>
-          <t>3.12×</t>
+          <t>3.36×</t>
         </is>
       </c>
       <c r="L7" s="11" t="inlineStr">
         <is>
-          <t>2.10×</t>
+          <t>2.24×</t>
         </is>
       </c>
       <c r="M7" s="11" t="inlineStr">
         <is>
-          <t>4.5×</t>
+          <t>5.9×</t>
         </is>
       </c>
     </row>
@@ -7238,12 +7238,12 @@
       </c>
       <c r="C8" s="14" t="inlineStr">
         <is>
-          <t>BBBY-WT</t>
+          <t>AEMD</t>
         </is>
       </c>
       <c r="D8" s="14" t="inlineStr">
         <is>
-          <t>BED BATH &amp; BEYOND, INC.  (BBBY, BBBY-WT)  (CIK 000</t>
+          <t>AETHLON MEDICAL INC</t>
         </is>
       </c>
       <c r="E8" s="14" t="inlineStr">
@@ -7253,7 +7253,7 @@
       </c>
       <c r="F8" s="14" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="G8" s="14" t="inlineStr">
@@ -7263,32 +7263,32 @@
       </c>
       <c r="H8" s="14" t="inlineStr">
         <is>
-          <t>A2</t>
+          <t>A2+F2</t>
         </is>
       </c>
       <c r="I8" s="14" t="inlineStr">
         <is>
-          <t>26%</t>
+          <t>22%</t>
         </is>
       </c>
       <c r="J8" s="14" t="inlineStr">
         <is>
-          <t>2.39×</t>
+          <t>2.53×</t>
         </is>
       </c>
       <c r="K8" s="14" t="inlineStr">
         <is>
-          <t>3.03×</t>
+          <t>3.29×</t>
         </is>
       </c>
       <c r="L8" s="14" t="inlineStr">
         <is>
-          <t>2.05×</t>
+          <t>2.20×</t>
         </is>
       </c>
       <c r="M8" s="14" t="inlineStr">
         <is>
-          <t>4.1×</t>
+          <t>5.4×</t>
         </is>
       </c>
     </row>
@@ -7303,12 +7303,12 @@
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>RNGE</t>
+          <t>LEG</t>
         </is>
       </c>
       <c r="D9" s="11" t="inlineStr">
         <is>
-          <t>RANGE IMPACT, INC.  (RNGE)  (CIK 0001438943)</t>
+          <t>LEGGETT &amp; PLATT INC</t>
         </is>
       </c>
       <c r="E9" s="11" t="inlineStr">
@@ -7318,7 +7318,7 @@
       </c>
       <c r="F9" s="11" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="G9" s="11" t="inlineStr">
@@ -7333,27 +7333,27 @@
       </c>
       <c r="I9" s="11" t="inlineStr">
         <is>
-          <t>26%</t>
+          <t>22%</t>
         </is>
       </c>
       <c r="J9" s="11" t="inlineStr">
         <is>
-          <t>2.39×</t>
+          <t>2.52×</t>
         </is>
       </c>
       <c r="K9" s="11" t="inlineStr">
         <is>
-          <t>3.03×</t>
+          <t>3.27×</t>
         </is>
       </c>
       <c r="L9" s="11" t="inlineStr">
         <is>
-          <t>2.05×</t>
+          <t>2.19×</t>
         </is>
       </c>
       <c r="M9" s="11" t="inlineStr">
         <is>
-          <t>4.1×</t>
+          <t>5.3×</t>
         </is>
       </c>
     </row>
@@ -7368,12 +7368,12 @@
       </c>
       <c r="C10" s="14" t="inlineStr">
         <is>
-          <t>REZI</t>
+          <t>BATL</t>
         </is>
       </c>
       <c r="D10" s="14" t="inlineStr">
         <is>
-          <t>RESIDEO TECHNOLOGIES, INC.  (REZI)  (CIK 000174033</t>
+          <t>BATTALION OIL CORP</t>
         </is>
       </c>
       <c r="E10" s="14" t="inlineStr">
@@ -7383,7 +7383,7 @@
       </c>
       <c r="F10" s="14" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="G10" s="14" t="inlineStr">
@@ -7398,27 +7398,27 @@
       </c>
       <c r="I10" s="14" t="inlineStr">
         <is>
-          <t>26%</t>
+          <t>24%</t>
         </is>
       </c>
       <c r="J10" s="14" t="inlineStr">
         <is>
-          <t>2.39×</t>
+          <t>2.47×</t>
         </is>
       </c>
       <c r="K10" s="14" t="inlineStr">
         <is>
-          <t>3.03×</t>
+          <t>3.18×</t>
         </is>
       </c>
       <c r="L10" s="14" t="inlineStr">
         <is>
-          <t>2.05×</t>
+          <t>2.14×</t>
         </is>
       </c>
       <c r="M10" s="14" t="inlineStr">
         <is>
-          <t>4.1×</t>
+          <t>4.8×</t>
         </is>
       </c>
     </row>
@@ -7433,22 +7433,22 @@
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>CVKD</t>
+          <t>NYSE:TGS</t>
         </is>
       </c>
       <c r="D11" s="11" t="inlineStr">
         <is>
-          <t>Cadrenal Therapeutics, Inc.  (CVKD)  (CIK 00019379</t>
+          <t>TGS (Transportadora de Gas del Sur)</t>
         </is>
       </c>
       <c r="E11" s="11" t="inlineStr">
         <is>
-          <t>United States/Canada</t>
+          <t>Latin America</t>
         </is>
       </c>
       <c r="F11" s="11" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="G11" s="11" t="inlineStr">
@@ -7458,32 +7458,32 @@
       </c>
       <c r="H11" s="11" t="inlineStr">
         <is>
-          <t>A2</t>
+          <t>A1</t>
         </is>
       </c>
       <c r="I11" s="11" t="inlineStr">
         <is>
-          <t>26%</t>
+          <t>24%</t>
         </is>
       </c>
       <c r="J11" s="11" t="inlineStr">
         <is>
-          <t>2.39×</t>
+          <t>2.44×</t>
         </is>
       </c>
       <c r="K11" s="11" t="inlineStr">
         <is>
-          <t>3.03×</t>
+          <t>3.12×</t>
         </is>
       </c>
       <c r="L11" s="11" t="inlineStr">
         <is>
-          <t>2.05×</t>
+          <t>2.10×</t>
         </is>
       </c>
       <c r="M11" s="11" t="inlineStr">
         <is>
-          <t>4.1×</t>
+          <t>4.5×</t>
         </is>
       </c>
     </row>
@@ -7498,12 +7498,12 @@
       </c>
       <c r="C12" s="14" t="inlineStr">
         <is>
-          <t>SRFM</t>
+          <t>EMI</t>
         </is>
       </c>
       <c r="D12" s="14" t="inlineStr">
         <is>
-          <t>SURF AIR MOBILITY INC.  (SRFM)  (CIK 0001936224)</t>
+          <t>Encore Medical, Inc.</t>
         </is>
       </c>
       <c r="E12" s="14" t="inlineStr">
@@ -7513,7 +7513,7 @@
       </c>
       <c r="F12" s="14" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="G12" s="14" t="inlineStr">
@@ -7523,32 +7523,32 @@
       </c>
       <c r="H12" s="14" t="inlineStr">
         <is>
-          <t>A2</t>
+          <t>A2+F2</t>
         </is>
       </c>
       <c r="I12" s="14" t="inlineStr">
         <is>
-          <t>26%</t>
+          <t>25%</t>
         </is>
       </c>
       <c r="J12" s="14" t="inlineStr">
         <is>
-          <t>2.39×</t>
+          <t>2.42×</t>
         </is>
       </c>
       <c r="K12" s="14" t="inlineStr">
         <is>
-          <t>3.03×</t>
+          <t>3.09×</t>
         </is>
       </c>
       <c r="L12" s="14" t="inlineStr">
         <is>
-          <t>2.05×</t>
+          <t>2.09×</t>
         </is>
       </c>
       <c r="M12" s="14" t="inlineStr">
         <is>
-          <t>4.1×</t>
+          <t>4.4×</t>
         </is>
       </c>
     </row>
@@ -7563,12 +7563,12 @@
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>HIVE</t>
+          <t>EHGO</t>
         </is>
       </c>
       <c r="D13" s="11" t="inlineStr">
         <is>
-          <t>HIVE Digital Technologies Ltd.  (HIVE)  (CIK 00017</t>
+          <t>EShallGo Inc.</t>
         </is>
       </c>
       <c r="E13" s="11" t="inlineStr">
@@ -7578,7 +7578,7 @@
       </c>
       <c r="F13" s="11" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="G13" s="11" t="inlineStr">
@@ -7593,27 +7593,27 @@
       </c>
       <c r="I13" s="11" t="inlineStr">
         <is>
-          <t>26%</t>
+          <t>25%</t>
         </is>
       </c>
       <c r="J13" s="11" t="inlineStr">
         <is>
-          <t>2.39×</t>
+          <t>2.41×</t>
         </is>
       </c>
       <c r="K13" s="11" t="inlineStr">
         <is>
-          <t>3.03×</t>
+          <t>3.08×</t>
         </is>
       </c>
       <c r="L13" s="11" t="inlineStr">
         <is>
-          <t>2.05×</t>
+          <t>2.08×</t>
         </is>
       </c>
       <c r="M13" s="11" t="inlineStr">
         <is>
-          <t>4.1×</t>
+          <t>4.3×</t>
         </is>
       </c>
     </row>
@@ -7628,12 +7628,12 @@
       </c>
       <c r="C14" s="14" t="inlineStr">
         <is>
-          <t>FMC</t>
+          <t>RNGE</t>
         </is>
       </c>
       <c r="D14" s="14" t="inlineStr">
         <is>
-          <t>FMC CORP  (FMC)  (CIK 0000037785)</t>
+          <t>RANGE IMPACT, INC.</t>
         </is>
       </c>
       <c r="E14" s="14" t="inlineStr">
@@ -7643,7 +7643,7 @@
       </c>
       <c r="F14" s="14" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="G14" s="14" t="inlineStr">
@@ -7658,27 +7658,27 @@
       </c>
       <c r="I14" s="14" t="inlineStr">
         <is>
-          <t>26%</t>
+          <t>25%</t>
         </is>
       </c>
       <c r="J14" s="14" t="inlineStr">
         <is>
-          <t>2.39×</t>
+          <t>2.41×</t>
         </is>
       </c>
       <c r="K14" s="14" t="inlineStr">
         <is>
-          <t>3.03×</t>
+          <t>3.08×</t>
         </is>
       </c>
       <c r="L14" s="14" t="inlineStr">
         <is>
-          <t>2.05×</t>
+          <t>2.08×</t>
         </is>
       </c>
       <c r="M14" s="14" t="inlineStr">
         <is>
-          <t>4.1×</t>
+          <t>4.3×</t>
         </is>
       </c>
     </row>
@@ -7693,12 +7693,12 @@
       </c>
       <c r="C15" s="11" t="inlineStr">
         <is>
-          <t>Q</t>
+          <t>CVKD</t>
         </is>
       </c>
       <c r="D15" s="11" t="inlineStr">
         <is>
-          <t>Qnity Electronics, Inc.  (Q)  (CIK 0002058873)</t>
+          <t>Cadrenal Therapeutics, Inc.</t>
         </is>
       </c>
       <c r="E15" s="11" t="inlineStr">
@@ -7708,7 +7708,7 @@
       </c>
       <c r="F15" s="11" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="G15" s="11" t="inlineStr">
@@ -7723,27 +7723,27 @@
       </c>
       <c r="I15" s="11" t="inlineStr">
         <is>
-          <t>26%</t>
+          <t>25%</t>
         </is>
       </c>
       <c r="J15" s="11" t="inlineStr">
         <is>
-          <t>2.39×</t>
+          <t>2.41×</t>
         </is>
       </c>
       <c r="K15" s="11" t="inlineStr">
         <is>
-          <t>3.03×</t>
+          <t>3.08×</t>
         </is>
       </c>
       <c r="L15" s="11" t="inlineStr">
         <is>
-          <t>2.05×</t>
+          <t>2.08×</t>
         </is>
       </c>
       <c r="M15" s="11" t="inlineStr">
         <is>
-          <t>4.1×</t>
+          <t>4.3×</t>
         </is>
       </c>
     </row>
@@ -7758,12 +7758,12 @@
       </c>
       <c r="C16" s="14" t="inlineStr">
         <is>
-          <t>ASNS</t>
+          <t>SRFM</t>
         </is>
       </c>
       <c r="D16" s="14" t="inlineStr">
         <is>
-          <t>ACTELIS NETWORKS INC  (ASNS)  (CIK 0001141284)</t>
+          <t>SURF AIR MOBILITY INC.</t>
         </is>
       </c>
       <c r="E16" s="14" t="inlineStr">
@@ -7773,7 +7773,7 @@
       </c>
       <c r="F16" s="14" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="G16" s="14" t="inlineStr">
@@ -7788,27 +7788,27 @@
       </c>
       <c r="I16" s="14" t="inlineStr">
         <is>
-          <t>26%</t>
+          <t>25%</t>
         </is>
       </c>
       <c r="J16" s="14" t="inlineStr">
         <is>
-          <t>2.39×</t>
+          <t>2.41×</t>
         </is>
       </c>
       <c r="K16" s="14" t="inlineStr">
         <is>
-          <t>3.03×</t>
+          <t>3.08×</t>
         </is>
       </c>
       <c r="L16" s="14" t="inlineStr">
         <is>
-          <t>2.05×</t>
+          <t>2.08×</t>
         </is>
       </c>
       <c r="M16" s="14" t="inlineStr">
         <is>
-          <t>4.1×</t>
+          <t>4.3×</t>
         </is>
       </c>
     </row>
@@ -7823,12 +7823,12 @@
       </c>
       <c r="C17" s="11" t="inlineStr">
         <is>
-          <t>INUV</t>
+          <t>HIVE</t>
         </is>
       </c>
       <c r="D17" s="11" t="inlineStr">
         <is>
-          <t>Inuvo, Inc.  (INUV)  (CIK 0000829323)</t>
+          <t>HIVE Digital Technologies Ltd.</t>
         </is>
       </c>
       <c r="E17" s="11" t="inlineStr">
@@ -7838,7 +7838,7 @@
       </c>
       <c r="F17" s="11" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="G17" s="11" t="inlineStr">
@@ -7853,27 +7853,27 @@
       </c>
       <c r="I17" s="11" t="inlineStr">
         <is>
-          <t>26%</t>
+          <t>25%</t>
         </is>
       </c>
       <c r="J17" s="11" t="inlineStr">
         <is>
-          <t>2.39×</t>
+          <t>2.41×</t>
         </is>
       </c>
       <c r="K17" s="11" t="inlineStr">
         <is>
-          <t>3.03×</t>
+          <t>3.08×</t>
         </is>
       </c>
       <c r="L17" s="11" t="inlineStr">
         <is>
-          <t>2.05×</t>
+          <t>2.08×</t>
         </is>
       </c>
       <c r="M17" s="11" t="inlineStr">
         <is>
-          <t>4.1×</t>
+          <t>4.3×</t>
         </is>
       </c>
     </row>
@@ -7888,12 +7888,12 @@
       </c>
       <c r="C18" s="14" t="inlineStr">
         <is>
-          <t>BATL</t>
+          <t>ASNS</t>
         </is>
       </c>
       <c r="D18" s="14" t="inlineStr">
         <is>
-          <t>['BATTALION OIL CORP  (BATL)  (CIK 0001282648)']</t>
+          <t>ACTELIS NETWORKS INC</t>
         </is>
       </c>
       <c r="E18" s="14" t="inlineStr">
@@ -7903,7 +7903,7 @@
       </c>
       <c r="F18" s="14" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="G18" s="14" t="inlineStr">
@@ -7918,27 +7918,27 @@
       </c>
       <c r="I18" s="14" t="inlineStr">
         <is>
-          <t>26%</t>
+          <t>25%</t>
         </is>
       </c>
       <c r="J18" s="14" t="inlineStr">
         <is>
-          <t>2.39×</t>
+          <t>2.41×</t>
         </is>
       </c>
       <c r="K18" s="14" t="inlineStr">
         <is>
-          <t>3.03×</t>
+          <t>3.08×</t>
         </is>
       </c>
       <c r="L18" s="14" t="inlineStr">
         <is>
-          <t>2.05×</t>
+          <t>2.08×</t>
         </is>
       </c>
       <c r="M18" s="14" t="inlineStr">
         <is>
-          <t>4.1×</t>
+          <t>4.3×</t>
         </is>
       </c>
     </row>
@@ -7953,22 +7953,22 @@
       </c>
       <c r="C19" s="11" t="inlineStr">
         <is>
-          <t>NYSE:EDN</t>
+          <t>INUV</t>
         </is>
       </c>
       <c r="D19" s="11" t="inlineStr">
         <is>
-          <t>Edenor</t>
+          <t>Inuvo, Inc.</t>
         </is>
       </c>
       <c r="E19" s="11" t="inlineStr">
         <is>
-          <t>Latin America</t>
+          <t>United States/Canada</t>
         </is>
       </c>
       <c r="F19" s="11" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="G19" s="11" t="inlineStr">
@@ -7978,32 +7978,32 @@
       </c>
       <c r="H19" s="11" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2</t>
         </is>
       </c>
       <c r="I19" s="11" t="inlineStr">
         <is>
-          <t>26%</t>
+          <t>25%</t>
         </is>
       </c>
       <c r="J19" s="11" t="inlineStr">
         <is>
-          <t>2.38×</t>
+          <t>2.41×</t>
         </is>
       </c>
       <c r="K19" s="11" t="inlineStr">
         <is>
-          <t>3.02×</t>
+          <t>3.08×</t>
         </is>
       </c>
       <c r="L19" s="11" t="inlineStr">
         <is>
-          <t>2.05×</t>
+          <t>2.08×</t>
         </is>
       </c>
       <c r="M19" s="11" t="inlineStr">
         <is>
-          <t>4.0×</t>
+          <t>4.3×</t>
         </is>
       </c>
     </row>
@@ -8018,12 +8018,12 @@
       </c>
       <c r="C20" s="14" t="inlineStr">
         <is>
-          <t>EMI</t>
+          <t>FMC</t>
         </is>
       </c>
       <c r="D20" s="14" t="inlineStr">
         <is>
-          <t>Encore Medical, Inc.  (EMI)  (CIK 0001838003)</t>
+          <t>FMC CORP</t>
         </is>
       </c>
       <c r="E20" s="14" t="inlineStr">
@@ -8033,7 +8033,7 @@
       </c>
       <c r="F20" s="14" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="G20" s="14" t="inlineStr">
@@ -8043,32 +8043,32 @@
       </c>
       <c r="H20" s="14" t="inlineStr">
         <is>
-          <t>A2+F2</t>
+          <t>A2</t>
         </is>
       </c>
       <c r="I20" s="14" t="inlineStr">
         <is>
-          <t>26%</t>
+          <t>25%</t>
         </is>
       </c>
       <c r="J20" s="14" t="inlineStr">
         <is>
-          <t>2.37×</t>
+          <t>2.40×</t>
         </is>
       </c>
       <c r="K20" s="14" t="inlineStr">
         <is>
-          <t>3.00×</t>
+          <t>3.06×</t>
         </is>
       </c>
       <c r="L20" s="14" t="inlineStr">
         <is>
-          <t>2.04×</t>
+          <t>2.07×</t>
         </is>
       </c>
       <c r="M20" s="14" t="inlineStr">
         <is>
-          <t>4.0×</t>
+          <t>4.2×</t>
         </is>
       </c>
     </row>
@@ -8083,22 +8083,22 @@
       </c>
       <c r="C21" s="11" t="inlineStr">
         <is>
-          <t>BIT:MB</t>
+          <t>NYSE:EDN</t>
         </is>
       </c>
       <c r="D21" s="11" t="inlineStr">
         <is>
-          <t>Mediobanca</t>
+          <t>Edenor</t>
         </is>
       </c>
       <c r="E21" s="11" t="inlineStr">
         <is>
-          <t>Continental Europe</t>
+          <t>Latin America</t>
         </is>
       </c>
       <c r="F21" s="11" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="G21" s="11" t="inlineStr">
@@ -8113,27 +8113,27 @@
       </c>
       <c r="I21" s="11" t="inlineStr">
         <is>
-          <t>27%</t>
+          <t>26%</t>
         </is>
       </c>
       <c r="J21" s="11" t="inlineStr">
         <is>
-          <t>2.33×</t>
+          <t>2.38×</t>
         </is>
       </c>
       <c r="K21" s="11" t="inlineStr">
         <is>
-          <t>2.94×</t>
+          <t>3.02×</t>
         </is>
       </c>
       <c r="L21" s="11" t="inlineStr">
         <is>
-          <t>2.00×</t>
+          <t>2.05×</t>
         </is>
       </c>
       <c r="M21" s="11" t="inlineStr">
         <is>
-          <t>3.7×</t>
+          <t>4.0×</t>
         </is>
       </c>
     </row>
@@ -8148,17 +8148,17 @@
       </c>
       <c r="C22" s="14" t="inlineStr">
         <is>
-          <t>ACF</t>
+          <t>BIT:MB</t>
         </is>
       </c>
       <c r="D22" s="14" t="inlineStr">
         <is>
-          <t>ACROW LIMITED</t>
+          <t>Mediobanca</t>
         </is>
       </c>
       <c r="E22" s="14" t="inlineStr">
         <is>
-          <t>SE Asia / Pacific</t>
+          <t>Continental Europe</t>
         </is>
       </c>
       <c r="F22" s="14" t="inlineStr">
@@ -8173,7 +8173,7 @@
       </c>
       <c r="H22" s="14" t="inlineStr">
         <is>
-          <t>A2+A1</t>
+          <t>A1</t>
         </is>
       </c>
       <c r="I22" s="14" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="C23" s="11" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>ACF</t>
         </is>
       </c>
       <c r="D23" s="11" t="inlineStr">
         <is>
-          <t>MEMPHASYS LIMITED.</t>
+          <t>ACROW LIMITED</t>
         </is>
       </c>
       <c r="E23" s="11" t="inlineStr">
@@ -8238,7 +8238,7 @@
       </c>
       <c r="H23" s="11" t="inlineStr">
         <is>
-          <t>A2+B</t>
+          <t>A2+A1</t>
         </is>
       </c>
       <c r="I23" s="11" t="inlineStr">
@@ -8278,17 +8278,17 @@
       </c>
       <c r="C24" s="14" t="inlineStr">
         <is>
-          <t>CIK:0001348911</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="D24" s="14" t="inlineStr">
         <is>
-          <t>KalVista Pharmaceuticals, Inc.</t>
+          <t>MEMPHASYS LIMITED.</t>
         </is>
       </c>
       <c r="E24" s="14" t="inlineStr">
         <is>
-          <t>United States/Canada</t>
+          <t>SE Asia / Pacific</t>
         </is>
       </c>
       <c r="F24" s="14" t="inlineStr">
@@ -8303,7 +8303,7 @@
       </c>
       <c r="H24" s="14" t="inlineStr">
         <is>
-          <t>A2+K3</t>
+          <t>A2+B</t>
         </is>
       </c>
       <c r="I24" s="14" t="inlineStr">
@@ -8343,22 +8343,22 @@
       </c>
       <c r="C25" s="11" t="inlineStr">
         <is>
-          <t>CIK:0001909770</t>
+          <t>NYSE:GGAL</t>
         </is>
       </c>
       <c r="D25" s="11" t="inlineStr">
         <is>
-          <t>KHEOBA CORP.</t>
+          <t>Banco Galicia</t>
         </is>
       </c>
       <c r="E25" s="11" t="inlineStr">
         <is>
-          <t>United States/Canada</t>
+          <t>Latin America</t>
         </is>
       </c>
       <c r="F25" s="11" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="G25" s="11" t="inlineStr">
@@ -8368,7 +8368,7 @@
       </c>
       <c r="H25" s="11" t="inlineStr">
         <is>
-          <t>A2+K3</t>
+          <t>A1</t>
         </is>
       </c>
       <c r="I25" s="11" t="inlineStr">
@@ -8383,7 +8383,7 @@
       </c>
       <c r="K25" s="11" t="inlineStr">
         <is>
-          <t>2.94×</t>
+          <t>2.92×</t>
         </is>
       </c>
       <c r="L25" s="11" t="inlineStr">
@@ -8393,7 +8393,7 @@
       </c>
       <c r="M25" s="11" t="inlineStr">
         <is>
-          <t>3.7×</t>
+          <t>3.6×</t>
         </is>
       </c>
     </row>
@@ -8401,29 +8401,29 @@
       <c r="A26" s="12" t="n">
         <v>22</v>
       </c>
-      <c r="B26" s="13" t="inlineStr">
-        <is>
-          <t>PROXY</t>
+      <c r="B26" s="16" t="inlineStr">
+        <is>
+          <t>REAL</t>
         </is>
       </c>
       <c r="C26" s="14" t="inlineStr">
         <is>
-          <t>NYSE:GGAL</t>
+          <t>NYSE:LAC</t>
         </is>
       </c>
       <c r="D26" s="14" t="inlineStr">
         <is>
-          <t>Banco Galicia</t>
+          <t>Lithium Americas</t>
         </is>
       </c>
       <c r="E26" s="14" t="inlineStr">
         <is>
-          <t>Latin America</t>
+          <t>United States/Canada</t>
         </is>
       </c>
       <c r="F26" s="14" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="G26" s="14" t="inlineStr">
@@ -8433,32 +8433,32 @@
       </c>
       <c r="H26" s="14" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2</t>
         </is>
       </c>
       <c r="I26" s="14" t="inlineStr">
         <is>
-          <t>27%</t>
+          <t>60%</t>
         </is>
       </c>
       <c r="J26" s="14" t="inlineStr">
         <is>
-          <t>2.33×</t>
+          <t>3.00×</t>
         </is>
       </c>
       <c r="K26" s="14" t="inlineStr">
         <is>
-          <t>2.92×</t>
+          <t>6.00×</t>
         </is>
       </c>
       <c r="L26" s="14" t="inlineStr">
         <is>
-          <t>2.00×</t>
+          <t>3.10×</t>
         </is>
       </c>
       <c r="M26" s="14" t="inlineStr">
         <is>
-          <t>3.6×</t>
+          <t>3.5×</t>
         </is>
       </c>
     </row>
@@ -8473,22 +8473,22 @@
       </c>
       <c r="C27" s="11" t="inlineStr">
         <is>
-          <t>NYSE:LAC</t>
+          <t>XETR:SZG</t>
         </is>
       </c>
       <c r="D27" s="11" t="inlineStr">
         <is>
-          <t>Lithium Americas</t>
+          <t>Salzgitter</t>
         </is>
       </c>
       <c r="E27" s="11" t="inlineStr">
         <is>
-          <t>United States/Canada</t>
+          <t>Continental Europe</t>
         </is>
       </c>
       <c r="F27" s="11" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="G27" s="11" t="inlineStr">
@@ -8503,27 +8503,27 @@
       </c>
       <c r="I27" s="11" t="inlineStr">
         <is>
-          <t>60%</t>
+          <t>45%</t>
         </is>
       </c>
       <c r="J27" s="11" t="inlineStr">
         <is>
-          <t>3.00×</t>
+          <t>2.50×</t>
         </is>
       </c>
       <c r="K27" s="11" t="inlineStr">
         <is>
-          <t>6.00×</t>
+          <t>4.50×</t>
         </is>
       </c>
       <c r="L27" s="11" t="inlineStr">
         <is>
-          <t>3.10×</t>
+          <t>2.51×</t>
         </is>
       </c>
       <c r="M27" s="11" t="inlineStr">
         <is>
-          <t>3.5×</t>
+          <t>3.4×</t>
         </is>
       </c>
     </row>
@@ -8531,29 +8531,29 @@
       <c r="A28" s="12" t="n">
         <v>24</v>
       </c>
-      <c r="B28" s="16" t="inlineStr">
-        <is>
-          <t>REAL</t>
+      <c r="B28" s="13" t="inlineStr">
+        <is>
+          <t>PROXY</t>
         </is>
       </c>
       <c r="C28" s="14" t="inlineStr">
         <is>
-          <t>XETR:SZG</t>
+          <t>NYSE:PAM</t>
         </is>
       </c>
       <c r="D28" s="14" t="inlineStr">
         <is>
-          <t>Salzgitter</t>
+          <t>Pampa Energía</t>
         </is>
       </c>
       <c r="E28" s="14" t="inlineStr">
         <is>
-          <t>Continental Europe</t>
+          <t>Latin America</t>
         </is>
       </c>
       <c r="F28" s="14" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="G28" s="14" t="inlineStr">
@@ -8563,27 +8563,27 @@
       </c>
       <c r="H28" s="14" t="inlineStr">
         <is>
-          <t>A2</t>
+          <t>A1</t>
         </is>
       </c>
       <c r="I28" s="14" t="inlineStr">
         <is>
-          <t>45%</t>
+          <t>28%</t>
         </is>
       </c>
       <c r="J28" s="14" t="inlineStr">
         <is>
-          <t>2.50×</t>
+          <t>2.29×</t>
         </is>
       </c>
       <c r="K28" s="14" t="inlineStr">
         <is>
-          <t>4.50×</t>
+          <t>2.87×</t>
         </is>
       </c>
       <c r="L28" s="14" t="inlineStr">
         <is>
-          <t>2.51×</t>
+          <t>1.96×</t>
         </is>
       </c>
       <c r="M28" s="14" t="inlineStr">
@@ -8603,22 +8603,22 @@
       </c>
       <c r="C29" s="11" t="inlineStr">
         <is>
-          <t>NYSE:PAM</t>
+          <t>3544</t>
         </is>
       </c>
       <c r="D29" s="11" t="inlineStr">
         <is>
-          <t>Pampa Energía</t>
+          <t>サツドラＨＤ</t>
         </is>
       </c>
       <c r="E29" s="11" t="inlineStr">
         <is>
-          <t>Latin America</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="F29" s="11" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="G29" s="11" t="inlineStr">
@@ -8628,32 +8628,32 @@
       </c>
       <c r="H29" s="11" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2+C</t>
         </is>
       </c>
       <c r="I29" s="11" t="inlineStr">
         <is>
-          <t>28%</t>
+          <t>29%</t>
         </is>
       </c>
       <c r="J29" s="11" t="inlineStr">
         <is>
-          <t>2.29×</t>
+          <t>2.26×</t>
         </is>
       </c>
       <c r="K29" s="11" t="inlineStr">
         <is>
-          <t>2.87×</t>
+          <t>2.80×</t>
         </is>
       </c>
       <c r="L29" s="11" t="inlineStr">
         <is>
-          <t>1.96×</t>
+          <t>1.93×</t>
         </is>
       </c>
       <c r="M29" s="11" t="inlineStr">
         <is>
-          <t>3.4×</t>
+          <t>3.2×</t>
         </is>
       </c>
     </row>
@@ -8696,8 +8696,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="52" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="37" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
     <col width="8" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
@@ -8768,12 +8768,12 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>AEMD</t>
+          <t>TBRG</t>
         </is>
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>AETHLON MEDICAL INC  (AEMD)  (CIK 0000882291)</t>
+          <t>TruBridge, Inc.</t>
         </is>
       </c>
       <c r="D5" s="11" t="inlineStr">
@@ -8783,17 +8783,17 @@
       </c>
       <c r="E5" s="11" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="F5" s="11" t="inlineStr">
         <is>
-          <t>A2+F2</t>
+          <t>A2+K3</t>
         </is>
       </c>
       <c r="G5" s="11" t="inlineStr">
         <is>
-          <t>4.9×</t>
+          <t>6.6×</t>
         </is>
       </c>
       <c r="H5" s="11" t="inlineStr">
@@ -8808,32 +8808,32 @@
       </c>
       <c r="B6" s="14" t="inlineStr">
         <is>
-          <t>NYSE:TGS</t>
+          <t>APTOF</t>
         </is>
       </c>
       <c r="C6" s="14" t="inlineStr">
         <is>
-          <t>TGS (Transportadora de Gas del Sur)</t>
+          <t>Aptose Biosciences Inc.</t>
         </is>
       </c>
       <c r="D6" s="14" t="inlineStr">
         <is>
-          <t>Latin America</t>
+          <t>United States/Canada</t>
         </is>
       </c>
       <c r="E6" s="14" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="F6" s="14" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2+K3</t>
         </is>
       </c>
       <c r="G6" s="14" t="inlineStr">
         <is>
-          <t>4.5×</t>
+          <t>5.9×</t>
         </is>
       </c>
       <c r="H6" s="14" t="inlineStr">
@@ -8848,12 +8848,12 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>BBBY-WT</t>
+          <t>AEMD</t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>BED BATH &amp; BEYOND, INC.  (BBBY, BBBY-WT)  (CIK 000</t>
+          <t>AETHLON MEDICAL INC</t>
         </is>
       </c>
       <c r="D7" s="11" t="inlineStr">
@@ -8863,17 +8863,17 @@
       </c>
       <c r="E7" s="11" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="F7" s="11" t="inlineStr">
         <is>
-          <t>A2</t>
+          <t>A2+F2</t>
         </is>
       </c>
       <c r="G7" s="11" t="inlineStr">
         <is>
-          <t>4.1×</t>
+          <t>5.4×</t>
         </is>
       </c>
       <c r="H7" s="11" t="inlineStr">
@@ -8888,12 +8888,12 @@
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>RNGE</t>
+          <t>LEG</t>
         </is>
       </c>
       <c r="C8" s="14" t="inlineStr">
         <is>
-          <t>RANGE IMPACT, INC.  (RNGE)  (CIK 0001438943)</t>
+          <t>LEGGETT &amp; PLATT INC</t>
         </is>
       </c>
       <c r="D8" s="14" t="inlineStr">
@@ -8903,7 +8903,7 @@
       </c>
       <c r="E8" s="14" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="F8" s="14" t="inlineStr">
@@ -8913,7 +8913,7 @@
       </c>
       <c r="G8" s="14" t="inlineStr">
         <is>
-          <t>4.1×</t>
+          <t>5.3×</t>
         </is>
       </c>
       <c r="H8" s="14" t="inlineStr">
@@ -8928,12 +8928,12 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>REZI</t>
+          <t>BATL</t>
         </is>
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>RESIDEO TECHNOLOGIES, INC.  (REZI)  (CIK 000174033</t>
+          <t>BATTALION OIL CORP</t>
         </is>
       </c>
       <c r="D9" s="11" t="inlineStr">
@@ -8943,7 +8943,7 @@
       </c>
       <c r="E9" s="11" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="F9" s="11" t="inlineStr">
@@ -8953,7 +8953,7 @@
       </c>
       <c r="G9" s="11" t="inlineStr">
         <is>
-          <t>4.1×</t>
+          <t>4.8×</t>
         </is>
       </c>
       <c r="H9" s="11" t="inlineStr">
@@ -8968,32 +8968,32 @@
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>CVKD</t>
+          <t>NYSE:TGS</t>
         </is>
       </c>
       <c r="C10" s="14" t="inlineStr">
         <is>
-          <t>Cadrenal Therapeutics, Inc.  (CVKD)  (CIK 00019379</t>
+          <t>TGS (Transportadora de Gas del Sur)</t>
         </is>
       </c>
       <c r="D10" s="14" t="inlineStr">
         <is>
-          <t>United States/Canada</t>
+          <t>Latin America</t>
         </is>
       </c>
       <c r="E10" s="14" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="F10" s="14" t="inlineStr">
         <is>
-          <t>A2</t>
+          <t>A1</t>
         </is>
       </c>
       <c r="G10" s="14" t="inlineStr">
         <is>
-          <t>4.1×</t>
+          <t>4.5×</t>
         </is>
       </c>
       <c r="H10" s="14" t="inlineStr">
@@ -9008,12 +9008,12 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>SRFM</t>
+          <t>EMI</t>
         </is>
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>SURF AIR MOBILITY INC.  (SRFM)  (CIK 0001936224)</t>
+          <t>Encore Medical, Inc.</t>
         </is>
       </c>
       <c r="D11" s="11" t="inlineStr">
@@ -9023,17 +9023,17 @@
       </c>
       <c r="E11" s="11" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="F11" s="11" t="inlineStr">
         <is>
-          <t>A2</t>
+          <t>A2+F2</t>
         </is>
       </c>
       <c r="G11" s="11" t="inlineStr">
         <is>
-          <t>4.1×</t>
+          <t>4.4×</t>
         </is>
       </c>
       <c r="H11" s="11" t="inlineStr">
@@ -9048,12 +9048,12 @@
       </c>
       <c r="B12" s="14" t="inlineStr">
         <is>
-          <t>HIVE</t>
+          <t>EHGO</t>
         </is>
       </c>
       <c r="C12" s="14" t="inlineStr">
         <is>
-          <t>HIVE Digital Technologies Ltd.  (HIVE)  (CIK 00017</t>
+          <t>EShallGo Inc.</t>
         </is>
       </c>
       <c r="D12" s="14" t="inlineStr">
@@ -9063,7 +9063,7 @@
       </c>
       <c r="E12" s="14" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="F12" s="14" t="inlineStr">
@@ -9073,7 +9073,7 @@
       </c>
       <c r="G12" s="14" t="inlineStr">
         <is>
-          <t>4.1×</t>
+          <t>4.3×</t>
         </is>
       </c>
       <c r="H12" s="14" t="inlineStr">
@@ -9088,12 +9088,12 @@
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>FMC</t>
+          <t>RNGE</t>
         </is>
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>FMC CORP  (FMC)  (CIK 0000037785)</t>
+          <t>RANGE IMPACT, INC.</t>
         </is>
       </c>
       <c r="D13" s="11" t="inlineStr">
@@ -9103,7 +9103,7 @@
       </c>
       <c r="E13" s="11" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="F13" s="11" t="inlineStr">
@@ -9113,7 +9113,7 @@
       </c>
       <c r="G13" s="11" t="inlineStr">
         <is>
-          <t>4.1×</t>
+          <t>4.3×</t>
         </is>
       </c>
       <c r="H13" s="11" t="inlineStr">
@@ -9128,12 +9128,12 @@
       </c>
       <c r="B14" s="14" t="inlineStr">
         <is>
-          <t>Q</t>
+          <t>CVKD</t>
         </is>
       </c>
       <c r="C14" s="14" t="inlineStr">
         <is>
-          <t>Qnity Electronics, Inc.  (Q)  (CIK 0002058873)</t>
+          <t>Cadrenal Therapeutics, Inc.</t>
         </is>
       </c>
       <c r="D14" s="14" t="inlineStr">
@@ -9143,7 +9143,7 @@
       </c>
       <c r="E14" s="14" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="F14" s="14" t="inlineStr">
@@ -9153,7 +9153,7 @@
       </c>
       <c r="G14" s="14" t="inlineStr">
         <is>
-          <t>4.1×</t>
+          <t>4.3×</t>
         </is>
       </c>
       <c r="H14" s="14" t="inlineStr">
@@ -9168,12 +9168,12 @@
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>ASNS</t>
+          <t>SRFM</t>
         </is>
       </c>
       <c r="C15" s="11" t="inlineStr">
         <is>
-          <t>ACTELIS NETWORKS INC  (ASNS)  (CIK 0001141284)</t>
+          <t>SURF AIR MOBILITY INC.</t>
         </is>
       </c>
       <c r="D15" s="11" t="inlineStr">
@@ -9183,7 +9183,7 @@
       </c>
       <c r="E15" s="11" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="F15" s="11" t="inlineStr">
@@ -9193,7 +9193,7 @@
       </c>
       <c r="G15" s="11" t="inlineStr">
         <is>
-          <t>4.1×</t>
+          <t>4.3×</t>
         </is>
       </c>
       <c r="H15" s="11" t="inlineStr">
@@ -9208,12 +9208,12 @@
       </c>
       <c r="B16" s="14" t="inlineStr">
         <is>
-          <t>INUV</t>
+          <t>HIVE</t>
         </is>
       </c>
       <c r="C16" s="14" t="inlineStr">
         <is>
-          <t>Inuvo, Inc.  (INUV)  (CIK 0000829323)</t>
+          <t>HIVE Digital Technologies Ltd.</t>
         </is>
       </c>
       <c r="D16" s="14" t="inlineStr">
@@ -9223,7 +9223,7 @@
       </c>
       <c r="E16" s="14" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="F16" s="14" t="inlineStr">
@@ -9233,7 +9233,7 @@
       </c>
       <c r="G16" s="14" t="inlineStr">
         <is>
-          <t>4.1×</t>
+          <t>4.3×</t>
         </is>
       </c>
       <c r="H16" s="14" t="inlineStr">
@@ -9248,12 +9248,12 @@
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>BATL</t>
+          <t>ASNS</t>
         </is>
       </c>
       <c r="C17" s="11" t="inlineStr">
         <is>
-          <t>['BATTALION OIL CORP  (BATL)  (CIK 0001282648)']</t>
+          <t>ACTELIS NETWORKS INC</t>
         </is>
       </c>
       <c r="D17" s="11" t="inlineStr">
@@ -9263,7 +9263,7 @@
       </c>
       <c r="E17" s="11" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="F17" s="11" t="inlineStr">
@@ -9273,7 +9273,7 @@
       </c>
       <c r="G17" s="11" t="inlineStr">
         <is>
-          <t>4.1×</t>
+          <t>4.3×</t>
         </is>
       </c>
       <c r="H17" s="11" t="inlineStr">
@@ -9288,32 +9288,32 @@
       </c>
       <c r="B18" s="14" t="inlineStr">
         <is>
-          <t>NYSE:EDN</t>
+          <t>INUV</t>
         </is>
       </c>
       <c r="C18" s="14" t="inlineStr">
         <is>
-          <t>Edenor</t>
+          <t>Inuvo, Inc.</t>
         </is>
       </c>
       <c r="D18" s="14" t="inlineStr">
         <is>
-          <t>Latin America</t>
+          <t>United States/Canada</t>
         </is>
       </c>
       <c r="E18" s="14" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="F18" s="14" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2</t>
         </is>
       </c>
       <c r="G18" s="14" t="inlineStr">
         <is>
-          <t>4.0×</t>
+          <t>4.3×</t>
         </is>
       </c>
       <c r="H18" s="14" t="inlineStr">
@@ -9328,12 +9328,12 @@
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>EMI</t>
+          <t>FMC</t>
         </is>
       </c>
       <c r="C19" s="11" t="inlineStr">
         <is>
-          <t>Encore Medical, Inc.  (EMI)  (CIK 0001838003)</t>
+          <t>FMC CORP</t>
         </is>
       </c>
       <c r="D19" s="11" t="inlineStr">
@@ -9343,17 +9343,17 @@
       </c>
       <c r="E19" s="11" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="F19" s="11" t="inlineStr">
         <is>
-          <t>A2+F2</t>
+          <t>A2</t>
         </is>
       </c>
       <c r="G19" s="11" t="inlineStr">
         <is>
-          <t>4.0×</t>
+          <t>4.2×</t>
         </is>
       </c>
       <c r="H19" s="11" t="inlineStr">
@@ -9368,22 +9368,22 @@
       </c>
       <c r="B20" s="14" t="inlineStr">
         <is>
-          <t>BIT:MB</t>
+          <t>NYSE:EDN</t>
         </is>
       </c>
       <c r="C20" s="14" t="inlineStr">
         <is>
-          <t>Mediobanca</t>
+          <t>Edenor</t>
         </is>
       </c>
       <c r="D20" s="14" t="inlineStr">
         <is>
-          <t>Continental Europe</t>
+          <t>Latin America</t>
         </is>
       </c>
       <c r="E20" s="14" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="F20" s="14" t="inlineStr">
@@ -9393,7 +9393,7 @@
       </c>
       <c r="G20" s="14" t="inlineStr">
         <is>
-          <t>3.7×</t>
+          <t>4.0×</t>
         </is>
       </c>
       <c r="H20" s="14" t="inlineStr">
@@ -9408,17 +9408,17 @@
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t>ACF</t>
+          <t>BIT:MB</t>
         </is>
       </c>
       <c r="C21" s="11" t="inlineStr">
         <is>
-          <t>ACROW LIMITED</t>
+          <t>Mediobanca</t>
         </is>
       </c>
       <c r="D21" s="11" t="inlineStr">
         <is>
-          <t>SE Asia / Pacific</t>
+          <t>Continental Europe</t>
         </is>
       </c>
       <c r="E21" s="11" t="inlineStr">
@@ -9428,7 +9428,7 @@
       </c>
       <c r="F21" s="11" t="inlineStr">
         <is>
-          <t>A2+A1</t>
+          <t>A1</t>
         </is>
       </c>
       <c r="G21" s="11" t="inlineStr">
@@ -9448,12 +9448,12 @@
       </c>
       <c r="B22" s="14" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>ACF</t>
         </is>
       </c>
       <c r="C22" s="14" t="inlineStr">
         <is>
-          <t>MEMPHASYS LIMITED.</t>
+          <t>ACROW LIMITED</t>
         </is>
       </c>
       <c r="D22" s="14" t="inlineStr">
@@ -9468,7 +9468,7 @@
       </c>
       <c r="F22" s="14" t="inlineStr">
         <is>
-          <t>A2+B</t>
+          <t>A2+A1</t>
         </is>
       </c>
       <c r="G22" s="14" t="inlineStr">
@@ -9488,17 +9488,17 @@
       </c>
       <c r="B23" s="11" t="inlineStr">
         <is>
-          <t>CIK:0001348911</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="C23" s="11" t="inlineStr">
         <is>
-          <t>KalVista Pharmaceuticals, Inc.</t>
+          <t>MEMPHASYS LIMITED.</t>
         </is>
       </c>
       <c r="D23" s="11" t="inlineStr">
         <is>
-          <t>United States/Canada</t>
+          <t>SE Asia / Pacific</t>
         </is>
       </c>
       <c r="E23" s="11" t="inlineStr">
@@ -9508,7 +9508,7 @@
       </c>
       <c r="F23" s="11" t="inlineStr">
         <is>
-          <t>A2+K3</t>
+          <t>A2+B</t>
         </is>
       </c>
       <c r="G23" s="11" t="inlineStr">
@@ -9528,32 +9528,32 @@
       </c>
       <c r="B24" s="14" t="inlineStr">
         <is>
-          <t>CIK:0001909770</t>
+          <t>NYSE:GGAL</t>
         </is>
       </c>
       <c r="C24" s="14" t="inlineStr">
         <is>
-          <t>KHEOBA CORP.</t>
+          <t>Banco Galicia</t>
         </is>
       </c>
       <c r="D24" s="14" t="inlineStr">
         <is>
-          <t>United States/Canada</t>
+          <t>Latin America</t>
         </is>
       </c>
       <c r="E24" s="14" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="F24" s="14" t="inlineStr">
         <is>
-          <t>A2+K3</t>
+          <t>A1</t>
         </is>
       </c>
       <c r="G24" s="14" t="inlineStr">
         <is>
-          <t>3.7×</t>
+          <t>3.6×</t>
         </is>
       </c>
       <c r="H24" s="14" t="inlineStr">

--- a/output/cyclepapa_risk_reward_workbook.xlsx
+++ b/output/cyclepapa_risk_reward_workbook.xlsx
@@ -608,7 +608,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Generated 2026-07-11</t>
+          <t>Generated 2026-07-12</t>
         </is>
       </c>
     </row>
@@ -6932,16 +6932,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M31"/>
+  <dimension ref="A1:M106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
     <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="11" customWidth="1" min="3" max="3"/>
-    <col width="37" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="52" customWidth="1" min="4" max="4"/>
     <col width="22" customWidth="1" min="5" max="5"/>
     <col width="8" customWidth="1" min="6" max="6"/>
-    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
     <col width="11" customWidth="1" min="8" max="8"/>
     <col width="11" customWidth="1" min="9" max="9"/>
     <col width="8" customWidth="1" min="10" max="10"/>
@@ -6953,14 +6953,14 @@
     <row r="1" ht="22" customHeight="1">
       <c r="A1" s="6" t="inlineStr">
         <is>
-          <t>Universe-wide top picks · ranked by quantitative reward/risk</t>
+          <t>Universe-wide top 100 · ranked by quantitative reward/risk (asymmetry)</t>
         </is>
       </c>
     </row>
     <row r="2" ht="38" customHeight="1">
       <c r="A2" s="7" t="inlineStr">
         <is>
-          <t>Universe coverage: 116 investable names (20 REAL waterfalls · 96 PROXY).  REAL uses the hand-built YAML's bottom-up bear/base/bull. PROXY uses a transparent formula on the universe-screener score + archetype tilt.</t>
+          <t>Universe coverage: 221 investable names (21 REAL waterfalls · 200 PROXY).  REAL uses the hand-built YAML's bottom-up bear/base/bull. PROXY uses a transparent formula on the universe-screener score + archetype tilt.</t>
         </is>
       </c>
     </row>
@@ -7108,22 +7108,22 @@
       </c>
       <c r="C6" s="14" t="inlineStr">
         <is>
-          <t>TBRG</t>
+          <t>NYSE:TGS</t>
         </is>
       </c>
       <c r="D6" s="14" t="inlineStr">
         <is>
-          <t>TruBridge, Inc.</t>
+          <t>TGS (Transportadora de Gas del Sur)</t>
         </is>
       </c>
       <c r="E6" s="14" t="inlineStr">
         <is>
-          <t>United States/Canada</t>
+          <t>Latin America</t>
         </is>
       </c>
       <c r="F6" s="14" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="G6" s="14" t="inlineStr">
@@ -7133,32 +7133,32 @@
       </c>
       <c r="H6" s="14" t="inlineStr">
         <is>
-          <t>A2+K3</t>
+          <t>A1</t>
         </is>
       </c>
       <c r="I6" s="14" t="inlineStr">
         <is>
-          <t>20%</t>
+          <t>24%</t>
         </is>
       </c>
       <c r="J6" s="14" t="inlineStr">
         <is>
-          <t>2.63×</t>
+          <t>2.44×</t>
         </is>
       </c>
       <c r="K6" s="14" t="inlineStr">
         <is>
-          <t>3.45×</t>
+          <t>3.12×</t>
         </is>
       </c>
       <c r="L6" s="14" t="inlineStr">
         <is>
-          <t>2.29×</t>
+          <t>2.10×</t>
         </is>
       </c>
       <c r="M6" s="14" t="inlineStr">
         <is>
-          <t>6.6×</t>
+          <t>4.5×</t>
         </is>
       </c>
     </row>
@@ -7173,22 +7173,22 @@
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>APTOF</t>
+          <t>NYSE:EDN</t>
         </is>
       </c>
       <c r="D7" s="11" t="inlineStr">
         <is>
-          <t>Aptose Biosciences Inc.</t>
+          <t>Edenor</t>
         </is>
       </c>
       <c r="E7" s="11" t="inlineStr">
         <is>
-          <t>United States/Canada</t>
+          <t>Latin America</t>
         </is>
       </c>
       <c r="F7" s="11" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="G7" s="11" t="inlineStr">
@@ -7198,32 +7198,32 @@
       </c>
       <c r="H7" s="11" t="inlineStr">
         <is>
-          <t>A2+K3</t>
+          <t>A1</t>
         </is>
       </c>
       <c r="I7" s="11" t="inlineStr">
         <is>
-          <t>21%</t>
+          <t>26%</t>
         </is>
       </c>
       <c r="J7" s="11" t="inlineStr">
         <is>
-          <t>2.58×</t>
+          <t>2.38×</t>
         </is>
       </c>
       <c r="K7" s="11" t="inlineStr">
         <is>
-          <t>3.36×</t>
+          <t>3.02×</t>
         </is>
       </c>
       <c r="L7" s="11" t="inlineStr">
         <is>
-          <t>2.24×</t>
+          <t>2.05×</t>
         </is>
       </c>
       <c r="M7" s="11" t="inlineStr">
         <is>
-          <t>5.9×</t>
+          <t>4.0×</t>
         </is>
       </c>
     </row>
@@ -7238,22 +7238,22 @@
       </c>
       <c r="C8" s="14" t="inlineStr">
         <is>
-          <t>AEMD</t>
+          <t>BIT:MB</t>
         </is>
       </c>
       <c r="D8" s="14" t="inlineStr">
         <is>
-          <t>AETHLON MEDICAL INC</t>
+          <t>Mediobanca</t>
         </is>
       </c>
       <c r="E8" s="14" t="inlineStr">
         <is>
-          <t>United States/Canada</t>
+          <t>Continental Europe</t>
         </is>
       </c>
       <c r="F8" s="14" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="G8" s="14" t="inlineStr">
@@ -7263,32 +7263,32 @@
       </c>
       <c r="H8" s="14" t="inlineStr">
         <is>
-          <t>A2+F2</t>
+          <t>A1</t>
         </is>
       </c>
       <c r="I8" s="14" t="inlineStr">
         <is>
-          <t>22%</t>
+          <t>27%</t>
         </is>
       </c>
       <c r="J8" s="14" t="inlineStr">
         <is>
-          <t>2.53×</t>
+          <t>2.33×</t>
         </is>
       </c>
       <c r="K8" s="14" t="inlineStr">
         <is>
-          <t>3.29×</t>
+          <t>2.94×</t>
         </is>
       </c>
       <c r="L8" s="14" t="inlineStr">
         <is>
-          <t>2.20×</t>
+          <t>2.00×</t>
         </is>
       </c>
       <c r="M8" s="14" t="inlineStr">
         <is>
-          <t>5.4×</t>
+          <t>3.7×</t>
         </is>
       </c>
     </row>
@@ -7303,22 +7303,22 @@
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>LEG</t>
+          <t>NYSE:GGAL</t>
         </is>
       </c>
       <c r="D9" s="11" t="inlineStr">
         <is>
-          <t>LEGGETT &amp; PLATT INC</t>
+          <t>Banco Galicia</t>
         </is>
       </c>
       <c r="E9" s="11" t="inlineStr">
         <is>
-          <t>United States/Canada</t>
+          <t>Latin America</t>
         </is>
       </c>
       <c r="F9" s="11" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="G9" s="11" t="inlineStr">
@@ -7328,32 +7328,32 @@
       </c>
       <c r="H9" s="11" t="inlineStr">
         <is>
-          <t>A2</t>
+          <t>A1</t>
         </is>
       </c>
       <c r="I9" s="11" t="inlineStr">
         <is>
-          <t>22%</t>
+          <t>27%</t>
         </is>
       </c>
       <c r="J9" s="11" t="inlineStr">
         <is>
-          <t>2.52×</t>
+          <t>2.33×</t>
         </is>
       </c>
       <c r="K9" s="11" t="inlineStr">
         <is>
-          <t>3.27×</t>
+          <t>2.92×</t>
         </is>
       </c>
       <c r="L9" s="11" t="inlineStr">
         <is>
-          <t>2.19×</t>
+          <t>2.00×</t>
         </is>
       </c>
       <c r="M9" s="11" t="inlineStr">
         <is>
-          <t>5.3×</t>
+          <t>3.6×</t>
         </is>
       </c>
     </row>
@@ -7361,19 +7361,19 @@
       <c r="A10" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="B10" s="13" t="inlineStr">
-        <is>
-          <t>PROXY</t>
+      <c r="B10" s="16" t="inlineStr">
+        <is>
+          <t>REAL</t>
         </is>
       </c>
       <c r="C10" s="14" t="inlineStr">
         <is>
-          <t>BATL</t>
+          <t>NYSE:LAC</t>
         </is>
       </c>
       <c r="D10" s="14" t="inlineStr">
         <is>
-          <t>BATTALION OIL CORP</t>
+          <t>Lithium Americas</t>
         </is>
       </c>
       <c r="E10" s="14" t="inlineStr">
@@ -7383,7 +7383,7 @@
       </c>
       <c r="F10" s="14" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="G10" s="14" t="inlineStr">
@@ -7398,27 +7398,27 @@
       </c>
       <c r="I10" s="14" t="inlineStr">
         <is>
-          <t>24%</t>
+          <t>60%</t>
         </is>
       </c>
       <c r="J10" s="14" t="inlineStr">
         <is>
-          <t>2.47×</t>
+          <t>3.00×</t>
         </is>
       </c>
       <c r="K10" s="14" t="inlineStr">
         <is>
-          <t>3.18×</t>
+          <t>6.00×</t>
         </is>
       </c>
       <c r="L10" s="14" t="inlineStr">
         <is>
-          <t>2.14×</t>
+          <t>3.10×</t>
         </is>
       </c>
       <c r="M10" s="14" t="inlineStr">
         <is>
-          <t>4.8×</t>
+          <t>3.5×</t>
         </is>
       </c>
     </row>
@@ -7426,29 +7426,29 @@
       <c r="A11" s="9" t="n">
         <v>7</v>
       </c>
-      <c r="B11" s="15" t="inlineStr">
-        <is>
-          <t>PROXY</t>
+      <c r="B11" s="10" t="inlineStr">
+        <is>
+          <t>REAL</t>
         </is>
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>NYSE:TGS</t>
+          <t>XETR:SZG</t>
         </is>
       </c>
       <c r="D11" s="11" t="inlineStr">
         <is>
-          <t>TGS (Transportadora de Gas del Sur)</t>
+          <t>Salzgitter</t>
         </is>
       </c>
       <c r="E11" s="11" t="inlineStr">
         <is>
-          <t>Latin America</t>
+          <t>Continental Europe</t>
         </is>
       </c>
       <c r="F11" s="11" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="G11" s="11" t="inlineStr">
@@ -7458,32 +7458,32 @@
       </c>
       <c r="H11" s="11" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2</t>
         </is>
       </c>
       <c r="I11" s="11" t="inlineStr">
         <is>
-          <t>24%</t>
+          <t>45%</t>
         </is>
       </c>
       <c r="J11" s="11" t="inlineStr">
         <is>
-          <t>2.44×</t>
+          <t>2.50×</t>
         </is>
       </c>
       <c r="K11" s="11" t="inlineStr">
         <is>
-          <t>3.12×</t>
+          <t>4.50×</t>
         </is>
       </c>
       <c r="L11" s="11" t="inlineStr">
         <is>
-          <t>2.10×</t>
+          <t>2.51×</t>
         </is>
       </c>
       <c r="M11" s="11" t="inlineStr">
         <is>
-          <t>4.5×</t>
+          <t>3.4×</t>
         </is>
       </c>
     </row>
@@ -7498,22 +7498,22 @@
       </c>
       <c r="C12" s="14" t="inlineStr">
         <is>
-          <t>EMI</t>
+          <t>NYSE:PAM</t>
         </is>
       </c>
       <c r="D12" s="14" t="inlineStr">
         <is>
-          <t>Encore Medical, Inc.</t>
+          <t>Pampa Energía</t>
         </is>
       </c>
       <c r="E12" s="14" t="inlineStr">
         <is>
-          <t>United States/Canada</t>
+          <t>Latin America</t>
         </is>
       </c>
       <c r="F12" s="14" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="G12" s="14" t="inlineStr">
@@ -7523,32 +7523,32 @@
       </c>
       <c r="H12" s="14" t="inlineStr">
         <is>
-          <t>A2+F2</t>
+          <t>A1</t>
         </is>
       </c>
       <c r="I12" s="14" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>28%</t>
         </is>
       </c>
       <c r="J12" s="14" t="inlineStr">
         <is>
-          <t>2.42×</t>
+          <t>2.29×</t>
         </is>
       </c>
       <c r="K12" s="14" t="inlineStr">
         <is>
-          <t>3.09×</t>
+          <t>2.87×</t>
         </is>
       </c>
       <c r="L12" s="14" t="inlineStr">
         <is>
-          <t>2.09×</t>
+          <t>1.96×</t>
         </is>
       </c>
       <c r="M12" s="14" t="inlineStr">
         <is>
-          <t>4.4×</t>
+          <t>3.4×</t>
         </is>
       </c>
     </row>
@@ -7556,29 +7556,29 @@
       <c r="A13" s="9" t="n">
         <v>9</v>
       </c>
-      <c r="B13" s="15" t="inlineStr">
-        <is>
-          <t>PROXY</t>
+      <c r="B13" s="10" t="inlineStr">
+        <is>
+          <t>REAL</t>
         </is>
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>EHGO</t>
+          <t>XETR:TKA</t>
         </is>
       </c>
       <c r="D13" s="11" t="inlineStr">
         <is>
-          <t>EShallGo Inc.</t>
+          <t>Thyssenkrupp Steel</t>
         </is>
       </c>
       <c r="E13" s="11" t="inlineStr">
         <is>
-          <t>United States/Canada</t>
+          <t>Continental Europe</t>
         </is>
       </c>
       <c r="F13" s="11" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="G13" s="11" t="inlineStr">
@@ -7588,32 +7588,32 @@
       </c>
       <c r="H13" s="11" t="inlineStr">
         <is>
-          <t>A2</t>
+          <t>H</t>
         </is>
       </c>
       <c r="I13" s="11" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>45%</t>
         </is>
       </c>
       <c r="J13" s="11" t="inlineStr">
         <is>
-          <t>2.41×</t>
+          <t>2.30×</t>
         </is>
       </c>
       <c r="K13" s="11" t="inlineStr">
         <is>
-          <t>3.08×</t>
+          <t>4.20×</t>
         </is>
       </c>
       <c r="L13" s="11" t="inlineStr">
         <is>
-          <t>2.08×</t>
+          <t>2.34×</t>
         </is>
       </c>
       <c r="M13" s="11" t="inlineStr">
         <is>
-          <t>4.3×</t>
+          <t>3.0×</t>
         </is>
       </c>
     </row>
@@ -7628,22 +7628,22 @@
       </c>
       <c r="C14" s="14" t="inlineStr">
         <is>
-          <t>RNGE</t>
+          <t>ACF</t>
         </is>
       </c>
       <c r="D14" s="14" t="inlineStr">
         <is>
-          <t>RANGE IMPACT, INC.</t>
+          <t>ACROW LIMITED</t>
         </is>
       </c>
       <c r="E14" s="14" t="inlineStr">
         <is>
-          <t>United States/Canada</t>
+          <t>SE Asia / Pacific</t>
         </is>
       </c>
       <c r="F14" s="14" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="G14" s="14" t="inlineStr">
@@ -7653,32 +7653,32 @@
       </c>
       <c r="H14" s="14" t="inlineStr">
         <is>
-          <t>A2</t>
+          <t>A1</t>
         </is>
       </c>
       <c r="I14" s="14" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>30%</t>
         </is>
       </c>
       <c r="J14" s="14" t="inlineStr">
         <is>
-          <t>2.41×</t>
+          <t>2.22×</t>
         </is>
       </c>
       <c r="K14" s="14" t="inlineStr">
         <is>
-          <t>3.08×</t>
+          <t>2.75×</t>
         </is>
       </c>
       <c r="L14" s="14" t="inlineStr">
         <is>
-          <t>2.08×</t>
+          <t>1.90×</t>
         </is>
       </c>
       <c r="M14" s="14" t="inlineStr">
         <is>
-          <t>4.3×</t>
+          <t>3.0×</t>
         </is>
       </c>
     </row>
@@ -7686,29 +7686,29 @@
       <c r="A15" s="9" t="n">
         <v>11</v>
       </c>
-      <c r="B15" s="15" t="inlineStr">
-        <is>
-          <t>PROXY</t>
+      <c r="B15" s="10" t="inlineStr">
+        <is>
+          <t>REAL</t>
         </is>
       </c>
       <c r="C15" s="11" t="inlineStr">
         <is>
-          <t>CVKD</t>
+          <t>NGX:GTCO</t>
         </is>
       </c>
       <c r="D15" s="11" t="inlineStr">
         <is>
-          <t>Cadrenal Therapeutics, Inc.</t>
+          <t>GTCO (Guaranty Trust)</t>
         </is>
       </c>
       <c r="E15" s="11" t="inlineStr">
         <is>
-          <t>United States/Canada</t>
+          <t>MEA / Frontier</t>
         </is>
       </c>
       <c r="F15" s="11" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="G15" s="11" t="inlineStr">
@@ -7718,32 +7718,32 @@
       </c>
       <c r="H15" s="11" t="inlineStr">
         <is>
-          <t>A2</t>
+          <t>G</t>
         </is>
       </c>
       <c r="I15" s="11" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>40%</t>
         </is>
       </c>
       <c r="J15" s="11" t="inlineStr">
         <is>
-          <t>2.41×</t>
+          <t>2.10×</t>
         </is>
       </c>
       <c r="K15" s="11" t="inlineStr">
         <is>
-          <t>3.08×</t>
+          <t>3.80×</t>
         </is>
       </c>
       <c r="L15" s="11" t="inlineStr">
         <is>
-          <t>2.08×</t>
+          <t>2.15×</t>
         </is>
       </c>
       <c r="M15" s="11" t="inlineStr">
         <is>
-          <t>4.3×</t>
+          <t>2.9×</t>
         </is>
       </c>
     </row>
@@ -7751,29 +7751,29 @@
       <c r="A16" s="12" t="n">
         <v>12</v>
       </c>
-      <c r="B16" s="13" t="inlineStr">
-        <is>
-          <t>PROXY</t>
+      <c r="B16" s="16" t="inlineStr">
+        <is>
+          <t>REAL</t>
         </is>
       </c>
       <c r="C16" s="14" t="inlineStr">
         <is>
-          <t>SRFM</t>
+          <t>STO:ELUX-B</t>
         </is>
       </c>
       <c r="D16" s="14" t="inlineStr">
         <is>
-          <t>SURF AIR MOBILITY INC.</t>
+          <t>AB Electrolux (Series B)</t>
         </is>
       </c>
       <c r="E16" s="14" t="inlineStr">
         <is>
-          <t>United States/Canada</t>
+          <t>Continental Europe</t>
         </is>
       </c>
       <c r="F16" s="14" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="G16" s="14" t="inlineStr">
@@ -7783,32 +7783,32 @@
       </c>
       <c r="H16" s="14" t="inlineStr">
         <is>
-          <t>A2</t>
+          <t>A1+D</t>
         </is>
       </c>
       <c r="I16" s="14" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>45%</t>
         </is>
       </c>
       <c r="J16" s="14" t="inlineStr">
         <is>
-          <t>2.41×</t>
+          <t>2.20×</t>
         </is>
       </c>
       <c r="K16" s="14" t="inlineStr">
         <is>
-          <t>3.08×</t>
+          <t>4.00×</t>
         </is>
       </c>
       <c r="L16" s="14" t="inlineStr">
         <is>
-          <t>2.08×</t>
+          <t>2.32×</t>
         </is>
       </c>
       <c r="M16" s="14" t="inlineStr">
         <is>
-          <t>4.3×</t>
+          <t>2.9×</t>
         </is>
       </c>
     </row>
@@ -7816,29 +7816,29 @@
       <c r="A17" s="9" t="n">
         <v>13</v>
       </c>
-      <c r="B17" s="15" t="inlineStr">
-        <is>
-          <t>PROXY</t>
+      <c r="B17" s="10" t="inlineStr">
+        <is>
+          <t>REAL</t>
         </is>
       </c>
       <c r="C17" s="11" t="inlineStr">
         <is>
-          <t>HIVE</t>
+          <t>TSE:6305</t>
         </is>
       </c>
       <c r="D17" s="11" t="inlineStr">
         <is>
-          <t>HIVE Digital Technologies Ltd.</t>
+          <t>Hitachi Construction Machinery</t>
         </is>
       </c>
       <c r="E17" s="11" t="inlineStr">
         <is>
-          <t>United States/Canada</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="F17" s="11" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="G17" s="11" t="inlineStr">
@@ -7848,7 +7848,7 @@
       </c>
       <c r="H17" s="11" t="inlineStr">
         <is>
-          <t>A2</t>
+          <t>H</t>
         </is>
       </c>
       <c r="I17" s="11" t="inlineStr">
@@ -7858,22 +7858,22 @@
       </c>
       <c r="J17" s="11" t="inlineStr">
         <is>
-          <t>2.41×</t>
+          <t>1.70×</t>
         </is>
       </c>
       <c r="K17" s="11" t="inlineStr">
         <is>
-          <t>3.08×</t>
+          <t>2.80×</t>
         </is>
       </c>
       <c r="L17" s="11" t="inlineStr">
         <is>
-          <t>2.08×</t>
+          <t>1.69×</t>
         </is>
       </c>
       <c r="M17" s="11" t="inlineStr">
         <is>
-          <t>4.3×</t>
+          <t>2.8×</t>
         </is>
       </c>
     </row>
@@ -7881,29 +7881,29 @@
       <c r="A18" s="12" t="n">
         <v>14</v>
       </c>
-      <c r="B18" s="13" t="inlineStr">
-        <is>
-          <t>PROXY</t>
+      <c r="B18" s="16" t="inlineStr">
+        <is>
+          <t>REAL</t>
         </is>
       </c>
       <c r="C18" s="14" t="inlineStr">
         <is>
-          <t>ASNS</t>
+          <t>DFM:DSI</t>
         </is>
       </c>
       <c r="D18" s="14" t="inlineStr">
         <is>
-          <t>ACTELIS NETWORKS INC</t>
+          <t>Drake &amp; Scull</t>
         </is>
       </c>
       <c r="E18" s="14" t="inlineStr">
         <is>
-          <t>United States/Canada</t>
+          <t>MEA / Frontier</t>
         </is>
       </c>
       <c r="F18" s="14" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="G18" s="14" t="inlineStr">
@@ -7918,27 +7918,27 @@
       </c>
       <c r="I18" s="14" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>45%</t>
         </is>
       </c>
       <c r="J18" s="14" t="inlineStr">
         <is>
-          <t>2.41×</t>
+          <t>2.30×</t>
         </is>
       </c>
       <c r="K18" s="14" t="inlineStr">
         <is>
-          <t>3.08×</t>
+          <t>4.20×</t>
         </is>
       </c>
       <c r="L18" s="14" t="inlineStr">
         <is>
-          <t>2.08×</t>
+          <t>2.25×</t>
         </is>
       </c>
       <c r="M18" s="14" t="inlineStr">
         <is>
-          <t>4.3×</t>
+          <t>2.8×</t>
         </is>
       </c>
     </row>
@@ -7946,29 +7946,29 @@
       <c r="A19" s="9" t="n">
         <v>15</v>
       </c>
-      <c r="B19" s="15" t="inlineStr">
-        <is>
-          <t>PROXY</t>
+      <c r="B19" s="10" t="inlineStr">
+        <is>
+          <t>REAL</t>
         </is>
       </c>
       <c r="C19" s="11" t="inlineStr">
         <is>
-          <t>INUV</t>
+          <t>BME:OHLA</t>
         </is>
       </c>
       <c r="D19" s="11" t="inlineStr">
         <is>
-          <t>Inuvo, Inc.</t>
+          <t>OHLA (former OHL)</t>
         </is>
       </c>
       <c r="E19" s="11" t="inlineStr">
         <is>
-          <t>United States/Canada</t>
+          <t>Continental Europe</t>
         </is>
       </c>
       <c r="F19" s="11" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="G19" s="11" t="inlineStr">
@@ -7978,32 +7978,32 @@
       </c>
       <c r="H19" s="11" t="inlineStr">
         <is>
-          <t>A2</t>
+          <t>A1</t>
         </is>
       </c>
       <c r="I19" s="11" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>50%</t>
         </is>
       </c>
       <c r="J19" s="11" t="inlineStr">
         <is>
-          <t>2.41×</t>
+          <t>2.40×</t>
         </is>
       </c>
       <c r="K19" s="11" t="inlineStr">
         <is>
-          <t>3.08×</t>
+          <t>4.50×</t>
         </is>
       </c>
       <c r="L19" s="11" t="inlineStr">
         <is>
-          <t>2.08×</t>
+          <t>2.35×</t>
         </is>
       </c>
       <c r="M19" s="11" t="inlineStr">
         <is>
-          <t>4.3×</t>
+          <t>2.7×</t>
         </is>
       </c>
     </row>
@@ -8011,29 +8011,29 @@
       <c r="A20" s="12" t="n">
         <v>16</v>
       </c>
-      <c r="B20" s="13" t="inlineStr">
-        <is>
-          <t>PROXY</t>
+      <c r="B20" s="16" t="inlineStr">
+        <is>
+          <t>REAL</t>
         </is>
       </c>
       <c r="C20" s="14" t="inlineStr">
         <is>
-          <t>FMC</t>
+          <t>EPA:ETL</t>
         </is>
       </c>
       <c r="D20" s="14" t="inlineStr">
         <is>
-          <t>FMC CORP</t>
+          <t>Eutelsat</t>
         </is>
       </c>
       <c r="E20" s="14" t="inlineStr">
         <is>
-          <t>United States/Canada</t>
+          <t>Continental Europe</t>
         </is>
       </c>
       <c r="F20" s="14" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="G20" s="14" t="inlineStr">
@@ -8043,32 +8043,32 @@
       </c>
       <c r="H20" s="14" t="inlineStr">
         <is>
-          <t>A2</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="I20" s="14" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>50%</t>
         </is>
       </c>
       <c r="J20" s="14" t="inlineStr">
         <is>
-          <t>2.40×</t>
+          <t>2.20×</t>
         </is>
       </c>
       <c r="K20" s="14" t="inlineStr">
         <is>
-          <t>3.06×</t>
+          <t>4.50×</t>
         </is>
       </c>
       <c r="L20" s="14" t="inlineStr">
         <is>
-          <t>2.07×</t>
+          <t>2.35×</t>
         </is>
       </c>
       <c r="M20" s="14" t="inlineStr">
         <is>
-          <t>4.2×</t>
+          <t>2.7×</t>
         </is>
       </c>
     </row>
@@ -8076,29 +8076,29 @@
       <c r="A21" s="9" t="n">
         <v>17</v>
       </c>
-      <c r="B21" s="15" t="inlineStr">
-        <is>
-          <t>PROXY</t>
+      <c r="B21" s="10" t="inlineStr">
+        <is>
+          <t>REAL</t>
         </is>
       </c>
       <c r="C21" s="11" t="inlineStr">
         <is>
-          <t>NYSE:EDN</t>
+          <t>EPA:WLN</t>
         </is>
       </c>
       <c r="D21" s="11" t="inlineStr">
         <is>
-          <t>Edenor</t>
+          <t>Worldline</t>
         </is>
       </c>
       <c r="E21" s="11" t="inlineStr">
         <is>
-          <t>Latin America</t>
+          <t>Continental Europe</t>
         </is>
       </c>
       <c r="F21" s="11" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="G21" s="11" t="inlineStr">
@@ -8108,32 +8108,32 @@
       </c>
       <c r="H21" s="11" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="I21" s="11" t="inlineStr">
         <is>
-          <t>26%</t>
+          <t>60%</t>
         </is>
       </c>
       <c r="J21" s="11" t="inlineStr">
         <is>
-          <t>2.38×</t>
+          <t>2.50×</t>
         </is>
       </c>
       <c r="K21" s="11" t="inlineStr">
         <is>
-          <t>3.02×</t>
+          <t>5.50×</t>
         </is>
       </c>
       <c r="L21" s="11" t="inlineStr">
         <is>
-          <t>2.05×</t>
+          <t>2.62×</t>
         </is>
       </c>
       <c r="M21" s="11" t="inlineStr">
         <is>
-          <t>4.0×</t>
+          <t>2.7×</t>
         </is>
       </c>
     </row>
@@ -8141,29 +8141,29 @@
       <c r="A22" s="12" t="n">
         <v>18</v>
       </c>
-      <c r="B22" s="13" t="inlineStr">
-        <is>
-          <t>PROXY</t>
+      <c r="B22" s="16" t="inlineStr">
+        <is>
+          <t>REAL</t>
         </is>
       </c>
       <c r="C22" s="14" t="inlineStr">
         <is>
-          <t>BIT:MB</t>
+          <t>KRX:241560</t>
         </is>
       </c>
       <c r="D22" s="14" t="inlineStr">
         <is>
-          <t>Mediobanca</t>
+          <t>Doosan Bobcat → Doosan Robotics merger</t>
         </is>
       </c>
       <c r="E22" s="14" t="inlineStr">
         <is>
-          <t>Continental Europe</t>
+          <t>Korea</t>
         </is>
       </c>
       <c r="F22" s="14" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="G22" s="14" t="inlineStr">
@@ -8173,32 +8173,32 @@
       </c>
       <c r="H22" s="14" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>H</t>
         </is>
       </c>
       <c r="I22" s="14" t="inlineStr">
         <is>
-          <t>27%</t>
+          <t>25%</t>
         </is>
       </c>
       <c r="J22" s="14" t="inlineStr">
         <is>
-          <t>2.33×</t>
+          <t>1.70×</t>
         </is>
       </c>
       <c r="K22" s="14" t="inlineStr">
         <is>
-          <t>2.94×</t>
+          <t>2.50×</t>
         </is>
       </c>
       <c r="L22" s="14" t="inlineStr">
         <is>
-          <t>2.00×</t>
+          <t>1.66×</t>
         </is>
       </c>
       <c r="M22" s="14" t="inlineStr">
         <is>
-          <t>3.7×</t>
+          <t>2.7×</t>
         </is>
       </c>
     </row>
@@ -8206,29 +8206,29 @@
       <c r="A23" s="9" t="n">
         <v>19</v>
       </c>
-      <c r="B23" s="15" t="inlineStr">
-        <is>
-          <t>PROXY</t>
+      <c r="B23" s="10" t="inlineStr">
+        <is>
+          <t>REAL</t>
         </is>
       </c>
       <c r="C23" s="11" t="inlineStr">
         <is>
-          <t>ACF</t>
+          <t>BME:SAB</t>
         </is>
       </c>
       <c r="D23" s="11" t="inlineStr">
         <is>
-          <t>ACROW LIMITED</t>
+          <t>Banco Sabadell</t>
         </is>
       </c>
       <c r="E23" s="11" t="inlineStr">
         <is>
-          <t>SE Asia / Pacific</t>
+          <t>Continental Europe</t>
         </is>
       </c>
       <c r="F23" s="11" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="G23" s="11" t="inlineStr">
@@ -8238,32 +8238,32 @@
       </c>
       <c r="H23" s="11" t="inlineStr">
         <is>
-          <t>A2+A1</t>
+          <t>A1</t>
         </is>
       </c>
       <c r="I23" s="11" t="inlineStr">
         <is>
-          <t>27%</t>
+          <t>25%</t>
         </is>
       </c>
       <c r="J23" s="11" t="inlineStr">
         <is>
-          <t>2.33×</t>
+          <t>1.65×</t>
         </is>
       </c>
       <c r="K23" s="11" t="inlineStr">
         <is>
-          <t>2.94×</t>
+          <t>2.40×</t>
         </is>
       </c>
       <c r="L23" s="11" t="inlineStr">
         <is>
-          <t>2.00×</t>
+          <t>1.66×</t>
         </is>
       </c>
       <c r="M23" s="11" t="inlineStr">
         <is>
-          <t>3.7×</t>
+          <t>2.6×</t>
         </is>
       </c>
     </row>
@@ -8278,22 +8278,22 @@
       </c>
       <c r="C24" s="14" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>BME:TLGO</t>
         </is>
       </c>
       <c r="D24" s="14" t="inlineStr">
         <is>
-          <t>MEMPHASYS LIMITED.</t>
+          <t>Talgo</t>
         </is>
       </c>
       <c r="E24" s="14" t="inlineStr">
         <is>
-          <t>SE Asia / Pacific</t>
+          <t>Continental Europe</t>
         </is>
       </c>
       <c r="F24" s="14" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="G24" s="14" t="inlineStr">
@@ -8303,32 +8303,32 @@
       </c>
       <c r="H24" s="14" t="inlineStr">
         <is>
-          <t>A2+B</t>
+          <t>A1</t>
         </is>
       </c>
       <c r="I24" s="14" t="inlineStr">
         <is>
-          <t>27%</t>
+          <t>32%</t>
         </is>
       </c>
       <c r="J24" s="14" t="inlineStr">
         <is>
-          <t>2.33×</t>
+          <t>2.16×</t>
         </is>
       </c>
       <c r="K24" s="14" t="inlineStr">
         <is>
-          <t>2.94×</t>
+          <t>2.64×</t>
         </is>
       </c>
       <c r="L24" s="14" t="inlineStr">
         <is>
-          <t>2.00×</t>
+          <t>1.84×</t>
         </is>
       </c>
       <c r="M24" s="14" t="inlineStr">
         <is>
-          <t>3.7×</t>
+          <t>2.6×</t>
         </is>
       </c>
     </row>
@@ -8336,19 +8336,19 @@
       <c r="A25" s="9" t="n">
         <v>21</v>
       </c>
-      <c r="B25" s="15" t="inlineStr">
-        <is>
-          <t>PROXY</t>
+      <c r="B25" s="10" t="inlineStr">
+        <is>
+          <t>REAL</t>
         </is>
       </c>
       <c r="C25" s="11" t="inlineStr">
         <is>
-          <t>NYSE:GGAL</t>
+          <t>NYSE:YPF</t>
         </is>
       </c>
       <c r="D25" s="11" t="inlineStr">
         <is>
-          <t>Banco Galicia</t>
+          <t>YPF</t>
         </is>
       </c>
       <c r="E25" s="11" t="inlineStr">
@@ -8358,7 +8358,7 @@
       </c>
       <c r="F25" s="11" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="G25" s="11" t="inlineStr">
@@ -8373,27 +8373,27 @@
       </c>
       <c r="I25" s="11" t="inlineStr">
         <is>
-          <t>27%</t>
+          <t>35%</t>
         </is>
       </c>
       <c r="J25" s="11" t="inlineStr">
         <is>
-          <t>2.33×</t>
+          <t>1.80×</t>
         </is>
       </c>
       <c r="K25" s="11" t="inlineStr">
         <is>
-          <t>2.92×</t>
+          <t>3.20×</t>
         </is>
       </c>
       <c r="L25" s="11" t="inlineStr">
         <is>
-          <t>2.00×</t>
+          <t>1.92×</t>
         </is>
       </c>
       <c r="M25" s="11" t="inlineStr">
         <is>
-          <t>3.6×</t>
+          <t>2.6×</t>
         </is>
       </c>
     </row>
@@ -8401,29 +8401,29 @@
       <c r="A26" s="12" t="n">
         <v>22</v>
       </c>
-      <c r="B26" s="16" t="inlineStr">
-        <is>
-          <t>REAL</t>
+      <c r="B26" s="13" t="inlineStr">
+        <is>
+          <t>PROXY</t>
         </is>
       </c>
       <c r="C26" s="14" t="inlineStr">
         <is>
-          <t>NYSE:LAC</t>
+          <t>LSE:ASC</t>
         </is>
       </c>
       <c r="D26" s="14" t="inlineStr">
         <is>
-          <t>Lithium Americas</t>
+          <t>ASOS</t>
         </is>
       </c>
       <c r="E26" s="14" t="inlineStr">
         <is>
-          <t>United States/Canada</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="F26" s="14" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="G26" s="14" t="inlineStr">
@@ -8433,32 +8433,32 @@
       </c>
       <c r="H26" s="14" t="inlineStr">
         <is>
-          <t>A2</t>
+          <t>A1</t>
         </is>
       </c>
       <c r="I26" s="14" t="inlineStr">
         <is>
-          <t>60%</t>
+          <t>32%</t>
         </is>
       </c>
       <c r="J26" s="14" t="inlineStr">
         <is>
-          <t>3.00×</t>
+          <t>2.16×</t>
         </is>
       </c>
       <c r="K26" s="14" t="inlineStr">
         <is>
-          <t>6.00×</t>
+          <t>2.64×</t>
         </is>
       </c>
       <c r="L26" s="14" t="inlineStr">
         <is>
-          <t>3.10×</t>
+          <t>1.84×</t>
         </is>
       </c>
       <c r="M26" s="14" t="inlineStr">
         <is>
-          <t>3.5×</t>
+          <t>2.6×</t>
         </is>
       </c>
     </row>
@@ -8466,29 +8466,29 @@
       <c r="A27" s="9" t="n">
         <v>23</v>
       </c>
-      <c r="B27" s="10" t="inlineStr">
-        <is>
-          <t>REAL</t>
+      <c r="B27" s="15" t="inlineStr">
+        <is>
+          <t>PROXY</t>
         </is>
       </c>
       <c r="C27" s="11" t="inlineStr">
         <is>
-          <t>XETR:SZG</t>
+          <t>TBRG</t>
         </is>
       </c>
       <c r="D27" s="11" t="inlineStr">
         <is>
-          <t>Salzgitter</t>
+          <t>TruBridge, Inc.</t>
         </is>
       </c>
       <c r="E27" s="11" t="inlineStr">
         <is>
-          <t>Continental Europe</t>
+          <t>United States/Canada</t>
         </is>
       </c>
       <c r="F27" s="11" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="G27" s="11" t="inlineStr">
@@ -8498,32 +8498,32 @@
       </c>
       <c r="H27" s="11" t="inlineStr">
         <is>
-          <t>A2</t>
+          <t>K3</t>
         </is>
       </c>
       <c r="I27" s="11" t="inlineStr">
         <is>
-          <t>45%</t>
+          <t>36%</t>
         </is>
       </c>
       <c r="J27" s="11" t="inlineStr">
         <is>
-          <t>2.50×</t>
+          <t>2.29×</t>
         </is>
       </c>
       <c r="K27" s="11" t="inlineStr">
         <is>
-          <t>4.50×</t>
+          <t>2.94×</t>
         </is>
       </c>
       <c r="L27" s="11" t="inlineStr">
         <is>
-          <t>2.51×</t>
+          <t>1.96×</t>
         </is>
       </c>
       <c r="M27" s="11" t="inlineStr">
         <is>
-          <t>3.4×</t>
+          <t>2.6×</t>
         </is>
       </c>
     </row>
@@ -8538,22 +8538,22 @@
       </c>
       <c r="C28" s="14" t="inlineStr">
         <is>
-          <t>NYSE:PAM</t>
+          <t>LEG</t>
         </is>
       </c>
       <c r="D28" s="14" t="inlineStr">
         <is>
-          <t>Pampa Energía</t>
+          <t>LEGGETT &amp; PLATT INC</t>
         </is>
       </c>
       <c r="E28" s="14" t="inlineStr">
         <is>
-          <t>Latin America</t>
+          <t>United States/Canada</t>
         </is>
       </c>
       <c r="F28" s="14" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="G28" s="14" t="inlineStr">
@@ -8563,32 +8563,32 @@
       </c>
       <c r="H28" s="14" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>C</t>
         </is>
       </c>
       <c r="I28" s="14" t="inlineStr">
         <is>
-          <t>28%</t>
+          <t>34%</t>
         </is>
       </c>
       <c r="J28" s="14" t="inlineStr">
         <is>
-          <t>2.29×</t>
+          <t>2.21×</t>
         </is>
       </c>
       <c r="K28" s="14" t="inlineStr">
         <is>
-          <t>2.87×</t>
+          <t>2.76×</t>
         </is>
       </c>
       <c r="L28" s="14" t="inlineStr">
         <is>
-          <t>1.96×</t>
+          <t>1.88×</t>
         </is>
       </c>
       <c r="M28" s="14" t="inlineStr">
         <is>
-          <t>3.4×</t>
+          <t>2.6×</t>
         </is>
       </c>
     </row>
@@ -8596,81 +8596,4956 @@
       <c r="A29" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="B29" s="15" t="inlineStr">
+      <c r="B29" s="10" t="inlineStr">
+        <is>
+          <t>REAL</t>
+        </is>
+      </c>
+      <c r="C29" s="11" t="inlineStr">
+        <is>
+          <t>LSE:DRX</t>
+        </is>
+      </c>
+      <c r="D29" s="11" t="inlineStr">
+        <is>
+          <t>Drax Group</t>
+        </is>
+      </c>
+      <c r="E29" s="11" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="F29" s="11" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+      <c r="G29" s="11" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H29" s="11" t="inlineStr">
+        <is>
+          <t>A1+G</t>
+        </is>
+      </c>
+      <c r="I29" s="11" t="inlineStr">
+        <is>
+          <t>55%</t>
+        </is>
+      </c>
+      <c r="J29" s="11" t="inlineStr">
+        <is>
+          <t>2.20×</t>
+        </is>
+      </c>
+      <c r="K29" s="11" t="inlineStr">
+        <is>
+          <t>4.50×</t>
+        </is>
+      </c>
+      <c r="L29" s="11" t="inlineStr">
+        <is>
+          <t>2.45×</t>
+        </is>
+      </c>
+      <c r="M29" s="11" t="inlineStr">
+        <is>
+          <t>2.6×</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="12" t="n">
+        <v>26</v>
+      </c>
+      <c r="B30" s="16" t="inlineStr">
+        <is>
+          <t>REAL</t>
+        </is>
+      </c>
+      <c r="C30" s="14" t="inlineStr">
+        <is>
+          <t>NASDAQ:UREE</t>
+        </is>
+      </c>
+      <c r="D30" s="14" t="inlineStr">
+        <is>
+          <t>USA Rare Earth</t>
+        </is>
+      </c>
+      <c r="E30" s="14" t="inlineStr">
+        <is>
+          <t>United States/Canada</t>
+        </is>
+      </c>
+      <c r="F30" s="14" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+      <c r="G30" s="14" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H30" s="14" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="I30" s="14" t="inlineStr">
+        <is>
+          <t>65%</t>
+        </is>
+      </c>
+      <c r="J30" s="14" t="inlineStr">
+        <is>
+          <t>2.50×</t>
+        </is>
+      </c>
+      <c r="K30" s="14" t="inlineStr">
+        <is>
+          <t>5.50×</t>
+        </is>
+      </c>
+      <c r="L30" s="14" t="inlineStr">
+        <is>
+          <t>2.71×</t>
+        </is>
+      </c>
+      <c r="M30" s="14" t="inlineStr">
+        <is>
+          <t>2.6×</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="9" t="n">
+        <v>27</v>
+      </c>
+      <c r="B31" s="15" t="inlineStr">
         <is>
           <t>PROXY</t>
         </is>
       </c>
-      <c r="C29" s="11" t="inlineStr">
+      <c r="C31" s="11" t="inlineStr">
+        <is>
+          <t>TSX:CFW</t>
+        </is>
+      </c>
+      <c r="D31" s="11" t="inlineStr">
+        <is>
+          <t>Calfrac Well Services</t>
+        </is>
+      </c>
+      <c r="E31" s="11" t="inlineStr">
+        <is>
+          <t>United States/Canada</t>
+        </is>
+      </c>
+      <c r="F31" s="11" t="inlineStr">
+        <is>
+          <t>0.73</t>
+        </is>
+      </c>
+      <c r="G31" s="11" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H31" s="11" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="I31" s="11" t="inlineStr">
+        <is>
+          <t>32%</t>
+        </is>
+      </c>
+      <c r="J31" s="11" t="inlineStr">
+        <is>
+          <t>2.14×</t>
+        </is>
+      </c>
+      <c r="K31" s="11" t="inlineStr">
+        <is>
+          <t>2.59×</t>
+        </is>
+      </c>
+      <c r="L31" s="11" t="inlineStr">
+        <is>
+          <t>1.81×</t>
+        </is>
+      </c>
+      <c r="M31" s="11" t="inlineStr">
+        <is>
+          <t>2.5×</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="12" t="n">
+        <v>28</v>
+      </c>
+      <c r="B32" s="13" t="inlineStr">
+        <is>
+          <t>PROXY</t>
+        </is>
+      </c>
+      <c r="C32" s="14" t="inlineStr">
+        <is>
+          <t>KRX:028260</t>
+        </is>
+      </c>
+      <c r="D32" s="14" t="inlineStr">
+        <is>
+          <t>Samsung C&amp;T</t>
+        </is>
+      </c>
+      <c r="E32" s="14" t="inlineStr">
+        <is>
+          <t>Korea</t>
+        </is>
+      </c>
+      <c r="F32" s="14" t="inlineStr">
+        <is>
+          <t>0.82</t>
+        </is>
+      </c>
+      <c r="G32" s="14" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H32" s="14" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="I32" s="14" t="inlineStr">
+        <is>
+          <t>40%</t>
+        </is>
+      </c>
+      <c r="J32" s="14" t="inlineStr">
+        <is>
+          <t>2.30×</t>
+        </is>
+      </c>
+      <c r="K32" s="14" t="inlineStr">
+        <is>
+          <t>3.00×</t>
+        </is>
+      </c>
+      <c r="L32" s="14" t="inlineStr">
+        <is>
+          <t>1.96×</t>
+        </is>
+      </c>
+      <c r="M32" s="14" t="inlineStr">
+        <is>
+          <t>2.4×</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="9" t="n">
+        <v>29</v>
+      </c>
+      <c r="B33" s="15" t="inlineStr">
+        <is>
+          <t>PROXY</t>
+        </is>
+      </c>
+      <c r="C33" s="11" t="inlineStr">
+        <is>
+          <t>LSE:AML</t>
+        </is>
+      </c>
+      <c r="D33" s="11" t="inlineStr">
+        <is>
+          <t>Aston Martin Lagonda</t>
+        </is>
+      </c>
+      <c r="E33" s="11" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="F33" s="11" t="inlineStr">
+        <is>
+          <t>0.70</t>
+        </is>
+      </c>
+      <c r="G33" s="11" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H33" s="11" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="I33" s="11" t="inlineStr">
+        <is>
+          <t>33%</t>
+        </is>
+      </c>
+      <c r="J33" s="11" t="inlineStr">
+        <is>
+          <t>2.11×</t>
+        </is>
+      </c>
+      <c r="K33" s="11" t="inlineStr">
+        <is>
+          <t>2.55×</t>
+        </is>
+      </c>
+      <c r="L33" s="11" t="inlineStr">
+        <is>
+          <t>1.79×</t>
+        </is>
+      </c>
+      <c r="M33" s="11" t="inlineStr">
+        <is>
+          <t>2.4×</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="12" t="n">
+        <v>30</v>
+      </c>
+      <c r="B34" s="13" t="inlineStr">
+        <is>
+          <t>PROXY</t>
+        </is>
+      </c>
+      <c r="C34" s="14" t="inlineStr">
+        <is>
+          <t>APTOF</t>
+        </is>
+      </c>
+      <c r="D34" s="14" t="inlineStr">
+        <is>
+          <t>Aptose Biosciences Inc.</t>
+        </is>
+      </c>
+      <c r="E34" s="14" t="inlineStr">
+        <is>
+          <t>United States/Canada</t>
+        </is>
+      </c>
+      <c r="F34" s="14" t="inlineStr">
+        <is>
+          <t>0.91</t>
+        </is>
+      </c>
+      <c r="G34" s="14" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H34" s="14" t="inlineStr">
+        <is>
+          <t>K3</t>
+        </is>
+      </c>
+      <c r="I34" s="14" t="inlineStr">
+        <is>
+          <t>38%</t>
+        </is>
+      </c>
+      <c r="J34" s="14" t="inlineStr">
+        <is>
+          <t>2.24×</t>
+        </is>
+      </c>
+      <c r="K34" s="14" t="inlineStr">
+        <is>
+          <t>2.87×</t>
+        </is>
+      </c>
+      <c r="L34" s="14" t="inlineStr">
+        <is>
+          <t>1.91×</t>
+        </is>
+      </c>
+      <c r="M34" s="14" t="inlineStr">
+        <is>
+          <t>2.4×</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="9" t="n">
+        <v>31</v>
+      </c>
+      <c r="B35" s="15" t="inlineStr">
+        <is>
+          <t>PROXY</t>
+        </is>
+      </c>
+      <c r="C35" s="11" t="inlineStr">
+        <is>
+          <t>HK:2202</t>
+        </is>
+      </c>
+      <c r="D35" s="11" t="inlineStr">
+        <is>
+          <t>Vanke</t>
+        </is>
+      </c>
+      <c r="E35" s="11" t="inlineStr">
+        <is>
+          <t>Greater China / HK</t>
+        </is>
+      </c>
+      <c r="F35" s="11" t="inlineStr">
+        <is>
+          <t>0.69</t>
+        </is>
+      </c>
+      <c r="G35" s="11" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H35" s="11" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="I35" s="11" t="inlineStr">
+        <is>
+          <t>33%</t>
+        </is>
+      </c>
+      <c r="J35" s="11" t="inlineStr">
+        <is>
+          <t>2.10×</t>
+        </is>
+      </c>
+      <c r="K35" s="11" t="inlineStr">
+        <is>
+          <t>2.54×</t>
+        </is>
+      </c>
+      <c r="L35" s="11" t="inlineStr">
+        <is>
+          <t>1.78×</t>
+        </is>
+      </c>
+      <c r="M35" s="11" t="inlineStr">
+        <is>
+          <t>2.3×</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="12" t="n">
+        <v>32</v>
+      </c>
+      <c r="B36" s="13" t="inlineStr">
+        <is>
+          <t>PROXY</t>
+        </is>
+      </c>
+      <c r="C36" s="14" t="inlineStr">
+        <is>
+          <t>LSE:VOD</t>
+        </is>
+      </c>
+      <c r="D36" s="14" t="inlineStr">
+        <is>
+          <t>Vodafone</t>
+        </is>
+      </c>
+      <c r="E36" s="14" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="F36" s="14" t="inlineStr">
+        <is>
+          <t>0.67</t>
+        </is>
+      </c>
+      <c r="G36" s="14" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H36" s="14" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="I36" s="14" t="inlineStr">
+        <is>
+          <t>34%</t>
+        </is>
+      </c>
+      <c r="J36" s="14" t="inlineStr">
+        <is>
+          <t>2.08×</t>
+        </is>
+      </c>
+      <c r="K36" s="14" t="inlineStr">
+        <is>
+          <t>2.50×</t>
+        </is>
+      </c>
+      <c r="L36" s="14" t="inlineStr">
+        <is>
+          <t>1.76×</t>
+        </is>
+      </c>
+      <c r="M36" s="14" t="inlineStr">
+        <is>
+          <t>2.3×</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="9" t="n">
+        <v>33</v>
+      </c>
+      <c r="B37" s="15" t="inlineStr">
+        <is>
+          <t>PROXY</t>
+        </is>
+      </c>
+      <c r="C37" s="11" t="inlineStr">
+        <is>
+          <t>LSE:TLW</t>
+        </is>
+      </c>
+      <c r="D37" s="11" t="inlineStr">
+        <is>
+          <t>Tullow Oil</t>
+        </is>
+      </c>
+      <c r="E37" s="11" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="F37" s="11" t="inlineStr">
+        <is>
+          <t>0.67</t>
+        </is>
+      </c>
+      <c r="G37" s="11" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H37" s="11" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="I37" s="11" t="inlineStr">
+        <is>
+          <t>34%</t>
+        </is>
+      </c>
+      <c r="J37" s="11" t="inlineStr">
+        <is>
+          <t>2.08×</t>
+        </is>
+      </c>
+      <c r="K37" s="11" t="inlineStr">
+        <is>
+          <t>2.50×</t>
+        </is>
+      </c>
+      <c r="L37" s="11" t="inlineStr">
+        <is>
+          <t>1.76×</t>
+        </is>
+      </c>
+      <c r="M37" s="11" t="inlineStr">
+        <is>
+          <t>2.3×</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="12" t="n">
+        <v>34</v>
+      </c>
+      <c r="B38" s="13" t="inlineStr">
+        <is>
+          <t>PROXY</t>
+        </is>
+      </c>
+      <c r="C38" s="14" t="inlineStr">
+        <is>
+          <t>NYSE:FFWM</t>
+        </is>
+      </c>
+      <c r="D38" s="14" t="inlineStr">
+        <is>
+          <t>First Foundation</t>
+        </is>
+      </c>
+      <c r="E38" s="14" t="inlineStr">
+        <is>
+          <t>United States/Canada</t>
+        </is>
+      </c>
+      <c r="F38" s="14" t="inlineStr">
+        <is>
+          <t>0.67</t>
+        </is>
+      </c>
+      <c r="G38" s="14" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H38" s="14" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="I38" s="14" t="inlineStr">
+        <is>
+          <t>34%</t>
+        </is>
+      </c>
+      <c r="J38" s="14" t="inlineStr">
+        <is>
+          <t>2.08×</t>
+        </is>
+      </c>
+      <c r="K38" s="14" t="inlineStr">
+        <is>
+          <t>2.50×</t>
+        </is>
+      </c>
+      <c r="L38" s="14" t="inlineStr">
+        <is>
+          <t>1.76×</t>
+        </is>
+      </c>
+      <c r="M38" s="14" t="inlineStr">
+        <is>
+          <t>2.3×</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="9" t="n">
+        <v>35</v>
+      </c>
+      <c r="B39" s="10" t="inlineStr">
+        <is>
+          <t>REAL</t>
+        </is>
+      </c>
+      <c r="C39" s="11" t="inlineStr">
+        <is>
+          <t>NYSE:HE</t>
+        </is>
+      </c>
+      <c r="D39" s="11" t="inlineStr">
+        <is>
+          <t>Hawaiian Electric Industries</t>
+        </is>
+      </c>
+      <c r="E39" s="11" t="inlineStr">
+        <is>
+          <t>United States/Canada</t>
+        </is>
+      </c>
+      <c r="F39" s="11" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+      <c r="G39" s="11" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H39" s="11" t="inlineStr">
+        <is>
+          <t>A1+G</t>
+        </is>
+      </c>
+      <c r="I39" s="11" t="inlineStr">
+        <is>
+          <t>40%</t>
+        </is>
+      </c>
+      <c r="J39" s="11" t="inlineStr">
+        <is>
+          <t>1.80×</t>
+        </is>
+      </c>
+      <c r="K39" s="11" t="inlineStr">
+        <is>
+          <t>3.00×</t>
+        </is>
+      </c>
+      <c r="L39" s="11" t="inlineStr">
+        <is>
+          <t>1.92×</t>
+        </is>
+      </c>
+      <c r="M39" s="11" t="inlineStr">
+        <is>
+          <t>2.3×</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="12" t="n">
+        <v>36</v>
+      </c>
+      <c r="B40" s="13" t="inlineStr">
+        <is>
+          <t>PROXY</t>
+        </is>
+      </c>
+      <c r="C40" s="14" t="inlineStr">
+        <is>
+          <t>TSE:8304</t>
+        </is>
+      </c>
+      <c r="D40" s="14" t="inlineStr">
+        <is>
+          <t>Aozora Bank</t>
+        </is>
+      </c>
+      <c r="E40" s="14" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="F40" s="14" t="inlineStr">
+        <is>
+          <t>0.75</t>
+        </is>
+      </c>
+      <c r="G40" s="14" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H40" s="14" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="I40" s="14" t="inlineStr">
+        <is>
+          <t>42%</t>
+        </is>
+      </c>
+      <c r="J40" s="14" t="inlineStr">
+        <is>
+          <t>2.23×</t>
+        </is>
+      </c>
+      <c r="K40" s="14" t="inlineStr">
+        <is>
+          <t>2.89×</t>
+        </is>
+      </c>
+      <c r="L40" s="14" t="inlineStr">
+        <is>
+          <t>1.90×</t>
+        </is>
+      </c>
+      <c r="M40" s="14" t="inlineStr">
+        <is>
+          <t>2.1×</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="9" t="n">
+        <v>37</v>
+      </c>
+      <c r="B41" s="10" t="inlineStr">
+        <is>
+          <t>REAL</t>
+        </is>
+      </c>
+      <c r="C41" s="11" t="inlineStr">
+        <is>
+          <t>NYSE/TSX:TMQ</t>
+        </is>
+      </c>
+      <c r="D41" s="11" t="inlineStr">
+        <is>
+          <t>Trilogy Metals</t>
+        </is>
+      </c>
+      <c r="E41" s="11" t="inlineStr">
+        <is>
+          <t>United States/Canada</t>
+        </is>
+      </c>
+      <c r="F41" s="11" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+      <c r="G41" s="11" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H41" s="11" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="I41" s="11" t="inlineStr">
+        <is>
+          <t>55%</t>
+        </is>
+      </c>
+      <c r="J41" s="11" t="inlineStr">
+        <is>
+          <t>2.20×</t>
+        </is>
+      </c>
+      <c r="K41" s="11" t="inlineStr">
+        <is>
+          <t>4.50×</t>
+        </is>
+      </c>
+      <c r="L41" s="11" t="inlineStr">
+        <is>
+          <t>2.14×</t>
+        </is>
+      </c>
+      <c r="M41" s="11" t="inlineStr">
+        <is>
+          <t>2.1×</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="12" t="n">
+        <v>38</v>
+      </c>
+      <c r="B42" s="13" t="inlineStr">
+        <is>
+          <t>PROXY</t>
+        </is>
+      </c>
+      <c r="C42" s="14" t="inlineStr">
+        <is>
+          <t>XETR:TUI1</t>
+        </is>
+      </c>
+      <c r="D42" s="14" t="inlineStr">
+        <is>
+          <t>Tui AG</t>
+        </is>
+      </c>
+      <c r="E42" s="14" t="inlineStr">
+        <is>
+          <t>Continental Europe</t>
+        </is>
+      </c>
+      <c r="F42" s="14" t="inlineStr">
+        <is>
+          <t>0.59</t>
+        </is>
+      </c>
+      <c r="G42" s="14" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H42" s="14" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="I42" s="14" t="inlineStr">
+        <is>
+          <t>36%</t>
+        </is>
+      </c>
+      <c r="J42" s="14" t="inlineStr">
+        <is>
+          <t>2.02×</t>
+        </is>
+      </c>
+      <c r="K42" s="14" t="inlineStr">
+        <is>
+          <t>2.38×</t>
+        </is>
+      </c>
+      <c r="L42" s="14" t="inlineStr">
+        <is>
+          <t>1.70×</t>
+        </is>
+      </c>
+      <c r="M42" s="14" t="inlineStr">
+        <is>
+          <t>2.0×</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="9" t="n">
+        <v>39</v>
+      </c>
+      <c r="B43" s="15" t="inlineStr">
+        <is>
+          <t>PROXY</t>
+        </is>
+      </c>
+      <c r="C43" s="11" t="inlineStr">
+        <is>
+          <t>LSE:PDL</t>
+        </is>
+      </c>
+      <c r="D43" s="11" t="inlineStr">
+        <is>
+          <t>Petra Diamonds</t>
+        </is>
+      </c>
+      <c r="E43" s="11" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="F43" s="11" t="inlineStr">
+        <is>
+          <t>0.60</t>
+        </is>
+      </c>
+      <c r="G43" s="11" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H43" s="11" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="I43" s="11" t="inlineStr">
+        <is>
+          <t>35%</t>
+        </is>
+      </c>
+      <c r="J43" s="11" t="inlineStr">
+        <is>
+          <t>2.02×</t>
+        </is>
+      </c>
+      <c r="K43" s="11" t="inlineStr">
+        <is>
+          <t>2.40×</t>
+        </is>
+      </c>
+      <c r="L43" s="11" t="inlineStr">
+        <is>
+          <t>1.70×</t>
+        </is>
+      </c>
+      <c r="M43" s="11" t="inlineStr">
+        <is>
+          <t>2.0×</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="12" t="n">
+        <v>40</v>
+      </c>
+      <c r="B44" s="16" t="inlineStr">
+        <is>
+          <t>REAL</t>
+        </is>
+      </c>
+      <c r="C44" s="14" t="inlineStr">
+        <is>
+          <t>NYSE:MP</t>
+        </is>
+      </c>
+      <c r="D44" s="14" t="inlineStr">
+        <is>
+          <t>MP Materials Corp</t>
+        </is>
+      </c>
+      <c r="E44" s="14" t="inlineStr">
+        <is>
+          <t>United States/Canada</t>
+        </is>
+      </c>
+      <c r="F44" s="14" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+      <c r="G44" s="14" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H44" s="14" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="I44" s="14" t="inlineStr">
+        <is>
+          <t>45%</t>
+        </is>
+      </c>
+      <c r="J44" s="14" t="inlineStr">
+        <is>
+          <t>1.80×</t>
+        </is>
+      </c>
+      <c r="K44" s="14" t="inlineStr">
+        <is>
+          <t>3.20×</t>
+        </is>
+      </c>
+      <c r="L44" s="14" t="inlineStr">
+        <is>
+          <t>1.90×</t>
+        </is>
+      </c>
+      <c r="M44" s="14" t="inlineStr">
+        <is>
+          <t>2.0×</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="9" t="n">
+        <v>41</v>
+      </c>
+      <c r="B45" s="15" t="inlineStr">
+        <is>
+          <t>PROXY</t>
+        </is>
+      </c>
+      <c r="C45" s="11" t="inlineStr">
+        <is>
+          <t>NYSE:AENZ</t>
+        </is>
+      </c>
+      <c r="D45" s="11" t="inlineStr">
+        <is>
+          <t>Aenza (former Graña y Montero)</t>
+        </is>
+      </c>
+      <c r="E45" s="11" t="inlineStr">
+        <is>
+          <t>Continental Europe</t>
+        </is>
+      </c>
+      <c r="F45" s="11" t="inlineStr">
+        <is>
+          <t>0.57</t>
+        </is>
+      </c>
+      <c r="G45" s="11" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H45" s="11" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="I45" s="11" t="inlineStr">
+        <is>
+          <t>36%</t>
+        </is>
+      </c>
+      <c r="J45" s="11" t="inlineStr">
+        <is>
+          <t>2.00×</t>
+        </is>
+      </c>
+      <c r="K45" s="11" t="inlineStr">
+        <is>
+          <t>2.35×</t>
+        </is>
+      </c>
+      <c r="L45" s="11" t="inlineStr">
+        <is>
+          <t>1.68×</t>
+        </is>
+      </c>
+      <c r="M45" s="11" t="inlineStr">
+        <is>
+          <t>1.9×</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="12" t="n">
+        <v>42</v>
+      </c>
+      <c r="B46" s="13" t="inlineStr">
+        <is>
+          <t>PROXY</t>
+        </is>
+      </c>
+      <c r="C46" s="14" t="inlineStr">
+        <is>
+          <t>KRX:034730</t>
+        </is>
+      </c>
+      <c r="D46" s="14" t="inlineStr">
+        <is>
+          <t>SK Inc</t>
+        </is>
+      </c>
+      <c r="E46" s="14" t="inlineStr">
+        <is>
+          <t>Korea</t>
+        </is>
+      </c>
+      <c r="F46" s="14" t="inlineStr">
+        <is>
+          <t>0.69</t>
+        </is>
+      </c>
+      <c r="G46" s="14" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H46" s="14" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="I46" s="14" t="inlineStr">
+        <is>
+          <t>44%</t>
+        </is>
+      </c>
+      <c r="J46" s="14" t="inlineStr">
+        <is>
+          <t>2.17×</t>
+        </is>
+      </c>
+      <c r="K46" s="14" t="inlineStr">
+        <is>
+          <t>2.79×</t>
+        </is>
+      </c>
+      <c r="L46" s="14" t="inlineStr">
+        <is>
+          <t>1.84×</t>
+        </is>
+      </c>
+      <c r="M46" s="14" t="inlineStr">
+        <is>
+          <t>1.9×</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="9" t="n">
+        <v>43</v>
+      </c>
+      <c r="B47" s="15" t="inlineStr">
+        <is>
+          <t>PROXY</t>
+        </is>
+      </c>
+      <c r="C47" s="11" t="inlineStr">
+        <is>
+          <t>NGX:ZENITHBANK</t>
+        </is>
+      </c>
+      <c r="D47" s="11" t="inlineStr">
+        <is>
+          <t>Zenith Bank</t>
+        </is>
+      </c>
+      <c r="E47" s="11" t="inlineStr">
+        <is>
+          <t>MEA / Frontier</t>
+        </is>
+      </c>
+      <c r="F47" s="11" t="inlineStr">
+        <is>
+          <t>0.76</t>
+        </is>
+      </c>
+      <c r="G47" s="11" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H47" s="11" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="I47" s="11" t="inlineStr">
+        <is>
+          <t>42%</t>
+        </is>
+      </c>
+      <c r="J47" s="11" t="inlineStr">
+        <is>
+          <t>2.11×</t>
+        </is>
+      </c>
+      <c r="K47" s="11" t="inlineStr">
+        <is>
+          <t>2.64×</t>
+        </is>
+      </c>
+      <c r="L47" s="11" t="inlineStr">
+        <is>
+          <t>1.78×</t>
+        </is>
+      </c>
+      <c r="M47" s="11" t="inlineStr">
+        <is>
+          <t>1.9×</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="12" t="n">
+        <v>44</v>
+      </c>
+      <c r="B48" s="16" t="inlineStr">
+        <is>
+          <t>REAL</t>
+        </is>
+      </c>
+      <c r="C48" s="14" t="inlineStr">
+        <is>
+          <t>NYSE:FLG</t>
+        </is>
+      </c>
+      <c r="D48" s="14" t="inlineStr">
+        <is>
+          <t>NYCB / Flagstar Financial</t>
+        </is>
+      </c>
+      <c r="E48" s="14" t="inlineStr">
+        <is>
+          <t>United States/Canada</t>
+        </is>
+      </c>
+      <c r="F48" s="14" t="inlineStr">
+        <is>
+          <t>0.91</t>
+        </is>
+      </c>
+      <c r="G48" s="14" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H48" s="14" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="I48" s="14" t="inlineStr">
+        <is>
+          <t>45%</t>
+        </is>
+      </c>
+      <c r="J48" s="14" t="inlineStr">
+        <is>
+          <t>1.85×</t>
+        </is>
+      </c>
+      <c r="K48" s="14" t="inlineStr">
+        <is>
+          <t>3.20×</t>
+        </is>
+      </c>
+      <c r="L48" s="14" t="inlineStr">
+        <is>
+          <t>1.86×</t>
+        </is>
+      </c>
+      <c r="M48" s="14" t="inlineStr">
+        <is>
+          <t>1.9×</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="9" t="n">
+        <v>45</v>
+      </c>
+      <c r="B49" s="15" t="inlineStr">
+        <is>
+          <t>PROXY</t>
+        </is>
+      </c>
+      <c r="C49" s="11" t="inlineStr">
+        <is>
+          <t>AEMD</t>
+        </is>
+      </c>
+      <c r="D49" s="11" t="inlineStr">
+        <is>
+          <t>AETHLON MEDICAL INC</t>
+        </is>
+      </c>
+      <c r="E49" s="11" t="inlineStr">
+        <is>
+          <t>United States/Canada</t>
+        </is>
+      </c>
+      <c r="F49" s="11" t="inlineStr">
+        <is>
+          <t>0.77</t>
+        </is>
+      </c>
+      <c r="G49" s="11" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H49" s="11" t="inlineStr">
+        <is>
+          <t>F2</t>
+        </is>
+      </c>
+      <c r="I49" s="11" t="inlineStr">
+        <is>
+          <t>42%</t>
+        </is>
+      </c>
+      <c r="J49" s="11" t="inlineStr">
+        <is>
+          <t>2.12×</t>
+        </is>
+      </c>
+      <c r="K49" s="11" t="inlineStr">
+        <is>
+          <t>2.66×</t>
+        </is>
+      </c>
+      <c r="L49" s="11" t="inlineStr">
+        <is>
+          <t>1.79×</t>
+        </is>
+      </c>
+      <c r="M49" s="11" t="inlineStr">
+        <is>
+          <t>1.9×</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="12" t="n">
+        <v>46</v>
+      </c>
+      <c r="B50" s="13" t="inlineStr">
+        <is>
+          <t>PROXY</t>
+        </is>
+      </c>
+      <c r="C50" s="14" t="inlineStr">
+        <is>
+          <t>EGX:COMI</t>
+        </is>
+      </c>
+      <c r="D50" s="14" t="inlineStr">
+        <is>
+          <t>Egypt Commercial International Bank</t>
+        </is>
+      </c>
+      <c r="E50" s="14" t="inlineStr">
+        <is>
+          <t>MEA / Frontier</t>
+        </is>
+      </c>
+      <c r="F50" s="14" t="inlineStr">
+        <is>
+          <t>0.75</t>
+        </is>
+      </c>
+      <c r="G50" s="14" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H50" s="14" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="I50" s="14" t="inlineStr">
+        <is>
+          <t>42%</t>
+        </is>
+      </c>
+      <c r="J50" s="14" t="inlineStr">
+        <is>
+          <t>2.10×</t>
+        </is>
+      </c>
+      <c r="K50" s="14" t="inlineStr">
+        <is>
+          <t>2.62×</t>
+        </is>
+      </c>
+      <c r="L50" s="14" t="inlineStr">
+        <is>
+          <t>1.77×</t>
+        </is>
+      </c>
+      <c r="M50" s="14" t="inlineStr">
+        <is>
+          <t>1.8×</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="9" t="n">
+        <v>47</v>
+      </c>
+      <c r="B51" s="15" t="inlineStr">
+        <is>
+          <t>PROXY</t>
+        </is>
+      </c>
+      <c r="C51" s="11" t="inlineStr">
+        <is>
+          <t>NGX:FIDELITYBK</t>
+        </is>
+      </c>
+      <c r="D51" s="11" t="inlineStr">
+        <is>
+          <t>Fidelity Bank</t>
+        </is>
+      </c>
+      <c r="E51" s="11" t="inlineStr">
+        <is>
+          <t>MEA / Frontier</t>
+        </is>
+      </c>
+      <c r="F51" s="11" t="inlineStr">
+        <is>
+          <t>0.73</t>
+        </is>
+      </c>
+      <c r="G51" s="11" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H51" s="11" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="I51" s="11" t="inlineStr">
+        <is>
+          <t>43%</t>
+        </is>
+      </c>
+      <c r="J51" s="11" t="inlineStr">
+        <is>
+          <t>2.08×</t>
+        </is>
+      </c>
+      <c r="K51" s="11" t="inlineStr">
+        <is>
+          <t>2.59×</t>
+        </is>
+      </c>
+      <c r="L51" s="11" t="inlineStr">
+        <is>
+          <t>1.76×</t>
+        </is>
+      </c>
+      <c r="M51" s="11" t="inlineStr">
+        <is>
+          <t>1.8×</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="12" t="n">
+        <v>48</v>
+      </c>
+      <c r="B52" s="13" t="inlineStr">
+        <is>
+          <t>PROXY</t>
+        </is>
+      </c>
+      <c r="C52" s="14" t="inlineStr">
+        <is>
+          <t>KRX:034220</t>
+        </is>
+      </c>
+      <c r="D52" s="14" t="inlineStr">
+        <is>
+          <t>LG Display</t>
+        </is>
+      </c>
+      <c r="E52" s="14" t="inlineStr">
+        <is>
+          <t>Korea</t>
+        </is>
+      </c>
+      <c r="F52" s="14" t="inlineStr">
+        <is>
+          <t>0.64</t>
+        </is>
+      </c>
+      <c r="G52" s="14" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H52" s="14" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="I52" s="14" t="inlineStr">
+        <is>
+          <t>46%</t>
+        </is>
+      </c>
+      <c r="J52" s="14" t="inlineStr">
+        <is>
+          <t>2.12×</t>
+        </is>
+      </c>
+      <c r="K52" s="14" t="inlineStr">
+        <is>
+          <t>2.71×</t>
+        </is>
+      </c>
+      <c r="L52" s="14" t="inlineStr">
+        <is>
+          <t>1.79×</t>
+        </is>
+      </c>
+      <c r="M52" s="14" t="inlineStr">
+        <is>
+          <t>1.7×</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="9" t="n">
+        <v>49</v>
+      </c>
+      <c r="B53" s="15" t="inlineStr">
+        <is>
+          <t>PROXY</t>
+        </is>
+      </c>
+      <c r="C53" s="11" t="inlineStr">
+        <is>
+          <t>EGX:TMGH</t>
+        </is>
+      </c>
+      <c r="D53" s="11" t="inlineStr">
+        <is>
+          <t>Talaat Moustafa Group</t>
+        </is>
+      </c>
+      <c r="E53" s="11" t="inlineStr">
+        <is>
+          <t>MEA / Frontier</t>
+        </is>
+      </c>
+      <c r="F53" s="11" t="inlineStr">
+        <is>
+          <t>0.72</t>
+        </is>
+      </c>
+      <c r="G53" s="11" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H53" s="11" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="I53" s="11" t="inlineStr">
+        <is>
+          <t>43%</t>
+        </is>
+      </c>
+      <c r="J53" s="11" t="inlineStr">
+        <is>
+          <t>2.07×</t>
+        </is>
+      </c>
+      <c r="K53" s="11" t="inlineStr">
+        <is>
+          <t>2.58×</t>
+        </is>
+      </c>
+      <c r="L53" s="11" t="inlineStr">
+        <is>
+          <t>1.75×</t>
+        </is>
+      </c>
+      <c r="M53" s="11" t="inlineStr">
+        <is>
+          <t>1.7×</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="12" t="n">
+        <v>50</v>
+      </c>
+      <c r="B54" s="13" t="inlineStr">
+        <is>
+          <t>PROXY</t>
+        </is>
+      </c>
+      <c r="C54" s="14" t="inlineStr">
+        <is>
+          <t>NYSE:SBSW</t>
+        </is>
+      </c>
+      <c r="D54" s="14" t="inlineStr">
+        <is>
+          <t>Sibanye-Stillwater</t>
+        </is>
+      </c>
+      <c r="E54" s="14" t="inlineStr">
+        <is>
+          <t>MEA / Frontier</t>
+        </is>
+      </c>
+      <c r="F54" s="14" t="inlineStr">
+        <is>
+          <t>0.71</t>
+        </is>
+      </c>
+      <c r="G54" s="14" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H54" s="14" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="I54" s="14" t="inlineStr">
+        <is>
+          <t>44%</t>
+        </is>
+      </c>
+      <c r="J54" s="14" t="inlineStr">
+        <is>
+          <t>2.06×</t>
+        </is>
+      </c>
+      <c r="K54" s="14" t="inlineStr">
+        <is>
+          <t>2.56×</t>
+        </is>
+      </c>
+      <c r="L54" s="14" t="inlineStr">
+        <is>
+          <t>1.74×</t>
+        </is>
+      </c>
+      <c r="M54" s="14" t="inlineStr">
+        <is>
+          <t>1.7×</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="9" t="n">
+        <v>51</v>
+      </c>
+      <c r="B55" s="15" t="inlineStr">
+        <is>
+          <t>PROXY</t>
+        </is>
+      </c>
+      <c r="C55" s="11" t="inlineStr">
+        <is>
+          <t>MEM</t>
+        </is>
+      </c>
+      <c r="D55" s="11" t="inlineStr">
+        <is>
+          <t>MEMPHASYS LIMITED.</t>
+        </is>
+      </c>
+      <c r="E55" s="11" t="inlineStr">
+        <is>
+          <t>SE Asia / Pacific</t>
+        </is>
+      </c>
+      <c r="F55" s="11" t="inlineStr">
+        <is>
+          <t>0.71</t>
+        </is>
+      </c>
+      <c r="G55" s="11" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H55" s="11" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="I55" s="11" t="inlineStr">
+        <is>
+          <t>44%</t>
+        </is>
+      </c>
+      <c r="J55" s="11" t="inlineStr">
+        <is>
+          <t>2.06×</t>
+        </is>
+      </c>
+      <c r="K55" s="11" t="inlineStr">
+        <is>
+          <t>2.56×</t>
+        </is>
+      </c>
+      <c r="L55" s="11" t="inlineStr">
+        <is>
+          <t>1.74×</t>
+        </is>
+      </c>
+      <c r="M55" s="11" t="inlineStr">
+        <is>
+          <t>1.7×</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="12" t="n">
+        <v>52</v>
+      </c>
+      <c r="B56" s="13" t="inlineStr">
+        <is>
+          <t>PROXY</t>
+        </is>
+      </c>
+      <c r="C56" s="14" t="inlineStr">
+        <is>
+          <t>CIK:0001348911</t>
+        </is>
+      </c>
+      <c r="D56" s="14" t="inlineStr">
+        <is>
+          <t>KalVista Pharmaceuticals, Inc.</t>
+        </is>
+      </c>
+      <c r="E56" s="14" t="inlineStr">
+        <is>
+          <t>United States/Canada</t>
+        </is>
+      </c>
+      <c r="F56" s="14" t="inlineStr">
+        <is>
+          <t>0.71</t>
+        </is>
+      </c>
+      <c r="G56" s="14" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H56" s="14" t="inlineStr">
+        <is>
+          <t>K3</t>
+        </is>
+      </c>
+      <c r="I56" s="14" t="inlineStr">
+        <is>
+          <t>44%</t>
+        </is>
+      </c>
+      <c r="J56" s="14" t="inlineStr">
+        <is>
+          <t>2.06×</t>
+        </is>
+      </c>
+      <c r="K56" s="14" t="inlineStr">
+        <is>
+          <t>2.56×</t>
+        </is>
+      </c>
+      <c r="L56" s="14" t="inlineStr">
+        <is>
+          <t>1.74×</t>
+        </is>
+      </c>
+      <c r="M56" s="14" t="inlineStr">
+        <is>
+          <t>1.7×</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="9" t="n">
+        <v>53</v>
+      </c>
+      <c r="B57" s="15" t="inlineStr">
+        <is>
+          <t>PROXY</t>
+        </is>
+      </c>
+      <c r="C57" s="11" t="inlineStr">
+        <is>
+          <t>CIK:0001909770</t>
+        </is>
+      </c>
+      <c r="D57" s="11" t="inlineStr">
+        <is>
+          <t>KHEOBA CORP.</t>
+        </is>
+      </c>
+      <c r="E57" s="11" t="inlineStr">
+        <is>
+          <t>United States/Canada</t>
+        </is>
+      </c>
+      <c r="F57" s="11" t="inlineStr">
+        <is>
+          <t>0.71</t>
+        </is>
+      </c>
+      <c r="G57" s="11" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H57" s="11" t="inlineStr">
+        <is>
+          <t>K3</t>
+        </is>
+      </c>
+      <c r="I57" s="11" t="inlineStr">
+        <is>
+          <t>44%</t>
+        </is>
+      </c>
+      <c r="J57" s="11" t="inlineStr">
+        <is>
+          <t>2.06×</t>
+        </is>
+      </c>
+      <c r="K57" s="11" t="inlineStr">
+        <is>
+          <t>2.56×</t>
+        </is>
+      </c>
+      <c r="L57" s="11" t="inlineStr">
+        <is>
+          <t>1.74×</t>
+        </is>
+      </c>
+      <c r="M57" s="11" t="inlineStr">
+        <is>
+          <t>1.7×</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="12" t="n">
+        <v>54</v>
+      </c>
+      <c r="B58" s="13" t="inlineStr">
+        <is>
+          <t>PROXY</t>
+        </is>
+      </c>
+      <c r="C58" s="14" t="inlineStr">
+        <is>
+          <t>CIK:0001489096</t>
+        </is>
+      </c>
+      <c r="D58" s="14" t="inlineStr">
+        <is>
+          <t>Thermon Group Holdings, Inc.</t>
+        </is>
+      </c>
+      <c r="E58" s="14" t="inlineStr">
+        <is>
+          <t>United States/Canada</t>
+        </is>
+      </c>
+      <c r="F58" s="14" t="inlineStr">
+        <is>
+          <t>0.71</t>
+        </is>
+      </c>
+      <c r="G58" s="14" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H58" s="14" t="inlineStr">
+        <is>
+          <t>K3</t>
+        </is>
+      </c>
+      <c r="I58" s="14" t="inlineStr">
+        <is>
+          <t>44%</t>
+        </is>
+      </c>
+      <c r="J58" s="14" t="inlineStr">
+        <is>
+          <t>2.06×</t>
+        </is>
+      </c>
+      <c r="K58" s="14" t="inlineStr">
+        <is>
+          <t>2.56×</t>
+        </is>
+      </c>
+      <c r="L58" s="14" t="inlineStr">
+        <is>
+          <t>1.74×</t>
+        </is>
+      </c>
+      <c r="M58" s="14" t="inlineStr">
+        <is>
+          <t>1.7×</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="9" t="n">
+        <v>55</v>
+      </c>
+      <c r="B59" s="15" t="inlineStr">
+        <is>
+          <t>PROXY</t>
+        </is>
+      </c>
+      <c r="C59" s="11" t="inlineStr">
+        <is>
+          <t>WYTC</t>
+        </is>
+      </c>
+      <c r="D59" s="11" t="inlineStr">
+        <is>
+          <t>WYTEC INTERNATIONAL INC</t>
+        </is>
+      </c>
+      <c r="E59" s="11" t="inlineStr">
+        <is>
+          <t>United States/Canada</t>
+        </is>
+      </c>
+      <c r="F59" s="11" t="inlineStr">
+        <is>
+          <t>0.71</t>
+        </is>
+      </c>
+      <c r="G59" s="11" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H59" s="11" t="inlineStr">
+        <is>
+          <t>K3</t>
+        </is>
+      </c>
+      <c r="I59" s="11" t="inlineStr">
+        <is>
+          <t>44%</t>
+        </is>
+      </c>
+      <c r="J59" s="11" t="inlineStr">
+        <is>
+          <t>2.06×</t>
+        </is>
+      </c>
+      <c r="K59" s="11" t="inlineStr">
+        <is>
+          <t>2.56×</t>
+        </is>
+      </c>
+      <c r="L59" s="11" t="inlineStr">
+        <is>
+          <t>1.74×</t>
+        </is>
+      </c>
+      <c r="M59" s="11" t="inlineStr">
+        <is>
+          <t>1.7×</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="12" t="n">
+        <v>56</v>
+      </c>
+      <c r="B60" s="13" t="inlineStr">
+        <is>
+          <t>PROXY</t>
+        </is>
+      </c>
+      <c r="C60" s="14" t="inlineStr">
+        <is>
+          <t>CIK:0001408100</t>
+        </is>
+      </c>
+      <c r="D60" s="14" t="inlineStr">
+        <is>
+          <t>Kennedy-Wilson Holdings, Inc.</t>
+        </is>
+      </c>
+      <c r="E60" s="14" t="inlineStr">
+        <is>
+          <t>United States/Canada</t>
+        </is>
+      </c>
+      <c r="F60" s="14" t="inlineStr">
+        <is>
+          <t>0.71</t>
+        </is>
+      </c>
+      <c r="G60" s="14" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H60" s="14" t="inlineStr">
+        <is>
+          <t>K3</t>
+        </is>
+      </c>
+      <c r="I60" s="14" t="inlineStr">
+        <is>
+          <t>44%</t>
+        </is>
+      </c>
+      <c r="J60" s="14" t="inlineStr">
+        <is>
+          <t>2.06×</t>
+        </is>
+      </c>
+      <c r="K60" s="14" t="inlineStr">
+        <is>
+          <t>2.56×</t>
+        </is>
+      </c>
+      <c r="L60" s="14" t="inlineStr">
+        <is>
+          <t>1.74×</t>
+        </is>
+      </c>
+      <c r="M60" s="14" t="inlineStr">
+        <is>
+          <t>1.7×</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="9" t="n">
+        <v>57</v>
+      </c>
+      <c r="B61" s="15" t="inlineStr">
+        <is>
+          <t>PROXY</t>
+        </is>
+      </c>
+      <c r="C61" s="11" t="inlineStr">
+        <is>
+          <t>CIK:0002073537</t>
+        </is>
+      </c>
+      <c r="D61" s="11" t="inlineStr">
+        <is>
+          <t>PIMCO Asset-Based Lending Co LLC</t>
+        </is>
+      </c>
+      <c r="E61" s="11" t="inlineStr">
+        <is>
+          <t>United States/Canada</t>
+        </is>
+      </c>
+      <c r="F61" s="11" t="inlineStr">
+        <is>
+          <t>0.71</t>
+        </is>
+      </c>
+      <c r="G61" s="11" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H61" s="11" t="inlineStr">
+        <is>
+          <t>K3</t>
+        </is>
+      </c>
+      <c r="I61" s="11" t="inlineStr">
+        <is>
+          <t>44%</t>
+        </is>
+      </c>
+      <c r="J61" s="11" t="inlineStr">
+        <is>
+          <t>2.06×</t>
+        </is>
+      </c>
+      <c r="K61" s="11" t="inlineStr">
+        <is>
+          <t>2.56×</t>
+        </is>
+      </c>
+      <c r="L61" s="11" t="inlineStr">
+        <is>
+          <t>1.74×</t>
+        </is>
+      </c>
+      <c r="M61" s="11" t="inlineStr">
+        <is>
+          <t>1.7×</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="12" t="n">
+        <v>58</v>
+      </c>
+      <c r="B62" s="13" t="inlineStr">
+        <is>
+          <t>PROXY</t>
+        </is>
+      </c>
+      <c r="C62" s="14" t="inlineStr">
+        <is>
+          <t>VIASP</t>
+        </is>
+      </c>
+      <c r="D62" s="14" t="inlineStr">
+        <is>
+          <t>Via Renewables, Inc.</t>
+        </is>
+      </c>
+      <c r="E62" s="14" t="inlineStr">
+        <is>
+          <t>United States/Canada</t>
+        </is>
+      </c>
+      <c r="F62" s="14" t="inlineStr">
+        <is>
+          <t>0.71</t>
+        </is>
+      </c>
+      <c r="G62" s="14" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H62" s="14" t="inlineStr">
+        <is>
+          <t>K3</t>
+        </is>
+      </c>
+      <c r="I62" s="14" t="inlineStr">
+        <is>
+          <t>44%</t>
+        </is>
+      </c>
+      <c r="J62" s="14" t="inlineStr">
+        <is>
+          <t>2.06×</t>
+        </is>
+      </c>
+      <c r="K62" s="14" t="inlineStr">
+        <is>
+          <t>2.56×</t>
+        </is>
+      </c>
+      <c r="L62" s="14" t="inlineStr">
+        <is>
+          <t>1.74×</t>
+        </is>
+      </c>
+      <c r="M62" s="14" t="inlineStr">
+        <is>
+          <t>1.7×</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="9" t="n">
+        <v>59</v>
+      </c>
+      <c r="B63" s="15" t="inlineStr">
+        <is>
+          <t>PROXY</t>
+        </is>
+      </c>
+      <c r="C63" s="11" t="inlineStr">
+        <is>
+          <t>CIK:0001117171</t>
+        </is>
+      </c>
+      <c r="D63" s="11" t="inlineStr">
+        <is>
+          <t>CBAK Energy Technology, Inc.</t>
+        </is>
+      </c>
+      <c r="E63" s="11" t="inlineStr">
+        <is>
+          <t>United States/Canada</t>
+        </is>
+      </c>
+      <c r="F63" s="11" t="inlineStr">
+        <is>
+          <t>0.71</t>
+        </is>
+      </c>
+      <c r="G63" s="11" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H63" s="11" t="inlineStr">
+        <is>
+          <t>K3</t>
+        </is>
+      </c>
+      <c r="I63" s="11" t="inlineStr">
+        <is>
+          <t>44%</t>
+        </is>
+      </c>
+      <c r="J63" s="11" t="inlineStr">
+        <is>
+          <t>2.06×</t>
+        </is>
+      </c>
+      <c r="K63" s="11" t="inlineStr">
+        <is>
+          <t>2.56×</t>
+        </is>
+      </c>
+      <c r="L63" s="11" t="inlineStr">
+        <is>
+          <t>1.74×</t>
+        </is>
+      </c>
+      <c r="M63" s="11" t="inlineStr">
+        <is>
+          <t>1.7×</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="12" t="n">
+        <v>60</v>
+      </c>
+      <c r="B64" s="13" t="inlineStr">
+        <is>
+          <t>PROXY</t>
+        </is>
+      </c>
+      <c r="C64" s="14" t="inlineStr">
+        <is>
+          <t>CIK:0001500305</t>
+        </is>
+      </c>
+      <c r="D64" s="14" t="inlineStr">
+        <is>
+          <t>Sustainable Projects Group Inc.</t>
+        </is>
+      </c>
+      <c r="E64" s="14" t="inlineStr">
+        <is>
+          <t>United States/Canada</t>
+        </is>
+      </c>
+      <c r="F64" s="14" t="inlineStr">
+        <is>
+          <t>0.71</t>
+        </is>
+      </c>
+      <c r="G64" s="14" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H64" s="14" t="inlineStr">
+        <is>
+          <t>K3</t>
+        </is>
+      </c>
+      <c r="I64" s="14" t="inlineStr">
+        <is>
+          <t>44%</t>
+        </is>
+      </c>
+      <c r="J64" s="14" t="inlineStr">
+        <is>
+          <t>2.06×</t>
+        </is>
+      </c>
+      <c r="K64" s="14" t="inlineStr">
+        <is>
+          <t>2.56×</t>
+        </is>
+      </c>
+      <c r="L64" s="14" t="inlineStr">
+        <is>
+          <t>1.74×</t>
+        </is>
+      </c>
+      <c r="M64" s="14" t="inlineStr">
+        <is>
+          <t>1.7×</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="9" t="n">
+        <v>61</v>
+      </c>
+      <c r="B65" s="15" t="inlineStr">
+        <is>
+          <t>PROXY</t>
+        </is>
+      </c>
+      <c r="C65" s="11" t="inlineStr">
+        <is>
+          <t>CIK:0001127703</t>
+        </is>
+      </c>
+      <c r="D65" s="11" t="inlineStr">
+        <is>
+          <t>PROASSURANCE CORP</t>
+        </is>
+      </c>
+      <c r="E65" s="11" t="inlineStr">
+        <is>
+          <t>United States/Canada</t>
+        </is>
+      </c>
+      <c r="F65" s="11" t="inlineStr">
+        <is>
+          <t>0.71</t>
+        </is>
+      </c>
+      <c r="G65" s="11" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H65" s="11" t="inlineStr">
+        <is>
+          <t>K3</t>
+        </is>
+      </c>
+      <c r="I65" s="11" t="inlineStr">
+        <is>
+          <t>44%</t>
+        </is>
+      </c>
+      <c r="J65" s="11" t="inlineStr">
+        <is>
+          <t>2.06×</t>
+        </is>
+      </c>
+      <c r="K65" s="11" t="inlineStr">
+        <is>
+          <t>2.56×</t>
+        </is>
+      </c>
+      <c r="L65" s="11" t="inlineStr">
+        <is>
+          <t>1.74×</t>
+        </is>
+      </c>
+      <c r="M65" s="11" t="inlineStr">
+        <is>
+          <t>1.7×</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="12" t="n">
+        <v>62</v>
+      </c>
+      <c r="B66" s="13" t="inlineStr">
+        <is>
+          <t>PROXY</t>
+        </is>
+      </c>
+      <c r="C66" s="14" t="inlineStr">
+        <is>
+          <t>CIK:0001900520</t>
+        </is>
+      </c>
+      <c r="D66" s="14" t="inlineStr">
+        <is>
+          <t>Lomond Therapeutics Holdings, Inc.</t>
+        </is>
+      </c>
+      <c r="E66" s="14" t="inlineStr">
+        <is>
+          <t>United States/Canada</t>
+        </is>
+      </c>
+      <c r="F66" s="14" t="inlineStr">
+        <is>
+          <t>0.71</t>
+        </is>
+      </c>
+      <c r="G66" s="14" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H66" s="14" t="inlineStr">
+        <is>
+          <t>K3</t>
+        </is>
+      </c>
+      <c r="I66" s="14" t="inlineStr">
+        <is>
+          <t>44%</t>
+        </is>
+      </c>
+      <c r="J66" s="14" t="inlineStr">
+        <is>
+          <t>2.06×</t>
+        </is>
+      </c>
+      <c r="K66" s="14" t="inlineStr">
+        <is>
+          <t>2.56×</t>
+        </is>
+      </c>
+      <c r="L66" s="14" t="inlineStr">
+        <is>
+          <t>1.74×</t>
+        </is>
+      </c>
+      <c r="M66" s="14" t="inlineStr">
+        <is>
+          <t>1.7×</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="9" t="n">
+        <v>63</v>
+      </c>
+      <c r="B67" s="15" t="inlineStr">
+        <is>
+          <t>PROXY</t>
+        </is>
+      </c>
+      <c r="C67" s="11" t="inlineStr">
+        <is>
+          <t>HK:1918</t>
+        </is>
+      </c>
+      <c r="D67" s="11" t="inlineStr">
+        <is>
+          <t>Sunac China</t>
+        </is>
+      </c>
+      <c r="E67" s="11" t="inlineStr">
+        <is>
+          <t>Greater China / HK</t>
+        </is>
+      </c>
+      <c r="F67" s="11" t="inlineStr">
+        <is>
+          <t>0.55</t>
+        </is>
+      </c>
+      <c r="G67" s="11" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H67" s="11" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="I67" s="11" t="inlineStr">
+        <is>
+          <t>48%</t>
+        </is>
+      </c>
+      <c r="J67" s="11" t="inlineStr">
+        <is>
+          <t>2.09×</t>
+        </is>
+      </c>
+      <c r="K67" s="11" t="inlineStr">
+        <is>
+          <t>2.67×</t>
+        </is>
+      </c>
+      <c r="L67" s="11" t="inlineStr">
+        <is>
+          <t>1.77×</t>
+        </is>
+      </c>
+      <c r="M67" s="11" t="inlineStr">
+        <is>
+          <t>1.6×</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="12" t="n">
+        <v>64</v>
+      </c>
+      <c r="B68" s="13" t="inlineStr">
+        <is>
+          <t>PROXY</t>
+        </is>
+      </c>
+      <c r="C68" s="14" t="inlineStr">
+        <is>
+          <t>8074</t>
+        </is>
+      </c>
+      <c r="D68" s="14" t="inlineStr">
+        <is>
+          <t>ＹＵＡＳＡ</t>
+        </is>
+      </c>
+      <c r="E68" s="14" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="F68" s="14" t="inlineStr">
+        <is>
+          <t>0.60</t>
+        </is>
+      </c>
+      <c r="G68" s="14" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H68" s="14" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="I68" s="14" t="inlineStr">
+        <is>
+          <t>47%</t>
+        </is>
+      </c>
+      <c r="J68" s="14" t="inlineStr">
+        <is>
+          <t>2.08×</t>
+        </is>
+      </c>
+      <c r="K68" s="14" t="inlineStr">
+        <is>
+          <t>2.64×</t>
+        </is>
+      </c>
+      <c r="L68" s="14" t="inlineStr">
+        <is>
+          <t>1.76×</t>
+        </is>
+      </c>
+      <c r="M68" s="14" t="inlineStr">
+        <is>
+          <t>1.6×</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="9" t="n">
+        <v>65</v>
+      </c>
+      <c r="B69" s="15" t="inlineStr">
+        <is>
+          <t>PROXY</t>
+        </is>
+      </c>
+      <c r="C69" s="11" t="inlineStr">
+        <is>
+          <t>2198</t>
+        </is>
+      </c>
+      <c r="D69" s="11" t="inlineStr">
+        <is>
+          <t>アイ・ケイ・ケイＨＤ</t>
+        </is>
+      </c>
+      <c r="E69" s="11" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="F69" s="11" t="inlineStr">
+        <is>
+          <t>0.60</t>
+        </is>
+      </c>
+      <c r="G69" s="11" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H69" s="11" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="I69" s="11" t="inlineStr">
+        <is>
+          <t>47%</t>
+        </is>
+      </c>
+      <c r="J69" s="11" t="inlineStr">
+        <is>
+          <t>2.08×</t>
+        </is>
+      </c>
+      <c r="K69" s="11" t="inlineStr">
+        <is>
+          <t>2.64×</t>
+        </is>
+      </c>
+      <c r="L69" s="11" t="inlineStr">
+        <is>
+          <t>1.76×</t>
+        </is>
+      </c>
+      <c r="M69" s="11" t="inlineStr">
+        <is>
+          <t>1.6×</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="12" t="n">
+        <v>66</v>
+      </c>
+      <c r="B70" s="13" t="inlineStr">
+        <is>
+          <t>PROXY</t>
+        </is>
+      </c>
+      <c r="C70" s="14" t="inlineStr">
+        <is>
+          <t>3454</t>
+        </is>
+      </c>
+      <c r="D70" s="14" t="inlineStr">
+        <is>
+          <t>ファーストブラザーズ</t>
+        </is>
+      </c>
+      <c r="E70" s="14" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="F70" s="14" t="inlineStr">
+        <is>
+          <t>0.60</t>
+        </is>
+      </c>
+      <c r="G70" s="14" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H70" s="14" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="I70" s="14" t="inlineStr">
+        <is>
+          <t>47%</t>
+        </is>
+      </c>
+      <c r="J70" s="14" t="inlineStr">
+        <is>
+          <t>2.08×</t>
+        </is>
+      </c>
+      <c r="K70" s="14" t="inlineStr">
+        <is>
+          <t>2.64×</t>
+        </is>
+      </c>
+      <c r="L70" s="14" t="inlineStr">
+        <is>
+          <t>1.76×</t>
+        </is>
+      </c>
+      <c r="M70" s="14" t="inlineStr">
+        <is>
+          <t>1.6×</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="9" t="n">
+        <v>67</v>
+      </c>
+      <c r="B71" s="15" t="inlineStr">
+        <is>
+          <t>PROXY</t>
+        </is>
+      </c>
+      <c r="C71" s="11" t="inlineStr">
+        <is>
+          <t>4641</t>
+        </is>
+      </c>
+      <c r="D71" s="11" t="inlineStr">
+        <is>
+          <t>アルプス技</t>
+        </is>
+      </c>
+      <c r="E71" s="11" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="F71" s="11" t="inlineStr">
+        <is>
+          <t>0.60</t>
+        </is>
+      </c>
+      <c r="G71" s="11" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H71" s="11" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="I71" s="11" t="inlineStr">
+        <is>
+          <t>47%</t>
+        </is>
+      </c>
+      <c r="J71" s="11" t="inlineStr">
+        <is>
+          <t>2.08×</t>
+        </is>
+      </c>
+      <c r="K71" s="11" t="inlineStr">
+        <is>
+          <t>2.64×</t>
+        </is>
+      </c>
+      <c r="L71" s="11" t="inlineStr">
+        <is>
+          <t>1.76×</t>
+        </is>
+      </c>
+      <c r="M71" s="11" t="inlineStr">
+        <is>
+          <t>1.6×</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="12" t="n">
+        <v>68</v>
+      </c>
+      <c r="B72" s="13" t="inlineStr">
+        <is>
+          <t>PROXY</t>
+        </is>
+      </c>
+      <c r="C72" s="14" t="inlineStr">
+        <is>
+          <t>4170</t>
+        </is>
+      </c>
+      <c r="D72" s="14" t="inlineStr">
+        <is>
+          <t>Ｇ－ＫａｉｚｅｎＰＦ</t>
+        </is>
+      </c>
+      <c r="E72" s="14" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="F72" s="14" t="inlineStr">
+        <is>
+          <t>0.60</t>
+        </is>
+      </c>
+      <c r="G72" s="14" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H72" s="14" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="I72" s="14" t="inlineStr">
+        <is>
+          <t>47%</t>
+        </is>
+      </c>
+      <c r="J72" s="14" t="inlineStr">
+        <is>
+          <t>2.08×</t>
+        </is>
+      </c>
+      <c r="K72" s="14" t="inlineStr">
+        <is>
+          <t>2.64×</t>
+        </is>
+      </c>
+      <c r="L72" s="14" t="inlineStr">
+        <is>
+          <t>1.76×</t>
+        </is>
+      </c>
+      <c r="M72" s="14" t="inlineStr">
+        <is>
+          <t>1.6×</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="9" t="n">
+        <v>69</v>
+      </c>
+      <c r="B73" s="15" t="inlineStr">
+        <is>
+          <t>PROXY</t>
+        </is>
+      </c>
+      <c r="C73" s="11" t="inlineStr">
+        <is>
+          <t>TSE:6753</t>
+        </is>
+      </c>
+      <c r="D73" s="11" t="inlineStr">
+        <is>
+          <t>Sharp</t>
+        </is>
+      </c>
+      <c r="E73" s="11" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="F73" s="11" t="inlineStr">
+        <is>
+          <t>0.59</t>
+        </is>
+      </c>
+      <c r="G73" s="11" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H73" s="11" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="I73" s="11" t="inlineStr">
+        <is>
+          <t>47%</t>
+        </is>
+      </c>
+      <c r="J73" s="11" t="inlineStr">
+        <is>
+          <t>2.08×</t>
+        </is>
+      </c>
+      <c r="K73" s="11" t="inlineStr">
+        <is>
+          <t>2.62×</t>
+        </is>
+      </c>
+      <c r="L73" s="11" t="inlineStr">
+        <is>
+          <t>1.75×</t>
+        </is>
+      </c>
+      <c r="M73" s="11" t="inlineStr">
+        <is>
+          <t>1.6×</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="12" t="n">
+        <v>70</v>
+      </c>
+      <c r="B74" s="13" t="inlineStr">
+        <is>
+          <t>PROXY</t>
+        </is>
+      </c>
+      <c r="C74" s="14" t="inlineStr">
         <is>
           <t>3544</t>
         </is>
       </c>
-      <c r="D29" s="11" t="inlineStr">
+      <c r="D74" s="14" t="inlineStr">
         <is>
           <t>サツドラＨＤ</t>
         </is>
       </c>
-      <c r="E29" s="11" t="inlineStr">
+      <c r="E74" s="14" t="inlineStr">
         <is>
           <t>Japan</t>
         </is>
       </c>
-      <c r="F29" s="11" t="inlineStr">
-        <is>
-          <t>0.87</t>
-        </is>
-      </c>
-      <c r="G29" s="11" t="inlineStr">
+      <c r="F74" s="14" t="inlineStr">
+        <is>
+          <t>0.56</t>
+        </is>
+      </c>
+      <c r="G74" s="14" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="H29" s="11" t="inlineStr">
-        <is>
-          <t>A2+C</t>
-        </is>
-      </c>
-      <c r="I29" s="11" t="inlineStr">
-        <is>
-          <t>29%</t>
-        </is>
-      </c>
-      <c r="J29" s="11" t="inlineStr">
-        <is>
-          <t>2.26×</t>
-        </is>
-      </c>
-      <c r="K29" s="11" t="inlineStr">
-        <is>
-          <t>2.80×</t>
-        </is>
-      </c>
-      <c r="L29" s="11" t="inlineStr">
-        <is>
-          <t>1.93×</t>
-        </is>
-      </c>
-      <c r="M29" s="11" t="inlineStr">
-        <is>
-          <t>3.2×</t>
-        </is>
-      </c>
-    </row>
-    <row r="30"/>
-    <row r="31" ht="60" customHeight="1">
-      <c r="A31" s="7" t="inlineStr">
-        <is>
-          <t>Reward/Risk = (EV× − 1) ÷ Bear loss.  Universe-screener output ranks 697 named candidates on archetype, vintage, status, size, region. Investable filter drops PASS_FALSE_FRIEND / ACQUIRED / ARC_DONE / REPEAT_RX and non-equity placeholder tickers ((state), (private), (delisted)). PROXY waterfall: bear_loss = max(0.10, 0.65 − 0.30·score), tilted ×0.75 for A1/A2 (sovereign-anchored floor). bull = 1.50 + 1.50·score, tilted ×1.10 for H, ×1.15 for F. Hand-built YAMLs override the proxy with bottom-up numbers.</t>
+      <c r="H74" s="14" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="I74" s="14" t="inlineStr">
+        <is>
+          <t>41%</t>
+        </is>
+      </c>
+      <c r="J74" s="14" t="inlineStr">
+        <is>
+          <t>1.97×</t>
+        </is>
+      </c>
+      <c r="K74" s="14" t="inlineStr">
+        <is>
+          <t>2.34×</t>
+        </is>
+      </c>
+      <c r="L74" s="14" t="inlineStr">
+        <is>
+          <t>1.65×</t>
+        </is>
+      </c>
+      <c r="M74" s="14" t="inlineStr">
+        <is>
+          <t>1.6×</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="9" t="n">
+        <v>71</v>
+      </c>
+      <c r="B75" s="15" t="inlineStr">
+        <is>
+          <t>PROXY</t>
+        </is>
+      </c>
+      <c r="C75" s="11" t="inlineStr">
+        <is>
+          <t>6897</t>
+        </is>
+      </c>
+      <c r="D75" s="11" t="inlineStr">
+        <is>
+          <t>ツインバード</t>
+        </is>
+      </c>
+      <c r="E75" s="11" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="F75" s="11" t="inlineStr">
+        <is>
+          <t>0.56</t>
+        </is>
+      </c>
+      <c r="G75" s="11" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H75" s="11" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="I75" s="11" t="inlineStr">
+        <is>
+          <t>41%</t>
+        </is>
+      </c>
+      <c r="J75" s="11" t="inlineStr">
+        <is>
+          <t>1.97×</t>
+        </is>
+      </c>
+      <c r="K75" s="11" t="inlineStr">
+        <is>
+          <t>2.34×</t>
+        </is>
+      </c>
+      <c r="L75" s="11" t="inlineStr">
+        <is>
+          <t>1.65×</t>
+        </is>
+      </c>
+      <c r="M75" s="11" t="inlineStr">
+        <is>
+          <t>1.6×</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="12" t="n">
+        <v>72</v>
+      </c>
+      <c r="B76" s="13" t="inlineStr">
+        <is>
+          <t>PROXY</t>
+        </is>
+      </c>
+      <c r="C76" s="14" t="inlineStr">
+        <is>
+          <t>4951</t>
+        </is>
+      </c>
+      <c r="D76" s="14" t="inlineStr">
+        <is>
+          <t>エステー</t>
+        </is>
+      </c>
+      <c r="E76" s="14" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="F76" s="14" t="inlineStr">
+        <is>
+          <t>0.56</t>
+        </is>
+      </c>
+      <c r="G76" s="14" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H76" s="14" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="I76" s="14" t="inlineStr">
+        <is>
+          <t>41%</t>
+        </is>
+      </c>
+      <c r="J76" s="14" t="inlineStr">
+        <is>
+          <t>1.97×</t>
+        </is>
+      </c>
+      <c r="K76" s="14" t="inlineStr">
+        <is>
+          <t>2.34×</t>
+        </is>
+      </c>
+      <c r="L76" s="14" t="inlineStr">
+        <is>
+          <t>1.65×</t>
+        </is>
+      </c>
+      <c r="M76" s="14" t="inlineStr">
+        <is>
+          <t>1.6×</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="9" t="n">
+        <v>73</v>
+      </c>
+      <c r="B77" s="15" t="inlineStr">
+        <is>
+          <t>PROXY</t>
+        </is>
+      </c>
+      <c r="C77" s="11" t="inlineStr">
+        <is>
+          <t>3659</t>
+        </is>
+      </c>
+      <c r="D77" s="11" t="inlineStr">
+        <is>
+          <t>ネクソン</t>
+        </is>
+      </c>
+      <c r="E77" s="11" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="F77" s="11" t="inlineStr">
+        <is>
+          <t>0.56</t>
+        </is>
+      </c>
+      <c r="G77" s="11" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H77" s="11" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="I77" s="11" t="inlineStr">
+        <is>
+          <t>41%</t>
+        </is>
+      </c>
+      <c r="J77" s="11" t="inlineStr">
+        <is>
+          <t>1.97×</t>
+        </is>
+      </c>
+      <c r="K77" s="11" t="inlineStr">
+        <is>
+          <t>2.34×</t>
+        </is>
+      </c>
+      <c r="L77" s="11" t="inlineStr">
+        <is>
+          <t>1.65×</t>
+        </is>
+      </c>
+      <c r="M77" s="11" t="inlineStr">
+        <is>
+          <t>1.6×</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="12" t="n">
+        <v>74</v>
+      </c>
+      <c r="B78" s="13" t="inlineStr">
+        <is>
+          <t>PROXY</t>
+        </is>
+      </c>
+      <c r="C78" s="14" t="inlineStr">
+        <is>
+          <t>B3:LIGT3</t>
+        </is>
+      </c>
+      <c r="D78" s="14" t="inlineStr">
+        <is>
+          <t>Light SA</t>
+        </is>
+      </c>
+      <c r="E78" s="14" t="inlineStr">
+        <is>
+          <t>Latin America</t>
+        </is>
+      </c>
+      <c r="F78" s="14" t="inlineStr">
+        <is>
+          <t>0.58</t>
+        </is>
+      </c>
+      <c r="G78" s="14" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H78" s="14" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="I78" s="14" t="inlineStr">
+        <is>
+          <t>40%</t>
+        </is>
+      </c>
+      <c r="J78" s="14" t="inlineStr">
+        <is>
+          <t>1.98×</t>
+        </is>
+      </c>
+      <c r="K78" s="14" t="inlineStr">
+        <is>
+          <t>2.37×</t>
+        </is>
+      </c>
+      <c r="L78" s="14" t="inlineStr">
+        <is>
+          <t>1.66×</t>
+        </is>
+      </c>
+      <c r="M78" s="14" t="inlineStr">
+        <is>
+          <t>1.6×</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="9" t="n">
+        <v>75</v>
+      </c>
+      <c r="B79" s="15" t="inlineStr">
+        <is>
+          <t>PROXY</t>
+        </is>
+      </c>
+      <c r="C79" s="11" t="inlineStr">
+        <is>
+          <t>NGX:ACCESSCORP</t>
+        </is>
+      </c>
+      <c r="D79" s="11" t="inlineStr">
+        <is>
+          <t>Access Holdings</t>
+        </is>
+      </c>
+      <c r="E79" s="11" t="inlineStr">
+        <is>
+          <t>MEA / Frontier</t>
+        </is>
+      </c>
+      <c r="F79" s="11" t="inlineStr">
+        <is>
+          <t>0.67</t>
+        </is>
+      </c>
+      <c r="G79" s="11" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H79" s="11" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="I79" s="11" t="inlineStr">
+        <is>
+          <t>45%</t>
+        </is>
+      </c>
+      <c r="J79" s="11" t="inlineStr">
+        <is>
+          <t>2.03×</t>
+        </is>
+      </c>
+      <c r="K79" s="11" t="inlineStr">
+        <is>
+          <t>2.50×</t>
+        </is>
+      </c>
+      <c r="L79" s="11" t="inlineStr">
+        <is>
+          <t>1.70×</t>
+        </is>
+      </c>
+      <c r="M79" s="11" t="inlineStr">
+        <is>
+          <t>1.6×</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="12" t="n">
+        <v>76</v>
+      </c>
+      <c r="B80" s="13" t="inlineStr">
+        <is>
+          <t>PROXY</t>
+        </is>
+      </c>
+      <c r="C80" s="14" t="inlineStr">
+        <is>
+          <t>ERM</t>
+        </is>
+      </c>
+      <c r="D80" s="14" t="inlineStr">
+        <is>
+          <t>EMMERSON RESOURCES LIMITED</t>
+        </is>
+      </c>
+      <c r="E80" s="14" t="inlineStr">
+        <is>
+          <t>SE Asia / Pacific</t>
+        </is>
+      </c>
+      <c r="F80" s="14" t="inlineStr">
+        <is>
+          <t>0.56</t>
+        </is>
+      </c>
+      <c r="G80" s="14" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H80" s="14" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="I80" s="14" t="inlineStr">
+        <is>
+          <t>41%</t>
+        </is>
+      </c>
+      <c r="J80" s="14" t="inlineStr">
+        <is>
+          <t>1.97×</t>
+        </is>
+      </c>
+      <c r="K80" s="14" t="inlineStr">
+        <is>
+          <t>2.34×</t>
+        </is>
+      </c>
+      <c r="L80" s="14" t="inlineStr">
+        <is>
+          <t>1.65×</t>
+        </is>
+      </c>
+      <c r="M80" s="14" t="inlineStr">
+        <is>
+          <t>1.6×</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="9" t="n">
+        <v>77</v>
+      </c>
+      <c r="B81" s="15" t="inlineStr">
+        <is>
+          <t>PROXY</t>
+        </is>
+      </c>
+      <c r="C81" s="11" t="inlineStr">
+        <is>
+          <t>PEX</t>
+        </is>
+      </c>
+      <c r="D81" s="11" t="inlineStr">
+        <is>
+          <t>PEEL MINING LIMITED</t>
+        </is>
+      </c>
+      <c r="E81" s="11" t="inlineStr">
+        <is>
+          <t>SE Asia / Pacific</t>
+        </is>
+      </c>
+      <c r="F81" s="11" t="inlineStr">
+        <is>
+          <t>0.56</t>
+        </is>
+      </c>
+      <c r="G81" s="11" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H81" s="11" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="I81" s="11" t="inlineStr">
+        <is>
+          <t>41%</t>
+        </is>
+      </c>
+      <c r="J81" s="11" t="inlineStr">
+        <is>
+          <t>1.97×</t>
+        </is>
+      </c>
+      <c r="K81" s="11" t="inlineStr">
+        <is>
+          <t>2.34×</t>
+        </is>
+      </c>
+      <c r="L81" s="11" t="inlineStr">
+        <is>
+          <t>1.65×</t>
+        </is>
+      </c>
+      <c r="M81" s="11" t="inlineStr">
+        <is>
+          <t>1.6×</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="12" t="n">
+        <v>78</v>
+      </c>
+      <c r="B82" s="13" t="inlineStr">
+        <is>
+          <t>PROXY</t>
+        </is>
+      </c>
+      <c r="C82" s="14" t="inlineStr">
+        <is>
+          <t>AIS</t>
+        </is>
+      </c>
+      <c r="D82" s="14" t="inlineStr">
+        <is>
+          <t>AERIS RESOURCES LIMITED</t>
+        </is>
+      </c>
+      <c r="E82" s="14" t="inlineStr">
+        <is>
+          <t>SE Asia / Pacific</t>
+        </is>
+      </c>
+      <c r="F82" s="14" t="inlineStr">
+        <is>
+          <t>0.56</t>
+        </is>
+      </c>
+      <c r="G82" s="14" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H82" s="14" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="I82" s="14" t="inlineStr">
+        <is>
+          <t>41%</t>
+        </is>
+      </c>
+      <c r="J82" s="14" t="inlineStr">
+        <is>
+          <t>1.97×</t>
+        </is>
+      </c>
+      <c r="K82" s="14" t="inlineStr">
+        <is>
+          <t>2.34×</t>
+        </is>
+      </c>
+      <c r="L82" s="14" t="inlineStr">
+        <is>
+          <t>1.65×</t>
+        </is>
+      </c>
+      <c r="M82" s="14" t="inlineStr">
+        <is>
+          <t>1.6×</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="9" t="n">
+        <v>79</v>
+      </c>
+      <c r="B83" s="15" t="inlineStr">
+        <is>
+          <t>PROXY</t>
+        </is>
+      </c>
+      <c r="C83" s="11" t="inlineStr">
+        <is>
+          <t>ASM</t>
+        </is>
+      </c>
+      <c r="D83" s="11" t="inlineStr">
+        <is>
+          <t>AUSTRALIAN STRATEGIC MATERIALS LIMITED</t>
+        </is>
+      </c>
+      <c r="E83" s="11" t="inlineStr">
+        <is>
+          <t>SE Asia / Pacific</t>
+        </is>
+      </c>
+      <c r="F83" s="11" t="inlineStr">
+        <is>
+          <t>0.56</t>
+        </is>
+      </c>
+      <c r="G83" s="11" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H83" s="11" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="I83" s="11" t="inlineStr">
+        <is>
+          <t>41%</t>
+        </is>
+      </c>
+      <c r="J83" s="11" t="inlineStr">
+        <is>
+          <t>1.97×</t>
+        </is>
+      </c>
+      <c r="K83" s="11" t="inlineStr">
+        <is>
+          <t>2.34×</t>
+        </is>
+      </c>
+      <c r="L83" s="11" t="inlineStr">
+        <is>
+          <t>1.65×</t>
+        </is>
+      </c>
+      <c r="M83" s="11" t="inlineStr">
+        <is>
+          <t>1.6×</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="12" t="n">
+        <v>80</v>
+      </c>
+      <c r="B84" s="13" t="inlineStr">
+        <is>
+          <t>PROXY</t>
+        </is>
+      </c>
+      <c r="C84" s="14" t="inlineStr">
+        <is>
+          <t>QUB</t>
+        </is>
+      </c>
+      <c r="D84" s="14" t="inlineStr">
+        <is>
+          <t>QUBE HOLDINGS LIMITED</t>
+        </is>
+      </c>
+      <c r="E84" s="14" t="inlineStr">
+        <is>
+          <t>SE Asia / Pacific</t>
+        </is>
+      </c>
+      <c r="F84" s="14" t="inlineStr">
+        <is>
+          <t>0.56</t>
+        </is>
+      </c>
+      <c r="G84" s="14" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H84" s="14" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="I84" s="14" t="inlineStr">
+        <is>
+          <t>41%</t>
+        </is>
+      </c>
+      <c r="J84" s="14" t="inlineStr">
+        <is>
+          <t>1.97×</t>
+        </is>
+      </c>
+      <c r="K84" s="14" t="inlineStr">
+        <is>
+          <t>2.34×</t>
+        </is>
+      </c>
+      <c r="L84" s="14" t="inlineStr">
+        <is>
+          <t>1.65×</t>
+        </is>
+      </c>
+      <c r="M84" s="14" t="inlineStr">
+        <is>
+          <t>1.6×</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="9" t="n">
+        <v>81</v>
+      </c>
+      <c r="B85" s="15" t="inlineStr">
+        <is>
+          <t>PROXY</t>
+        </is>
+      </c>
+      <c r="C85" s="11" t="inlineStr">
+        <is>
+          <t>NVA</t>
+        </is>
+      </c>
+      <c r="D85" s="11" t="inlineStr">
+        <is>
+          <t>NOVA MINERALS CORP</t>
+        </is>
+      </c>
+      <c r="E85" s="11" t="inlineStr">
+        <is>
+          <t>SE Asia / Pacific</t>
+        </is>
+      </c>
+      <c r="F85" s="11" t="inlineStr">
+        <is>
+          <t>0.56</t>
+        </is>
+      </c>
+      <c r="G85" s="11" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H85" s="11" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="I85" s="11" t="inlineStr">
+        <is>
+          <t>41%</t>
+        </is>
+      </c>
+      <c r="J85" s="11" t="inlineStr">
+        <is>
+          <t>1.97×</t>
+        </is>
+      </c>
+      <c r="K85" s="11" t="inlineStr">
+        <is>
+          <t>2.34×</t>
+        </is>
+      </c>
+      <c r="L85" s="11" t="inlineStr">
+        <is>
+          <t>1.65×</t>
+        </is>
+      </c>
+      <c r="M85" s="11" t="inlineStr">
+        <is>
+          <t>1.6×</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="12" t="n">
+        <v>82</v>
+      </c>
+      <c r="B86" s="13" t="inlineStr">
+        <is>
+          <t>PROXY</t>
+        </is>
+      </c>
+      <c r="C86" s="14" t="inlineStr">
+        <is>
+          <t>PAF</t>
+        </is>
+      </c>
+      <c r="D86" s="14" t="inlineStr">
+        <is>
+          <t>PAN AFRICAN RESOURCES PLC</t>
+        </is>
+      </c>
+      <c r="E86" s="14" t="inlineStr">
+        <is>
+          <t>SE Asia / Pacific</t>
+        </is>
+      </c>
+      <c r="F86" s="14" t="inlineStr">
+        <is>
+          <t>0.56</t>
+        </is>
+      </c>
+      <c r="G86" s="14" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H86" s="14" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="I86" s="14" t="inlineStr">
+        <is>
+          <t>41%</t>
+        </is>
+      </c>
+      <c r="J86" s="14" t="inlineStr">
+        <is>
+          <t>1.97×</t>
+        </is>
+      </c>
+      <c r="K86" s="14" t="inlineStr">
+        <is>
+          <t>2.34×</t>
+        </is>
+      </c>
+      <c r="L86" s="14" t="inlineStr">
+        <is>
+          <t>1.65×</t>
+        </is>
+      </c>
+      <c r="M86" s="14" t="inlineStr">
+        <is>
+          <t>1.6×</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="9" t="n">
+        <v>83</v>
+      </c>
+      <c r="B87" s="15" t="inlineStr">
+        <is>
+          <t>PROXY</t>
+        </is>
+      </c>
+      <c r="C87" s="11" t="inlineStr">
+        <is>
+          <t>QOR</t>
+        </is>
+      </c>
+      <c r="D87" s="11" t="inlineStr">
+        <is>
+          <t>QORIA LIMITED</t>
+        </is>
+      </c>
+      <c r="E87" s="11" t="inlineStr">
+        <is>
+          <t>SE Asia / Pacific</t>
+        </is>
+      </c>
+      <c r="F87" s="11" t="inlineStr">
+        <is>
+          <t>0.56</t>
+        </is>
+      </c>
+      <c r="G87" s="11" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H87" s="11" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="I87" s="11" t="inlineStr">
+        <is>
+          <t>41%</t>
+        </is>
+      </c>
+      <c r="J87" s="11" t="inlineStr">
+        <is>
+          <t>1.97×</t>
+        </is>
+      </c>
+      <c r="K87" s="11" t="inlineStr">
+        <is>
+          <t>2.34×</t>
+        </is>
+      </c>
+      <c r="L87" s="11" t="inlineStr">
+        <is>
+          <t>1.65×</t>
+        </is>
+      </c>
+      <c r="M87" s="11" t="inlineStr">
+        <is>
+          <t>1.6×</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="12" t="n">
+        <v>84</v>
+      </c>
+      <c r="B88" s="13" t="inlineStr">
+        <is>
+          <t>PROXY</t>
+        </is>
+      </c>
+      <c r="C88" s="14" t="inlineStr">
+        <is>
+          <t>LLM</t>
+        </is>
+      </c>
+      <c r="D88" s="14" t="inlineStr">
+        <is>
+          <t>LOYAL METALS LTD</t>
+        </is>
+      </c>
+      <c r="E88" s="14" t="inlineStr">
+        <is>
+          <t>SE Asia / Pacific</t>
+        </is>
+      </c>
+      <c r="F88" s="14" t="inlineStr">
+        <is>
+          <t>0.56</t>
+        </is>
+      </c>
+      <c r="G88" s="14" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H88" s="14" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="I88" s="14" t="inlineStr">
+        <is>
+          <t>41%</t>
+        </is>
+      </c>
+      <c r="J88" s="14" t="inlineStr">
+        <is>
+          <t>1.97×</t>
+        </is>
+      </c>
+      <c r="K88" s="14" t="inlineStr">
+        <is>
+          <t>2.34×</t>
+        </is>
+      </c>
+      <c r="L88" s="14" t="inlineStr">
+        <is>
+          <t>1.65×</t>
+        </is>
+      </c>
+      <c r="M88" s="14" t="inlineStr">
+        <is>
+          <t>1.6×</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="9" t="n">
+        <v>85</v>
+      </c>
+      <c r="B89" s="15" t="inlineStr">
+        <is>
+          <t>PROXY</t>
+        </is>
+      </c>
+      <c r="C89" s="11" t="inlineStr">
+        <is>
+          <t>EMI</t>
+        </is>
+      </c>
+      <c r="D89" s="11" t="inlineStr">
+        <is>
+          <t>Encore Medical, Inc.</t>
+        </is>
+      </c>
+      <c r="E89" s="11" t="inlineStr">
+        <is>
+          <t>United States/Canada</t>
+        </is>
+      </c>
+      <c r="F89" s="11" t="inlineStr">
+        <is>
+          <t>0.69</t>
+        </is>
+      </c>
+      <c r="G89" s="11" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H89" s="11" t="inlineStr">
+        <is>
+          <t>F2</t>
+        </is>
+      </c>
+      <c r="I89" s="11" t="inlineStr">
+        <is>
+          <t>44%</t>
+        </is>
+      </c>
+      <c r="J89" s="11" t="inlineStr">
+        <is>
+          <t>2.05×</t>
+        </is>
+      </c>
+      <c r="K89" s="11" t="inlineStr">
+        <is>
+          <t>2.54×</t>
+        </is>
+      </c>
+      <c r="L89" s="11" t="inlineStr">
+        <is>
+          <t>1.72×</t>
+        </is>
+      </c>
+      <c r="M89" s="11" t="inlineStr">
+        <is>
+          <t>1.6×</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="12" t="n">
+        <v>86</v>
+      </c>
+      <c r="B90" s="16" t="inlineStr">
+        <is>
+          <t>REAL</t>
+        </is>
+      </c>
+      <c r="C90" s="14" t="inlineStr">
+        <is>
+          <t>HKEX:SUNAC</t>
+        </is>
+      </c>
+      <c r="D90" s="14" t="inlineStr">
+        <is>
+          <t>Sunac China Holdings</t>
+        </is>
+      </c>
+      <c r="E90" s="14" t="inlineStr">
+        <is>
+          <t>Greater China / HK</t>
+        </is>
+      </c>
+      <c r="F90" s="14" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+      <c r="G90" s="14" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H90" s="14" t="inlineStr">
+        <is>
+          <t>F+A</t>
+        </is>
+      </c>
+      <c r="I90" s="14" t="inlineStr">
+        <is>
+          <t>70%</t>
+        </is>
+      </c>
+      <c r="J90" s="14" t="inlineStr">
+        <is>
+          <t>2.20×</t>
+        </is>
+      </c>
+      <c r="K90" s="14" t="inlineStr">
+        <is>
+          <t>5.50×</t>
+        </is>
+      </c>
+      <c r="L90" s="14" t="inlineStr">
+        <is>
+          <t>2.10×</t>
+        </is>
+      </c>
+      <c r="M90" s="14" t="inlineStr">
+        <is>
+          <t>1.6×</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="9" t="n">
+        <v>87</v>
+      </c>
+      <c r="B91" s="15" t="inlineStr">
+        <is>
+          <t>PROXY</t>
+        </is>
+      </c>
+      <c r="C91" s="11" t="inlineStr">
+        <is>
+          <t>VIE:VOE</t>
+        </is>
+      </c>
+      <c r="D91" s="11" t="inlineStr">
+        <is>
+          <t>voestalpine</t>
+        </is>
+      </c>
+      <c r="E91" s="11" t="inlineStr">
+        <is>
+          <t>Continental Europe</t>
+        </is>
+      </c>
+      <c r="F91" s="11" t="inlineStr">
+        <is>
+          <t>0.46</t>
+        </is>
+      </c>
+      <c r="G91" s="11" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H91" s="11" t="inlineStr">
+        <is>
+          <t>A2+A1</t>
+        </is>
+      </c>
+      <c r="I91" s="11" t="inlineStr">
+        <is>
+          <t>38%</t>
+        </is>
+      </c>
+      <c r="J91" s="11" t="inlineStr">
+        <is>
+          <t>1.90×</t>
+        </is>
+      </c>
+      <c r="K91" s="11" t="inlineStr">
+        <is>
+          <t>2.19×</t>
+        </is>
+      </c>
+      <c r="L91" s="11" t="inlineStr">
+        <is>
+          <t>1.59×</t>
+        </is>
+      </c>
+      <c r="M91" s="11" t="inlineStr">
+        <is>
+          <t>1.5×</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="12" t="n">
+        <v>88</v>
+      </c>
+      <c r="B92" s="13" t="inlineStr">
+        <is>
+          <t>PROXY</t>
+        </is>
+      </c>
+      <c r="C92" s="14" t="inlineStr">
+        <is>
+          <t>private</t>
+        </is>
+      </c>
+      <c r="D92" s="14" t="inlineStr">
+        <is>
+          <t>Aeroportos do Brasil (Vinci)</t>
+        </is>
+      </c>
+      <c r="E92" s="14" t="inlineStr">
+        <is>
+          <t>Latin America</t>
+        </is>
+      </c>
+      <c r="F92" s="14" t="inlineStr">
+        <is>
+          <t>0.44</t>
+        </is>
+      </c>
+      <c r="G92" s="14" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H92" s="14" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="I92" s="14" t="inlineStr">
+        <is>
+          <t>39%</t>
+        </is>
+      </c>
+      <c r="J92" s="14" t="inlineStr">
+        <is>
+          <t>1.89×</t>
+        </is>
+      </c>
+      <c r="K92" s="14" t="inlineStr">
+        <is>
+          <t>2.16×</t>
+        </is>
+      </c>
+      <c r="L92" s="14" t="inlineStr">
+        <is>
+          <t>1.57×</t>
+        </is>
+      </c>
+      <c r="M92" s="14" t="inlineStr">
+        <is>
+          <t>1.5×</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="9" t="n">
+        <v>89</v>
+      </c>
+      <c r="B93" s="15" t="inlineStr">
+        <is>
+          <t>PROXY</t>
+        </is>
+      </c>
+      <c r="C93" s="11" t="inlineStr">
+        <is>
+          <t>NGX:UBA</t>
+        </is>
+      </c>
+      <c r="D93" s="11" t="inlineStr">
+        <is>
+          <t>UBA</t>
+        </is>
+      </c>
+      <c r="E93" s="11" t="inlineStr">
+        <is>
+          <t>MEA / Frontier</t>
+        </is>
+      </c>
+      <c r="F93" s="11" t="inlineStr">
+        <is>
+          <t>0.66</t>
+        </is>
+      </c>
+      <c r="G93" s="11" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H93" s="11" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="I93" s="11" t="inlineStr">
+        <is>
+          <t>45%</t>
+        </is>
+      </c>
+      <c r="J93" s="11" t="inlineStr">
+        <is>
+          <t>2.02×</t>
+        </is>
+      </c>
+      <c r="K93" s="11" t="inlineStr">
+        <is>
+          <t>2.49×</t>
+        </is>
+      </c>
+      <c r="L93" s="11" t="inlineStr">
+        <is>
+          <t>1.70×</t>
+        </is>
+      </c>
+      <c r="M93" s="11" t="inlineStr">
+        <is>
+          <t>1.5×</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="12" t="n">
+        <v>90</v>
+      </c>
+      <c r="B94" s="13" t="inlineStr">
+        <is>
+          <t>PROXY</t>
+        </is>
+      </c>
+      <c r="C94" s="14" t="inlineStr">
+        <is>
+          <t>JSE:EOH</t>
+        </is>
+      </c>
+      <c r="D94" s="14" t="inlineStr">
+        <is>
+          <t>EOH Holdings</t>
+        </is>
+      </c>
+      <c r="E94" s="14" t="inlineStr">
+        <is>
+          <t>MEA / Frontier</t>
+        </is>
+      </c>
+      <c r="F94" s="14" t="inlineStr">
+        <is>
+          <t>0.64</t>
+        </is>
+      </c>
+      <c r="G94" s="14" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H94" s="14" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="I94" s="14" t="inlineStr">
+        <is>
+          <t>46%</t>
+        </is>
+      </c>
+      <c r="J94" s="14" t="inlineStr">
+        <is>
+          <t>2.00×</t>
+        </is>
+      </c>
+      <c r="K94" s="14" t="inlineStr">
+        <is>
+          <t>2.46×</t>
+        </is>
+      </c>
+      <c r="L94" s="14" t="inlineStr">
+        <is>
+          <t>1.68×</t>
+        </is>
+      </c>
+      <c r="M94" s="14" t="inlineStr">
+        <is>
+          <t>1.5×</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="9" t="n">
+        <v>91</v>
+      </c>
+      <c r="B95" s="15" t="inlineStr">
+        <is>
+          <t>PROXY</t>
+        </is>
+      </c>
+      <c r="C95" s="11" t="inlineStr">
+        <is>
+          <t>CIK:0001783876</t>
+        </is>
+      </c>
+      <c r="D95" s="11" t="inlineStr">
+        <is>
+          <t>Teamshares Inc.</t>
+        </is>
+      </c>
+      <c r="E95" s="11" t="inlineStr">
+        <is>
+          <t>United States/Canada</t>
+        </is>
+      </c>
+      <c r="F95" s="11" t="inlineStr">
+        <is>
+          <t>0.64</t>
+        </is>
+      </c>
+      <c r="G95" s="11" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H95" s="11" t="inlineStr">
+        <is>
+          <t>K3</t>
+        </is>
+      </c>
+      <c r="I95" s="11" t="inlineStr">
+        <is>
+          <t>46%</t>
+        </is>
+      </c>
+      <c r="J95" s="11" t="inlineStr">
+        <is>
+          <t>2.00×</t>
+        </is>
+      </c>
+      <c r="K95" s="11" t="inlineStr">
+        <is>
+          <t>2.46×</t>
+        </is>
+      </c>
+      <c r="L95" s="11" t="inlineStr">
+        <is>
+          <t>1.68×</t>
+        </is>
+      </c>
+      <c r="M95" s="11" t="inlineStr">
+        <is>
+          <t>1.5×</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="12" t="n">
+        <v>92</v>
+      </c>
+      <c r="B96" s="13" t="inlineStr">
+        <is>
+          <t>PROXY</t>
+        </is>
+      </c>
+      <c r="C96" s="14" t="inlineStr">
+        <is>
+          <t>CIK:0001574219</t>
+        </is>
+      </c>
+      <c r="D96" s="14" t="inlineStr">
+        <is>
+          <t>J.P. Morgan Chase Commercial Mortgage Securities T</t>
+        </is>
+      </c>
+      <c r="E96" s="14" t="inlineStr">
+        <is>
+          <t>United States/Canada</t>
+        </is>
+      </c>
+      <c r="F96" s="14" t="inlineStr">
+        <is>
+          <t>0.64</t>
+        </is>
+      </c>
+      <c r="G96" s="14" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H96" s="14" t="inlineStr">
+        <is>
+          <t>K3</t>
+        </is>
+      </c>
+      <c r="I96" s="14" t="inlineStr">
+        <is>
+          <t>46%</t>
+        </is>
+      </c>
+      <c r="J96" s="14" t="inlineStr">
+        <is>
+          <t>2.00×</t>
+        </is>
+      </c>
+      <c r="K96" s="14" t="inlineStr">
+        <is>
+          <t>2.46×</t>
+        </is>
+      </c>
+      <c r="L96" s="14" t="inlineStr">
+        <is>
+          <t>1.68×</t>
+        </is>
+      </c>
+      <c r="M96" s="14" t="inlineStr">
+        <is>
+          <t>1.5×</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="9" t="n">
+        <v>93</v>
+      </c>
+      <c r="B97" s="15" t="inlineStr">
+        <is>
+          <t>PROXY</t>
+        </is>
+      </c>
+      <c r="C97" s="11" t="inlineStr">
+        <is>
+          <t>TSE:6740</t>
+        </is>
+      </c>
+      <c r="D97" s="11" t="inlineStr">
+        <is>
+          <t>Japan Display</t>
+        </is>
+      </c>
+      <c r="E97" s="11" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="F97" s="11" t="inlineStr">
+        <is>
+          <t>0.54</t>
+        </is>
+      </c>
+      <c r="G97" s="11" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H97" s="11" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="I97" s="11" t="inlineStr">
+        <is>
+          <t>49%</t>
+        </is>
+      </c>
+      <c r="J97" s="11" t="inlineStr">
+        <is>
+          <t>2.03×</t>
+        </is>
+      </c>
+      <c r="K97" s="11" t="inlineStr">
+        <is>
+          <t>2.54×</t>
+        </is>
+      </c>
+      <c r="L97" s="11" t="inlineStr">
+        <is>
+          <t>1.70×</t>
+        </is>
+      </c>
+      <c r="M97" s="11" t="inlineStr">
+        <is>
+          <t>1.4×</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="12" t="n">
+        <v>94</v>
+      </c>
+      <c r="B98" s="13" t="inlineStr">
+        <is>
+          <t>PROXY</t>
+        </is>
+      </c>
+      <c r="C98" s="14" t="inlineStr">
+        <is>
+          <t>TSE</t>
+        </is>
+      </c>
+      <c r="D98" s="14" t="inlineStr">
+        <is>
+          <t>Rapidus-adjacent suppliers</t>
+        </is>
+      </c>
+      <c r="E98" s="14" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="F98" s="14" t="inlineStr">
+        <is>
+          <t>0.32</t>
+        </is>
+      </c>
+      <c r="G98" s="14" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H98" s="14" t="inlineStr">
+        <is>
+          <t>A2+H</t>
+        </is>
+      </c>
+      <c r="I98" s="14" t="inlineStr">
+        <is>
+          <t>42%</t>
+        </is>
+      </c>
+      <c r="J98" s="14" t="inlineStr">
+        <is>
+          <t>1.88×</t>
+        </is>
+      </c>
+      <c r="K98" s="14" t="inlineStr">
+        <is>
+          <t>2.18×</t>
+        </is>
+      </c>
+      <c r="L98" s="14" t="inlineStr">
+        <is>
+          <t>1.57×</t>
+        </is>
+      </c>
+      <c r="M98" s="14" t="inlineStr">
+        <is>
+          <t>1.4×</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="9" t="n">
+        <v>95</v>
+      </c>
+      <c r="B99" s="15" t="inlineStr">
+        <is>
+          <t>PROXY</t>
+        </is>
+      </c>
+      <c r="C99" s="11" t="inlineStr">
+        <is>
+          <t>NZX:SML</t>
+        </is>
+      </c>
+      <c r="D99" s="11" t="inlineStr">
+        <is>
+          <t>Synlait Milk</t>
+        </is>
+      </c>
+      <c r="E99" s="11" t="inlineStr">
+        <is>
+          <t>SE Asia / Pacific</t>
+        </is>
+      </c>
+      <c r="F99" s="11" t="inlineStr">
+        <is>
+          <t>0.61</t>
+        </is>
+      </c>
+      <c r="G99" s="11" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H99" s="11" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="I99" s="11" t="inlineStr">
+        <is>
+          <t>47%</t>
+        </is>
+      </c>
+      <c r="J99" s="11" t="inlineStr">
+        <is>
+          <t>1.97×</t>
+        </is>
+      </c>
+      <c r="K99" s="11" t="inlineStr">
+        <is>
+          <t>2.42×</t>
+        </is>
+      </c>
+      <c r="L99" s="11" t="inlineStr">
+        <is>
+          <t>1.65×</t>
+        </is>
+      </c>
+      <c r="M99" s="11" t="inlineStr">
+        <is>
+          <t>1.4×</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="12" t="n">
+        <v>96</v>
+      </c>
+      <c r="B100" s="13" t="inlineStr">
+        <is>
+          <t>PROXY</t>
+        </is>
+      </c>
+      <c r="C100" s="14" t="inlineStr">
+        <is>
+          <t>LSE:MTRO</t>
+        </is>
+      </c>
+      <c r="D100" s="14" t="inlineStr">
+        <is>
+          <t>Metro Bank</t>
+        </is>
+      </c>
+      <c r="E100" s="14" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="F100" s="14" t="inlineStr">
+        <is>
+          <t>0.51</t>
+        </is>
+      </c>
+      <c r="G100" s="14" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H100" s="14" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="I100" s="14" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="J100" s="14" t="inlineStr">
+        <is>
+          <t>2.00×</t>
+        </is>
+      </c>
+      <c r="K100" s="14" t="inlineStr">
+        <is>
+          <t>2.49×</t>
+        </is>
+      </c>
+      <c r="L100" s="14" t="inlineStr">
+        <is>
+          <t>1.67×</t>
+        </is>
+      </c>
+      <c r="M100" s="14" t="inlineStr">
+        <is>
+          <t>1.4×</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="9" t="n">
+        <v>97</v>
+      </c>
+      <c r="B101" s="15" t="inlineStr">
+        <is>
+          <t>PROXY</t>
+        </is>
+      </c>
+      <c r="C101" s="11" t="inlineStr">
+        <is>
+          <t>LSE:VANQ</t>
+        </is>
+      </c>
+      <c r="D101" s="11" t="inlineStr">
+        <is>
+          <t>Provident Financial → Vanquis Banking</t>
+        </is>
+      </c>
+      <c r="E101" s="11" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="F101" s="11" t="inlineStr">
+        <is>
+          <t>0.43</t>
+        </is>
+      </c>
+      <c r="G101" s="11" t="inlineStr">
+        <is>
+          <t>A (warn)</t>
+        </is>
+      </c>
+      <c r="H101" s="11" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="I101" s="11" t="inlineStr">
+        <is>
+          <t>39%</t>
+        </is>
+      </c>
+      <c r="J101" s="11" t="inlineStr">
+        <is>
+          <t>1.88×</t>
+        </is>
+      </c>
+      <c r="K101" s="11" t="inlineStr">
+        <is>
+          <t>2.15×</t>
+        </is>
+      </c>
+      <c r="L101" s="11" t="inlineStr">
+        <is>
+          <t>1.56×</t>
+        </is>
+      </c>
+      <c r="M101" s="11" t="inlineStr">
+        <is>
+          <t>1.4×</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="12" t="n">
+        <v>98</v>
+      </c>
+      <c r="B102" s="13" t="inlineStr">
+        <is>
+          <t>PROXY</t>
+        </is>
+      </c>
+      <c r="C102" s="14" t="inlineStr">
+        <is>
+          <t>VIE:WIE</t>
+        </is>
+      </c>
+      <c r="D102" s="14" t="inlineStr">
+        <is>
+          <t>Wienerberger</t>
+        </is>
+      </c>
+      <c r="E102" s="14" t="inlineStr">
+        <is>
+          <t>Continental Europe</t>
+        </is>
+      </c>
+      <c r="F102" s="14" t="inlineStr">
+        <is>
+          <t>0.35</t>
+        </is>
+      </c>
+      <c r="G102" s="14" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H102" s="14" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="I102" s="14" t="inlineStr">
+        <is>
+          <t>41%</t>
+        </is>
+      </c>
+      <c r="J102" s="14" t="inlineStr">
+        <is>
+          <t>1.81×</t>
+        </is>
+      </c>
+      <c r="K102" s="14" t="inlineStr">
+        <is>
+          <t>2.02×</t>
+        </is>
+      </c>
+      <c r="L102" s="14" t="inlineStr">
+        <is>
+          <t>1.50×</t>
+        </is>
+      </c>
+      <c r="M102" s="14" t="inlineStr">
+        <is>
+          <t>1.2×</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="9" t="n">
+        <v>99</v>
+      </c>
+      <c r="B103" s="15" t="inlineStr">
+        <is>
+          <t>PROXY</t>
+        </is>
+      </c>
+      <c r="C103" s="11" t="inlineStr">
+        <is>
+          <t>EPA:FER</t>
+        </is>
+      </c>
+      <c r="D103" s="11" t="inlineStr">
+        <is>
+          <t>Ferrovial</t>
+        </is>
+      </c>
+      <c r="E103" s="11" t="inlineStr">
+        <is>
+          <t>Continental Europe</t>
+        </is>
+      </c>
+      <c r="F103" s="11" t="inlineStr">
+        <is>
+          <t>0.35</t>
+        </is>
+      </c>
+      <c r="G103" s="11" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H103" s="11" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="I103" s="11" t="inlineStr">
+        <is>
+          <t>41%</t>
+        </is>
+      </c>
+      <c r="J103" s="11" t="inlineStr">
+        <is>
+          <t>1.81×</t>
+        </is>
+      </c>
+      <c r="K103" s="11" t="inlineStr">
+        <is>
+          <t>2.02×</t>
+        </is>
+      </c>
+      <c r="L103" s="11" t="inlineStr">
+        <is>
+          <t>1.50×</t>
+        </is>
+      </c>
+      <c r="M103" s="11" t="inlineStr">
+        <is>
+          <t>1.2×</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="12" t="n">
+        <v>100</v>
+      </c>
+      <c r="B104" s="13" t="inlineStr">
+        <is>
+          <t>PROXY</t>
+        </is>
+      </c>
+      <c r="C104" s="14" t="inlineStr">
+        <is>
+          <t>SIX:HOLN</t>
+        </is>
+      </c>
+      <c r="D104" s="14" t="inlineStr">
+        <is>
+          <t>Holcim</t>
+        </is>
+      </c>
+      <c r="E104" s="14" t="inlineStr">
+        <is>
+          <t>Continental Europe</t>
+        </is>
+      </c>
+      <c r="F104" s="14" t="inlineStr">
+        <is>
+          <t>0.34</t>
+        </is>
+      </c>
+      <c r="G104" s="14" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H104" s="14" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="I104" s="14" t="inlineStr">
+        <is>
+          <t>41%</t>
+        </is>
+      </c>
+      <c r="J104" s="14" t="inlineStr">
+        <is>
+          <t>1.80×</t>
+        </is>
+      </c>
+      <c r="K104" s="14" t="inlineStr">
+        <is>
+          <t>2.01×</t>
+        </is>
+      </c>
+      <c r="L104" s="14" t="inlineStr">
+        <is>
+          <t>1.49×</t>
+        </is>
+      </c>
+      <c r="M104" s="14" t="inlineStr">
+        <is>
+          <t>1.2×</t>
+        </is>
+      </c>
+    </row>
+    <row r="105"/>
+    <row r="106" ht="60" customHeight="1">
+      <c r="A106" s="7" t="inlineStr">
+        <is>
+          <t>Reward/Risk = (EV× − 1) ÷ Bear loss = the asymmetry metric.  The broad universe-screener scores the full candidate set on archetype, vintage, status, size, region, and cross-source corroboration; this asymmetric scan ranks the investable subset (221 names) by reward/risk. Investable filter drops PASS_FALSE_FRIEND / ACQUIRED / ARC_DONE / REPEAT_RX and non-equity placeholder tickers ((state), (private), (delisted)). PROXY waterfall: bear_loss = max(0.10, 0.65 − 0.30·score), tilted ×0.75 for A1/A2 (sovereign-anchored floor). bull = 1.50 + 1.50·score, tilted ×1.10 for H, ×1.15 for F. Hand-built YAMLs override the proxy with bottom-up numbers.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A31:M31"/>
+    <mergeCell ref="A106:M106"/>
     <mergeCell ref="A2:M2"/>
   </mergeCells>
-  <conditionalFormatting sqref="M5:M29">
+  <conditionalFormatting sqref="M5:M104">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -8696,13 +13571,13 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
     <col width="37" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
     <col width="8" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="27" customWidth="1" min="8" max="8"/>
+    <col width="36" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -8768,32 +13643,32 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>TBRG</t>
+          <t>NYSE:TGS</t>
         </is>
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>TruBridge, Inc.</t>
+          <t>TGS (Transportadora de Gas del Sur)</t>
         </is>
       </c>
       <c r="D5" s="11" t="inlineStr">
         <is>
-          <t>United States/Canada</t>
+          <t>Latin America</t>
         </is>
       </c>
       <c r="E5" s="11" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="F5" s="11" t="inlineStr">
         <is>
-          <t>A2+K3</t>
+          <t>A1</t>
         </is>
       </c>
       <c r="G5" s="11" t="inlineStr">
         <is>
-          <t>6.6×</t>
+          <t>4.5×</t>
         </is>
       </c>
       <c r="H5" s="11" t="inlineStr">
@@ -8808,32 +13683,32 @@
       </c>
       <c r="B6" s="14" t="inlineStr">
         <is>
-          <t>APTOF</t>
+          <t>NYSE:EDN</t>
         </is>
       </c>
       <c r="C6" s="14" t="inlineStr">
         <is>
-          <t>Aptose Biosciences Inc.</t>
+          <t>Edenor</t>
         </is>
       </c>
       <c r="D6" s="14" t="inlineStr">
         <is>
-          <t>United States/Canada</t>
+          <t>Latin America</t>
         </is>
       </c>
       <c r="E6" s="14" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="F6" s="14" t="inlineStr">
         <is>
-          <t>A2+K3</t>
+          <t>A1</t>
         </is>
       </c>
       <c r="G6" s="14" t="inlineStr">
         <is>
-          <t>5.9×</t>
+          <t>4.0×</t>
         </is>
       </c>
       <c r="H6" s="14" t="inlineStr">
@@ -8848,32 +13723,32 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>AEMD</t>
+          <t>BIT:MB</t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>AETHLON MEDICAL INC</t>
+          <t>Mediobanca</t>
         </is>
       </c>
       <c r="D7" s="11" t="inlineStr">
         <is>
-          <t>United States/Canada</t>
+          <t>Continental Europe</t>
         </is>
       </c>
       <c r="E7" s="11" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="F7" s="11" t="inlineStr">
         <is>
-          <t>A2+F2</t>
+          <t>A1</t>
         </is>
       </c>
       <c r="G7" s="11" t="inlineStr">
         <is>
-          <t>5.4×</t>
+          <t>3.7×</t>
         </is>
       </c>
       <c r="H7" s="11" t="inlineStr">
@@ -8888,32 +13763,32 @@
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>LEG</t>
+          <t>NYSE:GGAL</t>
         </is>
       </c>
       <c r="C8" s="14" t="inlineStr">
         <is>
-          <t>LEGGETT &amp; PLATT INC</t>
+          <t>Banco Galicia</t>
         </is>
       </c>
       <c r="D8" s="14" t="inlineStr">
         <is>
-          <t>United States/Canada</t>
+          <t>Latin America</t>
         </is>
       </c>
       <c r="E8" s="14" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="F8" s="14" t="inlineStr">
         <is>
-          <t>A2</t>
+          <t>A1</t>
         </is>
       </c>
       <c r="G8" s="14" t="inlineStr">
         <is>
-          <t>5.3×</t>
+          <t>3.6×</t>
         </is>
       </c>
       <c r="H8" s="14" t="inlineStr">
@@ -8924,36 +13799,36 @@
     </row>
     <row r="9">
       <c r="A9" s="9" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>BATL</t>
+          <t>NYSE:PAM</t>
         </is>
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>BATTALION OIL CORP</t>
+          <t>Pampa Energía</t>
         </is>
       </c>
       <c r="D9" s="11" t="inlineStr">
         <is>
-          <t>United States/Canada</t>
+          <t>Latin America</t>
         </is>
       </c>
       <c r="E9" s="11" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="F9" s="11" t="inlineStr">
         <is>
-          <t>A2</t>
+          <t>A1</t>
         </is>
       </c>
       <c r="G9" s="11" t="inlineStr">
         <is>
-          <t>4.8×</t>
+          <t>3.4×</t>
         </is>
       </c>
       <c r="H9" s="11" t="inlineStr">
@@ -8964,26 +13839,26 @@
     </row>
     <row r="10">
       <c r="A10" s="12" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>NYSE:TGS</t>
+          <t>ACF</t>
         </is>
       </c>
       <c r="C10" s="14" t="inlineStr">
         <is>
-          <t>TGS (Transportadora de Gas del Sur)</t>
+          <t>ACROW LIMITED</t>
         </is>
       </c>
       <c r="D10" s="14" t="inlineStr">
         <is>
-          <t>Latin America</t>
+          <t>SE Asia / Pacific</t>
         </is>
       </c>
       <c r="E10" s="14" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="F10" s="14" t="inlineStr">
@@ -8993,7 +13868,7 @@
       </c>
       <c r="G10" s="14" t="inlineStr">
         <is>
-          <t>4.5×</t>
+          <t>3.0×</t>
         </is>
       </c>
       <c r="H10" s="14" t="inlineStr">
@@ -9004,96 +13879,96 @@
     </row>
     <row r="11">
       <c r="A11" s="9" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>EMI</t>
+          <t>BME:TLGO</t>
         </is>
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>Encore Medical, Inc.</t>
+          <t>Talgo</t>
         </is>
       </c>
       <c r="D11" s="11" t="inlineStr">
         <is>
-          <t>United States/Canada</t>
+          <t>Continental Europe</t>
         </is>
       </c>
       <c r="E11" s="11" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="F11" s="11" t="inlineStr">
         <is>
-          <t>A2+F2</t>
+          <t>A1</t>
         </is>
       </c>
       <c r="G11" s="11" t="inlineStr">
         <is>
-          <t>4.4×</t>
+          <t>2.6×</t>
         </is>
       </c>
       <c r="H11" s="11" t="inlineStr">
         <is>
-          <t>Tier 1 — hand-deepen ASAP</t>
+          <t>Tier 2 — verify primary docs first</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="12" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="B12" s="14" t="inlineStr">
         <is>
-          <t>EHGO</t>
+          <t>LSE:ASC</t>
         </is>
       </c>
       <c r="C12" s="14" t="inlineStr">
         <is>
-          <t>EShallGo Inc.</t>
+          <t>ASOS</t>
         </is>
       </c>
       <c r="D12" s="14" t="inlineStr">
         <is>
-          <t>United States/Canada</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="E12" s="14" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="F12" s="14" t="inlineStr">
         <is>
-          <t>A2</t>
+          <t>A1</t>
         </is>
       </c>
       <c r="G12" s="14" t="inlineStr">
         <is>
-          <t>4.3×</t>
+          <t>2.6×</t>
         </is>
       </c>
       <c r="H12" s="14" t="inlineStr">
         <is>
-          <t>Tier 1 — hand-deepen ASAP</t>
+          <t>Tier 2 — verify primary docs first</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="9" t="n">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>RNGE</t>
+          <t>TBRG</t>
         </is>
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>RANGE IMPACT, INC.</t>
+          <t>TruBridge, Inc.</t>
         </is>
       </c>
       <c r="D13" s="11" t="inlineStr">
@@ -9103,17 +13978,17 @@
       </c>
       <c r="E13" s="11" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="F13" s="11" t="inlineStr">
         <is>
-          <t>A2</t>
+          <t>K3</t>
         </is>
       </c>
       <c r="G13" s="11" t="inlineStr">
         <is>
-          <t>4.3×</t>
+          <t>2.6×</t>
         </is>
       </c>
       <c r="H13" s="11" t="inlineStr">
@@ -9124,16 +13999,16 @@
     </row>
     <row r="14">
       <c r="A14" s="12" t="n">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="B14" s="14" t="inlineStr">
         <is>
-          <t>CVKD</t>
+          <t>LEG</t>
         </is>
       </c>
       <c r="C14" s="14" t="inlineStr">
         <is>
-          <t>Cadrenal Therapeutics, Inc.</t>
+          <t>LEGGETT &amp; PLATT INC</t>
         </is>
       </c>
       <c r="D14" s="14" t="inlineStr">
@@ -9143,17 +14018,17 @@
       </c>
       <c r="E14" s="14" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="F14" s="14" t="inlineStr">
         <is>
-          <t>A2</t>
+          <t>C</t>
         </is>
       </c>
       <c r="G14" s="14" t="inlineStr">
         <is>
-          <t>4.3×</t>
+          <t>2.6×</t>
         </is>
       </c>
       <c r="H14" s="14" t="inlineStr">
@@ -9164,16 +14039,16 @@
     </row>
     <row r="15">
       <c r="A15" s="9" t="n">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>SRFM</t>
+          <t>TSX:CFW</t>
         </is>
       </c>
       <c r="C15" s="11" t="inlineStr">
         <is>
-          <t>SURF AIR MOBILITY INC.</t>
+          <t>Calfrac Well Services</t>
         </is>
       </c>
       <c r="D15" s="11" t="inlineStr">
@@ -9183,57 +14058,57 @@
       </c>
       <c r="E15" s="11" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="F15" s="11" t="inlineStr">
         <is>
-          <t>A2</t>
+          <t>A1</t>
         </is>
       </c>
       <c r="G15" s="11" t="inlineStr">
         <is>
-          <t>4.3×</t>
+          <t>2.5×</t>
         </is>
       </c>
       <c r="H15" s="11" t="inlineStr">
         <is>
-          <t>Tier 1 — hand-deepen ASAP</t>
+          <t>Tier 2 — verify primary docs first</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="12" t="n">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="B16" s="14" t="inlineStr">
         <is>
-          <t>HIVE</t>
+          <t>KRX:028260</t>
         </is>
       </c>
       <c r="C16" s="14" t="inlineStr">
         <is>
-          <t>HIVE Digital Technologies Ltd.</t>
+          <t>Samsung C&amp;T</t>
         </is>
       </c>
       <c r="D16" s="14" t="inlineStr">
         <is>
-          <t>United States/Canada</t>
+          <t>Korea</t>
         </is>
       </c>
       <c r="E16" s="14" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="F16" s="14" t="inlineStr">
         <is>
-          <t>A2</t>
+          <t>H</t>
         </is>
       </c>
       <c r="G16" s="14" t="inlineStr">
         <is>
-          <t>4.3×</t>
+          <t>2.4×</t>
         </is>
       </c>
       <c r="H16" s="14" t="inlineStr">
@@ -9244,56 +14119,56 @@
     </row>
     <row r="17">
       <c r="A17" s="9" t="n">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>ASNS</t>
+          <t>LSE:AML</t>
         </is>
       </c>
       <c r="C17" s="11" t="inlineStr">
         <is>
-          <t>ACTELIS NETWORKS INC</t>
+          <t>Aston Martin Lagonda</t>
         </is>
       </c>
       <c r="D17" s="11" t="inlineStr">
         <is>
-          <t>United States/Canada</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="E17" s="11" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="F17" s="11" t="inlineStr">
         <is>
-          <t>A2</t>
+          <t>A1</t>
         </is>
       </c>
       <c r="G17" s="11" t="inlineStr">
         <is>
-          <t>4.3×</t>
+          <t>2.4×</t>
         </is>
       </c>
       <c r="H17" s="11" t="inlineStr">
         <is>
-          <t>Tier 1 — hand-deepen ASAP</t>
+          <t>Tier 2 — verify primary docs first</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="12" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="B18" s="14" t="inlineStr">
         <is>
-          <t>INUV</t>
+          <t>APTOF</t>
         </is>
       </c>
       <c r="C18" s="14" t="inlineStr">
         <is>
-          <t>Inuvo, Inc.</t>
+          <t>Aptose Biosciences Inc.</t>
         </is>
       </c>
       <c r="D18" s="14" t="inlineStr">
@@ -9303,17 +14178,17 @@
       </c>
       <c r="E18" s="14" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="F18" s="14" t="inlineStr">
         <is>
-          <t>A2</t>
+          <t>K3</t>
         </is>
       </c>
       <c r="G18" s="14" t="inlineStr">
         <is>
-          <t>4.3×</t>
+          <t>2.4×</t>
         </is>
       </c>
       <c r="H18" s="14" t="inlineStr">
@@ -9324,66 +14199,66 @@
     </row>
     <row r="19">
       <c r="A19" s="9" t="n">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>FMC</t>
+          <t>HK:2202</t>
         </is>
       </c>
       <c r="C19" s="11" t="inlineStr">
         <is>
-          <t>FMC CORP</t>
+          <t>Vanke</t>
         </is>
       </c>
       <c r="D19" s="11" t="inlineStr">
         <is>
-          <t>United States/Canada</t>
+          <t>Greater China / HK</t>
         </is>
       </c>
       <c r="E19" s="11" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="F19" s="11" t="inlineStr">
         <is>
-          <t>A2</t>
+          <t>A1</t>
         </is>
       </c>
       <c r="G19" s="11" t="inlineStr">
         <is>
-          <t>4.2×</t>
+          <t>2.3×</t>
         </is>
       </c>
       <c r="H19" s="11" t="inlineStr">
         <is>
-          <t>Tier 1 — hand-deepen ASAP</t>
+          <t>Tier 2 — verify primary docs first</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="12" t="n">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="B20" s="14" t="inlineStr">
         <is>
-          <t>NYSE:EDN</t>
+          <t>LSE:VOD</t>
         </is>
       </c>
       <c r="C20" s="14" t="inlineStr">
         <is>
-          <t>Edenor</t>
+          <t>Vodafone</t>
         </is>
       </c>
       <c r="D20" s="14" t="inlineStr">
         <is>
-          <t>Latin America</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="E20" s="14" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="F20" s="14" t="inlineStr">
@@ -9393,37 +14268,37 @@
       </c>
       <c r="G20" s="14" t="inlineStr">
         <is>
-          <t>4.0×</t>
+          <t>2.3×</t>
         </is>
       </c>
       <c r="H20" s="14" t="inlineStr">
         <is>
-          <t>Tier 1 — hand-deepen ASAP</t>
+          <t>Tier 2 — verify primary docs first</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="9" t="n">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t>BIT:MB</t>
+          <t>LSE:TLW</t>
         </is>
       </c>
       <c r="C21" s="11" t="inlineStr">
         <is>
-          <t>Mediobanca</t>
+          <t>Tullow Oil</t>
         </is>
       </c>
       <c r="D21" s="11" t="inlineStr">
         <is>
-          <t>Continental Europe</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="E21" s="11" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="F21" s="11" t="inlineStr">
@@ -9433,132 +14308,132 @@
       </c>
       <c r="G21" s="11" t="inlineStr">
         <is>
-          <t>3.7×</t>
+          <t>2.3×</t>
         </is>
       </c>
       <c r="H21" s="11" t="inlineStr">
         <is>
-          <t>Tier 1 — hand-deepen ASAP</t>
+          <t>Tier 2 — verify primary docs first</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="12" t="n">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="B22" s="14" t="inlineStr">
         <is>
-          <t>ACF</t>
+          <t>NYSE:FFWM</t>
         </is>
       </c>
       <c r="C22" s="14" t="inlineStr">
         <is>
-          <t>ACROW LIMITED</t>
+          <t>First Foundation</t>
         </is>
       </c>
       <c r="D22" s="14" t="inlineStr">
         <is>
-          <t>SE Asia / Pacific</t>
+          <t>United States/Canada</t>
         </is>
       </c>
       <c r="E22" s="14" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="F22" s="14" t="inlineStr">
         <is>
-          <t>A2+A1</t>
+          <t>A1</t>
         </is>
       </c>
       <c r="G22" s="14" t="inlineStr">
         <is>
-          <t>3.7×</t>
+          <t>2.3×</t>
         </is>
       </c>
       <c r="H22" s="14" t="inlineStr">
         <is>
-          <t>Tier 1 — hand-deepen ASAP</t>
+          <t>Tier 2 — verify primary docs first</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="9" t="n">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="B23" s="11" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>TSE:8304</t>
         </is>
       </c>
       <c r="C23" s="11" t="inlineStr">
         <is>
-          <t>MEMPHASYS LIMITED.</t>
+          <t>Aozora Bank</t>
         </is>
       </c>
       <c r="D23" s="11" t="inlineStr">
         <is>
-          <t>SE Asia / Pacific</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="E23" s="11" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="F23" s="11" t="inlineStr">
         <is>
-          <t>A2+B</t>
+          <t>H</t>
         </is>
       </c>
       <c r="G23" s="11" t="inlineStr">
         <is>
-          <t>3.7×</t>
+          <t>2.1×</t>
         </is>
       </c>
       <c r="H23" s="11" t="inlineStr">
         <is>
-          <t>Tier 1 — hand-deepen ASAP</t>
+          <t>Tier 2 — verify primary docs first</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="12" t="n">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="B24" s="14" t="inlineStr">
         <is>
-          <t>NYSE:GGAL</t>
+          <t>XETR:TUI1</t>
         </is>
       </c>
       <c r="C24" s="14" t="inlineStr">
         <is>
-          <t>Banco Galicia</t>
+          <t>Tui AG</t>
         </is>
       </c>
       <c r="D24" s="14" t="inlineStr">
         <is>
-          <t>Latin America</t>
+          <t>Continental Europe</t>
         </is>
       </c>
       <c r="E24" s="14" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="F24" s="14" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2</t>
         </is>
       </c>
       <c r="G24" s="14" t="inlineStr">
         <is>
-          <t>3.6×</t>
+          <t>2.0×</t>
         </is>
       </c>
       <c r="H24" s="14" t="inlineStr">
         <is>
-          <t>Tier 1 — hand-deepen ASAP</t>
+          <t>Tier 2 — verify primary docs first</t>
         </is>
       </c>
     </row>

--- a/output/cyclepapa_risk_reward_workbook.xlsx
+++ b/output/cyclepapa_risk_reward_workbook.xlsx
@@ -6938,10 +6938,10 @@
     <col width="60" customWidth="1" min="1" max="1"/>
     <col width="8" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="52" customWidth="1" min="4" max="4"/>
+    <col width="49" customWidth="1" min="4" max="4"/>
     <col width="22" customWidth="1" min="5" max="5"/>
     <col width="8" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
     <col width="11" customWidth="1" min="8" max="8"/>
     <col width="11" customWidth="1" min="9" max="9"/>
     <col width="8" customWidth="1" min="10" max="10"/>
@@ -6960,7 +6960,7 @@
     <row r="2" ht="38" customHeight="1">
       <c r="A2" s="7" t="inlineStr">
         <is>
-          <t>Universe coverage: 221 investable names (21 REAL waterfalls · 200 PROXY).  REAL uses the hand-built YAML's bottom-up bear/base/bull. PROXY uses a transparent formula on the universe-screener score + archetype tilt.</t>
+          <t>Universe coverage: 288 investable names (21 REAL waterfalls · 267 PROXY).  REAL uses the hand-built YAML's bottom-up bear/base/bull. PROXY uses a transparent formula on the universe-screener score + archetype tilt.</t>
         </is>
       </c>
     </row>
@@ -8408,22 +8408,22 @@
       </c>
       <c r="C26" s="14" t="inlineStr">
         <is>
-          <t>LSE:ASC</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D26" s="14" t="inlineStr">
         <is>
-          <t>ASOS</t>
+          <t>IRANI PAPEL E EMBALAGEM S.A.</t>
         </is>
       </c>
       <c r="E26" s="14" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Latin America</t>
         </is>
       </c>
       <c r="F26" s="14" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="G26" s="14" t="inlineStr">
@@ -8443,17 +8443,17 @@
       </c>
       <c r="J26" s="14" t="inlineStr">
         <is>
-          <t>2.16×</t>
+          <t>2.15×</t>
         </is>
       </c>
       <c r="K26" s="14" t="inlineStr">
         <is>
-          <t>2.64×</t>
+          <t>2.62×</t>
         </is>
       </c>
       <c r="L26" s="14" t="inlineStr">
         <is>
-          <t>1.84×</t>
+          <t>1.83×</t>
         </is>
       </c>
       <c r="M26" s="14" t="inlineStr">
@@ -8473,22 +8473,22 @@
       </c>
       <c r="C27" s="11" t="inlineStr">
         <is>
-          <t>TBRG</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D27" s="11" t="inlineStr">
         <is>
-          <t>TruBridge, Inc.</t>
+          <t>COMERC ENERGIA S.A.</t>
         </is>
       </c>
       <c r="E27" s="11" t="inlineStr">
         <is>
-          <t>United States/Canada</t>
+          <t>Latin America</t>
         </is>
       </c>
       <c r="F27" s="11" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="G27" s="11" t="inlineStr">
@@ -8498,27 +8498,27 @@
       </c>
       <c r="H27" s="11" t="inlineStr">
         <is>
-          <t>K3</t>
+          <t>A1</t>
         </is>
       </c>
       <c r="I27" s="11" t="inlineStr">
         <is>
-          <t>36%</t>
+          <t>32%</t>
         </is>
       </c>
       <c r="J27" s="11" t="inlineStr">
         <is>
-          <t>2.29×</t>
+          <t>2.15×</t>
         </is>
       </c>
       <c r="K27" s="11" t="inlineStr">
         <is>
-          <t>2.94×</t>
+          <t>2.62×</t>
         </is>
       </c>
       <c r="L27" s="11" t="inlineStr">
         <is>
-          <t>1.96×</t>
+          <t>1.83×</t>
         </is>
       </c>
       <c r="M27" s="11" t="inlineStr">
@@ -8538,22 +8538,22 @@
       </c>
       <c r="C28" s="14" t="inlineStr">
         <is>
-          <t>LEG</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D28" s="14" t="inlineStr">
         <is>
-          <t>LEGGETT &amp; PLATT INC</t>
+          <t>SOCIEDADE ABASTECIMENTO DE AGUA E SANEAMENTO SA</t>
         </is>
       </c>
       <c r="E28" s="14" t="inlineStr">
         <is>
-          <t>United States/Canada</t>
+          <t>Latin America</t>
         </is>
       </c>
       <c r="F28" s="14" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="G28" s="14" t="inlineStr">
@@ -8563,27 +8563,27 @@
       </c>
       <c r="H28" s="14" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A1</t>
         </is>
       </c>
       <c r="I28" s="14" t="inlineStr">
         <is>
-          <t>34%</t>
+          <t>32%</t>
         </is>
       </c>
       <c r="J28" s="14" t="inlineStr">
         <is>
-          <t>2.21×</t>
+          <t>2.15×</t>
         </is>
       </c>
       <c r="K28" s="14" t="inlineStr">
         <is>
-          <t>2.76×</t>
+          <t>2.62×</t>
         </is>
       </c>
       <c r="L28" s="14" t="inlineStr">
         <is>
-          <t>1.88×</t>
+          <t>1.83×</t>
         </is>
       </c>
       <c r="M28" s="14" t="inlineStr">
@@ -8596,29 +8596,29 @@
       <c r="A29" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="B29" s="10" t="inlineStr">
-        <is>
-          <t>REAL</t>
+      <c r="B29" s="15" t="inlineStr">
+        <is>
+          <t>PROXY</t>
         </is>
       </c>
       <c r="C29" s="11" t="inlineStr">
         <is>
-          <t>LSE:DRX</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D29" s="11" t="inlineStr">
         <is>
-          <t>Drax Group</t>
+          <t>MINERVA S/A</t>
         </is>
       </c>
       <c r="E29" s="11" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Latin America</t>
         </is>
       </c>
       <c r="F29" s="11" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="G29" s="11" t="inlineStr">
@@ -8628,27 +8628,27 @@
       </c>
       <c r="H29" s="11" t="inlineStr">
         <is>
-          <t>A1+G</t>
+          <t>A1</t>
         </is>
       </c>
       <c r="I29" s="11" t="inlineStr">
         <is>
-          <t>55%</t>
+          <t>32%</t>
         </is>
       </c>
       <c r="J29" s="11" t="inlineStr">
         <is>
-          <t>2.20×</t>
+          <t>2.15×</t>
         </is>
       </c>
       <c r="K29" s="11" t="inlineStr">
         <is>
-          <t>4.50×</t>
+          <t>2.62×</t>
         </is>
       </c>
       <c r="L29" s="11" t="inlineStr">
         <is>
-          <t>2.45×</t>
+          <t>1.83×</t>
         </is>
       </c>
       <c r="M29" s="11" t="inlineStr">
@@ -8661,29 +8661,29 @@
       <c r="A30" s="12" t="n">
         <v>26</v>
       </c>
-      <c r="B30" s="16" t="inlineStr">
-        <is>
-          <t>REAL</t>
+      <c r="B30" s="13" t="inlineStr">
+        <is>
+          <t>PROXY</t>
         </is>
       </c>
       <c r="C30" s="14" t="inlineStr">
         <is>
-          <t>NASDAQ:UREE</t>
+          <t>LSE:ASC</t>
         </is>
       </c>
       <c r="D30" s="14" t="inlineStr">
         <is>
-          <t>USA Rare Earth</t>
+          <t>ASOS</t>
         </is>
       </c>
       <c r="E30" s="14" t="inlineStr">
         <is>
-          <t>United States/Canada</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="F30" s="14" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="G30" s="14" t="inlineStr">
@@ -8693,27 +8693,27 @@
       </c>
       <c r="H30" s="14" t="inlineStr">
         <is>
-          <t>A2</t>
+          <t>A1</t>
         </is>
       </c>
       <c r="I30" s="14" t="inlineStr">
         <is>
-          <t>65%</t>
+          <t>32%</t>
         </is>
       </c>
       <c r="J30" s="14" t="inlineStr">
         <is>
-          <t>2.50×</t>
+          <t>2.16×</t>
         </is>
       </c>
       <c r="K30" s="14" t="inlineStr">
         <is>
-          <t>5.50×</t>
+          <t>2.64×</t>
         </is>
       </c>
       <c r="L30" s="14" t="inlineStr">
         <is>
-          <t>2.71×</t>
+          <t>1.84×</t>
         </is>
       </c>
       <c r="M30" s="14" t="inlineStr">
@@ -8733,12 +8733,12 @@
       </c>
       <c r="C31" s="11" t="inlineStr">
         <is>
-          <t>TSX:CFW</t>
+          <t>TBRG</t>
         </is>
       </c>
       <c r="D31" s="11" t="inlineStr">
         <is>
-          <t>Calfrac Well Services</t>
+          <t>TruBridge, Inc.</t>
         </is>
       </c>
       <c r="E31" s="11" t="inlineStr">
@@ -8748,7 +8748,7 @@
       </c>
       <c r="F31" s="11" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="G31" s="11" t="inlineStr">
@@ -8758,32 +8758,32 @@
       </c>
       <c r="H31" s="11" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>K3</t>
         </is>
       </c>
       <c r="I31" s="11" t="inlineStr">
         <is>
-          <t>32%</t>
+          <t>36%</t>
         </is>
       </c>
       <c r="J31" s="11" t="inlineStr">
         <is>
-          <t>2.14×</t>
+          <t>2.29×</t>
         </is>
       </c>
       <c r="K31" s="11" t="inlineStr">
         <is>
-          <t>2.59×</t>
+          <t>2.94×</t>
         </is>
       </c>
       <c r="L31" s="11" t="inlineStr">
         <is>
-          <t>1.81×</t>
+          <t>1.96×</t>
         </is>
       </c>
       <c r="M31" s="11" t="inlineStr">
         <is>
-          <t>2.5×</t>
+          <t>2.6×</t>
         </is>
       </c>
     </row>
@@ -8798,22 +8798,22 @@
       </c>
       <c r="C32" s="14" t="inlineStr">
         <is>
-          <t>KRX:028260</t>
+          <t>LEG</t>
         </is>
       </c>
       <c r="D32" s="14" t="inlineStr">
         <is>
-          <t>Samsung C&amp;T</t>
+          <t>LEGGETT &amp; PLATT INC</t>
         </is>
       </c>
       <c r="E32" s="14" t="inlineStr">
         <is>
-          <t>Korea</t>
+          <t>United States/Canada</t>
         </is>
       </c>
       <c r="F32" s="14" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="G32" s="14" t="inlineStr">
@@ -8823,32 +8823,32 @@
       </c>
       <c r="H32" s="14" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>C</t>
         </is>
       </c>
       <c r="I32" s="14" t="inlineStr">
         <is>
-          <t>40%</t>
+          <t>34%</t>
         </is>
       </c>
       <c r="J32" s="14" t="inlineStr">
         <is>
-          <t>2.30×</t>
+          <t>2.21×</t>
         </is>
       </c>
       <c r="K32" s="14" t="inlineStr">
         <is>
-          <t>3.00×</t>
+          <t>2.76×</t>
         </is>
       </c>
       <c r="L32" s="14" t="inlineStr">
         <is>
-          <t>1.96×</t>
+          <t>1.88×</t>
         </is>
       </c>
       <c r="M32" s="14" t="inlineStr">
         <is>
-          <t>2.4×</t>
+          <t>2.6×</t>
         </is>
       </c>
     </row>
@@ -8856,19 +8856,19 @@
       <c r="A33" s="9" t="n">
         <v>29</v>
       </c>
-      <c r="B33" s="15" t="inlineStr">
-        <is>
-          <t>PROXY</t>
+      <c r="B33" s="10" t="inlineStr">
+        <is>
+          <t>REAL</t>
         </is>
       </c>
       <c r="C33" s="11" t="inlineStr">
         <is>
-          <t>LSE:AML</t>
+          <t>LSE:DRX</t>
         </is>
       </c>
       <c r="D33" s="11" t="inlineStr">
         <is>
-          <t>Aston Martin Lagonda</t>
+          <t>Drax Group</t>
         </is>
       </c>
       <c r="E33" s="11" t="inlineStr">
@@ -8878,7 +8878,7 @@
       </c>
       <c r="F33" s="11" t="inlineStr">
         <is>
-          <t>0.70</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="G33" s="11" t="inlineStr">
@@ -8888,32 +8888,32 @@
       </c>
       <c r="H33" s="11" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A1+G</t>
         </is>
       </c>
       <c r="I33" s="11" t="inlineStr">
         <is>
-          <t>33%</t>
+          <t>55%</t>
         </is>
       </c>
       <c r="J33" s="11" t="inlineStr">
         <is>
-          <t>2.11×</t>
+          <t>2.20×</t>
         </is>
       </c>
       <c r="K33" s="11" t="inlineStr">
         <is>
-          <t>2.55×</t>
+          <t>4.50×</t>
         </is>
       </c>
       <c r="L33" s="11" t="inlineStr">
         <is>
-          <t>1.79×</t>
+          <t>2.45×</t>
         </is>
       </c>
       <c r="M33" s="11" t="inlineStr">
         <is>
-          <t>2.4×</t>
+          <t>2.6×</t>
         </is>
       </c>
     </row>
@@ -8921,19 +8921,19 @@
       <c r="A34" s="12" t="n">
         <v>30</v>
       </c>
-      <c r="B34" s="13" t="inlineStr">
-        <is>
-          <t>PROXY</t>
+      <c r="B34" s="16" t="inlineStr">
+        <is>
+          <t>REAL</t>
         </is>
       </c>
       <c r="C34" s="14" t="inlineStr">
         <is>
-          <t>APTOF</t>
+          <t>NASDAQ:UREE</t>
         </is>
       </c>
       <c r="D34" s="14" t="inlineStr">
         <is>
-          <t>Aptose Biosciences Inc.</t>
+          <t>USA Rare Earth</t>
         </is>
       </c>
       <c r="E34" s="14" t="inlineStr">
@@ -8943,7 +8943,7 @@
       </c>
       <c r="F34" s="14" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="G34" s="14" t="inlineStr">
@@ -8953,32 +8953,32 @@
       </c>
       <c r="H34" s="14" t="inlineStr">
         <is>
-          <t>K3</t>
+          <t>A2</t>
         </is>
       </c>
       <c r="I34" s="14" t="inlineStr">
         <is>
-          <t>38%</t>
+          <t>65%</t>
         </is>
       </c>
       <c r="J34" s="14" t="inlineStr">
         <is>
-          <t>2.24×</t>
+          <t>2.50×</t>
         </is>
       </c>
       <c r="K34" s="14" t="inlineStr">
         <is>
-          <t>2.87×</t>
+          <t>5.50×</t>
         </is>
       </c>
       <c r="L34" s="14" t="inlineStr">
         <is>
-          <t>1.91×</t>
+          <t>2.71×</t>
         </is>
       </c>
       <c r="M34" s="14" t="inlineStr">
         <is>
-          <t>2.4×</t>
+          <t>2.6×</t>
         </is>
       </c>
     </row>
@@ -8993,22 +8993,22 @@
       </c>
       <c r="C35" s="11" t="inlineStr">
         <is>
-          <t>HK:2202</t>
+          <t>TSX:CFW</t>
         </is>
       </c>
       <c r="D35" s="11" t="inlineStr">
         <is>
-          <t>Vanke</t>
+          <t>Calfrac Well Services</t>
         </is>
       </c>
       <c r="E35" s="11" t="inlineStr">
         <is>
-          <t>Greater China / HK</t>
+          <t>United States/Canada</t>
         </is>
       </c>
       <c r="F35" s="11" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="G35" s="11" t="inlineStr">
@@ -9023,27 +9023,27 @@
       </c>
       <c r="I35" s="11" t="inlineStr">
         <is>
-          <t>33%</t>
+          <t>32%</t>
         </is>
       </c>
       <c r="J35" s="11" t="inlineStr">
         <is>
-          <t>2.10×</t>
+          <t>2.14×</t>
         </is>
       </c>
       <c r="K35" s="11" t="inlineStr">
         <is>
-          <t>2.54×</t>
+          <t>2.59×</t>
         </is>
       </c>
       <c r="L35" s="11" t="inlineStr">
         <is>
-          <t>1.78×</t>
+          <t>1.81×</t>
         </is>
       </c>
       <c r="M35" s="11" t="inlineStr">
         <is>
-          <t>2.3×</t>
+          <t>2.5×</t>
         </is>
       </c>
     </row>
@@ -9058,22 +9058,22 @@
       </c>
       <c r="C36" s="14" t="inlineStr">
         <is>
-          <t>LSE:VOD</t>
+          <t>KRX:028260</t>
         </is>
       </c>
       <c r="D36" s="14" t="inlineStr">
         <is>
-          <t>Vodafone</t>
+          <t>Samsung C&amp;T</t>
         </is>
       </c>
       <c r="E36" s="14" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Korea</t>
         </is>
       </c>
       <c r="F36" s="14" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="G36" s="14" t="inlineStr">
@@ -9083,32 +9083,32 @@
       </c>
       <c r="H36" s="14" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>H</t>
         </is>
       </c>
       <c r="I36" s="14" t="inlineStr">
         <is>
-          <t>34%</t>
+          <t>40%</t>
         </is>
       </c>
       <c r="J36" s="14" t="inlineStr">
         <is>
-          <t>2.08×</t>
+          <t>2.30×</t>
         </is>
       </c>
       <c r="K36" s="14" t="inlineStr">
         <is>
-          <t>2.50×</t>
+          <t>3.00×</t>
         </is>
       </c>
       <c r="L36" s="14" t="inlineStr">
         <is>
-          <t>1.76×</t>
+          <t>1.96×</t>
         </is>
       </c>
       <c r="M36" s="14" t="inlineStr">
         <is>
-          <t>2.3×</t>
+          <t>2.4×</t>
         </is>
       </c>
     </row>
@@ -9123,12 +9123,12 @@
       </c>
       <c r="C37" s="11" t="inlineStr">
         <is>
-          <t>LSE:TLW</t>
+          <t>LSE:AML</t>
         </is>
       </c>
       <c r="D37" s="11" t="inlineStr">
         <is>
-          <t>Tullow Oil</t>
+          <t>Aston Martin Lagonda</t>
         </is>
       </c>
       <c r="E37" s="11" t="inlineStr">
@@ -9138,7 +9138,7 @@
       </c>
       <c r="F37" s="11" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="G37" s="11" t="inlineStr">
@@ -9153,27 +9153,27 @@
       </c>
       <c r="I37" s="11" t="inlineStr">
         <is>
-          <t>34%</t>
+          <t>33%</t>
         </is>
       </c>
       <c r="J37" s="11" t="inlineStr">
         <is>
-          <t>2.08×</t>
+          <t>2.11×</t>
         </is>
       </c>
       <c r="K37" s="11" t="inlineStr">
         <is>
-          <t>2.50×</t>
+          <t>2.55×</t>
         </is>
       </c>
       <c r="L37" s="11" t="inlineStr">
         <is>
-          <t>1.76×</t>
+          <t>1.79×</t>
         </is>
       </c>
       <c r="M37" s="11" t="inlineStr">
         <is>
-          <t>2.3×</t>
+          <t>2.4×</t>
         </is>
       </c>
     </row>
@@ -9188,12 +9188,12 @@
       </c>
       <c r="C38" s="14" t="inlineStr">
         <is>
-          <t>NYSE:FFWM</t>
+          <t>APTOF</t>
         </is>
       </c>
       <c r="D38" s="14" t="inlineStr">
         <is>
-          <t>First Foundation</t>
+          <t>Aptose Biosciences Inc.</t>
         </is>
       </c>
       <c r="E38" s="14" t="inlineStr">
@@ -9203,7 +9203,7 @@
       </c>
       <c r="F38" s="14" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="G38" s="14" t="inlineStr">
@@ -9213,32 +9213,32 @@
       </c>
       <c r="H38" s="14" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>K3</t>
         </is>
       </c>
       <c r="I38" s="14" t="inlineStr">
         <is>
-          <t>34%</t>
+          <t>38%</t>
         </is>
       </c>
       <c r="J38" s="14" t="inlineStr">
         <is>
-          <t>2.08×</t>
+          <t>2.24×</t>
         </is>
       </c>
       <c r="K38" s="14" t="inlineStr">
         <is>
-          <t>2.50×</t>
+          <t>2.87×</t>
         </is>
       </c>
       <c r="L38" s="14" t="inlineStr">
         <is>
-          <t>1.76×</t>
+          <t>1.91×</t>
         </is>
       </c>
       <c r="M38" s="14" t="inlineStr">
         <is>
-          <t>2.3×</t>
+          <t>2.4×</t>
         </is>
       </c>
     </row>
@@ -9246,29 +9246,29 @@
       <c r="A39" s="9" t="n">
         <v>35</v>
       </c>
-      <c r="B39" s="10" t="inlineStr">
-        <is>
-          <t>REAL</t>
+      <c r="B39" s="15" t="inlineStr">
+        <is>
+          <t>PROXY</t>
         </is>
       </c>
       <c r="C39" s="11" t="inlineStr">
         <is>
-          <t>NYSE:HE</t>
+          <t>HK:2202</t>
         </is>
       </c>
       <c r="D39" s="11" t="inlineStr">
         <is>
-          <t>Hawaiian Electric Industries</t>
+          <t>Vanke</t>
         </is>
       </c>
       <c r="E39" s="11" t="inlineStr">
         <is>
-          <t>United States/Canada</t>
+          <t>Greater China / HK</t>
         </is>
       </c>
       <c r="F39" s="11" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="G39" s="11" t="inlineStr">
@@ -9278,27 +9278,27 @@
       </c>
       <c r="H39" s="11" t="inlineStr">
         <is>
-          <t>A1+G</t>
+          <t>A1</t>
         </is>
       </c>
       <c r="I39" s="11" t="inlineStr">
         <is>
-          <t>40%</t>
+          <t>33%</t>
         </is>
       </c>
       <c r="J39" s="11" t="inlineStr">
         <is>
-          <t>1.80×</t>
+          <t>2.10×</t>
         </is>
       </c>
       <c r="K39" s="11" t="inlineStr">
         <is>
-          <t>3.00×</t>
+          <t>2.54×</t>
         </is>
       </c>
       <c r="L39" s="11" t="inlineStr">
         <is>
-          <t>1.92×</t>
+          <t>1.78×</t>
         </is>
       </c>
       <c r="M39" s="11" t="inlineStr">
@@ -9318,22 +9318,22 @@
       </c>
       <c r="C40" s="14" t="inlineStr">
         <is>
-          <t>TSE:8304</t>
+          <t>LSE:VOD</t>
         </is>
       </c>
       <c r="D40" s="14" t="inlineStr">
         <is>
-          <t>Aozora Bank</t>
+          <t>Vodafone</t>
         </is>
       </c>
       <c r="E40" s="14" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="F40" s="14" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="G40" s="14" t="inlineStr">
@@ -9343,32 +9343,32 @@
       </c>
       <c r="H40" s="14" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>A1</t>
         </is>
       </c>
       <c r="I40" s="14" t="inlineStr">
         <is>
-          <t>42%</t>
+          <t>34%</t>
         </is>
       </c>
       <c r="J40" s="14" t="inlineStr">
         <is>
-          <t>2.23×</t>
+          <t>2.08×</t>
         </is>
       </c>
       <c r="K40" s="14" t="inlineStr">
         <is>
-          <t>2.89×</t>
+          <t>2.50×</t>
         </is>
       </c>
       <c r="L40" s="14" t="inlineStr">
         <is>
-          <t>1.90×</t>
+          <t>1.76×</t>
         </is>
       </c>
       <c r="M40" s="14" t="inlineStr">
         <is>
-          <t>2.1×</t>
+          <t>2.3×</t>
         </is>
       </c>
     </row>
@@ -9376,29 +9376,29 @@
       <c r="A41" s="9" t="n">
         <v>37</v>
       </c>
-      <c r="B41" s="10" t="inlineStr">
-        <is>
-          <t>REAL</t>
+      <c r="B41" s="15" t="inlineStr">
+        <is>
+          <t>PROXY</t>
         </is>
       </c>
       <c r="C41" s="11" t="inlineStr">
         <is>
-          <t>NYSE/TSX:TMQ</t>
+          <t>LSE:TLW</t>
         </is>
       </c>
       <c r="D41" s="11" t="inlineStr">
         <is>
-          <t>Trilogy Metals</t>
+          <t>Tullow Oil</t>
         </is>
       </c>
       <c r="E41" s="11" t="inlineStr">
         <is>
-          <t>United States/Canada</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="F41" s="11" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="G41" s="11" t="inlineStr">
@@ -9408,32 +9408,32 @@
       </c>
       <c r="H41" s="11" t="inlineStr">
         <is>
-          <t>A2</t>
+          <t>A1</t>
         </is>
       </c>
       <c r="I41" s="11" t="inlineStr">
         <is>
-          <t>55%</t>
+          <t>34%</t>
         </is>
       </c>
       <c r="J41" s="11" t="inlineStr">
         <is>
-          <t>2.20×</t>
+          <t>2.08×</t>
         </is>
       </c>
       <c r="K41" s="11" t="inlineStr">
         <is>
-          <t>4.50×</t>
+          <t>2.50×</t>
         </is>
       </c>
       <c r="L41" s="11" t="inlineStr">
         <is>
-          <t>2.14×</t>
+          <t>1.76×</t>
         </is>
       </c>
       <c r="M41" s="11" t="inlineStr">
         <is>
-          <t>2.1×</t>
+          <t>2.3×</t>
         </is>
       </c>
     </row>
@@ -9448,22 +9448,22 @@
       </c>
       <c r="C42" s="14" t="inlineStr">
         <is>
-          <t>XETR:TUI1</t>
+          <t>NYSE:FFWM</t>
         </is>
       </c>
       <c r="D42" s="14" t="inlineStr">
         <is>
-          <t>Tui AG</t>
+          <t>First Foundation</t>
         </is>
       </c>
       <c r="E42" s="14" t="inlineStr">
         <is>
-          <t>Continental Europe</t>
+          <t>United States/Canada</t>
         </is>
       </c>
       <c r="F42" s="14" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="G42" s="14" t="inlineStr">
@@ -9473,32 +9473,32 @@
       </c>
       <c r="H42" s="14" t="inlineStr">
         <is>
-          <t>A2</t>
+          <t>A1</t>
         </is>
       </c>
       <c r="I42" s="14" t="inlineStr">
         <is>
-          <t>36%</t>
+          <t>34%</t>
         </is>
       </c>
       <c r="J42" s="14" t="inlineStr">
         <is>
-          <t>2.02×</t>
+          <t>2.08×</t>
         </is>
       </c>
       <c r="K42" s="14" t="inlineStr">
         <is>
-          <t>2.38×</t>
+          <t>2.50×</t>
         </is>
       </c>
       <c r="L42" s="14" t="inlineStr">
         <is>
-          <t>1.70×</t>
+          <t>1.76×</t>
         </is>
       </c>
       <c r="M42" s="14" t="inlineStr">
         <is>
-          <t>2.0×</t>
+          <t>2.3×</t>
         </is>
       </c>
     </row>
@@ -9506,29 +9506,29 @@
       <c r="A43" s="9" t="n">
         <v>39</v>
       </c>
-      <c r="B43" s="15" t="inlineStr">
-        <is>
-          <t>PROXY</t>
+      <c r="B43" s="10" t="inlineStr">
+        <is>
+          <t>REAL</t>
         </is>
       </c>
       <c r="C43" s="11" t="inlineStr">
         <is>
-          <t>LSE:PDL</t>
+          <t>NYSE:HE</t>
         </is>
       </c>
       <c r="D43" s="11" t="inlineStr">
         <is>
-          <t>Petra Diamonds</t>
+          <t>Hawaiian Electric Industries</t>
         </is>
       </c>
       <c r="E43" s="11" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>United States/Canada</t>
         </is>
       </c>
       <c r="F43" s="11" t="inlineStr">
         <is>
-          <t>0.60</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="G43" s="11" t="inlineStr">
@@ -9538,32 +9538,32 @@
       </c>
       <c r="H43" s="11" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A1+G</t>
         </is>
       </c>
       <c r="I43" s="11" t="inlineStr">
         <is>
-          <t>35%</t>
+          <t>40%</t>
         </is>
       </c>
       <c r="J43" s="11" t="inlineStr">
         <is>
-          <t>2.02×</t>
+          <t>1.80×</t>
         </is>
       </c>
       <c r="K43" s="11" t="inlineStr">
         <is>
-          <t>2.40×</t>
+          <t>3.00×</t>
         </is>
       </c>
       <c r="L43" s="11" t="inlineStr">
         <is>
-          <t>1.70×</t>
+          <t>1.92×</t>
         </is>
       </c>
       <c r="M43" s="11" t="inlineStr">
         <is>
-          <t>2.0×</t>
+          <t>2.3×</t>
         </is>
       </c>
     </row>
@@ -9571,29 +9571,29 @@
       <c r="A44" s="12" t="n">
         <v>40</v>
       </c>
-      <c r="B44" s="16" t="inlineStr">
-        <is>
-          <t>REAL</t>
+      <c r="B44" s="13" t="inlineStr">
+        <is>
+          <t>PROXY</t>
         </is>
       </c>
       <c r="C44" s="14" t="inlineStr">
         <is>
-          <t>NYSE:MP</t>
+          <t>TSE:8304</t>
         </is>
       </c>
       <c r="D44" s="14" t="inlineStr">
         <is>
-          <t>MP Materials Corp</t>
+          <t>Aozora Bank</t>
         </is>
       </c>
       <c r="E44" s="14" t="inlineStr">
         <is>
-          <t>United States/Canada</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="F44" s="14" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="G44" s="14" t="inlineStr">
@@ -9603,22 +9603,22 @@
       </c>
       <c r="H44" s="14" t="inlineStr">
         <is>
-          <t>A2</t>
+          <t>H</t>
         </is>
       </c>
       <c r="I44" s="14" t="inlineStr">
         <is>
-          <t>45%</t>
+          <t>42%</t>
         </is>
       </c>
       <c r="J44" s="14" t="inlineStr">
         <is>
-          <t>1.80×</t>
+          <t>2.23×</t>
         </is>
       </c>
       <c r="K44" s="14" t="inlineStr">
         <is>
-          <t>3.20×</t>
+          <t>2.89×</t>
         </is>
       </c>
       <c r="L44" s="14" t="inlineStr">
@@ -9628,7 +9628,7 @@
       </c>
       <c r="M44" s="14" t="inlineStr">
         <is>
-          <t>2.0×</t>
+          <t>2.1×</t>
         </is>
       </c>
     </row>
@@ -9636,29 +9636,29 @@
       <c r="A45" s="9" t="n">
         <v>41</v>
       </c>
-      <c r="B45" s="15" t="inlineStr">
-        <is>
-          <t>PROXY</t>
+      <c r="B45" s="10" t="inlineStr">
+        <is>
+          <t>REAL</t>
         </is>
       </c>
       <c r="C45" s="11" t="inlineStr">
         <is>
-          <t>NYSE:AENZ</t>
+          <t>NYSE/TSX:TMQ</t>
         </is>
       </c>
       <c r="D45" s="11" t="inlineStr">
         <is>
-          <t>Aenza (former Graña y Montero)</t>
+          <t>Trilogy Metals</t>
         </is>
       </c>
       <c r="E45" s="11" t="inlineStr">
         <is>
-          <t>Continental Europe</t>
+          <t>United States/Canada</t>
         </is>
       </c>
       <c r="F45" s="11" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="G45" s="11" t="inlineStr">
@@ -9673,27 +9673,27 @@
       </c>
       <c r="I45" s="11" t="inlineStr">
         <is>
-          <t>36%</t>
+          <t>55%</t>
         </is>
       </c>
       <c r="J45" s="11" t="inlineStr">
         <is>
-          <t>2.00×</t>
+          <t>2.20×</t>
         </is>
       </c>
       <c r="K45" s="11" t="inlineStr">
         <is>
-          <t>2.35×</t>
+          <t>4.50×</t>
         </is>
       </c>
       <c r="L45" s="11" t="inlineStr">
         <is>
-          <t>1.68×</t>
+          <t>2.14×</t>
         </is>
       </c>
       <c r="M45" s="11" t="inlineStr">
         <is>
-          <t>1.9×</t>
+          <t>2.1×</t>
         </is>
       </c>
     </row>
@@ -9708,22 +9708,22 @@
       </c>
       <c r="C46" s="14" t="inlineStr">
         <is>
-          <t>KRX:034730</t>
+          <t>XETR:TUI1</t>
         </is>
       </c>
       <c r="D46" s="14" t="inlineStr">
         <is>
-          <t>SK Inc</t>
+          <t>Tui AG</t>
         </is>
       </c>
       <c r="E46" s="14" t="inlineStr">
         <is>
-          <t>Korea</t>
+          <t>Continental Europe</t>
         </is>
       </c>
       <c r="F46" s="14" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="G46" s="14" t="inlineStr">
@@ -9733,32 +9733,32 @@
       </c>
       <c r="H46" s="14" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>A2</t>
         </is>
       </c>
       <c r="I46" s="14" t="inlineStr">
         <is>
-          <t>44%</t>
+          <t>36%</t>
         </is>
       </c>
       <c r="J46" s="14" t="inlineStr">
         <is>
-          <t>2.17×</t>
+          <t>2.02×</t>
         </is>
       </c>
       <c r="K46" s="14" t="inlineStr">
         <is>
-          <t>2.79×</t>
+          <t>2.38×</t>
         </is>
       </c>
       <c r="L46" s="14" t="inlineStr">
         <is>
-          <t>1.84×</t>
+          <t>1.70×</t>
         </is>
       </c>
       <c r="M46" s="14" t="inlineStr">
         <is>
-          <t>1.9×</t>
+          <t>2.0×</t>
         </is>
       </c>
     </row>
@@ -9773,22 +9773,22 @@
       </c>
       <c r="C47" s="11" t="inlineStr">
         <is>
-          <t>NGX:ZENITHBANK</t>
+          <t>LSE:PDL</t>
         </is>
       </c>
       <c r="D47" s="11" t="inlineStr">
         <is>
-          <t>Zenith Bank</t>
+          <t>Petra Diamonds</t>
         </is>
       </c>
       <c r="E47" s="11" t="inlineStr">
         <is>
-          <t>MEA / Frontier</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="F47" s="11" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.60</t>
         </is>
       </c>
       <c r="G47" s="11" t="inlineStr">
@@ -9798,32 +9798,32 @@
       </c>
       <c r="H47" s="11" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>A1</t>
         </is>
       </c>
       <c r="I47" s="11" t="inlineStr">
         <is>
-          <t>42%</t>
+          <t>35%</t>
         </is>
       </c>
       <c r="J47" s="11" t="inlineStr">
         <is>
-          <t>2.11×</t>
+          <t>2.02×</t>
         </is>
       </c>
       <c r="K47" s="11" t="inlineStr">
         <is>
-          <t>2.64×</t>
+          <t>2.40×</t>
         </is>
       </c>
       <c r="L47" s="11" t="inlineStr">
         <is>
-          <t>1.78×</t>
+          <t>1.70×</t>
         </is>
       </c>
       <c r="M47" s="11" t="inlineStr">
         <is>
-          <t>1.9×</t>
+          <t>2.0×</t>
         </is>
       </c>
     </row>
@@ -9838,12 +9838,12 @@
       </c>
       <c r="C48" s="14" t="inlineStr">
         <is>
-          <t>NYSE:FLG</t>
+          <t>NYSE:MP</t>
         </is>
       </c>
       <c r="D48" s="14" t="inlineStr">
         <is>
-          <t>NYCB / Flagstar Financial</t>
+          <t>MP Materials Corp</t>
         </is>
       </c>
       <c r="E48" s="14" t="inlineStr">
@@ -9853,7 +9853,7 @@
       </c>
       <c r="F48" s="14" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="G48" s="14" t="inlineStr">
@@ -9863,7 +9863,7 @@
       </c>
       <c r="H48" s="14" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2</t>
         </is>
       </c>
       <c r="I48" s="14" t="inlineStr">
@@ -9873,7 +9873,7 @@
       </c>
       <c r="J48" s="14" t="inlineStr">
         <is>
-          <t>1.85×</t>
+          <t>1.80×</t>
         </is>
       </c>
       <c r="K48" s="14" t="inlineStr">
@@ -9883,12 +9883,12 @@
       </c>
       <c r="L48" s="14" t="inlineStr">
         <is>
-          <t>1.86×</t>
+          <t>1.90×</t>
         </is>
       </c>
       <c r="M48" s="14" t="inlineStr">
         <is>
-          <t>1.9×</t>
+          <t>2.0×</t>
         </is>
       </c>
     </row>
@@ -9903,22 +9903,22 @@
       </c>
       <c r="C49" s="11" t="inlineStr">
         <is>
-          <t>AEMD</t>
+          <t>NYSE:AENZ</t>
         </is>
       </c>
       <c r="D49" s="11" t="inlineStr">
         <is>
-          <t>AETHLON MEDICAL INC</t>
+          <t>Aenza (former Graña y Montero)</t>
         </is>
       </c>
       <c r="E49" s="11" t="inlineStr">
         <is>
-          <t>United States/Canada</t>
+          <t>Continental Europe</t>
         </is>
       </c>
       <c r="F49" s="11" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="G49" s="11" t="inlineStr">
@@ -9928,27 +9928,27 @@
       </c>
       <c r="H49" s="11" t="inlineStr">
         <is>
-          <t>F2</t>
+          <t>A2</t>
         </is>
       </c>
       <c r="I49" s="11" t="inlineStr">
         <is>
-          <t>42%</t>
+          <t>36%</t>
         </is>
       </c>
       <c r="J49" s="11" t="inlineStr">
         <is>
-          <t>2.12×</t>
+          <t>2.00×</t>
         </is>
       </c>
       <c r="K49" s="11" t="inlineStr">
         <is>
-          <t>2.66×</t>
+          <t>2.35×</t>
         </is>
       </c>
       <c r="L49" s="11" t="inlineStr">
         <is>
-          <t>1.79×</t>
+          <t>1.68×</t>
         </is>
       </c>
       <c r="M49" s="11" t="inlineStr">
@@ -9968,22 +9968,22 @@
       </c>
       <c r="C50" s="14" t="inlineStr">
         <is>
-          <t>EGX:COMI</t>
+          <t>KRX:034730</t>
         </is>
       </c>
       <c r="D50" s="14" t="inlineStr">
         <is>
-          <t>Egypt Commercial International Bank</t>
+          <t>SK Inc</t>
         </is>
       </c>
       <c r="E50" s="14" t="inlineStr">
         <is>
-          <t>MEA / Frontier</t>
+          <t>Korea</t>
         </is>
       </c>
       <c r="F50" s="14" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="G50" s="14" t="inlineStr">
@@ -9993,32 +9993,32 @@
       </c>
       <c r="H50" s="14" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>H</t>
         </is>
       </c>
       <c r="I50" s="14" t="inlineStr">
         <is>
-          <t>42%</t>
+          <t>44%</t>
         </is>
       </c>
       <c r="J50" s="14" t="inlineStr">
         <is>
-          <t>2.10×</t>
+          <t>2.17×</t>
         </is>
       </c>
       <c r="K50" s="14" t="inlineStr">
         <is>
-          <t>2.62×</t>
+          <t>2.79×</t>
         </is>
       </c>
       <c r="L50" s="14" t="inlineStr">
         <is>
-          <t>1.77×</t>
+          <t>1.84×</t>
         </is>
       </c>
       <c r="M50" s="14" t="inlineStr">
         <is>
-          <t>1.8×</t>
+          <t>1.9×</t>
         </is>
       </c>
     </row>
@@ -10033,12 +10033,12 @@
       </c>
       <c r="C51" s="11" t="inlineStr">
         <is>
-          <t>NGX:FIDELITYBK</t>
+          <t>NGX:ZENITHBANK</t>
         </is>
       </c>
       <c r="D51" s="11" t="inlineStr">
         <is>
-          <t>Fidelity Bank</t>
+          <t>Zenith Bank</t>
         </is>
       </c>
       <c r="E51" s="11" t="inlineStr">
@@ -10048,7 +10048,7 @@
       </c>
       <c r="F51" s="11" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="G51" s="11" t="inlineStr">
@@ -10063,27 +10063,27 @@
       </c>
       <c r="I51" s="11" t="inlineStr">
         <is>
-          <t>43%</t>
+          <t>42%</t>
         </is>
       </c>
       <c r="J51" s="11" t="inlineStr">
         <is>
-          <t>2.08×</t>
+          <t>2.11×</t>
         </is>
       </c>
       <c r="K51" s="11" t="inlineStr">
         <is>
-          <t>2.59×</t>
+          <t>2.64×</t>
         </is>
       </c>
       <c r="L51" s="11" t="inlineStr">
         <is>
-          <t>1.76×</t>
+          <t>1.78×</t>
         </is>
       </c>
       <c r="M51" s="11" t="inlineStr">
         <is>
-          <t>1.8×</t>
+          <t>1.9×</t>
         </is>
       </c>
     </row>
@@ -10091,29 +10091,29 @@
       <c r="A52" s="12" t="n">
         <v>48</v>
       </c>
-      <c r="B52" s="13" t="inlineStr">
-        <is>
-          <t>PROXY</t>
+      <c r="B52" s="16" t="inlineStr">
+        <is>
+          <t>REAL</t>
         </is>
       </c>
       <c r="C52" s="14" t="inlineStr">
         <is>
-          <t>KRX:034220</t>
+          <t>NYSE:FLG</t>
         </is>
       </c>
       <c r="D52" s="14" t="inlineStr">
         <is>
-          <t>LG Display</t>
+          <t>NYCB / Flagstar Financial</t>
         </is>
       </c>
       <c r="E52" s="14" t="inlineStr">
         <is>
-          <t>Korea</t>
+          <t>United States/Canada</t>
         </is>
       </c>
       <c r="F52" s="14" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="G52" s="14" t="inlineStr">
@@ -10123,32 +10123,32 @@
       </c>
       <c r="H52" s="14" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>A1</t>
         </is>
       </c>
       <c r="I52" s="14" t="inlineStr">
         <is>
-          <t>46%</t>
+          <t>45%</t>
         </is>
       </c>
       <c r="J52" s="14" t="inlineStr">
         <is>
-          <t>2.12×</t>
+          <t>1.85×</t>
         </is>
       </c>
       <c r="K52" s="14" t="inlineStr">
         <is>
-          <t>2.71×</t>
+          <t>3.20×</t>
         </is>
       </c>
       <c r="L52" s="14" t="inlineStr">
         <is>
-          <t>1.79×</t>
+          <t>1.86×</t>
         </is>
       </c>
       <c r="M52" s="14" t="inlineStr">
         <is>
-          <t>1.7×</t>
+          <t>1.9×</t>
         </is>
       </c>
     </row>
@@ -10163,22 +10163,22 @@
       </c>
       <c r="C53" s="11" t="inlineStr">
         <is>
-          <t>EGX:TMGH</t>
+          <t>AEMD</t>
         </is>
       </c>
       <c r="D53" s="11" t="inlineStr">
         <is>
-          <t>Talaat Moustafa Group</t>
+          <t>AETHLON MEDICAL INC</t>
         </is>
       </c>
       <c r="E53" s="11" t="inlineStr">
         <is>
-          <t>MEA / Frontier</t>
+          <t>United States/Canada</t>
         </is>
       </c>
       <c r="F53" s="11" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="G53" s="11" t="inlineStr">
@@ -10188,32 +10188,32 @@
       </c>
       <c r="H53" s="11" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>F2</t>
         </is>
       </c>
       <c r="I53" s="11" t="inlineStr">
         <is>
-          <t>43%</t>
+          <t>42%</t>
         </is>
       </c>
       <c r="J53" s="11" t="inlineStr">
         <is>
-          <t>2.07×</t>
+          <t>2.12×</t>
         </is>
       </c>
       <c r="K53" s="11" t="inlineStr">
         <is>
-          <t>2.58×</t>
+          <t>2.66×</t>
         </is>
       </c>
       <c r="L53" s="11" t="inlineStr">
         <is>
-          <t>1.75×</t>
+          <t>1.79×</t>
         </is>
       </c>
       <c r="M53" s="11" t="inlineStr">
         <is>
-          <t>1.7×</t>
+          <t>1.9×</t>
         </is>
       </c>
     </row>
@@ -10228,12 +10228,12 @@
       </c>
       <c r="C54" s="14" t="inlineStr">
         <is>
-          <t>NYSE:SBSW</t>
+          <t>EGX:COMI</t>
         </is>
       </c>
       <c r="D54" s="14" t="inlineStr">
         <is>
-          <t>Sibanye-Stillwater</t>
+          <t>Egypt Commercial International Bank</t>
         </is>
       </c>
       <c r="E54" s="14" t="inlineStr">
@@ -10243,12 +10243,12 @@
       </c>
       <c r="F54" s="14" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="G54" s="14" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H54" s="14" t="inlineStr">
@@ -10258,27 +10258,27 @@
       </c>
       <c r="I54" s="14" t="inlineStr">
         <is>
-          <t>44%</t>
+          <t>42%</t>
         </is>
       </c>
       <c r="J54" s="14" t="inlineStr">
         <is>
-          <t>2.06×</t>
+          <t>2.10×</t>
         </is>
       </c>
       <c r="K54" s="14" t="inlineStr">
         <is>
-          <t>2.56×</t>
+          <t>2.62×</t>
         </is>
       </c>
       <c r="L54" s="14" t="inlineStr">
         <is>
-          <t>1.74×</t>
+          <t>1.77×</t>
         </is>
       </c>
       <c r="M54" s="14" t="inlineStr">
         <is>
-          <t>1.7×</t>
+          <t>1.8×</t>
         </is>
       </c>
     </row>
@@ -10293,22 +10293,22 @@
       </c>
       <c r="C55" s="11" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>NGX:FIDELITYBK</t>
         </is>
       </c>
       <c r="D55" s="11" t="inlineStr">
         <is>
-          <t>MEMPHASYS LIMITED.</t>
+          <t>Fidelity Bank</t>
         </is>
       </c>
       <c r="E55" s="11" t="inlineStr">
         <is>
-          <t>SE Asia / Pacific</t>
+          <t>MEA / Frontier</t>
         </is>
       </c>
       <c r="F55" s="11" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="G55" s="11" t="inlineStr">
@@ -10318,32 +10318,32 @@
       </c>
       <c r="H55" s="11" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>G</t>
         </is>
       </c>
       <c r="I55" s="11" t="inlineStr">
         <is>
-          <t>44%</t>
+          <t>43%</t>
         </is>
       </c>
       <c r="J55" s="11" t="inlineStr">
         <is>
-          <t>2.06×</t>
+          <t>2.08×</t>
         </is>
       </c>
       <c r="K55" s="11" t="inlineStr">
         <is>
-          <t>2.56×</t>
+          <t>2.59×</t>
         </is>
       </c>
       <c r="L55" s="11" t="inlineStr">
         <is>
-          <t>1.74×</t>
+          <t>1.76×</t>
         </is>
       </c>
       <c r="M55" s="11" t="inlineStr">
         <is>
-          <t>1.7×</t>
+          <t>1.8×</t>
         </is>
       </c>
     </row>
@@ -10358,22 +10358,22 @@
       </c>
       <c r="C56" s="14" t="inlineStr">
         <is>
-          <t>CIK:0001348911</t>
+          <t>KRX:034220</t>
         </is>
       </c>
       <c r="D56" s="14" t="inlineStr">
         <is>
-          <t>KalVista Pharmaceuticals, Inc.</t>
+          <t>LG Display</t>
         </is>
       </c>
       <c r="E56" s="14" t="inlineStr">
         <is>
-          <t>United States/Canada</t>
+          <t>Korea</t>
         </is>
       </c>
       <c r="F56" s="14" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="G56" s="14" t="inlineStr">
@@ -10383,27 +10383,27 @@
       </c>
       <c r="H56" s="14" t="inlineStr">
         <is>
-          <t>K3</t>
+          <t>H</t>
         </is>
       </c>
       <c r="I56" s="14" t="inlineStr">
         <is>
-          <t>44%</t>
+          <t>46%</t>
         </is>
       </c>
       <c r="J56" s="14" t="inlineStr">
         <is>
-          <t>2.06×</t>
+          <t>2.12×</t>
         </is>
       </c>
       <c r="K56" s="14" t="inlineStr">
         <is>
-          <t>2.56×</t>
+          <t>2.71×</t>
         </is>
       </c>
       <c r="L56" s="14" t="inlineStr">
         <is>
-          <t>1.74×</t>
+          <t>1.79×</t>
         </is>
       </c>
       <c r="M56" s="14" t="inlineStr">
@@ -10423,22 +10423,22 @@
       </c>
       <c r="C57" s="11" t="inlineStr">
         <is>
-          <t>CIK:0001909770</t>
+          <t>EGX:TMGH</t>
         </is>
       </c>
       <c r="D57" s="11" t="inlineStr">
         <is>
-          <t>KHEOBA CORP.</t>
+          <t>Talaat Moustafa Group</t>
         </is>
       </c>
       <c r="E57" s="11" t="inlineStr">
         <is>
-          <t>United States/Canada</t>
+          <t>MEA / Frontier</t>
         </is>
       </c>
       <c r="F57" s="11" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="G57" s="11" t="inlineStr">
@@ -10448,27 +10448,27 @@
       </c>
       <c r="H57" s="11" t="inlineStr">
         <is>
-          <t>K3</t>
+          <t>G</t>
         </is>
       </c>
       <c r="I57" s="11" t="inlineStr">
         <is>
-          <t>44%</t>
+          <t>43%</t>
         </is>
       </c>
       <c r="J57" s="11" t="inlineStr">
         <is>
-          <t>2.06×</t>
+          <t>2.07×</t>
         </is>
       </c>
       <c r="K57" s="11" t="inlineStr">
         <is>
-          <t>2.56×</t>
+          <t>2.58×</t>
         </is>
       </c>
       <c r="L57" s="11" t="inlineStr">
         <is>
-          <t>1.74×</t>
+          <t>1.75×</t>
         </is>
       </c>
       <c r="M57" s="11" t="inlineStr">
@@ -10488,17 +10488,17 @@
       </c>
       <c r="C58" s="14" t="inlineStr">
         <is>
-          <t>CIK:0001489096</t>
+          <t>NYSE:SBSW</t>
         </is>
       </c>
       <c r="D58" s="14" t="inlineStr">
         <is>
-          <t>Thermon Group Holdings, Inc.</t>
+          <t>Sibanye-Stillwater</t>
         </is>
       </c>
       <c r="E58" s="14" t="inlineStr">
         <is>
-          <t>United States/Canada</t>
+          <t>MEA / Frontier</t>
         </is>
       </c>
       <c r="F58" s="14" t="inlineStr">
@@ -10508,12 +10508,12 @@
       </c>
       <c r="G58" s="14" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H58" s="14" t="inlineStr">
         <is>
-          <t>K3</t>
+          <t>G</t>
         </is>
       </c>
       <c r="I58" s="14" t="inlineStr">
@@ -10553,17 +10553,17 @@
       </c>
       <c r="C59" s="11" t="inlineStr">
         <is>
-          <t>WYTC</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="D59" s="11" t="inlineStr">
         <is>
-          <t>WYTEC INTERNATIONAL INC</t>
+          <t>MEMPHASYS LIMITED.</t>
         </is>
       </c>
       <c r="E59" s="11" t="inlineStr">
         <is>
-          <t>United States/Canada</t>
+          <t>SE Asia / Pacific</t>
         </is>
       </c>
       <c r="F59" s="11" t="inlineStr">
@@ -10578,7 +10578,7 @@
       </c>
       <c r="H59" s="11" t="inlineStr">
         <is>
-          <t>K3</t>
+          <t>B</t>
         </is>
       </c>
       <c r="I59" s="11" t="inlineStr">
@@ -10618,12 +10618,12 @@
       </c>
       <c r="C60" s="14" t="inlineStr">
         <is>
-          <t>CIK:0001408100</t>
+          <t>CIK:0001348911</t>
         </is>
       </c>
       <c r="D60" s="14" t="inlineStr">
         <is>
-          <t>Kennedy-Wilson Holdings, Inc.</t>
+          <t>KalVista Pharmaceuticals, Inc.</t>
         </is>
       </c>
       <c r="E60" s="14" t="inlineStr">
@@ -10683,12 +10683,12 @@
       </c>
       <c r="C61" s="11" t="inlineStr">
         <is>
-          <t>CIK:0002073537</t>
+          <t>CIK:0001909770</t>
         </is>
       </c>
       <c r="D61" s="11" t="inlineStr">
         <is>
-          <t>PIMCO Asset-Based Lending Co LLC</t>
+          <t>KHEOBA CORP.</t>
         </is>
       </c>
       <c r="E61" s="11" t="inlineStr">
@@ -10748,12 +10748,12 @@
       </c>
       <c r="C62" s="14" t="inlineStr">
         <is>
-          <t>VIASP</t>
+          <t>CIK:0001489096</t>
         </is>
       </c>
       <c r="D62" s="14" t="inlineStr">
         <is>
-          <t>Via Renewables, Inc.</t>
+          <t>Thermon Group Holdings, Inc.</t>
         </is>
       </c>
       <c r="E62" s="14" t="inlineStr">
@@ -10813,12 +10813,12 @@
       </c>
       <c r="C63" s="11" t="inlineStr">
         <is>
-          <t>CIK:0001117171</t>
+          <t>WYTC</t>
         </is>
       </c>
       <c r="D63" s="11" t="inlineStr">
         <is>
-          <t>CBAK Energy Technology, Inc.</t>
+          <t>WYTEC INTERNATIONAL INC</t>
         </is>
       </c>
       <c r="E63" s="11" t="inlineStr">
@@ -10878,12 +10878,12 @@
       </c>
       <c r="C64" s="14" t="inlineStr">
         <is>
-          <t>CIK:0001500305</t>
+          <t>CIK:0001408100</t>
         </is>
       </c>
       <c r="D64" s="14" t="inlineStr">
         <is>
-          <t>Sustainable Projects Group Inc.</t>
+          <t>Kennedy-Wilson Holdings, Inc.</t>
         </is>
       </c>
       <c r="E64" s="14" t="inlineStr">
@@ -10943,12 +10943,12 @@
       </c>
       <c r="C65" s="11" t="inlineStr">
         <is>
-          <t>CIK:0001127703</t>
+          <t>CIK:0002073537</t>
         </is>
       </c>
       <c r="D65" s="11" t="inlineStr">
         <is>
-          <t>PROASSURANCE CORP</t>
+          <t>PIMCO Asset-Based Lending Co LLC</t>
         </is>
       </c>
       <c r="E65" s="11" t="inlineStr">
@@ -11008,12 +11008,12 @@
       </c>
       <c r="C66" s="14" t="inlineStr">
         <is>
-          <t>CIK:0001900520</t>
+          <t>VIASP</t>
         </is>
       </c>
       <c r="D66" s="14" t="inlineStr">
         <is>
-          <t>Lomond Therapeutics Holdings, Inc.</t>
+          <t>Via Renewables, Inc.</t>
         </is>
       </c>
       <c r="E66" s="14" t="inlineStr">
@@ -11073,22 +11073,22 @@
       </c>
       <c r="C67" s="11" t="inlineStr">
         <is>
-          <t>HK:1918</t>
+          <t>CIK:0001117171</t>
         </is>
       </c>
       <c r="D67" s="11" t="inlineStr">
         <is>
-          <t>Sunac China</t>
+          <t>CBAK Energy Technology, Inc.</t>
         </is>
       </c>
       <c r="E67" s="11" t="inlineStr">
         <is>
-          <t>Greater China / HK</t>
+          <t>United States/Canada</t>
         </is>
       </c>
       <c r="F67" s="11" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="G67" s="11" t="inlineStr">
@@ -11098,32 +11098,32 @@
       </c>
       <c r="H67" s="11" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>K3</t>
         </is>
       </c>
       <c r="I67" s="11" t="inlineStr">
         <is>
-          <t>48%</t>
+          <t>44%</t>
         </is>
       </c>
       <c r="J67" s="11" t="inlineStr">
         <is>
-          <t>2.09×</t>
+          <t>2.06×</t>
         </is>
       </c>
       <c r="K67" s="11" t="inlineStr">
         <is>
-          <t>2.67×</t>
+          <t>2.56×</t>
         </is>
       </c>
       <c r="L67" s="11" t="inlineStr">
         <is>
-          <t>1.77×</t>
+          <t>1.74×</t>
         </is>
       </c>
       <c r="M67" s="11" t="inlineStr">
         <is>
-          <t>1.6×</t>
+          <t>1.7×</t>
         </is>
       </c>
     </row>
@@ -11138,22 +11138,22 @@
       </c>
       <c r="C68" s="14" t="inlineStr">
         <is>
-          <t>8074</t>
+          <t>CIK:0001500305</t>
         </is>
       </c>
       <c r="D68" s="14" t="inlineStr">
         <is>
-          <t>ＹＵＡＳＡ</t>
+          <t>Sustainable Projects Group Inc.</t>
         </is>
       </c>
       <c r="E68" s="14" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States/Canada</t>
         </is>
       </c>
       <c r="F68" s="14" t="inlineStr">
         <is>
-          <t>0.60</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="G68" s="14" t="inlineStr">
@@ -11163,32 +11163,32 @@
       </c>
       <c r="H68" s="14" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>K3</t>
         </is>
       </c>
       <c r="I68" s="14" t="inlineStr">
         <is>
-          <t>47%</t>
+          <t>44%</t>
         </is>
       </c>
       <c r="J68" s="14" t="inlineStr">
         <is>
-          <t>2.08×</t>
+          <t>2.06×</t>
         </is>
       </c>
       <c r="K68" s="14" t="inlineStr">
         <is>
-          <t>2.64×</t>
+          <t>2.56×</t>
         </is>
       </c>
       <c r="L68" s="14" t="inlineStr">
         <is>
-          <t>1.76×</t>
+          <t>1.74×</t>
         </is>
       </c>
       <c r="M68" s="14" t="inlineStr">
         <is>
-          <t>1.6×</t>
+          <t>1.7×</t>
         </is>
       </c>
     </row>
@@ -11203,22 +11203,22 @@
       </c>
       <c r="C69" s="11" t="inlineStr">
         <is>
-          <t>2198</t>
+          <t>CIK:0001127703</t>
         </is>
       </c>
       <c r="D69" s="11" t="inlineStr">
         <is>
-          <t>アイ・ケイ・ケイＨＤ</t>
+          <t>PROASSURANCE CORP</t>
         </is>
       </c>
       <c r="E69" s="11" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States/Canada</t>
         </is>
       </c>
       <c r="F69" s="11" t="inlineStr">
         <is>
-          <t>0.60</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="G69" s="11" t="inlineStr">
@@ -11228,32 +11228,32 @@
       </c>
       <c r="H69" s="11" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>K3</t>
         </is>
       </c>
       <c r="I69" s="11" t="inlineStr">
         <is>
-          <t>47%</t>
+          <t>44%</t>
         </is>
       </c>
       <c r="J69" s="11" t="inlineStr">
         <is>
-          <t>2.08×</t>
+          <t>2.06×</t>
         </is>
       </c>
       <c r="K69" s="11" t="inlineStr">
         <is>
-          <t>2.64×</t>
+          <t>2.56×</t>
         </is>
       </c>
       <c r="L69" s="11" t="inlineStr">
         <is>
-          <t>1.76×</t>
+          <t>1.74×</t>
         </is>
       </c>
       <c r="M69" s="11" t="inlineStr">
         <is>
-          <t>1.6×</t>
+          <t>1.7×</t>
         </is>
       </c>
     </row>
@@ -11268,22 +11268,22 @@
       </c>
       <c r="C70" s="14" t="inlineStr">
         <is>
-          <t>3454</t>
+          <t>CIK:0001900520</t>
         </is>
       </c>
       <c r="D70" s="14" t="inlineStr">
         <is>
-          <t>ファーストブラザーズ</t>
+          <t>Lomond Therapeutics Holdings, Inc.</t>
         </is>
       </c>
       <c r="E70" s="14" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States/Canada</t>
         </is>
       </c>
       <c r="F70" s="14" t="inlineStr">
         <is>
-          <t>0.60</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="G70" s="14" t="inlineStr">
@@ -11293,32 +11293,32 @@
       </c>
       <c r="H70" s="14" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>K3</t>
         </is>
       </c>
       <c r="I70" s="14" t="inlineStr">
         <is>
-          <t>47%</t>
+          <t>44%</t>
         </is>
       </c>
       <c r="J70" s="14" t="inlineStr">
         <is>
-          <t>2.08×</t>
+          <t>2.06×</t>
         </is>
       </c>
       <c r="K70" s="14" t="inlineStr">
         <is>
-          <t>2.64×</t>
+          <t>2.56×</t>
         </is>
       </c>
       <c r="L70" s="14" t="inlineStr">
         <is>
-          <t>1.76×</t>
+          <t>1.74×</t>
         </is>
       </c>
       <c r="M70" s="14" t="inlineStr">
         <is>
-          <t>1.6×</t>
+          <t>1.7×</t>
         </is>
       </c>
     </row>
@@ -11333,22 +11333,22 @@
       </c>
       <c r="C71" s="11" t="inlineStr">
         <is>
-          <t>4641</t>
+          <t>HK:1918</t>
         </is>
       </c>
       <c r="D71" s="11" t="inlineStr">
         <is>
-          <t>アルプス技</t>
+          <t>Sunac China</t>
         </is>
       </c>
       <c r="E71" s="11" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Greater China / HK</t>
         </is>
       </c>
       <c r="F71" s="11" t="inlineStr">
         <is>
-          <t>0.60</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="G71" s="11" t="inlineStr">
@@ -11358,27 +11358,27 @@
       </c>
       <c r="H71" s="11" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I71" s="11" t="inlineStr">
         <is>
-          <t>47%</t>
+          <t>48%</t>
         </is>
       </c>
       <c r="J71" s="11" t="inlineStr">
         <is>
-          <t>2.08×</t>
+          <t>2.09×</t>
         </is>
       </c>
       <c r="K71" s="11" t="inlineStr">
         <is>
-          <t>2.64×</t>
+          <t>2.67×</t>
         </is>
       </c>
       <c r="L71" s="11" t="inlineStr">
         <is>
-          <t>1.76×</t>
+          <t>1.77×</t>
         </is>
       </c>
       <c r="M71" s="11" t="inlineStr">
@@ -11398,12 +11398,12 @@
       </c>
       <c r="C72" s="14" t="inlineStr">
         <is>
-          <t>4170</t>
+          <t>8074</t>
         </is>
       </c>
       <c r="D72" s="14" t="inlineStr">
         <is>
-          <t>Ｇ－ＫａｉｚｅｎＰＦ</t>
+          <t>ＹＵＡＳＡ</t>
         </is>
       </c>
       <c r="E72" s="14" t="inlineStr">
@@ -11463,12 +11463,12 @@
       </c>
       <c r="C73" s="11" t="inlineStr">
         <is>
-          <t>TSE:6753</t>
+          <t>2198</t>
         </is>
       </c>
       <c r="D73" s="11" t="inlineStr">
         <is>
-          <t>Sharp</t>
+          <t>アイ・ケイ・ケイＨＤ</t>
         </is>
       </c>
       <c r="E73" s="11" t="inlineStr">
@@ -11478,7 +11478,7 @@
       </c>
       <c r="F73" s="11" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>0.60</t>
         </is>
       </c>
       <c r="G73" s="11" t="inlineStr">
@@ -11503,12 +11503,12 @@
       </c>
       <c r="K73" s="11" t="inlineStr">
         <is>
-          <t>2.62×</t>
+          <t>2.64×</t>
         </is>
       </c>
       <c r="L73" s="11" t="inlineStr">
         <is>
-          <t>1.75×</t>
+          <t>1.76×</t>
         </is>
       </c>
       <c r="M73" s="11" t="inlineStr">
@@ -11528,12 +11528,12 @@
       </c>
       <c r="C74" s="14" t="inlineStr">
         <is>
-          <t>3544</t>
+          <t>3454</t>
         </is>
       </c>
       <c r="D74" s="14" t="inlineStr">
         <is>
-          <t>サツドラＨＤ</t>
+          <t>ファーストブラザーズ</t>
         </is>
       </c>
       <c r="E74" s="14" t="inlineStr">
@@ -11543,7 +11543,7 @@
       </c>
       <c r="F74" s="14" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>0.60</t>
         </is>
       </c>
       <c r="G74" s="14" t="inlineStr">
@@ -11553,27 +11553,27 @@
       </c>
       <c r="H74" s="14" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>H</t>
         </is>
       </c>
       <c r="I74" s="14" t="inlineStr">
         <is>
-          <t>41%</t>
+          <t>47%</t>
         </is>
       </c>
       <c r="J74" s="14" t="inlineStr">
         <is>
-          <t>1.97×</t>
+          <t>2.08×</t>
         </is>
       </c>
       <c r="K74" s="14" t="inlineStr">
         <is>
-          <t>2.34×</t>
+          <t>2.64×</t>
         </is>
       </c>
       <c r="L74" s="14" t="inlineStr">
         <is>
-          <t>1.65×</t>
+          <t>1.76×</t>
         </is>
       </c>
       <c r="M74" s="14" t="inlineStr">
@@ -11593,12 +11593,12 @@
       </c>
       <c r="C75" s="11" t="inlineStr">
         <is>
-          <t>6897</t>
+          <t>4641</t>
         </is>
       </c>
       <c r="D75" s="11" t="inlineStr">
         <is>
-          <t>ツインバード</t>
+          <t>アルプス技</t>
         </is>
       </c>
       <c r="E75" s="11" t="inlineStr">
@@ -11608,7 +11608,7 @@
       </c>
       <c r="F75" s="11" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>0.60</t>
         </is>
       </c>
       <c r="G75" s="11" t="inlineStr">
@@ -11618,27 +11618,27 @@
       </c>
       <c r="H75" s="11" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>H</t>
         </is>
       </c>
       <c r="I75" s="11" t="inlineStr">
         <is>
-          <t>41%</t>
+          <t>47%</t>
         </is>
       </c>
       <c r="J75" s="11" t="inlineStr">
         <is>
-          <t>1.97×</t>
+          <t>2.08×</t>
         </is>
       </c>
       <c r="K75" s="11" t="inlineStr">
         <is>
-          <t>2.34×</t>
+          <t>2.64×</t>
         </is>
       </c>
       <c r="L75" s="11" t="inlineStr">
         <is>
-          <t>1.65×</t>
+          <t>1.76×</t>
         </is>
       </c>
       <c r="M75" s="11" t="inlineStr">
@@ -11658,12 +11658,12 @@
       </c>
       <c r="C76" s="14" t="inlineStr">
         <is>
-          <t>4951</t>
+          <t>4170</t>
         </is>
       </c>
       <c r="D76" s="14" t="inlineStr">
         <is>
-          <t>エステー</t>
+          <t>Ｇ－ＫａｉｚｅｎＰＦ</t>
         </is>
       </c>
       <c r="E76" s="14" t="inlineStr">
@@ -11673,7 +11673,7 @@
       </c>
       <c r="F76" s="14" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>0.60</t>
         </is>
       </c>
       <c r="G76" s="14" t="inlineStr">
@@ -11683,27 +11683,27 @@
       </c>
       <c r="H76" s="14" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>H</t>
         </is>
       </c>
       <c r="I76" s="14" t="inlineStr">
         <is>
-          <t>41%</t>
+          <t>47%</t>
         </is>
       </c>
       <c r="J76" s="14" t="inlineStr">
         <is>
-          <t>1.97×</t>
+          <t>2.08×</t>
         </is>
       </c>
       <c r="K76" s="14" t="inlineStr">
         <is>
-          <t>2.34×</t>
+          <t>2.64×</t>
         </is>
       </c>
       <c r="L76" s="14" t="inlineStr">
         <is>
-          <t>1.65×</t>
+          <t>1.76×</t>
         </is>
       </c>
       <c r="M76" s="14" t="inlineStr">
@@ -11723,12 +11723,12 @@
       </c>
       <c r="C77" s="11" t="inlineStr">
         <is>
-          <t>3659</t>
+          <t>TSE:6753</t>
         </is>
       </c>
       <c r="D77" s="11" t="inlineStr">
         <is>
-          <t>ネクソン</t>
+          <t>Sharp</t>
         </is>
       </c>
       <c r="E77" s="11" t="inlineStr">
@@ -11738,7 +11738,7 @@
       </c>
       <c r="F77" s="11" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="G77" s="11" t="inlineStr">
@@ -11748,27 +11748,27 @@
       </c>
       <c r="H77" s="11" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>H</t>
         </is>
       </c>
       <c r="I77" s="11" t="inlineStr">
         <is>
-          <t>41%</t>
+          <t>47%</t>
         </is>
       </c>
       <c r="J77" s="11" t="inlineStr">
         <is>
-          <t>1.97×</t>
+          <t>2.08×</t>
         </is>
       </c>
       <c r="K77" s="11" t="inlineStr">
         <is>
-          <t>2.34×</t>
+          <t>2.62×</t>
         </is>
       </c>
       <c r="L77" s="11" t="inlineStr">
         <is>
-          <t>1.65×</t>
+          <t>1.75×</t>
         </is>
       </c>
       <c r="M77" s="11" t="inlineStr">
@@ -11788,22 +11788,22 @@
       </c>
       <c r="C78" s="14" t="inlineStr">
         <is>
-          <t>B3:LIGT3</t>
+          <t>3544</t>
         </is>
       </c>
       <c r="D78" s="14" t="inlineStr">
         <is>
-          <t>Light SA</t>
+          <t>サツドラＨＤ</t>
         </is>
       </c>
       <c r="E78" s="14" t="inlineStr">
         <is>
-          <t>Latin America</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="F78" s="14" t="inlineStr">
         <is>
-          <t>0.58</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="G78" s="14" t="inlineStr">
@@ -11813,27 +11813,27 @@
       </c>
       <c r="H78" s="14" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>C</t>
         </is>
       </c>
       <c r="I78" s="14" t="inlineStr">
         <is>
-          <t>40%</t>
+          <t>41%</t>
         </is>
       </c>
       <c r="J78" s="14" t="inlineStr">
         <is>
-          <t>1.98×</t>
+          <t>1.97×</t>
         </is>
       </c>
       <c r="K78" s="14" t="inlineStr">
         <is>
-          <t>2.37×</t>
+          <t>2.34×</t>
         </is>
       </c>
       <c r="L78" s="14" t="inlineStr">
         <is>
-          <t>1.66×</t>
+          <t>1.65×</t>
         </is>
       </c>
       <c r="M78" s="14" t="inlineStr">
@@ -11853,22 +11853,22 @@
       </c>
       <c r="C79" s="11" t="inlineStr">
         <is>
-          <t>NGX:ACCESSCORP</t>
+          <t>6897</t>
         </is>
       </c>
       <c r="D79" s="11" t="inlineStr">
         <is>
-          <t>Access Holdings</t>
+          <t>ツインバード</t>
         </is>
       </c>
       <c r="E79" s="11" t="inlineStr">
         <is>
-          <t>MEA / Frontier</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="F79" s="11" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="G79" s="11" t="inlineStr">
@@ -11878,27 +11878,27 @@
       </c>
       <c r="H79" s="11" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>C</t>
         </is>
       </c>
       <c r="I79" s="11" t="inlineStr">
         <is>
-          <t>45%</t>
+          <t>41%</t>
         </is>
       </c>
       <c r="J79" s="11" t="inlineStr">
         <is>
-          <t>2.03×</t>
+          <t>1.97×</t>
         </is>
       </c>
       <c r="K79" s="11" t="inlineStr">
         <is>
-          <t>2.50×</t>
+          <t>2.34×</t>
         </is>
       </c>
       <c r="L79" s="11" t="inlineStr">
         <is>
-          <t>1.70×</t>
+          <t>1.65×</t>
         </is>
       </c>
       <c r="M79" s="11" t="inlineStr">
@@ -11918,17 +11918,17 @@
       </c>
       <c r="C80" s="14" t="inlineStr">
         <is>
-          <t>ERM</t>
+          <t>4951</t>
         </is>
       </c>
       <c r="D80" s="14" t="inlineStr">
         <is>
-          <t>EMMERSON RESOURCES LIMITED</t>
+          <t>エステー</t>
         </is>
       </c>
       <c r="E80" s="14" t="inlineStr">
         <is>
-          <t>SE Asia / Pacific</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="F80" s="14" t="inlineStr">
@@ -11943,7 +11943,7 @@
       </c>
       <c r="H80" s="14" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>C</t>
         </is>
       </c>
       <c r="I80" s="14" t="inlineStr">
@@ -11983,17 +11983,17 @@
       </c>
       <c r="C81" s="11" t="inlineStr">
         <is>
-          <t>PEX</t>
+          <t>3659</t>
         </is>
       </c>
       <c r="D81" s="11" t="inlineStr">
         <is>
-          <t>PEEL MINING LIMITED</t>
+          <t>ネクソン</t>
         </is>
       </c>
       <c r="E81" s="11" t="inlineStr">
         <is>
-          <t>SE Asia / Pacific</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="F81" s="11" t="inlineStr">
@@ -12008,7 +12008,7 @@
       </c>
       <c r="H81" s="11" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>C</t>
         </is>
       </c>
       <c r="I81" s="11" t="inlineStr">
@@ -12048,22 +12048,22 @@
       </c>
       <c r="C82" s="14" t="inlineStr">
         <is>
-          <t>AIS</t>
+          <t>B3:LIGT3</t>
         </is>
       </c>
       <c r="D82" s="14" t="inlineStr">
         <is>
-          <t>AERIS RESOURCES LIMITED</t>
+          <t>Light SA</t>
         </is>
       </c>
       <c r="E82" s="14" t="inlineStr">
         <is>
-          <t>SE Asia / Pacific</t>
+          <t>Latin America</t>
         </is>
       </c>
       <c r="F82" s="14" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>0.58</t>
         </is>
       </c>
       <c r="G82" s="14" t="inlineStr">
@@ -12078,22 +12078,22 @@
       </c>
       <c r="I82" s="14" t="inlineStr">
         <is>
-          <t>41%</t>
+          <t>40%</t>
         </is>
       </c>
       <c r="J82" s="14" t="inlineStr">
         <is>
-          <t>1.97×</t>
+          <t>1.98×</t>
         </is>
       </c>
       <c r="K82" s="14" t="inlineStr">
         <is>
-          <t>2.34×</t>
+          <t>2.37×</t>
         </is>
       </c>
       <c r="L82" s="14" t="inlineStr">
         <is>
-          <t>1.65×</t>
+          <t>1.66×</t>
         </is>
       </c>
       <c r="M82" s="14" t="inlineStr">
@@ -12113,17 +12113,17 @@
       </c>
       <c r="C83" s="11" t="inlineStr">
         <is>
-          <t>ASM</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D83" s="11" t="inlineStr">
         <is>
-          <t>AUSTRALIAN STRATEGIC MATERIALS LIMITED</t>
+          <t>ATOM EDUCAÇÃO E EDITORA S.A.</t>
         </is>
       </c>
       <c r="E83" s="11" t="inlineStr">
         <is>
-          <t>SE Asia / Pacific</t>
+          <t>Latin America</t>
         </is>
       </c>
       <c r="F83" s="11" t="inlineStr">
@@ -12138,7 +12138,7 @@
       </c>
       <c r="H83" s="11" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>C</t>
         </is>
       </c>
       <c r="I83" s="11" t="inlineStr">
@@ -12178,17 +12178,17 @@
       </c>
       <c r="C84" s="14" t="inlineStr">
         <is>
-          <t>QUB</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D84" s="14" t="inlineStr">
         <is>
-          <t>QUBE HOLDINGS LIMITED</t>
+          <t>OI S.A. - EM RECUPERAÇÃO JUDICIAL</t>
         </is>
       </c>
       <c r="E84" s="14" t="inlineStr">
         <is>
-          <t>SE Asia / Pacific</t>
+          <t>Latin America</t>
         </is>
       </c>
       <c r="F84" s="14" t="inlineStr">
@@ -12243,17 +12243,17 @@
       </c>
       <c r="C85" s="11" t="inlineStr">
         <is>
-          <t>NVA</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D85" s="11" t="inlineStr">
         <is>
-          <t>NOVA MINERALS CORP</t>
+          <t>PETTENATI S.A. INDUSTRIA TEXTIL</t>
         </is>
       </c>
       <c r="E85" s="11" t="inlineStr">
         <is>
-          <t>SE Asia / Pacific</t>
+          <t>Latin America</t>
         </is>
       </c>
       <c r="F85" s="11" t="inlineStr">
@@ -12268,7 +12268,7 @@
       </c>
       <c r="H85" s="11" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>C</t>
         </is>
       </c>
       <c r="I85" s="11" t="inlineStr">
@@ -12308,17 +12308,17 @@
       </c>
       <c r="C86" s="14" t="inlineStr">
         <is>
-          <t>PAF</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D86" s="14" t="inlineStr">
         <is>
-          <t>PAN AFRICAN RESOURCES PLC</t>
+          <t>BBM LOGÍSTICA S.A.</t>
         </is>
       </c>
       <c r="E86" s="14" t="inlineStr">
         <is>
-          <t>SE Asia / Pacific</t>
+          <t>Latin America</t>
         </is>
       </c>
       <c r="F86" s="14" t="inlineStr">
@@ -12373,17 +12373,17 @@
       </c>
       <c r="C87" s="11" t="inlineStr">
         <is>
-          <t>QOR</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D87" s="11" t="inlineStr">
         <is>
-          <t>QORIA LIMITED</t>
+          <t>GRUPO TOKY S.A.</t>
         </is>
       </c>
       <c r="E87" s="11" t="inlineStr">
         <is>
-          <t>SE Asia / Pacific</t>
+          <t>Latin America</t>
         </is>
       </c>
       <c r="F87" s="11" t="inlineStr">
@@ -12438,22 +12438,22 @@
       </c>
       <c r="C88" s="14" t="inlineStr">
         <is>
-          <t>LLM</t>
+          <t>NGX:ACCESSCORP</t>
         </is>
       </c>
       <c r="D88" s="14" t="inlineStr">
         <is>
-          <t>LOYAL METALS LTD</t>
+          <t>Access Holdings</t>
         </is>
       </c>
       <c r="E88" s="14" t="inlineStr">
         <is>
-          <t>SE Asia / Pacific</t>
+          <t>MEA / Frontier</t>
         </is>
       </c>
       <c r="F88" s="14" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="G88" s="14" t="inlineStr">
@@ -12463,27 +12463,27 @@
       </c>
       <c r="H88" s="14" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>G</t>
         </is>
       </c>
       <c r="I88" s="14" t="inlineStr">
         <is>
-          <t>41%</t>
+          <t>45%</t>
         </is>
       </c>
       <c r="J88" s="14" t="inlineStr">
         <is>
-          <t>1.97×</t>
+          <t>2.03×</t>
         </is>
       </c>
       <c r="K88" s="14" t="inlineStr">
         <is>
-          <t>2.34×</t>
+          <t>2.50×</t>
         </is>
       </c>
       <c r="L88" s="14" t="inlineStr">
         <is>
-          <t>1.65×</t>
+          <t>1.70×</t>
         </is>
       </c>
       <c r="M88" s="14" t="inlineStr">
@@ -12503,22 +12503,22 @@
       </c>
       <c r="C89" s="11" t="inlineStr">
         <is>
-          <t>EMI</t>
+          <t>ERM</t>
         </is>
       </c>
       <c r="D89" s="11" t="inlineStr">
         <is>
-          <t>Encore Medical, Inc.</t>
+          <t>EMMERSON RESOURCES LIMITED</t>
         </is>
       </c>
       <c r="E89" s="11" t="inlineStr">
         <is>
-          <t>United States/Canada</t>
+          <t>SE Asia / Pacific</t>
         </is>
       </c>
       <c r="F89" s="11" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="G89" s="11" t="inlineStr">
@@ -12528,27 +12528,27 @@
       </c>
       <c r="H89" s="11" t="inlineStr">
         <is>
-          <t>F2</t>
+          <t>E</t>
         </is>
       </c>
       <c r="I89" s="11" t="inlineStr">
         <is>
-          <t>44%</t>
+          <t>41%</t>
         </is>
       </c>
       <c r="J89" s="11" t="inlineStr">
         <is>
-          <t>2.05×</t>
+          <t>1.97×</t>
         </is>
       </c>
       <c r="K89" s="11" t="inlineStr">
         <is>
-          <t>2.54×</t>
+          <t>2.34×</t>
         </is>
       </c>
       <c r="L89" s="11" t="inlineStr">
         <is>
-          <t>1.72×</t>
+          <t>1.65×</t>
         </is>
       </c>
       <c r="M89" s="11" t="inlineStr">
@@ -12561,59 +12561,59 @@
       <c r="A90" s="12" t="n">
         <v>86</v>
       </c>
-      <c r="B90" s="16" t="inlineStr">
-        <is>
-          <t>REAL</t>
+      <c r="B90" s="13" t="inlineStr">
+        <is>
+          <t>PROXY</t>
         </is>
       </c>
       <c r="C90" s="14" t="inlineStr">
         <is>
-          <t>HKEX:SUNAC</t>
+          <t>PEX</t>
         </is>
       </c>
       <c r="D90" s="14" t="inlineStr">
         <is>
-          <t>Sunac China Holdings</t>
+          <t>PEEL MINING LIMITED</t>
         </is>
       </c>
       <c r="E90" s="14" t="inlineStr">
         <is>
-          <t>Greater China / HK</t>
+          <t>SE Asia / Pacific</t>
         </is>
       </c>
       <c r="F90" s="14" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="G90" s="14" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H90" s="14" t="inlineStr">
         <is>
-          <t>F+A</t>
+          <t>E</t>
         </is>
       </c>
       <c r="I90" s="14" t="inlineStr">
         <is>
-          <t>70%</t>
+          <t>41%</t>
         </is>
       </c>
       <c r="J90" s="14" t="inlineStr">
         <is>
-          <t>2.20×</t>
+          <t>1.97×</t>
         </is>
       </c>
       <c r="K90" s="14" t="inlineStr">
         <is>
-          <t>5.50×</t>
+          <t>2.34×</t>
         </is>
       </c>
       <c r="L90" s="14" t="inlineStr">
         <is>
-          <t>2.10×</t>
+          <t>1.65×</t>
         </is>
       </c>
       <c r="M90" s="14" t="inlineStr">
@@ -12633,22 +12633,22 @@
       </c>
       <c r="C91" s="11" t="inlineStr">
         <is>
-          <t>VIE:VOE</t>
+          <t>AIS</t>
         </is>
       </c>
       <c r="D91" s="11" t="inlineStr">
         <is>
-          <t>voestalpine</t>
+          <t>AERIS RESOURCES LIMITED</t>
         </is>
       </c>
       <c r="E91" s="11" t="inlineStr">
         <is>
-          <t>Continental Europe</t>
+          <t>SE Asia / Pacific</t>
         </is>
       </c>
       <c r="F91" s="11" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="G91" s="11" t="inlineStr">
@@ -12658,32 +12658,32 @@
       </c>
       <c r="H91" s="11" t="inlineStr">
         <is>
-          <t>A2+A1</t>
+          <t>E</t>
         </is>
       </c>
       <c r="I91" s="11" t="inlineStr">
         <is>
-          <t>38%</t>
+          <t>41%</t>
         </is>
       </c>
       <c r="J91" s="11" t="inlineStr">
         <is>
-          <t>1.90×</t>
+          <t>1.97×</t>
         </is>
       </c>
       <c r="K91" s="11" t="inlineStr">
         <is>
-          <t>2.19×</t>
+          <t>2.34×</t>
         </is>
       </c>
       <c r="L91" s="11" t="inlineStr">
         <is>
-          <t>1.59×</t>
+          <t>1.65×</t>
         </is>
       </c>
       <c r="M91" s="11" t="inlineStr">
         <is>
-          <t>1.5×</t>
+          <t>1.6×</t>
         </is>
       </c>
     </row>
@@ -12698,22 +12698,22 @@
       </c>
       <c r="C92" s="14" t="inlineStr">
         <is>
-          <t>private</t>
+          <t>ASM</t>
         </is>
       </c>
       <c r="D92" s="14" t="inlineStr">
         <is>
-          <t>Aeroportos do Brasil (Vinci)</t>
+          <t>AUSTRALIAN STRATEGIC MATERIALS LIMITED</t>
         </is>
       </c>
       <c r="E92" s="14" t="inlineStr">
         <is>
-          <t>Latin America</t>
+          <t>SE Asia / Pacific</t>
         </is>
       </c>
       <c r="F92" s="14" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="G92" s="14" t="inlineStr">
@@ -12723,32 +12723,32 @@
       </c>
       <c r="H92" s="14" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>E</t>
         </is>
       </c>
       <c r="I92" s="14" t="inlineStr">
         <is>
-          <t>39%</t>
+          <t>41%</t>
         </is>
       </c>
       <c r="J92" s="14" t="inlineStr">
         <is>
-          <t>1.89×</t>
+          <t>1.97×</t>
         </is>
       </c>
       <c r="K92" s="14" t="inlineStr">
         <is>
-          <t>2.16×</t>
+          <t>2.34×</t>
         </is>
       </c>
       <c r="L92" s="14" t="inlineStr">
         <is>
-          <t>1.57×</t>
+          <t>1.65×</t>
         </is>
       </c>
       <c r="M92" s="14" t="inlineStr">
         <is>
-          <t>1.5×</t>
+          <t>1.6×</t>
         </is>
       </c>
     </row>
@@ -12763,22 +12763,22 @@
       </c>
       <c r="C93" s="11" t="inlineStr">
         <is>
-          <t>NGX:UBA</t>
+          <t>QUB</t>
         </is>
       </c>
       <c r="D93" s="11" t="inlineStr">
         <is>
-          <t>UBA</t>
+          <t>QUBE HOLDINGS LIMITED</t>
         </is>
       </c>
       <c r="E93" s="11" t="inlineStr">
         <is>
-          <t>MEA / Frontier</t>
+          <t>SE Asia / Pacific</t>
         </is>
       </c>
       <c r="F93" s="11" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="G93" s="11" t="inlineStr">
@@ -12788,32 +12788,32 @@
       </c>
       <c r="H93" s="11" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>E</t>
         </is>
       </c>
       <c r="I93" s="11" t="inlineStr">
         <is>
-          <t>45%</t>
+          <t>41%</t>
         </is>
       </c>
       <c r="J93" s="11" t="inlineStr">
         <is>
-          <t>2.02×</t>
+          <t>1.97×</t>
         </is>
       </c>
       <c r="K93" s="11" t="inlineStr">
         <is>
-          <t>2.49×</t>
+          <t>2.34×</t>
         </is>
       </c>
       <c r="L93" s="11" t="inlineStr">
         <is>
-          <t>1.70×</t>
+          <t>1.65×</t>
         </is>
       </c>
       <c r="M93" s="11" t="inlineStr">
         <is>
-          <t>1.5×</t>
+          <t>1.6×</t>
         </is>
       </c>
     </row>
@@ -12828,22 +12828,22 @@
       </c>
       <c r="C94" s="14" t="inlineStr">
         <is>
-          <t>JSE:EOH</t>
+          <t>NVA</t>
         </is>
       </c>
       <c r="D94" s="14" t="inlineStr">
         <is>
-          <t>EOH Holdings</t>
+          <t>NOVA MINERALS CORP</t>
         </is>
       </c>
       <c r="E94" s="14" t="inlineStr">
         <is>
-          <t>MEA / Frontier</t>
+          <t>SE Asia / Pacific</t>
         </is>
       </c>
       <c r="F94" s="14" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="G94" s="14" t="inlineStr">
@@ -12853,32 +12853,32 @@
       </c>
       <c r="H94" s="14" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>E</t>
         </is>
       </c>
       <c r="I94" s="14" t="inlineStr">
         <is>
-          <t>46%</t>
+          <t>41%</t>
         </is>
       </c>
       <c r="J94" s="14" t="inlineStr">
         <is>
-          <t>2.00×</t>
+          <t>1.97×</t>
         </is>
       </c>
       <c r="K94" s="14" t="inlineStr">
         <is>
-          <t>2.46×</t>
+          <t>2.34×</t>
         </is>
       </c>
       <c r="L94" s="14" t="inlineStr">
         <is>
-          <t>1.68×</t>
+          <t>1.65×</t>
         </is>
       </c>
       <c r="M94" s="14" t="inlineStr">
         <is>
-          <t>1.5×</t>
+          <t>1.6×</t>
         </is>
       </c>
     </row>
@@ -12893,22 +12893,22 @@
       </c>
       <c r="C95" s="11" t="inlineStr">
         <is>
-          <t>CIK:0001783876</t>
+          <t>PAF</t>
         </is>
       </c>
       <c r="D95" s="11" t="inlineStr">
         <is>
-          <t>Teamshares Inc.</t>
+          <t>PAN AFRICAN RESOURCES PLC</t>
         </is>
       </c>
       <c r="E95" s="11" t="inlineStr">
         <is>
-          <t>United States/Canada</t>
+          <t>SE Asia / Pacific</t>
         </is>
       </c>
       <c r="F95" s="11" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="G95" s="11" t="inlineStr">
@@ -12918,32 +12918,32 @@
       </c>
       <c r="H95" s="11" t="inlineStr">
         <is>
-          <t>K3</t>
+          <t>E</t>
         </is>
       </c>
       <c r="I95" s="11" t="inlineStr">
         <is>
-          <t>46%</t>
+          <t>41%</t>
         </is>
       </c>
       <c r="J95" s="11" t="inlineStr">
         <is>
-          <t>2.00×</t>
+          <t>1.97×</t>
         </is>
       </c>
       <c r="K95" s="11" t="inlineStr">
         <is>
-          <t>2.46×</t>
+          <t>2.34×</t>
         </is>
       </c>
       <c r="L95" s="11" t="inlineStr">
         <is>
-          <t>1.68×</t>
+          <t>1.65×</t>
         </is>
       </c>
       <c r="M95" s="11" t="inlineStr">
         <is>
-          <t>1.5×</t>
+          <t>1.6×</t>
         </is>
       </c>
     </row>
@@ -12958,22 +12958,22 @@
       </c>
       <c r="C96" s="14" t="inlineStr">
         <is>
-          <t>CIK:0001574219</t>
+          <t>QOR</t>
         </is>
       </c>
       <c r="D96" s="14" t="inlineStr">
         <is>
-          <t>J.P. Morgan Chase Commercial Mortgage Securities T</t>
+          <t>QORIA LIMITED</t>
         </is>
       </c>
       <c r="E96" s="14" t="inlineStr">
         <is>
-          <t>United States/Canada</t>
+          <t>SE Asia / Pacific</t>
         </is>
       </c>
       <c r="F96" s="14" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="G96" s="14" t="inlineStr">
@@ -12983,32 +12983,32 @@
       </c>
       <c r="H96" s="14" t="inlineStr">
         <is>
-          <t>K3</t>
+          <t>E</t>
         </is>
       </c>
       <c r="I96" s="14" t="inlineStr">
         <is>
-          <t>46%</t>
+          <t>41%</t>
         </is>
       </c>
       <c r="J96" s="14" t="inlineStr">
         <is>
-          <t>2.00×</t>
+          <t>1.97×</t>
         </is>
       </c>
       <c r="K96" s="14" t="inlineStr">
         <is>
-          <t>2.46×</t>
+          <t>2.34×</t>
         </is>
       </c>
       <c r="L96" s="14" t="inlineStr">
         <is>
-          <t>1.68×</t>
+          <t>1.65×</t>
         </is>
       </c>
       <c r="M96" s="14" t="inlineStr">
         <is>
-          <t>1.5×</t>
+          <t>1.6×</t>
         </is>
       </c>
     </row>
@@ -13023,22 +13023,22 @@
       </c>
       <c r="C97" s="11" t="inlineStr">
         <is>
-          <t>TSE:6740</t>
+          <t>LLM</t>
         </is>
       </c>
       <c r="D97" s="11" t="inlineStr">
         <is>
-          <t>Japan Display</t>
+          <t>LOYAL METALS LTD</t>
         </is>
       </c>
       <c r="E97" s="11" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>SE Asia / Pacific</t>
         </is>
       </c>
       <c r="F97" s="11" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="G97" s="11" t="inlineStr">
@@ -13048,32 +13048,32 @@
       </c>
       <c r="H97" s="11" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>E</t>
         </is>
       </c>
       <c r="I97" s="11" t="inlineStr">
         <is>
-          <t>49%</t>
+          <t>41%</t>
         </is>
       </c>
       <c r="J97" s="11" t="inlineStr">
         <is>
-          <t>2.03×</t>
+          <t>1.97×</t>
         </is>
       </c>
       <c r="K97" s="11" t="inlineStr">
         <is>
-          <t>2.54×</t>
+          <t>2.34×</t>
         </is>
       </c>
       <c r="L97" s="11" t="inlineStr">
         <is>
-          <t>1.70×</t>
+          <t>1.65×</t>
         </is>
       </c>
       <c r="M97" s="11" t="inlineStr">
         <is>
-          <t>1.4×</t>
+          <t>1.6×</t>
         </is>
       </c>
     </row>
@@ -13088,22 +13088,22 @@
       </c>
       <c r="C98" s="14" t="inlineStr">
         <is>
-          <t>TSE</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D98" s="14" t="inlineStr">
         <is>
-          <t>Rapidus-adjacent suppliers</t>
+          <t>REDCENTRIC PLC</t>
         </is>
       </c>
       <c r="E98" s="14" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="F98" s="14" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="G98" s="14" t="inlineStr">
@@ -13113,32 +13113,32 @@
       </c>
       <c r="H98" s="14" t="inlineStr">
         <is>
-          <t>A2+H</t>
+          <t>C</t>
         </is>
       </c>
       <c r="I98" s="14" t="inlineStr">
         <is>
-          <t>42%</t>
+          <t>41%</t>
         </is>
       </c>
       <c r="J98" s="14" t="inlineStr">
         <is>
-          <t>1.88×</t>
+          <t>1.97×</t>
         </is>
       </c>
       <c r="K98" s="14" t="inlineStr">
         <is>
-          <t>2.18×</t>
+          <t>2.34×</t>
         </is>
       </c>
       <c r="L98" s="14" t="inlineStr">
         <is>
-          <t>1.57×</t>
+          <t>1.65×</t>
         </is>
       </c>
       <c r="M98" s="14" t="inlineStr">
         <is>
-          <t>1.4×</t>
+          <t>1.6×</t>
         </is>
       </c>
     </row>
@@ -13153,22 +13153,22 @@
       </c>
       <c r="C99" s="11" t="inlineStr">
         <is>
-          <t>NZX:SML</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D99" s="11" t="inlineStr">
         <is>
-          <t>Synlait Milk</t>
+          <t>CT HEALTHCARE TRUST PLC</t>
         </is>
       </c>
       <c r="E99" s="11" t="inlineStr">
         <is>
-          <t>SE Asia / Pacific</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="F99" s="11" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="G99" s="11" t="inlineStr">
@@ -13178,12 +13178,12 @@
       </c>
       <c r="H99" s="11" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="I99" s="11" t="inlineStr">
         <is>
-          <t>47%</t>
+          <t>41%</t>
         </is>
       </c>
       <c r="J99" s="11" t="inlineStr">
@@ -13193,7 +13193,7 @@
       </c>
       <c r="K99" s="11" t="inlineStr">
         <is>
-          <t>2.42×</t>
+          <t>2.34×</t>
         </is>
       </c>
       <c r="L99" s="11" t="inlineStr">
@@ -13203,7 +13203,7 @@
       </c>
       <c r="M99" s="11" t="inlineStr">
         <is>
-          <t>1.4×</t>
+          <t>1.6×</t>
         </is>
       </c>
     </row>
@@ -13218,12 +13218,12 @@
       </c>
       <c r="C100" s="14" t="inlineStr">
         <is>
-          <t>LSE:MTRO</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D100" s="14" t="inlineStr">
         <is>
-          <t>Metro Bank</t>
+          <t>JUST GROUP PLC</t>
         </is>
       </c>
       <c r="E100" s="14" t="inlineStr">
@@ -13233,7 +13233,7 @@
       </c>
       <c r="F100" s="14" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="G100" s="14" t="inlineStr">
@@ -13243,32 +13243,32 @@
       </c>
       <c r="H100" s="14" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>C</t>
         </is>
       </c>
       <c r="I100" s="14" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>41%</t>
         </is>
       </c>
       <c r="J100" s="14" t="inlineStr">
         <is>
-          <t>2.00×</t>
+          <t>1.97×</t>
         </is>
       </c>
       <c r="K100" s="14" t="inlineStr">
         <is>
-          <t>2.49×</t>
+          <t>2.34×</t>
         </is>
       </c>
       <c r="L100" s="14" t="inlineStr">
         <is>
-          <t>1.67×</t>
+          <t>1.65×</t>
         </is>
       </c>
       <c r="M100" s="14" t="inlineStr">
         <is>
-          <t>1.4×</t>
+          <t>1.6×</t>
         </is>
       </c>
     </row>
@@ -13283,12 +13283,12 @@
       </c>
       <c r="C101" s="11" t="inlineStr">
         <is>
-          <t>LSE:VANQ</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D101" s="11" t="inlineStr">
         <is>
-          <t>Provident Financial → Vanquis Banking</t>
+          <t>Zambia (Republic of) (MoF)</t>
         </is>
       </c>
       <c r="E101" s="11" t="inlineStr">
@@ -13298,42 +13298,42 @@
       </c>
       <c r="F101" s="11" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="G101" s="11" t="inlineStr">
         <is>
-          <t>A (warn)</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H101" s="11" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>C</t>
         </is>
       </c>
       <c r="I101" s="11" t="inlineStr">
         <is>
-          <t>39%</t>
+          <t>41%</t>
         </is>
       </c>
       <c r="J101" s="11" t="inlineStr">
         <is>
-          <t>1.88×</t>
+          <t>1.97×</t>
         </is>
       </c>
       <c r="K101" s="11" t="inlineStr">
         <is>
-          <t>2.15×</t>
+          <t>2.34×</t>
         </is>
       </c>
       <c r="L101" s="11" t="inlineStr">
         <is>
-          <t>1.56×</t>
+          <t>1.65×</t>
         </is>
       </c>
       <c r="M101" s="11" t="inlineStr">
         <is>
-          <t>1.4×</t>
+          <t>1.6×</t>
         </is>
       </c>
     </row>
@@ -13348,22 +13348,22 @@
       </c>
       <c r="C102" s="14" t="inlineStr">
         <is>
-          <t>VIE:WIE</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D102" s="14" t="inlineStr">
         <is>
-          <t>Wienerberger</t>
+          <t>LEGAL &amp; GENERAL GROUP PLC</t>
         </is>
       </c>
       <c r="E102" s="14" t="inlineStr">
         <is>
-          <t>Continental Europe</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="F102" s="14" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="G102" s="14" t="inlineStr">
@@ -13373,7 +13373,7 @@
       </c>
       <c r="H102" s="14" t="inlineStr">
         <is>
-          <t>A2</t>
+          <t>C</t>
         </is>
       </c>
       <c r="I102" s="14" t="inlineStr">
@@ -13383,22 +13383,22 @@
       </c>
       <c r="J102" s="14" t="inlineStr">
         <is>
-          <t>1.81×</t>
+          <t>1.97×</t>
         </is>
       </c>
       <c r="K102" s="14" t="inlineStr">
         <is>
-          <t>2.02×</t>
+          <t>2.34×</t>
         </is>
       </c>
       <c r="L102" s="14" t="inlineStr">
         <is>
-          <t>1.50×</t>
+          <t>1.65×</t>
         </is>
       </c>
       <c r="M102" s="14" t="inlineStr">
         <is>
-          <t>1.2×</t>
+          <t>1.6×</t>
         </is>
       </c>
     </row>
@@ -13413,22 +13413,22 @@
       </c>
       <c r="C103" s="11" t="inlineStr">
         <is>
-          <t>EPA:FER</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D103" s="11" t="inlineStr">
         <is>
-          <t>Ferrovial</t>
+          <t>Treatt PLC</t>
         </is>
       </c>
       <c r="E103" s="11" t="inlineStr">
         <is>
-          <t>Continental Europe</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="F103" s="11" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="G103" s="11" t="inlineStr">
@@ -13438,7 +13438,7 @@
       </c>
       <c r="H103" s="11" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>E</t>
         </is>
       </c>
       <c r="I103" s="11" t="inlineStr">
@@ -13448,22 +13448,22 @@
       </c>
       <c r="J103" s="11" t="inlineStr">
         <is>
-          <t>1.81×</t>
+          <t>1.97×</t>
         </is>
       </c>
       <c r="K103" s="11" t="inlineStr">
         <is>
-          <t>2.02×</t>
+          <t>2.34×</t>
         </is>
       </c>
       <c r="L103" s="11" t="inlineStr">
         <is>
-          <t>1.50×</t>
+          <t>1.65×</t>
         </is>
       </c>
       <c r="M103" s="11" t="inlineStr">
         <is>
-          <t>1.2×</t>
+          <t>1.6×</t>
         </is>
       </c>
     </row>
@@ -13478,22 +13478,22 @@
       </c>
       <c r="C104" s="14" t="inlineStr">
         <is>
-          <t>SIX:HOLN</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D104" s="14" t="inlineStr">
         <is>
-          <t>Holcim</t>
+          <t>GLOBALDATA PLC</t>
         </is>
       </c>
       <c r="E104" s="14" t="inlineStr">
         <is>
-          <t>Continental Europe</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="F104" s="14" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="G104" s="14" t="inlineStr">
@@ -13503,7 +13503,7 @@
       </c>
       <c r="H104" s="14" t="inlineStr">
         <is>
-          <t>A2</t>
+          <t>C</t>
         </is>
       </c>
       <c r="I104" s="14" t="inlineStr">
@@ -13513,22 +13513,22 @@
       </c>
       <c r="J104" s="14" t="inlineStr">
         <is>
-          <t>1.80×</t>
+          <t>1.97×</t>
         </is>
       </c>
       <c r="K104" s="14" t="inlineStr">
         <is>
-          <t>2.01×</t>
+          <t>2.34×</t>
         </is>
       </c>
       <c r="L104" s="14" t="inlineStr">
         <is>
-          <t>1.49×</t>
+          <t>1.65×</t>
         </is>
       </c>
       <c r="M104" s="14" t="inlineStr">
         <is>
-          <t>1.2×</t>
+          <t>1.6×</t>
         </is>
       </c>
     </row>
@@ -13536,7 +13536,7 @@
     <row r="106" ht="60" customHeight="1">
       <c r="A106" s="7" t="inlineStr">
         <is>
-          <t>Reward/Risk = (EV× − 1) ÷ Bear loss = the asymmetry metric.  The broad universe-screener scores the full candidate set on archetype, vintage, status, size, region, and cross-source corroboration; this asymmetric scan ranks the investable subset (221 names) by reward/risk. Investable filter drops PASS_FALSE_FRIEND / ACQUIRED / ARC_DONE / REPEAT_RX and non-equity placeholder tickers ((state), (private), (delisted)). PROXY waterfall: bear_loss = max(0.10, 0.65 − 0.30·score), tilted ×0.75 for A1/A2 (sovereign-anchored floor). bull = 1.50 + 1.50·score, tilted ×1.10 for H, ×1.15 for F. Hand-built YAMLs override the proxy with bottom-up numbers.</t>
+          <t>Reward/Risk = (EV× − 1) ÷ Bear loss = the asymmetry metric.  The broad universe-screener scores the full candidate set on archetype, vintage, status, size, region, and cross-source corroboration; this asymmetric scan ranks the investable subset (288 names) by reward/risk. Investable filter drops PASS_FALSE_FRIEND / ACQUIRED / ARC_DONE / REPEAT_RX and non-equity placeholder tickers ((state), (private), (delisted)). PROXY waterfall: bear_loss = max(0.10, 0.65 − 0.30·score), tilted ×0.75 for A1/A2 (sovereign-anchored floor). bull = 1.50 + 1.50·score, tilted ×1.10 for H, ×1.15 for F. Hand-built YAMLs override the proxy with bottom-up numbers.</t>
         </is>
       </c>
     </row>
@@ -13572,7 +13572,7 @@
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="37" customWidth="1" min="3" max="3"/>
+    <col width="49" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
     <col width="8" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
@@ -13923,22 +13923,22 @@
       </c>
       <c r="B12" s="14" t="inlineStr">
         <is>
-          <t>LSE:ASC</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C12" s="14" t="inlineStr">
         <is>
-          <t>ASOS</t>
+          <t>IRANI PAPEL E EMBALAGEM S.A.</t>
         </is>
       </c>
       <c r="D12" s="14" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Latin America</t>
         </is>
       </c>
       <c r="E12" s="14" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="F12" s="14" t="inlineStr">
@@ -13963,27 +13963,27 @@
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>TBRG</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>TruBridge, Inc.</t>
+          <t>COMERC ENERGIA S.A.</t>
         </is>
       </c>
       <c r="D13" s="11" t="inlineStr">
         <is>
-          <t>United States/Canada</t>
+          <t>Latin America</t>
         </is>
       </c>
       <c r="E13" s="11" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="F13" s="11" t="inlineStr">
         <is>
-          <t>K3</t>
+          <t>A1</t>
         </is>
       </c>
       <c r="G13" s="11" t="inlineStr">
@@ -13993,7 +13993,7 @@
       </c>
       <c r="H13" s="11" t="inlineStr">
         <is>
-          <t>Tier 1 — hand-deepen ASAP</t>
+          <t>Tier 2 — verify primary docs first</t>
         </is>
       </c>
     </row>
@@ -14003,27 +14003,27 @@
       </c>
       <c r="B14" s="14" t="inlineStr">
         <is>
-          <t>LEG</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C14" s="14" t="inlineStr">
         <is>
-          <t>LEGGETT &amp; PLATT INC</t>
+          <t>SOCIEDADE ABASTECIMENTO DE AGUA E SANEAMENTO SA</t>
         </is>
       </c>
       <c r="D14" s="14" t="inlineStr">
         <is>
-          <t>United States/Canada</t>
+          <t>Latin America</t>
         </is>
       </c>
       <c r="E14" s="14" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="F14" s="14" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A1</t>
         </is>
       </c>
       <c r="G14" s="14" t="inlineStr">
@@ -14033,32 +14033,32 @@
       </c>
       <c r="H14" s="14" t="inlineStr">
         <is>
-          <t>Tier 1 — hand-deepen ASAP</t>
+          <t>Tier 2 — verify primary docs first</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="9" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>TSX:CFW</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C15" s="11" t="inlineStr">
         <is>
-          <t>Calfrac Well Services</t>
+          <t>MINERVA S/A</t>
         </is>
       </c>
       <c r="D15" s="11" t="inlineStr">
         <is>
-          <t>United States/Canada</t>
+          <t>Latin America</t>
         </is>
       </c>
       <c r="E15" s="11" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="F15" s="11" t="inlineStr">
@@ -14068,7 +14068,7 @@
       </c>
       <c r="G15" s="11" t="inlineStr">
         <is>
-          <t>2.5×</t>
+          <t>2.6×</t>
         </is>
       </c>
       <c r="H15" s="11" t="inlineStr">
@@ -14079,96 +14079,96 @@
     </row>
     <row r="16">
       <c r="A16" s="12" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B16" s="14" t="inlineStr">
         <is>
-          <t>KRX:028260</t>
+          <t>LSE:ASC</t>
         </is>
       </c>
       <c r="C16" s="14" t="inlineStr">
         <is>
-          <t>Samsung C&amp;T</t>
+          <t>ASOS</t>
         </is>
       </c>
       <c r="D16" s="14" t="inlineStr">
         <is>
-          <t>Korea</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="E16" s="14" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="F16" s="14" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>A1</t>
         </is>
       </c>
       <c r="G16" s="14" t="inlineStr">
         <is>
-          <t>2.4×</t>
+          <t>2.6×</t>
         </is>
       </c>
       <c r="H16" s="14" t="inlineStr">
         <is>
-          <t>Tier 1 — hand-deepen ASAP</t>
+          <t>Tier 2 — verify primary docs first</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="9" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>LSE:AML</t>
+          <t>TBRG</t>
         </is>
       </c>
       <c r="C17" s="11" t="inlineStr">
         <is>
-          <t>Aston Martin Lagonda</t>
+          <t>TruBridge, Inc.</t>
         </is>
       </c>
       <c r="D17" s="11" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>United States/Canada</t>
         </is>
       </c>
       <c r="E17" s="11" t="inlineStr">
         <is>
-          <t>0.70</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="F17" s="11" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>K3</t>
         </is>
       </c>
       <c r="G17" s="11" t="inlineStr">
         <is>
-          <t>2.4×</t>
+          <t>2.6×</t>
         </is>
       </c>
       <c r="H17" s="11" t="inlineStr">
         <is>
-          <t>Tier 2 — verify primary docs first</t>
+          <t>Tier 1 — hand-deepen ASAP</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="12" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B18" s="14" t="inlineStr">
         <is>
-          <t>APTOF</t>
+          <t>LEG</t>
         </is>
       </c>
       <c r="C18" s="14" t="inlineStr">
         <is>
-          <t>Aptose Biosciences Inc.</t>
+          <t>LEGGETT &amp; PLATT INC</t>
         </is>
       </c>
       <c r="D18" s="14" t="inlineStr">
@@ -14178,17 +14178,17 @@
       </c>
       <c r="E18" s="14" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="F18" s="14" t="inlineStr">
         <is>
-          <t>K3</t>
+          <t>C</t>
         </is>
       </c>
       <c r="G18" s="14" t="inlineStr">
         <is>
-          <t>2.4×</t>
+          <t>2.6×</t>
         </is>
       </c>
       <c r="H18" s="14" t="inlineStr">
@@ -14203,22 +14203,22 @@
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>HK:2202</t>
+          <t>TSX:CFW</t>
         </is>
       </c>
       <c r="C19" s="11" t="inlineStr">
         <is>
-          <t>Vanke</t>
+          <t>Calfrac Well Services</t>
         </is>
       </c>
       <c r="D19" s="11" t="inlineStr">
         <is>
-          <t>Greater China / HK</t>
+          <t>United States/Canada</t>
         </is>
       </c>
       <c r="E19" s="11" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="F19" s="11" t="inlineStr">
@@ -14228,7 +14228,7 @@
       </c>
       <c r="G19" s="11" t="inlineStr">
         <is>
-          <t>2.3×</t>
+          <t>2.5×</t>
         </is>
       </c>
       <c r="H19" s="11" t="inlineStr">
@@ -14243,37 +14243,37 @@
       </c>
       <c r="B20" s="14" t="inlineStr">
         <is>
-          <t>LSE:VOD</t>
+          <t>KRX:028260</t>
         </is>
       </c>
       <c r="C20" s="14" t="inlineStr">
         <is>
-          <t>Vodafone</t>
+          <t>Samsung C&amp;T</t>
         </is>
       </c>
       <c r="D20" s="14" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Korea</t>
         </is>
       </c>
       <c r="E20" s="14" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="F20" s="14" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>H</t>
         </is>
       </c>
       <c r="G20" s="14" t="inlineStr">
         <is>
-          <t>2.3×</t>
+          <t>2.4×</t>
         </is>
       </c>
       <c r="H20" s="14" t="inlineStr">
         <is>
-          <t>Tier 2 — verify primary docs first</t>
+          <t>Tier 1 — hand-deepen ASAP</t>
         </is>
       </c>
     </row>
@@ -14283,12 +14283,12 @@
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t>LSE:TLW</t>
+          <t>LSE:AML</t>
         </is>
       </c>
       <c r="C21" s="11" t="inlineStr">
         <is>
-          <t>Tullow Oil</t>
+          <t>Aston Martin Lagonda</t>
         </is>
       </c>
       <c r="D21" s="11" t="inlineStr">
@@ -14298,7 +14298,7 @@
       </c>
       <c r="E21" s="11" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="F21" s="11" t="inlineStr">
@@ -14308,7 +14308,7 @@
       </c>
       <c r="G21" s="11" t="inlineStr">
         <is>
-          <t>2.3×</t>
+          <t>2.4×</t>
         </is>
       </c>
       <c r="H21" s="11" t="inlineStr">
@@ -14323,12 +14323,12 @@
       </c>
       <c r="B22" s="14" t="inlineStr">
         <is>
-          <t>NYSE:FFWM</t>
+          <t>APTOF</t>
         </is>
       </c>
       <c r="C22" s="14" t="inlineStr">
         <is>
-          <t>First Foundation</t>
+          <t>Aptose Biosciences Inc.</t>
         </is>
       </c>
       <c r="D22" s="14" t="inlineStr">
@@ -14338,57 +14338,57 @@
       </c>
       <c r="E22" s="14" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="F22" s="14" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>K3</t>
         </is>
       </c>
       <c r="G22" s="14" t="inlineStr">
         <is>
-          <t>2.3×</t>
+          <t>2.4×</t>
         </is>
       </c>
       <c r="H22" s="14" t="inlineStr">
         <is>
-          <t>Tier 2 — verify primary docs first</t>
+          <t>Tier 1 — hand-deepen ASAP</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="9" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B23" s="11" t="inlineStr">
         <is>
-          <t>TSE:8304</t>
+          <t>HK:2202</t>
         </is>
       </c>
       <c r="C23" s="11" t="inlineStr">
         <is>
-          <t>Aozora Bank</t>
+          <t>Vanke</t>
         </is>
       </c>
       <c r="D23" s="11" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Greater China / HK</t>
         </is>
       </c>
       <c r="E23" s="11" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="F23" s="11" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>A1</t>
         </is>
       </c>
       <c r="G23" s="11" t="inlineStr">
         <is>
-          <t>2.1×</t>
+          <t>2.3×</t>
         </is>
       </c>
       <c r="H23" s="11" t="inlineStr">
@@ -14399,36 +14399,36 @@
     </row>
     <row r="24">
       <c r="A24" s="12" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B24" s="14" t="inlineStr">
         <is>
-          <t>XETR:TUI1</t>
+          <t>LSE:VOD</t>
         </is>
       </c>
       <c r="C24" s="14" t="inlineStr">
         <is>
-          <t>Tui AG</t>
+          <t>Vodafone</t>
         </is>
       </c>
       <c r="D24" s="14" t="inlineStr">
         <is>
-          <t>Continental Europe</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="E24" s="14" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="F24" s="14" t="inlineStr">
         <is>
-          <t>A2</t>
+          <t>A1</t>
         </is>
       </c>
       <c r="G24" s="14" t="inlineStr">
         <is>
-          <t>2.0×</t>
+          <t>2.3×</t>
         </is>
       </c>
       <c r="H24" s="14" t="inlineStr">

--- a/output/cyclepapa_risk_reward_workbook.xlsx
+++ b/output/cyclepapa_risk_reward_workbook.xlsx
@@ -6960,7 +6960,7 @@
     <row r="2" ht="38" customHeight="1">
       <c r="A2" s="7" t="inlineStr">
         <is>
-          <t>Universe coverage: 288 investable names (21 REAL waterfalls · 267 PROXY).  REAL uses the hand-built YAML's bottom-up bear/base/bull. PROXY uses a transparent formula on the universe-screener score + archetype tilt.</t>
+          <t>Universe coverage: 308 investable names (21 REAL waterfalls · 287 PROXY).  REAL uses the hand-built YAML's bottom-up bear/base/bull. PROXY uses a transparent formula on the universe-screener score + archetype tilt.</t>
         </is>
       </c>
     </row>
@@ -8668,22 +8668,22 @@
       </c>
       <c r="C30" s="14" t="inlineStr">
         <is>
-          <t>LSE:ASC</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D30" s="14" t="inlineStr">
         <is>
-          <t>ASOS</t>
+          <t>BRADESCO LEASING S.A. - ARRENDAMENTO MERCANTIL</t>
         </is>
       </c>
       <c r="E30" s="14" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Latin America</t>
         </is>
       </c>
       <c r="F30" s="14" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="G30" s="14" t="inlineStr">
@@ -8703,17 +8703,17 @@
       </c>
       <c r="J30" s="14" t="inlineStr">
         <is>
-          <t>2.16×</t>
+          <t>2.15×</t>
         </is>
       </c>
       <c r="K30" s="14" t="inlineStr">
         <is>
-          <t>2.64×</t>
+          <t>2.62×</t>
         </is>
       </c>
       <c r="L30" s="14" t="inlineStr">
         <is>
-          <t>1.84×</t>
+          <t>1.83×</t>
         </is>
       </c>
       <c r="M30" s="14" t="inlineStr">
@@ -8733,22 +8733,22 @@
       </c>
       <c r="C31" s="11" t="inlineStr">
         <is>
-          <t>TBRG</t>
+          <t>LSE:ASC</t>
         </is>
       </c>
       <c r="D31" s="11" t="inlineStr">
         <is>
-          <t>TruBridge, Inc.</t>
+          <t>ASOS</t>
         </is>
       </c>
       <c r="E31" s="11" t="inlineStr">
         <is>
-          <t>United States/Canada</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="F31" s="11" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="G31" s="11" t="inlineStr">
@@ -8758,27 +8758,27 @@
       </c>
       <c r="H31" s="11" t="inlineStr">
         <is>
-          <t>K3</t>
+          <t>A1</t>
         </is>
       </c>
       <c r="I31" s="11" t="inlineStr">
         <is>
-          <t>36%</t>
+          <t>32%</t>
         </is>
       </c>
       <c r="J31" s="11" t="inlineStr">
         <is>
-          <t>2.29×</t>
+          <t>2.16×</t>
         </is>
       </c>
       <c r="K31" s="11" t="inlineStr">
         <is>
-          <t>2.94×</t>
+          <t>2.64×</t>
         </is>
       </c>
       <c r="L31" s="11" t="inlineStr">
         <is>
-          <t>1.96×</t>
+          <t>1.84×</t>
         </is>
       </c>
       <c r="M31" s="11" t="inlineStr">
@@ -8798,12 +8798,12 @@
       </c>
       <c r="C32" s="14" t="inlineStr">
         <is>
-          <t>LEG</t>
+          <t>TBRG</t>
         </is>
       </c>
       <c r="D32" s="14" t="inlineStr">
         <is>
-          <t>LEGGETT &amp; PLATT INC</t>
+          <t>TruBridge, Inc.</t>
         </is>
       </c>
       <c r="E32" s="14" t="inlineStr">
@@ -8813,7 +8813,7 @@
       </c>
       <c r="F32" s="14" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="G32" s="14" t="inlineStr">
@@ -8823,27 +8823,27 @@
       </c>
       <c r="H32" s="14" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>K3</t>
         </is>
       </c>
       <c r="I32" s="14" t="inlineStr">
         <is>
-          <t>34%</t>
+          <t>36%</t>
         </is>
       </c>
       <c r="J32" s="14" t="inlineStr">
         <is>
-          <t>2.21×</t>
+          <t>2.29×</t>
         </is>
       </c>
       <c r="K32" s="14" t="inlineStr">
         <is>
-          <t>2.76×</t>
+          <t>2.94×</t>
         </is>
       </c>
       <c r="L32" s="14" t="inlineStr">
         <is>
-          <t>1.88×</t>
+          <t>1.96×</t>
         </is>
       </c>
       <c r="M32" s="14" t="inlineStr">
@@ -8856,29 +8856,29 @@
       <c r="A33" s="9" t="n">
         <v>29</v>
       </c>
-      <c r="B33" s="10" t="inlineStr">
-        <is>
-          <t>REAL</t>
+      <c r="B33" s="15" t="inlineStr">
+        <is>
+          <t>PROXY</t>
         </is>
       </c>
       <c r="C33" s="11" t="inlineStr">
         <is>
-          <t>LSE:DRX</t>
+          <t>LEG</t>
         </is>
       </c>
       <c r="D33" s="11" t="inlineStr">
         <is>
-          <t>Drax Group</t>
+          <t>LEGGETT &amp; PLATT INC</t>
         </is>
       </c>
       <c r="E33" s="11" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>United States/Canada</t>
         </is>
       </c>
       <c r="F33" s="11" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="G33" s="11" t="inlineStr">
@@ -8888,27 +8888,27 @@
       </c>
       <c r="H33" s="11" t="inlineStr">
         <is>
-          <t>A1+G</t>
+          <t>C</t>
         </is>
       </c>
       <c r="I33" s="11" t="inlineStr">
         <is>
-          <t>55%</t>
+          <t>34%</t>
         </is>
       </c>
       <c r="J33" s="11" t="inlineStr">
         <is>
-          <t>2.20×</t>
+          <t>2.21×</t>
         </is>
       </c>
       <c r="K33" s="11" t="inlineStr">
         <is>
-          <t>4.50×</t>
+          <t>2.76×</t>
         </is>
       </c>
       <c r="L33" s="11" t="inlineStr">
         <is>
-          <t>2.45×</t>
+          <t>1.88×</t>
         </is>
       </c>
       <c r="M33" s="11" t="inlineStr">
@@ -8928,17 +8928,17 @@
       </c>
       <c r="C34" s="14" t="inlineStr">
         <is>
-          <t>NASDAQ:UREE</t>
+          <t>LSE:DRX</t>
         </is>
       </c>
       <c r="D34" s="14" t="inlineStr">
         <is>
-          <t>USA Rare Earth</t>
+          <t>Drax Group</t>
         </is>
       </c>
       <c r="E34" s="14" t="inlineStr">
         <is>
-          <t>United States/Canada</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="F34" s="14" t="inlineStr">
@@ -8953,27 +8953,27 @@
       </c>
       <c r="H34" s="14" t="inlineStr">
         <is>
-          <t>A2</t>
+          <t>A1+G</t>
         </is>
       </c>
       <c r="I34" s="14" t="inlineStr">
         <is>
-          <t>65%</t>
+          <t>55%</t>
         </is>
       </c>
       <c r="J34" s="14" t="inlineStr">
         <is>
-          <t>2.50×</t>
+          <t>2.20×</t>
         </is>
       </c>
       <c r="K34" s="14" t="inlineStr">
         <is>
-          <t>5.50×</t>
+          <t>4.50×</t>
         </is>
       </c>
       <c r="L34" s="14" t="inlineStr">
         <is>
-          <t>2.71×</t>
+          <t>2.45×</t>
         </is>
       </c>
       <c r="M34" s="14" t="inlineStr">
@@ -8986,19 +8986,19 @@
       <c r="A35" s="9" t="n">
         <v>31</v>
       </c>
-      <c r="B35" s="15" t="inlineStr">
-        <is>
-          <t>PROXY</t>
+      <c r="B35" s="10" t="inlineStr">
+        <is>
+          <t>REAL</t>
         </is>
       </c>
       <c r="C35" s="11" t="inlineStr">
         <is>
-          <t>TSX:CFW</t>
+          <t>NASDAQ:UREE</t>
         </is>
       </c>
       <c r="D35" s="11" t="inlineStr">
         <is>
-          <t>Calfrac Well Services</t>
+          <t>USA Rare Earth</t>
         </is>
       </c>
       <c r="E35" s="11" t="inlineStr">
@@ -9008,7 +9008,7 @@
       </c>
       <c r="F35" s="11" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="G35" s="11" t="inlineStr">
@@ -9018,32 +9018,32 @@
       </c>
       <c r="H35" s="11" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2</t>
         </is>
       </c>
       <c r="I35" s="11" t="inlineStr">
         <is>
-          <t>32%</t>
+          <t>65%</t>
         </is>
       </c>
       <c r="J35" s="11" t="inlineStr">
         <is>
-          <t>2.14×</t>
+          <t>2.50×</t>
         </is>
       </c>
       <c r="K35" s="11" t="inlineStr">
         <is>
-          <t>2.59×</t>
+          <t>5.50×</t>
         </is>
       </c>
       <c r="L35" s="11" t="inlineStr">
         <is>
-          <t>1.81×</t>
+          <t>2.71×</t>
         </is>
       </c>
       <c r="M35" s="11" t="inlineStr">
         <is>
-          <t>2.5×</t>
+          <t>2.6×</t>
         </is>
       </c>
     </row>
@@ -9058,22 +9058,22 @@
       </c>
       <c r="C36" s="14" t="inlineStr">
         <is>
-          <t>KRX:028260</t>
+          <t>TSX:CFW</t>
         </is>
       </c>
       <c r="D36" s="14" t="inlineStr">
         <is>
-          <t>Samsung C&amp;T</t>
+          <t>Calfrac Well Services</t>
         </is>
       </c>
       <c r="E36" s="14" t="inlineStr">
         <is>
-          <t>Korea</t>
+          <t>United States/Canada</t>
         </is>
       </c>
       <c r="F36" s="14" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="G36" s="14" t="inlineStr">
@@ -9083,32 +9083,32 @@
       </c>
       <c r="H36" s="14" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>A1</t>
         </is>
       </c>
       <c r="I36" s="14" t="inlineStr">
         <is>
-          <t>40%</t>
+          <t>32%</t>
         </is>
       </c>
       <c r="J36" s="14" t="inlineStr">
         <is>
-          <t>2.30×</t>
+          <t>2.14×</t>
         </is>
       </c>
       <c r="K36" s="14" t="inlineStr">
         <is>
-          <t>3.00×</t>
+          <t>2.59×</t>
         </is>
       </c>
       <c r="L36" s="14" t="inlineStr">
         <is>
-          <t>1.96×</t>
+          <t>1.81×</t>
         </is>
       </c>
       <c r="M36" s="14" t="inlineStr">
         <is>
-          <t>2.4×</t>
+          <t>2.5×</t>
         </is>
       </c>
     </row>
@@ -9123,22 +9123,22 @@
       </c>
       <c r="C37" s="11" t="inlineStr">
         <is>
-          <t>LSE:AML</t>
+          <t>KRX:028260</t>
         </is>
       </c>
       <c r="D37" s="11" t="inlineStr">
         <is>
-          <t>Aston Martin Lagonda</t>
+          <t>Samsung C&amp;T</t>
         </is>
       </c>
       <c r="E37" s="11" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Korea</t>
         </is>
       </c>
       <c r="F37" s="11" t="inlineStr">
         <is>
-          <t>0.70</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="G37" s="11" t="inlineStr">
@@ -9148,27 +9148,27 @@
       </c>
       <c r="H37" s="11" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>H</t>
         </is>
       </c>
       <c r="I37" s="11" t="inlineStr">
         <is>
-          <t>33%</t>
+          <t>40%</t>
         </is>
       </c>
       <c r="J37" s="11" t="inlineStr">
         <is>
-          <t>2.11×</t>
+          <t>2.30×</t>
         </is>
       </c>
       <c r="K37" s="11" t="inlineStr">
         <is>
-          <t>2.55×</t>
+          <t>3.00×</t>
         </is>
       </c>
       <c r="L37" s="11" t="inlineStr">
         <is>
-          <t>1.79×</t>
+          <t>1.96×</t>
         </is>
       </c>
       <c r="M37" s="11" t="inlineStr">
@@ -9188,22 +9188,22 @@
       </c>
       <c r="C38" s="14" t="inlineStr">
         <is>
-          <t>APTOF</t>
+          <t>LSE:AML</t>
         </is>
       </c>
       <c r="D38" s="14" t="inlineStr">
         <is>
-          <t>Aptose Biosciences Inc.</t>
+          <t>Aston Martin Lagonda</t>
         </is>
       </c>
       <c r="E38" s="14" t="inlineStr">
         <is>
-          <t>United States/Canada</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="F38" s="14" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="G38" s="14" t="inlineStr">
@@ -9213,27 +9213,27 @@
       </c>
       <c r="H38" s="14" t="inlineStr">
         <is>
-          <t>K3</t>
+          <t>A1</t>
         </is>
       </c>
       <c r="I38" s="14" t="inlineStr">
         <is>
-          <t>38%</t>
+          <t>33%</t>
         </is>
       </c>
       <c r="J38" s="14" t="inlineStr">
         <is>
-          <t>2.24×</t>
+          <t>2.11×</t>
         </is>
       </c>
       <c r="K38" s="14" t="inlineStr">
         <is>
-          <t>2.87×</t>
+          <t>2.55×</t>
         </is>
       </c>
       <c r="L38" s="14" t="inlineStr">
         <is>
-          <t>1.91×</t>
+          <t>1.79×</t>
         </is>
       </c>
       <c r="M38" s="14" t="inlineStr">
@@ -9253,22 +9253,22 @@
       </c>
       <c r="C39" s="11" t="inlineStr">
         <is>
-          <t>HK:2202</t>
+          <t>APTOF</t>
         </is>
       </c>
       <c r="D39" s="11" t="inlineStr">
         <is>
-          <t>Vanke</t>
+          <t>Aptose Biosciences Inc.</t>
         </is>
       </c>
       <c r="E39" s="11" t="inlineStr">
         <is>
-          <t>Greater China / HK</t>
+          <t>United States/Canada</t>
         </is>
       </c>
       <c r="F39" s="11" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="G39" s="11" t="inlineStr">
@@ -9278,32 +9278,32 @@
       </c>
       <c r="H39" s="11" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>K3</t>
         </is>
       </c>
       <c r="I39" s="11" t="inlineStr">
         <is>
-          <t>33%</t>
+          <t>38%</t>
         </is>
       </c>
       <c r="J39" s="11" t="inlineStr">
         <is>
-          <t>2.10×</t>
+          <t>2.24×</t>
         </is>
       </c>
       <c r="K39" s="11" t="inlineStr">
         <is>
-          <t>2.54×</t>
+          <t>2.87×</t>
         </is>
       </c>
       <c r="L39" s="11" t="inlineStr">
         <is>
-          <t>1.78×</t>
+          <t>1.91×</t>
         </is>
       </c>
       <c r="M39" s="11" t="inlineStr">
         <is>
-          <t>2.3×</t>
+          <t>2.4×</t>
         </is>
       </c>
     </row>
@@ -9318,22 +9318,22 @@
       </c>
       <c r="C40" s="14" t="inlineStr">
         <is>
-          <t>LSE:VOD</t>
+          <t>HK:2202</t>
         </is>
       </c>
       <c r="D40" s="14" t="inlineStr">
         <is>
-          <t>Vodafone</t>
+          <t>Vanke</t>
         </is>
       </c>
       <c r="E40" s="14" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Greater China / HK</t>
         </is>
       </c>
       <c r="F40" s="14" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="G40" s="14" t="inlineStr">
@@ -9348,22 +9348,22 @@
       </c>
       <c r="I40" s="14" t="inlineStr">
         <is>
-          <t>34%</t>
+          <t>33%</t>
         </is>
       </c>
       <c r="J40" s="14" t="inlineStr">
         <is>
-          <t>2.08×</t>
+          <t>2.10×</t>
         </is>
       </c>
       <c r="K40" s="14" t="inlineStr">
         <is>
-          <t>2.50×</t>
+          <t>2.54×</t>
         </is>
       </c>
       <c r="L40" s="14" t="inlineStr">
         <is>
-          <t>1.76×</t>
+          <t>1.78×</t>
         </is>
       </c>
       <c r="M40" s="14" t="inlineStr">
@@ -9383,12 +9383,12 @@
       </c>
       <c r="C41" s="11" t="inlineStr">
         <is>
-          <t>LSE:TLW</t>
+          <t>LSE:VOD</t>
         </is>
       </c>
       <c r="D41" s="11" t="inlineStr">
         <is>
-          <t>Tullow Oil</t>
+          <t>Vodafone</t>
         </is>
       </c>
       <c r="E41" s="11" t="inlineStr">
@@ -9448,17 +9448,17 @@
       </c>
       <c r="C42" s="14" t="inlineStr">
         <is>
-          <t>NYSE:FFWM</t>
+          <t>LSE:TLW</t>
         </is>
       </c>
       <c r="D42" s="14" t="inlineStr">
         <is>
-          <t>First Foundation</t>
+          <t>Tullow Oil</t>
         </is>
       </c>
       <c r="E42" s="14" t="inlineStr">
         <is>
-          <t>United States/Canada</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="F42" s="14" t="inlineStr">
@@ -9506,19 +9506,19 @@
       <c r="A43" s="9" t="n">
         <v>39</v>
       </c>
-      <c r="B43" s="10" t="inlineStr">
-        <is>
-          <t>REAL</t>
+      <c r="B43" s="15" t="inlineStr">
+        <is>
+          <t>PROXY</t>
         </is>
       </c>
       <c r="C43" s="11" t="inlineStr">
         <is>
-          <t>NYSE:HE</t>
+          <t>NYSE:FFWM</t>
         </is>
       </c>
       <c r="D43" s="11" t="inlineStr">
         <is>
-          <t>Hawaiian Electric Industries</t>
+          <t>First Foundation</t>
         </is>
       </c>
       <c r="E43" s="11" t="inlineStr">
@@ -9528,7 +9528,7 @@
       </c>
       <c r="F43" s="11" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="G43" s="11" t="inlineStr">
@@ -9538,27 +9538,27 @@
       </c>
       <c r="H43" s="11" t="inlineStr">
         <is>
-          <t>A1+G</t>
+          <t>A1</t>
         </is>
       </c>
       <c r="I43" s="11" t="inlineStr">
         <is>
-          <t>40%</t>
+          <t>34%</t>
         </is>
       </c>
       <c r="J43" s="11" t="inlineStr">
         <is>
-          <t>1.80×</t>
+          <t>2.08×</t>
         </is>
       </c>
       <c r="K43" s="11" t="inlineStr">
         <is>
-          <t>3.00×</t>
+          <t>2.50×</t>
         </is>
       </c>
       <c r="L43" s="11" t="inlineStr">
         <is>
-          <t>1.92×</t>
+          <t>1.76×</t>
         </is>
       </c>
       <c r="M43" s="11" t="inlineStr">
@@ -9571,29 +9571,29 @@
       <c r="A44" s="12" t="n">
         <v>40</v>
       </c>
-      <c r="B44" s="13" t="inlineStr">
-        <is>
-          <t>PROXY</t>
+      <c r="B44" s="16" t="inlineStr">
+        <is>
+          <t>REAL</t>
         </is>
       </c>
       <c r="C44" s="14" t="inlineStr">
         <is>
-          <t>TSE:8304</t>
+          <t>NYSE:HE</t>
         </is>
       </c>
       <c r="D44" s="14" t="inlineStr">
         <is>
-          <t>Aozora Bank</t>
+          <t>Hawaiian Electric Industries</t>
         </is>
       </c>
       <c r="E44" s="14" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States/Canada</t>
         </is>
       </c>
       <c r="F44" s="14" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="G44" s="14" t="inlineStr">
@@ -9603,32 +9603,32 @@
       </c>
       <c r="H44" s="14" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>A1+G</t>
         </is>
       </c>
       <c r="I44" s="14" t="inlineStr">
         <is>
-          <t>42%</t>
+          <t>40%</t>
         </is>
       </c>
       <c r="J44" s="14" t="inlineStr">
         <is>
-          <t>2.23×</t>
+          <t>1.80×</t>
         </is>
       </c>
       <c r="K44" s="14" t="inlineStr">
         <is>
-          <t>2.89×</t>
+          <t>3.00×</t>
         </is>
       </c>
       <c r="L44" s="14" t="inlineStr">
         <is>
-          <t>1.90×</t>
+          <t>1.92×</t>
         </is>
       </c>
       <c r="M44" s="14" t="inlineStr">
         <is>
-          <t>2.1×</t>
+          <t>2.3×</t>
         </is>
       </c>
     </row>
@@ -9636,29 +9636,29 @@
       <c r="A45" s="9" t="n">
         <v>41</v>
       </c>
-      <c r="B45" s="10" t="inlineStr">
-        <is>
-          <t>REAL</t>
+      <c r="B45" s="15" t="inlineStr">
+        <is>
+          <t>PROXY</t>
         </is>
       </c>
       <c r="C45" s="11" t="inlineStr">
         <is>
-          <t>NYSE/TSX:TMQ</t>
+          <t>TSE:8304</t>
         </is>
       </c>
       <c r="D45" s="11" t="inlineStr">
         <is>
-          <t>Trilogy Metals</t>
+          <t>Aozora Bank</t>
         </is>
       </c>
       <c r="E45" s="11" t="inlineStr">
         <is>
-          <t>United States/Canada</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="F45" s="11" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="G45" s="11" t="inlineStr">
@@ -9668,27 +9668,27 @@
       </c>
       <c r="H45" s="11" t="inlineStr">
         <is>
-          <t>A2</t>
+          <t>H</t>
         </is>
       </c>
       <c r="I45" s="11" t="inlineStr">
         <is>
-          <t>55%</t>
+          <t>42%</t>
         </is>
       </c>
       <c r="J45" s="11" t="inlineStr">
         <is>
-          <t>2.20×</t>
+          <t>2.23×</t>
         </is>
       </c>
       <c r="K45" s="11" t="inlineStr">
         <is>
-          <t>4.50×</t>
+          <t>2.89×</t>
         </is>
       </c>
       <c r="L45" s="11" t="inlineStr">
         <is>
-          <t>2.14×</t>
+          <t>1.90×</t>
         </is>
       </c>
       <c r="M45" s="11" t="inlineStr">
@@ -9701,29 +9701,29 @@
       <c r="A46" s="12" t="n">
         <v>42</v>
       </c>
-      <c r="B46" s="13" t="inlineStr">
-        <is>
-          <t>PROXY</t>
+      <c r="B46" s="16" t="inlineStr">
+        <is>
+          <t>REAL</t>
         </is>
       </c>
       <c r="C46" s="14" t="inlineStr">
         <is>
-          <t>XETR:TUI1</t>
+          <t>NYSE/TSX:TMQ</t>
         </is>
       </c>
       <c r="D46" s="14" t="inlineStr">
         <is>
-          <t>Tui AG</t>
+          <t>Trilogy Metals</t>
         </is>
       </c>
       <c r="E46" s="14" t="inlineStr">
         <is>
-          <t>Continental Europe</t>
+          <t>United States/Canada</t>
         </is>
       </c>
       <c r="F46" s="14" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="G46" s="14" t="inlineStr">
@@ -9738,27 +9738,27 @@
       </c>
       <c r="I46" s="14" t="inlineStr">
         <is>
-          <t>36%</t>
+          <t>55%</t>
         </is>
       </c>
       <c r="J46" s="14" t="inlineStr">
         <is>
-          <t>2.02×</t>
+          <t>2.20×</t>
         </is>
       </c>
       <c r="K46" s="14" t="inlineStr">
         <is>
-          <t>2.38×</t>
+          <t>4.50×</t>
         </is>
       </c>
       <c r="L46" s="14" t="inlineStr">
         <is>
-          <t>1.70×</t>
+          <t>2.14×</t>
         </is>
       </c>
       <c r="M46" s="14" t="inlineStr">
         <is>
-          <t>2.0×</t>
+          <t>2.1×</t>
         </is>
       </c>
     </row>
@@ -9773,22 +9773,22 @@
       </c>
       <c r="C47" s="11" t="inlineStr">
         <is>
-          <t>LSE:PDL</t>
+          <t>XETR:TUI1</t>
         </is>
       </c>
       <c r="D47" s="11" t="inlineStr">
         <is>
-          <t>Petra Diamonds</t>
+          <t>Tui AG</t>
         </is>
       </c>
       <c r="E47" s="11" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Continental Europe</t>
         </is>
       </c>
       <c r="F47" s="11" t="inlineStr">
         <is>
-          <t>0.60</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="G47" s="11" t="inlineStr">
@@ -9798,12 +9798,12 @@
       </c>
       <c r="H47" s="11" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2</t>
         </is>
       </c>
       <c r="I47" s="11" t="inlineStr">
         <is>
-          <t>35%</t>
+          <t>36%</t>
         </is>
       </c>
       <c r="J47" s="11" t="inlineStr">
@@ -9813,7 +9813,7 @@
       </c>
       <c r="K47" s="11" t="inlineStr">
         <is>
-          <t>2.40×</t>
+          <t>2.38×</t>
         </is>
       </c>
       <c r="L47" s="11" t="inlineStr">
@@ -9831,29 +9831,29 @@
       <c r="A48" s="12" t="n">
         <v>44</v>
       </c>
-      <c r="B48" s="16" t="inlineStr">
-        <is>
-          <t>REAL</t>
+      <c r="B48" s="13" t="inlineStr">
+        <is>
+          <t>PROXY</t>
         </is>
       </c>
       <c r="C48" s="14" t="inlineStr">
         <is>
-          <t>NYSE:MP</t>
+          <t>LSE:PDL</t>
         </is>
       </c>
       <c r="D48" s="14" t="inlineStr">
         <is>
-          <t>MP Materials Corp</t>
+          <t>Petra Diamonds</t>
         </is>
       </c>
       <c r="E48" s="14" t="inlineStr">
         <is>
-          <t>United States/Canada</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="F48" s="14" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>0.60</t>
         </is>
       </c>
       <c r="G48" s="14" t="inlineStr">
@@ -9863,27 +9863,27 @@
       </c>
       <c r="H48" s="14" t="inlineStr">
         <is>
-          <t>A2</t>
+          <t>A1</t>
         </is>
       </c>
       <c r="I48" s="14" t="inlineStr">
         <is>
-          <t>45%</t>
+          <t>35%</t>
         </is>
       </c>
       <c r="J48" s="14" t="inlineStr">
         <is>
-          <t>1.80×</t>
+          <t>2.02×</t>
         </is>
       </c>
       <c r="K48" s="14" t="inlineStr">
         <is>
-          <t>3.20×</t>
+          <t>2.40×</t>
         </is>
       </c>
       <c r="L48" s="14" t="inlineStr">
         <is>
-          <t>1.90×</t>
+          <t>1.70×</t>
         </is>
       </c>
       <c r="M48" s="14" t="inlineStr">
@@ -9896,29 +9896,29 @@
       <c r="A49" s="9" t="n">
         <v>45</v>
       </c>
-      <c r="B49" s="15" t="inlineStr">
-        <is>
-          <t>PROXY</t>
+      <c r="B49" s="10" t="inlineStr">
+        <is>
+          <t>REAL</t>
         </is>
       </c>
       <c r="C49" s="11" t="inlineStr">
         <is>
-          <t>NYSE:AENZ</t>
+          <t>NYSE:MP</t>
         </is>
       </c>
       <c r="D49" s="11" t="inlineStr">
         <is>
-          <t>Aenza (former Graña y Montero)</t>
+          <t>MP Materials Corp</t>
         </is>
       </c>
       <c r="E49" s="11" t="inlineStr">
         <is>
-          <t>Continental Europe</t>
+          <t>United States/Canada</t>
         </is>
       </c>
       <c r="F49" s="11" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="G49" s="11" t="inlineStr">
@@ -9933,27 +9933,27 @@
       </c>
       <c r="I49" s="11" t="inlineStr">
         <is>
-          <t>36%</t>
+          <t>45%</t>
         </is>
       </c>
       <c r="J49" s="11" t="inlineStr">
         <is>
-          <t>2.00×</t>
+          <t>1.80×</t>
         </is>
       </c>
       <c r="K49" s="11" t="inlineStr">
         <is>
-          <t>2.35×</t>
+          <t>3.20×</t>
         </is>
       </c>
       <c r="L49" s="11" t="inlineStr">
         <is>
-          <t>1.68×</t>
+          <t>1.90×</t>
         </is>
       </c>
       <c r="M49" s="11" t="inlineStr">
         <is>
-          <t>1.9×</t>
+          <t>2.0×</t>
         </is>
       </c>
     </row>
@@ -9968,22 +9968,22 @@
       </c>
       <c r="C50" s="14" t="inlineStr">
         <is>
-          <t>KRX:034730</t>
+          <t>NYSE:AENZ</t>
         </is>
       </c>
       <c r="D50" s="14" t="inlineStr">
         <is>
-          <t>SK Inc</t>
+          <t>Aenza (former Graña y Montero)</t>
         </is>
       </c>
       <c r="E50" s="14" t="inlineStr">
         <is>
-          <t>Korea</t>
+          <t>Continental Europe</t>
         </is>
       </c>
       <c r="F50" s="14" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="G50" s="14" t="inlineStr">
@@ -9993,27 +9993,27 @@
       </c>
       <c r="H50" s="14" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>A2</t>
         </is>
       </c>
       <c r="I50" s="14" t="inlineStr">
         <is>
-          <t>44%</t>
+          <t>36%</t>
         </is>
       </c>
       <c r="J50" s="14" t="inlineStr">
         <is>
-          <t>2.17×</t>
+          <t>2.00×</t>
         </is>
       </c>
       <c r="K50" s="14" t="inlineStr">
         <is>
-          <t>2.79×</t>
+          <t>2.35×</t>
         </is>
       </c>
       <c r="L50" s="14" t="inlineStr">
         <is>
-          <t>1.84×</t>
+          <t>1.68×</t>
         </is>
       </c>
       <c r="M50" s="14" t="inlineStr">
@@ -10033,22 +10033,22 @@
       </c>
       <c r="C51" s="11" t="inlineStr">
         <is>
-          <t>NGX:ZENITHBANK</t>
+          <t>KRX:034730</t>
         </is>
       </c>
       <c r="D51" s="11" t="inlineStr">
         <is>
-          <t>Zenith Bank</t>
+          <t>SK Inc</t>
         </is>
       </c>
       <c r="E51" s="11" t="inlineStr">
         <is>
-          <t>MEA / Frontier</t>
+          <t>Korea</t>
         </is>
       </c>
       <c r="F51" s="11" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="G51" s="11" t="inlineStr">
@@ -10058,27 +10058,27 @@
       </c>
       <c r="H51" s="11" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>H</t>
         </is>
       </c>
       <c r="I51" s="11" t="inlineStr">
         <is>
-          <t>42%</t>
+          <t>44%</t>
         </is>
       </c>
       <c r="J51" s="11" t="inlineStr">
         <is>
-          <t>2.11×</t>
+          <t>2.17×</t>
         </is>
       </c>
       <c r="K51" s="11" t="inlineStr">
         <is>
-          <t>2.64×</t>
+          <t>2.79×</t>
         </is>
       </c>
       <c r="L51" s="11" t="inlineStr">
         <is>
-          <t>1.78×</t>
+          <t>1.84×</t>
         </is>
       </c>
       <c r="M51" s="11" t="inlineStr">
@@ -10091,29 +10091,29 @@
       <c r="A52" s="12" t="n">
         <v>48</v>
       </c>
-      <c r="B52" s="16" t="inlineStr">
-        <is>
-          <t>REAL</t>
+      <c r="B52" s="13" t="inlineStr">
+        <is>
+          <t>PROXY</t>
         </is>
       </c>
       <c r="C52" s="14" t="inlineStr">
         <is>
-          <t>NYSE:FLG</t>
+          <t>NGX:ZENITHBANK</t>
         </is>
       </c>
       <c r="D52" s="14" t="inlineStr">
         <is>
-          <t>NYCB / Flagstar Financial</t>
+          <t>Zenith Bank</t>
         </is>
       </c>
       <c r="E52" s="14" t="inlineStr">
         <is>
-          <t>United States/Canada</t>
+          <t>MEA / Frontier</t>
         </is>
       </c>
       <c r="F52" s="14" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="G52" s="14" t="inlineStr">
@@ -10123,27 +10123,27 @@
       </c>
       <c r="H52" s="14" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>G</t>
         </is>
       </c>
       <c r="I52" s="14" t="inlineStr">
         <is>
-          <t>45%</t>
+          <t>42%</t>
         </is>
       </c>
       <c r="J52" s="14" t="inlineStr">
         <is>
-          <t>1.85×</t>
+          <t>2.11×</t>
         </is>
       </c>
       <c r="K52" s="14" t="inlineStr">
         <is>
-          <t>3.20×</t>
+          <t>2.64×</t>
         </is>
       </c>
       <c r="L52" s="14" t="inlineStr">
         <is>
-          <t>1.86×</t>
+          <t>1.78×</t>
         </is>
       </c>
       <c r="M52" s="14" t="inlineStr">
@@ -10156,19 +10156,19 @@
       <c r="A53" s="9" t="n">
         <v>49</v>
       </c>
-      <c r="B53" s="15" t="inlineStr">
-        <is>
-          <t>PROXY</t>
+      <c r="B53" s="10" t="inlineStr">
+        <is>
+          <t>REAL</t>
         </is>
       </c>
       <c r="C53" s="11" t="inlineStr">
         <is>
-          <t>AEMD</t>
+          <t>NYSE:FLG</t>
         </is>
       </c>
       <c r="D53" s="11" t="inlineStr">
         <is>
-          <t>AETHLON MEDICAL INC</t>
+          <t>NYCB / Flagstar Financial</t>
         </is>
       </c>
       <c r="E53" s="11" t="inlineStr">
@@ -10178,7 +10178,7 @@
       </c>
       <c r="F53" s="11" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="G53" s="11" t="inlineStr">
@@ -10188,27 +10188,27 @@
       </c>
       <c r="H53" s="11" t="inlineStr">
         <is>
-          <t>F2</t>
+          <t>A1</t>
         </is>
       </c>
       <c r="I53" s="11" t="inlineStr">
         <is>
-          <t>42%</t>
+          <t>45%</t>
         </is>
       </c>
       <c r="J53" s="11" t="inlineStr">
         <is>
-          <t>2.12×</t>
+          <t>1.85×</t>
         </is>
       </c>
       <c r="K53" s="11" t="inlineStr">
         <is>
-          <t>2.66×</t>
+          <t>3.20×</t>
         </is>
       </c>
       <c r="L53" s="11" t="inlineStr">
         <is>
-          <t>1.79×</t>
+          <t>1.86×</t>
         </is>
       </c>
       <c r="M53" s="11" t="inlineStr">
@@ -10228,22 +10228,22 @@
       </c>
       <c r="C54" s="14" t="inlineStr">
         <is>
-          <t>EGX:COMI</t>
+          <t>AEMD</t>
         </is>
       </c>
       <c r="D54" s="14" t="inlineStr">
         <is>
-          <t>Egypt Commercial International Bank</t>
+          <t>AETHLON MEDICAL INC</t>
         </is>
       </c>
       <c r="E54" s="14" t="inlineStr">
         <is>
-          <t>MEA / Frontier</t>
+          <t>United States/Canada</t>
         </is>
       </c>
       <c r="F54" s="14" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="G54" s="14" t="inlineStr">
@@ -10253,7 +10253,7 @@
       </c>
       <c r="H54" s="14" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>F2</t>
         </is>
       </c>
       <c r="I54" s="14" t="inlineStr">
@@ -10263,22 +10263,22 @@
       </c>
       <c r="J54" s="14" t="inlineStr">
         <is>
-          <t>2.10×</t>
+          <t>2.12×</t>
         </is>
       </c>
       <c r="K54" s="14" t="inlineStr">
         <is>
-          <t>2.62×</t>
+          <t>2.66×</t>
         </is>
       </c>
       <c r="L54" s="14" t="inlineStr">
         <is>
-          <t>1.77×</t>
+          <t>1.79×</t>
         </is>
       </c>
       <c r="M54" s="14" t="inlineStr">
         <is>
-          <t>1.8×</t>
+          <t>1.9×</t>
         </is>
       </c>
     </row>
@@ -10293,12 +10293,12 @@
       </c>
       <c r="C55" s="11" t="inlineStr">
         <is>
-          <t>NGX:FIDELITYBK</t>
+          <t>EGX:COMI</t>
         </is>
       </c>
       <c r="D55" s="11" t="inlineStr">
         <is>
-          <t>Fidelity Bank</t>
+          <t>Egypt Commercial International Bank</t>
         </is>
       </c>
       <c r="E55" s="11" t="inlineStr">
@@ -10308,7 +10308,7 @@
       </c>
       <c r="F55" s="11" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="G55" s="11" t="inlineStr">
@@ -10323,22 +10323,22 @@
       </c>
       <c r="I55" s="11" t="inlineStr">
         <is>
-          <t>43%</t>
+          <t>42%</t>
         </is>
       </c>
       <c r="J55" s="11" t="inlineStr">
         <is>
-          <t>2.08×</t>
+          <t>2.10×</t>
         </is>
       </c>
       <c r="K55" s="11" t="inlineStr">
         <is>
-          <t>2.59×</t>
+          <t>2.62×</t>
         </is>
       </c>
       <c r="L55" s="11" t="inlineStr">
         <is>
-          <t>1.76×</t>
+          <t>1.77×</t>
         </is>
       </c>
       <c r="M55" s="11" t="inlineStr">
@@ -10358,22 +10358,22 @@
       </c>
       <c r="C56" s="14" t="inlineStr">
         <is>
-          <t>KRX:034220</t>
+          <t>NGX:FIDELITYBK</t>
         </is>
       </c>
       <c r="D56" s="14" t="inlineStr">
         <is>
-          <t>LG Display</t>
+          <t>Fidelity Bank</t>
         </is>
       </c>
       <c r="E56" s="14" t="inlineStr">
         <is>
-          <t>Korea</t>
+          <t>MEA / Frontier</t>
         </is>
       </c>
       <c r="F56" s="14" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="G56" s="14" t="inlineStr">
@@ -10383,32 +10383,32 @@
       </c>
       <c r="H56" s="14" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>G</t>
         </is>
       </c>
       <c r="I56" s="14" t="inlineStr">
         <is>
-          <t>46%</t>
+          <t>43%</t>
         </is>
       </c>
       <c r="J56" s="14" t="inlineStr">
         <is>
-          <t>2.12×</t>
+          <t>2.08×</t>
         </is>
       </c>
       <c r="K56" s="14" t="inlineStr">
         <is>
-          <t>2.71×</t>
+          <t>2.59×</t>
         </is>
       </c>
       <c r="L56" s="14" t="inlineStr">
         <is>
-          <t>1.79×</t>
+          <t>1.76×</t>
         </is>
       </c>
       <c r="M56" s="14" t="inlineStr">
         <is>
-          <t>1.7×</t>
+          <t>1.8×</t>
         </is>
       </c>
     </row>
@@ -10423,22 +10423,22 @@
       </c>
       <c r="C57" s="11" t="inlineStr">
         <is>
-          <t>EGX:TMGH</t>
+          <t>KRX:034220</t>
         </is>
       </c>
       <c r="D57" s="11" t="inlineStr">
         <is>
-          <t>Talaat Moustafa Group</t>
+          <t>LG Display</t>
         </is>
       </c>
       <c r="E57" s="11" t="inlineStr">
         <is>
-          <t>MEA / Frontier</t>
+          <t>Korea</t>
         </is>
       </c>
       <c r="F57" s="11" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="G57" s="11" t="inlineStr">
@@ -10448,27 +10448,27 @@
       </c>
       <c r="H57" s="11" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>H</t>
         </is>
       </c>
       <c r="I57" s="11" t="inlineStr">
         <is>
-          <t>43%</t>
+          <t>46%</t>
         </is>
       </c>
       <c r="J57" s="11" t="inlineStr">
         <is>
-          <t>2.07×</t>
+          <t>2.12×</t>
         </is>
       </c>
       <c r="K57" s="11" t="inlineStr">
         <is>
-          <t>2.58×</t>
+          <t>2.71×</t>
         </is>
       </c>
       <c r="L57" s="11" t="inlineStr">
         <is>
-          <t>1.75×</t>
+          <t>1.79×</t>
         </is>
       </c>
       <c r="M57" s="11" t="inlineStr">
@@ -10488,12 +10488,12 @@
       </c>
       <c r="C58" s="14" t="inlineStr">
         <is>
-          <t>NYSE:SBSW</t>
+          <t>EGX:TMGH</t>
         </is>
       </c>
       <c r="D58" s="14" t="inlineStr">
         <is>
-          <t>Sibanye-Stillwater</t>
+          <t>Talaat Moustafa Group</t>
         </is>
       </c>
       <c r="E58" s="14" t="inlineStr">
@@ -10503,12 +10503,12 @@
       </c>
       <c r="F58" s="14" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="G58" s="14" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H58" s="14" t="inlineStr">
@@ -10518,22 +10518,22 @@
       </c>
       <c r="I58" s="14" t="inlineStr">
         <is>
-          <t>44%</t>
+          <t>43%</t>
         </is>
       </c>
       <c r="J58" s="14" t="inlineStr">
         <is>
-          <t>2.06×</t>
+          <t>2.07×</t>
         </is>
       </c>
       <c r="K58" s="14" t="inlineStr">
         <is>
-          <t>2.56×</t>
+          <t>2.58×</t>
         </is>
       </c>
       <c r="L58" s="14" t="inlineStr">
         <is>
-          <t>1.74×</t>
+          <t>1.75×</t>
         </is>
       </c>
       <c r="M58" s="14" t="inlineStr">
@@ -10553,17 +10553,17 @@
       </c>
       <c r="C59" s="11" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>NYSE:SBSW</t>
         </is>
       </c>
       <c r="D59" s="11" t="inlineStr">
         <is>
-          <t>MEMPHASYS LIMITED.</t>
+          <t>Sibanye-Stillwater</t>
         </is>
       </c>
       <c r="E59" s="11" t="inlineStr">
         <is>
-          <t>SE Asia / Pacific</t>
+          <t>MEA / Frontier</t>
         </is>
       </c>
       <c r="F59" s="11" t="inlineStr">
@@ -10573,12 +10573,12 @@
       </c>
       <c r="G59" s="11" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H59" s="11" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>G</t>
         </is>
       </c>
       <c r="I59" s="11" t="inlineStr">
@@ -10618,17 +10618,17 @@
       </c>
       <c r="C60" s="14" t="inlineStr">
         <is>
-          <t>CIK:0001348911</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="D60" s="14" t="inlineStr">
         <is>
-          <t>KalVista Pharmaceuticals, Inc.</t>
+          <t>MEMPHASYS LIMITED.</t>
         </is>
       </c>
       <c r="E60" s="14" t="inlineStr">
         <is>
-          <t>United States/Canada</t>
+          <t>SE Asia / Pacific</t>
         </is>
       </c>
       <c r="F60" s="14" t="inlineStr">
@@ -10643,7 +10643,7 @@
       </c>
       <c r="H60" s="14" t="inlineStr">
         <is>
-          <t>K3</t>
+          <t>B</t>
         </is>
       </c>
       <c r="I60" s="14" t="inlineStr">
@@ -10683,12 +10683,12 @@
       </c>
       <c r="C61" s="11" t="inlineStr">
         <is>
-          <t>CIK:0001909770</t>
+          <t>CIK:0001348911</t>
         </is>
       </c>
       <c r="D61" s="11" t="inlineStr">
         <is>
-          <t>KHEOBA CORP.</t>
+          <t>KalVista Pharmaceuticals, Inc.</t>
         </is>
       </c>
       <c r="E61" s="11" t="inlineStr">
@@ -10748,12 +10748,12 @@
       </c>
       <c r="C62" s="14" t="inlineStr">
         <is>
-          <t>CIK:0001489096</t>
+          <t>CIK:0001909770</t>
         </is>
       </c>
       <c r="D62" s="14" t="inlineStr">
         <is>
-          <t>Thermon Group Holdings, Inc.</t>
+          <t>KHEOBA CORP.</t>
         </is>
       </c>
       <c r="E62" s="14" t="inlineStr">
@@ -10813,12 +10813,12 @@
       </c>
       <c r="C63" s="11" t="inlineStr">
         <is>
-          <t>WYTC</t>
+          <t>CIK:0001489096</t>
         </is>
       </c>
       <c r="D63" s="11" t="inlineStr">
         <is>
-          <t>WYTEC INTERNATIONAL INC</t>
+          <t>Thermon Group Holdings, Inc.</t>
         </is>
       </c>
       <c r="E63" s="11" t="inlineStr">
@@ -10878,12 +10878,12 @@
       </c>
       <c r="C64" s="14" t="inlineStr">
         <is>
-          <t>CIK:0001408100</t>
+          <t>WYTC</t>
         </is>
       </c>
       <c r="D64" s="14" t="inlineStr">
         <is>
-          <t>Kennedy-Wilson Holdings, Inc.</t>
+          <t>WYTEC INTERNATIONAL INC</t>
         </is>
       </c>
       <c r="E64" s="14" t="inlineStr">
@@ -10943,12 +10943,12 @@
       </c>
       <c r="C65" s="11" t="inlineStr">
         <is>
-          <t>CIK:0002073537</t>
+          <t>CIK:0001408100</t>
         </is>
       </c>
       <c r="D65" s="11" t="inlineStr">
         <is>
-          <t>PIMCO Asset-Based Lending Co LLC</t>
+          <t>Kennedy-Wilson Holdings, Inc.</t>
         </is>
       </c>
       <c r="E65" s="11" t="inlineStr">
@@ -11008,12 +11008,12 @@
       </c>
       <c r="C66" s="14" t="inlineStr">
         <is>
-          <t>VIASP</t>
+          <t>CIK:0002073537</t>
         </is>
       </c>
       <c r="D66" s="14" t="inlineStr">
         <is>
-          <t>Via Renewables, Inc.</t>
+          <t>PIMCO Asset-Based Lending Co LLC</t>
         </is>
       </c>
       <c r="E66" s="14" t="inlineStr">
@@ -11073,12 +11073,12 @@
       </c>
       <c r="C67" s="11" t="inlineStr">
         <is>
-          <t>CIK:0001117171</t>
+          <t>VIASP</t>
         </is>
       </c>
       <c r="D67" s="11" t="inlineStr">
         <is>
-          <t>CBAK Energy Technology, Inc.</t>
+          <t>Via Renewables, Inc.</t>
         </is>
       </c>
       <c r="E67" s="11" t="inlineStr">
@@ -11138,12 +11138,12 @@
       </c>
       <c r="C68" s="14" t="inlineStr">
         <is>
-          <t>CIK:0001500305</t>
+          <t>CIK:0001117171</t>
         </is>
       </c>
       <c r="D68" s="14" t="inlineStr">
         <is>
-          <t>Sustainable Projects Group Inc.</t>
+          <t>CBAK Energy Technology, Inc.</t>
         </is>
       </c>
       <c r="E68" s="14" t="inlineStr">
@@ -11203,12 +11203,12 @@
       </c>
       <c r="C69" s="11" t="inlineStr">
         <is>
-          <t>CIK:0001127703</t>
+          <t>CIK:0001500305</t>
         </is>
       </c>
       <c r="D69" s="11" t="inlineStr">
         <is>
-          <t>PROASSURANCE CORP</t>
+          <t>Sustainable Projects Group Inc.</t>
         </is>
       </c>
       <c r="E69" s="11" t="inlineStr">
@@ -11268,12 +11268,12 @@
       </c>
       <c r="C70" s="14" t="inlineStr">
         <is>
-          <t>CIK:0001900520</t>
+          <t>CIK:0001127703</t>
         </is>
       </c>
       <c r="D70" s="14" t="inlineStr">
         <is>
-          <t>Lomond Therapeutics Holdings, Inc.</t>
+          <t>PROASSURANCE CORP</t>
         </is>
       </c>
       <c r="E70" s="14" t="inlineStr">
@@ -11333,22 +11333,22 @@
       </c>
       <c r="C71" s="11" t="inlineStr">
         <is>
-          <t>HK:1918</t>
+          <t>CIK:0001900520</t>
         </is>
       </c>
       <c r="D71" s="11" t="inlineStr">
         <is>
-          <t>Sunac China</t>
+          <t>Lomond Therapeutics Holdings, Inc.</t>
         </is>
       </c>
       <c r="E71" s="11" t="inlineStr">
         <is>
-          <t>Greater China / HK</t>
+          <t>United States/Canada</t>
         </is>
       </c>
       <c r="F71" s="11" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="G71" s="11" t="inlineStr">
@@ -11358,32 +11358,32 @@
       </c>
       <c r="H71" s="11" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>K3</t>
         </is>
       </c>
       <c r="I71" s="11" t="inlineStr">
         <is>
-          <t>48%</t>
+          <t>44%</t>
         </is>
       </c>
       <c r="J71" s="11" t="inlineStr">
         <is>
-          <t>2.09×</t>
+          <t>2.06×</t>
         </is>
       </c>
       <c r="K71" s="11" t="inlineStr">
         <is>
-          <t>2.67×</t>
+          <t>2.56×</t>
         </is>
       </c>
       <c r="L71" s="11" t="inlineStr">
         <is>
-          <t>1.77×</t>
+          <t>1.74×</t>
         </is>
       </c>
       <c r="M71" s="11" t="inlineStr">
         <is>
-          <t>1.6×</t>
+          <t>1.7×</t>
         </is>
       </c>
     </row>
@@ -11398,22 +11398,22 @@
       </c>
       <c r="C72" s="14" t="inlineStr">
         <is>
-          <t>8074</t>
+          <t>HK:1918</t>
         </is>
       </c>
       <c r="D72" s="14" t="inlineStr">
         <is>
-          <t>ＹＵＡＳＡ</t>
+          <t>Sunac China</t>
         </is>
       </c>
       <c r="E72" s="14" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Greater China / HK</t>
         </is>
       </c>
       <c r="F72" s="14" t="inlineStr">
         <is>
-          <t>0.60</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="G72" s="14" t="inlineStr">
@@ -11423,27 +11423,27 @@
       </c>
       <c r="H72" s="14" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I72" s="14" t="inlineStr">
         <is>
-          <t>47%</t>
+          <t>48%</t>
         </is>
       </c>
       <c r="J72" s="14" t="inlineStr">
         <is>
-          <t>2.08×</t>
+          <t>2.09×</t>
         </is>
       </c>
       <c r="K72" s="14" t="inlineStr">
         <is>
-          <t>2.64×</t>
+          <t>2.67×</t>
         </is>
       </c>
       <c r="L72" s="14" t="inlineStr">
         <is>
-          <t>1.76×</t>
+          <t>1.77×</t>
         </is>
       </c>
       <c r="M72" s="14" t="inlineStr">
@@ -11463,12 +11463,12 @@
       </c>
       <c r="C73" s="11" t="inlineStr">
         <is>
-          <t>2198</t>
+          <t>8074</t>
         </is>
       </c>
       <c r="D73" s="11" t="inlineStr">
         <is>
-          <t>アイ・ケイ・ケイＨＤ</t>
+          <t>ＹＵＡＳＡ</t>
         </is>
       </c>
       <c r="E73" s="11" t="inlineStr">
@@ -11528,12 +11528,12 @@
       </c>
       <c r="C74" s="14" t="inlineStr">
         <is>
-          <t>3454</t>
+          <t>2198</t>
         </is>
       </c>
       <c r="D74" s="14" t="inlineStr">
         <is>
-          <t>ファーストブラザーズ</t>
+          <t>アイ・ケイ・ケイＨＤ</t>
         </is>
       </c>
       <c r="E74" s="14" t="inlineStr">
@@ -11593,12 +11593,12 @@
       </c>
       <c r="C75" s="11" t="inlineStr">
         <is>
-          <t>4641</t>
+          <t>3454</t>
         </is>
       </c>
       <c r="D75" s="11" t="inlineStr">
         <is>
-          <t>アルプス技</t>
+          <t>ファーストブラザーズ</t>
         </is>
       </c>
       <c r="E75" s="11" t="inlineStr">
@@ -11658,12 +11658,12 @@
       </c>
       <c r="C76" s="14" t="inlineStr">
         <is>
-          <t>4170</t>
+          <t>4641</t>
         </is>
       </c>
       <c r="D76" s="14" t="inlineStr">
         <is>
-          <t>Ｇ－ＫａｉｚｅｎＰＦ</t>
+          <t>アルプス技</t>
         </is>
       </c>
       <c r="E76" s="14" t="inlineStr">
@@ -11723,12 +11723,12 @@
       </c>
       <c r="C77" s="11" t="inlineStr">
         <is>
-          <t>TSE:6753</t>
+          <t>4170</t>
         </is>
       </c>
       <c r="D77" s="11" t="inlineStr">
         <is>
-          <t>Sharp</t>
+          <t>Ｇ－ＫａｉｚｅｎＰＦ</t>
         </is>
       </c>
       <c r="E77" s="11" t="inlineStr">
@@ -11738,7 +11738,7 @@
       </c>
       <c r="F77" s="11" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>0.60</t>
         </is>
       </c>
       <c r="G77" s="11" t="inlineStr">
@@ -11763,12 +11763,12 @@
       </c>
       <c r="K77" s="11" t="inlineStr">
         <is>
-          <t>2.62×</t>
+          <t>2.64×</t>
         </is>
       </c>
       <c r="L77" s="11" t="inlineStr">
         <is>
-          <t>1.75×</t>
+          <t>1.76×</t>
         </is>
       </c>
       <c r="M77" s="11" t="inlineStr">
@@ -11788,12 +11788,12 @@
       </c>
       <c r="C78" s="14" t="inlineStr">
         <is>
-          <t>3544</t>
+          <t>TSE:6753</t>
         </is>
       </c>
       <c r="D78" s="14" t="inlineStr">
         <is>
-          <t>サツドラＨＤ</t>
+          <t>Sharp</t>
         </is>
       </c>
       <c r="E78" s="14" t="inlineStr">
@@ -11803,7 +11803,7 @@
       </c>
       <c r="F78" s="14" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="G78" s="14" t="inlineStr">
@@ -11813,27 +11813,27 @@
       </c>
       <c r="H78" s="14" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>H</t>
         </is>
       </c>
       <c r="I78" s="14" t="inlineStr">
         <is>
-          <t>41%</t>
+          <t>47%</t>
         </is>
       </c>
       <c r="J78" s="14" t="inlineStr">
         <is>
-          <t>1.97×</t>
+          <t>2.08×</t>
         </is>
       </c>
       <c r="K78" s="14" t="inlineStr">
         <is>
-          <t>2.34×</t>
+          <t>2.62×</t>
         </is>
       </c>
       <c r="L78" s="14" t="inlineStr">
         <is>
-          <t>1.65×</t>
+          <t>1.75×</t>
         </is>
       </c>
       <c r="M78" s="14" t="inlineStr">
@@ -11853,12 +11853,12 @@
       </c>
       <c r="C79" s="11" t="inlineStr">
         <is>
-          <t>6897</t>
+          <t>3544</t>
         </is>
       </c>
       <c r="D79" s="11" t="inlineStr">
         <is>
-          <t>ツインバード</t>
+          <t>サツドラＨＤ</t>
         </is>
       </c>
       <c r="E79" s="11" t="inlineStr">
@@ -11918,12 +11918,12 @@
       </c>
       <c r="C80" s="14" t="inlineStr">
         <is>
-          <t>4951</t>
+          <t>6897</t>
         </is>
       </c>
       <c r="D80" s="14" t="inlineStr">
         <is>
-          <t>エステー</t>
+          <t>ツインバード</t>
         </is>
       </c>
       <c r="E80" s="14" t="inlineStr">
@@ -11983,12 +11983,12 @@
       </c>
       <c r="C81" s="11" t="inlineStr">
         <is>
-          <t>3659</t>
+          <t>4951</t>
         </is>
       </c>
       <c r="D81" s="11" t="inlineStr">
         <is>
-          <t>ネクソン</t>
+          <t>エステー</t>
         </is>
       </c>
       <c r="E81" s="11" t="inlineStr">
@@ -12048,22 +12048,22 @@
       </c>
       <c r="C82" s="14" t="inlineStr">
         <is>
-          <t>B3:LIGT3</t>
+          <t>3659</t>
         </is>
       </c>
       <c r="D82" s="14" t="inlineStr">
         <is>
-          <t>Light SA</t>
+          <t>ネクソン</t>
         </is>
       </c>
       <c r="E82" s="14" t="inlineStr">
         <is>
-          <t>Latin America</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="F82" s="14" t="inlineStr">
         <is>
-          <t>0.58</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="G82" s="14" t="inlineStr">
@@ -12073,27 +12073,27 @@
       </c>
       <c r="H82" s="14" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>C</t>
         </is>
       </c>
       <c r="I82" s="14" t="inlineStr">
         <is>
-          <t>40%</t>
+          <t>41%</t>
         </is>
       </c>
       <c r="J82" s="14" t="inlineStr">
         <is>
-          <t>1.98×</t>
+          <t>1.97×</t>
         </is>
       </c>
       <c r="K82" s="14" t="inlineStr">
         <is>
-          <t>2.37×</t>
+          <t>2.34×</t>
         </is>
       </c>
       <c r="L82" s="14" t="inlineStr">
         <is>
-          <t>1.66×</t>
+          <t>1.65×</t>
         </is>
       </c>
       <c r="M82" s="14" t="inlineStr">
@@ -12113,12 +12113,12 @@
       </c>
       <c r="C83" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>B3:LIGT3</t>
         </is>
       </c>
       <c r="D83" s="11" t="inlineStr">
         <is>
-          <t>ATOM EDUCAÇÃO E EDITORA S.A.</t>
+          <t>Light SA</t>
         </is>
       </c>
       <c r="E83" s="11" t="inlineStr">
@@ -12128,7 +12128,7 @@
       </c>
       <c r="F83" s="11" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>0.58</t>
         </is>
       </c>
       <c r="G83" s="11" t="inlineStr">
@@ -12138,27 +12138,27 @@
       </c>
       <c r="H83" s="11" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>E</t>
         </is>
       </c>
       <c r="I83" s="11" t="inlineStr">
         <is>
-          <t>41%</t>
+          <t>40%</t>
         </is>
       </c>
       <c r="J83" s="11" t="inlineStr">
         <is>
-          <t>1.97×</t>
+          <t>1.98×</t>
         </is>
       </c>
       <c r="K83" s="11" t="inlineStr">
         <is>
-          <t>2.34×</t>
+          <t>2.37×</t>
         </is>
       </c>
       <c r="L83" s="11" t="inlineStr">
         <is>
-          <t>1.65×</t>
+          <t>1.66×</t>
         </is>
       </c>
       <c r="M83" s="11" t="inlineStr">
@@ -12183,7 +12183,7 @@
       </c>
       <c r="D84" s="14" t="inlineStr">
         <is>
-          <t>OI S.A. - EM RECUPERAÇÃO JUDICIAL</t>
+          <t>ATOM EDUCAÇÃO E EDITORA S.A.</t>
         </is>
       </c>
       <c r="E84" s="14" t="inlineStr">
@@ -12203,7 +12203,7 @@
       </c>
       <c r="H84" s="14" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>C</t>
         </is>
       </c>
       <c r="I84" s="14" t="inlineStr">
@@ -12248,7 +12248,7 @@
       </c>
       <c r="D85" s="11" t="inlineStr">
         <is>
-          <t>PETTENATI S.A. INDUSTRIA TEXTIL</t>
+          <t>OI S.A. - EM RECUPERAÇÃO JUDICIAL</t>
         </is>
       </c>
       <c r="E85" s="11" t="inlineStr">
@@ -12268,7 +12268,7 @@
       </c>
       <c r="H85" s="11" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>E</t>
         </is>
       </c>
       <c r="I85" s="11" t="inlineStr">
@@ -12313,7 +12313,7 @@
       </c>
       <c r="D86" s="14" t="inlineStr">
         <is>
-          <t>BBM LOGÍSTICA S.A.</t>
+          <t>PETTENATI S.A. INDUSTRIA TEXTIL</t>
         </is>
       </c>
       <c r="E86" s="14" t="inlineStr">
@@ -12333,7 +12333,7 @@
       </c>
       <c r="H86" s="14" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>C</t>
         </is>
       </c>
       <c r="I86" s="14" t="inlineStr">
@@ -12378,7 +12378,7 @@
       </c>
       <c r="D87" s="11" t="inlineStr">
         <is>
-          <t>GRUPO TOKY S.A.</t>
+          <t>MANUFATURA DE BRINQUEDOS ESTRELA SA</t>
         </is>
       </c>
       <c r="E87" s="11" t="inlineStr">
@@ -12438,22 +12438,22 @@
       </c>
       <c r="C88" s="14" t="inlineStr">
         <is>
-          <t>NGX:ACCESSCORP</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D88" s="14" t="inlineStr">
         <is>
-          <t>Access Holdings</t>
+          <t>BBM LOGÍSTICA S.A.</t>
         </is>
       </c>
       <c r="E88" s="14" t="inlineStr">
         <is>
-          <t>MEA / Frontier</t>
+          <t>Latin America</t>
         </is>
       </c>
       <c r="F88" s="14" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="G88" s="14" t="inlineStr">
@@ -12463,27 +12463,27 @@
       </c>
       <c r="H88" s="14" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>E</t>
         </is>
       </c>
       <c r="I88" s="14" t="inlineStr">
         <is>
-          <t>45%</t>
+          <t>41%</t>
         </is>
       </c>
       <c r="J88" s="14" t="inlineStr">
         <is>
-          <t>2.03×</t>
+          <t>1.97×</t>
         </is>
       </c>
       <c r="K88" s="14" t="inlineStr">
         <is>
-          <t>2.50×</t>
+          <t>2.34×</t>
         </is>
       </c>
       <c r="L88" s="14" t="inlineStr">
         <is>
-          <t>1.70×</t>
+          <t>1.65×</t>
         </is>
       </c>
       <c r="M88" s="14" t="inlineStr">
@@ -12503,17 +12503,17 @@
       </c>
       <c r="C89" s="11" t="inlineStr">
         <is>
-          <t>ERM</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D89" s="11" t="inlineStr">
         <is>
-          <t>EMMERSON RESOURCES LIMITED</t>
+          <t>GRUPO TOKY S.A.</t>
         </is>
       </c>
       <c r="E89" s="11" t="inlineStr">
         <is>
-          <t>SE Asia / Pacific</t>
+          <t>Latin America</t>
         </is>
       </c>
       <c r="F89" s="11" t="inlineStr">
@@ -12568,22 +12568,22 @@
       </c>
       <c r="C90" s="14" t="inlineStr">
         <is>
-          <t>PEX</t>
+          <t>NGX:ACCESSCORP</t>
         </is>
       </c>
       <c r="D90" s="14" t="inlineStr">
         <is>
-          <t>PEEL MINING LIMITED</t>
+          <t>Access Holdings</t>
         </is>
       </c>
       <c r="E90" s="14" t="inlineStr">
         <is>
-          <t>SE Asia / Pacific</t>
+          <t>MEA / Frontier</t>
         </is>
       </c>
       <c r="F90" s="14" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="G90" s="14" t="inlineStr">
@@ -12593,27 +12593,27 @@
       </c>
       <c r="H90" s="14" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>G</t>
         </is>
       </c>
       <c r="I90" s="14" t="inlineStr">
         <is>
-          <t>41%</t>
+          <t>45%</t>
         </is>
       </c>
       <c r="J90" s="14" t="inlineStr">
         <is>
-          <t>1.97×</t>
+          <t>2.03×</t>
         </is>
       </c>
       <c r="K90" s="14" t="inlineStr">
         <is>
-          <t>2.34×</t>
+          <t>2.50×</t>
         </is>
       </c>
       <c r="L90" s="14" t="inlineStr">
         <is>
-          <t>1.65×</t>
+          <t>1.70×</t>
         </is>
       </c>
       <c r="M90" s="14" t="inlineStr">
@@ -12633,12 +12633,12 @@
       </c>
       <c r="C91" s="11" t="inlineStr">
         <is>
-          <t>AIS</t>
+          <t>ERM</t>
         </is>
       </c>
       <c r="D91" s="11" t="inlineStr">
         <is>
-          <t>AERIS RESOURCES LIMITED</t>
+          <t>EMMERSON RESOURCES LIMITED</t>
         </is>
       </c>
       <c r="E91" s="11" t="inlineStr">
@@ -12698,12 +12698,12 @@
       </c>
       <c r="C92" s="14" t="inlineStr">
         <is>
-          <t>ASM</t>
+          <t>PEX</t>
         </is>
       </c>
       <c r="D92" s="14" t="inlineStr">
         <is>
-          <t>AUSTRALIAN STRATEGIC MATERIALS LIMITED</t>
+          <t>PEEL MINING LIMITED</t>
         </is>
       </c>
       <c r="E92" s="14" t="inlineStr">
@@ -12763,12 +12763,12 @@
       </c>
       <c r="C93" s="11" t="inlineStr">
         <is>
-          <t>QUB</t>
+          <t>AIS</t>
         </is>
       </c>
       <c r="D93" s="11" t="inlineStr">
         <is>
-          <t>QUBE HOLDINGS LIMITED</t>
+          <t>AERIS RESOURCES LIMITED</t>
         </is>
       </c>
       <c r="E93" s="11" t="inlineStr">
@@ -12828,12 +12828,12 @@
       </c>
       <c r="C94" s="14" t="inlineStr">
         <is>
-          <t>NVA</t>
+          <t>ASM</t>
         </is>
       </c>
       <c r="D94" s="14" t="inlineStr">
         <is>
-          <t>NOVA MINERALS CORP</t>
+          <t>AUSTRALIAN STRATEGIC MATERIALS LIMITED</t>
         </is>
       </c>
       <c r="E94" s="14" t="inlineStr">
@@ -12893,12 +12893,12 @@
       </c>
       <c r="C95" s="11" t="inlineStr">
         <is>
-          <t>PAF</t>
+          <t>QUB</t>
         </is>
       </c>
       <c r="D95" s="11" t="inlineStr">
         <is>
-          <t>PAN AFRICAN RESOURCES PLC</t>
+          <t>QUBE HOLDINGS LIMITED</t>
         </is>
       </c>
       <c r="E95" s="11" t="inlineStr">
@@ -12958,12 +12958,12 @@
       </c>
       <c r="C96" s="14" t="inlineStr">
         <is>
-          <t>QOR</t>
+          <t>NVA</t>
         </is>
       </c>
       <c r="D96" s="14" t="inlineStr">
         <is>
-          <t>QORIA LIMITED</t>
+          <t>NOVA MINERALS CORP</t>
         </is>
       </c>
       <c r="E96" s="14" t="inlineStr">
@@ -13023,12 +13023,12 @@
       </c>
       <c r="C97" s="11" t="inlineStr">
         <is>
-          <t>LLM</t>
+          <t>PAF</t>
         </is>
       </c>
       <c r="D97" s="11" t="inlineStr">
         <is>
-          <t>LOYAL METALS LTD</t>
+          <t>PAN AFRICAN RESOURCES PLC</t>
         </is>
       </c>
       <c r="E97" s="11" t="inlineStr">
@@ -13088,17 +13088,17 @@
       </c>
       <c r="C98" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>QOR</t>
         </is>
       </c>
       <c r="D98" s="14" t="inlineStr">
         <is>
-          <t>REDCENTRIC PLC</t>
+          <t>QORIA LIMITED</t>
         </is>
       </c>
       <c r="E98" s="14" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>SE Asia / Pacific</t>
         </is>
       </c>
       <c r="F98" s="14" t="inlineStr">
@@ -13113,7 +13113,7 @@
       </c>
       <c r="H98" s="14" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>E</t>
         </is>
       </c>
       <c r="I98" s="14" t="inlineStr">
@@ -13153,17 +13153,17 @@
       </c>
       <c r="C99" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>LLM</t>
         </is>
       </c>
       <c r="D99" s="11" t="inlineStr">
         <is>
-          <t>CT HEALTHCARE TRUST PLC</t>
+          <t>LOYAL METALS LTD</t>
         </is>
       </c>
       <c r="E99" s="11" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>SE Asia / Pacific</t>
         </is>
       </c>
       <c r="F99" s="11" t="inlineStr">
@@ -13178,7 +13178,7 @@
       </c>
       <c r="H99" s="11" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>E</t>
         </is>
       </c>
       <c r="I99" s="11" t="inlineStr">
@@ -13223,7 +13223,7 @@
       </c>
       <c r="D100" s="14" t="inlineStr">
         <is>
-          <t>JUST GROUP PLC</t>
+          <t>REDCENTRIC PLC</t>
         </is>
       </c>
       <c r="E100" s="14" t="inlineStr">
@@ -13288,7 +13288,7 @@
       </c>
       <c r="D101" s="11" t="inlineStr">
         <is>
-          <t>Zambia (Republic of) (MoF)</t>
+          <t>CT HEALTHCARE TRUST PLC</t>
         </is>
       </c>
       <c r="E101" s="11" t="inlineStr">
@@ -13353,7 +13353,7 @@
       </c>
       <c r="D102" s="14" t="inlineStr">
         <is>
-          <t>LEGAL &amp; GENERAL GROUP PLC</t>
+          <t>JUST GROUP PLC</t>
         </is>
       </c>
       <c r="E102" s="14" t="inlineStr">
@@ -13418,7 +13418,7 @@
       </c>
       <c r="D103" s="11" t="inlineStr">
         <is>
-          <t>Treatt PLC</t>
+          <t>Zambia (Republic of) (MoF)</t>
         </is>
       </c>
       <c r="E103" s="11" t="inlineStr">
@@ -13438,7 +13438,7 @@
       </c>
       <c r="H103" s="11" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>C</t>
         </is>
       </c>
       <c r="I103" s="11" t="inlineStr">
@@ -13483,7 +13483,7 @@
       </c>
       <c r="D104" s="14" t="inlineStr">
         <is>
-          <t>GLOBALDATA PLC</t>
+          <t>LEGAL &amp; GENERAL GROUP PLC</t>
         </is>
       </c>
       <c r="E104" s="14" t="inlineStr">
@@ -13536,7 +13536,7 @@
     <row r="106" ht="60" customHeight="1">
       <c r="A106" s="7" t="inlineStr">
         <is>
-          <t>Reward/Risk = (EV× − 1) ÷ Bear loss = the asymmetry metric.  The broad universe-screener scores the full candidate set on archetype, vintage, status, size, region, and cross-source corroboration; this asymmetric scan ranks the investable subset (288 names) by reward/risk. Investable filter drops PASS_FALSE_FRIEND / ACQUIRED / ARC_DONE / REPEAT_RX and non-equity placeholder tickers ((state), (private), (delisted)). PROXY waterfall: bear_loss = max(0.10, 0.65 − 0.30·score), tilted ×0.75 for A1/A2 (sovereign-anchored floor). bull = 1.50 + 1.50·score, tilted ×1.10 for H, ×1.15 for F. Hand-built YAMLs override the proxy with bottom-up numbers.</t>
+          <t>Reward/Risk = (EV× − 1) ÷ Bear loss = the asymmetry metric.  The broad universe-screener scores the full candidate set on archetype, vintage, status, size, region, and cross-source corroboration; this asymmetric scan ranks the investable subset (308 names) by reward/risk. Investable filter drops PASS_FALSE_FRIEND / ACQUIRED / ARC_DONE / REPEAT_RX and non-equity placeholder tickers ((state), (private), (delisted)). PROXY waterfall: bear_loss = max(0.10, 0.65 − 0.30·score), tilted ×0.75 for A1/A2 (sovereign-anchored floor). bull = 1.50 + 1.50·score, tilted ×1.10 for H, ×1.15 for F. Hand-built YAMLs override the proxy with bottom-up numbers.</t>
         </is>
       </c>
     </row>
@@ -14083,22 +14083,22 @@
       </c>
       <c r="B16" s="14" t="inlineStr">
         <is>
-          <t>LSE:ASC</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C16" s="14" t="inlineStr">
         <is>
-          <t>ASOS</t>
+          <t>BRADESCO LEASING S.A. - ARRENDAMENTO MERCANTIL</t>
         </is>
       </c>
       <c r="D16" s="14" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Latin America</t>
         </is>
       </c>
       <c r="E16" s="14" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="F16" s="14" t="inlineStr">
@@ -14123,27 +14123,27 @@
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>TBRG</t>
+          <t>LSE:ASC</t>
         </is>
       </c>
       <c r="C17" s="11" t="inlineStr">
         <is>
-          <t>TruBridge, Inc.</t>
+          <t>ASOS</t>
         </is>
       </c>
       <c r="D17" s="11" t="inlineStr">
         <is>
-          <t>United States/Canada</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="E17" s="11" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="F17" s="11" t="inlineStr">
         <is>
-          <t>K3</t>
+          <t>A1</t>
         </is>
       </c>
       <c r="G17" s="11" t="inlineStr">
@@ -14153,7 +14153,7 @@
       </c>
       <c r="H17" s="11" t="inlineStr">
         <is>
-          <t>Tier 1 — hand-deepen ASAP</t>
+          <t>Tier 2 — verify primary docs first</t>
         </is>
       </c>
     </row>
@@ -14163,12 +14163,12 @@
       </c>
       <c r="B18" s="14" t="inlineStr">
         <is>
-          <t>LEG</t>
+          <t>TBRG</t>
         </is>
       </c>
       <c r="C18" s="14" t="inlineStr">
         <is>
-          <t>LEGGETT &amp; PLATT INC</t>
+          <t>TruBridge, Inc.</t>
         </is>
       </c>
       <c r="D18" s="14" t="inlineStr">
@@ -14178,12 +14178,12 @@
       </c>
       <c r="E18" s="14" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="F18" s="14" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>K3</t>
         </is>
       </c>
       <c r="G18" s="14" t="inlineStr">
@@ -14199,16 +14199,16 @@
     </row>
     <row r="19">
       <c r="A19" s="9" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>TSX:CFW</t>
+          <t>LEG</t>
         </is>
       </c>
       <c r="C19" s="11" t="inlineStr">
         <is>
-          <t>Calfrac Well Services</t>
+          <t>LEGGETT &amp; PLATT INC</t>
         </is>
       </c>
       <c r="D19" s="11" t="inlineStr">
@@ -14218,22 +14218,22 @@
       </c>
       <c r="E19" s="11" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="F19" s="11" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>C</t>
         </is>
       </c>
       <c r="G19" s="11" t="inlineStr">
         <is>
-          <t>2.5×</t>
+          <t>2.6×</t>
         </is>
       </c>
       <c r="H19" s="11" t="inlineStr">
         <is>
-          <t>Tier 2 — verify primary docs first</t>
+          <t>Tier 1 — hand-deepen ASAP</t>
         </is>
       </c>
     </row>
@@ -14243,37 +14243,37 @@
       </c>
       <c r="B20" s="14" t="inlineStr">
         <is>
-          <t>KRX:028260</t>
+          <t>TSX:CFW</t>
         </is>
       </c>
       <c r="C20" s="14" t="inlineStr">
         <is>
-          <t>Samsung C&amp;T</t>
+          <t>Calfrac Well Services</t>
         </is>
       </c>
       <c r="D20" s="14" t="inlineStr">
         <is>
-          <t>Korea</t>
+          <t>United States/Canada</t>
         </is>
       </c>
       <c r="E20" s="14" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="F20" s="14" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>A1</t>
         </is>
       </c>
       <c r="G20" s="14" t="inlineStr">
         <is>
-          <t>2.4×</t>
+          <t>2.5×</t>
         </is>
       </c>
       <c r="H20" s="14" t="inlineStr">
         <is>
-          <t>Tier 1 — hand-deepen ASAP</t>
+          <t>Tier 2 — verify primary docs first</t>
         </is>
       </c>
     </row>
@@ -14283,27 +14283,27 @@
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t>LSE:AML</t>
+          <t>KRX:028260</t>
         </is>
       </c>
       <c r="C21" s="11" t="inlineStr">
         <is>
-          <t>Aston Martin Lagonda</t>
+          <t>Samsung C&amp;T</t>
         </is>
       </c>
       <c r="D21" s="11" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Korea</t>
         </is>
       </c>
       <c r="E21" s="11" t="inlineStr">
         <is>
-          <t>0.70</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="F21" s="11" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>H</t>
         </is>
       </c>
       <c r="G21" s="11" t="inlineStr">
@@ -14313,7 +14313,7 @@
       </c>
       <c r="H21" s="11" t="inlineStr">
         <is>
-          <t>Tier 2 — verify primary docs first</t>
+          <t>Tier 1 — hand-deepen ASAP</t>
         </is>
       </c>
     </row>
@@ -14323,27 +14323,27 @@
       </c>
       <c r="B22" s="14" t="inlineStr">
         <is>
-          <t>APTOF</t>
+          <t>LSE:AML</t>
         </is>
       </c>
       <c r="C22" s="14" t="inlineStr">
         <is>
-          <t>Aptose Biosciences Inc.</t>
+          <t>Aston Martin Lagonda</t>
         </is>
       </c>
       <c r="D22" s="14" t="inlineStr">
         <is>
-          <t>United States/Canada</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="E22" s="14" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="F22" s="14" t="inlineStr">
         <is>
-          <t>K3</t>
+          <t>A1</t>
         </is>
       </c>
       <c r="G22" s="14" t="inlineStr">
@@ -14353,7 +14353,7 @@
       </c>
       <c r="H22" s="14" t="inlineStr">
         <is>
-          <t>Tier 1 — hand-deepen ASAP</t>
+          <t>Tier 2 — verify primary docs first</t>
         </is>
       </c>
     </row>
@@ -14363,37 +14363,37 @@
       </c>
       <c r="B23" s="11" t="inlineStr">
         <is>
-          <t>HK:2202</t>
+          <t>APTOF</t>
         </is>
       </c>
       <c r="C23" s="11" t="inlineStr">
         <is>
-          <t>Vanke</t>
+          <t>Aptose Biosciences Inc.</t>
         </is>
       </c>
       <c r="D23" s="11" t="inlineStr">
         <is>
-          <t>Greater China / HK</t>
+          <t>United States/Canada</t>
         </is>
       </c>
       <c r="E23" s="11" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="F23" s="11" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>K3</t>
         </is>
       </c>
       <c r="G23" s="11" t="inlineStr">
         <is>
-          <t>2.3×</t>
+          <t>2.4×</t>
         </is>
       </c>
       <c r="H23" s="11" t="inlineStr">
         <is>
-          <t>Tier 2 — verify primary docs first</t>
+          <t>Tier 1 — hand-deepen ASAP</t>
         </is>
       </c>
     </row>
@@ -14403,22 +14403,22 @@
       </c>
       <c r="B24" s="14" t="inlineStr">
         <is>
-          <t>LSE:VOD</t>
+          <t>HK:2202</t>
         </is>
       </c>
       <c r="C24" s="14" t="inlineStr">
         <is>
-          <t>Vodafone</t>
+          <t>Vanke</t>
         </is>
       </c>
       <c r="D24" s="14" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Greater China / HK</t>
         </is>
       </c>
       <c r="E24" s="14" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="F24" s="14" t="inlineStr">

--- a/output/cyclepapa_risk_reward_workbook.xlsx
+++ b/output/cyclepapa_risk_reward_workbook.xlsx
@@ -80,14 +80,14 @@
     </font>
     <font>
       <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="00111111"/>
+      <i val="1"/>
+      <color rgb="005B6B85"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Calibri"/>
-      <i val="1"/>
-      <color rgb="005B6B85"/>
+      <b val="1"/>
+      <color rgb="00111111"/>
       <sz val="10"/>
     </font>
   </fonts>
@@ -196,7 +196,7 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -205,13 +205,13 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -6938,7 +6938,7 @@
     <col width="60" customWidth="1" min="1" max="1"/>
     <col width="8" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="49" customWidth="1" min="4" max="4"/>
+    <col width="52" customWidth="1" min="4" max="4"/>
     <col width="22" customWidth="1" min="5" max="5"/>
     <col width="8" customWidth="1" min="6" max="6"/>
     <col width="8" customWidth="1" min="7" max="7"/>
@@ -6960,7 +6960,7 @@
     <row r="2" ht="38" customHeight="1">
       <c r="A2" s="7" t="inlineStr">
         <is>
-          <t>Universe coverage: 308 investable names (21 REAL waterfalls · 287 PROXY).  REAL uses the hand-built YAML's bottom-up bear/base/bull. PROXY uses a transparent formula on the universe-screener score + archetype tilt.</t>
+          <t>Universe coverage: 731 investable names (20 REAL waterfalls · 711 PROXY).  REAL uses the hand-built YAML's bottom-up bear/base/bull. PROXY uses a transparent formula on the universe-screener score + archetype tilt.</t>
         </is>
       </c>
     </row>
@@ -7038,27 +7038,27 @@
       </c>
       <c r="B5" s="10" t="inlineStr">
         <is>
-          <t>REAL</t>
+          <t>PROXY</t>
         </is>
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>EPA:LOCAL</t>
+          <t>NYSE:TGS</t>
         </is>
       </c>
       <c r="D5" s="11" t="inlineStr">
         <is>
-          <t>Solocal Group</t>
+          <t>TGS (Transportadora de Gas del Sur)</t>
         </is>
       </c>
       <c r="E5" s="11" t="inlineStr">
         <is>
-          <t>Continental Europe</t>
+          <t>Latin America</t>
         </is>
       </c>
       <c r="F5" s="11" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="G5" s="11" t="inlineStr">
@@ -7068,32 +7068,32 @@
       </c>
       <c r="H5" s="11" t="inlineStr">
         <is>
-          <t>E+A1</t>
+          <t>A1</t>
         </is>
       </c>
       <c r="I5" s="11" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>24%</t>
         </is>
       </c>
       <c r="J5" s="11" t="inlineStr">
         <is>
-          <t>3.50×</t>
+          <t>2.44×</t>
         </is>
       </c>
       <c r="K5" s="11" t="inlineStr">
         <is>
-          <t>7.50×</t>
+          <t>3.12×</t>
         </is>
       </c>
       <c r="L5" s="11" t="inlineStr">
         <is>
-          <t>4.04×</t>
+          <t>2.10×</t>
         </is>
       </c>
       <c r="M5" s="11" t="inlineStr">
         <is>
-          <t>20.2×</t>
+          <t>4.5×</t>
         </is>
       </c>
     </row>
@@ -7108,12 +7108,12 @@
       </c>
       <c r="C6" s="14" t="inlineStr">
         <is>
-          <t>NYSE:TGS</t>
+          <t>NYSE:EDN</t>
         </is>
       </c>
       <c r="D6" s="14" t="inlineStr">
         <is>
-          <t>TGS (Transportadora de Gas del Sur)</t>
+          <t>Edenor</t>
         </is>
       </c>
       <c r="E6" s="14" t="inlineStr">
@@ -7123,7 +7123,7 @@
       </c>
       <c r="F6" s="14" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="G6" s="14" t="inlineStr">
@@ -7138,27 +7138,27 @@
       </c>
       <c r="I6" s="14" t="inlineStr">
         <is>
-          <t>24%</t>
+          <t>26%</t>
         </is>
       </c>
       <c r="J6" s="14" t="inlineStr">
         <is>
-          <t>2.44×</t>
+          <t>2.38×</t>
         </is>
       </c>
       <c r="K6" s="14" t="inlineStr">
         <is>
-          <t>3.12×</t>
+          <t>3.02×</t>
         </is>
       </c>
       <c r="L6" s="14" t="inlineStr">
         <is>
-          <t>2.10×</t>
+          <t>2.05×</t>
         </is>
       </c>
       <c r="M6" s="14" t="inlineStr">
         <is>
-          <t>4.5×</t>
+          <t>4.0×</t>
         </is>
       </c>
     </row>
@@ -7166,29 +7166,29 @@
       <c r="A7" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="B7" s="15" t="inlineStr">
+      <c r="B7" s="10" t="inlineStr">
         <is>
           <t>PROXY</t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>NYSE:EDN</t>
+          <t>BIT:MB</t>
         </is>
       </c>
       <c r="D7" s="11" t="inlineStr">
         <is>
-          <t>Edenor</t>
+          <t>Mediobanca</t>
         </is>
       </c>
       <c r="E7" s="11" t="inlineStr">
         <is>
-          <t>Latin America</t>
+          <t>Continental Europe</t>
         </is>
       </c>
       <c r="F7" s="11" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="G7" s="11" t="inlineStr">
@@ -7203,27 +7203,27 @@
       </c>
       <c r="I7" s="11" t="inlineStr">
         <is>
-          <t>26%</t>
+          <t>27%</t>
         </is>
       </c>
       <c r="J7" s="11" t="inlineStr">
         <is>
-          <t>2.38×</t>
+          <t>2.33×</t>
         </is>
       </c>
       <c r="K7" s="11" t="inlineStr">
         <is>
-          <t>3.02×</t>
+          <t>2.94×</t>
         </is>
       </c>
       <c r="L7" s="11" t="inlineStr">
         <is>
-          <t>2.05×</t>
+          <t>2.00×</t>
         </is>
       </c>
       <c r="M7" s="11" t="inlineStr">
         <is>
-          <t>4.0×</t>
+          <t>3.7×</t>
         </is>
       </c>
     </row>
@@ -7238,22 +7238,22 @@
       </c>
       <c r="C8" s="14" t="inlineStr">
         <is>
-          <t>BIT:MB</t>
+          <t>NYSE:GGAL</t>
         </is>
       </c>
       <c r="D8" s="14" t="inlineStr">
         <is>
-          <t>Mediobanca</t>
+          <t>Banco Galicia</t>
         </is>
       </c>
       <c r="E8" s="14" t="inlineStr">
         <is>
-          <t>Continental Europe</t>
+          <t>Latin America</t>
         </is>
       </c>
       <c r="F8" s="14" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="G8" s="14" t="inlineStr">
@@ -7278,7 +7278,7 @@
       </c>
       <c r="K8" s="14" t="inlineStr">
         <is>
-          <t>2.94×</t>
+          <t>2.92×</t>
         </is>
       </c>
       <c r="L8" s="14" t="inlineStr">
@@ -7288,7 +7288,7 @@
       </c>
       <c r="M8" s="14" t="inlineStr">
         <is>
-          <t>3.7×</t>
+          <t>3.6×</t>
         </is>
       </c>
     </row>
@@ -7298,27 +7298,27 @@
       </c>
       <c r="B9" s="15" t="inlineStr">
         <is>
-          <t>PROXY</t>
+          <t>REAL</t>
         </is>
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>NYSE:GGAL</t>
+          <t>NYSE:LAC</t>
         </is>
       </c>
       <c r="D9" s="11" t="inlineStr">
         <is>
-          <t>Banco Galicia</t>
+          <t>Lithium Americas</t>
         </is>
       </c>
       <c r="E9" s="11" t="inlineStr">
         <is>
-          <t>Latin America</t>
+          <t>United States/Canada</t>
         </is>
       </c>
       <c r="F9" s="11" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="G9" s="11" t="inlineStr">
@@ -7328,32 +7328,32 @@
       </c>
       <c r="H9" s="11" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2</t>
         </is>
       </c>
       <c r="I9" s="11" t="inlineStr">
         <is>
-          <t>27%</t>
+          <t>60%</t>
         </is>
       </c>
       <c r="J9" s="11" t="inlineStr">
         <is>
-          <t>2.33×</t>
+          <t>3.00×</t>
         </is>
       </c>
       <c r="K9" s="11" t="inlineStr">
         <is>
-          <t>2.92×</t>
+          <t>6.00×</t>
         </is>
       </c>
       <c r="L9" s="11" t="inlineStr">
         <is>
-          <t>2.00×</t>
+          <t>3.10×</t>
         </is>
       </c>
       <c r="M9" s="11" t="inlineStr">
         <is>
-          <t>3.6×</t>
+          <t>3.5×</t>
         </is>
       </c>
     </row>
@@ -7361,29 +7361,29 @@
       <c r="A10" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="B10" s="16" t="inlineStr">
-        <is>
-          <t>REAL</t>
+      <c r="B10" s="13" t="inlineStr">
+        <is>
+          <t>PROXY</t>
         </is>
       </c>
       <c r="C10" s="14" t="inlineStr">
         <is>
-          <t>NYSE:LAC</t>
+          <t>NYSE:PAM</t>
         </is>
       </c>
       <c r="D10" s="14" t="inlineStr">
         <is>
-          <t>Lithium Americas</t>
+          <t>Pampa Energía</t>
         </is>
       </c>
       <c r="E10" s="14" t="inlineStr">
         <is>
-          <t>United States/Canada</t>
+          <t>Latin America</t>
         </is>
       </c>
       <c r="F10" s="14" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="G10" s="14" t="inlineStr">
@@ -7393,32 +7393,32 @@
       </c>
       <c r="H10" s="14" t="inlineStr">
         <is>
-          <t>A2</t>
+          <t>A1</t>
         </is>
       </c>
       <c r="I10" s="14" t="inlineStr">
         <is>
-          <t>60%</t>
+          <t>28%</t>
         </is>
       </c>
       <c r="J10" s="14" t="inlineStr">
         <is>
-          <t>3.00×</t>
+          <t>2.29×</t>
         </is>
       </c>
       <c r="K10" s="14" t="inlineStr">
         <is>
-          <t>6.00×</t>
+          <t>2.87×</t>
         </is>
       </c>
       <c r="L10" s="14" t="inlineStr">
         <is>
-          <t>3.10×</t>
+          <t>1.96×</t>
         </is>
       </c>
       <c r="M10" s="14" t="inlineStr">
         <is>
-          <t>3.5×</t>
+          <t>3.4×</t>
         </is>
       </c>
     </row>
@@ -7426,7 +7426,7 @@
       <c r="A11" s="9" t="n">
         <v>7</v>
       </c>
-      <c r="B11" s="10" t="inlineStr">
+      <c r="B11" s="15" t="inlineStr">
         <is>
           <t>REAL</t>
         </is>
@@ -7491,29 +7491,29 @@
       <c r="A12" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="B12" s="13" t="inlineStr">
-        <is>
-          <t>PROXY</t>
+      <c r="B12" s="16" t="inlineStr">
+        <is>
+          <t>REAL</t>
         </is>
       </c>
       <c r="C12" s="14" t="inlineStr">
         <is>
-          <t>NYSE:PAM</t>
+          <t>XETR:TKA</t>
         </is>
       </c>
       <c r="D12" s="14" t="inlineStr">
         <is>
-          <t>Pampa Energía</t>
+          <t>Thyssenkrupp Steel</t>
         </is>
       </c>
       <c r="E12" s="14" t="inlineStr">
         <is>
-          <t>Latin America</t>
+          <t>Continental Europe</t>
         </is>
       </c>
       <c r="F12" s="14" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="G12" s="14" t="inlineStr">
@@ -7523,32 +7523,32 @@
       </c>
       <c r="H12" s="14" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>H</t>
         </is>
       </c>
       <c r="I12" s="14" t="inlineStr">
         <is>
-          <t>28%</t>
+          <t>45%</t>
         </is>
       </c>
       <c r="J12" s="14" t="inlineStr">
         <is>
-          <t>2.29×</t>
+          <t>2.30×</t>
         </is>
       </c>
       <c r="K12" s="14" t="inlineStr">
         <is>
-          <t>2.87×</t>
+          <t>4.20×</t>
         </is>
       </c>
       <c r="L12" s="14" t="inlineStr">
         <is>
-          <t>1.96×</t>
+          <t>2.34×</t>
         </is>
       </c>
       <c r="M12" s="14" t="inlineStr">
         <is>
-          <t>3.4×</t>
+          <t>3.0×</t>
         </is>
       </c>
     </row>
@@ -7558,27 +7558,27 @@
       </c>
       <c r="B13" s="10" t="inlineStr">
         <is>
-          <t>REAL</t>
+          <t>PROXY</t>
         </is>
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>XETR:TKA</t>
+          <t>ACF</t>
         </is>
       </c>
       <c r="D13" s="11" t="inlineStr">
         <is>
-          <t>Thyssenkrupp Steel</t>
+          <t>ACROW LIMITED</t>
         </is>
       </c>
       <c r="E13" s="11" t="inlineStr">
         <is>
-          <t>Continental Europe</t>
+          <t>SE Asia / Pacific</t>
         </is>
       </c>
       <c r="F13" s="11" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="G13" s="11" t="inlineStr">
@@ -7588,27 +7588,27 @@
       </c>
       <c r="H13" s="11" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>A1</t>
         </is>
       </c>
       <c r="I13" s="11" t="inlineStr">
         <is>
-          <t>45%</t>
+          <t>30%</t>
         </is>
       </c>
       <c r="J13" s="11" t="inlineStr">
         <is>
-          <t>2.30×</t>
+          <t>2.22×</t>
         </is>
       </c>
       <c r="K13" s="11" t="inlineStr">
         <is>
-          <t>4.20×</t>
+          <t>2.75×</t>
         </is>
       </c>
       <c r="L13" s="11" t="inlineStr">
         <is>
-          <t>2.34×</t>
+          <t>1.90×</t>
         </is>
       </c>
       <c r="M13" s="11" t="inlineStr">
@@ -7621,29 +7621,29 @@
       <c r="A14" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="B14" s="13" t="inlineStr">
-        <is>
-          <t>PROXY</t>
+      <c r="B14" s="16" t="inlineStr">
+        <is>
+          <t>REAL</t>
         </is>
       </c>
       <c r="C14" s="14" t="inlineStr">
         <is>
-          <t>ACF</t>
+          <t>NGX:GTCO</t>
         </is>
       </c>
       <c r="D14" s="14" t="inlineStr">
         <is>
-          <t>ACROW LIMITED</t>
+          <t>GTCO (Guaranty Trust)</t>
         </is>
       </c>
       <c r="E14" s="14" t="inlineStr">
         <is>
-          <t>SE Asia / Pacific</t>
+          <t>MEA / Frontier</t>
         </is>
       </c>
       <c r="F14" s="14" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="G14" s="14" t="inlineStr">
@@ -7653,32 +7653,32 @@
       </c>
       <c r="H14" s="14" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>G</t>
         </is>
       </c>
       <c r="I14" s="14" t="inlineStr">
         <is>
-          <t>30%</t>
+          <t>40%</t>
         </is>
       </c>
       <c r="J14" s="14" t="inlineStr">
         <is>
-          <t>2.22×</t>
+          <t>2.10×</t>
         </is>
       </c>
       <c r="K14" s="14" t="inlineStr">
         <is>
-          <t>2.75×</t>
+          <t>3.80×</t>
         </is>
       </c>
       <c r="L14" s="14" t="inlineStr">
         <is>
-          <t>1.90×</t>
+          <t>2.15×</t>
         </is>
       </c>
       <c r="M14" s="14" t="inlineStr">
         <is>
-          <t>3.0×</t>
+          <t>2.9×</t>
         </is>
       </c>
     </row>
@@ -7686,29 +7686,29 @@
       <c r="A15" s="9" t="n">
         <v>11</v>
       </c>
-      <c r="B15" s="10" t="inlineStr">
+      <c r="B15" s="15" t="inlineStr">
         <is>
           <t>REAL</t>
         </is>
       </c>
       <c r="C15" s="11" t="inlineStr">
         <is>
-          <t>NGX:GTCO</t>
+          <t>STO:ELUX-B</t>
         </is>
       </c>
       <c r="D15" s="11" t="inlineStr">
         <is>
-          <t>GTCO (Guaranty Trust)</t>
+          <t>AB Electrolux (Series B)</t>
         </is>
       </c>
       <c r="E15" s="11" t="inlineStr">
         <is>
-          <t>MEA / Frontier</t>
+          <t>Continental Europe</t>
         </is>
       </c>
       <c r="F15" s="11" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="G15" s="11" t="inlineStr">
@@ -7718,27 +7718,27 @@
       </c>
       <c r="H15" s="11" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>A1+D</t>
         </is>
       </c>
       <c r="I15" s="11" t="inlineStr">
         <is>
-          <t>40%</t>
+          <t>45%</t>
         </is>
       </c>
       <c r="J15" s="11" t="inlineStr">
         <is>
-          <t>2.10×</t>
+          <t>2.20×</t>
         </is>
       </c>
       <c r="K15" s="11" t="inlineStr">
         <is>
-          <t>3.80×</t>
+          <t>4.00×</t>
         </is>
       </c>
       <c r="L15" s="11" t="inlineStr">
         <is>
-          <t>2.15×</t>
+          <t>2.32×</t>
         </is>
       </c>
       <c r="M15" s="11" t="inlineStr">
@@ -7758,22 +7758,22 @@
       </c>
       <c r="C16" s="14" t="inlineStr">
         <is>
-          <t>STO:ELUX-B</t>
+          <t>TSE:6305</t>
         </is>
       </c>
       <c r="D16" s="14" t="inlineStr">
         <is>
-          <t>AB Electrolux (Series B)</t>
+          <t>Hitachi Construction Machinery</t>
         </is>
       </c>
       <c r="E16" s="14" t="inlineStr">
         <is>
-          <t>Continental Europe</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="F16" s="14" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="G16" s="14" t="inlineStr">
@@ -7783,32 +7783,32 @@
       </c>
       <c r="H16" s="14" t="inlineStr">
         <is>
-          <t>A1+D</t>
+          <t>H</t>
         </is>
       </c>
       <c r="I16" s="14" t="inlineStr">
         <is>
-          <t>45%</t>
+          <t>25%</t>
         </is>
       </c>
       <c r="J16" s="14" t="inlineStr">
         <is>
-          <t>2.20×</t>
+          <t>1.70×</t>
         </is>
       </c>
       <c r="K16" s="14" t="inlineStr">
         <is>
-          <t>4.00×</t>
+          <t>2.80×</t>
         </is>
       </c>
       <c r="L16" s="14" t="inlineStr">
         <is>
-          <t>2.32×</t>
+          <t>1.69×</t>
         </is>
       </c>
       <c r="M16" s="14" t="inlineStr">
         <is>
-          <t>2.9×</t>
+          <t>2.8×</t>
         </is>
       </c>
     </row>
@@ -7816,29 +7816,29 @@
       <c r="A17" s="9" t="n">
         <v>13</v>
       </c>
-      <c r="B17" s="10" t="inlineStr">
+      <c r="B17" s="15" t="inlineStr">
         <is>
           <t>REAL</t>
         </is>
       </c>
       <c r="C17" s="11" t="inlineStr">
         <is>
-          <t>TSE:6305</t>
+          <t>DFM:DSI</t>
         </is>
       </c>
       <c r="D17" s="11" t="inlineStr">
         <is>
-          <t>Hitachi Construction Machinery</t>
+          <t>Drake &amp; Scull</t>
         </is>
       </c>
       <c r="E17" s="11" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>MEA / Frontier</t>
         </is>
       </c>
       <c r="F17" s="11" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="G17" s="11" t="inlineStr">
@@ -7848,27 +7848,27 @@
       </c>
       <c r="H17" s="11" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>A2</t>
         </is>
       </c>
       <c r="I17" s="11" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>45%</t>
         </is>
       </c>
       <c r="J17" s="11" t="inlineStr">
         <is>
-          <t>1.70×</t>
+          <t>2.30×</t>
         </is>
       </c>
       <c r="K17" s="11" t="inlineStr">
         <is>
-          <t>2.80×</t>
+          <t>4.20×</t>
         </is>
       </c>
       <c r="L17" s="11" t="inlineStr">
         <is>
-          <t>1.69×</t>
+          <t>2.25×</t>
         </is>
       </c>
       <c r="M17" s="11" t="inlineStr">
@@ -7888,22 +7888,22 @@
       </c>
       <c r="C18" s="14" t="inlineStr">
         <is>
-          <t>DFM:DSI</t>
+          <t>BME:OHLA</t>
         </is>
       </c>
       <c r="D18" s="14" t="inlineStr">
         <is>
-          <t>Drake &amp; Scull</t>
+          <t>OHLA (former OHL)</t>
         </is>
       </c>
       <c r="E18" s="14" t="inlineStr">
         <is>
-          <t>MEA / Frontier</t>
+          <t>Continental Europe</t>
         </is>
       </c>
       <c r="F18" s="14" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="G18" s="14" t="inlineStr">
@@ -7913,32 +7913,32 @@
       </c>
       <c r="H18" s="14" t="inlineStr">
         <is>
-          <t>A2</t>
+          <t>A1</t>
         </is>
       </c>
       <c r="I18" s="14" t="inlineStr">
         <is>
-          <t>45%</t>
+          <t>50%</t>
         </is>
       </c>
       <c r="J18" s="14" t="inlineStr">
         <is>
-          <t>2.30×</t>
+          <t>2.40×</t>
         </is>
       </c>
       <c r="K18" s="14" t="inlineStr">
         <is>
-          <t>4.20×</t>
+          <t>4.50×</t>
         </is>
       </c>
       <c r="L18" s="14" t="inlineStr">
         <is>
-          <t>2.25×</t>
+          <t>2.35×</t>
         </is>
       </c>
       <c r="M18" s="14" t="inlineStr">
         <is>
-          <t>2.8×</t>
+          <t>2.7×</t>
         </is>
       </c>
     </row>
@@ -7946,29 +7946,29 @@
       <c r="A19" s="9" t="n">
         <v>15</v>
       </c>
-      <c r="B19" s="10" t="inlineStr">
+      <c r="B19" s="15" t="inlineStr">
         <is>
           <t>REAL</t>
         </is>
       </c>
       <c r="C19" s="11" t="inlineStr">
         <is>
-          <t>BME:OHLA</t>
+          <t>KRX:241560</t>
         </is>
       </c>
       <c r="D19" s="11" t="inlineStr">
         <is>
-          <t>OHLA (former OHL)</t>
+          <t>Doosan Bobcat → Doosan Robotics merger</t>
         </is>
       </c>
       <c r="E19" s="11" t="inlineStr">
         <is>
-          <t>Continental Europe</t>
+          <t>Korea</t>
         </is>
       </c>
       <c r="F19" s="11" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="G19" s="11" t="inlineStr">
@@ -7978,27 +7978,27 @@
       </c>
       <c r="H19" s="11" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>H</t>
         </is>
       </c>
       <c r="I19" s="11" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>25%</t>
         </is>
       </c>
       <c r="J19" s="11" t="inlineStr">
         <is>
-          <t>2.40×</t>
+          <t>1.70×</t>
         </is>
       </c>
       <c r="K19" s="11" t="inlineStr">
         <is>
-          <t>4.50×</t>
+          <t>2.50×</t>
         </is>
       </c>
       <c r="L19" s="11" t="inlineStr">
         <is>
-          <t>2.35×</t>
+          <t>1.66×</t>
         </is>
       </c>
       <c r="M19" s="11" t="inlineStr">
@@ -8076,7 +8076,7 @@
       <c r="A21" s="9" t="n">
         <v>17</v>
       </c>
-      <c r="B21" s="10" t="inlineStr">
+      <c r="B21" s="15" t="inlineStr">
         <is>
           <t>REAL</t>
         </is>
@@ -8148,22 +8148,22 @@
       </c>
       <c r="C22" s="14" t="inlineStr">
         <is>
-          <t>KRX:241560</t>
+          <t>NYSE:YPF</t>
         </is>
       </c>
       <c r="D22" s="14" t="inlineStr">
         <is>
-          <t>Doosan Bobcat → Doosan Robotics merger</t>
+          <t>YPF</t>
         </is>
       </c>
       <c r="E22" s="14" t="inlineStr">
         <is>
-          <t>Korea</t>
+          <t>Latin America</t>
         </is>
       </c>
       <c r="F22" s="14" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="G22" s="14" t="inlineStr">
@@ -8173,32 +8173,32 @@
       </c>
       <c r="H22" s="14" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>A1</t>
         </is>
       </c>
       <c r="I22" s="14" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>35%</t>
         </is>
       </c>
       <c r="J22" s="14" t="inlineStr">
         <is>
-          <t>1.70×</t>
+          <t>1.80×</t>
         </is>
       </c>
       <c r="K22" s="14" t="inlineStr">
         <is>
-          <t>2.50×</t>
+          <t>3.20×</t>
         </is>
       </c>
       <c r="L22" s="14" t="inlineStr">
         <is>
-          <t>1.66×</t>
+          <t>1.92×</t>
         </is>
       </c>
       <c r="M22" s="14" t="inlineStr">
         <is>
-          <t>2.7×</t>
+          <t>2.6×</t>
         </is>
       </c>
     </row>
@@ -8206,7 +8206,7 @@
       <c r="A23" s="9" t="n">
         <v>19</v>
       </c>
-      <c r="B23" s="10" t="inlineStr">
+      <c r="B23" s="15" t="inlineStr">
         <is>
           <t>REAL</t>
         </is>
@@ -8278,22 +8278,22 @@
       </c>
       <c r="C24" s="14" t="inlineStr">
         <is>
-          <t>BME:TLGO</t>
+          <t>TBRG</t>
         </is>
       </c>
       <c r="D24" s="14" t="inlineStr">
         <is>
-          <t>Talgo</t>
+          <t>TruBridge, Inc.</t>
         </is>
       </c>
       <c r="E24" s="14" t="inlineStr">
         <is>
-          <t>Continental Europe</t>
+          <t>United States/Canada</t>
         </is>
       </c>
       <c r="F24" s="14" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="G24" s="14" t="inlineStr">
@@ -8303,27 +8303,27 @@
       </c>
       <c r="H24" s="14" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>K3</t>
         </is>
       </c>
       <c r="I24" s="14" t="inlineStr">
         <is>
-          <t>32%</t>
+          <t>36%</t>
         </is>
       </c>
       <c r="J24" s="14" t="inlineStr">
         <is>
-          <t>2.16×</t>
+          <t>2.29×</t>
         </is>
       </c>
       <c r="K24" s="14" t="inlineStr">
         <is>
-          <t>2.64×</t>
+          <t>2.94×</t>
         </is>
       </c>
       <c r="L24" s="14" t="inlineStr">
         <is>
-          <t>1.84×</t>
+          <t>1.96×</t>
         </is>
       </c>
       <c r="M24" s="14" t="inlineStr">
@@ -8338,27 +8338,27 @@
       </c>
       <c r="B25" s="10" t="inlineStr">
         <is>
-          <t>REAL</t>
+          <t>PROXY</t>
         </is>
       </c>
       <c r="C25" s="11" t="inlineStr">
         <is>
-          <t>NYSE:YPF</t>
+          <t>LEG</t>
         </is>
       </c>
       <c r="D25" s="11" t="inlineStr">
         <is>
-          <t>YPF</t>
+          <t>LEGGETT &amp; PLATT INC</t>
         </is>
       </c>
       <c r="E25" s="11" t="inlineStr">
         <is>
-          <t>Latin America</t>
+          <t>United States/Canada</t>
         </is>
       </c>
       <c r="F25" s="11" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="G25" s="11" t="inlineStr">
@@ -8368,27 +8368,27 @@
       </c>
       <c r="H25" s="11" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>C</t>
         </is>
       </c>
       <c r="I25" s="11" t="inlineStr">
         <is>
-          <t>35%</t>
+          <t>34%</t>
         </is>
       </c>
       <c r="J25" s="11" t="inlineStr">
         <is>
-          <t>1.80×</t>
+          <t>2.21×</t>
         </is>
       </c>
       <c r="K25" s="11" t="inlineStr">
         <is>
-          <t>3.20×</t>
+          <t>2.76×</t>
         </is>
       </c>
       <c r="L25" s="11" t="inlineStr">
         <is>
-          <t>1.92×</t>
+          <t>1.88×</t>
         </is>
       </c>
       <c r="M25" s="11" t="inlineStr">
@@ -8408,22 +8408,22 @@
       </c>
       <c r="C26" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>BME:TLGO</t>
         </is>
       </c>
       <c r="D26" s="14" t="inlineStr">
         <is>
-          <t>IRANI PAPEL E EMBALAGEM S.A.</t>
+          <t>Talgo</t>
         </is>
       </c>
       <c r="E26" s="14" t="inlineStr">
         <is>
-          <t>Latin America</t>
+          <t>Continental Europe</t>
         </is>
       </c>
       <c r="F26" s="14" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="G26" s="14" t="inlineStr">
@@ -8443,17 +8443,17 @@
       </c>
       <c r="J26" s="14" t="inlineStr">
         <is>
-          <t>2.15×</t>
+          <t>2.16×</t>
         </is>
       </c>
       <c r="K26" s="14" t="inlineStr">
         <is>
-          <t>2.62×</t>
+          <t>2.64×</t>
         </is>
       </c>
       <c r="L26" s="14" t="inlineStr">
         <is>
-          <t>1.83×</t>
+          <t>1.84×</t>
         </is>
       </c>
       <c r="M26" s="14" t="inlineStr">
@@ -8466,29 +8466,29 @@
       <c r="A27" s="9" t="n">
         <v>23</v>
       </c>
-      <c r="B27" s="15" t="inlineStr">
+      <c r="B27" s="10" t="inlineStr">
         <is>
           <t>PROXY</t>
         </is>
       </c>
       <c r="C27" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>LSE:ASC</t>
         </is>
       </c>
       <c r="D27" s="11" t="inlineStr">
         <is>
-          <t>COMERC ENERGIA S.A.</t>
+          <t>ASOS</t>
         </is>
       </c>
       <c r="E27" s="11" t="inlineStr">
         <is>
-          <t>Latin America</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="F27" s="11" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="G27" s="11" t="inlineStr">
@@ -8508,17 +8508,17 @@
       </c>
       <c r="J27" s="11" t="inlineStr">
         <is>
-          <t>2.15×</t>
+          <t>2.16×</t>
         </is>
       </c>
       <c r="K27" s="11" t="inlineStr">
         <is>
-          <t>2.62×</t>
+          <t>2.64×</t>
         </is>
       </c>
       <c r="L27" s="11" t="inlineStr">
         <is>
-          <t>1.83×</t>
+          <t>1.84×</t>
         </is>
       </c>
       <c r="M27" s="11" t="inlineStr">
@@ -8543,7 +8543,7 @@
       </c>
       <c r="D28" s="14" t="inlineStr">
         <is>
-          <t>SOCIEDADE ABASTECIMENTO DE AGUA E SANEAMENTO SA</t>
+          <t>IRANI PAPEL E EMBALAGEM S.A.</t>
         </is>
       </c>
       <c r="E28" s="14" t="inlineStr">
@@ -8596,7 +8596,7 @@
       <c r="A29" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="B29" s="15" t="inlineStr">
+      <c r="B29" s="10" t="inlineStr">
         <is>
           <t>PROXY</t>
         </is>
@@ -8608,7 +8608,7 @@
       </c>
       <c r="D29" s="11" t="inlineStr">
         <is>
-          <t>MINERVA S/A</t>
+          <t>COMERC ENERGIA S.A.</t>
         </is>
       </c>
       <c r="E29" s="11" t="inlineStr">
@@ -8673,7 +8673,7 @@
       </c>
       <c r="D30" s="14" t="inlineStr">
         <is>
-          <t>BRADESCO LEASING S.A. - ARRENDAMENTO MERCANTIL</t>
+          <t>SOCIEDADE ABASTECIMENTO DE AGUA E SANEAMENTO SA</t>
         </is>
       </c>
       <c r="E30" s="14" t="inlineStr">
@@ -8726,29 +8726,29 @@
       <c r="A31" s="9" t="n">
         <v>27</v>
       </c>
-      <c r="B31" s="15" t="inlineStr">
+      <c r="B31" s="10" t="inlineStr">
         <is>
           <t>PROXY</t>
         </is>
       </c>
       <c r="C31" s="11" t="inlineStr">
         <is>
-          <t>LSE:ASC</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D31" s="11" t="inlineStr">
         <is>
-          <t>ASOS</t>
+          <t>MINERVA S/A</t>
         </is>
       </c>
       <c r="E31" s="11" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Latin America</t>
         </is>
       </c>
       <c r="F31" s="11" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="G31" s="11" t="inlineStr">
@@ -8768,17 +8768,17 @@
       </c>
       <c r="J31" s="11" t="inlineStr">
         <is>
-          <t>2.16×</t>
+          <t>2.15×</t>
         </is>
       </c>
       <c r="K31" s="11" t="inlineStr">
         <is>
-          <t>2.64×</t>
+          <t>2.62×</t>
         </is>
       </c>
       <c r="L31" s="11" t="inlineStr">
         <is>
-          <t>1.84×</t>
+          <t>1.83×</t>
         </is>
       </c>
       <c r="M31" s="11" t="inlineStr">
@@ -8798,22 +8798,22 @@
       </c>
       <c r="C32" s="14" t="inlineStr">
         <is>
-          <t>TBRG</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D32" s="14" t="inlineStr">
         <is>
-          <t>TruBridge, Inc.</t>
+          <t>BRADESCO LEASING S.A. - ARRENDAMENTO MERCANTIL</t>
         </is>
       </c>
       <c r="E32" s="14" t="inlineStr">
         <is>
-          <t>United States/Canada</t>
+          <t>Latin America</t>
         </is>
       </c>
       <c r="F32" s="14" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="G32" s="14" t="inlineStr">
@@ -8823,27 +8823,27 @@
       </c>
       <c r="H32" s="14" t="inlineStr">
         <is>
-          <t>K3</t>
+          <t>A1</t>
         </is>
       </c>
       <c r="I32" s="14" t="inlineStr">
         <is>
-          <t>36%</t>
+          <t>32%</t>
         </is>
       </c>
       <c r="J32" s="14" t="inlineStr">
         <is>
-          <t>2.29×</t>
+          <t>2.15×</t>
         </is>
       </c>
       <c r="K32" s="14" t="inlineStr">
         <is>
-          <t>2.94×</t>
+          <t>2.62×</t>
         </is>
       </c>
       <c r="L32" s="14" t="inlineStr">
         <is>
-          <t>1.96×</t>
+          <t>1.83×</t>
         </is>
       </c>
       <c r="M32" s="14" t="inlineStr">
@@ -8858,27 +8858,27 @@
       </c>
       <c r="B33" s="15" t="inlineStr">
         <is>
-          <t>PROXY</t>
+          <t>REAL</t>
         </is>
       </c>
       <c r="C33" s="11" t="inlineStr">
         <is>
-          <t>LEG</t>
+          <t>LSE:DRX</t>
         </is>
       </c>
       <c r="D33" s="11" t="inlineStr">
         <is>
-          <t>LEGGETT &amp; PLATT INC</t>
+          <t>Drax Group</t>
         </is>
       </c>
       <c r="E33" s="11" t="inlineStr">
         <is>
-          <t>United States/Canada</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="F33" s="11" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="G33" s="11" t="inlineStr">
@@ -8888,27 +8888,27 @@
       </c>
       <c r="H33" s="11" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A1+G</t>
         </is>
       </c>
       <c r="I33" s="11" t="inlineStr">
         <is>
-          <t>34%</t>
+          <t>55%</t>
         </is>
       </c>
       <c r="J33" s="11" t="inlineStr">
         <is>
-          <t>2.21×</t>
+          <t>2.20×</t>
         </is>
       </c>
       <c r="K33" s="11" t="inlineStr">
         <is>
-          <t>2.76×</t>
+          <t>4.50×</t>
         </is>
       </c>
       <c r="L33" s="11" t="inlineStr">
         <is>
-          <t>1.88×</t>
+          <t>2.45×</t>
         </is>
       </c>
       <c r="M33" s="11" t="inlineStr">
@@ -8928,17 +8928,17 @@
       </c>
       <c r="C34" s="14" t="inlineStr">
         <is>
-          <t>LSE:DRX</t>
+          <t>NASDAQ:UREE</t>
         </is>
       </c>
       <c r="D34" s="14" t="inlineStr">
         <is>
-          <t>Drax Group</t>
+          <t>USA Rare Earth</t>
         </is>
       </c>
       <c r="E34" s="14" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>United States/Canada</t>
         </is>
       </c>
       <c r="F34" s="14" t="inlineStr">
@@ -8953,27 +8953,27 @@
       </c>
       <c r="H34" s="14" t="inlineStr">
         <is>
-          <t>A1+G</t>
+          <t>A2</t>
         </is>
       </c>
       <c r="I34" s="14" t="inlineStr">
         <is>
-          <t>55%</t>
+          <t>65%</t>
         </is>
       </c>
       <c r="J34" s="14" t="inlineStr">
         <is>
-          <t>2.20×</t>
+          <t>2.50×</t>
         </is>
       </c>
       <c r="K34" s="14" t="inlineStr">
         <is>
-          <t>4.50×</t>
+          <t>5.50×</t>
         </is>
       </c>
       <c r="L34" s="14" t="inlineStr">
         <is>
-          <t>2.45×</t>
+          <t>2.71×</t>
         </is>
       </c>
       <c r="M34" s="14" t="inlineStr">
@@ -8988,17 +8988,17 @@
       </c>
       <c r="B35" s="10" t="inlineStr">
         <is>
-          <t>REAL</t>
+          <t>PROXY</t>
         </is>
       </c>
       <c r="C35" s="11" t="inlineStr">
         <is>
-          <t>NASDAQ:UREE</t>
+          <t>TSX:CFW</t>
         </is>
       </c>
       <c r="D35" s="11" t="inlineStr">
         <is>
-          <t>USA Rare Earth</t>
+          <t>Calfrac Well Services</t>
         </is>
       </c>
       <c r="E35" s="11" t="inlineStr">
@@ -9008,7 +9008,7 @@
       </c>
       <c r="F35" s="11" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="G35" s="11" t="inlineStr">
@@ -9018,32 +9018,32 @@
       </c>
       <c r="H35" s="11" t="inlineStr">
         <is>
-          <t>A2</t>
+          <t>A1</t>
         </is>
       </c>
       <c r="I35" s="11" t="inlineStr">
         <is>
-          <t>65%</t>
+          <t>32%</t>
         </is>
       </c>
       <c r="J35" s="11" t="inlineStr">
         <is>
-          <t>2.50×</t>
+          <t>2.14×</t>
         </is>
       </c>
       <c r="K35" s="11" t="inlineStr">
         <is>
-          <t>5.50×</t>
+          <t>2.59×</t>
         </is>
       </c>
       <c r="L35" s="11" t="inlineStr">
         <is>
-          <t>2.71×</t>
+          <t>1.81×</t>
         </is>
       </c>
       <c r="M35" s="11" t="inlineStr">
         <is>
-          <t>2.6×</t>
+          <t>2.5×</t>
         </is>
       </c>
     </row>
@@ -9058,12 +9058,12 @@
       </c>
       <c r="C36" s="14" t="inlineStr">
         <is>
-          <t>TSX:CFW</t>
+          <t>APTOF</t>
         </is>
       </c>
       <c r="D36" s="14" t="inlineStr">
         <is>
-          <t>Calfrac Well Services</t>
+          <t>Aptose Biosciences Inc.</t>
         </is>
       </c>
       <c r="E36" s="14" t="inlineStr">
@@ -9073,7 +9073,7 @@
       </c>
       <c r="F36" s="14" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="G36" s="14" t="inlineStr">
@@ -9083,32 +9083,32 @@
       </c>
       <c r="H36" s="14" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>K3</t>
         </is>
       </c>
       <c r="I36" s="14" t="inlineStr">
         <is>
-          <t>32%</t>
+          <t>38%</t>
         </is>
       </c>
       <c r="J36" s="14" t="inlineStr">
         <is>
-          <t>2.14×</t>
+          <t>2.24×</t>
         </is>
       </c>
       <c r="K36" s="14" t="inlineStr">
         <is>
-          <t>2.59×</t>
+          <t>2.87×</t>
         </is>
       </c>
       <c r="L36" s="14" t="inlineStr">
         <is>
-          <t>1.81×</t>
+          <t>1.91×</t>
         </is>
       </c>
       <c r="M36" s="14" t="inlineStr">
         <is>
-          <t>2.5×</t>
+          <t>2.4×</t>
         </is>
       </c>
     </row>
@@ -9116,7 +9116,7 @@
       <c r="A37" s="9" t="n">
         <v>33</v>
       </c>
-      <c r="B37" s="15" t="inlineStr">
+      <c r="B37" s="10" t="inlineStr">
         <is>
           <t>PROXY</t>
         </is>
@@ -9246,29 +9246,29 @@
       <c r="A39" s="9" t="n">
         <v>35</v>
       </c>
-      <c r="B39" s="15" t="inlineStr">
+      <c r="B39" s="10" t="inlineStr">
         <is>
           <t>PROXY</t>
         </is>
       </c>
       <c r="C39" s="11" t="inlineStr">
         <is>
-          <t>APTOF</t>
+          <t>HK:2202</t>
         </is>
       </c>
       <c r="D39" s="11" t="inlineStr">
         <is>
-          <t>Aptose Biosciences Inc.</t>
+          <t>Vanke</t>
         </is>
       </c>
       <c r="E39" s="11" t="inlineStr">
         <is>
-          <t>United States/Canada</t>
+          <t>Greater China / HK</t>
         </is>
       </c>
       <c r="F39" s="11" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="G39" s="11" t="inlineStr">
@@ -9278,32 +9278,32 @@
       </c>
       <c r="H39" s="11" t="inlineStr">
         <is>
-          <t>K3</t>
+          <t>A1</t>
         </is>
       </c>
       <c r="I39" s="11" t="inlineStr">
         <is>
-          <t>38%</t>
+          <t>33%</t>
         </is>
       </c>
       <c r="J39" s="11" t="inlineStr">
         <is>
-          <t>2.24×</t>
+          <t>2.10×</t>
         </is>
       </c>
       <c r="K39" s="11" t="inlineStr">
         <is>
-          <t>2.87×</t>
+          <t>2.54×</t>
         </is>
       </c>
       <c r="L39" s="11" t="inlineStr">
         <is>
-          <t>1.91×</t>
+          <t>1.78×</t>
         </is>
       </c>
       <c r="M39" s="11" t="inlineStr">
         <is>
-          <t>2.4×</t>
+          <t>2.3×</t>
         </is>
       </c>
     </row>
@@ -9318,22 +9318,22 @@
       </c>
       <c r="C40" s="14" t="inlineStr">
         <is>
-          <t>HK:2202</t>
+          <t>LSE:VOD</t>
         </is>
       </c>
       <c r="D40" s="14" t="inlineStr">
         <is>
-          <t>Vanke</t>
+          <t>Vodafone</t>
         </is>
       </c>
       <c r="E40" s="14" t="inlineStr">
         <is>
-          <t>Greater China / HK</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="F40" s="14" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="G40" s="14" t="inlineStr">
@@ -9348,22 +9348,22 @@
       </c>
       <c r="I40" s="14" t="inlineStr">
         <is>
-          <t>33%</t>
+          <t>34%</t>
         </is>
       </c>
       <c r="J40" s="14" t="inlineStr">
         <is>
-          <t>2.10×</t>
+          <t>2.08×</t>
         </is>
       </c>
       <c r="K40" s="14" t="inlineStr">
         <is>
-          <t>2.54×</t>
+          <t>2.50×</t>
         </is>
       </c>
       <c r="L40" s="14" t="inlineStr">
         <is>
-          <t>1.78×</t>
+          <t>1.76×</t>
         </is>
       </c>
       <c r="M40" s="14" t="inlineStr">
@@ -9376,24 +9376,24 @@
       <c r="A41" s="9" t="n">
         <v>37</v>
       </c>
-      <c r="B41" s="15" t="inlineStr">
+      <c r="B41" s="10" t="inlineStr">
         <is>
           <t>PROXY</t>
         </is>
       </c>
       <c r="C41" s="11" t="inlineStr">
         <is>
-          <t>LSE:VOD</t>
+          <t>NYSE:FFWM</t>
         </is>
       </c>
       <c r="D41" s="11" t="inlineStr">
         <is>
-          <t>Vodafone</t>
+          <t>First Foundation</t>
         </is>
       </c>
       <c r="E41" s="11" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>United States/Canada</t>
         </is>
       </c>
       <c r="F41" s="11" t="inlineStr">
@@ -9508,17 +9508,17 @@
       </c>
       <c r="B43" s="15" t="inlineStr">
         <is>
-          <t>PROXY</t>
+          <t>REAL</t>
         </is>
       </c>
       <c r="C43" s="11" t="inlineStr">
         <is>
-          <t>NYSE:FFWM</t>
+          <t>NYSE:HE</t>
         </is>
       </c>
       <c r="D43" s="11" t="inlineStr">
         <is>
-          <t>First Foundation</t>
+          <t>Hawaiian Electric Industries</t>
         </is>
       </c>
       <c r="E43" s="11" t="inlineStr">
@@ -9528,7 +9528,7 @@
       </c>
       <c r="F43" s="11" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="G43" s="11" t="inlineStr">
@@ -9538,27 +9538,27 @@
       </c>
       <c r="H43" s="11" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A1+G</t>
         </is>
       </c>
       <c r="I43" s="11" t="inlineStr">
         <is>
-          <t>34%</t>
+          <t>40%</t>
         </is>
       </c>
       <c r="J43" s="11" t="inlineStr">
         <is>
-          <t>2.08×</t>
+          <t>1.80×</t>
         </is>
       </c>
       <c r="K43" s="11" t="inlineStr">
         <is>
-          <t>2.50×</t>
+          <t>3.00×</t>
         </is>
       </c>
       <c r="L43" s="11" t="inlineStr">
         <is>
-          <t>1.76×</t>
+          <t>1.92×</t>
         </is>
       </c>
       <c r="M43" s="11" t="inlineStr">
@@ -9571,29 +9571,29 @@
       <c r="A44" s="12" t="n">
         <v>40</v>
       </c>
-      <c r="B44" s="16" t="inlineStr">
-        <is>
-          <t>REAL</t>
+      <c r="B44" s="13" t="inlineStr">
+        <is>
+          <t>PROXY</t>
         </is>
       </c>
       <c r="C44" s="14" t="inlineStr">
         <is>
-          <t>NYSE:HE</t>
+          <t>TSE:8304</t>
         </is>
       </c>
       <c r="D44" s="14" t="inlineStr">
         <is>
-          <t>Hawaiian Electric Industries</t>
+          <t>Aozora Bank</t>
         </is>
       </c>
       <c r="E44" s="14" t="inlineStr">
         <is>
-          <t>United States/Canada</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="F44" s="14" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="G44" s="14" t="inlineStr">
@@ -9603,32 +9603,32 @@
       </c>
       <c r="H44" s="14" t="inlineStr">
         <is>
-          <t>A1+G</t>
+          <t>H</t>
         </is>
       </c>
       <c r="I44" s="14" t="inlineStr">
         <is>
-          <t>40%</t>
+          <t>42%</t>
         </is>
       </c>
       <c r="J44" s="14" t="inlineStr">
         <is>
-          <t>1.80×</t>
+          <t>2.23×</t>
         </is>
       </c>
       <c r="K44" s="14" t="inlineStr">
         <is>
-          <t>3.00×</t>
+          <t>2.89×</t>
         </is>
       </c>
       <c r="L44" s="14" t="inlineStr">
         <is>
-          <t>1.92×</t>
+          <t>1.90×</t>
         </is>
       </c>
       <c r="M44" s="14" t="inlineStr">
         <is>
-          <t>2.3×</t>
+          <t>2.1×</t>
         </is>
       </c>
     </row>
@@ -9638,27 +9638,27 @@
       </c>
       <c r="B45" s="15" t="inlineStr">
         <is>
-          <t>PROXY</t>
+          <t>REAL</t>
         </is>
       </c>
       <c r="C45" s="11" t="inlineStr">
         <is>
-          <t>TSE:8304</t>
+          <t>NYSE/TSX:TMQ</t>
         </is>
       </c>
       <c r="D45" s="11" t="inlineStr">
         <is>
-          <t>Aozora Bank</t>
+          <t>Trilogy Metals</t>
         </is>
       </c>
       <c r="E45" s="11" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States/Canada</t>
         </is>
       </c>
       <c r="F45" s="11" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="G45" s="11" t="inlineStr">
@@ -9668,27 +9668,27 @@
       </c>
       <c r="H45" s="11" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>A2</t>
         </is>
       </c>
       <c r="I45" s="11" t="inlineStr">
         <is>
-          <t>42%</t>
+          <t>55%</t>
         </is>
       </c>
       <c r="J45" s="11" t="inlineStr">
         <is>
-          <t>2.23×</t>
+          <t>2.20×</t>
         </is>
       </c>
       <c r="K45" s="11" t="inlineStr">
         <is>
-          <t>2.89×</t>
+          <t>4.50×</t>
         </is>
       </c>
       <c r="L45" s="11" t="inlineStr">
         <is>
-          <t>1.90×</t>
+          <t>2.14×</t>
         </is>
       </c>
       <c r="M45" s="11" t="inlineStr">
@@ -9701,29 +9701,29 @@
       <c r="A46" s="12" t="n">
         <v>42</v>
       </c>
-      <c r="B46" s="16" t="inlineStr">
-        <is>
-          <t>REAL</t>
+      <c r="B46" s="13" t="inlineStr">
+        <is>
+          <t>PROXY</t>
         </is>
       </c>
       <c r="C46" s="14" t="inlineStr">
         <is>
-          <t>NYSE/TSX:TMQ</t>
+          <t>LSE:PDL</t>
         </is>
       </c>
       <c r="D46" s="14" t="inlineStr">
         <is>
-          <t>Trilogy Metals</t>
+          <t>Petra Diamonds</t>
         </is>
       </c>
       <c r="E46" s="14" t="inlineStr">
         <is>
-          <t>United States/Canada</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="F46" s="14" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>0.60</t>
         </is>
       </c>
       <c r="G46" s="14" t="inlineStr">
@@ -9733,32 +9733,32 @@
       </c>
       <c r="H46" s="14" t="inlineStr">
         <is>
-          <t>A2</t>
+          <t>A1</t>
         </is>
       </c>
       <c r="I46" s="14" t="inlineStr">
         <is>
-          <t>55%</t>
+          <t>35%</t>
         </is>
       </c>
       <c r="J46" s="14" t="inlineStr">
         <is>
-          <t>2.20×</t>
+          <t>2.02×</t>
         </is>
       </c>
       <c r="K46" s="14" t="inlineStr">
         <is>
-          <t>4.50×</t>
+          <t>2.40×</t>
         </is>
       </c>
       <c r="L46" s="14" t="inlineStr">
         <is>
-          <t>2.14×</t>
+          <t>1.70×</t>
         </is>
       </c>
       <c r="M46" s="14" t="inlineStr">
         <is>
-          <t>2.1×</t>
+          <t>2.0×</t>
         </is>
       </c>
     </row>
@@ -9766,7 +9766,7 @@
       <c r="A47" s="9" t="n">
         <v>43</v>
       </c>
-      <c r="B47" s="15" t="inlineStr">
+      <c r="B47" s="10" t="inlineStr">
         <is>
           <t>PROXY</t>
         </is>
@@ -9831,29 +9831,29 @@
       <c r="A48" s="12" t="n">
         <v>44</v>
       </c>
-      <c r="B48" s="13" t="inlineStr">
-        <is>
-          <t>PROXY</t>
+      <c r="B48" s="16" t="inlineStr">
+        <is>
+          <t>REAL</t>
         </is>
       </c>
       <c r="C48" s="14" t="inlineStr">
         <is>
-          <t>LSE:PDL</t>
+          <t>NYSE:MP</t>
         </is>
       </c>
       <c r="D48" s="14" t="inlineStr">
         <is>
-          <t>Petra Diamonds</t>
+          <t>MP Materials Corp</t>
         </is>
       </c>
       <c r="E48" s="14" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>United States/Canada</t>
         </is>
       </c>
       <c r="F48" s="14" t="inlineStr">
         <is>
-          <t>0.60</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="G48" s="14" t="inlineStr">
@@ -9863,27 +9863,27 @@
       </c>
       <c r="H48" s="14" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2</t>
         </is>
       </c>
       <c r="I48" s="14" t="inlineStr">
         <is>
-          <t>35%</t>
+          <t>45%</t>
         </is>
       </c>
       <c r="J48" s="14" t="inlineStr">
         <is>
-          <t>2.02×</t>
+          <t>1.80×</t>
         </is>
       </c>
       <c r="K48" s="14" t="inlineStr">
         <is>
-          <t>2.40×</t>
+          <t>3.20×</t>
         </is>
       </c>
       <c r="L48" s="14" t="inlineStr">
         <is>
-          <t>1.70×</t>
+          <t>1.90×</t>
         </is>
       </c>
       <c r="M48" s="14" t="inlineStr">
@@ -9896,19 +9896,19 @@
       <c r="A49" s="9" t="n">
         <v>45</v>
       </c>
-      <c r="B49" s="10" t="inlineStr">
+      <c r="B49" s="15" t="inlineStr">
         <is>
           <t>REAL</t>
         </is>
       </c>
       <c r="C49" s="11" t="inlineStr">
         <is>
-          <t>NYSE:MP</t>
+          <t>NYSE:FLG</t>
         </is>
       </c>
       <c r="D49" s="11" t="inlineStr">
         <is>
-          <t>MP Materials Corp</t>
+          <t>NYCB / Flagstar Financial</t>
         </is>
       </c>
       <c r="E49" s="11" t="inlineStr">
@@ -9918,7 +9918,7 @@
       </c>
       <c r="F49" s="11" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="G49" s="11" t="inlineStr">
@@ -9928,7 +9928,7 @@
       </c>
       <c r="H49" s="11" t="inlineStr">
         <is>
-          <t>A2</t>
+          <t>A1</t>
         </is>
       </c>
       <c r="I49" s="11" t="inlineStr">
@@ -9938,7 +9938,7 @@
       </c>
       <c r="J49" s="11" t="inlineStr">
         <is>
-          <t>1.80×</t>
+          <t>1.85×</t>
         </is>
       </c>
       <c r="K49" s="11" t="inlineStr">
@@ -9948,12 +9948,12 @@
       </c>
       <c r="L49" s="11" t="inlineStr">
         <is>
-          <t>1.90×</t>
+          <t>1.86×</t>
         </is>
       </c>
       <c r="M49" s="11" t="inlineStr">
         <is>
-          <t>2.0×</t>
+          <t>1.9×</t>
         </is>
       </c>
     </row>
@@ -9968,22 +9968,22 @@
       </c>
       <c r="C50" s="14" t="inlineStr">
         <is>
-          <t>NYSE:AENZ</t>
+          <t>AEMD</t>
         </is>
       </c>
       <c r="D50" s="14" t="inlineStr">
         <is>
-          <t>Aenza (former Graña y Montero)</t>
+          <t>AETHLON MEDICAL INC</t>
         </is>
       </c>
       <c r="E50" s="14" t="inlineStr">
         <is>
-          <t>Continental Europe</t>
+          <t>United States/Canada</t>
         </is>
       </c>
       <c r="F50" s="14" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="G50" s="14" t="inlineStr">
@@ -9993,27 +9993,27 @@
       </c>
       <c r="H50" s="14" t="inlineStr">
         <is>
-          <t>A2</t>
+          <t>F2</t>
         </is>
       </c>
       <c r="I50" s="14" t="inlineStr">
         <is>
-          <t>36%</t>
+          <t>42%</t>
         </is>
       </c>
       <c r="J50" s="14" t="inlineStr">
         <is>
-          <t>2.00×</t>
+          <t>2.12×</t>
         </is>
       </c>
       <c r="K50" s="14" t="inlineStr">
         <is>
-          <t>2.35×</t>
+          <t>2.66×</t>
         </is>
       </c>
       <c r="L50" s="14" t="inlineStr">
         <is>
-          <t>1.68×</t>
+          <t>1.79×</t>
         </is>
       </c>
       <c r="M50" s="14" t="inlineStr">
@@ -10026,29 +10026,29 @@
       <c r="A51" s="9" t="n">
         <v>47</v>
       </c>
-      <c r="B51" s="15" t="inlineStr">
+      <c r="B51" s="10" t="inlineStr">
         <is>
           <t>PROXY</t>
         </is>
       </c>
       <c r="C51" s="11" t="inlineStr">
         <is>
-          <t>KRX:034730</t>
+          <t>NGX:ZENITHBANK</t>
         </is>
       </c>
       <c r="D51" s="11" t="inlineStr">
         <is>
-          <t>SK Inc</t>
+          <t>Zenith Bank</t>
         </is>
       </c>
       <c r="E51" s="11" t="inlineStr">
         <is>
-          <t>Korea</t>
+          <t>MEA / Frontier</t>
         </is>
       </c>
       <c r="F51" s="11" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="G51" s="11" t="inlineStr">
@@ -10058,27 +10058,27 @@
       </c>
       <c r="H51" s="11" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>G</t>
         </is>
       </c>
       <c r="I51" s="11" t="inlineStr">
         <is>
-          <t>44%</t>
+          <t>42%</t>
         </is>
       </c>
       <c r="J51" s="11" t="inlineStr">
         <is>
-          <t>2.17×</t>
+          <t>2.11×</t>
         </is>
       </c>
       <c r="K51" s="11" t="inlineStr">
         <is>
-          <t>2.79×</t>
+          <t>2.64×</t>
         </is>
       </c>
       <c r="L51" s="11" t="inlineStr">
         <is>
-          <t>1.84×</t>
+          <t>1.78×</t>
         </is>
       </c>
       <c r="M51" s="11" t="inlineStr">
@@ -10098,22 +10098,22 @@
       </c>
       <c r="C52" s="14" t="inlineStr">
         <is>
-          <t>NGX:ZENITHBANK</t>
+          <t>KRX:034730</t>
         </is>
       </c>
       <c r="D52" s="14" t="inlineStr">
         <is>
-          <t>Zenith Bank</t>
+          <t>SK Inc</t>
         </is>
       </c>
       <c r="E52" s="14" t="inlineStr">
         <is>
-          <t>MEA / Frontier</t>
+          <t>Korea</t>
         </is>
       </c>
       <c r="F52" s="14" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="G52" s="14" t="inlineStr">
@@ -10123,27 +10123,27 @@
       </c>
       <c r="H52" s="14" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>H</t>
         </is>
       </c>
       <c r="I52" s="14" t="inlineStr">
         <is>
-          <t>42%</t>
+          <t>44%</t>
         </is>
       </c>
       <c r="J52" s="14" t="inlineStr">
         <is>
-          <t>2.11×</t>
+          <t>2.17×</t>
         </is>
       </c>
       <c r="K52" s="14" t="inlineStr">
         <is>
-          <t>2.64×</t>
+          <t>2.79×</t>
         </is>
       </c>
       <c r="L52" s="14" t="inlineStr">
         <is>
-          <t>1.78×</t>
+          <t>1.84×</t>
         </is>
       </c>
       <c r="M52" s="14" t="inlineStr">
@@ -10158,27 +10158,27 @@
       </c>
       <c r="B53" s="10" t="inlineStr">
         <is>
-          <t>REAL</t>
+          <t>PROXY</t>
         </is>
       </c>
       <c r="C53" s="11" t="inlineStr">
         <is>
-          <t>NYSE:FLG</t>
+          <t>NYSE:AENZ</t>
         </is>
       </c>
       <c r="D53" s="11" t="inlineStr">
         <is>
-          <t>NYCB / Flagstar Financial</t>
+          <t>Aenza (former Graña y Montero)</t>
         </is>
       </c>
       <c r="E53" s="11" t="inlineStr">
         <is>
-          <t>United States/Canada</t>
+          <t>Continental Europe</t>
         </is>
       </c>
       <c r="F53" s="11" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="G53" s="11" t="inlineStr">
@@ -10188,27 +10188,27 @@
       </c>
       <c r="H53" s="11" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2</t>
         </is>
       </c>
       <c r="I53" s="11" t="inlineStr">
         <is>
-          <t>45%</t>
+          <t>36%</t>
         </is>
       </c>
       <c r="J53" s="11" t="inlineStr">
         <is>
-          <t>1.85×</t>
+          <t>2.00×</t>
         </is>
       </c>
       <c r="K53" s="11" t="inlineStr">
         <is>
-          <t>3.20×</t>
+          <t>2.35×</t>
         </is>
       </c>
       <c r="L53" s="11" t="inlineStr">
         <is>
-          <t>1.86×</t>
+          <t>1.68×</t>
         </is>
       </c>
       <c r="M53" s="11" t="inlineStr">
@@ -10228,22 +10228,22 @@
       </c>
       <c r="C54" s="14" t="inlineStr">
         <is>
-          <t>AEMD</t>
+          <t>EGX:COMI</t>
         </is>
       </c>
       <c r="D54" s="14" t="inlineStr">
         <is>
-          <t>AETHLON MEDICAL INC</t>
+          <t>Egypt Commercial International Bank</t>
         </is>
       </c>
       <c r="E54" s="14" t="inlineStr">
         <is>
-          <t>United States/Canada</t>
+          <t>MEA / Frontier</t>
         </is>
       </c>
       <c r="F54" s="14" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="G54" s="14" t="inlineStr">
@@ -10253,7 +10253,7 @@
       </c>
       <c r="H54" s="14" t="inlineStr">
         <is>
-          <t>F2</t>
+          <t>G</t>
         </is>
       </c>
       <c r="I54" s="14" t="inlineStr">
@@ -10263,22 +10263,22 @@
       </c>
       <c r="J54" s="14" t="inlineStr">
         <is>
-          <t>2.12×</t>
+          <t>2.10×</t>
         </is>
       </c>
       <c r="K54" s="14" t="inlineStr">
         <is>
-          <t>2.66×</t>
+          <t>2.62×</t>
         </is>
       </c>
       <c r="L54" s="14" t="inlineStr">
         <is>
-          <t>1.79×</t>
+          <t>1.77×</t>
         </is>
       </c>
       <c r="M54" s="14" t="inlineStr">
         <is>
-          <t>1.9×</t>
+          <t>1.8×</t>
         </is>
       </c>
     </row>
@@ -10286,19 +10286,19 @@
       <c r="A55" s="9" t="n">
         <v>51</v>
       </c>
-      <c r="B55" s="15" t="inlineStr">
+      <c r="B55" s="10" t="inlineStr">
         <is>
           <t>PROXY</t>
         </is>
       </c>
       <c r="C55" s="11" t="inlineStr">
         <is>
-          <t>EGX:COMI</t>
+          <t>NGX:FIDELITYBK</t>
         </is>
       </c>
       <c r="D55" s="11" t="inlineStr">
         <is>
-          <t>Egypt Commercial International Bank</t>
+          <t>Fidelity Bank</t>
         </is>
       </c>
       <c r="E55" s="11" t="inlineStr">
@@ -10308,7 +10308,7 @@
       </c>
       <c r="F55" s="11" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="G55" s="11" t="inlineStr">
@@ -10323,22 +10323,22 @@
       </c>
       <c r="I55" s="11" t="inlineStr">
         <is>
-          <t>42%</t>
+          <t>43%</t>
         </is>
       </c>
       <c r="J55" s="11" t="inlineStr">
         <is>
-          <t>2.10×</t>
+          <t>2.08×</t>
         </is>
       </c>
       <c r="K55" s="11" t="inlineStr">
         <is>
-          <t>2.62×</t>
+          <t>2.59×</t>
         </is>
       </c>
       <c r="L55" s="11" t="inlineStr">
         <is>
-          <t>1.77×</t>
+          <t>1.76×</t>
         </is>
       </c>
       <c r="M55" s="11" t="inlineStr">
@@ -10358,12 +10358,12 @@
       </c>
       <c r="C56" s="14" t="inlineStr">
         <is>
-          <t>NGX:FIDELITYBK</t>
+          <t>EGX:TMGH</t>
         </is>
       </c>
       <c r="D56" s="14" t="inlineStr">
         <is>
-          <t>Fidelity Bank</t>
+          <t>Talaat Moustafa Group</t>
         </is>
       </c>
       <c r="E56" s="14" t="inlineStr">
@@ -10373,7 +10373,7 @@
       </c>
       <c r="F56" s="14" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="G56" s="14" t="inlineStr">
@@ -10393,22 +10393,22 @@
       </c>
       <c r="J56" s="14" t="inlineStr">
         <is>
-          <t>2.08×</t>
+          <t>2.07×</t>
         </is>
       </c>
       <c r="K56" s="14" t="inlineStr">
         <is>
-          <t>2.59×</t>
+          <t>2.58×</t>
         </is>
       </c>
       <c r="L56" s="14" t="inlineStr">
         <is>
-          <t>1.76×</t>
+          <t>1.75×</t>
         </is>
       </c>
       <c r="M56" s="14" t="inlineStr">
         <is>
-          <t>1.8×</t>
+          <t>1.7×</t>
         </is>
       </c>
     </row>
@@ -10416,29 +10416,29 @@
       <c r="A57" s="9" t="n">
         <v>53</v>
       </c>
-      <c r="B57" s="15" t="inlineStr">
+      <c r="B57" s="10" t="inlineStr">
         <is>
           <t>PROXY</t>
         </is>
       </c>
       <c r="C57" s="11" t="inlineStr">
         <is>
-          <t>KRX:034220</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="D57" s="11" t="inlineStr">
         <is>
-          <t>LG Display</t>
+          <t>MEMPHASYS LIMITED.</t>
         </is>
       </c>
       <c r="E57" s="11" t="inlineStr">
         <is>
-          <t>Korea</t>
+          <t>SE Asia / Pacific</t>
         </is>
       </c>
       <c r="F57" s="11" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="G57" s="11" t="inlineStr">
@@ -10448,27 +10448,27 @@
       </c>
       <c r="H57" s="11" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>B</t>
         </is>
       </c>
       <c r="I57" s="11" t="inlineStr">
         <is>
-          <t>46%</t>
+          <t>44%</t>
         </is>
       </c>
       <c r="J57" s="11" t="inlineStr">
         <is>
-          <t>2.12×</t>
+          <t>2.06×</t>
         </is>
       </c>
       <c r="K57" s="11" t="inlineStr">
         <is>
-          <t>2.71×</t>
+          <t>2.56×</t>
         </is>
       </c>
       <c r="L57" s="11" t="inlineStr">
         <is>
-          <t>1.79×</t>
+          <t>1.74×</t>
         </is>
       </c>
       <c r="M57" s="11" t="inlineStr">
@@ -10488,22 +10488,22 @@
       </c>
       <c r="C58" s="14" t="inlineStr">
         <is>
-          <t>EGX:TMGH</t>
+          <t>CIK:0001348911</t>
         </is>
       </c>
       <c r="D58" s="14" t="inlineStr">
         <is>
-          <t>Talaat Moustafa Group</t>
+          <t>KalVista Pharmaceuticals, Inc.</t>
         </is>
       </c>
       <c r="E58" s="14" t="inlineStr">
         <is>
-          <t>MEA / Frontier</t>
+          <t>United States/Canada</t>
         </is>
       </c>
       <c r="F58" s="14" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="G58" s="14" t="inlineStr">
@@ -10513,27 +10513,27 @@
       </c>
       <c r="H58" s="14" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>K3</t>
         </is>
       </c>
       <c r="I58" s="14" t="inlineStr">
         <is>
-          <t>43%</t>
+          <t>44%</t>
         </is>
       </c>
       <c r="J58" s="14" t="inlineStr">
         <is>
-          <t>2.07×</t>
+          <t>2.06×</t>
         </is>
       </c>
       <c r="K58" s="14" t="inlineStr">
         <is>
-          <t>2.58×</t>
+          <t>2.56×</t>
         </is>
       </c>
       <c r="L58" s="14" t="inlineStr">
         <is>
-          <t>1.75×</t>
+          <t>1.74×</t>
         </is>
       </c>
       <c r="M58" s="14" t="inlineStr">
@@ -10546,24 +10546,24 @@
       <c r="A59" s="9" t="n">
         <v>55</v>
       </c>
-      <c r="B59" s="15" t="inlineStr">
+      <c r="B59" s="10" t="inlineStr">
         <is>
           <t>PROXY</t>
         </is>
       </c>
       <c r="C59" s="11" t="inlineStr">
         <is>
-          <t>NYSE:SBSW</t>
+          <t>CIK:0001909770</t>
         </is>
       </c>
       <c r="D59" s="11" t="inlineStr">
         <is>
-          <t>Sibanye-Stillwater</t>
+          <t>KHEOBA CORP.</t>
         </is>
       </c>
       <c r="E59" s="11" t="inlineStr">
         <is>
-          <t>MEA / Frontier</t>
+          <t>United States/Canada</t>
         </is>
       </c>
       <c r="F59" s="11" t="inlineStr">
@@ -10573,12 +10573,12 @@
       </c>
       <c r="G59" s="11" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H59" s="11" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>K3</t>
         </is>
       </c>
       <c r="I59" s="11" t="inlineStr">
@@ -10618,17 +10618,17 @@
       </c>
       <c r="C60" s="14" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>CIK:0001489096</t>
         </is>
       </c>
       <c r="D60" s="14" t="inlineStr">
         <is>
-          <t>MEMPHASYS LIMITED.</t>
+          <t>Thermon Group Holdings, Inc.</t>
         </is>
       </c>
       <c r="E60" s="14" t="inlineStr">
         <is>
-          <t>SE Asia / Pacific</t>
+          <t>United States/Canada</t>
         </is>
       </c>
       <c r="F60" s="14" t="inlineStr">
@@ -10643,7 +10643,7 @@
       </c>
       <c r="H60" s="14" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>K3</t>
         </is>
       </c>
       <c r="I60" s="14" t="inlineStr">
@@ -10676,19 +10676,19 @@
       <c r="A61" s="9" t="n">
         <v>57</v>
       </c>
-      <c r="B61" s="15" t="inlineStr">
+      <c r="B61" s="10" t="inlineStr">
         <is>
           <t>PROXY</t>
         </is>
       </c>
       <c r="C61" s="11" t="inlineStr">
         <is>
-          <t>CIK:0001348911</t>
+          <t>WYTC</t>
         </is>
       </c>
       <c r="D61" s="11" t="inlineStr">
         <is>
-          <t>KalVista Pharmaceuticals, Inc.</t>
+          <t>WYTEC INTERNATIONAL INC</t>
         </is>
       </c>
       <c r="E61" s="11" t="inlineStr">
@@ -10748,12 +10748,12 @@
       </c>
       <c r="C62" s="14" t="inlineStr">
         <is>
-          <t>CIK:0001909770</t>
+          <t>CIK:0001408100</t>
         </is>
       </c>
       <c r="D62" s="14" t="inlineStr">
         <is>
-          <t>KHEOBA CORP.</t>
+          <t>Kennedy-Wilson Holdings, Inc.</t>
         </is>
       </c>
       <c r="E62" s="14" t="inlineStr">
@@ -10806,19 +10806,19 @@
       <c r="A63" s="9" t="n">
         <v>59</v>
       </c>
-      <c r="B63" s="15" t="inlineStr">
+      <c r="B63" s="10" t="inlineStr">
         <is>
           <t>PROXY</t>
         </is>
       </c>
       <c r="C63" s="11" t="inlineStr">
         <is>
-          <t>CIK:0001489096</t>
+          <t>CIK:0002073537</t>
         </is>
       </c>
       <c r="D63" s="11" t="inlineStr">
         <is>
-          <t>Thermon Group Holdings, Inc.</t>
+          <t>PIMCO Asset-Based Lending Co LLC</t>
         </is>
       </c>
       <c r="E63" s="11" t="inlineStr">
@@ -10878,12 +10878,12 @@
       </c>
       <c r="C64" s="14" t="inlineStr">
         <is>
-          <t>WYTC</t>
+          <t>VIASP</t>
         </is>
       </c>
       <c r="D64" s="14" t="inlineStr">
         <is>
-          <t>WYTEC INTERNATIONAL INC</t>
+          <t>Via Renewables, Inc.</t>
         </is>
       </c>
       <c r="E64" s="14" t="inlineStr">
@@ -10936,19 +10936,19 @@
       <c r="A65" s="9" t="n">
         <v>61</v>
       </c>
-      <c r="B65" s="15" t="inlineStr">
+      <c r="B65" s="10" t="inlineStr">
         <is>
           <t>PROXY</t>
         </is>
       </c>
       <c r="C65" s="11" t="inlineStr">
         <is>
-          <t>CIK:0001408100</t>
+          <t>CIK:0001117171</t>
         </is>
       </c>
       <c r="D65" s="11" t="inlineStr">
         <is>
-          <t>Kennedy-Wilson Holdings, Inc.</t>
+          <t>CBAK Energy Technology, Inc.</t>
         </is>
       </c>
       <c r="E65" s="11" t="inlineStr">
@@ -11008,12 +11008,12 @@
       </c>
       <c r="C66" s="14" t="inlineStr">
         <is>
-          <t>CIK:0002073537</t>
+          <t>CIK:0001500305</t>
         </is>
       </c>
       <c r="D66" s="14" t="inlineStr">
         <is>
-          <t>PIMCO Asset-Based Lending Co LLC</t>
+          <t>Sustainable Projects Group Inc.</t>
         </is>
       </c>
       <c r="E66" s="14" t="inlineStr">
@@ -11066,19 +11066,19 @@
       <c r="A67" s="9" t="n">
         <v>63</v>
       </c>
-      <c r="B67" s="15" t="inlineStr">
+      <c r="B67" s="10" t="inlineStr">
         <is>
           <t>PROXY</t>
         </is>
       </c>
       <c r="C67" s="11" t="inlineStr">
         <is>
-          <t>VIASP</t>
+          <t>CIK:0001127703</t>
         </is>
       </c>
       <c r="D67" s="11" t="inlineStr">
         <is>
-          <t>Via Renewables, Inc.</t>
+          <t>PROASSURANCE CORP</t>
         </is>
       </c>
       <c r="E67" s="11" t="inlineStr">
@@ -11138,12 +11138,12 @@
       </c>
       <c r="C68" s="14" t="inlineStr">
         <is>
-          <t>CIK:0001117171</t>
+          <t>CIK:0001900520</t>
         </is>
       </c>
       <c r="D68" s="14" t="inlineStr">
         <is>
-          <t>CBAK Energy Technology, Inc.</t>
+          <t>Lomond Therapeutics Holdings, Inc.</t>
         </is>
       </c>
       <c r="E68" s="14" t="inlineStr">
@@ -11196,24 +11196,24 @@
       <c r="A69" s="9" t="n">
         <v>65</v>
       </c>
-      <c r="B69" s="15" t="inlineStr">
+      <c r="B69" s="10" t="inlineStr">
         <is>
           <t>PROXY</t>
         </is>
       </c>
       <c r="C69" s="11" t="inlineStr">
         <is>
-          <t>CIK:0001500305</t>
+          <t>NYSE:SBSW</t>
         </is>
       </c>
       <c r="D69" s="11" t="inlineStr">
         <is>
-          <t>Sustainable Projects Group Inc.</t>
+          <t>Sibanye-Stillwater</t>
         </is>
       </c>
       <c r="E69" s="11" t="inlineStr">
         <is>
-          <t>United States/Canada</t>
+          <t>MEA / Frontier</t>
         </is>
       </c>
       <c r="F69" s="11" t="inlineStr">
@@ -11223,12 +11223,12 @@
       </c>
       <c r="G69" s="11" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H69" s="11" t="inlineStr">
         <is>
-          <t>K3</t>
+          <t>G</t>
         </is>
       </c>
       <c r="I69" s="11" t="inlineStr">
@@ -11268,22 +11268,22 @@
       </c>
       <c r="C70" s="14" t="inlineStr">
         <is>
-          <t>CIK:0001127703</t>
+          <t>KRX:034220</t>
         </is>
       </c>
       <c r="D70" s="14" t="inlineStr">
         <is>
-          <t>PROASSURANCE CORP</t>
+          <t>LG Display</t>
         </is>
       </c>
       <c r="E70" s="14" t="inlineStr">
         <is>
-          <t>United States/Canada</t>
+          <t>Korea</t>
         </is>
       </c>
       <c r="F70" s="14" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="G70" s="14" t="inlineStr">
@@ -11293,27 +11293,27 @@
       </c>
       <c r="H70" s="14" t="inlineStr">
         <is>
-          <t>K3</t>
+          <t>H</t>
         </is>
       </c>
       <c r="I70" s="14" t="inlineStr">
         <is>
-          <t>44%</t>
+          <t>46%</t>
         </is>
       </c>
       <c r="J70" s="14" t="inlineStr">
         <is>
-          <t>2.06×</t>
+          <t>2.12×</t>
         </is>
       </c>
       <c r="K70" s="14" t="inlineStr">
         <is>
-          <t>2.56×</t>
+          <t>2.71×</t>
         </is>
       </c>
       <c r="L70" s="14" t="inlineStr">
         <is>
-          <t>1.74×</t>
+          <t>1.79×</t>
         </is>
       </c>
       <c r="M70" s="14" t="inlineStr">
@@ -11326,19 +11326,19 @@
       <c r="A71" s="9" t="n">
         <v>67</v>
       </c>
-      <c r="B71" s="15" t="inlineStr">
+      <c r="B71" s="10" t="inlineStr">
         <is>
           <t>PROXY</t>
         </is>
       </c>
       <c r="C71" s="11" t="inlineStr">
         <is>
-          <t>CIK:0001900520</t>
+          <t>EMI</t>
         </is>
       </c>
       <c r="D71" s="11" t="inlineStr">
         <is>
-          <t>Lomond Therapeutics Holdings, Inc.</t>
+          <t>Encore Medical, Inc.</t>
         </is>
       </c>
       <c r="E71" s="11" t="inlineStr">
@@ -11348,7 +11348,7 @@
       </c>
       <c r="F71" s="11" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="G71" s="11" t="inlineStr">
@@ -11358,7 +11358,7 @@
       </c>
       <c r="H71" s="11" t="inlineStr">
         <is>
-          <t>K3</t>
+          <t>F2</t>
         </is>
       </c>
       <c r="I71" s="11" t="inlineStr">
@@ -11368,22 +11368,22 @@
       </c>
       <c r="J71" s="11" t="inlineStr">
         <is>
-          <t>2.06×</t>
+          <t>2.05×</t>
         </is>
       </c>
       <c r="K71" s="11" t="inlineStr">
         <is>
-          <t>2.56×</t>
+          <t>2.54×</t>
         </is>
       </c>
       <c r="L71" s="11" t="inlineStr">
         <is>
-          <t>1.74×</t>
+          <t>1.72×</t>
         </is>
       </c>
       <c r="M71" s="11" t="inlineStr">
         <is>
-          <t>1.7×</t>
+          <t>1.6×</t>
         </is>
       </c>
     </row>
@@ -11398,22 +11398,22 @@
       </c>
       <c r="C72" s="14" t="inlineStr">
         <is>
-          <t>HK:1918</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D72" s="14" t="inlineStr">
         <is>
-          <t>Sunac China</t>
+          <t>Counter Narcotics Designations; Russia-related Des</t>
         </is>
       </c>
       <c r="E72" s="14" t="inlineStr">
         <is>
-          <t>Greater China / HK</t>
+          <t>United States/Canada</t>
         </is>
       </c>
       <c r="F72" s="14" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>0.68</t>
         </is>
       </c>
       <c r="G72" s="14" t="inlineStr">
@@ -11423,27 +11423,27 @@
       </c>
       <c r="H72" s="14" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>G</t>
         </is>
       </c>
       <c r="I72" s="14" t="inlineStr">
         <is>
-          <t>48%</t>
+          <t>45%</t>
         </is>
       </c>
       <c r="J72" s="14" t="inlineStr">
         <is>
-          <t>2.09×</t>
+          <t>2.04×</t>
         </is>
       </c>
       <c r="K72" s="14" t="inlineStr">
         <is>
-          <t>2.67×</t>
+          <t>2.52×</t>
         </is>
       </c>
       <c r="L72" s="14" t="inlineStr">
         <is>
-          <t>1.77×</t>
+          <t>1.71×</t>
         </is>
       </c>
       <c r="M72" s="14" t="inlineStr">
@@ -11456,29 +11456,29 @@
       <c r="A73" s="9" t="n">
         <v>69</v>
       </c>
-      <c r="B73" s="15" t="inlineStr">
+      <c r="B73" s="10" t="inlineStr">
         <is>
           <t>PROXY</t>
         </is>
       </c>
       <c r="C73" s="11" t="inlineStr">
         <is>
-          <t>8074</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D73" s="11" t="inlineStr">
         <is>
-          <t>ＹＵＡＳＡ</t>
+          <t>Russia-related Designations Removals</t>
         </is>
       </c>
       <c r="E73" s="11" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States/Canada</t>
         </is>
       </c>
       <c r="F73" s="11" t="inlineStr">
         <is>
-          <t>0.60</t>
+          <t>0.68</t>
         </is>
       </c>
       <c r="G73" s="11" t="inlineStr">
@@ -11488,27 +11488,27 @@
       </c>
       <c r="H73" s="11" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>G</t>
         </is>
       </c>
       <c r="I73" s="11" t="inlineStr">
         <is>
-          <t>47%</t>
+          <t>45%</t>
         </is>
       </c>
       <c r="J73" s="11" t="inlineStr">
         <is>
-          <t>2.08×</t>
+          <t>2.04×</t>
         </is>
       </c>
       <c r="K73" s="11" t="inlineStr">
         <is>
-          <t>2.64×</t>
+          <t>2.52×</t>
         </is>
       </c>
       <c r="L73" s="11" t="inlineStr">
         <is>
-          <t>1.76×</t>
+          <t>1.71×</t>
         </is>
       </c>
       <c r="M73" s="11" t="inlineStr">
@@ -11528,22 +11528,22 @@
       </c>
       <c r="C74" s="14" t="inlineStr">
         <is>
-          <t>2198</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D74" s="14" t="inlineStr">
         <is>
-          <t>アイ・ケイ・ケイＨＤ</t>
+          <t>Democratic Republic of the Congo-related Designati</t>
         </is>
       </c>
       <c r="E74" s="14" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States/Canada</t>
         </is>
       </c>
       <c r="F74" s="14" t="inlineStr">
         <is>
-          <t>0.60</t>
+          <t>0.68</t>
         </is>
       </c>
       <c r="G74" s="14" t="inlineStr">
@@ -11553,27 +11553,27 @@
       </c>
       <c r="H74" s="14" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>G</t>
         </is>
       </c>
       <c r="I74" s="14" t="inlineStr">
         <is>
-          <t>47%</t>
+          <t>45%</t>
         </is>
       </c>
       <c r="J74" s="14" t="inlineStr">
         <is>
-          <t>2.08×</t>
+          <t>2.04×</t>
         </is>
       </c>
       <c r="K74" s="14" t="inlineStr">
         <is>
-          <t>2.64×</t>
+          <t>2.52×</t>
         </is>
       </c>
       <c r="L74" s="14" t="inlineStr">
         <is>
-          <t>1.76×</t>
+          <t>1.71×</t>
         </is>
       </c>
       <c r="M74" s="14" t="inlineStr">
@@ -11586,29 +11586,29 @@
       <c r="A75" s="9" t="n">
         <v>71</v>
       </c>
-      <c r="B75" s="15" t="inlineStr">
+      <c r="B75" s="10" t="inlineStr">
         <is>
           <t>PROXY</t>
         </is>
       </c>
       <c r="C75" s="11" t="inlineStr">
         <is>
-          <t>3454</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D75" s="11" t="inlineStr">
         <is>
-          <t>ファーストブラザーズ</t>
+          <t>Issuance of Democratic Republic of the Congo-relat</t>
         </is>
       </c>
       <c r="E75" s="11" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States/Canada</t>
         </is>
       </c>
       <c r="F75" s="11" t="inlineStr">
         <is>
-          <t>0.60</t>
+          <t>0.68</t>
         </is>
       </c>
       <c r="G75" s="11" t="inlineStr">
@@ -11618,27 +11618,27 @@
       </c>
       <c r="H75" s="11" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>G</t>
         </is>
       </c>
       <c r="I75" s="11" t="inlineStr">
         <is>
-          <t>47%</t>
+          <t>45%</t>
         </is>
       </c>
       <c r="J75" s="11" t="inlineStr">
         <is>
-          <t>2.08×</t>
+          <t>2.04×</t>
         </is>
       </c>
       <c r="K75" s="11" t="inlineStr">
         <is>
-          <t>2.64×</t>
+          <t>2.52×</t>
         </is>
       </c>
       <c r="L75" s="11" t="inlineStr">
         <is>
-          <t>1.76×</t>
+          <t>1.71×</t>
         </is>
       </c>
       <c r="M75" s="11" t="inlineStr">
@@ -11658,22 +11658,22 @@
       </c>
       <c r="C76" s="14" t="inlineStr">
         <is>
-          <t>4641</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D76" s="14" t="inlineStr">
         <is>
-          <t>アルプス技</t>
+          <t>Issuance of Amended Russia-related General License</t>
         </is>
       </c>
       <c r="E76" s="14" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States/Canada</t>
         </is>
       </c>
       <c r="F76" s="14" t="inlineStr">
         <is>
-          <t>0.60</t>
+          <t>0.68</t>
         </is>
       </c>
       <c r="G76" s="14" t="inlineStr">
@@ -11683,27 +11683,27 @@
       </c>
       <c r="H76" s="14" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>G</t>
         </is>
       </c>
       <c r="I76" s="14" t="inlineStr">
         <is>
-          <t>47%</t>
+          <t>45%</t>
         </is>
       </c>
       <c r="J76" s="14" t="inlineStr">
         <is>
-          <t>2.08×</t>
+          <t>2.04×</t>
         </is>
       </c>
       <c r="K76" s="14" t="inlineStr">
         <is>
-          <t>2.64×</t>
+          <t>2.52×</t>
         </is>
       </c>
       <c r="L76" s="14" t="inlineStr">
         <is>
-          <t>1.76×</t>
+          <t>1.71×</t>
         </is>
       </c>
       <c r="M76" s="14" t="inlineStr">
@@ -11716,29 +11716,29 @@
       <c r="A77" s="9" t="n">
         <v>73</v>
       </c>
-      <c r="B77" s="15" t="inlineStr">
+      <c r="B77" s="10" t="inlineStr">
         <is>
           <t>PROXY</t>
         </is>
       </c>
       <c r="C77" s="11" t="inlineStr">
         <is>
-          <t>4170</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D77" s="11" t="inlineStr">
         <is>
-          <t>Ｇ－ＫａｉｚｅｎＰＦ</t>
+          <t>Issuance of Amended Iran-related General License</t>
         </is>
       </c>
       <c r="E77" s="11" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States/Canada</t>
         </is>
       </c>
       <c r="F77" s="11" t="inlineStr">
         <is>
-          <t>0.60</t>
+          <t>0.68</t>
         </is>
       </c>
       <c r="G77" s="11" t="inlineStr">
@@ -11748,27 +11748,27 @@
       </c>
       <c r="H77" s="11" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>G</t>
         </is>
       </c>
       <c r="I77" s="11" t="inlineStr">
         <is>
-          <t>47%</t>
+          <t>45%</t>
         </is>
       </c>
       <c r="J77" s="11" t="inlineStr">
         <is>
-          <t>2.08×</t>
+          <t>2.04×</t>
         </is>
       </c>
       <c r="K77" s="11" t="inlineStr">
         <is>
-          <t>2.64×</t>
+          <t>2.52×</t>
         </is>
       </c>
       <c r="L77" s="11" t="inlineStr">
         <is>
-          <t>1.76×</t>
+          <t>1.71×</t>
         </is>
       </c>
       <c r="M77" s="11" t="inlineStr">
@@ -11788,22 +11788,22 @@
       </c>
       <c r="C78" s="14" t="inlineStr">
         <is>
-          <t>TSE:6753</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D78" s="14" t="inlineStr">
         <is>
-          <t>Sharp</t>
+          <t>Transnational Criminal Organizations Designations;</t>
         </is>
       </c>
       <c r="E78" s="14" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States/Canada</t>
         </is>
       </c>
       <c r="F78" s="14" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>0.68</t>
         </is>
       </c>
       <c r="G78" s="14" t="inlineStr">
@@ -11813,27 +11813,27 @@
       </c>
       <c r="H78" s="14" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>G</t>
         </is>
       </c>
       <c r="I78" s="14" t="inlineStr">
         <is>
-          <t>47%</t>
+          <t>45%</t>
         </is>
       </c>
       <c r="J78" s="14" t="inlineStr">
         <is>
-          <t>2.08×</t>
+          <t>2.04×</t>
         </is>
       </c>
       <c r="K78" s="14" t="inlineStr">
         <is>
-          <t>2.62×</t>
+          <t>2.52×</t>
         </is>
       </c>
       <c r="L78" s="14" t="inlineStr">
         <is>
-          <t>1.75×</t>
+          <t>1.71×</t>
         </is>
       </c>
       <c r="M78" s="14" t="inlineStr">
@@ -11846,29 +11846,29 @@
       <c r="A79" s="9" t="n">
         <v>75</v>
       </c>
-      <c r="B79" s="15" t="inlineStr">
+      <c r="B79" s="10" t="inlineStr">
         <is>
           <t>PROXY</t>
         </is>
       </c>
       <c r="C79" s="11" t="inlineStr">
         <is>
-          <t>3544</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D79" s="11" t="inlineStr">
         <is>
-          <t>サツドラＨＤ</t>
+          <t>Cuba Designation; Russia-related Designations Remo</t>
         </is>
       </c>
       <c r="E79" s="11" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States/Canada</t>
         </is>
       </c>
       <c r="F79" s="11" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>0.68</t>
         </is>
       </c>
       <c r="G79" s="11" t="inlineStr">
@@ -11878,27 +11878,27 @@
       </c>
       <c r="H79" s="11" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>G</t>
         </is>
       </c>
       <c r="I79" s="11" t="inlineStr">
         <is>
-          <t>41%</t>
+          <t>45%</t>
         </is>
       </c>
       <c r="J79" s="11" t="inlineStr">
         <is>
-          <t>1.97×</t>
+          <t>2.04×</t>
         </is>
       </c>
       <c r="K79" s="11" t="inlineStr">
         <is>
-          <t>2.34×</t>
+          <t>2.52×</t>
         </is>
       </c>
       <c r="L79" s="11" t="inlineStr">
         <is>
-          <t>1.65×</t>
+          <t>1.71×</t>
         </is>
       </c>
       <c r="M79" s="11" t="inlineStr">
@@ -11918,22 +11918,22 @@
       </c>
       <c r="C80" s="14" t="inlineStr">
         <is>
-          <t>6897</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D80" s="14" t="inlineStr">
         <is>
-          <t>ツインバード</t>
+          <t>Non-Proliferation Designations; Iran-related Desig</t>
         </is>
       </c>
       <c r="E80" s="14" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States/Canada</t>
         </is>
       </c>
       <c r="F80" s="14" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>0.68</t>
         </is>
       </c>
       <c r="G80" s="14" t="inlineStr">
@@ -11943,27 +11943,27 @@
       </c>
       <c r="H80" s="14" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>G</t>
         </is>
       </c>
       <c r="I80" s="14" t="inlineStr">
         <is>
-          <t>41%</t>
+          <t>45%</t>
         </is>
       </c>
       <c r="J80" s="14" t="inlineStr">
         <is>
-          <t>1.97×</t>
+          <t>2.04×</t>
         </is>
       </c>
       <c r="K80" s="14" t="inlineStr">
         <is>
-          <t>2.34×</t>
+          <t>2.52×</t>
         </is>
       </c>
       <c r="L80" s="14" t="inlineStr">
         <is>
-          <t>1.65×</t>
+          <t>1.71×</t>
         </is>
       </c>
       <c r="M80" s="14" t="inlineStr">
@@ -11976,29 +11976,29 @@
       <c r="A81" s="9" t="n">
         <v>77</v>
       </c>
-      <c r="B81" s="15" t="inlineStr">
+      <c r="B81" s="10" t="inlineStr">
         <is>
           <t>PROXY</t>
         </is>
       </c>
       <c r="C81" s="11" t="inlineStr">
         <is>
-          <t>4951</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D81" s="11" t="inlineStr">
         <is>
-          <t>エステー</t>
+          <t>Designations Removals</t>
         </is>
       </c>
       <c r="E81" s="11" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States/Canada</t>
         </is>
       </c>
       <c r="F81" s="11" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>0.68</t>
         </is>
       </c>
       <c r="G81" s="11" t="inlineStr">
@@ -12008,27 +12008,27 @@
       </c>
       <c r="H81" s="11" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>G</t>
         </is>
       </c>
       <c r="I81" s="11" t="inlineStr">
         <is>
-          <t>41%</t>
+          <t>45%</t>
         </is>
       </c>
       <c r="J81" s="11" t="inlineStr">
         <is>
-          <t>1.97×</t>
+          <t>2.04×</t>
         </is>
       </c>
       <c r="K81" s="11" t="inlineStr">
         <is>
-          <t>2.34×</t>
+          <t>2.52×</t>
         </is>
       </c>
       <c r="L81" s="11" t="inlineStr">
         <is>
-          <t>1.65×</t>
+          <t>1.71×</t>
         </is>
       </c>
       <c r="M81" s="11" t="inlineStr">
@@ -12048,22 +12048,22 @@
       </c>
       <c r="C82" s="14" t="inlineStr">
         <is>
-          <t>3659</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D82" s="14" t="inlineStr">
         <is>
-          <t>ネクソン</t>
+          <t>Counter Terrorism and Counter Narcotics Designatio</t>
         </is>
       </c>
       <c r="E82" s="14" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States/Canada</t>
         </is>
       </c>
       <c r="F82" s="14" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>0.68</t>
         </is>
       </c>
       <c r="G82" s="14" t="inlineStr">
@@ -12073,27 +12073,27 @@
       </c>
       <c r="H82" s="14" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>G</t>
         </is>
       </c>
       <c r="I82" s="14" t="inlineStr">
         <is>
-          <t>41%</t>
+          <t>45%</t>
         </is>
       </c>
       <c r="J82" s="14" t="inlineStr">
         <is>
-          <t>1.97×</t>
+          <t>2.04×</t>
         </is>
       </c>
       <c r="K82" s="14" t="inlineStr">
         <is>
-          <t>2.34×</t>
+          <t>2.52×</t>
         </is>
       </c>
       <c r="L82" s="14" t="inlineStr">
         <is>
-          <t>1.65×</t>
+          <t>1.71×</t>
         </is>
       </c>
       <c r="M82" s="14" t="inlineStr">
@@ -12106,29 +12106,29 @@
       <c r="A83" s="9" t="n">
         <v>79</v>
       </c>
-      <c r="B83" s="15" t="inlineStr">
+      <c r="B83" s="10" t="inlineStr">
         <is>
           <t>PROXY</t>
         </is>
       </c>
       <c r="C83" s="11" t="inlineStr">
         <is>
-          <t>B3:LIGT3</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D83" s="11" t="inlineStr">
         <is>
-          <t>Light SA</t>
+          <t>Counter Terrorism and Iran-related Designations; C</t>
         </is>
       </c>
       <c r="E83" s="11" t="inlineStr">
         <is>
-          <t>Latin America</t>
+          <t>United States/Canada</t>
         </is>
       </c>
       <c r="F83" s="11" t="inlineStr">
         <is>
-          <t>0.58</t>
+          <t>0.68</t>
         </is>
       </c>
       <c r="G83" s="11" t="inlineStr">
@@ -12138,27 +12138,27 @@
       </c>
       <c r="H83" s="11" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>G</t>
         </is>
       </c>
       <c r="I83" s="11" t="inlineStr">
         <is>
-          <t>40%</t>
+          <t>45%</t>
         </is>
       </c>
       <c r="J83" s="11" t="inlineStr">
         <is>
-          <t>1.98×</t>
+          <t>2.04×</t>
         </is>
       </c>
       <c r="K83" s="11" t="inlineStr">
         <is>
-          <t>2.37×</t>
+          <t>2.52×</t>
         </is>
       </c>
       <c r="L83" s="11" t="inlineStr">
         <is>
-          <t>1.66×</t>
+          <t>1.71×</t>
         </is>
       </c>
       <c r="M83" s="11" t="inlineStr">
@@ -12183,17 +12183,17 @@
       </c>
       <c r="D84" s="14" t="inlineStr">
         <is>
-          <t>ATOM EDUCAÇÃO E EDITORA S.A.</t>
+          <t>Issuance of Venezuela-related General License</t>
         </is>
       </c>
       <c r="E84" s="14" t="inlineStr">
         <is>
-          <t>Latin America</t>
+          <t>United States/Canada</t>
         </is>
       </c>
       <c r="F84" s="14" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>0.68</t>
         </is>
       </c>
       <c r="G84" s="14" t="inlineStr">
@@ -12203,27 +12203,27 @@
       </c>
       <c r="H84" s="14" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>G</t>
         </is>
       </c>
       <c r="I84" s="14" t="inlineStr">
         <is>
-          <t>41%</t>
+          <t>45%</t>
         </is>
       </c>
       <c r="J84" s="14" t="inlineStr">
         <is>
-          <t>1.97×</t>
+          <t>2.04×</t>
         </is>
       </c>
       <c r="K84" s="14" t="inlineStr">
         <is>
-          <t>2.34×</t>
+          <t>2.52×</t>
         </is>
       </c>
       <c r="L84" s="14" t="inlineStr">
         <is>
-          <t>1.65×</t>
+          <t>1.71×</t>
         </is>
       </c>
       <c r="M84" s="14" t="inlineStr">
@@ -12236,7 +12236,7 @@
       <c r="A85" s="9" t="n">
         <v>81</v>
       </c>
-      <c r="B85" s="15" t="inlineStr">
+      <c r="B85" s="10" t="inlineStr">
         <is>
           <t>PROXY</t>
         </is>
@@ -12248,17 +12248,17 @@
       </c>
       <c r="D85" s="11" t="inlineStr">
         <is>
-          <t>OI S.A. - EM RECUPERAÇÃO JUDICIAL</t>
+          <t>Iran-related Designations; Issuance of Iran-relate</t>
         </is>
       </c>
       <c r="E85" s="11" t="inlineStr">
         <is>
-          <t>Latin America</t>
+          <t>United States/Canada</t>
         </is>
       </c>
       <c r="F85" s="11" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>0.68</t>
         </is>
       </c>
       <c r="G85" s="11" t="inlineStr">
@@ -12268,27 +12268,27 @@
       </c>
       <c r="H85" s="11" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>G</t>
         </is>
       </c>
       <c r="I85" s="11" t="inlineStr">
         <is>
-          <t>41%</t>
+          <t>45%</t>
         </is>
       </c>
       <c r="J85" s="11" t="inlineStr">
         <is>
-          <t>1.97×</t>
+          <t>2.04×</t>
         </is>
       </c>
       <c r="K85" s="11" t="inlineStr">
         <is>
-          <t>2.34×</t>
+          <t>2.52×</t>
         </is>
       </c>
       <c r="L85" s="11" t="inlineStr">
         <is>
-          <t>1.65×</t>
+          <t>1.71×</t>
         </is>
       </c>
       <c r="M85" s="11" t="inlineStr">
@@ -12313,17 +12313,17 @@
       </c>
       <c r="D86" s="14" t="inlineStr">
         <is>
-          <t>PETTENATI S.A. INDUSTRIA TEXTIL</t>
+          <t>Iran-related Designations; Counter Terrorism and I</t>
         </is>
       </c>
       <c r="E86" s="14" t="inlineStr">
         <is>
-          <t>Latin America</t>
+          <t>United States/Canada</t>
         </is>
       </c>
       <c r="F86" s="14" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>0.68</t>
         </is>
       </c>
       <c r="G86" s="14" t="inlineStr">
@@ -12333,27 +12333,27 @@
       </c>
       <c r="H86" s="14" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>G</t>
         </is>
       </c>
       <c r="I86" s="14" t="inlineStr">
         <is>
-          <t>41%</t>
+          <t>45%</t>
         </is>
       </c>
       <c r="J86" s="14" t="inlineStr">
         <is>
-          <t>1.97×</t>
+          <t>2.04×</t>
         </is>
       </c>
       <c r="K86" s="14" t="inlineStr">
         <is>
-          <t>2.34×</t>
+          <t>2.52×</t>
         </is>
       </c>
       <c r="L86" s="14" t="inlineStr">
         <is>
-          <t>1.65×</t>
+          <t>1.71×</t>
         </is>
       </c>
       <c r="M86" s="14" t="inlineStr">
@@ -12366,7 +12366,7 @@
       <c r="A87" s="9" t="n">
         <v>83</v>
       </c>
-      <c r="B87" s="15" t="inlineStr">
+      <c r="B87" s="10" t="inlineStr">
         <is>
           <t>PROXY</t>
         </is>
@@ -12378,17 +12378,17 @@
       </c>
       <c r="D87" s="11" t="inlineStr">
         <is>
-          <t>MANUFATURA DE BRINQUEDOS ESTRELA SA</t>
+          <t>Counter Terrorism, Counter Narcotics, and Cyber-re</t>
         </is>
       </c>
       <c r="E87" s="11" t="inlineStr">
         <is>
-          <t>Latin America</t>
+          <t>United States/Canada</t>
         </is>
       </c>
       <c r="F87" s="11" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>0.68</t>
         </is>
       </c>
       <c r="G87" s="11" t="inlineStr">
@@ -12398,27 +12398,27 @@
       </c>
       <c r="H87" s="11" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>G</t>
         </is>
       </c>
       <c r="I87" s="11" t="inlineStr">
         <is>
-          <t>41%</t>
+          <t>45%</t>
         </is>
       </c>
       <c r="J87" s="11" t="inlineStr">
         <is>
-          <t>1.97×</t>
+          <t>2.04×</t>
         </is>
       </c>
       <c r="K87" s="11" t="inlineStr">
         <is>
-          <t>2.34×</t>
+          <t>2.52×</t>
         </is>
       </c>
       <c r="L87" s="11" t="inlineStr">
         <is>
-          <t>1.65×</t>
+          <t>1.71×</t>
         </is>
       </c>
       <c r="M87" s="11" t="inlineStr">
@@ -12443,17 +12443,17 @@
       </c>
       <c r="D88" s="14" t="inlineStr">
         <is>
-          <t>BBM LOGÍSTICA S.A.</t>
+          <t>Nicaragua-related Designations; Issuance of Nicara</t>
         </is>
       </c>
       <c r="E88" s="14" t="inlineStr">
         <is>
-          <t>Latin America</t>
+          <t>United States/Canada</t>
         </is>
       </c>
       <c r="F88" s="14" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>0.68</t>
         </is>
       </c>
       <c r="G88" s="14" t="inlineStr">
@@ -12463,27 +12463,27 @@
       </c>
       <c r="H88" s="14" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>G</t>
         </is>
       </c>
       <c r="I88" s="14" t="inlineStr">
         <is>
-          <t>41%</t>
+          <t>45%</t>
         </is>
       </c>
       <c r="J88" s="14" t="inlineStr">
         <is>
-          <t>1.97×</t>
+          <t>2.04×</t>
         </is>
       </c>
       <c r="K88" s="14" t="inlineStr">
         <is>
-          <t>2.34×</t>
+          <t>2.52×</t>
         </is>
       </c>
       <c r="L88" s="14" t="inlineStr">
         <is>
-          <t>1.65×</t>
+          <t>1.71×</t>
         </is>
       </c>
       <c r="M88" s="14" t="inlineStr">
@@ -12496,29 +12496,29 @@
       <c r="A89" s="9" t="n">
         <v>85</v>
       </c>
-      <c r="B89" s="15" t="inlineStr">
+      <c r="B89" s="10" t="inlineStr">
         <is>
           <t>PROXY</t>
         </is>
       </c>
       <c r="C89" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>NGX:ACCESSCORP</t>
         </is>
       </c>
       <c r="D89" s="11" t="inlineStr">
         <is>
-          <t>GRUPO TOKY S.A.</t>
+          <t>Access Holdings</t>
         </is>
       </c>
       <c r="E89" s="11" t="inlineStr">
         <is>
-          <t>Latin America</t>
+          <t>MEA / Frontier</t>
         </is>
       </c>
       <c r="F89" s="11" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="G89" s="11" t="inlineStr">
@@ -12528,27 +12528,27 @@
       </c>
       <c r="H89" s="11" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>G</t>
         </is>
       </c>
       <c r="I89" s="11" t="inlineStr">
         <is>
-          <t>41%</t>
+          <t>45%</t>
         </is>
       </c>
       <c r="J89" s="11" t="inlineStr">
         <is>
-          <t>1.97×</t>
+          <t>2.03×</t>
         </is>
       </c>
       <c r="K89" s="11" t="inlineStr">
         <is>
-          <t>2.34×</t>
+          <t>2.50×</t>
         </is>
       </c>
       <c r="L89" s="11" t="inlineStr">
         <is>
-          <t>1.65×</t>
+          <t>1.70×</t>
         </is>
       </c>
       <c r="M89" s="11" t="inlineStr">
@@ -12568,22 +12568,22 @@
       </c>
       <c r="C90" s="14" t="inlineStr">
         <is>
-          <t>NGX:ACCESSCORP</t>
+          <t>8074</t>
         </is>
       </c>
       <c r="D90" s="14" t="inlineStr">
         <is>
-          <t>Access Holdings</t>
+          <t>ＹＵＡＳＡ</t>
         </is>
       </c>
       <c r="E90" s="14" t="inlineStr">
         <is>
-          <t>MEA / Frontier</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="F90" s="14" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>0.60</t>
         </is>
       </c>
       <c r="G90" s="14" t="inlineStr">
@@ -12593,27 +12593,27 @@
       </c>
       <c r="H90" s="14" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>H</t>
         </is>
       </c>
       <c r="I90" s="14" t="inlineStr">
         <is>
-          <t>45%</t>
+          <t>47%</t>
         </is>
       </c>
       <c r="J90" s="14" t="inlineStr">
         <is>
-          <t>2.03×</t>
+          <t>2.08×</t>
         </is>
       </c>
       <c r="K90" s="14" t="inlineStr">
         <is>
-          <t>2.50×</t>
+          <t>2.64×</t>
         </is>
       </c>
       <c r="L90" s="14" t="inlineStr">
         <is>
-          <t>1.70×</t>
+          <t>1.76×</t>
         </is>
       </c>
       <c r="M90" s="14" t="inlineStr">
@@ -12626,29 +12626,29 @@
       <c r="A91" s="9" t="n">
         <v>87</v>
       </c>
-      <c r="B91" s="15" t="inlineStr">
+      <c r="B91" s="10" t="inlineStr">
         <is>
           <t>PROXY</t>
         </is>
       </c>
       <c r="C91" s="11" t="inlineStr">
         <is>
-          <t>ERM</t>
+          <t>2198</t>
         </is>
       </c>
       <c r="D91" s="11" t="inlineStr">
         <is>
-          <t>EMMERSON RESOURCES LIMITED</t>
+          <t>アイ・ケイ・ケイＨＤ</t>
         </is>
       </c>
       <c r="E91" s="11" t="inlineStr">
         <is>
-          <t>SE Asia / Pacific</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="F91" s="11" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>0.60</t>
         </is>
       </c>
       <c r="G91" s="11" t="inlineStr">
@@ -12658,27 +12658,27 @@
       </c>
       <c r="H91" s="11" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>H</t>
         </is>
       </c>
       <c r="I91" s="11" t="inlineStr">
         <is>
-          <t>41%</t>
+          <t>47%</t>
         </is>
       </c>
       <c r="J91" s="11" t="inlineStr">
         <is>
-          <t>1.97×</t>
+          <t>2.08×</t>
         </is>
       </c>
       <c r="K91" s="11" t="inlineStr">
         <is>
-          <t>2.34×</t>
+          <t>2.64×</t>
         </is>
       </c>
       <c r="L91" s="11" t="inlineStr">
         <is>
-          <t>1.65×</t>
+          <t>1.76×</t>
         </is>
       </c>
       <c r="M91" s="11" t="inlineStr">
@@ -12698,22 +12698,22 @@
       </c>
       <c r="C92" s="14" t="inlineStr">
         <is>
-          <t>PEX</t>
+          <t>3454</t>
         </is>
       </c>
       <c r="D92" s="14" t="inlineStr">
         <is>
-          <t>PEEL MINING LIMITED</t>
+          <t>ファーストブラザーズ</t>
         </is>
       </c>
       <c r="E92" s="14" t="inlineStr">
         <is>
-          <t>SE Asia / Pacific</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="F92" s="14" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>0.60</t>
         </is>
       </c>
       <c r="G92" s="14" t="inlineStr">
@@ -12723,27 +12723,27 @@
       </c>
       <c r="H92" s="14" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>H</t>
         </is>
       </c>
       <c r="I92" s="14" t="inlineStr">
         <is>
-          <t>41%</t>
+          <t>47%</t>
         </is>
       </c>
       <c r="J92" s="14" t="inlineStr">
         <is>
-          <t>1.97×</t>
+          <t>2.08×</t>
         </is>
       </c>
       <c r="K92" s="14" t="inlineStr">
         <is>
-          <t>2.34×</t>
+          <t>2.64×</t>
         </is>
       </c>
       <c r="L92" s="14" t="inlineStr">
         <is>
-          <t>1.65×</t>
+          <t>1.76×</t>
         </is>
       </c>
       <c r="M92" s="14" t="inlineStr">
@@ -12756,29 +12756,29 @@
       <c r="A93" s="9" t="n">
         <v>89</v>
       </c>
-      <c r="B93" s="15" t="inlineStr">
+      <c r="B93" s="10" t="inlineStr">
         <is>
           <t>PROXY</t>
         </is>
       </c>
       <c r="C93" s="11" t="inlineStr">
         <is>
-          <t>AIS</t>
+          <t>4641</t>
         </is>
       </c>
       <c r="D93" s="11" t="inlineStr">
         <is>
-          <t>AERIS RESOURCES LIMITED</t>
+          <t>アルプス技</t>
         </is>
       </c>
       <c r="E93" s="11" t="inlineStr">
         <is>
-          <t>SE Asia / Pacific</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="F93" s="11" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>0.60</t>
         </is>
       </c>
       <c r="G93" s="11" t="inlineStr">
@@ -12788,27 +12788,27 @@
       </c>
       <c r="H93" s="11" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>H</t>
         </is>
       </c>
       <c r="I93" s="11" t="inlineStr">
         <is>
-          <t>41%</t>
+          <t>47%</t>
         </is>
       </c>
       <c r="J93" s="11" t="inlineStr">
         <is>
-          <t>1.97×</t>
+          <t>2.08×</t>
         </is>
       </c>
       <c r="K93" s="11" t="inlineStr">
         <is>
-          <t>2.34×</t>
+          <t>2.64×</t>
         </is>
       </c>
       <c r="L93" s="11" t="inlineStr">
         <is>
-          <t>1.65×</t>
+          <t>1.76×</t>
         </is>
       </c>
       <c r="M93" s="11" t="inlineStr">
@@ -12828,22 +12828,22 @@
       </c>
       <c r="C94" s="14" t="inlineStr">
         <is>
-          <t>ASM</t>
+          <t>4170</t>
         </is>
       </c>
       <c r="D94" s="14" t="inlineStr">
         <is>
-          <t>AUSTRALIAN STRATEGIC MATERIALS LIMITED</t>
+          <t>Ｇ－ＫａｉｚｅｎＰＦ</t>
         </is>
       </c>
       <c r="E94" s="14" t="inlineStr">
         <is>
-          <t>SE Asia / Pacific</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="F94" s="14" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>0.60</t>
         </is>
       </c>
       <c r="G94" s="14" t="inlineStr">
@@ -12853,27 +12853,27 @@
       </c>
       <c r="H94" s="14" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>H</t>
         </is>
       </c>
       <c r="I94" s="14" t="inlineStr">
         <is>
-          <t>41%</t>
+          <t>47%</t>
         </is>
       </c>
       <c r="J94" s="14" t="inlineStr">
         <is>
-          <t>1.97×</t>
+          <t>2.08×</t>
         </is>
       </c>
       <c r="K94" s="14" t="inlineStr">
         <is>
-          <t>2.34×</t>
+          <t>2.64×</t>
         </is>
       </c>
       <c r="L94" s="14" t="inlineStr">
         <is>
-          <t>1.65×</t>
+          <t>1.76×</t>
         </is>
       </c>
       <c r="M94" s="14" t="inlineStr">
@@ -12886,29 +12886,29 @@
       <c r="A95" s="9" t="n">
         <v>91</v>
       </c>
-      <c r="B95" s="15" t="inlineStr">
+      <c r="B95" s="10" t="inlineStr">
         <is>
           <t>PROXY</t>
         </is>
       </c>
       <c r="C95" s="11" t="inlineStr">
         <is>
-          <t>QUB</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="D95" s="11" t="inlineStr">
         <is>
-          <t>QUBE HOLDINGS LIMITED</t>
+          <t>GENCO SHIPPING &amp; TRADING LTD</t>
         </is>
       </c>
       <c r="E95" s="11" t="inlineStr">
         <is>
-          <t>SE Asia / Pacific</t>
+          <t>United States/Canada</t>
         </is>
       </c>
       <c r="F95" s="11" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>0.60</t>
         </is>
       </c>
       <c r="G95" s="11" t="inlineStr">
@@ -12918,27 +12918,27 @@
       </c>
       <c r="H95" s="11" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>H</t>
         </is>
       </c>
       <c r="I95" s="11" t="inlineStr">
         <is>
-          <t>41%</t>
+          <t>47%</t>
         </is>
       </c>
       <c r="J95" s="11" t="inlineStr">
         <is>
-          <t>1.97×</t>
+          <t>2.08×</t>
         </is>
       </c>
       <c r="K95" s="11" t="inlineStr">
         <is>
-          <t>2.34×</t>
+          <t>2.64×</t>
         </is>
       </c>
       <c r="L95" s="11" t="inlineStr">
         <is>
-          <t>1.65×</t>
+          <t>1.76×</t>
         </is>
       </c>
       <c r="M95" s="11" t="inlineStr">
@@ -12958,22 +12958,22 @@
       </c>
       <c r="C96" s="14" t="inlineStr">
         <is>
-          <t>NVA</t>
+          <t>SEER</t>
         </is>
       </c>
       <c r="D96" s="14" t="inlineStr">
         <is>
-          <t>NOVA MINERALS CORP</t>
+          <t>Seer, Inc.</t>
         </is>
       </c>
       <c r="E96" s="14" t="inlineStr">
         <is>
-          <t>SE Asia / Pacific</t>
+          <t>United States/Canada</t>
         </is>
       </c>
       <c r="F96" s="14" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>0.60</t>
         </is>
       </c>
       <c r="G96" s="14" t="inlineStr">
@@ -12983,27 +12983,27 @@
       </c>
       <c r="H96" s="14" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>H</t>
         </is>
       </c>
       <c r="I96" s="14" t="inlineStr">
         <is>
-          <t>41%</t>
+          <t>47%</t>
         </is>
       </c>
       <c r="J96" s="14" t="inlineStr">
         <is>
-          <t>1.97×</t>
+          <t>2.08×</t>
         </is>
       </c>
       <c r="K96" s="14" t="inlineStr">
         <is>
-          <t>2.34×</t>
+          <t>2.64×</t>
         </is>
       </c>
       <c r="L96" s="14" t="inlineStr">
         <is>
-          <t>1.65×</t>
+          <t>1.76×</t>
         </is>
       </c>
       <c r="M96" s="14" t="inlineStr">
@@ -13016,29 +13016,29 @@
       <c r="A97" s="9" t="n">
         <v>93</v>
       </c>
-      <c r="B97" s="15" t="inlineStr">
+      <c r="B97" s="10" t="inlineStr">
         <is>
           <t>PROXY</t>
         </is>
       </c>
       <c r="C97" s="11" t="inlineStr">
         <is>
-          <t>PAF</t>
+          <t>FRMI</t>
         </is>
       </c>
       <c r="D97" s="11" t="inlineStr">
         <is>
-          <t>PAN AFRICAN RESOURCES PLC</t>
+          <t>Fermi Inc.</t>
         </is>
       </c>
       <c r="E97" s="11" t="inlineStr">
         <is>
-          <t>SE Asia / Pacific</t>
+          <t>United States/Canada</t>
         </is>
       </c>
       <c r="F97" s="11" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>0.60</t>
         </is>
       </c>
       <c r="G97" s="11" t="inlineStr">
@@ -13048,27 +13048,27 @@
       </c>
       <c r="H97" s="11" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>H</t>
         </is>
       </c>
       <c r="I97" s="11" t="inlineStr">
         <is>
-          <t>41%</t>
+          <t>47%</t>
         </is>
       </c>
       <c r="J97" s="11" t="inlineStr">
         <is>
-          <t>1.97×</t>
+          <t>2.08×</t>
         </is>
       </c>
       <c r="K97" s="11" t="inlineStr">
         <is>
-          <t>2.34×</t>
+          <t>2.64×</t>
         </is>
       </c>
       <c r="L97" s="11" t="inlineStr">
         <is>
-          <t>1.65×</t>
+          <t>1.76×</t>
         </is>
       </c>
       <c r="M97" s="11" t="inlineStr">
@@ -13088,22 +13088,22 @@
       </c>
       <c r="C98" s="14" t="inlineStr">
         <is>
-          <t>QOR</t>
+          <t>CIK:0001098464</t>
         </is>
       </c>
       <c r="D98" s="14" t="inlineStr">
         <is>
-          <t>QORIA LIMITED</t>
+          <t>NEUGEBAUER TOBY R</t>
         </is>
       </c>
       <c r="E98" s="14" t="inlineStr">
         <is>
-          <t>SE Asia / Pacific</t>
+          <t>United States/Canada</t>
         </is>
       </c>
       <c r="F98" s="14" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>0.60</t>
         </is>
       </c>
       <c r="G98" s="14" t="inlineStr">
@@ -13113,27 +13113,27 @@
       </c>
       <c r="H98" s="14" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>H</t>
         </is>
       </c>
       <c r="I98" s="14" t="inlineStr">
         <is>
-          <t>41%</t>
+          <t>47%</t>
         </is>
       </c>
       <c r="J98" s="14" t="inlineStr">
         <is>
-          <t>1.97×</t>
+          <t>2.08×</t>
         </is>
       </c>
       <c r="K98" s="14" t="inlineStr">
         <is>
-          <t>2.34×</t>
+          <t>2.64×</t>
         </is>
       </c>
       <c r="L98" s="14" t="inlineStr">
         <is>
-          <t>1.65×</t>
+          <t>1.76×</t>
         </is>
       </c>
       <c r="M98" s="14" t="inlineStr">
@@ -13146,29 +13146,29 @@
       <c r="A99" s="9" t="n">
         <v>95</v>
       </c>
-      <c r="B99" s="15" t="inlineStr">
+      <c r="B99" s="10" t="inlineStr">
         <is>
           <t>PROXY</t>
         </is>
       </c>
       <c r="C99" s="11" t="inlineStr">
         <is>
-          <t>LLM</t>
+          <t>CIK:0001380585</t>
         </is>
       </c>
       <c r="D99" s="11" t="inlineStr">
         <is>
-          <t>LOYAL METALS LTD</t>
+          <t>Radoff Bradley Louis</t>
         </is>
       </c>
       <c r="E99" s="11" t="inlineStr">
         <is>
-          <t>SE Asia / Pacific</t>
+          <t>United States/Canada</t>
         </is>
       </c>
       <c r="F99" s="11" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>0.60</t>
         </is>
       </c>
       <c r="G99" s="11" t="inlineStr">
@@ -13178,27 +13178,27 @@
       </c>
       <c r="H99" s="11" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>H</t>
         </is>
       </c>
       <c r="I99" s="11" t="inlineStr">
         <is>
-          <t>41%</t>
+          <t>47%</t>
         </is>
       </c>
       <c r="J99" s="11" t="inlineStr">
         <is>
-          <t>1.97×</t>
+          <t>2.08×</t>
         </is>
       </c>
       <c r="K99" s="11" t="inlineStr">
         <is>
-          <t>2.34×</t>
+          <t>2.64×</t>
         </is>
       </c>
       <c r="L99" s="11" t="inlineStr">
         <is>
-          <t>1.65×</t>
+          <t>1.76×</t>
         </is>
       </c>
       <c r="M99" s="11" t="inlineStr">
@@ -13218,22 +13218,22 @@
       </c>
       <c r="C100" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>TSE:6753</t>
         </is>
       </c>
       <c r="D100" s="14" t="inlineStr">
         <is>
-          <t>REDCENTRIC PLC</t>
+          <t>Sharp</t>
         </is>
       </c>
       <c r="E100" s="14" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="F100" s="14" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="G100" s="14" t="inlineStr">
@@ -13243,27 +13243,27 @@
       </c>
       <c r="H100" s="14" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>H</t>
         </is>
       </c>
       <c r="I100" s="14" t="inlineStr">
         <is>
-          <t>41%</t>
+          <t>47%</t>
         </is>
       </c>
       <c r="J100" s="14" t="inlineStr">
         <is>
-          <t>1.97×</t>
+          <t>2.08×</t>
         </is>
       </c>
       <c r="K100" s="14" t="inlineStr">
         <is>
-          <t>2.34×</t>
+          <t>2.62×</t>
         </is>
       </c>
       <c r="L100" s="14" t="inlineStr">
         <is>
-          <t>1.65×</t>
+          <t>1.75×</t>
         </is>
       </c>
       <c r="M100" s="14" t="inlineStr">
@@ -13276,29 +13276,29 @@
       <c r="A101" s="9" t="n">
         <v>97</v>
       </c>
-      <c r="B101" s="15" t="inlineStr">
+      <c r="B101" s="10" t="inlineStr">
         <is>
           <t>PROXY</t>
         </is>
       </c>
       <c r="C101" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>B3:LIGT3</t>
         </is>
       </c>
       <c r="D101" s="11" t="inlineStr">
         <is>
-          <t>CT HEALTHCARE TRUST PLC</t>
+          <t>Light SA</t>
         </is>
       </c>
       <c r="E101" s="11" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Latin America</t>
         </is>
       </c>
       <c r="F101" s="11" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>0.58</t>
         </is>
       </c>
       <c r="G101" s="11" t="inlineStr">
@@ -13308,27 +13308,27 @@
       </c>
       <c r="H101" s="11" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>E</t>
         </is>
       </c>
       <c r="I101" s="11" t="inlineStr">
         <is>
-          <t>41%</t>
+          <t>40%</t>
         </is>
       </c>
       <c r="J101" s="11" t="inlineStr">
         <is>
-          <t>1.97×</t>
+          <t>1.98×</t>
         </is>
       </c>
       <c r="K101" s="11" t="inlineStr">
         <is>
-          <t>2.34×</t>
+          <t>2.37×</t>
         </is>
       </c>
       <c r="L101" s="11" t="inlineStr">
         <is>
-          <t>1.65×</t>
+          <t>1.66×</t>
         </is>
       </c>
       <c r="M101" s="11" t="inlineStr">
@@ -13353,7 +13353,7 @@
       </c>
       <c r="D102" s="14" t="inlineStr">
         <is>
-          <t>JUST GROUP PLC</t>
+          <t>REDCENTRIC PLC</t>
         </is>
       </c>
       <c r="E102" s="14" t="inlineStr">
@@ -13406,7 +13406,7 @@
       <c r="A103" s="9" t="n">
         <v>99</v>
       </c>
-      <c r="B103" s="15" t="inlineStr">
+      <c r="B103" s="10" t="inlineStr">
         <is>
           <t>PROXY</t>
         </is>
@@ -13418,7 +13418,7 @@
       </c>
       <c r="D103" s="11" t="inlineStr">
         <is>
-          <t>Zambia (Republic of) (MoF)</t>
+          <t>CT HEALTHCARE TRUST PLC</t>
         </is>
       </c>
       <c r="E103" s="11" t="inlineStr">
@@ -13483,7 +13483,7 @@
       </c>
       <c r="D104" s="14" t="inlineStr">
         <is>
-          <t>LEGAL &amp; GENERAL GROUP PLC</t>
+          <t>JUST GROUP PLC</t>
         </is>
       </c>
       <c r="E104" s="14" t="inlineStr">
@@ -13536,7 +13536,7 @@
     <row r="106" ht="60" customHeight="1">
       <c r="A106" s="7" t="inlineStr">
         <is>
-          <t>Reward/Risk = (EV× − 1) ÷ Bear loss = the asymmetry metric.  The broad universe-screener scores the full candidate set on archetype, vintage, status, size, region, and cross-source corroboration; this asymmetric scan ranks the investable subset (308 names) by reward/risk. Investable filter drops PASS_FALSE_FRIEND / ACQUIRED / ARC_DONE / REPEAT_RX and non-equity placeholder tickers ((state), (private), (delisted)). PROXY waterfall: bear_loss = max(0.10, 0.65 − 0.30·score), tilted ×0.75 for A1/A2 (sovereign-anchored floor). bull = 1.50 + 1.50·score, tilted ×1.10 for H, ×1.15 for F. Hand-built YAMLs override the proxy with bottom-up numbers.</t>
+          <t>Reward/Risk = (EV× − 1) ÷ Bear loss = the asymmetry metric.  The broad universe-screener scores the full candidate set on archetype, vintage, status, size, region, and cross-source corroboration; this asymmetric scan ranks the investable subset (731 names) by reward/risk. Investable filter drops PASS_FALSE_FRIEND / ACQUIRED / ARC_DONE / REPEAT_RX and non-equity placeholder tickers ((state), (private), (delisted)). PROXY waterfall: bear_loss = max(0.10, 0.65 − 0.30·score), tilted ×0.75 for A1/A2 (sovereign-anchored floor). bull = 1.50 + 1.50·score, tilted ×1.10 for H, ×1.15 for F. Hand-built YAMLs override the proxy with bottom-up numbers.</t>
         </is>
       </c>
     </row>
@@ -13639,7 +13639,7 @@
     </row>
     <row r="5">
       <c r="A5" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
@@ -13679,7 +13679,7 @@
     </row>
     <row r="6">
       <c r="A6" s="12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B6" s="14" t="inlineStr">
         <is>
@@ -13719,7 +13719,7 @@
     </row>
     <row r="7">
       <c r="A7" s="9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
@@ -13759,7 +13759,7 @@
     </row>
     <row r="8">
       <c r="A8" s="12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
@@ -13799,7 +13799,7 @@
     </row>
     <row r="9">
       <c r="A9" s="9" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
@@ -13839,7 +13839,7 @@
     </row>
     <row r="10">
       <c r="A10" s="12" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
@@ -13883,27 +13883,27 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>BME:TLGO</t>
+          <t>TBRG</t>
         </is>
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>Talgo</t>
+          <t>TruBridge, Inc.</t>
         </is>
       </c>
       <c r="D11" s="11" t="inlineStr">
         <is>
-          <t>Continental Europe</t>
+          <t>United States/Canada</t>
         </is>
       </c>
       <c r="E11" s="11" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="F11" s="11" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>K3</t>
         </is>
       </c>
       <c r="G11" s="11" t="inlineStr">
@@ -13913,37 +13913,37 @@
       </c>
       <c r="H11" s="11" t="inlineStr">
         <is>
-          <t>Tier 2 — verify primary docs first</t>
+          <t>Tier 1 — hand-deepen ASAP</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="12" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B12" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>LEG</t>
         </is>
       </c>
       <c r="C12" s="14" t="inlineStr">
         <is>
-          <t>IRANI PAPEL E EMBALAGEM S.A.</t>
+          <t>LEGGETT &amp; PLATT INC</t>
         </is>
       </c>
       <c r="D12" s="14" t="inlineStr">
         <is>
-          <t>Latin America</t>
+          <t>United States/Canada</t>
         </is>
       </c>
       <c r="E12" s="14" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="F12" s="14" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>C</t>
         </is>
       </c>
       <c r="G12" s="14" t="inlineStr">
@@ -13953,32 +13953,32 @@
       </c>
       <c r="H12" s="14" t="inlineStr">
         <is>
-          <t>Tier 2 — verify primary docs first</t>
+          <t>Tier 1 — hand-deepen ASAP</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="9" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>BME:TLGO</t>
         </is>
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>COMERC ENERGIA S.A.</t>
+          <t>Talgo</t>
         </is>
       </c>
       <c r="D13" s="11" t="inlineStr">
         <is>
-          <t>Latin America</t>
+          <t>Continental Europe</t>
         </is>
       </c>
       <c r="E13" s="11" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="F13" s="11" t="inlineStr">
@@ -13999,26 +13999,26 @@
     </row>
     <row r="14">
       <c r="A14" s="12" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B14" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>LSE:ASC</t>
         </is>
       </c>
       <c r="C14" s="14" t="inlineStr">
         <is>
-          <t>SOCIEDADE ABASTECIMENTO DE AGUA E SANEAMENTO SA</t>
+          <t>ASOS</t>
         </is>
       </c>
       <c r="D14" s="14" t="inlineStr">
         <is>
-          <t>Latin America</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="E14" s="14" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="F14" s="14" t="inlineStr">
@@ -14039,7 +14039,7 @@
     </row>
     <row r="15">
       <c r="A15" s="9" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
@@ -14048,7 +14048,7 @@
       </c>
       <c r="C15" s="11" t="inlineStr">
         <is>
-          <t>MINERVA S/A</t>
+          <t>IRANI PAPEL E EMBALAGEM S.A.</t>
         </is>
       </c>
       <c r="D15" s="11" t="inlineStr">
@@ -14079,7 +14079,7 @@
     </row>
     <row r="16">
       <c r="A16" s="12" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B16" s="14" t="inlineStr">
         <is>
@@ -14088,7 +14088,7 @@
       </c>
       <c r="C16" s="14" t="inlineStr">
         <is>
-          <t>BRADESCO LEASING S.A. - ARRENDAMENTO MERCANTIL</t>
+          <t>COMERC ENERGIA S.A.</t>
         </is>
       </c>
       <c r="D16" s="14" t="inlineStr">
@@ -14119,26 +14119,26 @@
     </row>
     <row r="17">
       <c r="A17" s="9" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>LSE:ASC</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C17" s="11" t="inlineStr">
         <is>
-          <t>ASOS</t>
+          <t>SOCIEDADE ABASTECIMENTO DE AGUA E SANEAMENTO SA</t>
         </is>
       </c>
       <c r="D17" s="11" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Latin America</t>
         </is>
       </c>
       <c r="E17" s="11" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="F17" s="11" t="inlineStr">
@@ -14159,31 +14159,31 @@
     </row>
     <row r="18">
       <c r="A18" s="12" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B18" s="14" t="inlineStr">
         <is>
-          <t>TBRG</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C18" s="14" t="inlineStr">
         <is>
-          <t>TruBridge, Inc.</t>
+          <t>MINERVA S/A</t>
         </is>
       </c>
       <c r="D18" s="14" t="inlineStr">
         <is>
-          <t>United States/Canada</t>
+          <t>Latin America</t>
         </is>
       </c>
       <c r="E18" s="14" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="F18" s="14" t="inlineStr">
         <is>
-          <t>K3</t>
+          <t>A1</t>
         </is>
       </c>
       <c r="G18" s="14" t="inlineStr">
@@ -14193,37 +14193,37 @@
       </c>
       <c r="H18" s="14" t="inlineStr">
         <is>
-          <t>Tier 1 — hand-deepen ASAP</t>
+          <t>Tier 2 — verify primary docs first</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="9" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>LEG</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C19" s="11" t="inlineStr">
         <is>
-          <t>LEGGETT &amp; PLATT INC</t>
+          <t>BRADESCO LEASING S.A. - ARRENDAMENTO MERCANTIL</t>
         </is>
       </c>
       <c r="D19" s="11" t="inlineStr">
         <is>
-          <t>United States/Canada</t>
+          <t>Latin America</t>
         </is>
       </c>
       <c r="E19" s="11" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="F19" s="11" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A1</t>
         </is>
       </c>
       <c r="G19" s="11" t="inlineStr">
@@ -14233,13 +14233,13 @@
       </c>
       <c r="H19" s="11" t="inlineStr">
         <is>
-          <t>Tier 1 — hand-deepen ASAP</t>
+          <t>Tier 2 — verify primary docs first</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="12" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B20" s="14" t="inlineStr">
         <is>
@@ -14279,31 +14279,31 @@
     </row>
     <row r="21">
       <c r="A21" s="9" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t>KRX:028260</t>
+          <t>APTOF</t>
         </is>
       </c>
       <c r="C21" s="11" t="inlineStr">
         <is>
-          <t>Samsung C&amp;T</t>
+          <t>Aptose Biosciences Inc.</t>
         </is>
       </c>
       <c r="D21" s="11" t="inlineStr">
         <is>
-          <t>Korea</t>
+          <t>United States/Canada</t>
         </is>
       </c>
       <c r="E21" s="11" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="F21" s="11" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>K3</t>
         </is>
       </c>
       <c r="G21" s="11" t="inlineStr">
@@ -14319,31 +14319,31 @@
     </row>
     <row r="22">
       <c r="A22" s="12" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B22" s="14" t="inlineStr">
         <is>
-          <t>LSE:AML</t>
+          <t>KRX:028260</t>
         </is>
       </c>
       <c r="C22" s="14" t="inlineStr">
         <is>
-          <t>Aston Martin Lagonda</t>
+          <t>Samsung C&amp;T</t>
         </is>
       </c>
       <c r="D22" s="14" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Korea</t>
         </is>
       </c>
       <c r="E22" s="14" t="inlineStr">
         <is>
-          <t>0.70</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="F22" s="14" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>H</t>
         </is>
       </c>
       <c r="G22" s="14" t="inlineStr">
@@ -14353,37 +14353,37 @@
       </c>
       <c r="H22" s="14" t="inlineStr">
         <is>
-          <t>Tier 2 — verify primary docs first</t>
+          <t>Tier 1 — hand-deepen ASAP</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="9" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B23" s="11" t="inlineStr">
         <is>
-          <t>APTOF</t>
+          <t>LSE:AML</t>
         </is>
       </c>
       <c r="C23" s="11" t="inlineStr">
         <is>
-          <t>Aptose Biosciences Inc.</t>
+          <t>Aston Martin Lagonda</t>
         </is>
       </c>
       <c r="D23" s="11" t="inlineStr">
         <is>
-          <t>United States/Canada</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="E23" s="11" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="F23" s="11" t="inlineStr">
         <is>
-          <t>K3</t>
+          <t>A1</t>
         </is>
       </c>
       <c r="G23" s="11" t="inlineStr">
@@ -14393,13 +14393,13 @@
       </c>
       <c r="H23" s="11" t="inlineStr">
         <is>
-          <t>Tier 1 — hand-deepen ASAP</t>
+          <t>Tier 2 — verify primary docs first</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="12" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B24" s="14" t="inlineStr">
         <is>

--- a/output/cyclepapa_risk_reward_workbook.xlsx
+++ b/output/cyclepapa_risk_reward_workbook.xlsx
@@ -709,7 +709,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L27"/>
+  <dimension ref="A1:L71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -875,12 +875,12 @@
     <row r="7">
       <c r="A7" s="12" t="inlineStr">
         <is>
-          <t>Valaris Ltd</t>
+          <t>DIEBOLD NIXDORF, Inc</t>
         </is>
       </c>
       <c r="B7" s="14" t="inlineStr">
         <is>
-          <t>VAL</t>
+          <t>DBD</t>
         </is>
       </c>
       <c r="C7" s="14" t="inlineStr">
@@ -890,7 +890,7 @@
       </c>
       <c r="D7" s="14" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>August 12, 2023</t>
         </is>
       </c>
       <c r="E7" s="14" t="inlineStr">
@@ -930,19 +930,19 @@
       </c>
       <c r="L7" s="14" t="inlineStr">
         <is>
-          <t>filer emerged 2021 (~61mo ago) — overhang likely cleared; low le</t>
+          <t>filer emerged August 12, 2023 (~35mo ago) — overhang likely clea</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="9" t="inlineStr">
         <is>
-          <t>CBL &amp; ASSOCIATES PROPERTIES IN</t>
+          <t>Valaris Ltd</t>
         </is>
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>CBL</t>
+          <t>VAL</t>
         </is>
       </c>
       <c r="C8" s="11" t="inlineStr">
@@ -952,7 +952,7 @@
       </c>
       <c r="D8" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="E8" s="11" t="inlineStr">
@@ -992,24 +992,24 @@
       </c>
       <c r="L8" s="11" t="inlineStr">
         <is>
-          <t>net cash balance sheet; EBIT/EV 2% (neutral (0-20%))</t>
+          <t>filer emerged 2021 (~61mo ago) — overhang likely cleared; low le</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="12" t="inlineStr">
         <is>
-          <t>California Resources Corp</t>
+          <t>CBL &amp; ASSOCIATES PROPERTIES IN</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>CRC</t>
+          <t>CBL</t>
         </is>
       </c>
       <c r="C9" s="14" t="inlineStr">
         <is>
-          <t>~</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="D9" s="14" t="inlineStr">
@@ -1054,29 +1054,29 @@
       </c>
       <c r="L9" s="14" t="inlineStr">
         <is>
-          <t>low leverage (ND/EBIT 2.3×); EBIT/EV 13% (neutral (0-20%))</t>
+          <t>net cash balance sheet; EBIT/EV 2% (neutral (0-20%))</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="9" t="inlineStr">
         <is>
-          <t>RMR GROUP INC.</t>
+          <t>SANDRIDGE ENERGY INC</t>
         </is>
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>RMR</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>~</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="D10" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>October 4, 2016</t>
         </is>
       </c>
       <c r="E10" s="11" t="inlineStr">
@@ -1116,29 +1116,29 @@
       </c>
       <c r="L10" s="11" t="inlineStr">
         <is>
-          <t>net cash balance sheet; positive EBIT</t>
+          <t>filer emerged October 4, 2016 (~118mo ago) — overhang likely cle</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="12" t="inlineStr">
         <is>
-          <t>APA Corp</t>
+          <t>ARMSTRONG WORLD INDUSTRIES INC</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
         <is>
-          <t>APA</t>
+          <t>AWI</t>
         </is>
       </c>
       <c r="C11" s="14" t="inlineStr">
         <is>
-          <t>~</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="D11" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2006</t>
         </is>
       </c>
       <c r="E11" s="14" t="inlineStr">
@@ -1178,19 +1178,19 @@
       </c>
       <c r="L11" s="14" t="inlineStr">
         <is>
-          <t>low leverage (ND/EBIT 2.7×); EBIT/EV 25% (PRIORITY (&gt;20%))</t>
+          <t>filer emerged 2006 (~241mo ago) — overhang likely cleared; low l</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="9" t="inlineStr">
         <is>
-          <t>WW INTERNATIONAL, INC.</t>
+          <t>TIDEWATER INC</t>
         </is>
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>WW</t>
+          <t>TDW</t>
         </is>
       </c>
       <c r="C12" s="11" t="inlineStr">
@@ -1200,59 +1200,59 @@
       </c>
       <c r="D12" s="11" t="inlineStr">
         <is>
-          <t>March 31, 2026</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="E12" s="11" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="F12" s="11" t="inlineStr">
         <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="G12" s="11" t="inlineStr">
+        <is>
           <t>●</t>
         </is>
       </c>
-      <c r="G12" s="11" t="inlineStr">
+      <c r="H12" s="11" t="inlineStr">
         <is>
           <t>·</t>
         </is>
       </c>
-      <c r="H12" s="11" t="inlineStr">
+      <c r="I12" s="11" t="inlineStr">
         <is>
           <t>·</t>
         </is>
       </c>
-      <c r="I12" s="11" t="inlineStr">
-        <is>
-          <t>·</t>
-        </is>
-      </c>
       <c r="J12" s="11" t="inlineStr">
         <is>
-          <t>·</t>
+          <t>●</t>
         </is>
       </c>
       <c r="K12" s="11" t="inlineStr">
         <is>
-          <t>forced-creditor overhang</t>
+          <t>—</t>
         </is>
       </c>
       <c r="L12" s="11" t="inlineStr">
         <is>
-          <t>filer emerged March 31, 2026 (~4mo ago) — live forced-seller ove</t>
+          <t>filer emerged 2017 (~109mo ago) — overhang likely cleared; low l</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="12" t="inlineStr">
         <is>
-          <t>WOLFSPEED, INC.</t>
+          <t>STIFEL FINANCIAL CORP</t>
         </is>
       </c>
       <c r="B13" s="14" t="inlineStr">
         <is>
-          <t>WOLF</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="C13" s="14" t="inlineStr">
@@ -1262,59 +1262,59 @@
       </c>
       <c r="D13" s="14" t="inlineStr">
         <is>
-          <t>January 29, 2026</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E13" s="14" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="F13" s="14" t="inlineStr">
         <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="G13" s="14" t="inlineStr">
+        <is>
           <t>●</t>
         </is>
       </c>
-      <c r="G13" s="14" t="inlineStr">
+      <c r="H13" s="14" t="inlineStr">
         <is>
           <t>·</t>
         </is>
       </c>
-      <c r="H13" s="14" t="inlineStr">
+      <c r="I13" s="14" t="inlineStr">
         <is>
           <t>·</t>
         </is>
       </c>
-      <c r="I13" s="14" t="inlineStr">
-        <is>
-          <t>·</t>
-        </is>
-      </c>
       <c r="J13" s="14" t="inlineStr">
         <is>
-          <t>·</t>
+          <t>●</t>
         </is>
       </c>
       <c r="K13" s="14" t="inlineStr">
         <is>
-          <t>forced-creditor overhang</t>
+          <t>—</t>
         </is>
       </c>
       <c r="L13" s="14" t="inlineStr">
         <is>
-          <t>filer emerged January 29, 2026 (~6mo ago) — live forced-seller o</t>
+          <t>net cash balance sheet; EBIT/EV 2% (neutral (0-20%))</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="9" t="inlineStr">
         <is>
-          <t>Nine Energy Service, Inc.</t>
+          <t>ITRON, INC.</t>
         </is>
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>NINE</t>
+          <t>ITRI</t>
         </is>
       </c>
       <c r="C14" s="11" t="inlineStr">
@@ -1329,7 +1329,7 @@
       </c>
       <c r="E14" s="11" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="F14" s="11" t="inlineStr">
@@ -1339,19 +1339,19 @@
       </c>
       <c r="G14" s="11" t="inlineStr">
         <is>
+          <t>●</t>
+        </is>
+      </c>
+      <c r="H14" s="11" t="inlineStr">
+        <is>
           <t>·</t>
         </is>
       </c>
-      <c r="H14" s="11" t="inlineStr">
+      <c r="I14" s="11" t="inlineStr">
         <is>
           <t>·</t>
         </is>
       </c>
-      <c r="I14" s="11" t="inlineStr">
-        <is>
-          <t>·</t>
-        </is>
-      </c>
       <c r="J14" s="11" t="inlineStr">
         <is>
           <t>●</t>
@@ -1364,19 +1364,19 @@
       </c>
       <c r="L14" s="11" t="inlineStr">
         <is>
-          <t>EBIT/EV 0% (neutral (0-20%))</t>
+          <t>low leverage (ND/EBIT 0.7×); EBIT/EV 7% (neutral (0-20%))</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="12" t="inlineStr">
         <is>
-          <t>Red Rock Resorts, Inc.</t>
+          <t>PAR PACIFIC HOLDINGS, INC.</t>
         </is>
       </c>
       <c r="B15" s="14" t="inlineStr">
         <is>
-          <t>RRR</t>
+          <t>PARR</t>
         </is>
       </c>
       <c r="C15" s="14" t="inlineStr">
@@ -1386,12 +1386,12 @@
       </c>
       <c r="D15" s="14" t="inlineStr">
         <is>
-          <t>2011</t>
+          <t>August 31, 2012</t>
         </is>
       </c>
       <c r="E15" s="14" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="F15" s="14" t="inlineStr">
@@ -1401,19 +1401,19 @@
       </c>
       <c r="G15" s="14" t="inlineStr">
         <is>
+          <t>●</t>
+        </is>
+      </c>
+      <c r="H15" s="14" t="inlineStr">
+        <is>
           <t>·</t>
         </is>
       </c>
-      <c r="H15" s="14" t="inlineStr">
+      <c r="I15" s="14" t="inlineStr">
         <is>
           <t>·</t>
         </is>
       </c>
-      <c r="I15" s="14" t="inlineStr">
-        <is>
-          <t>·</t>
-        </is>
-      </c>
       <c r="J15" s="14" t="inlineStr">
         <is>
           <t>●</t>
@@ -1426,19 +1426,19 @@
       </c>
       <c r="L15" s="14" t="inlineStr">
         <is>
-          <t>filer emerged 2011 (~181mo ago) — overhang likely cleared; posit</t>
+          <t>filer emerged August 31, 2012 (~167mo ago) — overhang likely cle</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="9" t="inlineStr">
         <is>
-          <t>SEADRILL Ltd</t>
+          <t>VISTEON CORP</t>
         </is>
       </c>
       <c r="B16" s="11" t="inlineStr">
         <is>
-          <t>SDRL</t>
+          <t>VC</t>
         </is>
       </c>
       <c r="C16" s="11" t="inlineStr">
@@ -1453,7 +1453,7 @@
       </c>
       <c r="E16" s="11" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="F16" s="11" t="inlineStr">
@@ -1463,19 +1463,19 @@
       </c>
       <c r="G16" s="11" t="inlineStr">
         <is>
+          <t>●</t>
+        </is>
+      </c>
+      <c r="H16" s="11" t="inlineStr">
+        <is>
           <t>·</t>
         </is>
       </c>
-      <c r="H16" s="11" t="inlineStr">
+      <c r="I16" s="11" t="inlineStr">
         <is>
           <t>·</t>
         </is>
       </c>
-      <c r="I16" s="11" t="inlineStr">
-        <is>
-          <t>·</t>
-        </is>
-      </c>
       <c r="J16" s="11" t="inlineStr">
         <is>
           <t>●</t>
@@ -1488,19 +1488,19 @@
       </c>
       <c r="L16" s="11" t="inlineStr">
         <is>
-          <t>EBIT/EV 2% (neutral (0-20%))</t>
+          <t>net cash balance sheet; EBIT/EV 1% (neutral (0-20%))</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="12" t="inlineStr">
         <is>
-          <t>Phoenix Energy One, LLC</t>
+          <t>Spok Holdings, Inc</t>
         </is>
       </c>
       <c r="B17" s="14" t="inlineStr">
         <is>
-          <t>PHXE-P</t>
+          <t>SPOK</t>
         </is>
       </c>
       <c r="C17" s="14" t="inlineStr">
@@ -1510,12 +1510,12 @@
       </c>
       <c r="D17" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="E17" s="14" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="F17" s="14" t="inlineStr">
@@ -1525,19 +1525,19 @@
       </c>
       <c r="G17" s="14" t="inlineStr">
         <is>
+          <t>●</t>
+        </is>
+      </c>
+      <c r="H17" s="14" t="inlineStr">
+        <is>
           <t>·</t>
         </is>
       </c>
-      <c r="H17" s="14" t="inlineStr">
+      <c r="I17" s="14" t="inlineStr">
         <is>
           <t>·</t>
         </is>
       </c>
-      <c r="I17" s="14" t="inlineStr">
-        <is>
-          <t>·</t>
-        </is>
-      </c>
       <c r="J17" s="14" t="inlineStr">
         <is>
           <t>●</t>
@@ -1550,19 +1550,19 @@
       </c>
       <c r="L17" s="14" t="inlineStr">
         <is>
-          <t>EBIT/EV 4% (neutral (0-20%))</t>
+          <t>filer emerged 2002 (~289mo ago) — overhang likely cleared; net c</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="9" t="inlineStr">
         <is>
-          <t>Noble Corp plc</t>
+          <t>HOULIHAN LOKEY, INC.</t>
         </is>
       </c>
       <c r="B18" s="11" t="inlineStr">
         <is>
-          <t>NE</t>
+          <t>HLI</t>
         </is>
       </c>
       <c r="C18" s="11" t="inlineStr">
@@ -1577,7 +1577,7 @@
       </c>
       <c r="E18" s="11" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="F18" s="11" t="inlineStr">
@@ -1587,19 +1587,19 @@
       </c>
       <c r="G18" s="11" t="inlineStr">
         <is>
+          <t>●</t>
+        </is>
+      </c>
+      <c r="H18" s="11" t="inlineStr">
+        <is>
           <t>·</t>
         </is>
       </c>
-      <c r="H18" s="11" t="inlineStr">
+      <c r="I18" s="11" t="inlineStr">
         <is>
           <t>·</t>
         </is>
       </c>
-      <c r="I18" s="11" t="inlineStr">
-        <is>
-          <t>·</t>
-        </is>
-      </c>
       <c r="J18" s="11" t="inlineStr">
         <is>
           <t>●</t>
@@ -1612,19 +1612,19 @@
       </c>
       <c r="L18" s="11" t="inlineStr">
         <is>
-          <t>EBIT/EV 5% (neutral (0-20%))</t>
+          <t>net cash balance sheet; positive EBIT</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="12" t="inlineStr">
         <is>
-          <t>NEXSTAR MEDIA GROUP, INC.</t>
+          <t>Victoria's Secret &amp; Co.</t>
         </is>
       </c>
       <c r="B19" s="14" t="inlineStr">
         <is>
-          <t>NXST</t>
+          <t>VSCO</t>
         </is>
       </c>
       <c r="C19" s="14" t="inlineStr">
@@ -1634,12 +1634,12 @@
       </c>
       <c r="D19" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="E19" s="14" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="F19" s="14" t="inlineStr">
@@ -1649,19 +1649,19 @@
       </c>
       <c r="G19" s="14" t="inlineStr">
         <is>
+          <t>●</t>
+        </is>
+      </c>
+      <c r="H19" s="14" t="inlineStr">
+        <is>
           <t>·</t>
         </is>
       </c>
-      <c r="H19" s="14" t="inlineStr">
+      <c r="I19" s="14" t="inlineStr">
         <is>
           <t>·</t>
         </is>
       </c>
-      <c r="I19" s="14" t="inlineStr">
-        <is>
-          <t>·</t>
-        </is>
-      </c>
       <c r="J19" s="14" t="inlineStr">
         <is>
           <t>●</t>
@@ -1674,56 +1674,56 @@
       </c>
       <c r="L19" s="14" t="inlineStr">
         <is>
-          <t>EBIT/EV 6% (neutral (0-20%))</t>
+          <t>filer emerged 2019 (~85mo ago) — overhang likely cleared; low le</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="9" t="inlineStr">
         <is>
-          <t>Capstone Energy Plus, Inc.</t>
+          <t>Diversified Energy Co</t>
         </is>
       </c>
       <c r="B20" s="11" t="inlineStr">
         <is>
-          <t>CGEH</t>
+          <t>DEC</t>
         </is>
       </c>
       <c r="C20" s="11" t="inlineStr">
         <is>
-          <t>~</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="D20" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>July 4, 2025</t>
         </is>
       </c>
       <c r="E20" s="11" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="F20" s="11" t="inlineStr">
         <is>
+          <t>●</t>
+        </is>
+      </c>
+      <c r="G20" s="11" t="inlineStr">
+        <is>
           <t>·</t>
         </is>
       </c>
-      <c r="G20" s="11" t="inlineStr">
+      <c r="H20" s="11" t="inlineStr">
         <is>
           <t>·</t>
         </is>
       </c>
-      <c r="H20" s="11" t="inlineStr">
+      <c r="I20" s="11" t="inlineStr">
         <is>
           <t>·</t>
         </is>
       </c>
-      <c r="I20" s="11" t="inlineStr">
-        <is>
-          <t>·</t>
-        </is>
-      </c>
       <c r="J20" s="11" t="inlineStr">
         <is>
           <t>●</t>
@@ -1731,24 +1731,24 @@
       </c>
       <c r="K20" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>forced-creditor overhang</t>
         </is>
       </c>
       <c r="L20" s="11" t="inlineStr">
         <is>
-          <t>EBIT/EV 1% (neutral (0-20%))</t>
+          <t>filer emerged July 4, 2025 (~13mo ago) — live forced-seller over</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="12" t="inlineStr">
         <is>
-          <t>GoHealth, Inc.</t>
+          <t>Sinclair, Inc.</t>
         </is>
       </c>
       <c r="B21" s="14" t="inlineStr">
         <is>
-          <t>GOCO</t>
+          <t>SBGI</t>
         </is>
       </c>
       <c r="C21" s="14" t="inlineStr">
@@ -1763,7 +1763,7 @@
       </c>
       <c r="E21" s="14" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="F21" s="14" t="inlineStr">
@@ -1773,86 +1773,2618 @@
       </c>
       <c r="G21" s="14" t="inlineStr">
         <is>
+          <t>●</t>
+        </is>
+      </c>
+      <c r="H21" s="14" t="inlineStr">
+        <is>
           <t>·</t>
         </is>
       </c>
-      <c r="H21" s="14" t="inlineStr">
+      <c r="I21" s="14" t="inlineStr">
         <is>
           <t>·</t>
         </is>
       </c>
-      <c r="I21" s="14" t="inlineStr">
+      <c r="J21" s="14" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
+      <c r="K21" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L21" s="14" t="inlineStr">
+        <is>
+          <t>net cash balance sheet; positive EBIT</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="9" t="inlineStr">
+        <is>
+          <t>Venture Global, Inc.</t>
+        </is>
+      </c>
+      <c r="B22" s="11" t="inlineStr">
+        <is>
+          <t>VG</t>
+        </is>
+      </c>
+      <c r="C22" s="11" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="D22" s="11" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E22" s="11" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="F22" s="11" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
+      <c r="G22" s="11" t="inlineStr">
         <is>
           <t>·</t>
         </is>
       </c>
-      <c r="J21" s="14" t="inlineStr">
+      <c r="H22" s="11" t="inlineStr">
         <is>
           <t>·</t>
         </is>
       </c>
-      <c r="K21" s="14" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L21" s="14" t="inlineStr"/>
-    </row>
-    <row r="22"/>
-    <row r="23"/>
+      <c r="I22" s="11" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="J22" s="11" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
+      <c r="K22" s="11" t="inlineStr">
+        <is>
+          <t>forced-creditor overhang</t>
+        </is>
+      </c>
+      <c r="L22" s="11" t="inlineStr">
+        <is>
+          <t>filer emerged 2025 (~13mo ago) — live forced-seller overhang; po</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="12" t="inlineStr">
+        <is>
+          <t>California Resources Corp</t>
+        </is>
+      </c>
+      <c r="B23" s="14" t="inlineStr">
+        <is>
+          <t>CRC</t>
+        </is>
+      </c>
+      <c r="C23" s="14" t="inlineStr">
+        <is>
+          <t>~</t>
+        </is>
+      </c>
+      <c r="D23" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E23" s="14" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="F23" s="14" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="G23" s="14" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
+      <c r="H23" s="14" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="I23" s="14" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="J23" s="14" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
+      <c r="K23" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L23" s="14" t="inlineStr">
+        <is>
+          <t>low leverage (ND/EBIT 2.3×); EBIT/EV 13% (neutral (0-20%))</t>
+        </is>
+      </c>
+    </row>
     <row r="24">
-      <c r="A24" s="6" t="inlineStr">
-        <is>
-          <t>Set aside — filer's own emergence unconfirmed (verify; not scored, not dropped)</t>
+      <c r="A24" s="9" t="inlineStr">
+        <is>
+          <t>INFINITY NATURAL RESOURCES, IN</t>
+        </is>
+      </c>
+      <c r="B24" s="11" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="C24" s="11" t="inlineStr">
+        <is>
+          <t>~</t>
+        </is>
+      </c>
+      <c r="D24" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E24" s="11" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="F24" s="11" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="G24" s="11" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
+      <c r="H24" s="11" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="I24" s="11" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="J24" s="11" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
+      <c r="K24" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L24" s="11" t="inlineStr">
+        <is>
+          <t>low leverage (ND/EBIT 0.7×); positive EBIT</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="8" t="inlineStr">
-        <is>
-          <t>Name</t>
-        </is>
-      </c>
-      <c r="B25" s="8" t="inlineStr">
-        <is>
-          <t>Ticker</t>
-        </is>
-      </c>
-      <c r="C25" s="8" t="inlineStr">
-        <is>
-          <t>Filing context</t>
+      <c r="A25" s="12" t="inlineStr">
+        <is>
+          <t>Jefferies Financial Group Inc.</t>
+        </is>
+      </c>
+      <c r="B25" s="14" t="inlineStr">
+        <is>
+          <t>JEF</t>
+        </is>
+      </c>
+      <c r="C25" s="14" t="inlineStr">
+        <is>
+          <t>~</t>
+        </is>
+      </c>
+      <c r="D25" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E25" s="14" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="F25" s="14" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="G25" s="14" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
+      <c r="H25" s="14" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
+      <c r="I25" s="14" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="J25" s="14" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K25" s="14" t="inlineStr">
+        <is>
+          <t>excess-emergence-cash</t>
+        </is>
+      </c>
+      <c r="L25" s="14" t="inlineStr">
+        <is>
+          <t>net cash balance sheet; net cash = 107% of mkt cap (net-debt bur</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="9" t="inlineStr">
         <is>
-          <t>EASTMAN CHEMICAL CO</t>
+          <t>GULFPORT ENERGY CORP</t>
         </is>
       </c>
       <c r="B26" s="11" t="inlineStr">
         <is>
-          <t>EMN</t>
+          <t>GPOR</t>
         </is>
       </c>
       <c r="C26" s="11" t="inlineStr">
         <is>
-          <t>(bankruptcy reference is a non-filer possessive)</t>
+          <t>~</t>
+        </is>
+      </c>
+      <c r="D26" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E26" s="11" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="F26" s="11" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="G26" s="11" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
+      <c r="H26" s="11" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="I26" s="11" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="J26" s="11" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
+      <c r="K26" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L26" s="11" t="inlineStr">
+        <is>
+          <t>low leverage (ND/EBIT 1.3×); EBIT/EV 15% (neutral (0-20%))</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="12" t="inlineStr">
         <is>
+          <t>AGCO CORP /DE</t>
+        </is>
+      </c>
+      <c r="B27" s="14" t="inlineStr">
+        <is>
+          <t>AGCO</t>
+        </is>
+      </c>
+      <c r="C27" s="14" t="inlineStr">
+        <is>
+          <t>~</t>
+        </is>
+      </c>
+      <c r="D27" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E27" s="14" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="F27" s="14" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="G27" s="14" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
+      <c r="H27" s="14" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="I27" s="14" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="J27" s="14" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
+      <c r="K27" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L27" s="14" t="inlineStr">
+        <is>
+          <t>low leverage (ND/EBIT 3.0×); EBIT/EV 4% (neutral (0-20%))</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="9" t="inlineStr">
+        <is>
+          <t>Bristow Group Inc.</t>
+        </is>
+      </c>
+      <c r="B28" s="11" t="inlineStr">
+        <is>
+          <t>VTOL</t>
+        </is>
+      </c>
+      <c r="C28" s="11" t="inlineStr">
+        <is>
+          <t>~</t>
+        </is>
+      </c>
+      <c r="D28" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E28" s="11" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="F28" s="11" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="G28" s="11" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
+      <c r="H28" s="11" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="I28" s="11" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="J28" s="11" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
+      <c r="K28" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L28" s="11" t="inlineStr">
+        <is>
+          <t>low leverage (ND/EBIT 2.7×); EBIT/EV 7% (neutral (0-20%))</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="12" t="inlineStr">
+        <is>
+          <t>RMR GROUP INC.</t>
+        </is>
+      </c>
+      <c r="B29" s="14" t="inlineStr">
+        <is>
+          <t>RMR</t>
+        </is>
+      </c>
+      <c r="C29" s="14" t="inlineStr">
+        <is>
+          <t>~</t>
+        </is>
+      </c>
+      <c r="D29" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E29" s="14" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="F29" s="14" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="G29" s="14" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
+      <c r="H29" s="14" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="I29" s="14" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="J29" s="14" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
+      <c r="K29" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L29" s="14" t="inlineStr">
+        <is>
+          <t>net cash balance sheet; positive EBIT</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="9" t="inlineStr">
+        <is>
+          <t>APA Corp</t>
+        </is>
+      </c>
+      <c r="B30" s="11" t="inlineStr">
+        <is>
+          <t>APA</t>
+        </is>
+      </c>
+      <c r="C30" s="11" t="inlineStr">
+        <is>
+          <t>~</t>
+        </is>
+      </c>
+      <c r="D30" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E30" s="11" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="F30" s="11" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="G30" s="11" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
+      <c r="H30" s="11" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="I30" s="11" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="J30" s="11" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
+      <c r="K30" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L30" s="11" t="inlineStr">
+        <is>
+          <t>low leverage (ND/EBIT 2.7×); EBIT/EV 25% (PRIORITY (&gt;20%))</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="12" t="inlineStr">
+        <is>
+          <t>WW INTERNATIONAL, INC.</t>
+        </is>
+      </c>
+      <c r="B31" s="14" t="inlineStr">
+        <is>
+          <t>WW</t>
+        </is>
+      </c>
+      <c r="C31" s="14" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="D31" s="14" t="inlineStr">
+        <is>
+          <t>December 31, 2025</t>
+        </is>
+      </c>
+      <c r="E31" s="14" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="F31" s="14" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
+      <c r="G31" s="14" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="H31" s="14" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="I31" s="14" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="J31" s="14" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K31" s="14" t="inlineStr">
+        <is>
+          <t>forced-creditor overhang</t>
+        </is>
+      </c>
+      <c r="L31" s="14" t="inlineStr">
+        <is>
+          <t>filer emerged December 31, 2025 (~7mo ago) — live forced-seller</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="9" t="inlineStr">
+        <is>
+          <t>WOLFSPEED, INC.</t>
+        </is>
+      </c>
+      <c r="B32" s="11" t="inlineStr">
+        <is>
+          <t>WOLF</t>
+        </is>
+      </c>
+      <c r="C32" s="11" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="D32" s="11" t="inlineStr">
+        <is>
+          <t>January 29, 2026</t>
+        </is>
+      </c>
+      <c r="E32" s="11" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="F32" s="11" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
+      <c r="G32" s="11" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="H32" s="11" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="I32" s="11" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="J32" s="11" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K32" s="11" t="inlineStr">
+        <is>
+          <t>forced-creditor overhang</t>
+        </is>
+      </c>
+      <c r="L32" s="11" t="inlineStr">
+        <is>
+          <t>filer emerged January 29, 2026 (~6mo ago) — live forced-seller o</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="12" t="inlineStr">
+        <is>
+          <t>GOLAR LNG LTD</t>
+        </is>
+      </c>
+      <c r="B33" s="14" t="inlineStr">
+        <is>
+          <t>GLNG</t>
+        </is>
+      </c>
+      <c r="C33" s="14" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="D33" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E33" s="14" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="F33" s="14" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="G33" s="14" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="H33" s="14" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="I33" s="14" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="J33" s="14" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
+      <c r="K33" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L33" s="14" t="inlineStr">
+        <is>
+          <t>EBIT/EV 1% (neutral (0-20%))</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="9" t="inlineStr">
+        <is>
+          <t>Nine Energy Service, Inc.</t>
+        </is>
+      </c>
+      <c r="B34" s="11" t="inlineStr">
+        <is>
+          <t>NINE</t>
+        </is>
+      </c>
+      <c r="C34" s="11" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="D34" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E34" s="11" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="F34" s="11" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="G34" s="11" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="H34" s="11" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="I34" s="11" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="J34" s="11" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
+      <c r="K34" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L34" s="11" t="inlineStr">
+        <is>
+          <t>EBIT/EV 0% (neutral (0-20%))</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="12" t="inlineStr">
+        <is>
+          <t>Red Rock Resorts, Inc.</t>
+        </is>
+      </c>
+      <c r="B35" s="14" t="inlineStr">
+        <is>
+          <t>RRR</t>
+        </is>
+      </c>
+      <c r="C35" s="14" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="D35" s="14" t="inlineStr">
+        <is>
+          <t>2011</t>
+        </is>
+      </c>
+      <c r="E35" s="14" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="F35" s="14" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="G35" s="14" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="H35" s="14" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="I35" s="14" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="J35" s="14" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
+      <c r="K35" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L35" s="14" t="inlineStr">
+        <is>
+          <t>filer emerged 2011 (~181mo ago) — overhang likely cleared; posit</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="9" t="inlineStr">
+        <is>
+          <t>SEADRILL Ltd</t>
+        </is>
+      </c>
+      <c r="B36" s="11" t="inlineStr">
+        <is>
+          <t>SDRL</t>
+        </is>
+      </c>
+      <c r="C36" s="11" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="D36" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E36" s="11" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="F36" s="11" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="G36" s="11" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="H36" s="11" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="I36" s="11" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="J36" s="11" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
+      <c r="K36" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L36" s="11" t="inlineStr">
+        <is>
+          <t>EBIT/EV 2% (neutral (0-20%))</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="12" t="inlineStr">
+        <is>
+          <t>Phoenix Energy One, LLC</t>
+        </is>
+      </c>
+      <c r="B37" s="14" t="inlineStr">
+        <is>
+          <t>PHXE-P</t>
+        </is>
+      </c>
+      <c r="C37" s="14" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="D37" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E37" s="14" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="F37" s="14" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="G37" s="14" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="H37" s="14" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="I37" s="14" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="J37" s="14" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
+      <c r="K37" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L37" s="14" t="inlineStr">
+        <is>
+          <t>EBIT/EV 4% (neutral (0-20%))</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="9" t="inlineStr">
+        <is>
+          <t>Noble Corp plc</t>
+        </is>
+      </c>
+      <c r="B38" s="11" t="inlineStr">
+        <is>
+          <t>NE</t>
+        </is>
+      </c>
+      <c r="C38" s="11" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="D38" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E38" s="11" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="F38" s="11" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="G38" s="11" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="H38" s="11" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="I38" s="11" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="J38" s="11" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
+      <c r="K38" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L38" s="11" t="inlineStr">
+        <is>
+          <t>EBIT/EV 5% (neutral (0-20%))</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="12" t="inlineStr">
+        <is>
+          <t>CLEVELAND-CLIFFS INC.</t>
+        </is>
+      </c>
+      <c r="B39" s="14" t="inlineStr">
+        <is>
+          <t>CLF</t>
+        </is>
+      </c>
+      <c r="C39" s="14" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="D39" s="14" t="inlineStr">
+        <is>
+          <t>2042</t>
+        </is>
+      </c>
+      <c r="E39" s="14" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="F39" s="14" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
+      <c r="G39" s="14" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="H39" s="14" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="I39" s="14" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="J39" s="14" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K39" s="14" t="inlineStr">
+        <is>
+          <t>forced-creditor overhang</t>
+        </is>
+      </c>
+      <c r="L39" s="14" t="inlineStr">
+        <is>
+          <t>filer emerged 2042 (~-192mo ago) — live forced-seller overhang</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="9" t="inlineStr">
+        <is>
+          <t>Capstone Green Energy Holdings</t>
+        </is>
+      </c>
+      <c r="B40" s="11" t="inlineStr">
+        <is>
+          <t>CGEH</t>
+        </is>
+      </c>
+      <c r="C40" s="11" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="D40" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E40" s="11" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="F40" s="11" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="G40" s="11" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="H40" s="11" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="I40" s="11" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="J40" s="11" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
+      <c r="K40" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L40" s="11" t="inlineStr">
+        <is>
+          <t>EBIT/EV 1% (neutral (0-20%))</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="12" t="inlineStr">
+        <is>
+          <t>NEXSTAR MEDIA GROUP, INC.</t>
+        </is>
+      </c>
+      <c r="B41" s="14" t="inlineStr">
+        <is>
+          <t>NXST</t>
+        </is>
+      </c>
+      <c r="C41" s="14" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="D41" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E41" s="14" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="F41" s="14" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="G41" s="14" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="H41" s="14" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="I41" s="14" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="J41" s="14" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
+      <c r="K41" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L41" s="14" t="inlineStr">
+        <is>
+          <t>EBIT/EV 6% (neutral (0-20%))</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="9" t="inlineStr">
+        <is>
+          <t>TruBridge, Inc.</t>
+        </is>
+      </c>
+      <c r="B42" s="11" t="inlineStr">
+        <is>
+          <t>TBRG</t>
+        </is>
+      </c>
+      <c r="C42" s="11" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="D42" s="11" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="E42" s="11" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="F42" s="11" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="G42" s="11" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="H42" s="11" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="I42" s="11" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="J42" s="11" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
+      <c r="K42" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L42" s="11" t="inlineStr">
+        <is>
+          <t>filer emerged 2020 (~73mo ago) — overhang likely cleared; EBIT/E</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="12" t="inlineStr">
+        <is>
+          <t>Clean Energy Fuels Corp.</t>
+        </is>
+      </c>
+      <c r="B43" s="14" t="inlineStr">
+        <is>
+          <t>CLNE</t>
+        </is>
+      </c>
+      <c r="C43" s="14" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="D43" s="14" t="inlineStr">
+        <is>
+          <t>September 1, 2025</t>
+        </is>
+      </c>
+      <c r="E43" s="14" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="F43" s="14" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
+      <c r="G43" s="14" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="H43" s="14" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="I43" s="14" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="J43" s="14" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K43" s="14" t="inlineStr">
+        <is>
+          <t>forced-creditor overhang</t>
+        </is>
+      </c>
+      <c r="L43" s="14" t="inlineStr">
+        <is>
+          <t>filer emerged September 1, 2025 (~11mo ago) — live forced-seller</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="9" t="inlineStr">
+        <is>
+          <t>Smart Sand, Inc.</t>
+        </is>
+      </c>
+      <c r="B44" s="11" t="inlineStr">
+        <is>
+          <t>SND</t>
+        </is>
+      </c>
+      <c r="C44" s="11" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="D44" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E44" s="11" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="F44" s="11" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="G44" s="11" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
+      <c r="H44" s="11" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="I44" s="11" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="J44" s="11" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K44" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L44" s="11" t="inlineStr">
+        <is>
+          <t>net cash balance sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="12" t="inlineStr">
+        <is>
+          <t>Sila Realty Trust, Inc.</t>
+        </is>
+      </c>
+      <c r="B45" s="14" t="inlineStr">
+        <is>
+          <t>SILA</t>
+        </is>
+      </c>
+      <c r="C45" s="14" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="D45" s="14" t="inlineStr">
+        <is>
+          <t>February 16, 2024</t>
+        </is>
+      </c>
+      <c r="E45" s="14" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="F45" s="14" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="G45" s="14" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="H45" s="14" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="I45" s="14" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="J45" s="14" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
+      <c r="K45" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L45" s="14" t="inlineStr">
+        <is>
+          <t>filer emerged February 16, 2024 (~29mo ago) — overhang likely cl</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="9" t="inlineStr">
+        <is>
+          <t>CLOVER HEALTH INVESTMENTS, COR</t>
+        </is>
+      </c>
+      <c r="B46" s="11" t="inlineStr">
+        <is>
+          <t>CLOV</t>
+        </is>
+      </c>
+      <c r="C46" s="11" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="D46" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E46" s="11" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="F46" s="11" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="G46" s="11" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
+      <c r="H46" s="11" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="I46" s="11" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="J46" s="11" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K46" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L46" s="11" t="inlineStr">
+        <is>
+          <t>net cash balance sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="12" t="inlineStr">
+        <is>
+          <t>Sable Offshore Corp.</t>
+        </is>
+      </c>
+      <c r="B47" s="14" t="inlineStr">
+        <is>
+          <t>SOC</t>
+        </is>
+      </c>
+      <c r="C47" s="14" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="D47" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E47" s="14" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="F47" s="14" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="G47" s="14" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
+      <c r="H47" s="14" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="I47" s="14" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="J47" s="14" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K47" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L47" s="14" t="inlineStr">
+        <is>
+          <t>net cash balance sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="9" t="inlineStr">
+        <is>
+          <t>Ridgepost Capital, Inc.</t>
+        </is>
+      </c>
+      <c r="B48" s="11" t="inlineStr">
+        <is>
+          <t>RPC</t>
+        </is>
+      </c>
+      <c r="C48" s="11" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="D48" s="11" t="inlineStr">
+        <is>
+          <t>May 3, 2017</t>
+        </is>
+      </c>
+      <c r="E48" s="11" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="F48" s="11" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="G48" s="11" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="H48" s="11" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="I48" s="11" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="J48" s="11" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
+      <c r="K48" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L48" s="11" t="inlineStr">
+        <is>
+          <t>filer emerged May 3, 2017 (~111mo ago) — overhang likely cleared</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="12" t="inlineStr">
+        <is>
+          <t>FERRELLGAS PARTNERS L P</t>
+        </is>
+      </c>
+      <c r="B49" s="14" t="inlineStr">
+        <is>
+          <t>FGPR</t>
+        </is>
+      </c>
+      <c r="C49" s="14" t="inlineStr">
+        <is>
+          <t>~</t>
+        </is>
+      </c>
+      <c r="D49" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E49" s="14" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="F49" s="14" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="G49" s="14" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="H49" s="14" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="I49" s="14" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="J49" s="14" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
+      <c r="K49" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L49" s="14" t="inlineStr">
+        <is>
+          <t>EBIT/EV 3% (neutral (0-20%))</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="9" t="inlineStr">
+        <is>
+          <t>EchoStar CORP</t>
+        </is>
+      </c>
+      <c r="B50" s="11" t="inlineStr">
+        <is>
+          <t>SATS</t>
+        </is>
+      </c>
+      <c r="C50" s="11" t="inlineStr">
+        <is>
+          <t>~</t>
+        </is>
+      </c>
+      <c r="D50" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E50" s="11" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="F50" s="11" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="G50" s="11" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
+      <c r="H50" s="11" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="I50" s="11" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="J50" s="11" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K50" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L50" s="11" t="inlineStr">
+        <is>
+          <t>net cash balance sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="12" t="inlineStr">
+        <is>
+          <t>Fortune Brands Innovations, In</t>
+        </is>
+      </c>
+      <c r="B51" s="14" t="inlineStr">
+        <is>
+          <t>FBIN</t>
+        </is>
+      </c>
+      <c r="C51" s="14" t="inlineStr">
+        <is>
+          <t>~</t>
+        </is>
+      </c>
+      <c r="D51" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E51" s="14" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="F51" s="14" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="G51" s="14" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="H51" s="14" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="I51" s="14" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="J51" s="14" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
+      <c r="K51" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L51" s="14" t="inlineStr">
+        <is>
+          <t>EBIT/EV 5% (neutral (0-20%))</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="9" t="inlineStr">
+        <is>
+          <t>Beneficient</t>
+        </is>
+      </c>
+      <c r="B52" s="11" t="inlineStr">
+        <is>
+          <t>BENF</t>
+        </is>
+      </c>
+      <c r="C52" s="11" t="inlineStr">
+        <is>
+          <t>~</t>
+        </is>
+      </c>
+      <c r="D52" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E52" s="11" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="F52" s="11" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="G52" s="11" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
+      <c r="H52" s="11" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="I52" s="11" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="J52" s="11" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K52" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L52" s="11" t="inlineStr">
+        <is>
+          <t>net cash balance sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="12" t="inlineStr">
+        <is>
+          <t>Fifth Era Acquisition Corp I</t>
+        </is>
+      </c>
+      <c r="B53" s="14" t="inlineStr">
+        <is>
+          <t>FERA</t>
+        </is>
+      </c>
+      <c r="C53" s="14" t="inlineStr">
+        <is>
+          <t>~</t>
+        </is>
+      </c>
+      <c r="D53" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E53" s="14" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="F53" s="14" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="G53" s="14" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
+      <c r="H53" s="14" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="I53" s="14" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="J53" s="14" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K53" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L53" s="14" t="inlineStr">
+        <is>
+          <t>net cash balance sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="9" t="inlineStr">
+        <is>
+          <t>Xanadu Quantum Technologies Lt</t>
+        </is>
+      </c>
+      <c r="B54" s="11" t="inlineStr">
+        <is>
+          <t>XNDU</t>
+        </is>
+      </c>
+      <c r="C54" s="11" t="inlineStr">
+        <is>
+          <t>~</t>
+        </is>
+      </c>
+      <c r="D54" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E54" s="11" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="F54" s="11" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="G54" s="11" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
+      <c r="H54" s="11" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="I54" s="11" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="J54" s="11" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K54" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L54" s="11" t="inlineStr">
+        <is>
+          <t>net cash balance sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="12" t="inlineStr">
+        <is>
+          <t>Cinemark Holdings, Inc.</t>
+        </is>
+      </c>
+      <c r="B55" s="14" t="inlineStr">
+        <is>
+          <t>CNK</t>
+        </is>
+      </c>
+      <c r="C55" s="14" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="D55" s="14" t="inlineStr">
+        <is>
+          <t>August 7, 2023</t>
+        </is>
+      </c>
+      <c r="E55" s="14" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="F55" s="14" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="G55" s="14" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="H55" s="14" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="I55" s="14" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="J55" s="14" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K55" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L55" s="14" t="inlineStr">
+        <is>
+          <t>filer emerged August 7, 2023 (~35mo ago) — overhang likely clear</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="9" t="inlineStr">
+        <is>
+          <t>iHeartMedia, Inc.</t>
+        </is>
+      </c>
+      <c r="B56" s="11" t="inlineStr">
+        <is>
+          <t>IHRT</t>
+        </is>
+      </c>
+      <c r="C56" s="11" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="D56" s="11" t="inlineStr">
+        <is>
+          <t>May 1, 2019</t>
+        </is>
+      </c>
+      <c r="E56" s="11" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="F56" s="11" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="G56" s="11" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="H56" s="11" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="I56" s="11" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="J56" s="11" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K56" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L56" s="11" t="inlineStr">
+        <is>
+          <t>filer emerged May 1, 2019 (~87mo ago) — overhang likely cleared</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="12" t="inlineStr">
+        <is>
+          <t>Tronox Holdings plc</t>
+        </is>
+      </c>
+      <c r="B57" s="14" t="inlineStr">
+        <is>
+          <t>TROX</t>
+        </is>
+      </c>
+      <c r="C57" s="14" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="D57" s="14" t="inlineStr">
+        <is>
+          <t>November 30, 2010</t>
+        </is>
+      </c>
+      <c r="E57" s="14" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="F57" s="14" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="G57" s="14" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="H57" s="14" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="I57" s="14" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="J57" s="14" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K57" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L57" s="14" t="inlineStr">
+        <is>
+          <t>filer emerged November 30, 2010 (~188mo ago) — overhang likely c</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="9" t="inlineStr">
+        <is>
+          <t>GoHealth, Inc.</t>
+        </is>
+      </c>
+      <c r="B58" s="11" t="inlineStr">
+        <is>
+          <t>GOCO</t>
+        </is>
+      </c>
+      <c r="C58" s="11" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="D58" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E58" s="11" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="F58" s="11" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="G58" s="11" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="H58" s="11" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="I58" s="11" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="J58" s="11" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K58" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L58" s="11" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="12" t="inlineStr">
+        <is>
+          <t>Core Scientific, Inc./tx</t>
+        </is>
+      </c>
+      <c r="B59" s="14" t="inlineStr">
+        <is>
+          <t>CORZ</t>
+        </is>
+      </c>
+      <c r="C59" s="14" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="D59" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E59" s="14" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="F59" s="14" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="G59" s="14" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="H59" s="14" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="I59" s="14" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="J59" s="14" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K59" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L59" s="14" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="9" t="inlineStr">
+        <is>
+          <t>Atlanta Braves Holdings, Inc.</t>
+        </is>
+      </c>
+      <c r="B60" s="11" t="inlineStr">
+        <is>
+          <t>BATRA</t>
+        </is>
+      </c>
+      <c r="C60" s="11" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="D60" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E60" s="11" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="F60" s="11" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="G60" s="11" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="H60" s="11" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="I60" s="11" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="J60" s="11" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K60" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L60" s="11" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="12" t="inlineStr">
+        <is>
+          <t>AMPCO PITTSBURGH CORP</t>
+        </is>
+      </c>
+      <c r="B61" s="14" t="inlineStr">
+        <is>
+          <t>AP</t>
+        </is>
+      </c>
+      <c r="C61" s="14" t="inlineStr">
+        <is>
+          <t>~</t>
+        </is>
+      </c>
+      <c r="D61" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E61" s="14" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="F61" s="14" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="G61" s="14" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="H61" s="14" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="I61" s="14" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="J61" s="14" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K61" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L61" s="14" t="inlineStr"/>
+    </row>
+    <row r="62"/>
+    <row r="63"/>
+    <row r="64">
+      <c r="A64" s="6" t="inlineStr">
+        <is>
+          <t>Set aside — filer's own emergence unconfirmed (verify; not scored, not dropped)</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="8" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B65" s="8" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
+      <c r="C65" s="8" t="inlineStr">
+        <is>
+          <t>Filing context</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="9" t="inlineStr">
+        <is>
+          <t>OCTAVE SPECIALTY GROUP INC</t>
+        </is>
+      </c>
+      <c r="B66" s="11" t="inlineStr">
+        <is>
+          <t>OSG</t>
+        </is>
+      </c>
+      <c r="C66" s="11" t="inlineStr">
+        <is>
+          <t>(bankruptcy reference is a non-filer possessive)</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="12" t="inlineStr">
+        <is>
+          <t>EASTMAN CHEMICAL CO</t>
+        </is>
+      </c>
+      <c r="B67" s="14" t="inlineStr">
+        <is>
+          <t>EMN</t>
+        </is>
+      </c>
+      <c r="C67" s="14" t="inlineStr">
+        <is>
+          <t>(bankruptcy reference is a non-filer possessive)</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="9" t="inlineStr">
+        <is>
           <t>PG&amp;E Corp</t>
         </is>
       </c>
-      <c r="B27" s="14" t="inlineStr">
+      <c r="B68" s="11" t="inlineStr">
         <is>
           <t>PCG</t>
         </is>
       </c>
-      <c r="C27" s="14" t="inlineStr">
+      <c r="C68" s="11" t="inlineStr">
+        <is>
+          <t>(bankruptcy reference is a non-filer possessive)</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="12" t="inlineStr">
+        <is>
+          <t>National CineMedia, Inc.</t>
+        </is>
+      </c>
+      <c r="B69" s="14" t="inlineStr">
+        <is>
+          <t>NCMI</t>
+        </is>
+      </c>
+      <c r="C69" s="14" t="inlineStr">
+        <is>
+          <t>(bankruptcy reference is a non-filer possessive)</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="9" t="inlineStr">
+        <is>
+          <t>MODIV INDUSTRIAL, INC.</t>
+        </is>
+      </c>
+      <c r="B70" s="11" t="inlineStr">
+        <is>
+          <t>MDV</t>
+        </is>
+      </c>
+      <c r="C70" s="11" t="inlineStr">
+        <is>
+          <t>(bankruptcy reference is a non-filer possessive)</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="12" t="inlineStr">
+        <is>
+          <t>LibreMax Asset-Backed Income F</t>
+        </is>
+      </c>
+      <c r="B71" s="14" t="inlineStr"/>
+      <c r="C71" s="14" t="inlineStr">
         <is>
           <t>(bankruptcy reference is a non-filer possessive)</t>
         </is>

--- a/output/cyclepapa_risk_reward_workbook.xlsx
+++ b/output/cyclepapa_risk_reward_workbook.xlsx
@@ -4691,7 +4691,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F51"/>
+  <dimension ref="A1:F245"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -4699,7 +4699,7 @@
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="8" customWidth="1" min="4" max="4"/>
     <col width="8" customWidth="1" min="5" max="5"/>
-    <col width="52" customWidth="1" min="6" max="6"/>
+    <col width="50" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4759,12 +4759,12 @@
     <row r="6">
       <c r="A6" s="9" t="inlineStr">
         <is>
-          <t>APA Corp</t>
+          <t>FERRELLGAS PARTNERS L P</t>
         </is>
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>APA</t>
+          <t>FGPR</t>
         </is>
       </c>
       <c r="C6" s="11" t="inlineStr">
@@ -4784,29 +4784,29 @@
       </c>
       <c r="F6" s="11" t="inlineStr">
         <is>
-          <t>EBIT/EV 25% → PRIORITY (&gt;20%)</t>
+          <t>EBIT/EV 82% → PRIORITY (&gt;20%)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="12" t="inlineStr">
         <is>
-          <t>Noble Corp plc</t>
+          <t>APA Corp</t>
         </is>
       </c>
       <c r="B7" s="14" t="inlineStr">
         <is>
-          <t>NE</t>
+          <t>APA</t>
         </is>
       </c>
       <c r="C7" s="14" t="inlineStr">
         <is>
-          <t>neutral (0-20%)</t>
+          <t>PRIORITY (&gt;20%)</t>
         </is>
       </c>
       <c r="D7" s="14" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E7" s="14" t="inlineStr">
@@ -4816,19 +4816,19 @@
       </c>
       <c r="F7" s="14" t="inlineStr">
         <is>
-          <t>EBIT/EV 5% → neutral (0-20%); fresh-start</t>
+          <t>EBIT/EV 25% → PRIORITY (&gt;20%)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="9" t="inlineStr">
         <is>
-          <t>Valaris Ltd</t>
+          <t>DIEBOLD NIXDORF, Inc</t>
         </is>
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>VAL</t>
+          <t>DBD</t>
         </is>
       </c>
       <c r="C8" s="11" t="inlineStr">
@@ -4848,20 +4848,24 @@
       </c>
       <c r="F8" s="11" t="inlineStr">
         <is>
-          <t>EBIT/EV 7% → neutral (0-20%); fresh-start</t>
+          <t>EBIT/EV 4% → neutral (0-20%); fresh-start</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="12" t="inlineStr">
         <is>
-          <t>OFFICE PROPERTIES INCOME TRUST</t>
-        </is>
-      </c>
-      <c r="B9" s="14" t="inlineStr"/>
+          <t>Valaris Ltd</t>
+        </is>
+      </c>
+      <c r="B9" s="14" t="inlineStr">
+        <is>
+          <t>VAL</t>
+        </is>
+      </c>
       <c r="C9" s="14" t="inlineStr">
         <is>
-          <t>positive-EBIT</t>
+          <t>neutral (0-20%)</t>
         </is>
       </c>
       <c r="D9" s="14" t="inlineStr">
@@ -4876,24 +4880,24 @@
       </c>
       <c r="F9" s="14" t="inlineStr">
         <is>
-          <t>EBIT positive ($54M); EV/price n/a; fresh-start</t>
+          <t>EBIT/EV 7% → neutral (0-20%); fresh-start</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="9" t="inlineStr">
         <is>
-          <t>Red Rock Resorts, Inc.</t>
+          <t>CBL &amp; ASSOCIATES PROPERTIES INC</t>
         </is>
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>RRR</t>
+          <t>CBL</t>
         </is>
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>positive-EBIT</t>
+          <t>neutral (0-20%)</t>
         </is>
       </c>
       <c r="D10" s="11" t="inlineStr">
@@ -4908,19 +4912,19 @@
       </c>
       <c r="F10" s="11" t="inlineStr">
         <is>
-          <t>EBIT positive ($597M); EV/price n/a; fresh-start</t>
+          <t>EBIT/EV 2% → neutral (0-20%); fresh-start</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="12" t="inlineStr">
         <is>
-          <t>Cushman &amp; Wakefield Ltd.</t>
+          <t>CENTRUS ENERGY CORP</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
         <is>
-          <t>CWK</t>
+          <t>LEU</t>
         </is>
       </c>
       <c r="C11" s="14" t="inlineStr">
@@ -4930,7 +4934,7 @@
       </c>
       <c r="D11" s="14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E11" s="14" t="inlineStr">
@@ -4940,29 +4944,29 @@
       </c>
       <c r="F11" s="14" t="inlineStr">
         <is>
-          <t>EBIT/EV 6% → neutral (0-20%)</t>
+          <t>EBIT/EV 2% → neutral (0-20%); fresh-start</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="9" t="inlineStr">
         <is>
-          <t>FEDERATED HERMES, INC.</t>
+          <t>GOLAR LNG LTD</t>
         </is>
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>FHI</t>
+          <t>GLNG</t>
         </is>
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>positive-EBIT</t>
+          <t>neutral (0-20%)</t>
         </is>
       </c>
       <c r="D12" s="11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E12" s="11" t="inlineStr">
@@ -4972,19 +4976,19 @@
       </c>
       <c r="F12" s="11" t="inlineStr">
         <is>
-          <t>EBIT positive ($514M); EV/price n/a</t>
+          <t>EBIT/EV 1% → neutral (0-20%); fresh-start</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="12" t="inlineStr">
         <is>
-          <t>EASTMAN CHEMICAL CO</t>
+          <t>SANDRIDGE ENERGY INC</t>
         </is>
       </c>
       <c r="B13" s="14" t="inlineStr">
         <is>
-          <t>EMN</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="C13" s="14" t="inlineStr">
@@ -4994,7 +4998,7 @@
       </c>
       <c r="D13" s="14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E13" s="14" t="inlineStr">
@@ -5004,19 +5008,19 @@
       </c>
       <c r="F13" s="14" t="inlineStr">
         <is>
-          <t>EBIT/EV 10% → neutral (0-20%)</t>
+          <t>EBIT/EV 12% → neutral (0-20%); fresh-start</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="9" t="inlineStr">
         <is>
-          <t>WEYCO GROUP INC</t>
+          <t>Nine Energy Service, Inc.</t>
         </is>
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>WEYS</t>
+          <t>NINE</t>
         </is>
       </c>
       <c r="C14" s="11" t="inlineStr">
@@ -5026,7 +5030,7 @@
       </c>
       <c r="D14" s="11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E14" s="11" t="inlineStr">
@@ -5036,19 +5040,19 @@
       </c>
       <c r="F14" s="11" t="inlineStr">
         <is>
-          <t>EBIT/EV 8% → neutral (0-20%)</t>
+          <t>EBIT/EV 0% → neutral (0-20%); fresh-start</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="12" t="inlineStr">
         <is>
-          <t>Compass Diversified Holdings</t>
+          <t>California Resources Corp</t>
         </is>
       </c>
       <c r="B15" s="14" t="inlineStr">
         <is>
-          <t>CODI</t>
+          <t>CRC</t>
         </is>
       </c>
       <c r="C15" s="14" t="inlineStr">
@@ -5058,7 +5062,7 @@
       </c>
       <c r="D15" s="14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E15" s="14" t="inlineStr">
@@ -5068,29 +5072,29 @@
       </c>
       <c r="F15" s="14" t="inlineStr">
         <is>
-          <t>EBIT/EV 1% → neutral (0-20%)</t>
+          <t>EBIT/EV 13% → neutral (0-20%); fresh-start</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="9" t="inlineStr">
         <is>
-          <t>ZEBRA TECHNOLOGIES CORP</t>
+          <t>Red Rock Resorts, Inc.</t>
         </is>
       </c>
       <c r="B16" s="11" t="inlineStr">
         <is>
-          <t>ZBRA</t>
+          <t>RRR</t>
         </is>
       </c>
       <c r="C16" s="11" t="inlineStr">
         <is>
-          <t>neutral (0-20%)</t>
+          <t>positive-EBIT</t>
         </is>
       </c>
       <c r="D16" s="11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E16" s="11" t="inlineStr">
@@ -5100,19 +5104,19 @@
       </c>
       <c r="F16" s="11" t="inlineStr">
         <is>
-          <t>EBIT/EV 4% → neutral (0-20%)</t>
+          <t>EBIT positive ($597M); EV/price n/a; fresh-start</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="12" t="inlineStr">
         <is>
-          <t>SKYWORKS SOLUTIONS, INC.</t>
+          <t>SEADRILL Ltd</t>
         </is>
       </c>
       <c r="B17" s="14" t="inlineStr">
         <is>
-          <t>SWKS</t>
+          <t>SDRL</t>
         </is>
       </c>
       <c r="C17" s="14" t="inlineStr">
@@ -5122,7 +5126,7 @@
       </c>
       <c r="D17" s="14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E17" s="14" t="inlineStr">
@@ -5132,19 +5136,19 @@
       </c>
       <c r="F17" s="14" t="inlineStr">
         <is>
-          <t>EBIT/EV 5% → neutral (0-20%)</t>
+          <t>EBIT/EV 2% → neutral (0-20%); fresh-start</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="9" t="inlineStr">
         <is>
-          <t>Versigent PLC</t>
+          <t>Phoenix Energy One, LLC</t>
         </is>
       </c>
       <c r="B18" s="11" t="inlineStr">
         <is>
-          <t>VGNT</t>
+          <t>PHXE-P</t>
         </is>
       </c>
       <c r="C18" s="11" t="inlineStr">
@@ -5154,7 +5158,7 @@
       </c>
       <c r="D18" s="11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E18" s="11" t="inlineStr">
@@ -5164,19 +5168,19 @@
       </c>
       <c r="F18" s="11" t="inlineStr">
         <is>
-          <t>EBIT/EV 1% → neutral (0-20%)</t>
+          <t>EBIT/EV 4% → neutral (0-20%); fresh-start</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="12" t="inlineStr">
         <is>
-          <t>BARRETT BUSINESS SERVICES INC</t>
+          <t>Noble Corp plc</t>
         </is>
       </c>
       <c r="B19" s="14" t="inlineStr">
         <is>
-          <t>BBSI</t>
+          <t>NE</t>
         </is>
       </c>
       <c r="C19" s="14" t="inlineStr">
@@ -5186,7 +5190,7 @@
       </c>
       <c r="D19" s="14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E19" s="14" t="inlineStr">
@@ -5196,29 +5200,29 @@
       </c>
       <c r="F19" s="14" t="inlineStr">
         <is>
-          <t>EBIT/EV 4% → neutral (0-20%)</t>
+          <t>EBIT/EV 5% → neutral (0-20%); fresh-start</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="9" t="inlineStr">
         <is>
-          <t>Abacus Global Management, Inc.</t>
+          <t>INFINITY NATURAL RESOURCES, INC.</t>
         </is>
       </c>
       <c r="B20" s="11" t="inlineStr">
         <is>
-          <t>ABX</t>
+          <t>INR</t>
         </is>
       </c>
       <c r="C20" s="11" t="inlineStr">
         <is>
-          <t>neutral (0-20%)</t>
+          <t>positive-EBIT</t>
         </is>
       </c>
       <c r="D20" s="11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E20" s="11" t="inlineStr">
@@ -5228,19 +5232,19 @@
       </c>
       <c r="F20" s="11" t="inlineStr">
         <is>
-          <t>EBIT/EV 6% → neutral (0-20%)</t>
+          <t>EBIT positive ($12M); EV/price n/a; fresh-start</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="12" t="inlineStr">
         <is>
-          <t>GoDaddy Inc.</t>
+          <t>ARMSTRONG WORLD INDUSTRIES INC</t>
         </is>
       </c>
       <c r="B21" s="14" t="inlineStr">
         <is>
-          <t>GDDY</t>
+          <t>AWI</t>
         </is>
       </c>
       <c r="C21" s="14" t="inlineStr">
@@ -5260,24 +5264,20 @@
       </c>
       <c r="F21" s="14" t="inlineStr">
         <is>
-          <t>EBIT/EV 9% → neutral (0-20%)</t>
+          <t>EBIT/EV 7% → neutral (0-20%)</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="9" t="inlineStr">
         <is>
-          <t>Capstone Energy Plus, Inc.</t>
-        </is>
-      </c>
-      <c r="B22" s="11" t="inlineStr">
-        <is>
-          <t>CGEH</t>
-        </is>
-      </c>
+          <t>JERSEY CENTRAL POWER &amp; LIGHT CO</t>
+        </is>
+      </c>
+      <c r="B22" s="11" t="inlineStr"/>
       <c r="C22" s="11" t="inlineStr">
         <is>
-          <t>neutral (0-20%)</t>
+          <t>positive-EBIT</t>
         </is>
       </c>
       <c r="D22" s="11" t="inlineStr">
@@ -5292,19 +5292,19 @@
       </c>
       <c r="F22" s="11" t="inlineStr">
         <is>
-          <t>EBIT/EV 1% → neutral (0-20%)</t>
+          <t>EBIT positive ($102M); EV/price n/a</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="12" t="inlineStr">
         <is>
-          <t>UGI CORP /PA/</t>
+          <t>TIDEWATER INC</t>
         </is>
       </c>
       <c r="B23" s="14" t="inlineStr">
         <is>
-          <t>UGI</t>
+          <t>TDW</t>
         </is>
       </c>
       <c r="C23" s="14" t="inlineStr">
@@ -5324,24 +5324,24 @@
       </c>
       <c r="F23" s="14" t="inlineStr">
         <is>
-          <t>EBIT/EV 6% → neutral (0-20%)</t>
+          <t>EBIT/EV 8% → neutral (0-20%)</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="9" t="inlineStr">
         <is>
-          <t>Privia Health Group, Inc.</t>
+          <t>SunOpta Inc.</t>
         </is>
       </c>
       <c r="B24" s="11" t="inlineStr">
         <is>
-          <t>PRVA</t>
+          <t>STKL</t>
         </is>
       </c>
       <c r="C24" s="11" t="inlineStr">
         <is>
-          <t>neutral (0-20%)</t>
+          <t>positive-EBIT</t>
         </is>
       </c>
       <c r="D24" s="11" t="inlineStr">
@@ -5356,19 +5356,19 @@
       </c>
       <c r="F24" s="11" t="inlineStr">
         <is>
-          <t>EBIT/EV 1% → neutral (0-20%)</t>
+          <t>EBIT positive ($40M); EV/price n/a</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="12" t="inlineStr">
         <is>
-          <t>NATURES SUNSHINE PRODUCTS INC</t>
+          <t>STIFEL FINANCIAL CORP</t>
         </is>
       </c>
       <c r="B25" s="14" t="inlineStr">
         <is>
-          <t>NATR</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="C25" s="14" t="inlineStr">
@@ -5388,24 +5388,20 @@
       </c>
       <c r="F25" s="14" t="inlineStr">
         <is>
-          <t>EBIT/EV 7% → neutral (0-20%)</t>
+          <t>EBIT/EV 2% → neutral (0-20%)</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="9" t="inlineStr">
         <is>
-          <t>MDU RESOURCES GROUP INC</t>
-        </is>
-      </c>
-      <c r="B26" s="11" t="inlineStr">
-        <is>
-          <t>MDU</t>
-        </is>
-      </c>
+          <t>CONTINENTAL RESOURCES, INC</t>
+        </is>
+      </c>
+      <c r="B26" s="11" t="inlineStr"/>
       <c r="C26" s="11" t="inlineStr">
         <is>
-          <t>neutral (0-20%)</t>
+          <t>positive-EBIT</t>
         </is>
       </c>
       <c r="D26" s="11" t="inlineStr">
@@ -5420,29 +5416,29 @@
       </c>
       <c r="F26" s="11" t="inlineStr">
         <is>
-          <t>EBIT/EV 7% → neutral (0-20%)</t>
+          <t>EBIT positive ($2863M); EV/price n/a</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="12" t="inlineStr">
         <is>
-          <t>QVC Group, Inc.</t>
+          <t>ITRON, INC.</t>
         </is>
       </c>
       <c r="B27" s="14" t="inlineStr">
         <is>
-          <t>QVCGA</t>
+          <t>ITRI</t>
         </is>
       </c>
       <c r="C27" s="14" t="inlineStr">
         <is>
-          <t>AVOID (neg EBIT)</t>
+          <t>neutral (0-20%)</t>
         </is>
       </c>
       <c r="D27" s="14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E27" s="14" t="inlineStr">
@@ -5452,29 +5448,29 @@
       </c>
       <c r="F27" s="14" t="inlineStr">
         <is>
-          <t>EBIT NEGATIVE ($-2098M); EV/price n/a; fresh-start</t>
+          <t>EBIT/EV 7% → neutral (0-20%)</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="9" t="inlineStr">
         <is>
-          <t>Copper Property CTL Pass Through T</t>
+          <t>PAR PACIFIC HOLDINGS, INC.</t>
         </is>
       </c>
       <c r="B28" s="11" t="inlineStr">
         <is>
-          <t>CPPTL</t>
+          <t>PARR</t>
         </is>
       </c>
       <c r="C28" s="11" t="inlineStr">
         <is>
-          <t>no-data</t>
+          <t>neutral (0-20%)</t>
         </is>
       </c>
       <c r="D28" s="11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E28" s="11" t="inlineStr">
@@ -5484,29 +5480,29 @@
       </c>
       <c r="F28" s="11" t="inlineStr">
         <is>
-          <t>fresh-start</t>
+          <t>EBIT/EV 9% → neutral (0-20%)</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="12" t="inlineStr">
         <is>
-          <t>WOLFSPEED, INC.</t>
+          <t>ZYNEX INC</t>
         </is>
       </c>
       <c r="B29" s="14" t="inlineStr">
         <is>
-          <t>WOLF</t>
+          <t>ZYXIQ</t>
         </is>
       </c>
       <c r="C29" s="14" t="inlineStr">
         <is>
-          <t>AVOID (&lt;0%)</t>
+          <t>positive-EBIT</t>
         </is>
       </c>
       <c r="D29" s="14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E29" s="14" t="inlineStr">
@@ -5516,25 +5512,29 @@
       </c>
       <c r="F29" s="14" t="inlineStr">
         <is>
-          <t>EBIT/EV -21% → AVOID (&lt;0%); fresh-start</t>
+          <t>EBIT positive ($6M); EV/price n/a</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="9" t="inlineStr">
         <is>
-          <t>Keenova Therapeutics plc</t>
-        </is>
-      </c>
-      <c r="B30" s="11" t="inlineStr"/>
+          <t>GULFPORT ENERGY CORP</t>
+        </is>
+      </c>
+      <c r="B30" s="11" t="inlineStr">
+        <is>
+          <t>GPOR</t>
+        </is>
+      </c>
       <c r="C30" s="11" t="inlineStr">
         <is>
-          <t>AVOID (neg EBIT)</t>
+          <t>neutral (0-20%)</t>
         </is>
       </c>
       <c r="D30" s="11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E30" s="11" t="inlineStr">
@@ -5544,29 +5544,29 @@
       </c>
       <c r="F30" s="11" t="inlineStr">
         <is>
-          <t>EBIT NEGATIVE ($-348M); EV/price n/a; fresh-start</t>
+          <t>EBIT/EV 15% → neutral (0-20%)</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="12" t="inlineStr">
         <is>
-          <t>WW INTERNATIONAL, INC.</t>
+          <t>AGCO CORP /DE</t>
         </is>
       </c>
       <c r="B31" s="14" t="inlineStr">
         <is>
-          <t>WW</t>
+          <t>AGCO</t>
         </is>
       </c>
       <c r="C31" s="14" t="inlineStr">
         <is>
-          <t>AVOID (&lt;0%)</t>
+          <t>neutral (0-20%)</t>
         </is>
       </c>
       <c r="D31" s="14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E31" s="14" t="inlineStr">
@@ -5576,25 +5576,29 @@
       </c>
       <c r="F31" s="14" t="inlineStr">
         <is>
-          <t>EBIT/EV -0% → AVOID (&lt;0%); fresh-start</t>
+          <t>EBIT/EV 4% → neutral (0-20%)</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="9" t="inlineStr">
         <is>
-          <t>Matternet, Inc.</t>
-        </is>
-      </c>
-      <c r="B32" s="11" t="inlineStr"/>
+          <t>EASTMAN CHEMICAL CO</t>
+        </is>
+      </c>
+      <c r="B32" s="11" t="inlineStr">
+        <is>
+          <t>EMN</t>
+        </is>
+      </c>
       <c r="C32" s="11" t="inlineStr">
         <is>
-          <t>AVOID (neg EBIT)</t>
+          <t>neutral (0-20%)</t>
         </is>
       </c>
       <c r="D32" s="11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E32" s="11" t="inlineStr">
@@ -5604,29 +5608,29 @@
       </c>
       <c r="F32" s="11" t="inlineStr">
         <is>
-          <t>EBIT NEGATIVE ($-0M); EV/price n/a</t>
+          <t>EBIT/EV 10% → neutral (0-20%)</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="12" t="inlineStr">
         <is>
-          <t>GoHealth, Inc.</t>
+          <t>Capstone Green Energy Holdings, In</t>
         </is>
       </c>
       <c r="B33" s="14" t="inlineStr">
         <is>
-          <t>GOCO</t>
+          <t>CGEH</t>
         </is>
       </c>
       <c r="C33" s="14" t="inlineStr">
         <is>
-          <t>AVOID (neg EBIT)</t>
+          <t>neutral (0-20%)</t>
         </is>
       </c>
       <c r="D33" s="14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E33" s="14" t="inlineStr">
@@ -5636,29 +5640,29 @@
       </c>
       <c r="F33" s="14" t="inlineStr">
         <is>
-          <t>EBIT NEGATIVE ($-413M); EV/price n/a</t>
+          <t>EBIT/EV 1% → neutral (0-20%)</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="9" t="inlineStr">
         <is>
-          <t>CARMAX INC</t>
+          <t>VISTEON CORP</t>
         </is>
       </c>
       <c r="B34" s="11" t="inlineStr">
         <is>
-          <t>KMX</t>
+          <t>VC</t>
         </is>
       </c>
       <c r="C34" s="11" t="inlineStr">
         <is>
-          <t>no-data</t>
+          <t>neutral (0-20%)</t>
         </is>
       </c>
       <c r="D34" s="11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E34" s="11" t="inlineStr">
@@ -5666,27 +5670,31 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F34" s="11" t="inlineStr"/>
+      <c r="F34" s="11" t="inlineStr">
+        <is>
+          <t>EBIT/EV 1% → neutral (0-20%)</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="12" t="inlineStr">
         <is>
-          <t>Chemours Co</t>
+          <t>NEXSTAR MEDIA GROUP, INC.</t>
         </is>
       </c>
       <c r="B35" s="14" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>NXST</t>
         </is>
       </c>
       <c r="C35" s="14" t="inlineStr">
         <is>
-          <t>no-data</t>
+          <t>neutral (0-20%)</t>
         </is>
       </c>
       <c r="D35" s="14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E35" s="14" t="inlineStr">
@@ -5694,27 +5702,31 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F35" s="14" t="inlineStr"/>
+      <c r="F35" s="14" t="inlineStr">
+        <is>
+          <t>EBIT/EV 6% → neutral (0-20%)</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="9" t="inlineStr">
         <is>
-          <t>CUMULUS MEDIA INC</t>
+          <t>TruBridge, Inc.</t>
         </is>
       </c>
       <c r="B36" s="11" t="inlineStr">
         <is>
-          <t>CMLS</t>
+          <t>TBRG</t>
         </is>
       </c>
       <c r="C36" s="11" t="inlineStr">
         <is>
-          <t>AVOID (neg EBIT)</t>
+          <t>neutral (0-20%)</t>
         </is>
       </c>
       <c r="D36" s="11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E36" s="11" t="inlineStr">
@@ -5724,29 +5736,29 @@
       </c>
       <c r="F36" s="11" t="inlineStr">
         <is>
-          <t>EBIT NEGATIVE ($-138M); EV/price n/a</t>
+          <t>EBIT/EV 4% → neutral (0-20%)</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="12" t="inlineStr">
         <is>
-          <t>Fossil Group, Inc.</t>
+          <t>Spok Holdings, Inc</t>
         </is>
       </c>
       <c r="B37" s="14" t="inlineStr">
         <is>
-          <t>FOSL</t>
+          <t>SPOK</t>
         </is>
       </c>
       <c r="C37" s="14" t="inlineStr">
         <is>
-          <t>AVOID (&lt;0%)</t>
+          <t>neutral (0-20%)</t>
         </is>
       </c>
       <c r="D37" s="14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E37" s="14" t="inlineStr">
@@ -5756,29 +5768,29 @@
       </c>
       <c r="F37" s="14" t="inlineStr">
         <is>
-          <t>EBIT/EV -8% → AVOID (&lt;0%)</t>
+          <t>EBIT/EV 8% → neutral (0-20%)</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="9" t="inlineStr">
         <is>
-          <t>ALT5 Sigma Corp</t>
+          <t>HOULIHAN LOKEY, INC.</t>
         </is>
       </c>
       <c r="B38" s="11" t="inlineStr">
         <is>
-          <t>ALTS</t>
+          <t>HLI</t>
         </is>
       </c>
       <c r="C38" s="11" t="inlineStr">
         <is>
-          <t>AVOID (neg EBIT)</t>
+          <t>positive-EBIT</t>
         </is>
       </c>
       <c r="D38" s="11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E38" s="11" t="inlineStr">
@@ -5788,29 +5800,25 @@
       </c>
       <c r="F38" s="11" t="inlineStr">
         <is>
-          <t>EBIT NEGATIVE ($-23M); EV/price n/a</t>
+          <t>EBIT positive ($527M); EV/price n/a</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="12" t="inlineStr">
         <is>
-          <t>PERRIGO Co plc</t>
-        </is>
-      </c>
-      <c r="B39" s="14" t="inlineStr">
-        <is>
-          <t>PRGO</t>
-        </is>
-      </c>
+          <t>OFFICE PROPERTIES INCOME TRUST</t>
+        </is>
+      </c>
+      <c r="B39" s="14" t="inlineStr"/>
       <c r="C39" s="14" t="inlineStr">
         <is>
-          <t>AVOID (&lt;0%)</t>
+          <t>positive-EBIT</t>
         </is>
       </c>
       <c r="D39" s="14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E39" s="14" t="inlineStr">
@@ -5820,29 +5828,29 @@
       </c>
       <c r="F39" s="14" t="inlineStr">
         <is>
-          <t>EBIT/EV -17% → AVOID (&lt;0%)</t>
+          <t>EBIT positive ($54M); EV/price n/a</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="9" t="inlineStr">
         <is>
-          <t>QVC INC</t>
+          <t>Fortune Brands Innovations, Inc.</t>
         </is>
       </c>
       <c r="B40" s="11" t="inlineStr">
         <is>
-          <t>QVCC</t>
+          <t>FBIN</t>
         </is>
       </c>
       <c r="C40" s="11" t="inlineStr">
         <is>
-          <t>AVOID (neg EBIT)</t>
+          <t>neutral (0-20%)</t>
         </is>
       </c>
       <c r="D40" s="11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E40" s="11" t="inlineStr">
@@ -5852,29 +5860,29 @@
       </c>
       <c r="F40" s="11" t="inlineStr">
         <is>
-          <t>EBIT NEGATIVE ($-2017M); EV/price n/a</t>
+          <t>EBIT/EV 5% → neutral (0-20%)</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="12" t="inlineStr">
         <is>
-          <t>PACIFIC BIOSCIENCES OF CALIFORNIA,</t>
+          <t>Bristow Group Inc.</t>
         </is>
       </c>
       <c r="B41" s="14" t="inlineStr">
         <is>
-          <t>PACB</t>
+          <t>VTOL</t>
         </is>
       </c>
       <c r="C41" s="14" t="inlineStr">
         <is>
-          <t>AVOID (&lt;0%)</t>
+          <t>neutral (0-20%)</t>
         </is>
       </c>
       <c r="D41" s="14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E41" s="14" t="inlineStr">
@@ -5884,29 +5892,29 @@
       </c>
       <c r="F41" s="14" t="inlineStr">
         <is>
-          <t>EBIT/EV -48% → AVOID (&lt;0%)</t>
+          <t>EBIT/EV 7% → neutral (0-20%)</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="9" t="inlineStr">
         <is>
-          <t>iHeartMedia, Inc.</t>
+          <t>Sila Realty Trust, Inc.</t>
         </is>
       </c>
       <c r="B42" s="11" t="inlineStr">
         <is>
-          <t>IHRT</t>
+          <t>SILA</t>
         </is>
       </c>
       <c r="C42" s="11" t="inlineStr">
         <is>
-          <t>AVOID (neg EBIT)</t>
+          <t>neutral (0-20%)</t>
         </is>
       </c>
       <c r="D42" s="11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E42" s="11" t="inlineStr">
@@ -5916,29 +5924,29 @@
       </c>
       <c r="F42" s="11" t="inlineStr">
         <is>
-          <t>EBIT NEGATIVE ($-21M); EV/price n/a</t>
+          <t>EBIT/EV 1% → neutral (0-20%)</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="12" t="inlineStr">
         <is>
-          <t>Ernexa Therapeutics Inc.</t>
+          <t>RMR GROUP INC.</t>
         </is>
       </c>
       <c r="B43" s="14" t="inlineStr">
         <is>
-          <t>ERNA</t>
+          <t>RMR</t>
         </is>
       </c>
       <c r="C43" s="14" t="inlineStr">
         <is>
-          <t>AVOID (&lt;0%)</t>
+          <t>positive-EBIT</t>
         </is>
       </c>
       <c r="D43" s="14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E43" s="14" t="inlineStr">
@@ -5948,29 +5956,29 @@
       </c>
       <c r="F43" s="14" t="inlineStr">
         <is>
-          <t>EBIT/EV -5% → AVOID (&lt;0%)</t>
+          <t>EBIT positive ($42M); EV/price n/a</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="9" t="inlineStr">
         <is>
-          <t>NovoCure Ltd</t>
+          <t>MODIV INDUSTRIAL, INC.</t>
         </is>
       </c>
       <c r="B44" s="11" t="inlineStr">
         <is>
-          <t>NVCR</t>
+          <t>MDV</t>
         </is>
       </c>
       <c r="C44" s="11" t="inlineStr">
         <is>
-          <t>AVOID (&lt;0%)</t>
+          <t>neutral (0-20%)</t>
         </is>
       </c>
       <c r="D44" s="11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E44" s="11" t="inlineStr">
@@ -5980,29 +5988,29 @@
       </c>
       <c r="F44" s="11" t="inlineStr">
         <is>
-          <t>EBIT/EV -7% → AVOID (&lt;0%)</t>
+          <t>EBIT/EV 4% → neutral (0-20%)</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="12" t="inlineStr">
         <is>
-          <t>FARMERS NATIONAL BANC CORP /OH/</t>
+          <t>Ridgepost Capital, Inc.</t>
         </is>
       </c>
       <c r="B45" s="14" t="inlineStr">
         <is>
-          <t>FMNB</t>
+          <t>RPC</t>
         </is>
       </c>
       <c r="C45" s="14" t="inlineStr">
         <is>
-          <t>no-data</t>
+          <t>positive-EBIT</t>
         </is>
       </c>
       <c r="D45" s="14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E45" s="14" t="inlineStr">
@@ -6010,23 +6018,31 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F45" s="14" t="inlineStr"/>
+      <c r="F45" s="14" t="inlineStr">
+        <is>
+          <t>EBIT positive ($66M); EV/price n/a</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="9" t="inlineStr">
         <is>
-          <t>Ionetix Corp / DE /</t>
-        </is>
-      </c>
-      <c r="B46" s="11" t="inlineStr"/>
+          <t>Victoria's Secret &amp; Co.</t>
+        </is>
+      </c>
+      <c r="B46" s="11" t="inlineStr">
+        <is>
+          <t>VSCO</t>
+        </is>
+      </c>
       <c r="C46" s="11" t="inlineStr">
         <is>
-          <t>no-data</t>
+          <t>neutral (0-20%)</t>
         </is>
       </c>
       <c r="D46" s="11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E46" s="11" t="inlineStr">
@@ -6034,27 +6050,31 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F46" s="11" t="inlineStr"/>
+      <c r="F46" s="11" t="inlineStr">
+        <is>
+          <t>EBIT/EV 3% → neutral (0-20%)</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="12" t="inlineStr">
         <is>
-          <t>Teamshares Inc</t>
+          <t>Diversified Energy Co</t>
         </is>
       </c>
       <c r="B47" s="14" t="inlineStr">
         <is>
-          <t>LOKV</t>
+          <t>DEC</t>
         </is>
       </c>
       <c r="C47" s="14" t="inlineStr">
         <is>
-          <t>AVOID (neg EBIT)</t>
+          <t>neutral (0-20%)</t>
         </is>
       </c>
       <c r="D47" s="14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E47" s="14" t="inlineStr">
@@ -6064,29 +6084,29 @@
       </c>
       <c r="F47" s="14" t="inlineStr">
         <is>
-          <t>EBIT NEGATIVE ($-9M); EV/price n/a</t>
+          <t>EBIT/EV 4% → neutral (0-20%)</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="9" t="inlineStr">
         <is>
-          <t>Finwise Bancorp</t>
+          <t>Sinclair, Inc.</t>
         </is>
       </c>
       <c r="B48" s="11" t="inlineStr">
         <is>
-          <t>FINW</t>
+          <t>SBGI</t>
         </is>
       </c>
       <c r="C48" s="11" t="inlineStr">
         <is>
-          <t>no-data</t>
+          <t>positive-EBIT</t>
         </is>
       </c>
       <c r="D48" s="11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E48" s="11" t="inlineStr">
@@ -6094,27 +6114,31 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F48" s="11" t="inlineStr"/>
+      <c r="F48" s="11" t="inlineStr">
+        <is>
+          <t>EBIT positive ($173M); EV/price n/a</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="12" t="inlineStr">
         <is>
-          <t>WASHINGTON TRUST BANCORP INC</t>
+          <t>Venture Global, Inc.</t>
         </is>
       </c>
       <c r="B49" s="14" t="inlineStr">
         <is>
-          <t>WASH</t>
+          <t>VG</t>
         </is>
       </c>
       <c r="C49" s="14" t="inlineStr">
         <is>
-          <t>no-data</t>
+          <t>positive-EBIT</t>
         </is>
       </c>
       <c r="D49" s="14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E49" s="14" t="inlineStr">
@@ -6122,23 +6146,31 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F49" s="14" t="inlineStr"/>
+      <c r="F49" s="14" t="inlineStr">
+        <is>
+          <t>EBIT positive ($5156M); EV/price n/a</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="9" t="inlineStr">
         <is>
-          <t>Federal Home Loan Bank of Indianap</t>
-        </is>
-      </c>
-      <c r="B50" s="11" t="inlineStr"/>
+          <t>SKYWORKS SOLUTIONS, INC.</t>
+        </is>
+      </c>
+      <c r="B50" s="11" t="inlineStr">
+        <is>
+          <t>SWKS</t>
+        </is>
+      </c>
       <c r="C50" s="11" t="inlineStr">
         <is>
-          <t>no-data</t>
+          <t>neutral (0-20%)</t>
         </is>
       </c>
       <c r="D50" s="11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E50" s="11" t="inlineStr">
@@ -6146,39 +6178,5839 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F50" s="11" t="inlineStr"/>
+      <c r="F50" s="11" t="inlineStr">
+        <is>
+          <t>EBIT/EV 5% → neutral (0-20%)</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="12" t="inlineStr">
         <is>
+          <t>LSB INDUSTRIES, INC.</t>
+        </is>
+      </c>
+      <c r="B51" s="14" t="inlineStr">
+        <is>
+          <t>LXU</t>
+        </is>
+      </c>
+      <c r="C51" s="14" t="inlineStr">
+        <is>
+          <t>neutral (0-20%)</t>
+        </is>
+      </c>
+      <c r="D51" s="14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E51" s="14" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F51" s="14" t="inlineStr">
+        <is>
+          <t>EBIT/EV 7% → neutral (0-20%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="9" t="inlineStr">
+        <is>
+          <t>MDU RESOURCES GROUP INC</t>
+        </is>
+      </c>
+      <c r="B52" s="11" t="inlineStr">
+        <is>
+          <t>MDU</t>
+        </is>
+      </c>
+      <c r="C52" s="11" t="inlineStr">
+        <is>
+          <t>neutral (0-20%)</t>
+        </is>
+      </c>
+      <c r="D52" s="11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E52" s="11" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F52" s="11" t="inlineStr">
+        <is>
+          <t>EBIT/EV 7% → neutral (0-20%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="12" t="inlineStr">
+        <is>
+          <t>BRINKS CO</t>
+        </is>
+      </c>
+      <c r="B53" s="14" t="inlineStr">
+        <is>
+          <t>BCO</t>
+        </is>
+      </c>
+      <c r="C53" s="14" t="inlineStr">
+        <is>
+          <t>neutral (0-20%)</t>
+        </is>
+      </c>
+      <c r="D53" s="14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E53" s="14" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F53" s="14" t="inlineStr">
+        <is>
+          <t>EBIT/EV 6% → neutral (0-20%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="9" t="inlineStr">
+        <is>
+          <t>WEYCO GROUP INC</t>
+        </is>
+      </c>
+      <c r="B54" s="11" t="inlineStr">
+        <is>
+          <t>WEYS</t>
+        </is>
+      </c>
+      <c r="C54" s="11" t="inlineStr">
+        <is>
+          <t>neutral (0-20%)</t>
+        </is>
+      </c>
+      <c r="D54" s="11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E54" s="11" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F54" s="11" t="inlineStr">
+        <is>
+          <t>EBIT/EV 8% → neutral (0-20%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="12" t="inlineStr">
+        <is>
+          <t>Coeur Mining, Inc.</t>
+        </is>
+      </c>
+      <c r="B55" s="14" t="inlineStr">
+        <is>
+          <t>CDE</t>
+        </is>
+      </c>
+      <c r="C55" s="14" t="inlineStr">
+        <is>
+          <t>neutral (0-20%)</t>
+        </is>
+      </c>
+      <c r="D55" s="14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E55" s="14" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F55" s="14" t="inlineStr">
+        <is>
+          <t>EBIT/EV 7% → neutral (0-20%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="9" t="inlineStr">
+        <is>
+          <t>NATURES SUNSHINE PRODUCTS INC</t>
+        </is>
+      </c>
+      <c r="B56" s="11" t="inlineStr">
+        <is>
+          <t>NATR</t>
+        </is>
+      </c>
+      <c r="C56" s="11" t="inlineStr">
+        <is>
+          <t>neutral (0-20%)</t>
+        </is>
+      </c>
+      <c r="D56" s="11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E56" s="11" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F56" s="11" t="inlineStr">
+        <is>
+          <t>EBIT/EV 7% → neutral (0-20%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="12" t="inlineStr">
+        <is>
+          <t>NEW ENGLAND REALTY ASSOCIATES LIMI</t>
+        </is>
+      </c>
+      <c r="B57" s="14" t="inlineStr">
+        <is>
+          <t>NEN</t>
+        </is>
+      </c>
+      <c r="C57" s="14" t="inlineStr">
+        <is>
+          <t>neutral (0-20%)</t>
+        </is>
+      </c>
+      <c r="D57" s="14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E57" s="14" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F57" s="14" t="inlineStr">
+        <is>
+          <t>EBIT/EV 0% → neutral (0-20%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="9" t="inlineStr">
+        <is>
+          <t>Light &amp; Wonder, Inc.</t>
+        </is>
+      </c>
+      <c r="B58" s="11" t="inlineStr">
+        <is>
+          <t>LNWO</t>
+        </is>
+      </c>
+      <c r="C58" s="11" t="inlineStr">
+        <is>
+          <t>neutral (0-20%)</t>
+        </is>
+      </c>
+      <c r="D58" s="11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E58" s="11" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F58" s="11" t="inlineStr">
+        <is>
+          <t>EBIT/EV 6% → neutral (0-20%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="12" t="inlineStr">
+        <is>
+          <t>ASTEC INDUSTRIES INC</t>
+        </is>
+      </c>
+      <c r="B59" s="14" t="inlineStr">
+        <is>
+          <t>ASTE</t>
+        </is>
+      </c>
+      <c r="C59" s="14" t="inlineStr">
+        <is>
+          <t>neutral (0-20%)</t>
+        </is>
+      </c>
+      <c r="D59" s="14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E59" s="14" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F59" s="14" t="inlineStr">
+        <is>
+          <t>EBIT/EV 4% → neutral (0-20%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="9" t="inlineStr">
+        <is>
+          <t>C21 Investments Inc.</t>
+        </is>
+      </c>
+      <c r="B60" s="11" t="inlineStr">
+        <is>
+          <t>CWLXF</t>
+        </is>
+      </c>
+      <c r="C60" s="11" t="inlineStr">
+        <is>
+          <t>positive-EBIT</t>
+        </is>
+      </c>
+      <c r="D60" s="11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E60" s="11" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F60" s="11" t="inlineStr">
+        <is>
+          <t>EBIT positive ($2M); EV/price n/a</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="12" t="inlineStr">
+        <is>
+          <t>ZEBRA TECHNOLOGIES CORP</t>
+        </is>
+      </c>
+      <c r="B61" s="14" t="inlineStr">
+        <is>
+          <t>ZBRA</t>
+        </is>
+      </c>
+      <c r="C61" s="14" t="inlineStr">
+        <is>
+          <t>neutral (0-20%)</t>
+        </is>
+      </c>
+      <c r="D61" s="14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E61" s="14" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F61" s="14" t="inlineStr">
+        <is>
+          <t>EBIT/EV 4% → neutral (0-20%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="9" t="inlineStr">
+        <is>
+          <t>UGI CORP /PA/</t>
+        </is>
+      </c>
+      <c r="B62" s="11" t="inlineStr">
+        <is>
+          <t>UGI</t>
+        </is>
+      </c>
+      <c r="C62" s="11" t="inlineStr">
+        <is>
+          <t>neutral (0-20%)</t>
+        </is>
+      </c>
+      <c r="D62" s="11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E62" s="11" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F62" s="11" t="inlineStr">
+        <is>
+          <t>EBIT/EV 6% → neutral (0-20%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="12" t="inlineStr">
+        <is>
+          <t>STRATUS PROPERTIES INC</t>
+        </is>
+      </c>
+      <c r="B63" s="14" t="inlineStr">
+        <is>
+          <t>STRS</t>
+        </is>
+      </c>
+      <c r="C63" s="14" t="inlineStr">
+        <is>
+          <t>neutral (0-20%)</t>
+        </is>
+      </c>
+      <c r="D63" s="14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E63" s="14" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F63" s="14" t="inlineStr">
+        <is>
+          <t>EBIT/EV 4% → neutral (0-20%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="9" t="inlineStr">
+        <is>
+          <t>OMEGA HEALTHCARE INVESTORS INC</t>
+        </is>
+      </c>
+      <c r="B64" s="11" t="inlineStr">
+        <is>
+          <t>OHI</t>
+        </is>
+      </c>
+      <c r="C64" s="11" t="inlineStr">
+        <is>
+          <t>neutral (0-20%)</t>
+        </is>
+      </c>
+      <c r="D64" s="11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E64" s="11" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F64" s="11" t="inlineStr">
+        <is>
+          <t>EBIT/EV 3% → neutral (0-20%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="12" t="inlineStr">
+        <is>
+          <t>BARRETT BUSINESS SERVICES INC</t>
+        </is>
+      </c>
+      <c r="B65" s="14" t="inlineStr">
+        <is>
+          <t>BBSI</t>
+        </is>
+      </c>
+      <c r="C65" s="14" t="inlineStr">
+        <is>
+          <t>neutral (0-20%)</t>
+        </is>
+      </c>
+      <c r="D65" s="14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E65" s="14" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F65" s="14" t="inlineStr">
+        <is>
+          <t>EBIT/EV 4% → neutral (0-20%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="9" t="inlineStr">
+        <is>
+          <t>AMERICAN EAGLE OUTFITTERS INC</t>
+        </is>
+      </c>
+      <c r="B66" s="11" t="inlineStr">
+        <is>
+          <t>AEO</t>
+        </is>
+      </c>
+      <c r="C66" s="11" t="inlineStr">
+        <is>
+          <t>neutral (0-20%)</t>
+        </is>
+      </c>
+      <c r="D66" s="11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E66" s="11" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F66" s="11" t="inlineStr">
+        <is>
+          <t>EBIT/EV 8% → neutral (0-20%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="12" t="inlineStr">
+        <is>
+          <t>HANOVER INSURANCE GROUP, INC.</t>
+        </is>
+      </c>
+      <c r="B67" s="14" t="inlineStr">
+        <is>
+          <t>THG</t>
+        </is>
+      </c>
+      <c r="C67" s="14" t="inlineStr">
+        <is>
+          <t>neutral (0-20%)</t>
+        </is>
+      </c>
+      <c r="D67" s="14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E67" s="14" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F67" s="14" t="inlineStr">
+        <is>
+          <t>EBIT/EV 5% → neutral (0-20%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="9" t="inlineStr">
+        <is>
+          <t>MSC INDUSTRIAL DIRECT CO INC</t>
+        </is>
+      </c>
+      <c r="B68" s="11" t="inlineStr">
+        <is>
+          <t>MSM</t>
+        </is>
+      </c>
+      <c r="C68" s="11" t="inlineStr">
+        <is>
+          <t>neutral (0-20%)</t>
+        </is>
+      </c>
+      <c r="D68" s="11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E68" s="11" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F68" s="11" t="inlineStr">
+        <is>
+          <t>EBIT/EV 4% → neutral (0-20%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="12" t="inlineStr">
+        <is>
+          <t>ANI PHARMACEUTICALS INC</t>
+        </is>
+      </c>
+      <c r="B69" s="14" t="inlineStr">
+        <is>
+          <t>ANIP</t>
+        </is>
+      </c>
+      <c r="C69" s="14" t="inlineStr">
+        <is>
+          <t>neutral (0-20%)</t>
+        </is>
+      </c>
+      <c r="D69" s="14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E69" s="14" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F69" s="14" t="inlineStr">
+        <is>
+          <t>EBIT/EV 4% → neutral (0-20%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="9" t="inlineStr">
+        <is>
+          <t>PERDOCEO EDUCATION Corp</t>
+        </is>
+      </c>
+      <c r="B70" s="11" t="inlineStr">
+        <is>
+          <t>PRDO</t>
+        </is>
+      </c>
+      <c r="C70" s="11" t="inlineStr">
+        <is>
+          <t>neutral (0-20%)</t>
+        </is>
+      </c>
+      <c r="D70" s="11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E70" s="11" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F70" s="11" t="inlineStr">
+        <is>
+          <t>EBIT/EV 11% → neutral (0-20%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="12" t="inlineStr">
+        <is>
+          <t>GETTY REALTY CORP /MD/</t>
+        </is>
+      </c>
+      <c r="B71" s="14" t="inlineStr">
+        <is>
+          <t>GTY</t>
+        </is>
+      </c>
+      <c r="C71" s="14" t="inlineStr">
+        <is>
+          <t>neutral (0-20%)</t>
+        </is>
+      </c>
+      <c r="D71" s="14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E71" s="14" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F71" s="14" t="inlineStr">
+        <is>
+          <t>EBIT/EV 4% → neutral (0-20%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="9" t="inlineStr">
+        <is>
+          <t>FEDERATED HERMES, INC.</t>
+        </is>
+      </c>
+      <c r="B72" s="11" t="inlineStr">
+        <is>
+          <t>FHI</t>
+        </is>
+      </c>
+      <c r="C72" s="11" t="inlineStr">
+        <is>
+          <t>positive-EBIT</t>
+        </is>
+      </c>
+      <c r="D72" s="11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E72" s="11" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F72" s="11" t="inlineStr">
+        <is>
+          <t>EBIT positive ($514M); EV/price n/a</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="12" t="inlineStr">
+        <is>
+          <t>AMERICAN STATES WATER CO</t>
+        </is>
+      </c>
+      <c r="B73" s="14" t="inlineStr">
+        <is>
+          <t>AWR</t>
+        </is>
+      </c>
+      <c r="C73" s="14" t="inlineStr">
+        <is>
+          <t>neutral (0-20%)</t>
+        </is>
+      </c>
+      <c r="D73" s="14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E73" s="14" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F73" s="14" t="inlineStr">
+        <is>
+          <t>EBIT/EV 6% → neutral (0-20%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="9" t="inlineStr">
+        <is>
+          <t>MARINEMAX INC</t>
+        </is>
+      </c>
+      <c r="B74" s="11" t="inlineStr">
+        <is>
+          <t>HZO</t>
+        </is>
+      </c>
+      <c r="C74" s="11" t="inlineStr">
+        <is>
+          <t>neutral (0-20%)</t>
+        </is>
+      </c>
+      <c r="D74" s="11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E74" s="11" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F74" s="11" t="inlineStr">
+        <is>
+          <t>EBIT/EV 2% → neutral (0-20%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="12" t="inlineStr">
+        <is>
+          <t>LAMAR ADVERTISING CO/NEW</t>
+        </is>
+      </c>
+      <c r="B75" s="14" t="inlineStr">
+        <is>
+          <t>LAMR</t>
+        </is>
+      </c>
+      <c r="C75" s="14" t="inlineStr">
+        <is>
+          <t>positive-EBIT</t>
+        </is>
+      </c>
+      <c r="D75" s="14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E75" s="14" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F75" s="14" t="inlineStr">
+        <is>
+          <t>EBIT positive ($774M); EV/price n/a</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="9" t="inlineStr">
+        <is>
+          <t>CHARLES RIVER LABORATORIES INTERNA</t>
+        </is>
+      </c>
+      <c r="B76" s="11" t="inlineStr">
+        <is>
+          <t>CRL</t>
+        </is>
+      </c>
+      <c r="C76" s="11" t="inlineStr">
+        <is>
+          <t>neutral (0-20%)</t>
+        </is>
+      </c>
+      <c r="D76" s="11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E76" s="11" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F76" s="11" t="inlineStr">
+        <is>
+          <t>EBIT/EV 0% → neutral (0-20%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="12" t="inlineStr">
+        <is>
+          <t>ALLIANCEBERNSTEIN L.P.</t>
+        </is>
+      </c>
+      <c r="B77" s="14" t="inlineStr"/>
+      <c r="C77" s="14" t="inlineStr">
+        <is>
+          <t>positive-EBIT</t>
+        </is>
+      </c>
+      <c r="D77" s="14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E77" s="14" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F77" s="14" t="inlineStr">
+        <is>
+          <t>EBIT positive ($1050M); EV/price n/a</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="9" t="inlineStr">
+        <is>
+          <t>PDF SOLUTIONS INC</t>
+        </is>
+      </c>
+      <c r="B78" s="11" t="inlineStr">
+        <is>
+          <t>PDFS</t>
+        </is>
+      </c>
+      <c r="C78" s="11" t="inlineStr">
+        <is>
+          <t>neutral (0-20%)</t>
+        </is>
+      </c>
+      <c r="D78" s="11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E78" s="11" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F78" s="11" t="inlineStr">
+        <is>
+          <t>EBIT/EV 0% → neutral (0-20%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="12" t="inlineStr">
+        <is>
+          <t>BLACKBAUD INC</t>
+        </is>
+      </c>
+      <c r="B79" s="14" t="inlineStr">
+        <is>
+          <t>BLKB</t>
+        </is>
+      </c>
+      <c r="C79" s="14" t="inlineStr">
+        <is>
+          <t>neutral (0-20%)</t>
+        </is>
+      </c>
+      <c r="D79" s="14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E79" s="14" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F79" s="14" t="inlineStr">
+        <is>
+          <t>EBIT/EV 5% → neutral (0-20%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="9" t="inlineStr">
+        <is>
+          <t>CapForce Inc.</t>
+        </is>
+      </c>
+      <c r="B80" s="11" t="inlineStr">
+        <is>
+          <t>OPGN</t>
+        </is>
+      </c>
+      <c r="C80" s="11" t="inlineStr">
+        <is>
+          <t>positive-EBIT</t>
+        </is>
+      </c>
+      <c r="D80" s="11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E80" s="11" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F80" s="11" t="inlineStr">
+        <is>
+          <t>EBIT positive ($24M); EV/price n/a</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="12" t="inlineStr">
+        <is>
+          <t>Crocs, Inc.</t>
+        </is>
+      </c>
+      <c r="B81" s="14" t="inlineStr">
+        <is>
+          <t>CROX</t>
+        </is>
+      </c>
+      <c r="C81" s="14" t="inlineStr">
+        <is>
+          <t>neutral (0-20%)</t>
+        </is>
+      </c>
+      <c r="D81" s="14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E81" s="14" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F81" s="14" t="inlineStr">
+        <is>
+          <t>EBIT/EV 2% → neutral (0-20%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="9" t="inlineStr">
+        <is>
+          <t>Compass Diversified Holdings</t>
+        </is>
+      </c>
+      <c r="B82" s="11" t="inlineStr">
+        <is>
+          <t>CODI</t>
+        </is>
+      </c>
+      <c r="C82" s="11" t="inlineStr">
+        <is>
+          <t>neutral (0-20%)</t>
+        </is>
+      </c>
+      <c r="D82" s="11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E82" s="11" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F82" s="11" t="inlineStr">
+        <is>
+          <t>EBIT/EV 1% → neutral (0-20%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="12" t="inlineStr">
+        <is>
+          <t>Pacira BioSciences, Inc.</t>
+        </is>
+      </c>
+      <c r="B83" s="14" t="inlineStr">
+        <is>
+          <t>PCRX</t>
+        </is>
+      </c>
+      <c r="C83" s="14" t="inlineStr">
+        <is>
+          <t>neutral (0-20%)</t>
+        </is>
+      </c>
+      <c r="D83" s="14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E83" s="14" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F83" s="14" t="inlineStr">
+        <is>
+          <t>EBIT/EV 1% → neutral (0-20%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="9" t="inlineStr">
+        <is>
+          <t>Booz Allen Hamilton Holding Corp</t>
+        </is>
+      </c>
+      <c r="B84" s="11" t="inlineStr">
+        <is>
+          <t>BAH</t>
+        </is>
+      </c>
+      <c r="C84" s="11" t="inlineStr">
+        <is>
+          <t>neutral (0-20%)</t>
+        </is>
+      </c>
+      <c r="D84" s="11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E84" s="11" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F84" s="11" t="inlineStr">
+        <is>
+          <t>EBIT/EV 8% → neutral (0-20%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="12" t="inlineStr">
+        <is>
+          <t>Proto Labs Inc</t>
+        </is>
+      </c>
+      <c r="B85" s="14" t="inlineStr">
+        <is>
+          <t>PRLB</t>
+        </is>
+      </c>
+      <c r="C85" s="14" t="inlineStr">
+        <is>
+          <t>neutral (0-20%)</t>
+        </is>
+      </c>
+      <c r="D85" s="14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E85" s="14" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F85" s="14" t="inlineStr">
+        <is>
+          <t>EBIT/EV 1% → neutral (0-20%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="9" t="inlineStr">
+        <is>
+          <t>Contango ORE, Inc.</t>
+        </is>
+      </c>
+      <c r="B86" s="11" t="inlineStr">
+        <is>
+          <t>CTGO</t>
+        </is>
+      </c>
+      <c r="C86" s="11" t="inlineStr">
+        <is>
+          <t>neutral (0-20%)</t>
+        </is>
+      </c>
+      <c r="D86" s="11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E86" s="11" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F86" s="11" t="inlineStr">
+        <is>
+          <t>EBIT/EV 20% → neutral (0-20%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="12" t="inlineStr">
+        <is>
+          <t>Knowles Corp</t>
+        </is>
+      </c>
+      <c r="B87" s="14" t="inlineStr">
+        <is>
+          <t>KN</t>
+        </is>
+      </c>
+      <c r="C87" s="14" t="inlineStr">
+        <is>
+          <t>positive-EBIT</t>
+        </is>
+      </c>
+      <c r="D87" s="14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E87" s="14" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F87" s="14" t="inlineStr">
+        <is>
+          <t>EBIT positive ($70M); EV/price n/a</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="9" t="inlineStr">
+        <is>
+          <t>ProPetro Holding Corp.</t>
+        </is>
+      </c>
+      <c r="B88" s="11" t="inlineStr">
+        <is>
+          <t>PUMP</t>
+        </is>
+      </c>
+      <c r="C88" s="11" t="inlineStr">
+        <is>
+          <t>neutral (0-20%)</t>
+        </is>
+      </c>
+      <c r="D88" s="11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E88" s="11" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F88" s="11" t="inlineStr">
+        <is>
+          <t>EBIT/EV 0% → neutral (0-20%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="12" t="inlineStr">
+        <is>
+          <t>CARVANA CO.</t>
+        </is>
+      </c>
+      <c r="B89" s="14" t="inlineStr">
+        <is>
+          <t>CVNA</t>
+        </is>
+      </c>
+      <c r="C89" s="14" t="inlineStr">
+        <is>
+          <t>positive-EBIT</t>
+        </is>
+      </c>
+      <c r="D89" s="14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E89" s="14" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F89" s="14" t="inlineStr">
+        <is>
+          <t>EBIT positive ($1881M); EV/price n/a</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="9" t="inlineStr">
+        <is>
+          <t>Privia Health Group, Inc.</t>
+        </is>
+      </c>
+      <c r="B90" s="11" t="inlineStr">
+        <is>
+          <t>PRVA</t>
+        </is>
+      </c>
+      <c r="C90" s="11" t="inlineStr">
+        <is>
+          <t>neutral (0-20%)</t>
+        </is>
+      </c>
+      <c r="D90" s="11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E90" s="11" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F90" s="11" t="inlineStr">
+        <is>
+          <t>EBIT/EV 1% → neutral (0-20%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="12" t="inlineStr">
+        <is>
+          <t>Abacus Global Management, Inc.</t>
+        </is>
+      </c>
+      <c r="B91" s="14" t="inlineStr">
+        <is>
+          <t>ABX</t>
+        </is>
+      </c>
+      <c r="C91" s="14" t="inlineStr">
+        <is>
+          <t>neutral (0-20%)</t>
+        </is>
+      </c>
+      <c r="D91" s="14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E91" s="14" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F91" s="14" t="inlineStr">
+        <is>
+          <t>EBIT/EV 6% → neutral (0-20%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="9" t="inlineStr">
+        <is>
+          <t>Volato Group, Inc.</t>
+        </is>
+      </c>
+      <c r="B92" s="11" t="inlineStr">
+        <is>
+          <t>SOAR</t>
+        </is>
+      </c>
+      <c r="C92" s="11" t="inlineStr">
+        <is>
+          <t>positive-EBIT</t>
+        </is>
+      </c>
+      <c r="D92" s="11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E92" s="11" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F92" s="11" t="inlineStr">
+        <is>
+          <t>EBIT positive ($4M); EV/price n/a</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="12" t="inlineStr">
+        <is>
+          <t>Hesai Group</t>
+        </is>
+      </c>
+      <c r="B93" s="14" t="inlineStr">
+        <is>
+          <t>HSAI</t>
+        </is>
+      </c>
+      <c r="C93" s="14" t="inlineStr">
+        <is>
+          <t>neutral (0-20%)</t>
+        </is>
+      </c>
+      <c r="D93" s="14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E93" s="14" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F93" s="14" t="inlineStr">
+        <is>
+          <t>EBIT/EV 1% → neutral (0-20%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="9" t="inlineStr">
+        <is>
+          <t>Solventum Corp</t>
+        </is>
+      </c>
+      <c r="B94" s="11" t="inlineStr">
+        <is>
+          <t>SOLV</t>
+        </is>
+      </c>
+      <c r="C94" s="11" t="inlineStr">
+        <is>
+          <t>neutral (0-20%)</t>
+        </is>
+      </c>
+      <c r="D94" s="11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E94" s="11" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F94" s="11" t="inlineStr">
+        <is>
+          <t>EBIT/EV 10% → neutral (0-20%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="12" t="inlineStr">
+        <is>
+          <t>Versigent PLC</t>
+        </is>
+      </c>
+      <c r="B95" s="14" t="inlineStr">
+        <is>
+          <t>VGNT</t>
+        </is>
+      </c>
+      <c r="C95" s="14" t="inlineStr">
+        <is>
+          <t>neutral (0-20%)</t>
+        </is>
+      </c>
+      <c r="D95" s="14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E95" s="14" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F95" s="14" t="inlineStr">
+        <is>
+          <t>EBIT/EV 1% → neutral (0-20%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="9" t="inlineStr">
+        <is>
+          <t>ARKO Petroleum Corp.</t>
+        </is>
+      </c>
+      <c r="B96" s="11" t="inlineStr">
+        <is>
+          <t>APC</t>
+        </is>
+      </c>
+      <c r="C96" s="11" t="inlineStr">
+        <is>
+          <t>neutral (0-20%)</t>
+        </is>
+      </c>
+      <c r="D96" s="11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E96" s="11" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F96" s="11" t="inlineStr">
+        <is>
+          <t>EBIT/EV 1% → neutral (0-20%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="12" t="inlineStr">
+        <is>
+          <t>WW INTERNATIONAL, INC.</t>
+        </is>
+      </c>
+      <c r="B97" s="14" t="inlineStr">
+        <is>
+          <t>WW</t>
+        </is>
+      </c>
+      <c r="C97" s="14" t="inlineStr">
+        <is>
+          <t>AVOID (&lt;0%)</t>
+        </is>
+      </c>
+      <c r="D97" s="14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E97" s="14" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F97" s="14" t="inlineStr">
+        <is>
+          <t>EBIT/EV -0% → AVOID (&lt;0%); fresh-start</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="9" t="inlineStr">
+        <is>
+          <t>WOLFSPEED, INC.</t>
+        </is>
+      </c>
+      <c r="B98" s="11" t="inlineStr">
+        <is>
+          <t>WOLF</t>
+        </is>
+      </c>
+      <c r="C98" s="11" t="inlineStr">
+        <is>
+          <t>AVOID (&lt;0%)</t>
+        </is>
+      </c>
+      <c r="D98" s="11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E98" s="11" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F98" s="11" t="inlineStr">
+        <is>
+          <t>EBIT/EV -21% → AVOID (&lt;0%); fresh-start</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="12" t="inlineStr">
+        <is>
+          <t>Copper Property CTL Pass Through T</t>
+        </is>
+      </c>
+      <c r="B99" s="14" t="inlineStr">
+        <is>
+          <t>CPPTL</t>
+        </is>
+      </c>
+      <c r="C99" s="14" t="inlineStr">
+        <is>
+          <t>no-data</t>
+        </is>
+      </c>
+      <c r="D99" s="14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E99" s="14" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F99" s="14" t="inlineStr">
+        <is>
+          <t>fresh-start</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="9" t="inlineStr">
+        <is>
+          <t>Tailored Brands, Inc. / DE</t>
+        </is>
+      </c>
+      <c r="B100" s="11" t="inlineStr"/>
+      <c r="C100" s="11" t="inlineStr">
+        <is>
+          <t>no-data</t>
+        </is>
+      </c>
+      <c r="D100" s="11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E100" s="11" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F100" s="11" t="inlineStr">
+        <is>
+          <t>fresh-start</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="12" t="inlineStr">
+        <is>
+          <t>AMPCO PITTSBURGH CORP</t>
+        </is>
+      </c>
+      <c r="B101" s="14" t="inlineStr">
+        <is>
+          <t>AP</t>
+        </is>
+      </c>
+      <c r="C101" s="14" t="inlineStr">
+        <is>
+          <t>AVOID (&lt;0%)</t>
+        </is>
+      </c>
+      <c r="D101" s="14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E101" s="14" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F101" s="14" t="inlineStr">
+        <is>
+          <t>EBIT/EV -9% → AVOID (&lt;0%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="9" t="inlineStr">
+        <is>
+          <t>Jefferies Financial Group Inc.</t>
+        </is>
+      </c>
+      <c r="B102" s="11" t="inlineStr">
+        <is>
+          <t>JEF</t>
+        </is>
+      </c>
+      <c r="C102" s="11" t="inlineStr">
+        <is>
+          <t>AVOID (&lt;0%)</t>
+        </is>
+      </c>
+      <c r="D102" s="11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E102" s="11" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F102" s="11" t="inlineStr">
+        <is>
+          <t>EBIT/EV -0% → AVOID (&lt;0%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="12" t="inlineStr">
+        <is>
+          <t>AMERISERV FINANCIAL INC /PA/</t>
+        </is>
+      </c>
+      <c r="B103" s="14" t="inlineStr">
+        <is>
+          <t>ASRV</t>
+        </is>
+      </c>
+      <c r="C103" s="14" t="inlineStr">
+        <is>
+          <t>no-data</t>
+        </is>
+      </c>
+      <c r="D103" s="14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E103" s="14" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F103" s="14" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="9" t="inlineStr">
+        <is>
+          <t>MAGNA INTERNATIONAL INC</t>
+        </is>
+      </c>
+      <c r="B104" s="11" t="inlineStr">
+        <is>
+          <t>MGA</t>
+        </is>
+      </c>
+      <c r="C104" s="11" t="inlineStr">
+        <is>
+          <t>no-data</t>
+        </is>
+      </c>
+      <c r="D104" s="11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E104" s="11" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F104" s="11" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="12" t="inlineStr">
+        <is>
+          <t>POPULAR, INC.</t>
+        </is>
+      </c>
+      <c r="B105" s="14" t="inlineStr">
+        <is>
+          <t>BPOP</t>
+        </is>
+      </c>
+      <c r="C105" s="14" t="inlineStr">
+        <is>
+          <t>no-data</t>
+        </is>
+      </c>
+      <c r="D105" s="14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E105" s="14" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F105" s="14" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="9" t="inlineStr">
+        <is>
+          <t>CLEVELAND-CLIFFS INC.</t>
+        </is>
+      </c>
+      <c r="B106" s="11" t="inlineStr">
+        <is>
+          <t>CLF</t>
+        </is>
+      </c>
+      <c r="C106" s="11" t="inlineStr">
+        <is>
+          <t>AVOID (&lt;0%)</t>
+        </is>
+      </c>
+      <c r="D106" s="11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E106" s="11" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F106" s="11" t="inlineStr">
+        <is>
+          <t>EBIT/EV -8% → AVOID (&lt;0%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="12" t="inlineStr">
+        <is>
+          <t>ICAHN ENTERPRISES L.P.</t>
+        </is>
+      </c>
+      <c r="B107" s="14" t="inlineStr">
+        <is>
+          <t>IEP</t>
+        </is>
+      </c>
+      <c r="C107" s="14" t="inlineStr">
+        <is>
+          <t>no-data</t>
+        </is>
+      </c>
+      <c r="D107" s="14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E107" s="14" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F107" s="14" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" s="9" t="inlineStr">
+        <is>
+          <t>ALT5 Sigma Corp</t>
+        </is>
+      </c>
+      <c r="B108" s="11" t="inlineStr">
+        <is>
+          <t>ALTS</t>
+        </is>
+      </c>
+      <c r="C108" s="11" t="inlineStr">
+        <is>
+          <t>AVOID (neg EBIT)</t>
+        </is>
+      </c>
+      <c r="D108" s="11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E108" s="11" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F108" s="11" t="inlineStr">
+        <is>
+          <t>EBIT NEGATIVE ($-23M); EV/price n/a</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="12" t="inlineStr">
+        <is>
+          <t>OCTAVE SPECIALTY GROUP INC</t>
+        </is>
+      </c>
+      <c r="B109" s="14" t="inlineStr">
+        <is>
+          <t>OSG</t>
+        </is>
+      </c>
+      <c r="C109" s="14" t="inlineStr">
+        <is>
+          <t>no-data</t>
+        </is>
+      </c>
+      <c r="D109" s="14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E109" s="14" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F109" s="14" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="9" t="inlineStr">
+        <is>
+          <t>AES CORP</t>
+        </is>
+      </c>
+      <c r="B110" s="11" t="inlineStr">
+        <is>
+          <t>AES</t>
+        </is>
+      </c>
+      <c r="C110" s="11" t="inlineStr">
+        <is>
+          <t>no-data</t>
+        </is>
+      </c>
+      <c r="D110" s="11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E110" s="11" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F110" s="11" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" s="12" t="inlineStr">
+        <is>
+          <t>ROYAL BANK OF CANADA</t>
+        </is>
+      </c>
+      <c r="B111" s="14" t="inlineStr">
+        <is>
+          <t>RY</t>
+        </is>
+      </c>
+      <c r="C111" s="14" t="inlineStr">
+        <is>
+          <t>no-data</t>
+        </is>
+      </c>
+      <c r="D111" s="14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E111" s="14" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F111" s="14" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" s="9" t="inlineStr">
+        <is>
+          <t>PRECISION DRILLING Corp</t>
+        </is>
+      </c>
+      <c r="B112" s="11" t="inlineStr">
+        <is>
+          <t>PDS</t>
+        </is>
+      </c>
+      <c r="C112" s="11" t="inlineStr">
+        <is>
+          <t>no-data</t>
+        </is>
+      </c>
+      <c r="D112" s="11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E112" s="11" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F112" s="11" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="12" t="inlineStr">
+        <is>
+          <t>ALEXANDRIA REAL ESTATE EQUITIES, I</t>
+        </is>
+      </c>
+      <c r="B113" s="14" t="inlineStr">
+        <is>
+          <t>ARE</t>
+        </is>
+      </c>
+      <c r="C113" s="14" t="inlineStr">
+        <is>
+          <t>no-data</t>
+        </is>
+      </c>
+      <c r="D113" s="14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E113" s="14" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F113" s="14" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" s="9" t="inlineStr">
+        <is>
+          <t>LATAM AIRLINES GROUP S.A.</t>
+        </is>
+      </c>
+      <c r="B114" s="11" t="inlineStr">
+        <is>
+          <t>LTM</t>
+        </is>
+      </c>
+      <c r="C114" s="11" t="inlineStr">
+        <is>
+          <t>no-data</t>
+        </is>
+      </c>
+      <c r="D114" s="11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E114" s="11" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F114" s="11" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" s="12" t="inlineStr">
+        <is>
+          <t>CUMULUS MEDIA INC</t>
+        </is>
+      </c>
+      <c r="B115" s="14" t="inlineStr">
+        <is>
+          <t>CMLS</t>
+        </is>
+      </c>
+      <c r="C115" s="14" t="inlineStr">
+        <is>
+          <t>AVOID (neg EBIT)</t>
+        </is>
+      </c>
+      <c r="D115" s="14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E115" s="14" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F115" s="14" t="inlineStr">
+        <is>
+          <t>EBIT NEGATIVE ($-138M); EV/price n/a</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="9" t="inlineStr">
+        <is>
+          <t>TRANSALTA CORP</t>
+        </is>
+      </c>
+      <c r="B116" s="11" t="inlineStr">
+        <is>
+          <t>TAC</t>
+        </is>
+      </c>
+      <c r="C116" s="11" t="inlineStr">
+        <is>
+          <t>no-data</t>
+        </is>
+      </c>
+      <c r="D116" s="11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E116" s="11" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F116" s="11" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" s="12" t="inlineStr">
+        <is>
+          <t>IROBOT CORP</t>
+        </is>
+      </c>
+      <c r="B117" s="14" t="inlineStr">
+        <is>
+          <t>IRBTQ</t>
+        </is>
+      </c>
+      <c r="C117" s="14" t="inlineStr">
+        <is>
+          <t>AVOID (neg EBIT)</t>
+        </is>
+      </c>
+      <c r="D117" s="14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E117" s="14" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F117" s="14" t="inlineStr">
+        <is>
+          <t>EBIT NEGATIVE ($-103M); EV/price n/a</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="9" t="inlineStr">
+        <is>
+          <t>QVC INC</t>
+        </is>
+      </c>
+      <c r="B118" s="11" t="inlineStr">
+        <is>
+          <t>QVCC</t>
+        </is>
+      </c>
+      <c r="C118" s="11" t="inlineStr">
+        <is>
+          <t>AVOID (neg EBIT)</t>
+        </is>
+      </c>
+      <c r="D118" s="11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E118" s="11" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F118" s="11" t="inlineStr">
+        <is>
+          <t>EBIT NEGATIVE ($-2017M); EV/price n/a</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="12" t="inlineStr">
+        <is>
+          <t>VERMILION ENERGY INC.</t>
+        </is>
+      </c>
+      <c r="B119" s="14" t="inlineStr">
+        <is>
+          <t>VET</t>
+        </is>
+      </c>
+      <c r="C119" s="14" t="inlineStr">
+        <is>
+          <t>no-data</t>
+        </is>
+      </c>
+      <c r="D119" s="14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E119" s="14" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F119" s="14" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" s="9" t="inlineStr">
+        <is>
+          <t>Wheaton Precious Metals Corp.</t>
+        </is>
+      </c>
+      <c r="B120" s="11" t="inlineStr">
+        <is>
+          <t>WPM</t>
+        </is>
+      </c>
+      <c r="C120" s="11" t="inlineStr">
+        <is>
+          <t>no-data</t>
+        </is>
+      </c>
+      <c r="D120" s="11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E120" s="11" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F120" s="11" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" s="12" t="inlineStr">
+        <is>
+          <t>OBSIDIAN ENERGY LTD.</t>
+        </is>
+      </c>
+      <c r="B121" s="14" t="inlineStr">
+        <is>
+          <t>OBE</t>
+        </is>
+      </c>
+      <c r="C121" s="14" t="inlineStr">
+        <is>
+          <t>no-data</t>
+        </is>
+      </c>
+      <c r="D121" s="14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E121" s="14" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F121" s="14" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" s="9" t="inlineStr">
+        <is>
+          <t>QVC Group, Inc.</t>
+        </is>
+      </c>
+      <c r="B122" s="11" t="inlineStr">
+        <is>
+          <t>QVCGA</t>
+        </is>
+      </c>
+      <c r="C122" s="11" t="inlineStr">
+        <is>
+          <t>AVOID (neg EBIT)</t>
+        </is>
+      </c>
+      <c r="D122" s="11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E122" s="11" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F122" s="11" t="inlineStr">
+        <is>
+          <t>EBIT NEGATIVE ($-2098M); EV/price n/a</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="12" t="inlineStr">
+        <is>
+          <t>Clean Energy Fuels Corp.</t>
+        </is>
+      </c>
+      <c r="B123" s="14" t="inlineStr">
+        <is>
+          <t>CLNE</t>
+        </is>
+      </c>
+      <c r="C123" s="14" t="inlineStr">
+        <is>
+          <t>AVOID (&lt;0%)</t>
+        </is>
+      </c>
+      <c r="D123" s="14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E123" s="14" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F123" s="14" t="inlineStr">
+        <is>
+          <t>EBIT/EV -20% → AVOID (&lt;0%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="9" t="inlineStr">
+        <is>
+          <t>BlackRock TCP Capital Corp.</t>
+        </is>
+      </c>
+      <c r="B124" s="11" t="inlineStr">
+        <is>
+          <t>TCPC</t>
+        </is>
+      </c>
+      <c r="C124" s="11" t="inlineStr">
+        <is>
+          <t>no-data</t>
+        </is>
+      </c>
+      <c r="D124" s="11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E124" s="11" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F124" s="11" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" s="12" t="inlineStr">
+        <is>
+          <t>National CineMedia, Inc.</t>
+        </is>
+      </c>
+      <c r="B125" s="14" t="inlineStr">
+        <is>
+          <t>NCMI</t>
+        </is>
+      </c>
+      <c r="C125" s="14" t="inlineStr">
+        <is>
+          <t>AVOID (&lt;0%)</t>
+        </is>
+      </c>
+      <c r="D125" s="14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E125" s="14" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F125" s="14" t="inlineStr">
+        <is>
+          <t>EBIT/EV -3% → AVOID (&lt;0%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="9" t="inlineStr">
+        <is>
+          <t>Cinemark Holdings, Inc.</t>
+        </is>
+      </c>
+      <c r="B126" s="11" t="inlineStr">
+        <is>
+          <t>CNK</t>
+        </is>
+      </c>
+      <c r="C126" s="11" t="inlineStr">
+        <is>
+          <t>AVOID (&lt;0%)</t>
+        </is>
+      </c>
+      <c r="D126" s="11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E126" s="11" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F126" s="11" t="inlineStr">
+        <is>
+          <t>EBIT/EV -6% → AVOID (&lt;0%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="12" t="inlineStr">
+        <is>
+          <t>iHeartMedia, Inc.</t>
+        </is>
+      </c>
+      <c r="B127" s="14" t="inlineStr">
+        <is>
+          <t>IHRT</t>
+        </is>
+      </c>
+      <c r="C127" s="14" t="inlineStr">
+        <is>
+          <t>AVOID (neg EBIT)</t>
+        </is>
+      </c>
+      <c r="D127" s="14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E127" s="14" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F127" s="14" t="inlineStr">
+        <is>
+          <t>EBIT NEGATIVE ($-21M); EV/price n/a</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="9" t="inlineStr">
+        <is>
+          <t>EchoStar CORP</t>
+        </is>
+      </c>
+      <c r="B128" s="11" t="inlineStr">
+        <is>
+          <t>SATS</t>
+        </is>
+      </c>
+      <c r="C128" s="11" t="inlineStr">
+        <is>
+          <t>AVOID (neg EBIT)</t>
+        </is>
+      </c>
+      <c r="D128" s="11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E128" s="11" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F128" s="11" t="inlineStr">
+        <is>
+          <t>EBIT NEGATIVE ($-17723M); EV/price n/a</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="12" t="inlineStr">
+        <is>
+          <t>AZUL SA</t>
+        </is>
+      </c>
+      <c r="B129" s="14" t="inlineStr">
+        <is>
+          <t>AZLUY</t>
+        </is>
+      </c>
+      <c r="C129" s="14" t="inlineStr">
+        <is>
+          <t>no-data</t>
+        </is>
+      </c>
+      <c r="D129" s="14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E129" s="14" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F129" s="14" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" s="9" t="inlineStr">
+        <is>
+          <t>Smart Sand, Inc.</t>
+        </is>
+      </c>
+      <c r="B130" s="11" t="inlineStr">
+        <is>
+          <t>SND</t>
+        </is>
+      </c>
+      <c r="C130" s="11" t="inlineStr">
+        <is>
+          <t>AVOID (&lt;0%)</t>
+        </is>
+      </c>
+      <c r="D130" s="11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E130" s="11" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F130" s="11" t="inlineStr">
+        <is>
+          <t>EBIT/EV -2% → AVOID (&lt;0%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="12" t="inlineStr">
+        <is>
+          <t>Tronox Holdings plc</t>
+        </is>
+      </c>
+      <c r="B131" s="14" t="inlineStr">
+        <is>
+          <t>TROX</t>
+        </is>
+      </c>
+      <c r="C131" s="14" t="inlineStr">
+        <is>
+          <t>AVOID (&lt;0%)</t>
+        </is>
+      </c>
+      <c r="D131" s="14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E131" s="14" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F131" s="14" t="inlineStr">
+        <is>
+          <t>EBIT/EV -5% → AVOID (&lt;0%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="9" t="inlineStr">
+        <is>
+          <t>Grupo Aeromexico, S.A.B. de C.V.</t>
+        </is>
+      </c>
+      <c r="B132" s="11" t="inlineStr">
+        <is>
+          <t>AERO</t>
+        </is>
+      </c>
+      <c r="C132" s="11" t="inlineStr">
+        <is>
+          <t>no-data</t>
+        </is>
+      </c>
+      <c r="D132" s="11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E132" s="11" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F132" s="11" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" s="12" t="inlineStr">
+        <is>
+          <t>Keenova Therapeutics plc</t>
+        </is>
+      </c>
+      <c r="B133" s="14" t="inlineStr"/>
+      <c r="C133" s="14" t="inlineStr">
+        <is>
+          <t>AVOID (neg EBIT)</t>
+        </is>
+      </c>
+      <c r="D133" s="14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E133" s="14" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F133" s="14" t="inlineStr">
+        <is>
+          <t>EBIT NEGATIVE ($-348M); EV/price n/a</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="9" t="inlineStr">
+        <is>
+          <t>Silver Point Specialty Lending Fun</t>
+        </is>
+      </c>
+      <c r="B134" s="11" t="inlineStr"/>
+      <c r="C134" s="11" t="inlineStr">
+        <is>
+          <t>no-data</t>
+        </is>
+      </c>
+      <c r="D134" s="11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E134" s="11" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F134" s="11" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" s="12" t="inlineStr">
+        <is>
+          <t>HERTZ GLOBAL HOLDINGS, INC</t>
+        </is>
+      </c>
+      <c r="B135" s="14" t="inlineStr">
+        <is>
+          <t>HTZ</t>
+        </is>
+      </c>
+      <c r="C135" s="14" t="inlineStr">
+        <is>
+          <t>no-data</t>
+        </is>
+      </c>
+      <c r="D135" s="14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E135" s="14" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F135" s="14" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" s="9" t="inlineStr">
+        <is>
+          <t>CORPORACION AMERICA AIRPORTS S.A.</t>
+        </is>
+      </c>
+      <c r="B136" s="11" t="inlineStr">
+        <is>
+          <t>CAAP</t>
+        </is>
+      </c>
+      <c r="C136" s="11" t="inlineStr">
+        <is>
+          <t>no-data</t>
+        </is>
+      </c>
+      <c r="D136" s="11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E136" s="11" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F136" s="11" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" s="12" t="inlineStr">
+        <is>
+          <t>Garrett Motion Inc.</t>
+        </is>
+      </c>
+      <c r="B137" s="14" t="inlineStr">
+        <is>
+          <t>GTX</t>
+        </is>
+      </c>
+      <c r="C137" s="14" t="inlineStr">
+        <is>
+          <t>no-data</t>
+        </is>
+      </c>
+      <c r="D137" s="14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E137" s="14" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F137" s="14" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="A138" s="9" t="inlineStr">
+        <is>
+          <t>Beneficient</t>
+        </is>
+      </c>
+      <c r="B138" s="11" t="inlineStr">
+        <is>
+          <t>BENF</t>
+        </is>
+      </c>
+      <c r="C138" s="11" t="inlineStr">
+        <is>
+          <t>AVOID (neg EBIT)</t>
+        </is>
+      </c>
+      <c r="D138" s="11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E138" s="11" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F138" s="11" t="inlineStr">
+        <is>
+          <t>EBIT NEGATIVE ($-167M); EV/price n/a</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="12" t="inlineStr">
+        <is>
+          <t>CLOVER HEALTH INVESTMENTS, CORP. /</t>
+        </is>
+      </c>
+      <c r="B139" s="14" t="inlineStr">
+        <is>
+          <t>CLOV</t>
+        </is>
+      </c>
+      <c r="C139" s="14" t="inlineStr">
+        <is>
+          <t>AVOID (neg EBIT)</t>
+        </is>
+      </c>
+      <c r="D139" s="14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E139" s="14" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F139" s="14" t="inlineStr">
+        <is>
+          <t>EBIT NEGATIVE ($-86M); EV/price n/a</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="9" t="inlineStr">
+        <is>
+          <t>GoHealth, Inc.</t>
+        </is>
+      </c>
+      <c r="B140" s="11" t="inlineStr">
+        <is>
+          <t>GOCO</t>
+        </is>
+      </c>
+      <c r="C140" s="11" t="inlineStr">
+        <is>
+          <t>AVOID (neg EBIT)</t>
+        </is>
+      </c>
+      <c r="D140" s="11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E140" s="11" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F140" s="11" t="inlineStr">
+        <is>
+          <t>EBIT NEGATIVE ($-413M); EV/price n/a</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="12" t="inlineStr">
+        <is>
+          <t>Docebo Inc.</t>
+        </is>
+      </c>
+      <c r="B141" s="14" t="inlineStr">
+        <is>
+          <t>DCBO</t>
+        </is>
+      </c>
+      <c r="C141" s="14" t="inlineStr">
+        <is>
+          <t>no-data</t>
+        </is>
+      </c>
+      <c r="D141" s="14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E141" s="14" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F141" s="14" t="inlineStr"/>
+    </row>
+    <row r="142">
+      <c r="A142" s="9" t="inlineStr">
+        <is>
+          <t>Sable Offshore Corp.</t>
+        </is>
+      </c>
+      <c r="B142" s="11" t="inlineStr">
+        <is>
+          <t>SOC</t>
+        </is>
+      </c>
+      <c r="C142" s="11" t="inlineStr">
+        <is>
+          <t>AVOID (&lt;0%)</t>
+        </is>
+      </c>
+      <c r="D142" s="11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E142" s="11" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F142" s="11" t="inlineStr">
+        <is>
+          <t>EBIT/EV -24% → AVOID (&lt;0%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="12" t="inlineStr">
+        <is>
+          <t>Core Scientific, Inc./tx</t>
+        </is>
+      </c>
+      <c r="B143" s="14" t="inlineStr">
+        <is>
+          <t>CORZ</t>
+        </is>
+      </c>
+      <c r="C143" s="14" t="inlineStr">
+        <is>
+          <t>AVOID (&lt;0%)</t>
+        </is>
+      </c>
+      <c r="D143" s="14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E143" s="14" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F143" s="14" t="inlineStr">
+        <is>
+          <t>EBIT/EV -2% → AVOID (&lt;0%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="9" t="inlineStr">
+        <is>
+          <t>Galaxy Digital Inc.</t>
+        </is>
+      </c>
+      <c r="B144" s="11" t="inlineStr">
+        <is>
+          <t>GLXY</t>
+        </is>
+      </c>
+      <c r="C144" s="11" t="inlineStr">
+        <is>
+          <t>no-data</t>
+        </is>
+      </c>
+      <c r="D144" s="11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E144" s="11" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F144" s="11" t="inlineStr"/>
+    </row>
+    <row r="145">
+      <c r="A145" s="12" t="inlineStr">
+        <is>
+          <t>WhiteHawk Income Corp</t>
+        </is>
+      </c>
+      <c r="B145" s="14" t="inlineStr">
+        <is>
+          <t>WHK</t>
+        </is>
+      </c>
+      <c r="C145" s="14" t="inlineStr">
+        <is>
+          <t>no-data</t>
+        </is>
+      </c>
+      <c r="D145" s="14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E145" s="14" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F145" s="14" t="inlineStr"/>
+    </row>
+    <row r="146">
+      <c r="A146" s="9" t="inlineStr">
+        <is>
+          <t>Atlanta Braves Holdings, Inc.</t>
+        </is>
+      </c>
+      <c r="B146" s="11" t="inlineStr">
+        <is>
+          <t>BATRA</t>
+        </is>
+      </c>
+      <c r="C146" s="11" t="inlineStr">
+        <is>
+          <t>AVOID (neg EBIT)</t>
+        </is>
+      </c>
+      <c r="D146" s="11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E146" s="11" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F146" s="11" t="inlineStr">
+        <is>
+          <t>EBIT NEGATIVE ($-14M); EV/price n/a</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="12" t="inlineStr">
+        <is>
+          <t>Twin Hospitality Group Inc.</t>
+        </is>
+      </c>
+      <c r="B147" s="14" t="inlineStr">
+        <is>
+          <t>TWNP</t>
+        </is>
+      </c>
+      <c r="C147" s="14" t="inlineStr">
+        <is>
+          <t>AVOID (neg EBIT)</t>
+        </is>
+      </c>
+      <c r="D147" s="14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E147" s="14" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F147" s="14" t="inlineStr">
+        <is>
+          <t>EBIT NEGATIVE ($-8M); EV/price n/a</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="9" t="inlineStr">
+        <is>
+          <t>Vine Hill Capital Investment Corp.</t>
+        </is>
+      </c>
+      <c r="B148" s="11" t="inlineStr">
+        <is>
+          <t>VCIC</t>
+        </is>
+      </c>
+      <c r="C148" s="11" t="inlineStr">
+        <is>
+          <t>AVOID (neg EBIT)</t>
+        </is>
+      </c>
+      <c r="D148" s="11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E148" s="11" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F148" s="11" t="inlineStr">
+        <is>
+          <t>EBIT NEGATIVE ($-4M); EV/price n/a</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="12" t="inlineStr">
+        <is>
+          <t>Fifth Era Acquisition Corp I</t>
+        </is>
+      </c>
+      <c r="B149" s="14" t="inlineStr">
+        <is>
+          <t>FERA</t>
+        </is>
+      </c>
+      <c r="C149" s="14" t="inlineStr">
+        <is>
+          <t>AVOID (neg EBIT)</t>
+        </is>
+      </c>
+      <c r="D149" s="14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E149" s="14" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F149" s="14" t="inlineStr">
+        <is>
+          <t>EBIT NEGATIVE ($-4M); EV/price n/a</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="9" t="inlineStr">
+        <is>
+          <t>First Eagle Tactical Municipal Opp</t>
+        </is>
+      </c>
+      <c r="B150" s="11" t="inlineStr"/>
+      <c r="C150" s="11" t="inlineStr">
+        <is>
+          <t>no-data</t>
+        </is>
+      </c>
+      <c r="D150" s="11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E150" s="11" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F150" s="11" t="inlineStr"/>
+    </row>
+    <row r="151">
+      <c r="A151" s="12" t="inlineStr">
+        <is>
+          <t>LibreMax Asset-Backed Income Fund</t>
+        </is>
+      </c>
+      <c r="B151" s="14" t="inlineStr"/>
+      <c r="C151" s="14" t="inlineStr">
+        <is>
+          <t>no-data</t>
+        </is>
+      </c>
+      <c r="D151" s="14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E151" s="14" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F151" s="14" t="inlineStr"/>
+    </row>
+    <row r="152">
+      <c r="A152" s="9" t="inlineStr">
+        <is>
+          <t>PRESIDIO PRODUCTION Co</t>
+        </is>
+      </c>
+      <c r="B152" s="11" t="inlineStr">
+        <is>
+          <t>FTW</t>
+        </is>
+      </c>
+      <c r="C152" s="11" t="inlineStr">
+        <is>
+          <t>no-data</t>
+        </is>
+      </c>
+      <c r="D152" s="11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E152" s="11" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F152" s="11" t="inlineStr"/>
+    </row>
+    <row r="153">
+      <c r="A153" s="12" t="inlineStr">
+        <is>
+          <t>Odysseus Holdings Ltd</t>
+        </is>
+      </c>
+      <c r="B153" s="14" t="inlineStr"/>
+      <c r="C153" s="14" t="inlineStr">
+        <is>
+          <t>no-data</t>
+        </is>
+      </c>
+      <c r="D153" s="14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E153" s="14" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F153" s="14" t="inlineStr"/>
+    </row>
+    <row r="154">
+      <c r="A154" s="9" t="inlineStr">
+        <is>
+          <t>Aristotle Pacific Enhanced CLO Inc</t>
+        </is>
+      </c>
+      <c r="B154" s="11" t="inlineStr"/>
+      <c r="C154" s="11" t="inlineStr">
+        <is>
+          <t>no-data</t>
+        </is>
+      </c>
+      <c r="D154" s="11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E154" s="11" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F154" s="11" t="inlineStr"/>
+    </row>
+    <row r="155">
+      <c r="A155" s="12" t="inlineStr">
+        <is>
+          <t>CopperTech Metals Inc.</t>
+        </is>
+      </c>
+      <c r="B155" s="14" t="inlineStr">
+        <is>
+          <t>CUX</t>
+        </is>
+      </c>
+      <c r="C155" s="14" t="inlineStr">
+        <is>
+          <t>no-data</t>
+        </is>
+      </c>
+      <c r="D155" s="14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E155" s="14" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F155" s="14" t="inlineStr"/>
+    </row>
+    <row r="156">
+      <c r="A156" s="9" t="inlineStr">
+        <is>
+          <t>Rare Earths Americas, Inc.</t>
+        </is>
+      </c>
+      <c r="B156" s="11" t="inlineStr"/>
+      <c r="C156" s="11" t="inlineStr">
+        <is>
+          <t>AVOID (neg EBIT)</t>
+        </is>
+      </c>
+      <c r="D156" s="11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E156" s="11" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F156" s="11" t="inlineStr">
+        <is>
+          <t>EBIT NEGATIVE ($-5M); EV/price n/a</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="12" t="inlineStr">
+        <is>
+          <t>Xanadu Quantum Technologies Ltd</t>
+        </is>
+      </c>
+      <c r="B157" s="14" t="inlineStr">
+        <is>
+          <t>XNDU</t>
+        </is>
+      </c>
+      <c r="C157" s="14" t="inlineStr">
+        <is>
+          <t>AVOID (neg EBIT)</t>
+        </is>
+      </c>
+      <c r="D157" s="14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E157" s="14" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F157" s="14" t="inlineStr">
+        <is>
+          <t>EBIT NEGATIVE ($-23M); EV/price n/a</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="9" t="inlineStr">
+        <is>
+          <t>Mountain Crest Acquisition 6 Corp.</t>
+        </is>
+      </c>
+      <c r="B158" s="11" t="inlineStr"/>
+      <c r="C158" s="11" t="inlineStr">
+        <is>
+          <t>AVOID (neg EBIT)</t>
+        </is>
+      </c>
+      <c r="D158" s="11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E158" s="11" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F158" s="11" t="inlineStr">
+        <is>
+          <t>EBIT NEGATIVE ($-0M); EV/price n/a</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="12" t="inlineStr">
+        <is>
+          <t>Osprey Acquisition Corp. III</t>
+        </is>
+      </c>
+      <c r="B159" s="14" t="inlineStr"/>
+      <c r="C159" s="14" t="inlineStr">
+        <is>
+          <t>no-data</t>
+        </is>
+      </c>
+      <c r="D159" s="14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E159" s="14" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F159" s="14" t="inlineStr"/>
+    </row>
+    <row r="160">
+      <c r="A160" s="9" t="inlineStr">
+        <is>
+          <t>BAXTER INTERNATIONAL INC</t>
+        </is>
+      </c>
+      <c r="B160" s="11" t="inlineStr">
+        <is>
+          <t>BAX</t>
+        </is>
+      </c>
+      <c r="C160" s="11" t="inlineStr">
+        <is>
+          <t>AVOID (&lt;0%)</t>
+        </is>
+      </c>
+      <c r="D160" s="11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E160" s="11" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F160" s="11" t="inlineStr">
+        <is>
+          <t>EBIT/EV -1% → AVOID (&lt;0%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="12" t="inlineStr">
+        <is>
+          <t>BRT Apartments Corp.</t>
+        </is>
+      </c>
+      <c r="B161" s="14" t="inlineStr">
+        <is>
+          <t>BRT</t>
+        </is>
+      </c>
+      <c r="C161" s="14" t="inlineStr">
+        <is>
+          <t>AVOID (&lt;0%)</t>
+        </is>
+      </c>
+      <c r="D161" s="14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E161" s="14" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F161" s="14" t="inlineStr">
+        <is>
+          <t>EBIT/EV -2% → AVOID (&lt;0%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="9" t="inlineStr">
+        <is>
+          <t>LINCOLN NATIONAL CORP</t>
+        </is>
+      </c>
+      <c r="B162" s="11" t="inlineStr">
+        <is>
+          <t>LNC</t>
+        </is>
+      </c>
+      <c r="C162" s="11" t="inlineStr">
+        <is>
+          <t>no-data</t>
+        </is>
+      </c>
+      <c r="D162" s="11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E162" s="11" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F162" s="11" t="inlineStr"/>
+    </row>
+    <row r="163">
+      <c r="A163" s="12" t="inlineStr">
+        <is>
+          <t>ROGERS CORP</t>
+        </is>
+      </c>
+      <c r="B163" s="14" t="inlineStr">
+        <is>
+          <t>ROG</t>
+        </is>
+      </c>
+      <c r="C163" s="14" t="inlineStr">
+        <is>
+          <t>AVOID (&lt;0%)</t>
+        </is>
+      </c>
+      <c r="D163" s="14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E163" s="14" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F163" s="14" t="inlineStr">
+        <is>
+          <t>EBIT/EV -2% → AVOID (&lt;0%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="9" t="inlineStr">
+        <is>
+          <t>WORLD ACCEPTANCE CORP</t>
+        </is>
+      </c>
+      <c r="B164" s="11" t="inlineStr">
+        <is>
+          <t>WRLD</t>
+        </is>
+      </c>
+      <c r="C164" s="11" t="inlineStr">
+        <is>
+          <t>no-data</t>
+        </is>
+      </c>
+      <c r="D164" s="11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E164" s="11" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F164" s="11" t="inlineStr"/>
+    </row>
+    <row r="165">
+      <c r="A165" s="12" t="inlineStr">
+        <is>
+          <t>FARMERS NATIONAL BANC CORP /OH/</t>
+        </is>
+      </c>
+      <c r="B165" s="14" t="inlineStr">
+        <is>
+          <t>FMNB</t>
+        </is>
+      </c>
+      <c r="C165" s="14" t="inlineStr">
+        <is>
+          <t>no-data</t>
+        </is>
+      </c>
+      <c r="D165" s="14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E165" s="14" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F165" s="14" t="inlineStr"/>
+    </row>
+    <row r="166">
+      <c r="A166" s="9" t="inlineStr">
+        <is>
+          <t>CASEYS GENERAL STORES INC</t>
+        </is>
+      </c>
+      <c r="B166" s="11" t="inlineStr">
+        <is>
+          <t>CASY</t>
+        </is>
+      </c>
+      <c r="C166" s="11" t="inlineStr">
+        <is>
+          <t>no-data</t>
+        </is>
+      </c>
+      <c r="D166" s="11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E166" s="11" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F166" s="11" t="inlineStr"/>
+    </row>
+    <row r="167">
+      <c r="A167" s="12" t="inlineStr">
+        <is>
+          <t>CADIZ INC</t>
+        </is>
+      </c>
+      <c r="B167" s="14" t="inlineStr">
+        <is>
+          <t>CDZI</t>
+        </is>
+      </c>
+      <c r="C167" s="14" t="inlineStr">
+        <is>
+          <t>AVOID (&lt;0%)</t>
+        </is>
+      </c>
+      <c r="D167" s="14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E167" s="14" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F167" s="14" t="inlineStr">
+        <is>
+          <t>EBIT/EV -7% → AVOID (&lt;0%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="9" t="inlineStr">
+        <is>
+          <t>WASHINGTON TRUST BANCORP INC</t>
+        </is>
+      </c>
+      <c r="B168" s="11" t="inlineStr">
+        <is>
+          <t>WASH</t>
+        </is>
+      </c>
+      <c r="C168" s="11" t="inlineStr">
+        <is>
+          <t>no-data</t>
+        </is>
+      </c>
+      <c r="D168" s="11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E168" s="11" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F168" s="11" t="inlineStr"/>
+    </row>
+    <row r="169">
+      <c r="A169" s="12" t="inlineStr">
+        <is>
+          <t>Ernexa Therapeutics Inc.</t>
+        </is>
+      </c>
+      <c r="B169" s="14" t="inlineStr">
+        <is>
+          <t>ERNA</t>
+        </is>
+      </c>
+      <c r="C169" s="14" t="inlineStr">
+        <is>
+          <t>AVOID (&lt;0%)</t>
+        </is>
+      </c>
+      <c r="D169" s="14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E169" s="14" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F169" s="14" t="inlineStr">
+        <is>
+          <t>EBIT/EV -6% → AVOID (&lt;0%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="9" t="inlineStr">
+        <is>
+          <t>PAN AMERICAN SILVER CORP</t>
+        </is>
+      </c>
+      <c r="B170" s="11" t="inlineStr">
+        <is>
+          <t>PAAS</t>
+        </is>
+      </c>
+      <c r="C170" s="11" t="inlineStr">
+        <is>
+          <t>no-data</t>
+        </is>
+      </c>
+      <c r="D170" s="11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E170" s="11" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F170" s="11" t="inlineStr"/>
+    </row>
+    <row r="171">
+      <c r="A171" s="12" t="inlineStr">
+        <is>
+          <t>ALLIANCEBERNSTEIN HOLDING L.P.</t>
+        </is>
+      </c>
+      <c r="B171" s="14" t="inlineStr">
+        <is>
+          <t>AB</t>
+        </is>
+      </c>
+      <c r="C171" s="14" t="inlineStr">
+        <is>
+          <t>no-data</t>
+        </is>
+      </c>
+      <c r="D171" s="14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E171" s="14" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F171" s="14" t="inlineStr"/>
+    </row>
+    <row r="172">
+      <c r="A172" s="9" t="inlineStr">
+        <is>
+          <t>KEMPER Corp</t>
+        </is>
+      </c>
+      <c r="B172" s="11" t="inlineStr">
+        <is>
+          <t>KMPB</t>
+        </is>
+      </c>
+      <c r="C172" s="11" t="inlineStr">
+        <is>
+          <t>AVOID (&lt;0%)</t>
+        </is>
+      </c>
+      <c r="D172" s="11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E172" s="11" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F172" s="11" t="inlineStr">
+        <is>
+          <t>EBIT/EV -1% → AVOID (&lt;0%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="12" t="inlineStr">
+        <is>
+          <t>Fossil Group, Inc.</t>
+        </is>
+      </c>
+      <c r="B173" s="14" t="inlineStr">
+        <is>
+          <t>FOSL</t>
+        </is>
+      </c>
+      <c r="C173" s="14" t="inlineStr">
+        <is>
+          <t>AVOID (&lt;0%)</t>
+        </is>
+      </c>
+      <c r="D173" s="14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E173" s="14" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F173" s="14" t="inlineStr">
+        <is>
+          <t>EBIT/EV -8% → AVOID (&lt;0%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="9" t="inlineStr">
+        <is>
+          <t>RADIAN GROUP INC</t>
+        </is>
+      </c>
+      <c r="B174" s="11" t="inlineStr">
+        <is>
+          <t>RDN</t>
+        </is>
+      </c>
+      <c r="C174" s="11" t="inlineStr">
+        <is>
+          <t>AVOID (&lt;0%)</t>
+        </is>
+      </c>
+      <c r="D174" s="11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E174" s="11" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F174" s="11" t="inlineStr">
+        <is>
+          <t>EBIT/EV -2% → AVOID (&lt;0%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="12" t="inlineStr">
+        <is>
+          <t>INTEGRA LIFESCIENCES HOLDINGS CORP</t>
+        </is>
+      </c>
+      <c r="B175" s="14" t="inlineStr">
+        <is>
+          <t>IART</t>
+        </is>
+      </c>
+      <c r="C175" s="14" t="inlineStr">
+        <is>
+          <t>AVOID (&lt;0%)</t>
+        </is>
+      </c>
+      <c r="D175" s="14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E175" s="14" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F175" s="14" t="inlineStr">
+        <is>
+          <t>EBIT/EV -13% → AVOID (&lt;0%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="9" t="inlineStr">
+        <is>
+          <t>ADTRAN Holdings, Inc.</t>
+        </is>
+      </c>
+      <c r="B176" s="11" t="inlineStr">
+        <is>
+          <t>ADTN</t>
+        </is>
+      </c>
+      <c r="C176" s="11" t="inlineStr">
+        <is>
+          <t>AVOID (&lt;0%)</t>
+        </is>
+      </c>
+      <c r="D176" s="11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E176" s="11" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F176" s="11" t="inlineStr">
+        <is>
+          <t>EBIT/EV -1% → AVOID (&lt;0%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="12" t="inlineStr">
+        <is>
           <t>EDAP TMS SA</t>
         </is>
       </c>
-      <c r="B51" s="14" t="inlineStr">
+      <c r="B177" s="14" t="inlineStr">
         <is>
           <t>EDAP</t>
         </is>
       </c>
-      <c r="C51" s="14" t="inlineStr">
+      <c r="C177" s="14" t="inlineStr">
         <is>
           <t>AVOID (&lt;0%)</t>
         </is>
       </c>
-      <c r="D51" s="14" t="inlineStr">
+      <c r="D177" s="14" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E51" s="14" t="inlineStr">
+      <c r="E177" s="14" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="F51" s="14" t="inlineStr">
+      <c r="F177" s="14" t="inlineStr">
         <is>
           <t>EBIT/EV -12% → AVOID (&lt;0%)</t>
         </is>
       </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="9" t="inlineStr">
+        <is>
+          <t>PROSPERITY BANCSHARES INC</t>
+        </is>
+      </c>
+      <c r="B178" s="11" t="inlineStr">
+        <is>
+          <t>PB</t>
+        </is>
+      </c>
+      <c r="C178" s="11" t="inlineStr">
+        <is>
+          <t>no-data</t>
+        </is>
+      </c>
+      <c r="D178" s="11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E178" s="11" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F178" s="11" t="inlineStr"/>
+    </row>
+    <row r="179">
+      <c r="A179" s="12" t="inlineStr">
+        <is>
+          <t>PEOPLES BANCORP OF NORTH CAROLINA</t>
+        </is>
+      </c>
+      <c r="B179" s="14" t="inlineStr">
+        <is>
+          <t>PEBK</t>
+        </is>
+      </c>
+      <c r="C179" s="14" t="inlineStr">
+        <is>
+          <t>no-data</t>
+        </is>
+      </c>
+      <c r="D179" s="14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E179" s="14" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F179" s="14" t="inlineStr"/>
+    </row>
+    <row r="180">
+      <c r="A180" s="9" t="inlineStr">
+        <is>
+          <t>SIERRA BANCORP</t>
+        </is>
+      </c>
+      <c r="B180" s="11" t="inlineStr">
+        <is>
+          <t>BSRR</t>
+        </is>
+      </c>
+      <c r="C180" s="11" t="inlineStr">
+        <is>
+          <t>no-data</t>
+        </is>
+      </c>
+      <c r="D180" s="11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E180" s="11" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F180" s="11" t="inlineStr"/>
+    </row>
+    <row r="181">
+      <c r="A181" s="12" t="inlineStr">
+        <is>
+          <t>GOLD RESOURCE CORP</t>
+        </is>
+      </c>
+      <c r="B181" s="14" t="inlineStr">
+        <is>
+          <t>GORO</t>
+        </is>
+      </c>
+      <c r="C181" s="14" t="inlineStr">
+        <is>
+          <t>AVOID (&lt;0%)</t>
+        </is>
+      </c>
+      <c r="D181" s="14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E181" s="14" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F181" s="14" t="inlineStr">
+        <is>
+          <t>EBIT/EV -1% → AVOID (&lt;0%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="9" t="inlineStr">
+        <is>
+          <t>CARMAX INC</t>
+        </is>
+      </c>
+      <c r="B182" s="11" t="inlineStr">
+        <is>
+          <t>KMX</t>
+        </is>
+      </c>
+      <c r="C182" s="11" t="inlineStr">
+        <is>
+          <t>no-data</t>
+        </is>
+      </c>
+      <c r="D182" s="11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E182" s="11" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F182" s="11" t="inlineStr"/>
+    </row>
+    <row r="183">
+      <c r="A183" s="12" t="inlineStr">
+        <is>
+          <t>SEABRIDGE GOLD INC</t>
+        </is>
+      </c>
+      <c r="B183" s="14" t="inlineStr">
+        <is>
+          <t>SA</t>
+        </is>
+      </c>
+      <c r="C183" s="14" t="inlineStr">
+        <is>
+          <t>no-data</t>
+        </is>
+      </c>
+      <c r="D183" s="14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E183" s="14" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F183" s="14" t="inlineStr"/>
+    </row>
+    <row r="184">
+      <c r="A184" s="9" t="inlineStr">
+        <is>
+          <t>IMMUNIC, INC.</t>
+        </is>
+      </c>
+      <c r="B184" s="11" t="inlineStr">
+        <is>
+          <t>IMUX</t>
+        </is>
+      </c>
+      <c r="C184" s="11" t="inlineStr">
+        <is>
+          <t>AVOID (&lt;0%)</t>
+        </is>
+      </c>
+      <c r="D184" s="11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E184" s="11" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F184" s="11" t="inlineStr">
+        <is>
+          <t>EBIT/EV -5% → AVOID (&lt;0%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="12" t="inlineStr">
+        <is>
+          <t>PACIFIC BIOSCIENCES OF CALIFORNIA,</t>
+        </is>
+      </c>
+      <c r="B185" s="14" t="inlineStr">
+        <is>
+          <t>PACB</t>
+        </is>
+      </c>
+      <c r="C185" s="14" t="inlineStr">
+        <is>
+          <t>AVOID (&lt;0%)</t>
+        </is>
+      </c>
+      <c r="D185" s="14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E185" s="14" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F185" s="14" t="inlineStr">
+        <is>
+          <t>EBIT/EV -49% → AVOID (&lt;0%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="9" t="inlineStr">
+        <is>
+          <t>BV Financial, Inc.</t>
+        </is>
+      </c>
+      <c r="B186" s="11" t="inlineStr">
+        <is>
+          <t>BVFL</t>
+        </is>
+      </c>
+      <c r="C186" s="11" t="inlineStr">
+        <is>
+          <t>no-data</t>
+        </is>
+      </c>
+      <c r="D186" s="11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E186" s="11" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F186" s="11" t="inlineStr"/>
+    </row>
+    <row r="187">
+      <c r="A187" s="12" t="inlineStr">
+        <is>
+          <t>Hudbay Minerals Inc.</t>
+        </is>
+      </c>
+      <c r="B187" s="14" t="inlineStr">
+        <is>
+          <t>HBM</t>
+        </is>
+      </c>
+      <c r="C187" s="14" t="inlineStr">
+        <is>
+          <t>no-data</t>
+        </is>
+      </c>
+      <c r="D187" s="14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E187" s="14" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F187" s="14" t="inlineStr"/>
+    </row>
+    <row r="188">
+      <c r="A188" s="9" t="inlineStr">
+        <is>
+          <t>AtriCure, Inc.</t>
+        </is>
+      </c>
+      <c r="B188" s="11" t="inlineStr">
+        <is>
+          <t>ATRC</t>
+        </is>
+      </c>
+      <c r="C188" s="11" t="inlineStr">
+        <is>
+          <t>AVOID (&lt;0%)</t>
+        </is>
+      </c>
+      <c r="D188" s="11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E188" s="11" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F188" s="11" t="inlineStr">
+        <is>
+          <t>EBIT/EV -1% → AVOID (&lt;0%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="12" t="inlineStr">
+        <is>
+          <t>Federal Home Loan Bank of Indianap</t>
+        </is>
+      </c>
+      <c r="B189" s="14" t="inlineStr"/>
+      <c r="C189" s="14" t="inlineStr">
+        <is>
+          <t>no-data</t>
+        </is>
+      </c>
+      <c r="D189" s="14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E189" s="14" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F189" s="14" t="inlineStr"/>
+    </row>
+    <row r="190">
+      <c r="A190" s="9" t="inlineStr">
+        <is>
+          <t>Federal Home Loan Bank of Dallas</t>
+        </is>
+      </c>
+      <c r="B190" s="11" t="inlineStr"/>
+      <c r="C190" s="11" t="inlineStr">
+        <is>
+          <t>no-data</t>
+        </is>
+      </c>
+      <c r="D190" s="11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E190" s="11" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F190" s="11" t="inlineStr"/>
+    </row>
+    <row r="191">
+      <c r="A191" s="12" t="inlineStr">
+        <is>
+          <t>AMC ENTERTAINMENT HOLDINGS, INC.</t>
+        </is>
+      </c>
+      <c r="B191" s="14" t="inlineStr">
+        <is>
+          <t>AMC</t>
+        </is>
+      </c>
+      <c r="C191" s="14" t="inlineStr">
+        <is>
+          <t>AVOID (&lt;0%)</t>
+        </is>
+      </c>
+      <c r="D191" s="14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E191" s="14" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F191" s="14" t="inlineStr">
+        <is>
+          <t>EBIT/EV -0% → AVOID (&lt;0%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="9" t="inlineStr">
+        <is>
+          <t>ProShares Trust II</t>
+        </is>
+      </c>
+      <c r="B192" s="11" t="inlineStr">
+        <is>
+          <t>AGQ</t>
+        </is>
+      </c>
+      <c r="C192" s="11" t="inlineStr">
+        <is>
+          <t>no-data</t>
+        </is>
+      </c>
+      <c r="D192" s="11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E192" s="11" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F192" s="11" t="inlineStr"/>
+    </row>
+    <row r="193">
+      <c r="A193" s="12" t="inlineStr">
+        <is>
+          <t>Hamilton Lane INC</t>
+        </is>
+      </c>
+      <c r="B193" s="14" t="inlineStr">
+        <is>
+          <t>HLNE</t>
+        </is>
+      </c>
+      <c r="C193" s="14" t="inlineStr">
+        <is>
+          <t>no-data</t>
+        </is>
+      </c>
+      <c r="D193" s="14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E193" s="14" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F193" s="14" t="inlineStr"/>
+    </row>
+    <row r="194">
+      <c r="A194" s="9" t="inlineStr">
+        <is>
+          <t>ARDELYX, INC.</t>
+        </is>
+      </c>
+      <c r="B194" s="11" t="inlineStr">
+        <is>
+          <t>ARDX</t>
+        </is>
+      </c>
+      <c r="C194" s="11" t="inlineStr">
+        <is>
+          <t>AVOID (&lt;0%)</t>
+        </is>
+      </c>
+      <c r="D194" s="11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E194" s="11" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F194" s="11" t="inlineStr">
+        <is>
+          <t>EBIT/EV -3% → AVOID (&lt;0%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="12" t="inlineStr">
+        <is>
+          <t>ECOPETROL S.A.</t>
+        </is>
+      </c>
+      <c r="B195" s="14" t="inlineStr">
+        <is>
+          <t>EC</t>
+        </is>
+      </c>
+      <c r="C195" s="14" t="inlineStr">
+        <is>
+          <t>no-data</t>
+        </is>
+      </c>
+      <c r="D195" s="14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E195" s="14" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F195" s="14" t="inlineStr"/>
+    </row>
+    <row r="196">
+      <c r="A196" s="9" t="inlineStr">
+        <is>
+          <t>WORKIVA INC</t>
+        </is>
+      </c>
+      <c r="B196" s="11" t="inlineStr">
+        <is>
+          <t>WK</t>
+        </is>
+      </c>
+      <c r="C196" s="11" t="inlineStr">
+        <is>
+          <t>AVOID (neg EBIT)</t>
+        </is>
+      </c>
+      <c r="D196" s="11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E196" s="11" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F196" s="11" t="inlineStr">
+        <is>
+          <t>EBIT NEGATIVE ($-42M); EV/price n/a</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="12" t="inlineStr">
+        <is>
+          <t>Backblaze, Inc.</t>
+        </is>
+      </c>
+      <c r="B197" s="14" t="inlineStr">
+        <is>
+          <t>BLZE</t>
+        </is>
+      </c>
+      <c r="C197" s="14" t="inlineStr">
+        <is>
+          <t>AVOID (&lt;0%)</t>
+        </is>
+      </c>
+      <c r="D197" s="14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E197" s="14" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F197" s="14" t="inlineStr">
+        <is>
+          <t>EBIT/EV -3% → AVOID (&lt;0%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="9" t="inlineStr">
+        <is>
+          <t>Ryerson Holding Corp</t>
+        </is>
+      </c>
+      <c r="B198" s="11" t="inlineStr">
+        <is>
+          <t>RYZ</t>
+        </is>
+      </c>
+      <c r="C198" s="11" t="inlineStr">
+        <is>
+          <t>AVOID (&lt;0%)</t>
+        </is>
+      </c>
+      <c r="D198" s="11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E198" s="11" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F198" s="11" t="inlineStr">
+        <is>
+          <t>EBIT/EV -1% → AVOID (&lt;0%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="12" t="inlineStr">
+        <is>
+          <t>Northfield Bancorp, Inc.</t>
+        </is>
+      </c>
+      <c r="B199" s="14" t="inlineStr">
+        <is>
+          <t>NFBK</t>
+        </is>
+      </c>
+      <c r="C199" s="14" t="inlineStr">
+        <is>
+          <t>no-data</t>
+        </is>
+      </c>
+      <c r="D199" s="14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E199" s="14" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F199" s="14" t="inlineStr"/>
+    </row>
+    <row r="200">
+      <c r="A200" s="9" t="inlineStr">
+        <is>
+          <t>STRATASYS LTD.</t>
+        </is>
+      </c>
+      <c r="B200" s="11" t="inlineStr">
+        <is>
+          <t>SSYS</t>
+        </is>
+      </c>
+      <c r="C200" s="11" t="inlineStr">
+        <is>
+          <t>AVOID (&lt;0%)</t>
+        </is>
+      </c>
+      <c r="D200" s="11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E200" s="11" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F200" s="11" t="inlineStr">
+        <is>
+          <t>EBIT/EV -9% → AVOID (&lt;0%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="12" t="inlineStr">
+        <is>
+          <t>Regional Management Corp.</t>
+        </is>
+      </c>
+      <c r="B201" s="14" t="inlineStr">
+        <is>
+          <t>RM</t>
+        </is>
+      </c>
+      <c r="C201" s="14" t="inlineStr">
+        <is>
+          <t>no-data</t>
+        </is>
+      </c>
+      <c r="D201" s="14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E201" s="14" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F201" s="14" t="inlineStr"/>
+    </row>
+    <row r="202">
+      <c r="A202" s="9" t="inlineStr">
+        <is>
+          <t>HomeTrust Bancshares, Inc.</t>
+        </is>
+      </c>
+      <c r="B202" s="11" t="inlineStr">
+        <is>
+          <t>HTB</t>
+        </is>
+      </c>
+      <c r="C202" s="11" t="inlineStr">
+        <is>
+          <t>no-data</t>
+        </is>
+      </c>
+      <c r="D202" s="11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E202" s="11" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F202" s="11" t="inlineStr"/>
+    </row>
+    <row r="203">
+      <c r="A203" s="12" t="inlineStr">
+        <is>
+          <t>PEMBINA PIPELINE CORP</t>
+        </is>
+      </c>
+      <c r="B203" s="14" t="inlineStr">
+        <is>
+          <t>PBA</t>
+        </is>
+      </c>
+      <c r="C203" s="14" t="inlineStr">
+        <is>
+          <t>no-data</t>
+        </is>
+      </c>
+      <c r="D203" s="14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E203" s="14" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F203" s="14" t="inlineStr"/>
+    </row>
+    <row r="204">
+      <c r="A204" s="9" t="inlineStr">
+        <is>
+          <t>PERRIGO Co plc</t>
+        </is>
+      </c>
+      <c r="B204" s="11" t="inlineStr">
+        <is>
+          <t>PRGO</t>
+        </is>
+      </c>
+      <c r="C204" s="11" t="inlineStr">
+        <is>
+          <t>AVOID (&lt;0%)</t>
+        </is>
+      </c>
+      <c r="D204" s="11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E204" s="11" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F204" s="11" t="inlineStr">
+        <is>
+          <t>EBIT/EV -17% → AVOID (&lt;0%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="12" t="inlineStr">
+        <is>
+          <t>Blue Bird Corp</t>
+        </is>
+      </c>
+      <c r="B205" s="14" t="inlineStr">
+        <is>
+          <t>BLBD</t>
+        </is>
+      </c>
+      <c r="C205" s="14" t="inlineStr">
+        <is>
+          <t>no-data</t>
+        </is>
+      </c>
+      <c r="D205" s="14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E205" s="14" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F205" s="14" t="inlineStr"/>
+    </row>
+    <row r="206">
+      <c r="A206" s="9" t="inlineStr">
+        <is>
+          <t>RAYONIER ADVANCED MATERIALS INC.</t>
+        </is>
+      </c>
+      <c r="B206" s="11" t="inlineStr">
+        <is>
+          <t>RYAM</t>
+        </is>
+      </c>
+      <c r="C206" s="11" t="inlineStr">
+        <is>
+          <t>no-data</t>
+        </is>
+      </c>
+      <c r="D206" s="11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E206" s="11" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F206" s="11" t="inlineStr"/>
+    </row>
+    <row r="207">
+      <c r="A207" s="12" t="inlineStr">
+        <is>
+          <t>Celcuity Inc.</t>
+        </is>
+      </c>
+      <c r="B207" s="14" t="inlineStr">
+        <is>
+          <t>CELC</t>
+        </is>
+      </c>
+      <c r="C207" s="14" t="inlineStr">
+        <is>
+          <t>no-data</t>
+        </is>
+      </c>
+      <c r="D207" s="14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E207" s="14" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F207" s="14" t="inlineStr"/>
+    </row>
+    <row r="208">
+      <c r="A208" s="9" t="inlineStr">
+        <is>
+          <t>GoDaddy Inc.</t>
+        </is>
+      </c>
+      <c r="B208" s="11" t="inlineStr">
+        <is>
+          <t>GDDY</t>
+        </is>
+      </c>
+      <c r="C208" s="11" t="inlineStr">
+        <is>
+          <t>no-data</t>
+        </is>
+      </c>
+      <c r="D208" s="11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E208" s="11" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F208" s="11" t="inlineStr"/>
+    </row>
+    <row r="209">
+      <c r="A209" s="12" t="inlineStr">
+        <is>
+          <t>Chemours Co</t>
+        </is>
+      </c>
+      <c r="B209" s="14" t="inlineStr">
+        <is>
+          <t>CC</t>
+        </is>
+      </c>
+      <c r="C209" s="14" t="inlineStr">
+        <is>
+          <t>no-data</t>
+        </is>
+      </c>
+      <c r="D209" s="14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E209" s="14" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F209" s="14" t="inlineStr"/>
+    </row>
+    <row r="210">
+      <c r="A210" s="9" t="inlineStr">
+        <is>
+          <t>Cushman &amp; Wakefield Ltd.</t>
+        </is>
+      </c>
+      <c r="B210" s="11" t="inlineStr">
+        <is>
+          <t>CWK</t>
+        </is>
+      </c>
+      <c r="C210" s="11" t="inlineStr">
+        <is>
+          <t>no-data</t>
+        </is>
+      </c>
+      <c r="D210" s="11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E210" s="11" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F210" s="11" t="inlineStr"/>
+    </row>
+    <row r="211">
+      <c r="A211" s="12" t="inlineStr">
+        <is>
+          <t>Flutter Entertainment plc</t>
+        </is>
+      </c>
+      <c r="B211" s="14" t="inlineStr">
+        <is>
+          <t>FLUT</t>
+        </is>
+      </c>
+      <c r="C211" s="14" t="inlineStr">
+        <is>
+          <t>no-data</t>
+        </is>
+      </c>
+      <c r="D211" s="14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E211" s="14" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F211" s="14" t="inlineStr"/>
+    </row>
+    <row r="212">
+      <c r="A212" s="9" t="inlineStr">
+        <is>
+          <t>Kraft Heinz Co</t>
+        </is>
+      </c>
+      <c r="B212" s="11" t="inlineStr">
+        <is>
+          <t>KHC</t>
+        </is>
+      </c>
+      <c r="C212" s="11" t="inlineStr">
+        <is>
+          <t>no-data</t>
+        </is>
+      </c>
+      <c r="D212" s="11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E212" s="11" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F212" s="11" t="inlineStr"/>
+    </row>
+    <row r="213">
+      <c r="A213" s="12" t="inlineStr">
+        <is>
+          <t>NovoCure Ltd</t>
+        </is>
+      </c>
+      <c r="B213" s="14" t="inlineStr">
+        <is>
+          <t>NVCR</t>
+        </is>
+      </c>
+      <c r="C213" s="14" t="inlineStr">
+        <is>
+          <t>no-data</t>
+        </is>
+      </c>
+      <c r="D213" s="14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E213" s="14" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F213" s="14" t="inlineStr"/>
+    </row>
+    <row r="214">
+      <c r="A214" s="9" t="inlineStr">
+        <is>
+          <t>BEYOND MEAT, INC.</t>
+        </is>
+      </c>
+      <c r="B214" s="11" t="inlineStr">
+        <is>
+          <t>BYND</t>
+        </is>
+      </c>
+      <c r="C214" s="11" t="inlineStr">
+        <is>
+          <t>AVOID (neg EBIT)</t>
+        </is>
+      </c>
+      <c r="D214" s="11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E214" s="11" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F214" s="11" t="inlineStr">
+        <is>
+          <t>EBIT NEGATIVE ($-334M); EV/price n/a</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="12" t="inlineStr">
+        <is>
+          <t>Ramaco Resources, Inc.</t>
+        </is>
+      </c>
+      <c r="B215" s="14" t="inlineStr">
+        <is>
+          <t>METC</t>
+        </is>
+      </c>
+      <c r="C215" s="14" t="inlineStr">
+        <is>
+          <t>AVOID (&lt;0%)</t>
+        </is>
+      </c>
+      <c r="D215" s="14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E215" s="14" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F215" s="14" t="inlineStr">
+        <is>
+          <t>EBIT/EV -8% → AVOID (&lt;0%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="9" t="inlineStr">
+        <is>
+          <t>TALOS ENERGY INC.</t>
+        </is>
+      </c>
+      <c r="B216" s="11" t="inlineStr">
+        <is>
+          <t>TALO</t>
+        </is>
+      </c>
+      <c r="C216" s="11" t="inlineStr">
+        <is>
+          <t>AVOID (&lt;0%)</t>
+        </is>
+      </c>
+      <c r="D216" s="11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E216" s="11" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F216" s="11" t="inlineStr">
+        <is>
+          <t>EBIT/EV -10% → AVOID (&lt;0%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="12" t="inlineStr">
+        <is>
+          <t>DOW INC.</t>
+        </is>
+      </c>
+      <c r="B217" s="14" t="inlineStr">
+        <is>
+          <t>DOW</t>
+        </is>
+      </c>
+      <c r="C217" s="14" t="inlineStr">
+        <is>
+          <t>no-data</t>
+        </is>
+      </c>
+      <c r="D217" s="14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E217" s="14" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F217" s="14" t="inlineStr"/>
+    </row>
+    <row r="218">
+      <c r="A218" s="9" t="inlineStr">
+        <is>
+          <t>Luminar Technologies, Inc./DE</t>
+        </is>
+      </c>
+      <c r="B218" s="11" t="inlineStr">
+        <is>
+          <t>LAZRQ</t>
+        </is>
+      </c>
+      <c r="C218" s="11" t="inlineStr">
+        <is>
+          <t>AVOID (neg EBIT)</t>
+        </is>
+      </c>
+      <c r="D218" s="11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E218" s="11" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F218" s="11" t="inlineStr">
+        <is>
+          <t>EBIT NEGATIVE ($-297M); EV/price n/a</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="12" t="inlineStr">
+        <is>
+          <t>SeeQC, Inc.</t>
+        </is>
+      </c>
+      <c r="B219" s="14" t="inlineStr">
+        <is>
+          <t>SEQC</t>
+        </is>
+      </c>
+      <c r="C219" s="14" t="inlineStr">
+        <is>
+          <t>no-data</t>
+        </is>
+      </c>
+      <c r="D219" s="14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E219" s="14" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F219" s="14" t="inlineStr"/>
+    </row>
+    <row r="220">
+      <c r="A220" s="9" t="inlineStr">
+        <is>
+          <t>Third Coast Bancshares, Inc.</t>
+        </is>
+      </c>
+      <c r="B220" s="11" t="inlineStr">
+        <is>
+          <t>TCBX</t>
+        </is>
+      </c>
+      <c r="C220" s="11" t="inlineStr">
+        <is>
+          <t>no-data</t>
+        </is>
+      </c>
+      <c r="D220" s="11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E220" s="11" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F220" s="11" t="inlineStr"/>
+    </row>
+    <row r="221">
+      <c r="A221" s="12" t="inlineStr">
+        <is>
+          <t>Woodbridge Liquidation Trust</t>
+        </is>
+      </c>
+      <c r="B221" s="14" t="inlineStr">
+        <is>
+          <t>WBQNL</t>
+        </is>
+      </c>
+      <c r="C221" s="14" t="inlineStr">
+        <is>
+          <t>no-data</t>
+        </is>
+      </c>
+      <c r="D221" s="14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E221" s="14" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F221" s="14" t="inlineStr"/>
+    </row>
+    <row r="222">
+      <c r="A222" s="9" t="inlineStr">
+        <is>
+          <t>Wheels Up Experience Inc.</t>
+        </is>
+      </c>
+      <c r="B222" s="11" t="inlineStr">
+        <is>
+          <t>UP</t>
+        </is>
+      </c>
+      <c r="C222" s="11" t="inlineStr">
+        <is>
+          <t>AVOID (&lt;0%)</t>
+        </is>
+      </c>
+      <c r="D222" s="11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E222" s="11" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F222" s="11" t="inlineStr">
+        <is>
+          <t>EBIT/EV -3% → AVOID (&lt;0%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="12" t="inlineStr">
+        <is>
+          <t>Dave Inc./DE</t>
+        </is>
+      </c>
+      <c r="B223" s="14" t="inlineStr">
+        <is>
+          <t>DAVE</t>
+        </is>
+      </c>
+      <c r="C223" s="14" t="inlineStr">
+        <is>
+          <t>AVOID (neg EBIT)</t>
+        </is>
+      </c>
+      <c r="D223" s="14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E223" s="14" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F223" s="14" t="inlineStr">
+        <is>
+          <t>EBIT NEGATIVE ($-6M); EV/price n/a</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="9" t="inlineStr">
+        <is>
+          <t>FLYEXCLUSIVE INC.</t>
+        </is>
+      </c>
+      <c r="B224" s="11" t="inlineStr">
+        <is>
+          <t>FLYX</t>
+        </is>
+      </c>
+      <c r="C224" s="11" t="inlineStr">
+        <is>
+          <t>AVOID (neg EBIT)</t>
+        </is>
+      </c>
+      <c r="D224" s="11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E224" s="11" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F224" s="11" t="inlineStr">
+        <is>
+          <t>EBIT NEGATIVE ($-47M); EV/price n/a</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="12" t="inlineStr">
+        <is>
+          <t>Liftoff Mobile, Inc.</t>
+        </is>
+      </c>
+      <c r="B225" s="14" t="inlineStr"/>
+      <c r="C225" s="14" t="inlineStr">
+        <is>
+          <t>no-data</t>
+        </is>
+      </c>
+      <c r="D225" s="14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E225" s="14" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F225" s="14" t="inlineStr"/>
+    </row>
+    <row r="226">
+      <c r="A226" s="9" t="inlineStr">
+        <is>
+          <t>Finwise Bancorp</t>
+        </is>
+      </c>
+      <c r="B226" s="11" t="inlineStr">
+        <is>
+          <t>FINW</t>
+        </is>
+      </c>
+      <c r="C226" s="11" t="inlineStr">
+        <is>
+          <t>no-data</t>
+        </is>
+      </c>
+      <c r="D226" s="11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E226" s="11" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F226" s="11" t="inlineStr"/>
+    </row>
+    <row r="227">
+      <c r="A227" s="12" t="inlineStr">
+        <is>
+          <t>Angel Studios, Inc.</t>
+        </is>
+      </c>
+      <c r="B227" s="14" t="inlineStr">
+        <is>
+          <t>ANGX</t>
+        </is>
+      </c>
+      <c r="C227" s="14" t="inlineStr">
+        <is>
+          <t>AVOID (neg EBIT)</t>
+        </is>
+      </c>
+      <c r="D227" s="14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E227" s="14" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F227" s="14" t="inlineStr">
+        <is>
+          <t>EBIT NEGATIVE ($-164M); EV/price n/a</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="9" t="inlineStr">
+        <is>
+          <t>Wallbox N.V.</t>
+        </is>
+      </c>
+      <c r="B228" s="11" t="inlineStr">
+        <is>
+          <t>WBX</t>
+        </is>
+      </c>
+      <c r="C228" s="11" t="inlineStr">
+        <is>
+          <t>no-data</t>
+        </is>
+      </c>
+      <c r="D228" s="11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E228" s="11" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F228" s="11" t="inlineStr"/>
+    </row>
+    <row r="229">
+      <c r="A229" s="12" t="inlineStr">
+        <is>
+          <t>RXO, Inc.</t>
+        </is>
+      </c>
+      <c r="B229" s="14" t="inlineStr">
+        <is>
+          <t>RXO</t>
+        </is>
+      </c>
+      <c r="C229" s="14" t="inlineStr">
+        <is>
+          <t>AVOID (&lt;0%)</t>
+        </is>
+      </c>
+      <c r="D229" s="14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E229" s="14" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F229" s="14" t="inlineStr">
+        <is>
+          <t>EBIT/EV -2% → AVOID (&lt;0%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="9" t="inlineStr">
+        <is>
+          <t>Zymeworks Inc.</t>
+        </is>
+      </c>
+      <c r="B230" s="11" t="inlineStr">
+        <is>
+          <t>ZYME</t>
+        </is>
+      </c>
+      <c r="C230" s="11" t="inlineStr">
+        <is>
+          <t>AVOID (&lt;0%)</t>
+        </is>
+      </c>
+      <c r="D230" s="11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E230" s="11" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F230" s="11" t="inlineStr">
+        <is>
+          <t>EBIT/EV -5% → AVOID (&lt;0%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="12" t="inlineStr">
+        <is>
+          <t>KKR Infrastructure Conglomerate LL</t>
+        </is>
+      </c>
+      <c r="B231" s="14" t="inlineStr"/>
+      <c r="C231" s="14" t="inlineStr">
+        <is>
+          <t>no-data</t>
+        </is>
+      </c>
+      <c r="D231" s="14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E231" s="14" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F231" s="14" t="inlineStr"/>
+    </row>
+    <row r="232">
+      <c r="A232" s="9" t="inlineStr">
+        <is>
+          <t>KKR Private Equity Conglomerate LL</t>
+        </is>
+      </c>
+      <c r="B232" s="11" t="inlineStr"/>
+      <c r="C232" s="11" t="inlineStr">
+        <is>
+          <t>no-data</t>
+        </is>
+      </c>
+      <c r="D232" s="11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E232" s="11" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F232" s="11" t="inlineStr"/>
+    </row>
+    <row r="233">
+      <c r="A233" s="12" t="inlineStr">
+        <is>
+          <t>Ionic Digital Inc.</t>
+        </is>
+      </c>
+      <c r="B233" s="14" t="inlineStr"/>
+      <c r="C233" s="14" t="inlineStr">
+        <is>
+          <t>no-data</t>
+        </is>
+      </c>
+      <c r="D233" s="14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E233" s="14" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F233" s="14" t="inlineStr"/>
+    </row>
+    <row r="234">
+      <c r="A234" s="9" t="inlineStr">
+        <is>
+          <t>Fortress Private Lending Fund</t>
+        </is>
+      </c>
+      <c r="B234" s="11" t="inlineStr"/>
+      <c r="C234" s="11" t="inlineStr">
+        <is>
+          <t>no-data</t>
+        </is>
+      </c>
+      <c r="D234" s="11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E234" s="11" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F234" s="11" t="inlineStr"/>
+    </row>
+    <row r="235">
+      <c r="A235" s="12" t="inlineStr">
+        <is>
+          <t>GigCapital7 Corp.</t>
+        </is>
+      </c>
+      <c r="B235" s="14" t="inlineStr">
+        <is>
+          <t>GIG</t>
+        </is>
+      </c>
+      <c r="C235" s="14" t="inlineStr">
+        <is>
+          <t>AVOID (&lt;0%)</t>
+        </is>
+      </c>
+      <c r="D235" s="14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E235" s="14" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F235" s="14" t="inlineStr">
+        <is>
+          <t>EBIT/EV -3% → AVOID (&lt;0%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="9" t="inlineStr">
+        <is>
+          <t>EQT Infrastructure Co LLC</t>
+        </is>
+      </c>
+      <c r="B236" s="11" t="inlineStr"/>
+      <c r="C236" s="11" t="inlineStr">
+        <is>
+          <t>positive-EBIT</t>
+        </is>
+      </c>
+      <c r="D236" s="11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E236" s="11" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F236" s="11" t="inlineStr">
+        <is>
+          <t>EBIT NEGATIVE ($0M); EV/price n/a</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="12" t="inlineStr">
+        <is>
+          <t>Teamshares Inc</t>
+        </is>
+      </c>
+      <c r="B237" s="14" t="inlineStr">
+        <is>
+          <t>LOKV</t>
+        </is>
+      </c>
+      <c r="C237" s="14" t="inlineStr">
+        <is>
+          <t>AVOID (neg EBIT)</t>
+        </is>
+      </c>
+      <c r="D237" s="14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E237" s="14" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F237" s="14" t="inlineStr">
+        <is>
+          <t>EBIT NEGATIVE ($-9M); EV/price n/a</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="9" t="inlineStr">
+        <is>
+          <t>Cartesian Growth Corp III</t>
+        </is>
+      </c>
+      <c r="B238" s="11" t="inlineStr">
+        <is>
+          <t>CGCT</t>
+        </is>
+      </c>
+      <c r="C238" s="11" t="inlineStr">
+        <is>
+          <t>AVOID (neg EBIT)</t>
+        </is>
+      </c>
+      <c r="D238" s="11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E238" s="11" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F238" s="11" t="inlineStr">
+        <is>
+          <t>EBIT NEGATIVE ($-1M); EV/price n/a</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="12" t="inlineStr">
+        <is>
+          <t>Solstice Advanced Materials Inc.</t>
+        </is>
+      </c>
+      <c r="B239" s="14" t="inlineStr">
+        <is>
+          <t>SOLS</t>
+        </is>
+      </c>
+      <c r="C239" s="14" t="inlineStr">
+        <is>
+          <t>no-data</t>
+        </is>
+      </c>
+      <c r="D239" s="14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E239" s="14" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F239" s="14" t="inlineStr"/>
+    </row>
+    <row r="240">
+      <c r="A240" s="9" t="inlineStr">
+        <is>
+          <t>Matternet, Inc.</t>
+        </is>
+      </c>
+      <c r="B240" s="11" t="inlineStr"/>
+      <c r="C240" s="11" t="inlineStr">
+        <is>
+          <t>AVOID (neg EBIT)</t>
+        </is>
+      </c>
+      <c r="D240" s="11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E240" s="11" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F240" s="11" t="inlineStr">
+        <is>
+          <t>EBIT NEGATIVE ($-0M); EV/price n/a</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="12" t="inlineStr">
+        <is>
+          <t>FedEx Freight Holding Company, Inc</t>
+        </is>
+      </c>
+      <c r="B241" s="14" t="inlineStr">
+        <is>
+          <t>FDXF</t>
+        </is>
+      </c>
+      <c r="C241" s="14" t="inlineStr">
+        <is>
+          <t>no-data</t>
+        </is>
+      </c>
+      <c r="D241" s="14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E241" s="14" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F241" s="14" t="inlineStr"/>
+    </row>
+    <row r="242">
+      <c r="A242" s="9" t="inlineStr">
+        <is>
+          <t>Elemental Royalty Corp</t>
+        </is>
+      </c>
+      <c r="B242" s="11" t="inlineStr">
+        <is>
+          <t>ELE</t>
+        </is>
+      </c>
+      <c r="C242" s="11" t="inlineStr">
+        <is>
+          <t>no-data</t>
+        </is>
+      </c>
+      <c r="D242" s="11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E242" s="11" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F242" s="11" t="inlineStr"/>
+    </row>
+    <row r="243">
+      <c r="A243" s="12" t="inlineStr">
+        <is>
+          <t>EagleRock Land, LLC</t>
+        </is>
+      </c>
+      <c r="B243" s="14" t="inlineStr"/>
+      <c r="C243" s="14" t="inlineStr">
+        <is>
+          <t>no-data</t>
+        </is>
+      </c>
+      <c r="D243" s="14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E243" s="14" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F243" s="14" t="inlineStr"/>
+    </row>
+    <row r="244">
+      <c r="A244" s="9" t="inlineStr">
+        <is>
+          <t>Csquare, Inc.</t>
+        </is>
+      </c>
+      <c r="B244" s="11" t="inlineStr"/>
+      <c r="C244" s="11" t="inlineStr">
+        <is>
+          <t>no-data</t>
+        </is>
+      </c>
+      <c r="D244" s="11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E244" s="11" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F244" s="11" t="inlineStr"/>
+    </row>
+    <row r="245">
+      <c r="A245" s="12" t="inlineStr">
+        <is>
+          <t>Ionetix Corp / DE /</t>
+        </is>
+      </c>
+      <c r="B245" s="14" t="inlineStr"/>
+      <c r="C245" s="14" t="inlineStr">
+        <is>
+          <t>no-data</t>
+        </is>
+      </c>
+      <c r="D245" s="14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E245" s="14" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F245" s="14" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/output/cyclepapa_risk_reward_workbook.xlsx
+++ b/output/cyclepapa_risk_reward_workbook.xlsx
@@ -617,7 +617,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Generated 2026-07-21</t>
+          <t>Generated 2026-07-22</t>
         </is>
       </c>
     </row>
@@ -2487,7 +2487,7 @@
       </c>
       <c r="M30" s="11" t="inlineStr">
         <is>
-          <t>low leverage (ND/EBIT 2.7×); EBIT/EV 25% (PRIORITY (&gt;20%))</t>
+          <t>low leverage (ND/EBIT 2.7×); EBIT/EV 24% (PRIORITY (&gt;20%))</t>
         </is>
       </c>
     </row>
@@ -3023,7 +3023,7 @@
       </c>
       <c r="M38" s="11" t="inlineStr">
         <is>
-          <t>EBIT/EV 5% (neutral (0-20%))</t>
+          <t>EBIT/EV 4% (neutral (0-20%))</t>
         </is>
       </c>
     </row>
@@ -4162,7 +4162,7 @@
       </c>
       <c r="M55" s="14" t="inlineStr">
         <is>
-          <t>filer emerged August 7, 2023 (~35mo ago) — overhang likely clear</t>
+          <t>filer emerged August 7, 2023 (~36mo ago) — overhang likely clear</t>
         </is>
       </c>
     </row>

--- a/output/cyclepapa_risk_reward_workbook.xlsx
+++ b/output/cyclepapa_risk_reward_workbook.xlsx
@@ -709,11 +709,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M71"/>
+  <dimension ref="A1:M88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
-    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
     <col width="50" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="8" customWidth="1" min="5" max="5"/>
@@ -1958,17 +1958,17 @@
     <row r="23">
       <c r="A23" s="12" t="inlineStr">
         <is>
-          <t>California Resources Corp</t>
+          <t>Warrior Met Coal</t>
         </is>
       </c>
       <c r="B23" s="14" t="inlineStr">
         <is>
-          <t>CRC</t>
+          <t>NYSE:HCC</t>
         </is>
       </c>
       <c r="C23" s="14" t="inlineStr">
         <is>
-          <t>~</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="D23" s="14" t="inlineStr">
@@ -2018,19 +2018,19 @@
       </c>
       <c r="M23" s="14" t="inlineStr">
         <is>
-          <t>low leverage (ND/EBIT 2.3×); EBIT/EV 13% (neutral (0-20%))</t>
+          <t>net cash balance sheet; EBIT/EV 1% (neutral (0-20%))</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="9" t="inlineStr">
         <is>
-          <t>INFINITY NATURAL RESOURCES, IN</t>
+          <t>California Resources Corp</t>
         </is>
       </c>
       <c r="B24" s="11" t="inlineStr">
         <is>
-          <t>INR</t>
+          <t>CRC</t>
         </is>
       </c>
       <c r="C24" s="11" t="inlineStr">
@@ -2050,7 +2050,7 @@
       </c>
       <c r="F24" s="11" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>deep</t>
         </is>
       </c>
       <c r="G24" s="11" t="inlineStr">
@@ -2085,19 +2085,19 @@
       </c>
       <c r="M24" s="11" t="inlineStr">
         <is>
-          <t>low leverage (ND/EBIT 0.7×); positive EBIT</t>
+          <t>low leverage (ND/EBIT 2.3×); EBIT/EV 13% (neutral (0-20%))</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="12" t="inlineStr">
         <is>
-          <t>Jefferies Financial Group Inc.</t>
+          <t>INFINITY NATURAL RESOURCES, IN</t>
         </is>
       </c>
       <c r="B25" s="14" t="inlineStr">
         <is>
-          <t>JEF</t>
+          <t>INR</t>
         </is>
       </c>
       <c r="C25" s="14" t="inlineStr">
@@ -2117,7 +2117,7 @@
       </c>
       <c r="F25" s="14" t="inlineStr">
         <is>
-          <t>deep</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="G25" s="14" t="inlineStr">
@@ -2132,39 +2132,39 @@
       </c>
       <c r="I25" s="14" t="inlineStr">
         <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="J25" s="14" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K25" s="14" t="inlineStr">
+        <is>
           <t>●</t>
         </is>
       </c>
-      <c r="J25" s="14" t="inlineStr">
-        <is>
-          <t>·</t>
-        </is>
-      </c>
-      <c r="K25" s="14" t="inlineStr">
-        <is>
-          <t>·</t>
-        </is>
-      </c>
       <c r="L25" s="14" t="inlineStr">
         <is>
-          <t>excess-emergence-cash</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M25" s="14" t="inlineStr">
         <is>
-          <t>net cash balance sheet; net cash = 106% of mkt cap (net-debt bur</t>
+          <t>low leverage (ND/EBIT 0.7×); positive EBIT</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="9" t="inlineStr">
         <is>
-          <t>GULFPORT ENERGY CORP</t>
+          <t>Jefferies Financial Group Inc.</t>
         </is>
       </c>
       <c r="B26" s="11" t="inlineStr">
         <is>
-          <t>GPOR</t>
+          <t>JEF</t>
         </is>
       </c>
       <c r="C26" s="11" t="inlineStr">
@@ -2199,39 +2199,39 @@
       </c>
       <c r="I26" s="11" t="inlineStr">
         <is>
+          <t>●</t>
+        </is>
+      </c>
+      <c r="J26" s="11" t="inlineStr">
+        <is>
           <t>·</t>
         </is>
       </c>
-      <c r="J26" s="11" t="inlineStr">
+      <c r="K26" s="11" t="inlineStr">
         <is>
           <t>·</t>
         </is>
       </c>
-      <c r="K26" s="11" t="inlineStr">
-        <is>
-          <t>●</t>
-        </is>
-      </c>
       <c r="L26" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>excess-emergence-cash</t>
         </is>
       </c>
       <c r="M26" s="11" t="inlineStr">
         <is>
-          <t>low leverage (ND/EBIT 1.3×); EBIT/EV 15% (neutral (0-20%))</t>
+          <t>net cash balance sheet; net cash = 106% of mkt cap (net-debt bur</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="12" t="inlineStr">
         <is>
-          <t>AGCO CORP /DE</t>
+          <t>GULFPORT ENERGY CORP</t>
         </is>
       </c>
       <c r="B27" s="14" t="inlineStr">
         <is>
-          <t>AGCO</t>
+          <t>GPOR</t>
         </is>
       </c>
       <c r="C27" s="14" t="inlineStr">
@@ -2286,19 +2286,19 @@
       </c>
       <c r="M27" s="14" t="inlineStr">
         <is>
-          <t>low leverage (ND/EBIT 3.0×); EBIT/EV 4% (neutral (0-20%))</t>
+          <t>low leverage (ND/EBIT 1.3×); EBIT/EV 15% (neutral (0-20%))</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="9" t="inlineStr">
         <is>
-          <t>Bristow Group Inc.</t>
+          <t>AGCO CORP /DE</t>
         </is>
       </c>
       <c r="B28" s="11" t="inlineStr">
         <is>
-          <t>VTOL</t>
+          <t>AGCO</t>
         </is>
       </c>
       <c r="C28" s="11" t="inlineStr">
@@ -2353,19 +2353,19 @@
       </c>
       <c r="M28" s="11" t="inlineStr">
         <is>
-          <t>low leverage (ND/EBIT 2.7×); EBIT/EV 7% (neutral (0-20%))</t>
+          <t>low leverage (ND/EBIT 3.0×); EBIT/EV 4% (neutral (0-20%))</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="12" t="inlineStr">
         <is>
-          <t>RMR GROUP INC.</t>
+          <t>Bristow Group Inc.</t>
         </is>
       </c>
       <c r="B29" s="14" t="inlineStr">
         <is>
-          <t>RMR</t>
+          <t>VTOL</t>
         </is>
       </c>
       <c r="C29" s="14" t="inlineStr">
@@ -2385,7 +2385,7 @@
       </c>
       <c r="F29" s="14" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>deep</t>
         </is>
       </c>
       <c r="G29" s="14" t="inlineStr">
@@ -2420,19 +2420,19 @@
       </c>
       <c r="M29" s="14" t="inlineStr">
         <is>
-          <t>net cash balance sheet; positive EBIT</t>
+          <t>low leverage (ND/EBIT 2.7×); EBIT/EV 7% (neutral (0-20%))</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="9" t="inlineStr">
         <is>
-          <t>APA Corp</t>
+          <t>RMR GROUP INC.</t>
         </is>
       </c>
       <c r="B30" s="11" t="inlineStr">
         <is>
-          <t>APA</t>
+          <t>RMR</t>
         </is>
       </c>
       <c r="C30" s="11" t="inlineStr">
@@ -2452,7 +2452,7 @@
       </c>
       <c r="F30" s="11" t="inlineStr">
         <is>
-          <t>deep</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="G30" s="11" t="inlineStr">
@@ -2487,86 +2487,86 @@
       </c>
       <c r="M30" s="11" t="inlineStr">
         <is>
-          <t>low leverage (ND/EBIT 2.7×); EBIT/EV 24% (PRIORITY (&gt;20%))</t>
+          <t>net cash balance sheet; positive EBIT</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="12" t="inlineStr">
         <is>
-          <t>WW INTERNATIONAL, INC.</t>
+          <t>APA Corp</t>
         </is>
       </c>
       <c r="B31" s="14" t="inlineStr">
         <is>
-          <t>WW</t>
+          <t>APA</t>
         </is>
       </c>
       <c r="C31" s="14" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>~</t>
         </is>
       </c>
       <c r="D31" s="14" t="inlineStr">
         <is>
-          <t>December 31, 2025</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E31" s="14" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="F31" s="14" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>deep</t>
         </is>
       </c>
       <c r="G31" s="14" t="inlineStr">
         <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="H31" s="14" t="inlineStr">
+        <is>
           <t>●</t>
         </is>
       </c>
-      <c r="H31" s="14" t="inlineStr">
+      <c r="I31" s="14" t="inlineStr">
         <is>
           <t>·</t>
         </is>
       </c>
-      <c r="I31" s="14" t="inlineStr">
+      <c r="J31" s="14" t="inlineStr">
         <is>
           <t>·</t>
         </is>
       </c>
-      <c r="J31" s="14" t="inlineStr">
-        <is>
-          <t>·</t>
-        </is>
-      </c>
       <c r="K31" s="14" t="inlineStr">
         <is>
-          <t>·</t>
+          <t>●</t>
         </is>
       </c>
       <c r="L31" s="14" t="inlineStr">
         <is>
-          <t>forced-creditor overhang</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M31" s="14" t="inlineStr">
         <is>
-          <t>filer emerged December 31, 2025 (~7mo ago) — live forced-seller</t>
+          <t>low leverage (ND/EBIT 2.7×); EBIT/EV 24% (PRIORITY (&gt;20%))</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="9" t="inlineStr">
         <is>
-          <t>WOLFSPEED, INC.</t>
+          <t>WW INTERNATIONAL, INC.</t>
         </is>
       </c>
       <c r="B32" s="11" t="inlineStr">
         <is>
-          <t>WOLF</t>
+          <t>WW</t>
         </is>
       </c>
       <c r="C32" s="11" t="inlineStr">
@@ -2576,7 +2576,7 @@
       </c>
       <c r="D32" s="11" t="inlineStr">
         <is>
-          <t>January 29, 2026</t>
+          <t>December 31, 2025</t>
         </is>
       </c>
       <c r="E32" s="11" t="inlineStr">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="F32" s="11" t="inlineStr">
         <is>
-          <t>deep</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="G32" s="11" t="inlineStr">
@@ -2621,19 +2621,19 @@
       </c>
       <c r="M32" s="11" t="inlineStr">
         <is>
-          <t>filer emerged January 29, 2026 (~6mo ago) — live forced-seller o</t>
+          <t>filer emerged December 31, 2025 (~7mo ago) — live forced-seller</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="12" t="inlineStr">
         <is>
-          <t>GOLAR LNG LTD</t>
+          <t>WOLFSPEED, INC.</t>
         </is>
       </c>
       <c r="B33" s="14" t="inlineStr">
         <is>
-          <t>GLNG</t>
+          <t>WOLF</t>
         </is>
       </c>
       <c r="C33" s="14" t="inlineStr">
@@ -2643,7 +2643,7 @@
       </c>
       <c r="D33" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>January 29, 2026</t>
         </is>
       </c>
       <c r="E33" s="14" t="inlineStr">
@@ -2658,49 +2658,49 @@
       </c>
       <c r="G33" s="14" t="inlineStr">
         <is>
+          <t>●</t>
+        </is>
+      </c>
+      <c r="H33" s="14" t="inlineStr">
+        <is>
           <t>·</t>
         </is>
       </c>
-      <c r="H33" s="14" t="inlineStr">
+      <c r="I33" s="14" t="inlineStr">
         <is>
           <t>·</t>
         </is>
       </c>
-      <c r="I33" s="14" t="inlineStr">
+      <c r="J33" s="14" t="inlineStr">
         <is>
           <t>·</t>
         </is>
       </c>
-      <c r="J33" s="14" t="inlineStr">
+      <c r="K33" s="14" t="inlineStr">
         <is>
           <t>·</t>
         </is>
       </c>
-      <c r="K33" s="14" t="inlineStr">
-        <is>
-          <t>●</t>
-        </is>
-      </c>
       <c r="L33" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>forced-creditor overhang</t>
         </is>
       </c>
       <c r="M33" s="14" t="inlineStr">
         <is>
-          <t>EBIT/EV 1% (neutral (0-20%))</t>
+          <t>filer emerged January 29, 2026 (~6mo ago) — live forced-seller o</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="9" t="inlineStr">
         <is>
-          <t>Nine Energy Service, Inc.</t>
+          <t>GOLAR LNG LTD</t>
         </is>
       </c>
       <c r="B34" s="11" t="inlineStr">
         <is>
-          <t>NINE</t>
+          <t>GLNG</t>
         </is>
       </c>
       <c r="C34" s="11" t="inlineStr">
@@ -2720,7 +2720,7 @@
       </c>
       <c r="F34" s="11" t="inlineStr">
         <is>
-          <t>thin</t>
+          <t>deep</t>
         </is>
       </c>
       <c r="G34" s="11" t="inlineStr">
@@ -2755,19 +2755,19 @@
       </c>
       <c r="M34" s="11" t="inlineStr">
         <is>
-          <t>EBIT/EV 0% (neutral (0-20%))</t>
+          <t>EBIT/EV 1% (neutral (0-20%))</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="12" t="inlineStr">
         <is>
-          <t>Red Rock Resorts, Inc.</t>
+          <t>Nine Energy Service, Inc.</t>
         </is>
       </c>
       <c r="B35" s="14" t="inlineStr">
         <is>
-          <t>RRR</t>
+          <t>NINE</t>
         </is>
       </c>
       <c r="C35" s="14" t="inlineStr">
@@ -2777,7 +2777,7 @@
       </c>
       <c r="D35" s="14" t="inlineStr">
         <is>
-          <t>2011</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E35" s="14" t="inlineStr">
@@ -2787,7 +2787,7 @@
       </c>
       <c r="F35" s="14" t="inlineStr">
         <is>
-          <t>deep</t>
+          <t>thin</t>
         </is>
       </c>
       <c r="G35" s="14" t="inlineStr">
@@ -2822,19 +2822,19 @@
       </c>
       <c r="M35" s="14" t="inlineStr">
         <is>
-          <t>filer emerged 2011 (~181mo ago) — overhang likely cleared; posit</t>
+          <t>EBIT/EV 0% (neutral (0-20%))</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="9" t="inlineStr">
         <is>
-          <t>SEADRILL Ltd</t>
+          <t>Red Rock Resorts, Inc.</t>
         </is>
       </c>
       <c r="B36" s="11" t="inlineStr">
         <is>
-          <t>SDRL</t>
+          <t>RRR</t>
         </is>
       </c>
       <c r="C36" s="11" t="inlineStr">
@@ -2844,7 +2844,7 @@
       </c>
       <c r="D36" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2011</t>
         </is>
       </c>
       <c r="E36" s="11" t="inlineStr">
@@ -2889,19 +2889,19 @@
       </c>
       <c r="M36" s="11" t="inlineStr">
         <is>
-          <t>EBIT/EV 2% (neutral (0-20%))</t>
+          <t>filer emerged 2011 (~181mo ago) — overhang likely cleared; posit</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="12" t="inlineStr">
         <is>
-          <t>Phoenix Energy One, LLC</t>
+          <t>SEADRILL Ltd</t>
         </is>
       </c>
       <c r="B37" s="14" t="inlineStr">
         <is>
-          <t>PHXE-P</t>
+          <t>SDRL</t>
         </is>
       </c>
       <c r="C37" s="14" t="inlineStr">
@@ -2921,7 +2921,7 @@
       </c>
       <c r="F37" s="14" t="inlineStr">
         <is>
-          <t>thin</t>
+          <t>deep</t>
         </is>
       </c>
       <c r="G37" s="14" t="inlineStr">
@@ -2956,19 +2956,19 @@
       </c>
       <c r="M37" s="14" t="inlineStr">
         <is>
-          <t>EBIT/EV 4% (neutral (0-20%))</t>
+          <t>EBIT/EV 2% (neutral (0-20%))</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="9" t="inlineStr">
         <is>
-          <t>Noble Corp plc</t>
+          <t>Phoenix Energy One, LLC</t>
         </is>
       </c>
       <c r="B38" s="11" t="inlineStr">
         <is>
-          <t>NE</t>
+          <t>PHXE-P</t>
         </is>
       </c>
       <c r="C38" s="11" t="inlineStr">
@@ -2988,7 +2988,7 @@
       </c>
       <c r="F38" s="11" t="inlineStr">
         <is>
-          <t>deep</t>
+          <t>thin</t>
         </is>
       </c>
       <c r="G38" s="11" t="inlineStr">
@@ -3030,12 +3030,12 @@
     <row r="39">
       <c r="A39" s="12" t="inlineStr">
         <is>
-          <t>CLEVELAND-CLIFFS INC.</t>
+          <t>Noble Corp plc</t>
         </is>
       </c>
       <c r="B39" s="14" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>NE</t>
         </is>
       </c>
       <c r="C39" s="14" t="inlineStr">
@@ -3045,7 +3045,7 @@
       </c>
       <c r="D39" s="14" t="inlineStr">
         <is>
-          <t>2042</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E39" s="14" t="inlineStr">
@@ -3060,49 +3060,49 @@
       </c>
       <c r="G39" s="14" t="inlineStr">
         <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="H39" s="14" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="I39" s="14" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="J39" s="14" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K39" s="14" t="inlineStr">
+        <is>
           <t>●</t>
         </is>
       </c>
-      <c r="H39" s="14" t="inlineStr">
-        <is>
-          <t>·</t>
-        </is>
-      </c>
-      <c r="I39" s="14" t="inlineStr">
-        <is>
-          <t>·</t>
-        </is>
-      </c>
-      <c r="J39" s="14" t="inlineStr">
-        <is>
-          <t>·</t>
-        </is>
-      </c>
-      <c r="K39" s="14" t="inlineStr">
-        <is>
-          <t>·</t>
-        </is>
-      </c>
       <c r="L39" s="14" t="inlineStr">
         <is>
-          <t>forced-creditor overhang</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M39" s="14" t="inlineStr">
         <is>
-          <t>filer emerged 2042 (~-192mo ago) — live forced-seller overhang</t>
+          <t>EBIT/EV 4% (neutral (0-20%))</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="9" t="inlineStr">
         <is>
-          <t>Capstone Green Energy Holdings</t>
+          <t>CLEVELAND-CLIFFS INC.</t>
         </is>
       </c>
       <c r="B40" s="11" t="inlineStr">
         <is>
-          <t>CGEH</t>
+          <t>CLF</t>
         </is>
       </c>
       <c r="C40" s="11" t="inlineStr">
@@ -3112,7 +3112,7 @@
       </c>
       <c r="D40" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2042</t>
         </is>
       </c>
       <c r="E40" s="11" t="inlineStr">
@@ -3122,54 +3122,54 @@
       </c>
       <c r="F40" s="11" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>deep</t>
         </is>
       </c>
       <c r="G40" s="11" t="inlineStr">
         <is>
+          <t>●</t>
+        </is>
+      </c>
+      <c r="H40" s="11" t="inlineStr">
+        <is>
           <t>·</t>
         </is>
       </c>
-      <c r="H40" s="11" t="inlineStr">
+      <c r="I40" s="11" t="inlineStr">
         <is>
           <t>·</t>
         </is>
       </c>
-      <c r="I40" s="11" t="inlineStr">
+      <c r="J40" s="11" t="inlineStr">
         <is>
           <t>·</t>
         </is>
       </c>
-      <c r="J40" s="11" t="inlineStr">
+      <c r="K40" s="11" t="inlineStr">
         <is>
           <t>·</t>
         </is>
       </c>
-      <c r="K40" s="11" t="inlineStr">
-        <is>
-          <t>●</t>
-        </is>
-      </c>
       <c r="L40" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>forced-creditor overhang</t>
         </is>
       </c>
       <c r="M40" s="11" t="inlineStr">
         <is>
-          <t>EBIT/EV 1% (neutral (0-20%))</t>
+          <t>filer emerged 2042 (~-192mo ago) — live forced-seller overhang</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="12" t="inlineStr">
         <is>
-          <t>NEXSTAR MEDIA GROUP, INC.</t>
+          <t>Capstone Green Energy Holdings</t>
         </is>
       </c>
       <c r="B41" s="14" t="inlineStr">
         <is>
-          <t>NXST</t>
+          <t>CGEH</t>
         </is>
       </c>
       <c r="C41" s="14" t="inlineStr">
@@ -3189,7 +3189,7 @@
       </c>
       <c r="F41" s="14" t="inlineStr">
         <is>
-          <t>deep</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="G41" s="14" t="inlineStr">
@@ -3224,19 +3224,19 @@
       </c>
       <c r="M41" s="14" t="inlineStr">
         <is>
-          <t>EBIT/EV 6% (neutral (0-20%))</t>
+          <t>EBIT/EV 1% (neutral (0-20%))</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="9" t="inlineStr">
         <is>
-          <t>TruBridge, Inc.</t>
+          <t>NEXSTAR MEDIA GROUP, INC.</t>
         </is>
       </c>
       <c r="B42" s="11" t="inlineStr">
         <is>
-          <t>TBRG</t>
+          <t>NXST</t>
         </is>
       </c>
       <c r="C42" s="11" t="inlineStr">
@@ -3246,7 +3246,7 @@
       </c>
       <c r="D42" s="11" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E42" s="11" t="inlineStr">
@@ -3291,19 +3291,19 @@
       </c>
       <c r="M42" s="11" t="inlineStr">
         <is>
-          <t>filer emerged 2020 (~73mo ago) — overhang likely cleared; EBIT/E</t>
+          <t>EBIT/EV 6% (neutral (0-20%))</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="12" t="inlineStr">
         <is>
-          <t>Clean Energy Fuels Corp.</t>
+          <t>TruBridge, Inc.</t>
         </is>
       </c>
       <c r="B43" s="14" t="inlineStr">
         <is>
-          <t>CLNE</t>
+          <t>TBRG</t>
         </is>
       </c>
       <c r="C43" s="14" t="inlineStr">
@@ -3313,7 +3313,7 @@
       </c>
       <c r="D43" s="14" t="inlineStr">
         <is>
-          <t>September 1, 2025</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="E43" s="14" t="inlineStr">
@@ -3323,54 +3323,54 @@
       </c>
       <c r="F43" s="14" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>deep</t>
         </is>
       </c>
       <c r="G43" s="14" t="inlineStr">
         <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="H43" s="14" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="I43" s="14" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="J43" s="14" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K43" s="14" t="inlineStr">
+        <is>
           <t>●</t>
         </is>
       </c>
-      <c r="H43" s="14" t="inlineStr">
-        <is>
-          <t>·</t>
-        </is>
-      </c>
-      <c r="I43" s="14" t="inlineStr">
-        <is>
-          <t>·</t>
-        </is>
-      </c>
-      <c r="J43" s="14" t="inlineStr">
-        <is>
-          <t>·</t>
-        </is>
-      </c>
-      <c r="K43" s="14" t="inlineStr">
-        <is>
-          <t>·</t>
-        </is>
-      </c>
       <c r="L43" s="14" t="inlineStr">
         <is>
-          <t>forced-creditor overhang</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M43" s="14" t="inlineStr">
         <is>
-          <t>filer emerged September 1, 2025 (~11mo ago) — live forced-seller</t>
+          <t>filer emerged 2020 (~73mo ago) — overhang likely cleared; EBIT/E</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="9" t="inlineStr">
         <is>
-          <t>Smart Sand, Inc.</t>
+          <t>Clean Energy Fuels Corp.</t>
         </is>
       </c>
       <c r="B44" s="11" t="inlineStr">
         <is>
-          <t>SND</t>
+          <t>CLNE</t>
         </is>
       </c>
       <c r="C44" s="11" t="inlineStr">
@@ -3380,7 +3380,7 @@
       </c>
       <c r="D44" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>September 1, 2025</t>
         </is>
       </c>
       <c r="E44" s="11" t="inlineStr">
@@ -3395,14 +3395,14 @@
       </c>
       <c r="G44" s="11" t="inlineStr">
         <is>
+          <t>●</t>
+        </is>
+      </c>
+      <c r="H44" s="11" t="inlineStr">
+        <is>
           <t>·</t>
         </is>
       </c>
-      <c r="H44" s="11" t="inlineStr">
-        <is>
-          <t>●</t>
-        </is>
-      </c>
       <c r="I44" s="11" t="inlineStr">
         <is>
           <t>·</t>
@@ -3420,24 +3420,24 @@
       </c>
       <c r="L44" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>forced-creditor overhang</t>
         </is>
       </c>
       <c r="M44" s="11" t="inlineStr">
         <is>
-          <t>net cash balance sheet</t>
+          <t>filer emerged September 1, 2025 (~11mo ago) — live forced-seller</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="12" t="inlineStr">
         <is>
-          <t>Sila Realty Trust, Inc.</t>
+          <t>Smart Sand, Inc.</t>
         </is>
       </c>
       <c r="B45" s="14" t="inlineStr">
         <is>
-          <t>SILA</t>
+          <t>SND</t>
         </is>
       </c>
       <c r="C45" s="14" t="inlineStr">
@@ -3447,7 +3447,7 @@
       </c>
       <c r="D45" s="14" t="inlineStr">
         <is>
-          <t>February 16, 2024</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E45" s="14" t="inlineStr">
@@ -3457,7 +3457,7 @@
       </c>
       <c r="F45" s="14" t="inlineStr">
         <is>
-          <t>deep</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="G45" s="14" t="inlineStr">
@@ -3467,24 +3467,24 @@
       </c>
       <c r="H45" s="14" t="inlineStr">
         <is>
+          <t>●</t>
+        </is>
+      </c>
+      <c r="I45" s="14" t="inlineStr">
+        <is>
           <t>·</t>
         </is>
       </c>
-      <c r="I45" s="14" t="inlineStr">
+      <c r="J45" s="14" t="inlineStr">
         <is>
           <t>·</t>
         </is>
       </c>
-      <c r="J45" s="14" t="inlineStr">
+      <c r="K45" s="14" t="inlineStr">
         <is>
           <t>·</t>
         </is>
       </c>
-      <c r="K45" s="14" t="inlineStr">
-        <is>
-          <t>●</t>
-        </is>
-      </c>
       <c r="L45" s="14" t="inlineStr">
         <is>
           <t>—</t>
@@ -3492,19 +3492,19 @@
       </c>
       <c r="M45" s="14" t="inlineStr">
         <is>
-          <t>filer emerged February 16, 2024 (~29mo ago) — overhang likely cl</t>
+          <t>net cash balance sheet</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="9" t="inlineStr">
         <is>
-          <t>CLOVER HEALTH INVESTMENTS, COR</t>
+          <t>Sila Realty Trust, Inc.</t>
         </is>
       </c>
       <c r="B46" s="11" t="inlineStr">
         <is>
-          <t>CLOV</t>
+          <t>SILA</t>
         </is>
       </c>
       <c r="C46" s="11" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="D46" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>February 16, 2024</t>
         </is>
       </c>
       <c r="E46" s="11" t="inlineStr">
@@ -3534,24 +3534,24 @@
       </c>
       <c r="H46" s="11" t="inlineStr">
         <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="I46" s="11" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="J46" s="11" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K46" s="11" t="inlineStr">
+        <is>
           <t>●</t>
         </is>
       </c>
-      <c r="I46" s="11" t="inlineStr">
-        <is>
-          <t>·</t>
-        </is>
-      </c>
-      <c r="J46" s="11" t="inlineStr">
-        <is>
-          <t>·</t>
-        </is>
-      </c>
-      <c r="K46" s="11" t="inlineStr">
-        <is>
-          <t>·</t>
-        </is>
-      </c>
       <c r="L46" s="11" t="inlineStr">
         <is>
           <t>—</t>
@@ -3559,19 +3559,19 @@
       </c>
       <c r="M46" s="11" t="inlineStr">
         <is>
-          <t>net cash balance sheet</t>
+          <t>filer emerged February 16, 2024 (~29mo ago) — overhang likely cl</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="12" t="inlineStr">
         <is>
-          <t>Sable Offshore Corp.</t>
+          <t>CLOVER HEALTH INVESTMENTS, COR</t>
         </is>
       </c>
       <c r="B47" s="14" t="inlineStr">
         <is>
-          <t>SOC</t>
+          <t>CLOV</t>
         </is>
       </c>
       <c r="C47" s="14" t="inlineStr">
@@ -3633,12 +3633,12 @@
     <row r="48">
       <c r="A48" s="9" t="inlineStr">
         <is>
-          <t>Ridgepost Capital, Inc.</t>
+          <t>Sable Offshore Corp.</t>
         </is>
       </c>
       <c r="B48" s="11" t="inlineStr">
         <is>
-          <t>RPC</t>
+          <t>SOC</t>
         </is>
       </c>
       <c r="C48" s="11" t="inlineStr">
@@ -3648,7 +3648,7 @@
       </c>
       <c r="D48" s="11" t="inlineStr">
         <is>
-          <t>May 3, 2017</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E48" s="11" t="inlineStr">
@@ -3658,7 +3658,7 @@
       </c>
       <c r="F48" s="11" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>deep</t>
         </is>
       </c>
       <c r="G48" s="11" t="inlineStr">
@@ -3668,24 +3668,24 @@
       </c>
       <c r="H48" s="11" t="inlineStr">
         <is>
+          <t>●</t>
+        </is>
+      </c>
+      <c r="I48" s="11" t="inlineStr">
+        <is>
           <t>·</t>
         </is>
       </c>
-      <c r="I48" s="11" t="inlineStr">
+      <c r="J48" s="11" t="inlineStr">
         <is>
           <t>·</t>
         </is>
       </c>
-      <c r="J48" s="11" t="inlineStr">
+      <c r="K48" s="11" t="inlineStr">
         <is>
           <t>·</t>
         </is>
       </c>
-      <c r="K48" s="11" t="inlineStr">
-        <is>
-          <t>●</t>
-        </is>
-      </c>
       <c r="L48" s="11" t="inlineStr">
         <is>
           <t>—</t>
@@ -3693,29 +3693,29 @@
       </c>
       <c r="M48" s="11" t="inlineStr">
         <is>
-          <t>filer emerged May 3, 2017 (~111mo ago) — overhang likely cleared</t>
+          <t>net cash balance sheet</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="12" t="inlineStr">
         <is>
-          <t>FERRELLGAS PARTNERS L P</t>
+          <t>Ridgepost Capital, Inc.</t>
         </is>
       </c>
       <c r="B49" s="14" t="inlineStr">
         <is>
-          <t>FGPR</t>
+          <t>RPC</t>
         </is>
       </c>
       <c r="C49" s="14" t="inlineStr">
         <is>
-          <t>~</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="D49" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>May 3, 2017</t>
         </is>
       </c>
       <c r="E49" s="14" t="inlineStr">
@@ -3725,7 +3725,7 @@
       </c>
       <c r="F49" s="14" t="inlineStr">
         <is>
-          <t>micro</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="G49" s="14" t="inlineStr">
@@ -3760,24 +3760,24 @@
       </c>
       <c r="M49" s="14" t="inlineStr">
         <is>
-          <t>EBIT/EV 3% (neutral (0-20%))</t>
+          <t>filer emerged May 3, 2017 (~111mo ago) — overhang likely cleared</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="9" t="inlineStr">
         <is>
-          <t>EchoStar CORP</t>
+          <t>Core Natural Resources</t>
         </is>
       </c>
       <c r="B50" s="11" t="inlineStr">
         <is>
-          <t>SATS</t>
+          <t>NYSE:CNR</t>
         </is>
       </c>
       <c r="C50" s="11" t="inlineStr">
         <is>
-          <t>~</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="D50" s="11" t="inlineStr">
@@ -3834,17 +3834,17 @@
     <row r="51">
       <c r="A51" s="12" t="inlineStr">
         <is>
-          <t>Fortune Brands Innovations, In</t>
+          <t>Alpha Metallurgical Resources</t>
         </is>
       </c>
       <c r="B51" s="14" t="inlineStr">
         <is>
-          <t>FBIN</t>
+          <t>NYSE:AMR</t>
         </is>
       </c>
       <c r="C51" s="14" t="inlineStr">
         <is>
-          <t>~</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="D51" s="14" t="inlineStr">
@@ -3869,24 +3869,24 @@
       </c>
       <c r="H51" s="14" t="inlineStr">
         <is>
+          <t>●</t>
+        </is>
+      </c>
+      <c r="I51" s="14" t="inlineStr">
+        <is>
           <t>·</t>
         </is>
       </c>
-      <c r="I51" s="14" t="inlineStr">
+      <c r="J51" s="14" t="inlineStr">
         <is>
           <t>·</t>
         </is>
       </c>
-      <c r="J51" s="14" t="inlineStr">
+      <c r="K51" s="14" t="inlineStr">
         <is>
           <t>·</t>
         </is>
       </c>
-      <c r="K51" s="14" t="inlineStr">
-        <is>
-          <t>●</t>
-        </is>
-      </c>
       <c r="L51" s="14" t="inlineStr">
         <is>
           <t>—</t>
@@ -3894,24 +3894,24 @@
       </c>
       <c r="M51" s="14" t="inlineStr">
         <is>
-          <t>EBIT/EV 5% (neutral (0-20%))</t>
+          <t>net cash balance sheet</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="9" t="inlineStr">
         <is>
-          <t>Beneficient</t>
+          <t>Peabody Energy</t>
         </is>
       </c>
       <c r="B52" s="11" t="inlineStr">
         <is>
-          <t>BENF</t>
+          <t>NYSE:BTU</t>
         </is>
       </c>
       <c r="C52" s="11" t="inlineStr">
         <is>
-          <t>~</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="D52" s="11" t="inlineStr">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="F52" s="11" t="inlineStr">
         <is>
-          <t>micro</t>
+          <t>deep</t>
         </is>
       </c>
       <c r="G52" s="11" t="inlineStr">
@@ -3968,12 +3968,12 @@
     <row r="53">
       <c r="A53" s="12" t="inlineStr">
         <is>
-          <t>Fifth Era Acquisition Corp I</t>
+          <t>FERRELLGAS PARTNERS L P</t>
         </is>
       </c>
       <c r="B53" s="14" t="inlineStr">
         <is>
-          <t>FERA</t>
+          <t>FGPR</t>
         </is>
       </c>
       <c r="C53" s="14" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="F53" s="14" t="inlineStr">
         <is>
-          <t>thin</t>
+          <t>micro</t>
         </is>
       </c>
       <c r="G53" s="14" t="inlineStr">
@@ -4003,24 +4003,24 @@
       </c>
       <c r="H53" s="14" t="inlineStr">
         <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="I53" s="14" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="J53" s="14" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K53" s="14" t="inlineStr">
+        <is>
           <t>●</t>
         </is>
       </c>
-      <c r="I53" s="14" t="inlineStr">
-        <is>
-          <t>·</t>
-        </is>
-      </c>
-      <c r="J53" s="14" t="inlineStr">
-        <is>
-          <t>·</t>
-        </is>
-      </c>
-      <c r="K53" s="14" t="inlineStr">
-        <is>
-          <t>·</t>
-        </is>
-      </c>
       <c r="L53" s="14" t="inlineStr">
         <is>
           <t>—</t>
@@ -4028,19 +4028,19 @@
       </c>
       <c r="M53" s="14" t="inlineStr">
         <is>
-          <t>net cash balance sheet</t>
+          <t>EBIT/EV 3% (neutral (0-20%))</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="9" t="inlineStr">
         <is>
-          <t>Xanadu Quantum Technologies Lt</t>
+          <t>EchoStar CORP</t>
         </is>
       </c>
       <c r="B54" s="11" t="inlineStr">
         <is>
-          <t>XNDU</t>
+          <t>SATS</t>
         </is>
       </c>
       <c r="C54" s="11" t="inlineStr">
@@ -4102,27 +4102,27 @@
     <row r="55">
       <c r="A55" s="12" t="inlineStr">
         <is>
-          <t>Cinemark Holdings, Inc.</t>
+          <t>Fortune Brands Innovations, In</t>
         </is>
       </c>
       <c r="B55" s="14" t="inlineStr">
         <is>
-          <t>CNK</t>
+          <t>FBIN</t>
         </is>
       </c>
       <c r="C55" s="14" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>~</t>
         </is>
       </c>
       <c r="D55" s="14" t="inlineStr">
         <is>
-          <t>August 7, 2023</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E55" s="14" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="F55" s="14" t="inlineStr">
@@ -4152,7 +4152,7 @@
       </c>
       <c r="K55" s="14" t="inlineStr">
         <is>
-          <t>·</t>
+          <t>●</t>
         </is>
       </c>
       <c r="L55" s="14" t="inlineStr">
@@ -4162,39 +4162,39 @@
       </c>
       <c r="M55" s="14" t="inlineStr">
         <is>
-          <t>filer emerged August 7, 2023 (~36mo ago) — overhang likely clear</t>
+          <t>EBIT/EV 5% (neutral (0-20%))</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="9" t="inlineStr">
         <is>
-          <t>iHeartMedia, Inc.</t>
+          <t>Beneficient</t>
         </is>
       </c>
       <c r="B56" s="11" t="inlineStr">
         <is>
-          <t>IHRT</t>
+          <t>BENF</t>
         </is>
       </c>
       <c r="C56" s="11" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>~</t>
         </is>
       </c>
       <c r="D56" s="11" t="inlineStr">
         <is>
-          <t>May 1, 2019</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E56" s="11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="F56" s="11" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>micro</t>
         </is>
       </c>
       <c r="G56" s="11" t="inlineStr">
@@ -4204,24 +4204,24 @@
       </c>
       <c r="H56" s="11" t="inlineStr">
         <is>
+          <t>●</t>
+        </is>
+      </c>
+      <c r="I56" s="11" t="inlineStr">
+        <is>
           <t>·</t>
         </is>
       </c>
-      <c r="I56" s="11" t="inlineStr">
+      <c r="J56" s="11" t="inlineStr">
         <is>
           <t>·</t>
         </is>
       </c>
-      <c r="J56" s="11" t="inlineStr">
+      <c r="K56" s="11" t="inlineStr">
         <is>
           <t>·</t>
         </is>
       </c>
-      <c r="K56" s="11" t="inlineStr">
-        <is>
-          <t>·</t>
-        </is>
-      </c>
       <c r="L56" s="11" t="inlineStr">
         <is>
           <t>—</t>
@@ -4229,39 +4229,39 @@
       </c>
       <c r="M56" s="11" t="inlineStr">
         <is>
-          <t>filer emerged May 1, 2019 (~87mo ago) — overhang likely cleared</t>
+          <t>net cash balance sheet</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="12" t="inlineStr">
         <is>
-          <t>Tronox Holdings plc</t>
+          <t>Fifth Era Acquisition Corp I</t>
         </is>
       </c>
       <c r="B57" s="14" t="inlineStr">
         <is>
-          <t>TROX</t>
+          <t>FERA</t>
         </is>
       </c>
       <c r="C57" s="14" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>~</t>
         </is>
       </c>
       <c r="D57" s="14" t="inlineStr">
         <is>
-          <t>November 30, 2010</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E57" s="14" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="F57" s="14" t="inlineStr">
         <is>
-          <t>deep</t>
+          <t>thin</t>
         </is>
       </c>
       <c r="G57" s="14" t="inlineStr">
@@ -4271,24 +4271,24 @@
       </c>
       <c r="H57" s="14" t="inlineStr">
         <is>
+          <t>●</t>
+        </is>
+      </c>
+      <c r="I57" s="14" t="inlineStr">
+        <is>
           <t>·</t>
         </is>
       </c>
-      <c r="I57" s="14" t="inlineStr">
+      <c r="J57" s="14" t="inlineStr">
         <is>
           <t>·</t>
         </is>
       </c>
-      <c r="J57" s="14" t="inlineStr">
+      <c r="K57" s="14" t="inlineStr">
         <is>
           <t>·</t>
         </is>
       </c>
-      <c r="K57" s="14" t="inlineStr">
-        <is>
-          <t>·</t>
-        </is>
-      </c>
       <c r="L57" s="14" t="inlineStr">
         <is>
           <t>—</t>
@@ -4296,24 +4296,24 @@
       </c>
       <c r="M57" s="14" t="inlineStr">
         <is>
-          <t>filer emerged November 30, 2010 (~188mo ago) — overhang likely c</t>
+          <t>net cash balance sheet</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="9" t="inlineStr">
         <is>
-          <t>GoHealth, Inc.</t>
+          <t>Xanadu Quantum Technologies Lt</t>
         </is>
       </c>
       <c r="B58" s="11" t="inlineStr">
         <is>
-          <t>GOCO</t>
+          <t>XNDU</t>
         </is>
       </c>
       <c r="C58" s="11" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>~</t>
         </is>
       </c>
       <c r="D58" s="11" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="E58" s="11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="F58" s="11" t="inlineStr">
         <is>
-          <t>micro</t>
+          <t>deep</t>
         </is>
       </c>
       <c r="G58" s="11" t="inlineStr">
@@ -4338,40 +4338,44 @@
       </c>
       <c r="H58" s="11" t="inlineStr">
         <is>
+          <t>●</t>
+        </is>
+      </c>
+      <c r="I58" s="11" t="inlineStr">
+        <is>
           <t>·</t>
         </is>
       </c>
-      <c r="I58" s="11" t="inlineStr">
+      <c r="J58" s="11" t="inlineStr">
         <is>
           <t>·</t>
         </is>
       </c>
-      <c r="J58" s="11" t="inlineStr">
+      <c r="K58" s="11" t="inlineStr">
         <is>
           <t>·</t>
         </is>
       </c>
-      <c r="K58" s="11" t="inlineStr">
-        <is>
-          <t>·</t>
-        </is>
-      </c>
       <c r="L58" s="11" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="M58" s="11" t="inlineStr"/>
+      <c r="M58" s="11" t="inlineStr">
+        <is>
+          <t>net cash balance sheet</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="12" t="inlineStr">
         <is>
-          <t>Core Scientific, Inc./tx</t>
+          <t>Cinemark Holdings, Inc.</t>
         </is>
       </c>
       <c r="B59" s="14" t="inlineStr">
         <is>
-          <t>CORZ</t>
+          <t>CNK</t>
         </is>
       </c>
       <c r="C59" s="14" t="inlineStr">
@@ -4381,7 +4385,7 @@
       </c>
       <c r="D59" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>August 7, 2023</t>
         </is>
       </c>
       <c r="E59" s="14" t="inlineStr">
@@ -4424,17 +4428,21 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M59" s="14" t="inlineStr"/>
+      <c r="M59" s="14" t="inlineStr">
+        <is>
+          <t>filer emerged August 7, 2023 (~36mo ago) — overhang likely clear</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="9" t="inlineStr">
         <is>
-          <t>Atlanta Braves Holdings, Inc.</t>
+          <t>iHeartMedia, Inc.</t>
         </is>
       </c>
       <c r="B60" s="11" t="inlineStr">
         <is>
-          <t>BATRA</t>
+          <t>IHRT</t>
         </is>
       </c>
       <c r="C60" s="11" t="inlineStr">
@@ -4444,7 +4452,7 @@
       </c>
       <c r="D60" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>May 1, 2019</t>
         </is>
       </c>
       <c r="E60" s="11" t="inlineStr">
@@ -4487,27 +4495,31 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M60" s="11" t="inlineStr"/>
+      <c r="M60" s="11" t="inlineStr">
+        <is>
+          <t>filer emerged May 1, 2019 (~87mo ago) — overhang likely cleared</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="12" t="inlineStr">
         <is>
-          <t>AMPCO PITTSBURGH CORP</t>
+          <t>Tronox Holdings plc</t>
         </is>
       </c>
       <c r="B61" s="14" t="inlineStr">
         <is>
-          <t>AP</t>
+          <t>TROX</t>
         </is>
       </c>
       <c r="C61" s="14" t="inlineStr">
         <is>
-          <t>~</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="D61" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>November 30, 2010</t>
         </is>
       </c>
       <c r="E61" s="14" t="inlineStr">
@@ -4517,160 +4529,1283 @@
       </c>
       <c r="F61" s="14" t="inlineStr">
         <is>
+          <t>deep</t>
+        </is>
+      </c>
+      <c r="G61" s="14" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="H61" s="14" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="I61" s="14" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="J61" s="14" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K61" s="14" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="L61" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M61" s="14" t="inlineStr">
+        <is>
+          <t>filer emerged November 30, 2010 (~188mo ago) — overhang likely c</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="9" t="inlineStr">
+        <is>
+          <t>GoHealth, Inc.</t>
+        </is>
+      </c>
+      <c r="B62" s="11" t="inlineStr">
+        <is>
+          <t>GOCO</t>
+        </is>
+      </c>
+      <c r="C62" s="11" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="D62" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E62" s="11" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="F62" s="11" t="inlineStr">
+        <is>
+          <t>micro</t>
+        </is>
+      </c>
+      <c r="G62" s="11" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="H62" s="11" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="I62" s="11" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="J62" s="11" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K62" s="11" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="L62" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M62" s="11" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="12" t="inlineStr">
+        <is>
+          <t>Core Scientific, Inc./tx</t>
+        </is>
+      </c>
+      <c r="B63" s="14" t="inlineStr">
+        <is>
+          <t>CORZ</t>
+        </is>
+      </c>
+      <c r="C63" s="14" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="D63" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E63" s="14" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="F63" s="14" t="inlineStr">
+        <is>
+          <t>deep</t>
+        </is>
+      </c>
+      <c r="G63" s="14" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="H63" s="14" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="I63" s="14" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="J63" s="14" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K63" s="14" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="L63" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M63" s="14" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="9" t="inlineStr">
+        <is>
+          <t>Atlanta Braves Holdings, Inc.</t>
+        </is>
+      </c>
+      <c r="B64" s="11" t="inlineStr">
+        <is>
+          <t>BATRA</t>
+        </is>
+      </c>
+      <c r="C64" s="11" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="D64" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E64" s="11" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="F64" s="11" t="inlineStr">
+        <is>
           <t>ok</t>
         </is>
       </c>
-      <c r="G61" s="14" t="inlineStr">
+      <c r="G64" s="11" t="inlineStr">
         <is>
           <t>·</t>
         </is>
       </c>
-      <c r="H61" s="14" t="inlineStr">
+      <c r="H64" s="11" t="inlineStr">
         <is>
           <t>·</t>
         </is>
       </c>
-      <c r="I61" s="14" t="inlineStr">
+      <c r="I64" s="11" t="inlineStr">
         <is>
           <t>·</t>
         </is>
       </c>
-      <c r="J61" s="14" t="inlineStr">
+      <c r="J64" s="11" t="inlineStr">
         <is>
           <t>·</t>
         </is>
       </c>
-      <c r="K61" s="14" t="inlineStr">
+      <c r="K64" s="11" t="inlineStr">
         <is>
           <t>·</t>
         </is>
       </c>
-      <c r="L61" s="14" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M61" s="14" t="inlineStr"/>
-    </row>
-    <row r="62"/>
-    <row r="63"/>
-    <row r="64">
-      <c r="A64" s="6" t="inlineStr">
-        <is>
-          <t>Set aside — filer's own emergence unconfirmed (verify; not scored, not dropped)</t>
-        </is>
-      </c>
+      <c r="L64" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M64" s="11" t="inlineStr"/>
     </row>
     <row r="65">
-      <c r="A65" s="8" t="inlineStr">
-        <is>
-          <t>Name</t>
-        </is>
-      </c>
-      <c r="B65" s="8" t="inlineStr">
-        <is>
-          <t>Ticker</t>
-        </is>
-      </c>
-      <c r="C65" s="8" t="inlineStr">
-        <is>
-          <t>Filing context</t>
-        </is>
-      </c>
+      <c r="A65" s="12" t="inlineStr">
+        <is>
+          <t>PAL Holdings (Philippine Airli</t>
+        </is>
+      </c>
+      <c r="B65" s="14" t="inlineStr">
+        <is>
+          <t>PSE:PAL</t>
+        </is>
+      </c>
+      <c r="C65" s="14" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="D65" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E65" s="14" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="F65" s="14" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="G65" s="14" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="H65" s="14" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="I65" s="14" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="J65" s="14" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K65" s="14" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="L65" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M65" s="14" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="9" t="inlineStr">
         <is>
-          <t>OCTAVE SPECIALTY GROUP INC</t>
+          <t>AMPCO PITTSBURGH CORP</t>
         </is>
       </c>
       <c r="B66" s="11" t="inlineStr">
         <is>
-          <t>OSG</t>
+          <t>AP</t>
         </is>
       </c>
       <c r="C66" s="11" t="inlineStr">
         <is>
-          <t>(bankruptcy reference is a non-filer possessive)</t>
-        </is>
-      </c>
+          <t>~</t>
+        </is>
+      </c>
+      <c r="D66" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E66" s="11" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="F66" s="11" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="G66" s="11" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="H66" s="11" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="I66" s="11" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="J66" s="11" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K66" s="11" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="L66" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M66" s="11" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="12" t="inlineStr">
         <is>
-          <t>EASTMAN CHEMICAL CO</t>
+          <t>McDermott International</t>
         </is>
       </c>
       <c r="B67" s="14" t="inlineStr">
         <is>
-          <t>EMN</t>
+          <t>OTC:MCDIF</t>
         </is>
       </c>
       <c r="C67" s="14" t="inlineStr">
         <is>
-          <t>(bankruptcy reference is a non-filer possessive)</t>
+          <t>~</t>
+        </is>
+      </c>
+      <c r="D67" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E67" s="14" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="F67" s="14" t="inlineStr">
+        <is>
+          <t>thin</t>
+        </is>
+      </c>
+      <c r="G67" s="14" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="H67" s="14" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="I67" s="14" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="J67" s="14" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K67" s="14" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="L67" s="14" t="inlineStr">
+        <is>
+          <t>hand-curated post-reorg</t>
+        </is>
+      </c>
+      <c r="M67" s="14" t="inlineStr">
+        <is>
+          <t>universe.md Bucket C (OTC/foreign; SEC financials unavailable —</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="9" t="inlineStr">
         <is>
-          <t>PG&amp;E Corp</t>
+          <t>Orpea / Emeis</t>
         </is>
       </c>
       <c r="B68" s="11" t="inlineStr">
         <is>
-          <t>PCG</t>
+          <t>EPA:EMEIS</t>
         </is>
       </c>
       <c r="C68" s="11" t="inlineStr">
         <is>
-          <t>(bankruptcy reference is a non-filer possessive)</t>
+          <t>~</t>
+        </is>
+      </c>
+      <c r="D68" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E68" s="11" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="F68" s="11" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="G68" s="11" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="H68" s="11" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="I68" s="11" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="J68" s="11" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K68" s="11" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="L68" s="11" t="inlineStr">
+        <is>
+          <t>hand-curated post-reorg</t>
+        </is>
+      </c>
+      <c r="M68" s="11" t="inlineStr">
+        <is>
+          <t>universe.md Bucket C (OTC/foreign; SEC financials unavailable —</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="12" t="inlineStr">
         <is>
-          <t>National CineMedia, Inc.</t>
+          <t>Vallourec</t>
         </is>
       </c>
       <c r="B69" s="14" t="inlineStr">
         <is>
-          <t>NCMI</t>
+          <t>EPA:VK</t>
         </is>
       </c>
       <c r="C69" s="14" t="inlineStr">
         <is>
-          <t>(bankruptcy reference is a non-filer possessive)</t>
+          <t>~</t>
+        </is>
+      </c>
+      <c r="D69" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E69" s="14" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="F69" s="14" t="inlineStr">
+        <is>
+          <t>deep</t>
+        </is>
+      </c>
+      <c r="G69" s="14" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="H69" s="14" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="I69" s="14" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="J69" s="14" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K69" s="14" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="L69" s="14" t="inlineStr">
+        <is>
+          <t>hand-curated post-reorg</t>
+        </is>
+      </c>
+      <c r="M69" s="14" t="inlineStr">
+        <is>
+          <t>universe.md Bucket C (OTC/foreign; SEC financials unavailable —</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="9" t="inlineStr">
         <is>
-          <t>MODIV INDUSTRIAL, INC.</t>
+          <t>Solocal Group</t>
         </is>
       </c>
       <c r="B70" s="11" t="inlineStr">
         <is>
-          <t>MDV</t>
+          <t>EPA:LOCAL</t>
         </is>
       </c>
       <c r="C70" s="11" t="inlineStr">
         <is>
-          <t>(bankruptcy reference is a non-filer possessive)</t>
+          <t>~</t>
+        </is>
+      </c>
+      <c r="D70" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E70" s="11" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="F70" s="11" t="inlineStr">
+        <is>
+          <t>micro</t>
+        </is>
+      </c>
+      <c r="G70" s="11" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="H70" s="11" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="I70" s="11" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="J70" s="11" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K70" s="11" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="L70" s="11" t="inlineStr">
+        <is>
+          <t>hand-curated post-reorg</t>
+        </is>
+      </c>
+      <c r="M70" s="11" t="inlineStr">
+        <is>
+          <t>universe.md Bucket C (OTC/foreign; SEC financials unavailable —</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="12" t="inlineStr">
         <is>
+          <t>Intrum</t>
+        </is>
+      </c>
+      <c r="B71" s="14" t="inlineStr">
+        <is>
+          <t>ST:INTRUM</t>
+        </is>
+      </c>
+      <c r="C71" s="14" t="inlineStr">
+        <is>
+          <t>~</t>
+        </is>
+      </c>
+      <c r="D71" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E71" s="14" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="F71" s="14" t="inlineStr">
+        <is>
+          <t>deep</t>
+        </is>
+      </c>
+      <c r="G71" s="14" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="H71" s="14" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="I71" s="14" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="J71" s="14" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K71" s="14" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="L71" s="14" t="inlineStr">
+        <is>
+          <t>hand-curated post-reorg</t>
+        </is>
+      </c>
+      <c r="M71" s="14" t="inlineStr">
+        <is>
+          <t>universe.md Bucket C (OTC/foreign; SEC financials unavailable —</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="9" t="inlineStr">
+        <is>
+          <t>Norwegian Air Shuttle</t>
+        </is>
+      </c>
+      <c r="B72" s="11" t="inlineStr">
+        <is>
+          <t>OSL:NAS</t>
+        </is>
+      </c>
+      <c r="C72" s="11" t="inlineStr">
+        <is>
+          <t>~</t>
+        </is>
+      </c>
+      <c r="D72" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E72" s="11" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="F72" s="11" t="inlineStr">
+        <is>
+          <t>deep</t>
+        </is>
+      </c>
+      <c r="G72" s="11" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="H72" s="11" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="I72" s="11" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="J72" s="11" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K72" s="11" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="L72" s="11" t="inlineStr">
+        <is>
+          <t>hand-curated post-reorg</t>
+        </is>
+      </c>
+      <c r="M72" s="11" t="inlineStr">
+        <is>
+          <t>universe.md Bucket C (OTC/foreign; SEC financials unavailable —</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="12" t="inlineStr">
+        <is>
+          <t>HMM (Hyundai Merchant Marine)</t>
+        </is>
+      </c>
+      <c r="B73" s="14" t="inlineStr">
+        <is>
+          <t>KRX:011200</t>
+        </is>
+      </c>
+      <c r="C73" s="14" t="inlineStr">
+        <is>
+          <t>~</t>
+        </is>
+      </c>
+      <c r="D73" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E73" s="14" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="F73" s="14" t="inlineStr">
+        <is>
+          <t>deep</t>
+        </is>
+      </c>
+      <c r="G73" s="14" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="H73" s="14" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="I73" s="14" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="J73" s="14" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K73" s="14" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="L73" s="14" t="inlineStr">
+        <is>
+          <t>hand-curated post-reorg</t>
+        </is>
+      </c>
+      <c r="M73" s="14" t="inlineStr">
+        <is>
+          <t>universe.md Bucket C (OTC/foreign; SEC financials unavailable —</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="9" t="inlineStr">
+        <is>
+          <t>Sri Rejeki Isman (Sritex)</t>
+        </is>
+      </c>
+      <c r="B74" s="11" t="inlineStr">
+        <is>
+          <t>IDX:SRIL</t>
+        </is>
+      </c>
+      <c r="C74" s="11" t="inlineStr">
+        <is>
+          <t>~</t>
+        </is>
+      </c>
+      <c r="D74" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E74" s="11" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="F74" s="11" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="G74" s="11" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="H74" s="11" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="I74" s="11" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="J74" s="11" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K74" s="11" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="L74" s="11" t="inlineStr">
+        <is>
+          <t>hand-curated post-reorg</t>
+        </is>
+      </c>
+      <c r="M74" s="11" t="inlineStr">
+        <is>
+          <t>universe.md Bucket C (OTC/foreign; SEC financials unavailable —</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="12" t="inlineStr">
+        <is>
+          <t>AirAsia X</t>
+        </is>
+      </c>
+      <c r="B75" s="14" t="inlineStr">
+        <is>
+          <t>KLSE:5238</t>
+        </is>
+      </c>
+      <c r="C75" s="14" t="inlineStr">
+        <is>
+          <t>~</t>
+        </is>
+      </c>
+      <c r="D75" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E75" s="14" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="F75" s="14" t="inlineStr">
+        <is>
+          <t>deep</t>
+        </is>
+      </c>
+      <c r="G75" s="14" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="H75" s="14" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="I75" s="14" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="J75" s="14" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K75" s="14" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="L75" s="14" t="inlineStr">
+        <is>
+          <t>hand-curated post-reorg</t>
+        </is>
+      </c>
+      <c r="M75" s="14" t="inlineStr">
+        <is>
+          <t>universe.md Bucket C (OTC/foreign; SEC financials unavailable —</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="9" t="inlineStr">
+        <is>
+          <t>Lupatech</t>
+        </is>
+      </c>
+      <c r="B76" s="11" t="inlineStr">
+        <is>
+          <t>B3:LUPA3</t>
+        </is>
+      </c>
+      <c r="C76" s="11" t="inlineStr">
+        <is>
+          <t>~</t>
+        </is>
+      </c>
+      <c r="D76" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E76" s="11" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="F76" s="11" t="inlineStr">
+        <is>
+          <t>micro</t>
+        </is>
+      </c>
+      <c r="G76" s="11" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="H76" s="11" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="I76" s="11" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="J76" s="11" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K76" s="11" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="L76" s="11" t="inlineStr">
+        <is>
+          <t>hand-curated post-reorg</t>
+        </is>
+      </c>
+      <c r="M76" s="11" t="inlineStr">
+        <is>
+          <t>universe.md Bucket C (OTC/foreign; SEC financials unavailable —</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="12" t="inlineStr">
+        <is>
+          <t>Drake &amp; Scull</t>
+        </is>
+      </c>
+      <c r="B77" s="14" t="inlineStr">
+        <is>
+          <t>DFM:DSI</t>
+        </is>
+      </c>
+      <c r="C77" s="14" t="inlineStr">
+        <is>
+          <t>~</t>
+        </is>
+      </c>
+      <c r="D77" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E77" s="14" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="F77" s="14" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="G77" s="14" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="H77" s="14" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="I77" s="14" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="J77" s="14" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K77" s="14" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="L77" s="14" t="inlineStr">
+        <is>
+          <t>hand-curated post-reorg</t>
+        </is>
+      </c>
+      <c r="M77" s="14" t="inlineStr">
+        <is>
+          <t>universe.md Bucket C (OTC/foreign; SEC financials unavailable —</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="9" t="inlineStr">
+        <is>
+          <t>OI SA</t>
+        </is>
+      </c>
+      <c r="B78" s="11" t="inlineStr">
+        <is>
+          <t>B3:OIBR3</t>
+        </is>
+      </c>
+      <c r="C78" s="11" t="inlineStr">
+        <is>
+          <t>~</t>
+        </is>
+      </c>
+      <c r="D78" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E78" s="11" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="F78" s="11" t="inlineStr">
+        <is>
+          <t>micro</t>
+        </is>
+      </c>
+      <c r="G78" s="11" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="H78" s="11" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="I78" s="11" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="J78" s="11" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K78" s="11" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="L78" s="11" t="inlineStr">
+        <is>
+          <t>hand-curated post-reorg</t>
+        </is>
+      </c>
+      <c r="M78" s="11" t="inlineStr">
+        <is>
+          <t>universe.md Bucket C (OTC/foreign; SEC financials unavailable —</t>
+        </is>
+      </c>
+    </row>
+    <row r="79"/>
+    <row r="80"/>
+    <row r="81">
+      <c r="A81" s="6" t="inlineStr">
+        <is>
+          <t>Set aside — filer's own emergence unconfirmed (verify; not scored, not dropped)</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="8" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B82" s="8" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
+      <c r="C82" s="8" t="inlineStr">
+        <is>
+          <t>Filing context</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="9" t="inlineStr">
+        <is>
+          <t>OCTAVE SPECIALTY GROUP INC</t>
+        </is>
+      </c>
+      <c r="B83" s="11" t="inlineStr">
+        <is>
+          <t>OSG</t>
+        </is>
+      </c>
+      <c r="C83" s="11" t="inlineStr">
+        <is>
+          <t>(bankruptcy reference is a non-filer possessive)</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="12" t="inlineStr">
+        <is>
+          <t>EASTMAN CHEMICAL CO</t>
+        </is>
+      </c>
+      <c r="B84" s="14" t="inlineStr">
+        <is>
+          <t>EMN</t>
+        </is>
+      </c>
+      <c r="C84" s="14" t="inlineStr">
+        <is>
+          <t>(bankruptcy reference is a non-filer possessive)</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="9" t="inlineStr">
+        <is>
+          <t>PG&amp;E Corp</t>
+        </is>
+      </c>
+      <c r="B85" s="11" t="inlineStr">
+        <is>
+          <t>PCG</t>
+        </is>
+      </c>
+      <c r="C85" s="11" t="inlineStr">
+        <is>
+          <t>(bankruptcy reference is a non-filer possessive)</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="12" t="inlineStr">
+        <is>
+          <t>National CineMedia, Inc.</t>
+        </is>
+      </c>
+      <c r="B86" s="14" t="inlineStr">
+        <is>
+          <t>NCMI</t>
+        </is>
+      </c>
+      <c r="C86" s="14" t="inlineStr">
+        <is>
+          <t>(bankruptcy reference is a non-filer possessive)</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="9" t="inlineStr">
+        <is>
+          <t>MODIV INDUSTRIAL, INC.</t>
+        </is>
+      </c>
+      <c r="B87" s="11" t="inlineStr">
+        <is>
+          <t>MDV</t>
+        </is>
+      </c>
+      <c r="C87" s="11" t="inlineStr">
+        <is>
+          <t>(bankruptcy reference is a non-filer possessive)</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="12" t="inlineStr">
+        <is>
           <t>LibreMax Asset-Backed Income F</t>
         </is>
       </c>
-      <c r="B71" s="14" t="inlineStr"/>
-      <c r="C71" s="14" t="inlineStr">
+      <c r="B88" s="14" t="inlineStr"/>
+      <c r="C88" s="14" t="inlineStr">
         <is>
           <t>(bankruptcy reference is a non-filer possessive)</t>
         </is>
